--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2035B6-269B-447A-A6B3-4E94191D2136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA1C4CB-553C-44FB-AB3F-B1C1864ECDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="373">
   <si>
     <t>Canal</t>
   </si>
@@ -235,18 +235,6 @@
     <t>Hidalgo</t>
   </si>
   <si>
-    <t>Huejutla</t>
-  </si>
-  <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Opinión</t>
-  </si>
-  <si>
-    <t>Columnista</t>
-  </si>
-  <si>
     <t>Reconstrucción de escuela</t>
   </si>
   <si>
@@ -283,18 +271,9 @@
     <t>VAN A DEMOLER PRIMARIA EN TULANCINGO; EDIFICARÁN OTRA</t>
   </si>
   <si>
-    <t>Francisco Bautista</t>
-  </si>
-  <si>
     <t>Veida Martínez Miranda</t>
   </si>
   <si>
-    <t>Tepeji del Río</t>
-  </si>
-  <si>
-    <t>Paquete de apoyos escolares</t>
-  </si>
-  <si>
     <t>Natividad Castrejón Valdez</t>
   </si>
   <si>
@@ -304,913 +283,889 @@
     <t>Tula</t>
   </si>
   <si>
-    <t>Reportaje</t>
-  </si>
-  <si>
     <t>Salomón Hernández</t>
   </si>
   <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
     <t>SEPH, Ayuntamiento</t>
   </si>
   <si>
     <t>PGJEH, Ayuntamiento</t>
   </si>
   <si>
-    <t>SEPH, IHE, Gobernador, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Relleno Sanitario</t>
-  </si>
-  <si>
     <t>Semarnath</t>
   </si>
   <si>
     <t>Fiestas Patrias</t>
   </si>
   <si>
-    <t>Socorro Ávila</t>
-  </si>
-  <si>
-    <t>Teodoro Santos</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Julio Menchaca Salazar, Tania Valdez Cuéllar, Nancy Adriana León Vite, Josefina Serrano Bautista, Ofelia Ramírez Hernández</t>
-  </si>
-  <si>
-    <t>Inseguridad Carretera</t>
-  </si>
-  <si>
     <t>Berenice Gamboa</t>
   </si>
   <si>
-    <t>Santiago Tulantepec</t>
-  </si>
-  <si>
-    <t>Proceso Por Feminicidio</t>
-  </si>
-  <si>
-    <t>Serán 5 mil elementos en operativo patrio</t>
-  </si>
-  <si>
-    <t>Con motivo de los festejos alusivos al Grito de Independencia, el secretario de Seguridad Pública, Salvador Cruz, informó que cinco mil elementos de seguridad estarán desplegados en Hidalgo, principalmente en Plaza Juárez de Pachuca.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública desplegará a 5 mil efectivos en Hidalgo para resguardar las celebraciones del Grito de Independencia en Plaza Juárez.</t>
-  </si>
-  <si>
     <t>SSPH</t>
   </si>
   <si>
-    <t>SSPH, Segobh, Ayuntamientos</t>
-  </si>
-  <si>
     <t>Salvador Cruz Neri</t>
   </si>
   <si>
-    <t>Irrumpen estudiantes de El Mexe en el evento</t>
-  </si>
-  <si>
-    <t>Estudiantes de la Escuela Normal Rural Luis Villa-Real El Mexe irrumpieron en el evento de la presidenta Claudia Sheinbaum en Pachuca para exigir el esclarecimiento de la muerte de un compañero originario de Huehuetla y plantear demandas educativas.</t>
-  </si>
-  <si>
     <t>El Mexe</t>
   </si>
   <si>
-    <t>Normalistas de El Mexe irrumpieron durante el evento de Claudia Sheinbaum en el recinto ferial para exigir justicia por el fallecimiento de un estudiante y atención a demandas escolares.</t>
-  </si>
-  <si>
     <t>Blanca Soriano</t>
   </si>
   <si>
-    <t>SEPH, Segobh, Gobernación, Presidencia, PGJEH</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna, Luciano Cornejo, Abraham Mendoza Zenteno</t>
-  </si>
-  <si>
-    <t>Hacen falta traductores indígenas</t>
-  </si>
-  <si>
-    <t>El gobernador indígena del estado de Hidalgo, Cuauhtémoc Lucio Ramírez Alonso, advirtió sobre la falta de traductores suficientes en lenguas originarias (náhuatl, otomí y tepehua) para garantizar el acceso a la justicia en los tribunales de Tula y en la entidad.</t>
-  </si>
-  <si>
-    <t>Apoyo a pueblos originarios</t>
-  </si>
-  <si>
-    <t>El gobernador indígena de Hidalgo señaló la escasez de intérpretes capacitados en lenguas maternas para atender procesos judiciales en la región de Tula y el estado.</t>
-  </si>
-  <si>
     <t>César Martínez</t>
   </si>
   <si>
     <t>Gobernador</t>
   </si>
   <si>
-    <t>Gobernador, PGJEH, Planeación, CEDSPI</t>
-  </si>
-  <si>
-    <t>Cuauhtémoc Lucio Ramírez Alonso</t>
-  </si>
-  <si>
-    <t>Gobierno entrega uniformes, útiles y calzado a estudiantes de Tula-Tepeji</t>
-  </si>
-  <si>
-    <t>El titular del Instituto Hidalguense de Educación, Natividad Castrejón, encabezó en Tepeji del Río, Tula de Allende y Atotonilco de Tula la distribución de útiles, zapatos, libros y equipamiento de cómputo para apoyar la economía familiar y la permanencia escolar.</t>
-  </si>
-  <si>
-    <t>Autoridades de la SEPH y del IHE entregaron paquetes de útiles, uniformes y calzado a estudiantes de nivel básico en planteles de Tepeji, Tula y Atotonilco de Tula.</t>
-  </si>
-  <si>
-    <t>Más de 5 mil policías participarán en el operativo de fiestas patrias</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo desplegará más de 5 mil efectivos policiales en los 84 municipios para resguardar las celebraciones del 15 de septiembre, reforzando la vigilancia en la Plaza Juárez de Pachuca e imponiendo mano dura contra tiros al aire.</t>
-  </si>
-  <si>
-    <t>La SSPH desplegará a 5 mil agentes de seguridad en la entidad para resguardar la ceremonia del Grito de Independencia en Plaza Juárez y el resto de los municipios.</t>
-  </si>
-  <si>
     <t>Dulce Castillo</t>
   </si>
   <si>
-    <t>SSPH, Segobh, PC, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Disminuye actividad charra en la entidad</t>
-  </si>
-  <si>
-    <t>El número de asociaciones charras activas en Hidalgo disminuyó de 90 a entre 65 y 75 agrupaciones debido a los crecientes costos del deporte y la escasez de ganado, expresando la directiva de la Asociación de Charros de Pachuca su respaldo a la tauromaquia.</t>
-  </si>
-  <si>
     <t>Día del Charro</t>
   </si>
   <si>
-    <t>Reportaje sobre la reducción del número de agrupaciones charras en Hidalgo ante el encarecimiento de insumos y ganado, así como su respaldo gremial a la fiesta brava.</t>
-  </si>
-  <si>
-    <t>Cultura, Presidencia</t>
-  </si>
-  <si>
-    <t>Gerardo Anselmo Mejía Arteaga</t>
-  </si>
-  <si>
-    <t>Participa IHE en jornada contra el maltrato infantil</t>
-  </si>
-  <si>
-    <t>El IHE llevó a cabo la Segunda Jornada Nacional de Concientización sobre el Abuso Sexual y Maltrato Infantil en Mineral de la Reforma, acercando pláticas de seguridad digital y prevención de violencia a familias y docentes.</t>
-  </si>
-  <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Maltrato infantil</t>
-  </si>
-  <si>
-    <t>Autoridades educativas y de seguridad impartieron talleres de cibernética y prevención del maltrato infantil a la comunidad escolar de Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>SEPH, IHE, SSH, PGJEH, CDHEH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Nancy Adriana León Vite, Claudia Huerta Ruiz</t>
-  </si>
-  <si>
-    <t>En pausa, 50 carpetas por delitos electorales del proceso 2023-2024</t>
-  </si>
-  <si>
-    <t>Rumbo al proceso electoral 2023-2024, se mantienen en curso 50 carpetas de investigación por diversas violaciones a la ley, reconoció la fiscal especializada en Delitos Electorales, Diana Jeanethe Rodríguez López, señalando que la mayoría derivan de violencia a través de redes sociales o perfiles falsos.</t>
-  </si>
-  <si>
-    <t>Delitos Electorales</t>
-  </si>
-  <si>
-    <t>La fiscal especializada en Delitos Electorales reportó que existen cerca de 50 carpetas de investigación pendientes del proceso electoral 2023-2024 por diversas inconsistencias.</t>
-  </si>
-  <si>
-    <t>PGJEH, IEEH</t>
-  </si>
-  <si>
-    <t>Diana Jeanethe Rodríguez López</t>
-  </si>
-  <si>
-    <t>Banca Multiva, lista para financiar proyectos</t>
-  </si>
-  <si>
-    <t>La conversación sobre infraestructura en el país entra en una nueva etapa: una vez definidos los proyectos estratégicos, la atención se centra en acelerar su materialización, señalaron expertos de Multiva. La directiva Tamara Caballero destacó la viabilidad de financiar proyectos clave como el tren AIFA-Pachuca y el plan hídrico del Valle del Mezquital.</t>
-  </si>
-  <si>
-    <t>Atracción De Inversiones</t>
-  </si>
-  <si>
-    <t>Banca Multiva expresó su interés en financiar proyectos estratégicos de infraestructura en Hidalgo, destacando la certidumbre jurídica y la coordinación con el gobierno estatal.</t>
-  </si>
-  <si>
-    <t>Gobernador, Sipdus, Presidencia</t>
-  </si>
-  <si>
-    <t>Tamara Caballero, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Detienen a un hombre acusado de asalto</t>
-  </si>
-  <si>
-    <t>Un hombre de 26 años fue detenido en Tepeapulco por su presunta participación en al menos siete asaltos a tiendas de conveniencia cometidos en Hidalgo y el Estado de México, de acuerdo con la SSPH.</t>
-  </si>
-  <si>
-    <t>Tepeapulco</t>
-  </si>
-  <si>
-    <t>Aprehensión</t>
-  </si>
-  <si>
-    <t>Elementos de la SSPH detuvieron en Tepeapulco a un sujeto de 26 años relacionado con al menos siete asaltos a tiendas de conveniencia en Hidalgo y Edomex.</t>
-  </si>
-  <si>
-    <t>SSPH, PGJEH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Reportan 22 casos de gusano barrenador</t>
-  </si>
-  <si>
-    <t>Entre enero y agosto de este año se han registrado en Hidalgo 22 casos de gusano barrenador del ganado en humanos, de los cuales siete han sido en mujeres y 15 en hombres en 20 municipios del estado. De acuerdo con la Secretaría de Salud del estado (SSH) de los 22 casos 18 ya fueron dados de alta, dos están en seguimiento y dos más fallecieron.</t>
-  </si>
-  <si>
-    <t>Gusano barrenador</t>
-  </si>
-  <si>
-    <t>La SSH reportó acumulado de 22 casos de gusano barrenador en humanos en 20 municipios de Hidalgo, registrando dos fallecimientos y 18 altas médicas.</t>
-  </si>
-  <si>
-    <t>SSH, Saderh, Presidencia</t>
-  </si>
-  <si>
-    <t>Empresarios celebran los proyectos de la federación</t>
-  </si>
-  <si>
-    <t>El director general de Canacope Servytur Pachuca, Carlos Gamiño Ríos, celebró que la federación mantenga un fuerte interés en Hidalgo a través de proyectos de seguridad, infraestructura industrial y el tren México-Pachuca, lo cual detonará la derrama económica en la zona metropolitana.</t>
-  </si>
-  <si>
-    <t>La Canacope Servytur Pachuca reconoció la atención del gobierno federal en la atracción de inversiones, reactivación de parques industriales y conectividad con el tren México-Pachuca.</t>
-  </si>
-  <si>
     <t>Lourdes Naranjo</t>
   </si>
   <si>
     <t>Sedeco</t>
   </si>
   <si>
-    <t>Sedeco, Presidencia</t>
-  </si>
-  <si>
-    <t>Carlos Gamiño Ríos, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>Vigilarán fiestas 5 mil uniformados</t>
-  </si>
-  <si>
-    <t>El secretario de Seguridad Pública de Hidalgo, Salvador Cruz Neri, informó que alrededor de 5 mil elementos participarán en el operativo con motivo de las Fiestas Patrias en todo el estado, reforzando la vigilancia en la Plaza Juárez de Pachuca e imponiendo mano dura contra las detonaciones de arma de fuego al aire.</t>
-  </si>
-  <si>
-    <t>La SSPH desplegará a 5 mil efectivos de seguridad para resguardar las celebraciones del Grito de Independencia en los 84 municipios, implementando operativos preventivos contra disparos al aire.</t>
-  </si>
-  <si>
     <t>Ricardo Calleja</t>
   </si>
   <si>
-    <t>Plantean tener reuniones tras homicidio de un estudiante</t>
-  </si>
-  <si>
-    <t>Tras la protesta de estudiantes de la Normal Rural El Mexe por el homicidio de un compañero, el procurador Francisco Fernández Hasbún acordó reunirse con familiares de la víctima para informar sobre el avance de la carpeta de investigación, mientras que Gobernación federal anunció mesas de trabajo sobre los predios de la institución.</t>
-  </si>
-  <si>
-    <t>Francisco I. Madero</t>
-  </si>
-  <si>
-    <t>Autoridades de la PGJEH y la Segob entablaron diálogo con estudiantes y familiares del alumno de El Mexe fallecido para dar seguimiento a las investigaciones y solicitudes territoriales.</t>
-  </si>
-  <si>
-    <t>PGJEH, Segobh, SEPH</t>
-  </si>
-  <si>
-    <t>Francisco Fernández Hasbun, Luciano Cornejo Barrera</t>
-  </si>
-  <si>
-    <t>Asaltan dos negocios en Tizayuca el fin de semana</t>
-  </si>
-  <si>
-    <t>Dos establecimientos comerciales fueron asaltados por sujetos armados a bordo de motocicletas en Tizayuca. En el caso de Haciendas de Tizayuca, el propietario forcejeó con el delincuente y el arma de fuego se encasquilló, permitiendo que las clientas se resguardaran.</t>
-  </si>
-  <si>
-    <t>Asalto A Comercio</t>
-  </si>
-  <si>
-    <t>Comercios de Tizayuca fueron blanco de asaltos violentos por sujetos armados en motocicleta en Haciendas de Tizayuca y el fraccionamiento Héroes de Tizayuca.</t>
-  </si>
-  <si>
-    <t>Javier Quezada</t>
-  </si>
-  <si>
-    <t>SSPH, Ayuntamiento, PGJEH</t>
-  </si>
-  <si>
-    <t>Atacan con una bomba casera auto de docente</t>
-  </si>
-  <si>
-    <t>El profesor y activista Onésimo Pérez Lara denunció que sujetos desconocidos lanzaron un artefacto explosivo casero con gasolina dentro de su camioneta estacionada frente a su domicilio en Tlanchinol, provocando daños materiales por fuego.</t>
-  </si>
-  <si>
     <t>Tlanchinol</t>
   </si>
   <si>
     <t>Ataque Armado</t>
   </si>
   <si>
-    <t>El profesor y activista Onésimo Pérez Lara denunció un atentado con bomba casera contra su camioneta en Tlanchinol, atribuyendo la agresión a su labor comunitaria.</t>
-  </si>
-  <si>
-    <t>PGJEH, SSPH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Onésimo Pérez Lara</t>
-  </si>
-  <si>
-    <t>2 mil libros de la Fundación Elena Poniatowska a escuelas de Hidalgo</t>
-  </si>
-  <si>
-    <t>Con el objetivo de acercar materiales de lectura a las comunidades escolares y fomentar el hábito de la lectura entre la niñez hidalguense, la Fundación Elena Poniatowska Amor, S.C. realizó la donación de 2 mil libros a la Secretaría de Educación Pública de Hidalgo (SEPH), encabezada por Natividad Castrejón Valdez.</t>
-  </si>
-  <si>
-    <t>Fomento A La Lectura</t>
-  </si>
-  <si>
-    <t>La Fundación Elena Poniatowska donó 2 mil libros a la SEPH para su distribución en escuelas de educación básica en Hidalgo, fortaleciendo el fomento a la lectura.</t>
-  </si>
-  <si>
     <t>SEPH, IHE, Gobernador</t>
   </si>
   <si>
-    <t>Natividad Castrejón Valdez, Nancy Adriana León Vite, María del Rosario Ramírez Hernández, Tatiana Nogueira</t>
-  </si>
-  <si>
-    <t>Computación, Óptica y láseres</t>
-  </si>
-  <si>
-    <t>Columna académica del Colegio del Estado de Hidalgo sobre los avances, aplicaciones e interacciones tecnológicas entre la computación, los sistemas ópticos y la física de láseres en la investigación contemporánea.</t>
-  </si>
-  <si>
-    <t>Divulgación científica</t>
-  </si>
-  <si>
-    <t>Análisis académico del Colegio del Estado de Hidalgo sobre la evolución e impacto científico de la computación, óptica y física de láseres.</t>
-  </si>
-  <si>
-    <t>SEPH, Universidades, Otros</t>
-  </si>
-  <si>
-    <t>Alfonso Padilla Vivanco, Pastor Badillo Flores</t>
-  </si>
-  <si>
-    <t>DESARROLLAN EN LA UPH LENTES ASISTIDOS PARA PERSONAS CON DISCAPACIDAD VISUAL</t>
-  </si>
-  <si>
-    <t>Estudiantes de la Universidad Politécnica de Huejutla (UPH) desarrollaron un prototipo de lentes asistidos que detecta obstáculos y emite alertas sonoras en tiempo real, con el propósito de brindar mayor autonomía y seguridad en los desplazamientos diarios de personas con discapacidad visual.</t>
-  </si>
-  <si>
-    <t>Innovación tecnológica</t>
-  </si>
-  <si>
-    <t>Alumnos de la Universidad Politécnica de Huejutla diseñaron lentes asistidos con sensores ultrasónicos para facilitar la movilidad segura de personas con discapacidad visual.</t>
-  </si>
-  <si>
-    <t>SEPH, Universidades</t>
-  </si>
-  <si>
-    <t>Martina Hernández Hernández, Marilin Montiel Vera, Bruno Rómero Hernández, Samuel Rómero Hernández</t>
-  </si>
-  <si>
-    <t>Desplegarán más de 5 mil elementos de seguridad por Fiestas Patrias en Hidalgo</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) desplegará un operativo de vigilancia y prevención en los 84 municipios de la entidad con motivo de las celebraciones de las Fiestas Patrias, los días 15 y 16 de septiembre. Participarán 5,580 elementos de la Policía Estatal, municipal, Bomberos, C5i y Protección Civil.</t>
-  </si>
-  <si>
-    <t>La SSPH desplegará más de 5 mil elementos policiacos y monitoreo permanente del C5i en los 84 municipios para resguardar las festividades del Grito de Independencia.</t>
-  </si>
-  <si>
     <t>Marco Cerón</t>
   </si>
   <si>
-    <t>SSPH, C5i, PC, Segobh, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Cae hombre implicado en al menos siete asaltos en Hidalgo y Edomex</t>
-  </si>
-  <si>
-    <t>Elementos de la Policía Estatal y Municipal detuvieron en Tepeapulco a un hombre identificado como M.A.V.M de 26 años, presuntamente relacionado con al menos siete asaltos a tiendas de conveniencia en Hidalgo y el Estado de México. Se le aseguró una réplica de arma de fuego, dosis de droga y celulares.</t>
-  </si>
-  <si>
-    <t>Policías estatales y municipales aprehendieron en Tepeapulco a un sujeto investigado por al menos siete asaltos a tiendas de conveniencia en Hidalgo y el Estado de México.</t>
-  </si>
-  <si>
-    <t>M. A. V. M.</t>
-  </si>
-  <si>
-    <t>INCREMENTAN INTENTOS DE SUICIDIO Y DEPRESIÓN EN EL ESTADO DE HIDALGO</t>
-  </si>
-  <si>
-    <t>En poco menos de cuatro años, los servicios de salud en Hidalgo han registrado más de 200 atenciones por intentos de suicidio, además de un incremento en pacientes con depresión y lesiones autoinfligidas intencionalmente, con mayor afectación en mujeres, reportó la SSA federal. Entre 2020 y 2026 se acumularon 772 decesos por suicidio en la entidad.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud reportó que entre 2020 y 2026 Hidalgo acumuló 772 fallecimientos por suicidio y más de 200 atenciones por intentos, identificando a adolescentes de 15 a 19 años y mujeres como los sectores más vulnerables.</t>
-  </si>
-  <si>
     <t>Carmen Hernández</t>
   </si>
   <si>
-    <t>SSH, Presidencia, Salud</t>
-  </si>
-  <si>
-    <t>NORMALISTAS SE PRONUNCIAN EN EVENTO DE LA PRESIDENTA</t>
-  </si>
-  <si>
-    <t>Estudiantes de la Escuela Normal Rural Luis Villarreal El Mexe tiraron una valla de seguridad y se manifestaron al finalizar el discurso de la presidenta Claudia Sheinbaum en Pachuca, exigiendo la habilitación total de dormitorios y comedor, así como avances en las investigaciones por la muerte de un compañero originario de Huehuetla.</t>
-  </si>
-  <si>
-    <t>Alumnos de El Mexe protestaron durante el acto de Claudia Sheinbaum en el recinto ferial para demandar espacios dignos e internado completo, mientras la PGJEH acordó una nueva mesa de diálogo para informar sobre las indagatorias del alumno fallecido.</t>
-  </si>
-  <si>
-    <t>SEPH, PGJEH, Presidencia, Gobernación</t>
-  </si>
-  <si>
-    <t>Francisco Fernández Hasbun, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>LA CONSTRUCCIÓN DEL NUEVO CERESO PODRÍA ATRASARSE, SEÑALA CRUZ NERI</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría de Seguridad Pública de Hidalgo, Salvador Cruz Neri, reconoció que la edificación del nuevo penal regional podría postergarse para 2027 debido a la falta de concreción en la compra de terrenos que cumplan con los requerimientos técnicos, evaluando predios en Huichapan y Jacala.</t>
-  </si>
-  <si>
-    <t>Construcción de Cereso</t>
-  </si>
-  <si>
-    <t>El secretario de Seguridad Pública, Salvador Cruz Neri, admitió que los 80 mdp destinados al nuevo Cereso regional podrían aplicarse hasta 2027 si no se asegura la tenencia de la tierra antes de que concluya el año.</t>
-  </si>
-  <si>
-    <t>SSPH, Segobh</t>
-  </si>
-  <si>
-    <t>DESPLEGARÁN 5 MIL ELEMENTOS PARA VIGILAR FIESTAS PATRIAS</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo implementará un despliegue de 5 mil efectivos en los 84 municipios para garantizar el orden durante los festejos patrios del 15 de septiembre, instalando filtros de revisión en Plaza Juárez y supervisando la prohibición de disparos de arma de fuego.</t>
-  </si>
-  <si>
-    <t>El secretario de Seguridad Pública, Salvador Cruz Neri, anunció un operativo con 5 mil policías, puestos de control y asistencia médica para resguardar la ceremonia del Grito de Independencia.</t>
-  </si>
-  <si>
-    <t>SSPH, Segobh, PC, Bomberos, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Salvador Cruz Neri, Carlos Rivera</t>
-  </si>
-  <si>
-    <t>FRAUDE, ROBOS DE VEHÍCULO Y MOTOCICLETA, CONCENTRAN DENUNCIAS EN CUAUTEPEC</t>
-  </si>
-  <si>
-    <t>El Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública reportó que el fraude (19 carpetas), el robo de automóvil (15) y de motocicleta (11) encabezaron los delitos patrimoniales en Cuautepec de Hinojosa de enero al cierre de julio de 2026.</t>
-  </si>
-  <si>
-    <t>Cuautepec</t>
-  </si>
-  <si>
-    <t>Cifras del SESNSP revelaron un repunte en investigaciones por fraude y robo de unidades en Cuautepec, concentrándose la mayor sustracción de vehículos durante la feria patronal de junio.</t>
-  </si>
-  <si>
     <t>María Antonieta Islas</t>
   </si>
   <si>
-    <t>PGJEH, Ayuntamiento, SESNSP</t>
-  </si>
-  <si>
-    <t>Jorge Hernández Araus</t>
-  </si>
-  <si>
-    <t>ATACAN LA CAMIONETA DE DIRIGENTE DE ASOCIACIÓN</t>
-  </si>
-  <si>
-    <t>Un sujeto lanzó una bomba casera incendiaria contra la camioneta de Onésimo Pérez Lara, presidente de la Asociación Certeza, Progreso y Desarrollo para Todos, ocasionando daños materiales en el vehículo estacionado afuera de su vivienda en Tlanchinol.</t>
-  </si>
-  <si>
-    <t>El activista Onésimo Pérez Lara sufrió un atentado con explosivo casero contra su camioneta en Tlanchinol, atribuyendo la agresión a represalias por su labor en conflictos de tierras comunales.</t>
-  </si>
-  <si>
-    <t>ESCUELAS REFUERZAN PREVENCIÓN INFANTIL</t>
-  </si>
-  <si>
-    <t>Docentes, estudiantes y autoridades del IHE desarrollaron la II Jornada Nacional de Concientización contra el Abuso Sexual y Maltrato Infantil en la primaria José Vasconcelos de Mineral de la Reforma, acercando talleres de la Policía Cibernética y protocolos de actuación.</t>
-  </si>
-  <si>
-    <t>La SEPH e instituciones de seguridad impartieron charlas sobre prevención de violencia digital y derechos de la infancia a la comunidad escolar de Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>SEPH, IHE, Policía Cibernética, PGJEH, CDHEH, Sipinna</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Nancy Adriana León Vite</t>
-  </si>
-  <si>
-    <t>PLANEA CENHIES AMPLIAR OFERTA ACADÉMICA</t>
-  </si>
-  <si>
-    <t>El Centro de Estudios de Enseñanza Superior (Cenhies) anunció proyectos para expandir su oferta de licenciaturas y posgrados para el ciclo escolar 2027, informó el directivo Alejandro Chapey Ramírez Zúñiga.</t>
-  </si>
-  <si>
-    <t>Oferta académica</t>
-  </si>
-  <si>
-    <t>El Cenhies alista la apertura de nuevas carreras profesionales para fortalecer su cobertura educativa en la zona metropolitana de Pachuca.</t>
-  </si>
-  <si>
-    <t>Alejandro Chapey Ramírez Zúñiga</t>
-  </si>
-  <si>
-    <t>En vísperas del nuevo proceso, hay casos rezagados de elecciones pasadas</t>
-  </si>
-  <si>
-    <t>La titular de la Fiscalía Especializada en Delitos Electorales de Hidalgo, Diana Jeaneth Rodríguez López, reconoció que aún cuentan con cerca de 50 carpetas de investigación sin sentencia correspondientes al Proceso Electoral Local 2023-2024, la gran mayoría vinculadas con violencia digital contra mujeres realizada a través de perfiles falsos.</t>
-  </si>
-  <si>
-    <t>La titular de la Fiscalía Especializada en Delitos Electorales, Diana Jeaneth Rodríguez, reportó la existencia de cerca de 50 carpetas pendientes del proceso 2023-2024, principalmente por violencia digital contra mujeres.</t>
-  </si>
-  <si>
-    <t>PGJEH, TEEH, IEEH</t>
-  </si>
-  <si>
-    <t>Diana Jeaneth Rodríguez López</t>
-  </si>
-  <si>
-    <t>Dos meses después, Saderh libera equipos fotovoltaicos en Tulancingo</t>
-  </si>
-  <si>
-    <t>Tras permanecer durante dos meses en la explanada de la presidencia municipal de Tulancingo para corregir detalles y fallas de funcionamiento, la Saderh en Hidalgo, encabezada por Napoleón González Pérez, realizó la entrega formal de sistemas fotovoltaicos móviles de bombeo e insumos agrícolas a productores de más de 20 municipios.</t>
-  </si>
-  <si>
-    <t>Entrega De Equipo</t>
-  </si>
-  <si>
-    <t>La Saderh entregó sistemas fotovoltaicos móviles de bombeo e insumos agrícolas a productores de más de 20 municipios tras resolver fallas técnicas registradas en los equipos.</t>
-  </si>
-  <si>
-    <t>Nathali González</t>
-  </si>
-  <si>
-    <t>Saderh, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez</t>
-  </si>
-  <si>
-    <t>Prevén sentencia por triple feminicidio este mismo mes</t>
-  </si>
-  <si>
-    <t>Tras desahogarse la totalidad de las pruebas en la audiencia del 10 de septiembre ante el tribunal de juicio oral en Tulancingo, el proceso penal contra los tres acusados del triple feminicidio ocurrido en Santiago Tulantepec en julio de 2024 avanzó a la fase de alegatos finales fijada para el 24 de septiembre, proyectándose la emisión de la sentencia antes de que concluya el mes.</t>
-  </si>
-  <si>
-    <t>El tribunal de juicio oral programó para el 24 de septiembre la audiencia de alegatos finales en el proceso por el triple feminicidio de Santiago Tulantepec, proyectando emitir la sentencia este mes.</t>
-  </si>
-  <si>
-    <t>PGJEH, TSJEH, Fiscalía de Género</t>
-  </si>
-  <si>
-    <t>R. G. Y., O. Y. C., D. G. C.</t>
-  </si>
-  <si>
-    <t>Reiteran el cierre de tiradero en región Tula</t>
-  </si>
-  <si>
-    <t>El relleno sanitario ubicado en Siete Mezquites permanecerá cerrado y no podrá recibir residuos, reiteraron autoridades estatales durante una reunión de seguimiento con habitantes y ejidatarios de Tula. Asimismo, se acordó realizar una visita el próximo 17 de septiembre para inspeccionar el retiro de desechos acumulados.</t>
-  </si>
-  <si>
-    <t>Autoridades estatales ratificaron el cierre definitivo del tiradero Siete Mezquites en Tula y programaron una inspección técnica con pobladores para el 17 de septiembre.</t>
-  </si>
-  <si>
-    <t>Semarnath, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Asaltos en el Arco Norte bajan 71% durante 2026</t>
-  </si>
-  <si>
-    <t>Los asaltos consumados en la autopista Arco Norte disminuyeron 71 por ciento durante el primer semestre de 2026, al pasar de 77 casos registrados entre enero y junio de 2025 a 22 en el mismo periodo de este año. En el periodo se desplegaron 97 operativos coordinados entre Hidalgo, Estado de México, Tlaxcala, Puebla y Querétaro, logrando la recuperación de seis vehículos con reporte de robo y el cierre de 25 accesos clandestinos.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Gobierno reportó una reducción del 71% en asaltos consumados en el Arco Norte tras el despliegue de 97 operativos interestatales y la clausura de 25 accesos ilegales.</t>
-  </si>
-  <si>
-    <t>Segobh, SICT, GN, Presidencia</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna</t>
-  </si>
-  <si>
-    <t>Participa IHE en jornada de concientización contra el abuso y maltrato infantil</t>
-  </si>
-  <si>
-    <t>El Instituto Hidalguense de Educación (IHE) participó en la segunda Jornada Nacional de Concientización sobre la Gravedad del Abuso Sexual y Maltrato Infantil realizada en la primaria José Vasconcelos de Mineral de la Reforma. Durante la actividad, la Policía Cibernética impartió la plática masiva Juega y navega con inteligencia para promover el uso seguro de redes sociales en el entorno escolar.</t>
-  </si>
-  <si>
-    <t>Autoridades de la SEPH y del IHE encabezaron talleres sobre prevención de abuso infantil y ciberseguridad para la comunidad escolar de Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>ITESA destaca en prueba EGEL PLUS</t>
-  </si>
-  <si>
-    <t>El 72.4 por ciento de los egresados de Ingeniería en Industrias Alimentarias del Instituto Tecnológico Superior del Oriente del Estado de Hidalgo (ITESA) obtuvo un desempeño satisfactorio o sobresaliente en la evaluación EGEL Plus del Ceneval, incorporando la carrera al Padrón de Alto Rendimiento.</t>
-  </si>
-  <si>
-    <t>Apan</t>
-  </si>
-  <si>
-    <t>Excelencia académica</t>
-  </si>
-  <si>
-    <t>El ITESA ingresó al Padrón de Alto Rendimiento del Ceneval luego de que más del 72% de sus egresados de Ingeniería Alimentaria aprobaran la prueba EGEL Plus.</t>
-  </si>
-  <si>
-    <t>UTTT realiza Expo Empleo Regional</t>
-  </si>
-  <si>
-    <t>Más de 30 empresas y estudiantes de la Universidad Tecnológica de Tula-Tepeji (UTTT) participaron en la Expo Empleo Regional, ofreciendo vacantes de vinculación laboral directa a egresados y alumnos de la región.</t>
-  </si>
-  <si>
-    <t>Vinculación Laboral</t>
-  </si>
-  <si>
-    <t>La UTTT reunió a más de 30 empresas en la Expo Empleo Regional para promover la inserción laboral de sus universitarios y egresados.</t>
-  </si>
-  <si>
-    <t>SEPH, Universidades, STPSH</t>
-  </si>
-  <si>
-    <t>Habrá recortes y desvíos en el transporte público por fiestas patrias</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte (Semot), en coordinación con el Sitmah y el STCH, informó que con motivo de las celebraciones por el aniversario de la Independencia de México se realizarán recortes operativos los días 14, 15 y 16 de septiembre en la ruta troncal del Tuzobús, cerrando las estaciones Presidente Alemán, Plaza Juárez, Niños Héroes y Centro Histórico, habilitando una Ruta Emergente sin costo.</t>
-  </si>
-  <si>
-    <t>Recorte Operativo</t>
-  </si>
-  <si>
-    <t>La Semot y el Sitmah anunciaron recortes operativos en el Tuzobús y cierre de estaciones céntricas del 14 al 16 de septiembre por las Fiestas Patrias, implementando una ruta emergente gratuita.</t>
-  </si>
-  <si>
-    <t>Semot, Sitmah, STCH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Por obras del tren AIFA-Pachuca colonias tendrán afectaciones en el suministro de agua</t>
-  </si>
-  <si>
-    <t>Más de 13 colonias del sector oriente de la Zona Metropolitana de Pachuca presentarán interrupciones en el servicio de agua potable a partir del lunes 14 de septiembre a las 7:00 horas, debido a las maniobras que realizará la Sedena para la construcción del tren AIFA-Pachuca. El titular de Caasim, Juan Evel Chávez Trovamala, informó que el restablecimiento comenzará el 15 de septiembre pero podría extenderse hasta 96 horas, disponiéndose del apoyo de pipas.</t>
-  </si>
-  <si>
-    <t>Abasto de agua</t>
-  </si>
-  <si>
-    <t>Caasim alertó que más de 13 colonias de la zona metropolitana de Pachuca sufrirán cortes de agua a partir del 14 de septiembre debido a las obras del tren AIFA-Pachuca ejecutadas por la Sedena.</t>
-  </si>
-  <si>
-    <t>Sipdus, Caasim, Presidencia, Sedena</t>
-  </si>
-  <si>
-    <t>Juan Evel Chávez Trovamala</t>
-  </si>
-  <si>
-    <t>Licitan áreas comerciales para el Sector Primario</t>
-  </si>
-  <si>
-    <t>La Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS) publicó la licitación pública EO-SIPDUS-N136-2026 para la edificación de locales comerciales, sanitarios, cuarto de control y cisterna en el Sector Primario de Pachuca, con un capital contable mínimo requerido de 3.9 mdp y fallo programado para el 28 de septiembre.</t>
-  </si>
-  <si>
-    <t>Licitaciones</t>
-  </si>
-  <si>
-    <t>La Sipdus lanzó la convocatoria de licitación para la edificación de áreas comerciales e infraestructura básica en el Sector Primario de Pachuca.</t>
-  </si>
-  <si>
-    <t>Sipdus, Gobernador</t>
-  </si>
-  <si>
-    <t>Destaca Hidalgo en la gestión fitosanitaria y monitoreo aéreo</t>
-  </si>
-  <si>
-    <t>De acuerdo con el informe del Sivicoff de la Semarnat y Conafor, Hidalgo se ubica entre los estados con menor superficie forestal dañada por plagas (559.8 hectáreas, 1.82% del total nacional) y ocupa el tercer lugar nacional en notificaciones fitosanitarias autorizadas con 111 permisos de saneamiento, además de participar en el programa de monitoreo aéreo en 118 mil hectáreas.</t>
-  </si>
-  <si>
-    <t>Saneamiento forestal</t>
-  </si>
-  <si>
-    <t>Hidalgo se posicionó en el tercer lugar nacional con más permisos de saneamiento forestal autorizados y una de las menores hectáreas afectadas por plagas en el país.</t>
-  </si>
-  <si>
-    <t>Semarnath, Presidencia, Medio ambiente</t>
-  </si>
-  <si>
-    <t>Recordarán a El Santo con especial Noche de Museos en Tulancingo</t>
-  </si>
-  <si>
-    <t>La Jefatura de Museos de Tulancingo organizará una edición especial de Noche de Museos el 23 de septiembre para conmemorar el 109 aniversario del natalicio de Rodolfo Guzmán Huerta 'El Santo', realizando recorridos históricos en el Museo del Santo, espacio cultural que además recibirá obras de reemplazo de duela y mantenimiento integral.</t>
-  </si>
-  <si>
-    <t>Aniversario natalicio</t>
-  </si>
-  <si>
-    <t>El municipio de Tulancingo celebrará una Noche de Museos dedicada a El Santo en el 109 aniversario de su nacimiento, realizando mejoras en la infraestructura del recinto.</t>
-  </si>
-  <si>
-    <t>Cultura, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Rodolfo Guzmán Huerta</t>
-  </si>
-  <si>
-    <t>ALCOHOL, PRINCIPAL SUSTANCIA DE CONSUMO INICIAL EN HIDALGO</t>
-  </si>
-  <si>
-    <t>En 2025, en Hidalgo, el alcohol se ubicó como la principal droga de inicio, al concentrar 61% de los casos, por encima de sustancias como tabaco, cannabis, metanfetaminas, inhalables, solventes, cocaína y opiáceos, informó la responsable del programa de Alcohol y Tabaco de la Subsecretaría de Salud Pública, Vianey Garza Reséndiz. Por grupos de edad, las y los adolescentes de 12 a 17 años concentran el mayor porcentaje de consumo inicial, con 42 por ciento, equivalente a 3 mil 901 casos. Le siguen las personas de 20 a 29 años, con 24 por ciento (2 mil 274 casos), y el grupo de 30 a 49 años, con 22 por ciento (2 mil 056 casos). En el marco de las fiestas patrias, la Secretaría de Salud de Hidalgo (SSH) hizo un llamado a la población a disfrutar evitando el consumo excesivo de alcohol.</t>
-  </si>
-  <si>
-    <t>Consumo de alcohol</t>
-  </si>
-  <si>
-    <t>La SSH reportó que el alcohol representó el 61% de las sustancias de consumo inicial en Hidalgo, afectando principalmente a adolescentes de 12 a 17 años con 3 mil 901 casos registrados.</t>
-  </si>
-  <si>
     <t>SSH, Presidencia</t>
   </si>
   <si>
-    <t>Vianey Garza Reséndiz</t>
-  </si>
-  <si>
-    <t>Zonas altas de Pachuca y la Reforma son puntos críticos por robo de agua</t>
-  </si>
-  <si>
-    <t>Los puntos críticos de clandestinaje se encuentran en las zonas alejadas y altas de Pachuca, así como en el municipio de Mineral de la Reforma, ambos con infraestructura más antigua y menor acceso al servicio. Desde 2022 la Caasim ha detectado más de 13 mil 700 tomas clandestinas. El funcionario explicó que, de acuerdo con la ley, a partir de la tercera reincidencia localizada se inicia una denuncia penal. Mientras tanto, se trabaja con el área jurídica del organismo para permitir que las sanciones contra las personas a quienes se les detecte una toma clandestina sean más severas.</t>
-  </si>
-  <si>
-    <t>Robo De Agua</t>
-  </si>
-  <si>
-    <t>La Caasim ha detectado más de 13 mil 700 tomas clandestinas de agua potable desde 2022, concentrándose la mayor incidencia en colonias altas de Pachuca y Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>Sipdus, Caasim, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Van 15 fallecimientos por Covid-19 en la entidad</t>
-  </si>
-  <si>
-    <t>Con 15 registros al corte de la semana 35 del informe de Vigilancia Epidemiológica de Enfermedad Respiratoria Viral, Hidalgo encabeza el número de fallecimientos por Covid-19 a nivel nacional con el 23.4% del total del país (64 defunciones acumuladas en México). Adicionalmente, la entidad registra 175 casos confirmados de Covid-19 y se ubica en el quinto lugar nacional en influenza con 26 casos positivos y una defunción.</t>
-  </si>
-  <si>
-    <t>Covid 19</t>
-  </si>
-  <si>
-    <t>Hidalgo encabezó la estadística nacional de fallecimientos por Covid-19 en 2026 con 15 decesos registrados (23.4% del país) y 175 contagios confirmados, según el informe epidemiológico federal.</t>
-  </si>
-  <si>
-    <t>AVANZA 75% TRANSICIÓN DE PROCURADURÍA A FISCALÍA DE HIDALGO</t>
-  </si>
-  <si>
-    <t>La transición de Procuraduría General de Justicia del Estado a Fiscalía General de Justicia lleva al menos un avance del 75%, informó el encargado del Despacho de la PGJEH, Francisco Fernández Hasbun. El funcionario explicó que los pendientes corresponden a aspectos administrativos, nómina, seguridad social y digitalización del archivo, operando en la práctica como Fiscalía. Las nuevas instalaciones se ubicarán en San Agustín Tlaxiaca y el plazo constitucional vence el 22 de julio de 2028.</t>
-  </si>
-  <si>
-    <t>Transición a Fiscalía</t>
-  </si>
-  <si>
-    <t>La PGJEH reportó un avance del 75% en el proceso de transición hacia Fiscalía General de Justicia, avanzando en la digitalización de archivos y en la construcción de su nueva sede en San Agustín Tlaxiaca.</t>
-  </si>
-  <si>
-    <t>PGJEH, Congreso, Gobernador</t>
-  </si>
-  <si>
-    <t>Francisco Fernández Hasbun</t>
-  </si>
-  <si>
-    <t>Detectan hasta 2 mil establecimientos de Airbnb en Hidalgo; regulación sigue en proceso</t>
-  </si>
-  <si>
-    <t>Al menos 2 mil establecimientos que ofrecen servicios de hospedaje mediante Airbnb se tienen identificados en Hidalgo, principalmente en destinos como Huasca de Ocampo, Real del Monte y Mineral del Chico, informó la titular de la Secretaría de Turismo estatal, Elizabeth Quintanar. La funcionaria señaló que se negocia la implementación de un registro obligatorio de anfitriones y el cobro de impuestos locales para combatir la informalidad.</t>
-  </si>
-  <si>
-    <t>Airbnb</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo de Hidalgo identificó 2 mil alojamientos ofertados a través de Airbnb en municipios como Huasca y Real del Monte, avanzando en acuerdos para su regulación fiscal e inscripción obligatoria.</t>
-  </si>
-  <si>
-    <t>Turismo</t>
-  </si>
-  <si>
-    <t>Turismo, Hacienda, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar Gómez</t>
-  </si>
-  <si>
-    <t>Hidarte Tulancingo podría abrir sus puertas este mes de septiembre</t>
-  </si>
-  <si>
-    <t>La tienda Hidarte en el municipio de Tulancingo podría abrir sus puertas el próximo 14 o 15 de septiembre, informó Ricardo Gómez Moreno, titular de la Secretaría de Bienestar e Inclusión Social (Sebiso). El funcionario explicó que el espacio recibirá piezas artesanales de la región de Tulancingo, Otomí-Tepehua y Acaxochitlán, operando bajo la administración municipal sin cobro de comisiones para las personas artesanas.</t>
-  </si>
-  <si>
     <t>Hidarte</t>
   </si>
   <si>
-    <t>La Sebiso anunció la próxima apertura de la tienda Hidarte en Tulancingo para comercializar artesanías del Valle de Tulancingo, la región Otomí-Tepehua y Acaxochitlán sin costo para los productores.</t>
-  </si>
-  <si>
     <t>Bienestar</t>
   </si>
   <si>
-    <t>Bienestar, Ayuntamiento, Hidarte</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>Estrategias para la prevención del suicidio en México</t>
-  </si>
-  <si>
-    <t>Columna de opinión de Patricia González López que analiza las estadísticas del INEGI y la OMS en el marco del Día Mundial de la Prevención del Suicidio. Detalla que en México se contabilizaron 8,709 muertes por suicidio en 2026 con mayor prevalencia en jóvenes de 15 a 29 años, proponiendo restringir el acceso a medios letales, capacitar personal de salud e integrar la prevención en escuelas y comunidades.</t>
-  </si>
-  <si>
-    <t>Patricia González analiza las estadísticas del INEGI sobre suicidio en México y propone fortalecer las políticas de salud mental, la atención temprana y la concienciación social.</t>
-  </si>
-  <si>
-    <t>Patricia González López</t>
-  </si>
-  <si>
-    <t>SSPH desplegará operativo de seguridad por las Fiestas Patrias</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) activará un despliegue de 5,580 elementos de la Policía Estatal, municipales, Bomberos, C5i y Protección Civil en los 84 municipios con motivo de los festejos patrios del 15 y 16 de septiembre. En Pachuca se establecerán filtros de revisión y control vial en Plaza Juárez, prohibiéndose el acceso con armas, envases de vidrio o alcohol.</t>
-  </si>
-  <si>
-    <t>La SSPH desplegará a más de 5,500 elementos de seguridad y monitoreo del C5i en los 84 municipios para resguardar los festejos patrios del 15 y 16 de septiembre.</t>
-  </si>
-  <si>
-    <t>SSPH, C5i, PC, Bomberos, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Cae por asalto a tienda de conveniencia</t>
-  </si>
-  <si>
-    <t>Policías estatales arrestaron en Tepeapulco a un sujeto identificado como M. A. V. M., de 26 años, presuntamente involucrado en al menos siete robos a tiendas de conveniencia en Hidalgo y el Estado de México. Al momento de ser intervenido se le decomisó una réplica de arma de fuego, 120 dosis de marihuana, 43 dosis de cristal y una motocicleta con alteración en sus números de serie.</t>
-  </si>
-  <si>
-    <t>Policías estatales arrestaron en Tepeapulco a un hombre de 26 años vinculado con siete asaltos a comercios en Hidalgo y Edomex, decomisándole dosis de droga y una réplica de arma.</t>
-  </si>
-  <si>
-    <t>Celebraron la Gesta Heroica de los Niños Héroes</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo coordinó la ceremonia cívica del 179 Aniversario de la Gesta Heroica de los Niños Héroes de Chapultepec. En la conmemoración se rindiéron honores a la bandera y el titular de la SSPH, Salvador Cruz Neri, pronunció el discurso oficial refrendando el compromiso de honrar la historia patria.</t>
-  </si>
-  <si>
-    <t>Conmemoración Aniversario</t>
-  </si>
-  <si>
-    <t>La SSPH encabezó en Pachuca la ceremonia cívico-militar por el 179 Aniversario de la Gesta Heroica de los Niños Héroes de Chapultepec.</t>
-  </si>
-  <si>
-    <t>SSPH, Presidencia, Sedena, Ejército</t>
-  </si>
-  <si>
-    <t>SEGURIDAD ACTIVA OPERATIVO FIESTAS PATRIAS PARA HIDALGO</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) desplegará un operativo de vigilancia en los 84 municipios durante el 15 y 16 de septiembre con 5,580 elementos de la Policía Estatal, municipal, Bomberos, C5i y Protección Civil. En Pachuca se establecerán filtros de revisión en Plaza Juárez y estará prohibido ingresar con armas o bebidas alcohólicas.</t>
-  </si>
-  <si>
-    <t>La SSPH activará un dispositivo de seguridad con 5,580 efectivos y monitoreo del C5i en los 84 municipios para resguardar los festejos patrios del 15 y 16 de septiembre.</t>
-  </si>
-  <si>
-    <t>CAMBIAN RUTAS DE TRANSPORTE POR EL GRITO Y EL DESFILE</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte (Semot) anunció ajustes al transporte público en Pachuca los días 14, 15 y 16 de septiembre. Cerraren estaciones céntricas del Tuzobús como Presidente Alemán, Plaza Juárez, Niños Héroes y Centro Histórico, extendiendo horarios la noche del 15 y habilitando una ruta emergente sin costo para el desfile del 16.</t>
-  </si>
-  <si>
-    <t>La Semot implementará modificaciones de itinerarios, extensión de horarios y cierres de estaciones del Tuzobús en Pachuca durante las celebraciones de las Fiestas Patrias.</t>
-  </si>
-  <si>
-    <t>El inmueble de la primaria Aquiles Serdán en Tulancingo será demolido y reconstruido en su totalidad debido a severas fallas en su estructura. El titular de la SEPH, Natividad Castrejón, confirmó que las obras abarcarán el ciclo escolar 2026-2027, evaluando alternativas presenciales temporales o esquemas virtuales e híbridos para el alumnado.</t>
-  </si>
-  <si>
-    <t>La SEPH demolerá y reconstruirá la primaria Aquiles Serdán en Tulancingo debido a daños en su infraestructura, evaluando alternativas presenciales o híbridas para los estudiantes.</t>
+    <t>Charros y escaramuzas recorren calles céntricas</t>
+  </si>
+  <si>
+    <t>Con motivo de la conmemoración del Día del Charro, charros y escaramuzas recorrieron las calles del centro de Pachuca desde la avenida Revolución hasta el Reloj Monumental, rindiendo homenaje a Roberto López por sus 50 años de trayectoria en la charrería hidalguense.</t>
+  </si>
+  <si>
+    <t>Charros y escaramuzas desfilaron por el centro de Pachuca para celebrar el Día del Charro y homenajear a Roberto López por 50 años de trayectoria.</t>
+  </si>
+  <si>
+    <t>Luis Carlos León</t>
+  </si>
+  <si>
+    <t>Cultura, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Roberto López</t>
+  </si>
+  <si>
+    <t>Propone Julio Menchaca transformar transparencia</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar envió al Congreso de Hidalgo un paquete de iniciativas para actualizar el marco normativo estatal en materia de transparencia, sustituyendo la estructura del Itaih para crear el Subsistema de Transparencia del Estado de Hidalgo integrado al Sistema Nacional.</t>
+  </si>
+  <si>
+    <t>Transparencia</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca presentó al Congreso propuestas para reestructurar los órganos de transparencia y control interno en la entidad.</t>
+  </si>
+  <si>
+    <t>Gustavo Vargas</t>
+  </si>
+  <si>
+    <t>Gobernador, Congreso, Contraloría, Itaipen</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Piden que el estudio cubra otras especies</t>
+  </si>
+  <si>
+    <t>La Asociación Hidalguense para la Protección de los Animales solicitó ampliar el estudio biológico del tren AIFA-Pachuca en seis municipios para proteger otras especies como murciélagos, conejos, tlacuaches, armadillos y cactáceas además del águila real.</t>
+  </si>
+  <si>
+    <t>Protección Animal</t>
+  </si>
+  <si>
+    <t>Activistas pidieron extender el estudio de impacto ambiental del tren AIFA-Pachuca a más especies de fauna y flora en la franja del proyecto.</t>
+  </si>
+  <si>
+    <t>Semarnath, Presidencia, SICT, Oficialía Mayor</t>
+  </si>
+  <si>
+    <t>Paola Monterrubio</t>
+  </si>
+  <si>
+    <t>Protegen territorio del puma, en Xithi</t>
+  </si>
+  <si>
+    <t>Pobladores y autoridades de Xithi en Tepetitlán recibieron un apoyo de 460 mil pesos para delimitar el territorio habitado por el puma captado en cámaras trampa y evitar incursiones a zonas habitadas o ataques al ganado.</t>
+  </si>
+  <si>
+    <t>Tepetitlán</t>
+  </si>
+  <si>
+    <t>Rescate de especies</t>
+  </si>
+  <si>
+    <t>Ejidatarios de Xithi en Tepetitlán destinaron recursos para el monitoreo y resguardo del hábitat del puma para prevenir conflictos con la población.</t>
+  </si>
+  <si>
+    <t>Rosalía Maldonado</t>
+  </si>
+  <si>
+    <t>Semarnath, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Ana Elsa Castillo Cea</t>
+  </si>
+  <si>
+    <t>Acude artista de Tezontepec a Colombia</t>
+  </si>
+  <si>
+    <t>El artista visual e investigador Javier Acevedo, originario de Tezontepec de Aldama, fue seleccionado para realizar una residencia artística en Colombia para desarrollar su proyecto 'Ensambles viscosos' sobre cuerpos de agua.</t>
+  </si>
+  <si>
+    <t>Tezontepec de Aldama</t>
+  </si>
+  <si>
+    <t>Intercambio Artístico</t>
+  </si>
+  <si>
+    <t>El creador hidalguense Javier Acevedo participará en una residencia artística en Colombia para exponer su obra sobre el territorio y el agua.</t>
+  </si>
+  <si>
+    <t>Javier Acevedo</t>
+  </si>
+  <si>
+    <t>Analizarán con IA problemática vial</t>
+  </si>
+  <si>
+    <t>El gobierno estatal instalará tres cámaras con Inteligencia Artificial en puentes del bulevar Felipe Ángeles para analizar el flujo vehicular y remodelará 34 estaciones del Tuzobús para mejorar el sistema de transporte en Pachuca.</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor aplicará tecnología de IA para evaluar la carga vehicular en el bulevar Felipe Ángeles y proyecta mantenimiento a 34 estaciones del Tuzobús.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Semot, Sitmah</t>
+  </si>
+  <si>
+    <t>Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>Definirán tarifas para taxi</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte (Semot) alista la definición del tarifario oficial de taxis en Pachuca previo a la Feria San Francisco 2026, recaudando además 190 mil pesos por sanciones por invasión al carril confinado del Tuzobús.</t>
+  </si>
+  <si>
+    <t>Tarifario de taxis</t>
+  </si>
+  <si>
+    <t>La Semot actualizará las tarifas de taxis en Pachuca rumbo a las festividades feriales e informó sobre sanciones aplicadas por invadir el carril del Tuzobús.</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah, Sipdus</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles Gutiérrez</t>
+  </si>
+  <si>
+    <t>Alcaldías olvidan al campo señala UNTA Hidalgo</t>
+  </si>
+  <si>
+    <t>La dirigencia estatal de la Unión Nacional de Trabajadores Agrícolas (UNTA) acusó a los ayuntamientos hidalguenses de desatender al sector campesino y omitir la asignación de presupuestos para proyectos productivos agropecuarios.</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>La UNTA Hidalgo reprobó que las administraciones municipales no destinen recursos para la reactivación económica y fomento del sector agrícola.</t>
+  </si>
+  <si>
+    <t>Alma Leticia Sánchez</t>
+  </si>
+  <si>
+    <t>Saderh, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Martha López Ríos</t>
+  </si>
+  <si>
+    <t>Charros desfilan en conmemoración de su día</t>
+  </si>
+  <si>
+    <t>Con motivo de la conmemoración del Día del Charro, integrantes de la Asociación de Charros del Estado de Hidalgo desfilaron ataviados con traje típico por las calles del centro de Pachuca desde avenida Revolución hasta el Reloj Monumental, enalteciendo esta tradición declarada Patrimonio Cultural Inmaterial.</t>
+  </si>
+  <si>
+    <t>Integrantes de la Asociación de Charros de Hidalgo desfilaron por el centro de Pachuca para celebrar el Día del Charro y enaltecer la tradición charra.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca envía al Congreso local paquete de reformas en transparencia</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar envió al Congreso de Hidalgo un paquete de reformas para crear 'Transparencia para el Pueblo de Hidalgo' como órgano desconcentrado de la Contraloría y el Subsistema de Transparencia estatal, reorganizando la protección de datos tras la desaparición del ITAIH.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca envió iniciativas al Congreso para reestructurar la transparencia y control interno, creando Transparencia para el Pueblo de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Adela Garmez</t>
+  </si>
+  <si>
+    <t>Gobernador, Congreso, Contraloría, Itaipen, Planeación, TSJEH</t>
+  </si>
+  <si>
+    <t>Comité Estatal de Formación valora propuestas de instrucción docente</t>
+  </si>
+  <si>
+    <t>El Comité Estatal de Formación Continua de Hidalgo analizó la oferta académica del Programa para el Desarrollo Profesional Docente (Prodep) 2026 para fortalecer la capacitación de maestras y maestros de educación básica, con la participación de la coordinadora de Educación Básica, Nancy Adriana León Vite.</t>
+  </si>
+  <si>
+    <t>Boletín</t>
+  </si>
+  <si>
+    <t>Prodep</t>
+  </si>
+  <si>
+    <t>El Comité Estatal de Formación Continua evaluó las acciones formativas del Prodep 2026 para impulsar la profesionalización del magisterio hidalguense.</t>
+  </si>
+  <si>
+    <t>Comunicado gubernamental</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Nancy Adriana León Vite, María de Lourdes Reyes Pérez, María del Rosario Ramírez Hernández, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Medirá IA flujo vehicular para solucionar congestionamientos</t>
+  </si>
+  <si>
+    <t>El gobierno de Hidalgo instalará tres cámaras con tecnología de Inteligencia Artificial en puentes del bulevar Felipe Ángeles con una inversión de hasta 600 mil pesos para analizar el tránsito hacia la CDMX y definir soluciones viales. A su vez, la Semot descartó la apertura del carril del Tuzobús al no reducir el tráfico.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor aplicará Inteligencia Artificial para medir el tránsito en el bulevar Felipe Ángeles, mientras la Semot descartó abrir el carril del Tuzobús.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Semot, Sitmah, SICT, Congreso</t>
+  </si>
+  <si>
+    <t>Orlando Ángeles Pérez, Lyzbeth Robles Gutiérrez</t>
+  </si>
+  <si>
+    <t>Prevén entregar este año el nuevo Hospital General</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo prevé concluir este año la transferencia del nuevo Hospital General de Pachuca al IMSS-Bienestar tras dos años de trámites y verificaciones federales. Además, reportó que el Hospital de Actopan lleva más de 90% de avance.</t>
+  </si>
+  <si>
+    <t>Nuevo Hospital General</t>
+  </si>
+  <si>
+    <t>La SSH proyecta entregar este año el nuevo Hospital General de Pachuca al IMSS-Bienestar e informó avances superiores al 90% en el nosocomio de Actopan.</t>
+  </si>
+  <si>
+    <t>SSH, IMSS-Bienestar, Sipdus, Presidencia</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>Registra Hidalgo una baja en casos de suicidio</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo reportó más de 40 muertes por suicidio en 2026, lo que representa una baja frente a los 146 casos de 2024 y más de 150 de 2025, manteniendo la atención preventiva en Cecosama y mesas de trabajo municipales.</t>
+  </si>
+  <si>
+    <t>La SSH registró una disminución en fallecimientos por suicidio en Hidalgo durante 2026, reforzando la atención psicológica preventiva en los municipios.</t>
+  </si>
+  <si>
+    <t>SSH, Cecosama, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Gobierno lanzará licitación para remodelar estaciones del Tuzobús</t>
+  </si>
+  <si>
+    <t>La Sipdus emitirá en octubre la licitación para remodelar las 34 estaciones del Tuzobús. Oficialía Mayor reportó que la afluencia subió a más de 91 mil pasajeros diarios y los tiempos de traslado bajaron 30%, mientras que Semot ha recaudado 190 mil pesos por 81 multas por invadir el carril confinado.</t>
+  </si>
+  <si>
+    <t>Rehabilitación estaciones Tuzobús</t>
+  </si>
+  <si>
+    <t>El gobierno estatal licitará la remodelación de 34 estaciones del Tuzobús e informó sobre el incremento de usuarios a 91 mil diarios y sanciones por invadir el carril.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Sipdus, Semot, Sitmah</t>
+  </si>
+  <si>
+    <t>Defiende Semot permanencia del carril confinado</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte (Semot) defendió la permanencia del carril exclusivo del Tuzobús sobre el bulevar Felipe Ángeles, al señalar que su confinamiento permitió elevar la eficiencia operativa del sistema de 75 a 99 por ciento, incrementar el número de usuarios y reducir los siniestros viales. La titular de la dependencia, Lyzbeth Robles Gutiérrez, sostuvo que el carril reservado tiene como prioridad proteger a las más de 60 mil personas que utilizan diariamente la ruta troncal, rechazando que sea el causante del tráfico sobre esa vía.</t>
+  </si>
+  <si>
+    <t>Carril confinado</t>
+  </si>
+  <si>
+    <t>La Semot justificó la vigencia del carril confinado del Tuzobús al argumentar que elevó la eficiencia al 99% y atiende a más de 60 mil usuarios diarios en Pachuca.</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Puértolas</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah, STCH, Presidencia, Sipdus</t>
+  </si>
+  <si>
+    <t>Eficiencia del transporte metropolitano, de 75 a 99%</t>
+  </si>
+  <si>
+    <t>La eficiencia del sistema de transporte metropolitano pasó de 75 a 99 por ciento desde que el gobierno de Hidalgo asumió su operación directamente el pasado 1 de agosto a través del Sitmah. El oficial mayor, Edgar Orlando Ángeles Pérez, detalló que se incorporaron 140 autobuses y 383 operadores certificados, incrementando la afluencia diaria en la ruta troncal y alimentadoras de 68 mil usuarios en junio a 91 mil 923 en septiembre.</t>
+  </si>
+  <si>
+    <t>Afluencia Tuzobús</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor reportó que la operación estatal del transporte metropolitano elevó la eficiencia a 99% y la afluencia de usuarios a cerca de 92 mil diarios.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Sitmah, Semot, Gobernador</t>
+  </si>
+  <si>
+    <t>Prohiben disparos al aire durante el Grito</t>
+  </si>
+  <si>
+    <t>El secretario de Seguridad Pública de Hidalgo, Salvador Cruz Neri, advirtió que no se tolerarán disparos de arma de fuego al aire durante las celebraciones de las Fiestas Patrias, recordando que esta conducta constituye un delito sancionado con hasta dos años de prisión en el Código Penal estatal.</t>
+  </si>
+  <si>
+    <t>La SSPH advirtió que sancionará penalmente los disparos de arma de fuego al aire durante los festejos del Grito de Independencia.</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH, Segobh</t>
+  </si>
+  <si>
+    <t>Aún pendiente transferencia de hospital</t>
+  </si>
+  <si>
+    <t>La secretaria de Salud de Hidalgo, Vanesa Escalante Arroyo, señaló que el proceso de transferencia del nuevo Hospital General de Pachuca al IMSS-Bienestar continúa pendiente tras dos años de gestiones, esperando concluir las verificaciones federales para su operación.</t>
+  </si>
+  <si>
+    <t>La SSH reportó que sigue en revisión la transferencia del nuevo Hospital General de Pachuca al esquema IMSS-Bienestar.</t>
+  </si>
+  <si>
+    <t>SSH, IMSS-Bienestar, Presidencia</t>
+  </si>
+  <si>
+    <t>Sin puente por fiestas patrias</t>
+  </si>
+  <si>
+    <t>El calendario escolar oficial de la SEP contempla únicamente la suspensión de labores el miércoles 16 de septiembre por las Fiestas Patrias, por lo que las actividades escolares iniciaron de forma regular el martes.</t>
+  </si>
+  <si>
+    <t>El calendario educativo marcó únicamente el 16 de septiembre como suspensión oficial de clases por festejos patrios.</t>
+  </si>
+  <si>
+    <t>SEPH, Presidencia</t>
+  </si>
+  <si>
+    <t>Registran más de 40 suicidios en ocho meses</t>
+  </si>
+  <si>
+    <t>Entre enero y agosto de 2026 Hidalgo acumuló más de 40 fallecimientos por suicidio, reflejando un descenso respecto a años anteriores según datos de la Secretaría de Salud estatal, concentrándose la mayor atención preventiva en jóvenes de 15 a 19 años.</t>
+  </si>
+  <si>
+    <t>La SSH contabilizó más de 40 suicidios en los primeros ocho meses del año, destacando una baja general de casos en la entidad.</t>
+  </si>
+  <si>
+    <t>Alejandro Reyes</t>
+  </si>
+  <si>
+    <t>Más de mil 700 personas acudieron a seis funciones gratuitas de cine en lenguas originarias</t>
+  </si>
+  <si>
+    <t>La muestra itinerante de cine en lenguas originarias congregó a más de mil 700 asistentes durante seis funciones gratuitas en cinco municipios hidalguenses para promover la diversidad lingüística.</t>
+  </si>
+  <si>
+    <t>Cine Comunitario</t>
+  </si>
+  <si>
+    <t>Más de 1,700 espectadores disfrutaron de la muestra de cine en lenguas indígenas en municipios de Hidalgo.</t>
+  </si>
+  <si>
+    <t>La planta Tula de Cruz Azul produce ya 600 toneladas diarias de cemento blanco</t>
+  </si>
+  <si>
+    <t>La fábrica de Cruz Azul en Tula alcanzó una producción diaria de 600 toneladas de cemento blanco y alista el reinicio de líneas de cemento gris, informó Mario Francisco Morán.</t>
+  </si>
+  <si>
+    <t>Cruz Azul</t>
+  </si>
+  <si>
+    <t>La planta de Cruz Azul en Tula reactivó operaciones alcanzando 600 toneladas diarias de cemento blanco.</t>
+  </si>
+  <si>
+    <t>Sedeco, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Mario Francisco Morán</t>
+  </si>
+  <si>
+    <t>El gobernador envía serie de iniciativas al Congreso</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar envió al Congreso local un paquete de iniciativas orientado a actualizar el marco jurídico estatal en materia de transparencia, protección de datos personales, control interno y simplificación administrativa, planteando la creación de Transparencia para el Pueblo de Hidalgo y el Subsistema de Transparencia del Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca envió un paquete de iniciativas al Congreso para reestructurar el sistema de transparencia estatal y protección de datos tras la extinción del ITAIH.</t>
+  </si>
+  <si>
+    <t>Gobernador, Congreso, Contraloría, Itaipen, Planeación</t>
+  </si>
+  <si>
+    <t>PREPARAN UN ANÁLISIS CON IA DEL TRÁFICO</t>
+  </si>
+  <si>
+    <t>En los próximos 15 días, instalarán tres videocámaras de inteligencia artificial en los puentes del Tecnológico de Monterrey, la Procuraduría de Hidalgo y Matilde, como parte de un análisis del comportamiento vehicular sobre el bulevar Felipe Ángeles; por ahora, continuará en funcionamiento el carril confinado del Tuzobús.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor instalará tres cámaras con IA en el bulevar Felipe Ángeles para evaluar soluciones viales, mientras la Semot descartó la apertura del carril confinado del Tuzobús.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Semot, Sitmah, Congreso, Sipdus</t>
+  </si>
+  <si>
+    <t>Edgar Orlando Ángeles Pérez, Lyzbeth Robles Gutiérrez</t>
+  </si>
+  <si>
+    <t>Le retiran la concesión a una ruta por caso Minero</t>
+  </si>
+  <si>
+    <t>Por carecer de seguro vial, la Secretaría de Movilidad y Transporte de Hidalgo (Semot) le retiró una concesión de transporte a la ruta Tilcuautla-Pachuca, involucrada en el accidente registrado el 20 de mayo de este año en el bulevar Minero, el cual dejó un saldo de una mujer sin vida y a 13 personas lesionadas.</t>
+  </si>
+  <si>
+    <t>Concesiones transporte público</t>
+  </si>
+  <si>
+    <t>La Semot revocó la concesión a la unidad de la ruta Tilcuautla-Pachuca accidentada en el bulevar Minero por no contar con póliza de seguro de viajero.</t>
+  </si>
+  <si>
+    <t>Semot, PGJEH, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles Gutiérrez, Julio N.</t>
+  </si>
+  <si>
+    <t>Copriseh supervisará la venta de alimentos durante fiestas patrias</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo (SSH) y la Copriseh implementarán acciones de vigilancia y fomento sanitario en los 84 municipios de la entidad por medio de sus 12 delegaciones sanitarias durante las Fiestas Patrias 2026, dirigidas a comerciantes y manejadores de alimentos y bebidas.</t>
+  </si>
+  <si>
+    <t>Vigilancia Sanitaria</t>
+  </si>
+  <si>
+    <t>La Copriseh supervisará las condiciones sanitarias de puestos de alimentos y bebidas durante los festejos del Grito de Independencia en los 84 municipios de Hidalgo.</t>
+  </si>
+  <si>
+    <t>SSH, Copriseh, Ayuntamientos, SSPH, PC</t>
+  </si>
+  <si>
+    <t>Alberto Mercado Hernández</t>
+  </si>
+  <si>
+    <t>Charros apoyan tauromaquia ante consulta</t>
+  </si>
+  <si>
+    <t>Los charros de Pachuca manifestaron su respaldo a las corridas de toros ante la consulta sobre la tauromaquia, al considerar que existe una relación histórica y cultural entre la fiesta taurina y la charrería. Gerardo Anselmo Mejía, vicepresidente de la Asociación de Charros de Pachuca, sostuvo que el gremio respalda la tauromaquia.</t>
+  </si>
+  <si>
+    <t>Tauromaquia</t>
+  </si>
+  <si>
+    <t>La Asociación de Charros de Pachuca respaldó la continuidad de la tauromaquia ante la consulta pública, resaltando su hermandad cultural e histórica.</t>
+  </si>
+  <si>
+    <t>Gerardo Anselmo Mejía</t>
+  </si>
+  <si>
+    <t>Desmantelan un taller de regrabado en Pachuca: SSPH</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH), en coordinación con la PGJEH y la Sedena, ejecutó una orden de cateo en un inmueble del fraccionamiento Valle Diamante Plus en Pachuca, desarticulando un taller adaptado para el regrabado y clonación de documentos de identificación vehicular, deteniendo a un hombre (C. A. G. R.).</t>
+  </si>
+  <si>
+    <t>Cateo</t>
+  </si>
+  <si>
+    <t>Fuerzas de seguridad desmantelaron en Pachuca un taller clandestino de clonación de documentos vehiculares y placas robadas, arrestando a un presunto implicado.</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH, Sedena, Presidencia</t>
+  </si>
+  <si>
+    <t>C. A. G. R.</t>
+  </si>
+  <si>
+    <t>Entregarán hospital a la federación este año</t>
+  </si>
+  <si>
+    <t>Este año se terminará la transferencia del nuevo Hospital General de Pachuca al IMSS-Bienestar, ya que la Secretaría de Infraestructura sigue pasando los reportes sobre la intervención realizada en el inmueble ubicado en San Agustín Tlaxiaca, indicó la titular de la SSH, Vanesa Escalante Arroyo.</t>
+  </si>
+  <si>
+    <t>La SSH prevé concretar este año la transferencia del nuevo Hospital General de Pachuca al sistema IMSS-Bienestar tras revisiones técnicas y entrega de minutas de obra.</t>
+  </si>
+  <si>
+    <t>SSH, IMSS-Bienestar, Sipdus, Contraloría, Presidencia</t>
+  </si>
+  <si>
+    <t>Suicidios en Hidalgo aumentaron 8.2 por ciento en un año</t>
+  </si>
+  <si>
+    <t>En un año, los suicidios en Hidalgo incrementaron 8.2 por ciento; las personas adolescentes y jóvenes de entre 15 y 24 años son el grupo poblacional con más intentos de quitarse la vida, de acuerdo con datos de la Secretaría de Salud estatal (SSH), registrándose 159 casos en 2025 y más de 40 en lo que va de 2026.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo informó un alza del 8.2% en suicidios en 2025 y convocó a mesas de trabajo integrales para atender la salud mental en jóvenes y adolescentes.</t>
+  </si>
+  <si>
+    <t>Inauguran la tienda Hidarte de Tulancingo</t>
+  </si>
+  <si>
+    <t>Este lunes fue inaugurated la tienda Hidarte: Casa de las Artesanías en Tulancingo, ubicada en el Centro Cultural Ricardo Garibay, espacio que expone para su venta productos de 22 artesanas y productores de la región sin cobro de comisiones.</t>
+  </si>
+  <si>
+    <t>La alcaldía de Tulancingo y la Sebiso inauguraron la tienda Hidarte en el Centro Cultural Ricardo Garibay para comercializar piezas de 22 artesanos locales.</t>
+  </si>
+  <si>
+    <t>Mirely Santos</t>
+  </si>
+  <si>
+    <t>Bienestar, Ayuntamiento, Hidarte, Cultura</t>
+  </si>
+  <si>
+    <t>Lorena García Cázares</t>
+  </si>
+  <si>
+    <t>Impulsa Menchaca la creación de nueva estructura de transparencia en Hidalgo</t>
+  </si>
+  <si>
+    <t>Con el objetivo de fortalecer la transparencia y la protección de datos, el gobernador Julio Menchaca Salazar envió una serie de iniciativas al Congreso estatal, además de plantear medidas para fortalecer la simplificación administrativa y la transformación digital. Entre las principales propuestas se encuentra la creación del organismo denominado Transparencia para el Pueblo de Hidalgo, así como del Subsistema de Transparencia del estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca envió iniciativas al Congreso estatal para reestructurar el sistema de transparencia y protección de datos, creando Transparencia para el Pueblo de Hidalgo.</t>
+  </si>
+  <si>
+    <t>“UN MITO” QUE CARRIL CONFINADO DEL TUZOBÚS GENERE TRÁFICO EN FELIPE ÁNGELES; HARÁN ANÁLISIS</t>
+  </si>
+  <si>
+    <t>La secretaria de Movilidad y Transporte del Estado de Hidalgo (Semot), Lizbeth Robles Gutiérrez, calificó como “un mito” que el congestionamiento vehicular sobre el bulevar Felipe Ángeles sea por mantener el carril confinado del Sistema de Transporte Metropolitano (Tuzobús), al señalar que dicha medida ha logrado reducir los registros de siniestros viales, tener mayor eficiencia con el incremento del número de viajes en un 29% y la reducción de los tiempos de traslado de las personas usuarias.</t>
+  </si>
+  <si>
+    <t>La Semot defendió la permanencia del carril confinado del Tuzobús al reducir accidentes y elevar viajes 29%, anunciando el uso de Inteligencia Artificial para evaluar soluciones viales.</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah, STCH, SICT, Presidencia</t>
+  </si>
+  <si>
+    <t>Pierde concesión ruta Tilcuautla-Pachuca involucrada en accidente en Bulevar Minero</t>
+  </si>
+  <si>
+    <t>Por falta de póliza de seguro vigente, le fue retirada la concesión a la ruta del transporte público colectivo Tilcuautla-Pachuca, luego de que una de sus unidades se viera involucrada en el incidente registrado el pasado 20 de mayo sobre el bulevar Minero, en Pachuca, que dejó como saldo una persona sin vida y 17 más lesionadas.</t>
+  </si>
+  <si>
+    <t>La Semot revocó la concesión a la colectiva de la ruta Tilcuautla-Pachuca accidentada en el bulevar Minero tras confirmar que no contaba con póliza de seguro activa.</t>
+  </si>
+  <si>
+    <t>Tizayuca, entre las zonas con mayor riesgo suicida en Hidalgo</t>
+  </si>
+  <si>
+    <t>Tizayuca es identificada como una de las zonas de Hidalgo con mayor riesgo suicida, debido a la presencia de factores como violencia familiar y abandono, así se dio a conocer durante la rueda de prensa con motivo del Día Mundial de la Prevención del Suicidio. La titular de la SSH, Vanesa Escalante Arroyo, explicó que en 2024 se registraron 146 muertes por suicidio y se atendieron 1,020 intentos.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo ubicó a Tizayuca como municipio prioritario por riesgo suicida y violencia familiar, reforzando la atención en los seis centros Cecosama.</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo, Yolanda Pérez Martínez</t>
+  </si>
+  <si>
+    <t>A dos años de proceso, avanza transferencia del nuevo Hospital General Pachuca</t>
+  </si>
+  <si>
+    <t>Autoridades del IMSS-Bienestar federal realizaron dos visitas al Hospital General Pachuca, ubicado en San Agustín Tlaxiaca, como parte del proceso para concretar la transferencia del inmueble al Gobierno Federal, informó la secretaria de Salud de Hidalgo, Vanesa Escalante. El trámite para incorporar el hospital lleva alrededor de dos años.</t>
+  </si>
+  <si>
+    <t>La SSH reportó avances en las auditorías de infraestructura para completar la entrega del nuevo Hospital General de Pachuca al sistema IMSS-Bienestar federal.</t>
+  </si>
+  <si>
+    <t>DESMANTELAN CENTRO DE CLONACIÓN DE DOCUMENTACIÓN EN PACHUCA</t>
+  </si>
+  <si>
+    <t>Elementos adscritos a la Secretaría de Seguridad Pública estatal (SSPH) desmantelaron inmueble que estaba adaptado como taller de regrabado y clonación de identificaciones vehiculares en la ciudad de Pachuca. Durante el cateo en Valle Diamante Plus, detuvieron a un hombre identificado como C.A.G.R.</t>
+  </si>
+  <si>
+    <t>Fuerzas estatales y federales aseguraron en Pachuca un taller clandestino de clonación de documentos vehiculares y vehículos robados, arrestando a un sujeto.</t>
+  </si>
+  <si>
+    <t>SEMOT RETIRA CONCESIÓN A COMBI QUE DEJÓ 17 HERIDOS</t>
+  </si>
+  <si>
+    <t>A casi cuatro meses de que una camioneta particular y una unidad del transporte público se vieron involucrados en un accidente sobre el bulevar Minero, en Pachuca, la Secretaría de Movilidad y Transporte (Semot) revocó la concesión a la combi por no contar con seguro vigente.</t>
+  </si>
+  <si>
+    <t>La Semot revocó la concesión a la combi de la ruta Tilcuautla-Pachuca accidentada en el bulevar Minero tras confirmar que no contaba con seguro vehicular activo.</t>
+  </si>
+  <si>
+    <t>TRAS QUEJAS, TAXIS TENDRÁN NUEVA TARIFA EN HIDALGO</t>
+  </si>
+  <si>
+    <t>La próxima semana se dará a conocer la nueva tarifa de los taxis, luego de varios meses de análisis y de múltiples quejas por cobros excesivos, dio a conocer Lyzbeth Robles Gutiérrez, titular de la Secretaría de Movilidad y Transporte (Semot).</t>
+  </si>
+  <si>
+    <t>La Semot anunciará la próxima semana la reestructuración definitiva de las tarifas de taxi en Pachuca para evitar cobros excesivos a usuarios.</t>
+  </si>
+  <si>
+    <t>Semot, Gobernador</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles Gutiérrez, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>JULIO MENCHACA MANDA AL CONGRESO RELEVO DEL ITAIH</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar envió al Congreso de Hidalgo un paquete de iniciativas para definir cómo operará el nuevo modelo de transparencia y protección de datos personales tras la desaparición del Instituto de Transparencia, Acceso a la Información Pública Gubernamental y Protección de Datos Personales (Itaih).</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca planteó la creación de Transparencia para el Pueblo de Hidalgo y el Subsistema de Transparencia estatal tras la extinción del ITAIH.</t>
+  </si>
+  <si>
+    <t>Luis Godínez</t>
+  </si>
+  <si>
+    <t>ABRIR EL CARRIL CONFINADO NO AMINORARÁ EL TRÁFICO: SEMOT</t>
+  </si>
+  <si>
+    <t>La secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez, consideró que es un 'mito' que el carril confinado del Sistema de Transporte Metropolitano genera tráfico en el sur de Pachuca. En tanto, el oficial mayor, Edgar Orlando Ángeles Pérez, anunció que se instalarán cámaras con inteligencia artificial sobre el bulevar Felipe Ángeles.</t>
+  </si>
+  <si>
+    <t>La Semot sostuvo que el carril exclusivo del Tuzobús protege a más de 91 mil usuarios diarios y Oficialía Mayor probará cámaras con Inteligencia Artificial para medir el tránsito viales.</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah, Oficialía Mayor, PGJEH</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles Gutiérrez, Edgar Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>BUSCA SNTE HIDALGO BLINDAR AUTONOMÍA</t>
+  </si>
+  <si>
+    <t>Ante la posibilidad de que el periodo de la actual dirigencia de la sección XV del SNTE en Hidalgo se extienda por un año, el secretario general, Said Vargas Sáenz, argumentó que el propósito es blindar la autonomía sindical para evitar injerencias políticas rumbo a las elecciones de 2027.</t>
+  </si>
+  <si>
+    <t>Dirigencia Partidista</t>
+  </si>
+  <si>
+    <t>El dirigente de la Sección XV del SNTE, Said Vargas, afirmó que la extensión de su gestión busca blindar al sindicato magisterial frente al proceso electoral de 2027.</t>
+  </si>
+  <si>
+    <t>Said Vargas Sáenz</t>
+  </si>
+  <si>
+    <t>REPORTAN 40 SUICIDIOS EN HIDALGO EN LO QUE VA DE 2026</t>
+  </si>
+  <si>
+    <t>La secretaria de Salud en la entidad, Vanesa Escalante Arroyo, dio a conocer que en lo que va del año se han registrado 40 suicidios en Hidalgo, concentrándose la mayor incidencia en adolescentes de 15 a 19 años en municipios metropolitanos.</t>
+  </si>
+  <si>
+    <t>La SSH contabilizó 40 decesos por suicidio en Hidalgo durante 2026 e hizo un llamado a aprovechar la atención psicológica gratuita en los seis centros Cecosama del estado.</t>
+  </si>
+  <si>
+    <t>TRAS 4 AÑOS, NUEVO HOSPITAL GENERAL DE PACHUCA PASARÁ AL IMSS-BIENESTAR</t>
+  </si>
+  <si>
+    <t>A casi cuatro años de su inauguración, la Secretaría de Salud de Hidalgo está por concretar formalmente la transferencia de los servicios del nuevo Hospital General de Pachuca al IMSS-Bienestar federal para su conclusión y puesta en marcha.</t>
+  </si>
+  <si>
+    <t>La SSH afina detalles de las minutas de obra y revisiones técnicas para transferir el nuevo Hospital General de Pachuca al esquema IMSS-Bienestar federal.</t>
+  </si>
+  <si>
+    <t>INAUGURAN LA TIENDA HIDARTE TULANCINGO</t>
+  </si>
+  <si>
+    <t>Con 22 expositores abrió sus puertas la Tienda Hidarte en el Centro Cultural Ricardo Garibay de Tulancingo, impulsada por Sebiso y el gobierno municipal para comercializar piezas artesanales sin cobro de comisión.</t>
+  </si>
+  <si>
+    <t>La Sebiso y la alcaldía de Tulancingo inauguraron la sucursal de Hidarte en el Centro Cultural Garibay para proyectar las creaciones de 22 artesanos locales.</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno, Lorena García Cázares, Minerva Rosales Gayosso, José Antonio Rodríguez Arango</t>
+  </si>
+  <si>
+    <t>DEMANDAN MAYOR SEGURIDAD TRAS EL INCENDIO DE UNIDAD</t>
+  </si>
+  <si>
+    <t>Integrantes de la Asociación Certeza, Progreso y Desarrollo para Todos se reunieron con el alcalde de Tlanchinol, Gabino Hernández Vite, para pedir reforzar la vigilancia tras el incendio intencional de la camioneta de su dirigente, Onésimo Pérez Lara, quien presentó denuncia ante el MP.</t>
+  </si>
+  <si>
+    <t>Integrantes de una organización social de Tlanchinol solicitaron reforzar la seguridad municipal tras el atentado incendiario contra el vehículo de su presidente Onésimo Pérez.</t>
+  </si>
+  <si>
+    <t>Onésimo Pérez Lara, Gabino Hernández Vite</t>
+  </si>
+  <si>
+    <t>Copriseh realizará revisiones de fomento sanitario</t>
+  </si>
+  <si>
+    <t>Con motivo de las fiestas patrias, la Comisión para la Protección contra Riesgos Sanitarios del Estado de Hidalgo (Copriseh) implementará acciones de vigilancia y fomento sanitario en los 84 municipios de la entidad, con el propósito de prevenir riesgos y proteger la salud de la población en establecimientos de alimentos y bebidas.</t>
+  </si>
+  <si>
+    <t>La Copriseh desplegará operativos de fomento y vigilancia sanitaria en puestos de alimentos y bebidas en los 84 municipios por las Fiestas Patrias.</t>
+  </si>
+  <si>
+    <t>SSH, Copriseh, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>PC estatal recomienda evitar el uso de pirotecnia</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos del Estado exhortó a la población a evitar el uso de pirotecnia en Fiestas Patrias, destacando que en septiembre las lesiones por quemaduras aumentan 300%. Asimismo, recordó que realizar disparos al aire constituye un delito grave.</t>
+  </si>
+  <si>
+    <t>Pirotecnia</t>
+  </si>
+  <si>
+    <t>Protección Civil de Hidalgo exhortó a suspender la quema de pirotecnia por el incremento del 300% en quemaduras durante septiembre e inhibir disparos al aire.</t>
+  </si>
+  <si>
+    <t>Ana Luisa Vega</t>
+  </si>
+  <si>
+    <t>Segobh, PC, SSPH</t>
+  </si>
+  <si>
+    <t>Remodelarán estaciones de transporte metropolitano</t>
+  </si>
+  <si>
+    <t>El oficial mayor del gobierno estatal, Edgar Orlando Ángeles Pérez, informó que las 34 estaciones del Transporte Metropolitano (Tuzobús) serán remodeladas tras concluir el proyecto ejecutivo, licitándose a finales de septiembre para arrancar en octubre, destacando que el flujo diario subió a 91,923 pasajeros.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor licitará la rehabilitación de las 34 estaciones del Tuzobús en octubre e informó que la afluencia diaria creció 34%, alcanzando los 91,923 usuarios.</t>
+  </si>
+  <si>
+    <t>Oscar Raúl Pérez</t>
+  </si>
+  <si>
+    <t>Edgar Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad, detalló operativos ejecutados en 14 municipios de Hidalgo</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca y el Gabinete de Seguridad reportaron la detención de 24 personas en 14 municipios, el decomiso de 4,521 dosis de narcóticos, armas y vehículos, la desarticulación de narcomenudeo en Tepeapulco y huachicol en Tizayuca y Tepetitlán, la localización de 21 personas desaparecidas y el despliegue de 5 mil policías para Fiestas Patrias.</t>
+  </si>
+  <si>
+    <t>Operativo de Seguridad</t>
+  </si>
+  <si>
+    <t>El Gabinete de Seguridad de Hidalgo informó la captura de 24 personas, decomisos de droga y huachicol en 14 municipios, y el despliegue de 5 mil policías para Fiestas Patrias.</t>
+  </si>
+  <si>
+    <t>SSPH, Gobernador, PGJEH, Gabinete de Seguridad, CBPEH</t>
+  </si>
+  <si>
+    <t>SSPH desmantela local; clonaban identificaciones vehiculares</t>
+  </si>
+  <si>
+    <t>La SSPH, PGJEH y Sedena ejecutaron un cateo en un inmueble del fraccionamiento Valle Diamante Plus en Pachuca, desarticulando un taller de regrabado y clonación de placas, licencias y tarjetas de circulación, arrestando a C. A. G. R..</t>
+  </si>
+  <si>
+    <t>Fuerzas estatales y federales aseguraron en Pachuca un taller clandestino de clonación de placas y documentos vehiculares, arrestando a un presunto implicado.</t>
+  </si>
+  <si>
+    <t>Desfilan charros por calles de Pachuca</t>
+  </si>
+  <si>
+    <t>Cerca de un centenar de charros y escaramuzas tomaron las calles del centro de Pachuca para conmemorar el Día Nacional del Charro. El contingente partió del Estadio Revolución, recorrió avenidas principales como Allende, Matamoros, Guerrero y rodó la explanada del Reloj Monumental antes de concluir en el Lienzo Charro de Pachuca.</t>
+  </si>
+  <si>
+    <t>Charros y escaramuzas desfilaron por las principales calles del centro histórico de Pachuca para conmemorar el Día Nacional del Charro.</t>
+  </si>
+  <si>
+    <t>MEXE SOSTIENE PROTESTA POR MUERTE DE NORMALISTA</t>
+  </si>
+  <si>
+    <t>Estudiantes de la Escuela Normal Rural Luis Villarreal 'El Mexe' mantuvieron una manifestación pacífica en las inmediaciones de la PGJEH en Pachuca para dar seguimiento al caso del homicidio de su compañero. Tras reunirse con autoridades ministeriales, acordaron mesas de trabajo semanales para revisar los avances de la carpeta de investigación.</t>
+  </si>
+  <si>
+    <t>Normalistas de El Mexe protestaron frente a la PGJEH para exigir justicia por el homicidio de un compañero y acordaron reuniones semanales de seguimiento.</t>
+  </si>
+  <si>
+    <t>Erick Perales</t>
+  </si>
+  <si>
+    <t>PGJEH, Presidencia, SEPH</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum Pardo, Alejandro Moreno Cárdenas</t>
+  </si>
+  <si>
+    <t>QUITAN CONCESIÓN TRAS ACCIDENTE EN BULEVAR EL MINERO</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte de Hidalgo (Semot) revocó la concesión a una Urvan de la ruta Tilcuautla-Pachuca tras confirmar que circulaba sin póliza de seguro vigente al momento de volcarse sobre el bulevar Minero el pasado 20 de mayo, percance que dejó un saldo de un fallecido y 17 lesionados.</t>
+  </si>
+  <si>
+    <t>La Semot retiró la concesión a la colectivo de la ruta Tilcuautla-Pachuca involucrada en un accidente en el bulevar Minero por no contar con póliza de seguro activa.</t>
+  </si>
+  <si>
+    <t>USARÁN IA PARA RESOLVER TRÁFICO AL SUR DE PACHUCA</t>
+  </si>
+  <si>
+    <t>El gobierno de Hidalgo invertirá hasta 600 mil pesos en la instalación de tres cámaras dotadas con Inteligencia Artificial en puentes peatonales del bulevar Felipe Ángeles para analizar el flujo vehicular en tiempo real hacia la CDMX. Asimismo, la Semot reportó un aumento del 34% en usuarios diarios del Tuzobús.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor colocará tres cámaras con IA en el bulevar Felipe Ángeles para evaluar soluciones viales, reportando además 91 mil usuarios diarios en el Tuzobús.</t>
+  </si>
+  <si>
+    <t>CLONABAN DOCUMENTOS VEHICULARES EN PACHUCA</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH), en coordinación con la PGJEH y la Sedena, cateó y desmanteló una vivienda en el fraccionamiento Valle Diamante Plus en Pachuca adaptada como taller clandestino de clonación de placas, licencias y tarjetas de circulación, arrestando a un hombre (C. A. G. R.).</t>
+  </si>
+  <si>
+    <t>Fuerzas de seguridad desmantelaron un taller de clonación de placas y documentos vehiculares en Valle Diamante Plus de Pachuca, capturando a un presunto implicado.</t>
+  </si>
+  <si>
+    <t>El edificio de la escuela primaria Aquiles Serdán en Tulancingo deberá ser demolido y reconstruido en su totalidad debido a fallas estructurales severas. El secretario de Educación, Natividad Castrejón, indicó que los trabajos requerirán todo el ciclo escolar 2026-2027 y se evalúan opciones presenciales o híbridas para las clases.</t>
+  </si>
+  <si>
+    <t>La SEPH demolerá y reconstruirá completamente la primaria Aquiles Serdán en Tulancingo tras detectar daños estructurales en el inmueble.</t>
   </si>
 </sst>
 </file>
@@ -1392,8 +1347,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ56" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ56" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ59" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ59" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1825,7 +1780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1974,28 +1929,28 @@
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>102</v>
+      <c r="D2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="F2" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G2">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R2">
@@ -2004,76 +1959,76 @@
       <c r="S2">
         <v>13262</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W2" t="s">
-        <v>93</v>
-      </c>
-      <c r="X2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="W2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" t="s">
-        <v>69</v>
+      <c r="Z2" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA2">
         <v>20</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>106</v>
+      <c r="AF2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" t="s">
-        <v>108</v>
+      <c r="D3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="F3" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
-      <c r="H3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" t="s">
-        <v>42</v>
+      <c r="H3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2081,76 +2036,76 @@
       <c r="S3">
         <v>13262</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W3" t="s">
-        <v>109</v>
-      </c>
-      <c r="X3" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="W3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA3">
-        <v>15</v>
-      </c>
-      <c r="AB3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AC3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AG3" t="s">
+      <c r="AF3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>113</v>
+      <c r="AH3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" t="s">
-        <v>115</v>
+      <c r="D4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="F4" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G4">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" t="s">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2158,75 +2113,75 @@
       <c r="S4">
         <v>13262</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W4" t="s">
-        <v>116</v>
-      </c>
-      <c r="X4" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="W4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA4">
-        <v>24</v>
-      </c>
-      <c r="AB4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AG4" t="s">
+      <c r="AF4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AJ4" t="s">
+      <c r="AH4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI4" s="2" t="s">
         <v>121</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="E5" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="F5" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R5">
@@ -2235,75 +2190,75 @@
       <c r="S5">
         <v>13262</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V5" t="s">
+      <c r="V5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA5">
+        <v>20</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="X5" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA5">
-        <v>24</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>96</v>
+      <c r="AI5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" t="s">
-        <v>126</v>
+      <c r="A6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="F6" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G6">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R6">
@@ -2312,76 +2267,76 @@
       <c r="S6">
         <v>13262</v>
       </c>
-      <c r="T6" t="s">
+      <c r="T6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V6" t="s">
+      <c r="V6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W6" t="s">
-        <v>93</v>
-      </c>
-      <c r="X6" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y6" t="s">
+      <c r="W6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z6" t="s">
-        <v>69</v>
+      <c r="Z6" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA6">
-        <v>20</v>
-      </c>
-      <c r="AB6" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AC6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AG6" t="s">
+      <c r="AF6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>106</v>
+      <c r="AH6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" t="s">
-        <v>131</v>
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="F7" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I7" t="s">
-        <v>42</v>
+      <c r="I7" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2389,76 +2344,76 @@
       <c r="S7">
         <v>13262</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V7" t="s">
-        <v>85</v>
-      </c>
-      <c r="W7" t="s">
-        <v>132</v>
-      </c>
-      <c r="X7" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y7" t="s">
+      <c r="V7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="Z7" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA7">
         <v>24</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AB7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AC7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AD7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF7" t="s">
-        <v>128</v>
-      </c>
-      <c r="AG7" t="s">
+      <c r="AF7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>135</v>
+      <c r="AH7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" t="s">
-        <v>137</v>
+      <c r="A8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="F8" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G8">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" t="s">
-        <v>49</v>
+        <v>9</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2466,75 +2421,75 @@
       <c r="S8">
         <v>13262</v>
       </c>
-      <c r="T8" t="s">
+      <c r="T8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V8" t="s">
+      <c r="V8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W8" t="s">
-        <v>139</v>
-      </c>
-      <c r="X8" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y8" t="s">
+      <c r="W8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="Z8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA8">
         <v>20</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AB8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AC8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AD8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>141</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>142</v>
+      <c r="AF8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" t="s">
-        <v>144</v>
+      <c r="A9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="F9" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G9">
-        <v>4</v>
-      </c>
-      <c r="H9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="R9">
@@ -2543,75 +2498,75 @@
       <c r="S9">
         <v>13262</v>
       </c>
-      <c r="T9" t="s">
+      <c r="T9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V9" t="s">
+      <c r="V9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W9" t="s">
-        <v>145</v>
-      </c>
-      <c r="X9" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z9" t="s">
+      <c r="W9" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA9">
-        <v>15</v>
-      </c>
-      <c r="AB9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AC9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG9" t="s">
+      <c r="AF9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>148</v>
+      <c r="AH9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10" t="s">
-        <v>150</v>
+      <c r="A10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="F10" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G10">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R10">
@@ -2620,75 +2575,73 @@
       <c r="S10">
         <v>13262</v>
       </c>
-      <c r="T10" t="s">
+      <c r="T10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V10" t="s">
+      <c r="V10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W10" t="s">
-        <v>151</v>
-      </c>
-      <c r="X10" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y10" t="s">
+      <c r="W10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z10" t="s">
-        <v>69</v>
+      <c r="Z10" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA10">
-        <v>24</v>
-      </c>
-      <c r="AB10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AC10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AD10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF10" t="s">
+      <c r="AF10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AG10" t="s">
+      <c r="AG10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AH10" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>153</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>154</v>
-      </c>
+      <c r="AH10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ10" s="2"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>156</v>
+      <c r="A11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="F11" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G11">
-        <v>8</v>
-      </c>
-      <c r="H11" t="s">
-        <v>157</v>
-      </c>
-      <c r="I11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R11">
@@ -2697,73 +2650,76 @@
       <c r="S11">
         <v>13262</v>
       </c>
-      <c r="T11" t="s">
+      <c r="T11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V11" t="s">
+      <c r="V11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W11" t="s">
-        <v>158</v>
-      </c>
-      <c r="X11" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>43</v>
+      <c r="W11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA11">
-        <v>10</v>
-      </c>
-      <c r="AB11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AC11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>160</v>
+      <c r="AF11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" t="s">
-        <v>162</v>
+      <c r="A12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="F12" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G12">
-        <v>8</v>
-      </c>
-      <c r="H12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I12" t="s">
-        <v>42</v>
+      <c r="I12" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2771,72 +2727,78 @@
       <c r="S12">
         <v>13262</v>
       </c>
-      <c r="T12" t="s">
+      <c r="T12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V12" t="s">
-        <v>37</v>
-      </c>
-      <c r="W12" t="s">
-        <v>163</v>
-      </c>
-      <c r="X12" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z12" t="s">
+      <c r="V12" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z12" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA12">
-        <v>10</v>
-      </c>
-      <c r="AB12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AC12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD12" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF12" t="s">
+      <c r="AE12" t="s">
+        <v>170</v>
+      </c>
+      <c r="AF12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AG12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AH12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>165</v>
+      <c r="AH12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>166</v>
-      </c>
-      <c r="E13" t="s">
-        <v>167</v>
+      <c r="A13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="F13" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G13">
-        <v>6</v>
-      </c>
-      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R13">
@@ -2845,75 +2807,75 @@
       <c r="S13">
         <v>13262</v>
       </c>
-      <c r="T13" t="s">
+      <c r="T13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V13" t="s">
+      <c r="V13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W13" t="s">
-        <v>151</v>
-      </c>
-      <c r="X13" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y13" t="s">
+      <c r="W13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z13" t="s">
-        <v>43</v>
+      <c r="Z13" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA13">
-        <v>20</v>
-      </c>
-      <c r="AB13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AC13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD13" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG13" t="s">
+      <c r="AF13" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH13" t="s">
-        <v>170</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>172</v>
+      <c r="AH13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" t="s">
-        <v>174</v>
+      <c r="A14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="F14" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G14">
-        <v>7</v>
-      </c>
-      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R14">
@@ -2922,76 +2884,76 @@
       <c r="S14">
         <v>13262</v>
       </c>
-      <c r="T14" t="s">
+      <c r="T14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V14" t="s">
+      <c r="V14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W14" t="s">
-        <v>93</v>
-      </c>
-      <c r="X14" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y14" t="s">
+      <c r="W14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z14" t="s">
-        <v>69</v>
+      <c r="Z14" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA14">
-        <v>20</v>
-      </c>
-      <c r="AB14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AC14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AD14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF14" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG14" t="s">
+      <c r="AF14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH14" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>106</v>
+      <c r="AH14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>177</v>
-      </c>
-      <c r="E15" t="s">
-        <v>178</v>
+      <c r="A15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="F15" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G15">
-        <v>7</v>
-      </c>
-      <c r="H15" t="s">
-        <v>179</v>
-      </c>
-      <c r="I15" t="s">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2999,76 +2961,76 @@
       <c r="S15">
         <v>13262</v>
       </c>
-      <c r="T15" t="s">
+      <c r="T15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V15" t="s">
+      <c r="V15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W15" t="s">
-        <v>109</v>
-      </c>
-      <c r="X15" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y15" t="s">
+      <c r="W15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="Z15" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA15">
         <v>20</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AB15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AC15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AD15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG15" t="s">
+      <c r="AF15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>181</v>
-      </c>
-      <c r="AJ15" t="s">
+      <c r="AH15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI15" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>183</v>
-      </c>
-      <c r="E16" t="s">
-        <v>184</v>
+      <c r="A16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="F16" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G16">
-        <v>10</v>
-      </c>
-      <c r="H16" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" t="s">
-        <v>42</v>
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3076,73 +3038,76 @@
       <c r="S16">
         <v>13262</v>
       </c>
-      <c r="T16" t="s">
+      <c r="T16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V16" t="s">
+      <c r="V16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W16" t="s">
-        <v>185</v>
-      </c>
-      <c r="X16" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y16" t="s">
+      <c r="W16" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z16" t="s">
-        <v>43</v>
+      <c r="Z16" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA16">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AC16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>187</v>
-      </c>
-      <c r="AG16" t="s">
+      <c r="AF16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH16" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>188</v>
+      <c r="AH16" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>189</v>
-      </c>
-      <c r="E17" t="s">
-        <v>190</v>
+      <c r="A17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="F17" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G17">
-        <v>10</v>
-      </c>
-      <c r="H17" t="s">
-        <v>191</v>
-      </c>
-      <c r="I17" t="s">
-        <v>42</v>
+        <v>2</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3150,75 +3115,75 @@
       <c r="S17">
         <v>13262</v>
       </c>
-      <c r="T17" t="s">
+      <c r="T17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V17" t="s">
+      <c r="V17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W17" t="s">
-        <v>192</v>
-      </c>
-      <c r="X17" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y17" t="s">
+      <c r="W17" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z17" t="s">
-        <v>43</v>
+      <c r="Z17" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA17">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AC17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AD17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF17" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG17" t="s">
+      <c r="AF17" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH17" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>194</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>195</v>
+      <c r="AH17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI17" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" t="s">
-        <v>196</v>
-      </c>
-      <c r="E18" t="s">
-        <v>197</v>
+      <c r="A18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="F18" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
-      <c r="H18" t="s">
-        <v>61</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="H18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R18">
@@ -3227,76 +3192,76 @@
       <c r="S18">
         <v>13262</v>
       </c>
-      <c r="T18" t="s">
+      <c r="T18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V18" t="s">
+      <c r="V18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W18" t="s">
-        <v>198</v>
-      </c>
-      <c r="X18" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y18" t="s">
+      <c r="W18" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z18" t="s">
-        <v>69</v>
+      <c r="Z18" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA18">
         <v>20</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AB18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AC18" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AD18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF18" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>200</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>201</v>
+      <c r="AF18" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI18" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" t="s">
-        <v>202</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="A19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>203</v>
       </c>
+      <c r="E19" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="F19" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G19">
-        <v>2</v>
-      </c>
-      <c r="H19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I19" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3304,76 +3269,76 @@
       <c r="S19">
         <v>13262</v>
       </c>
-      <c r="T19" t="s">
+      <c r="T19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V19" t="s">
-        <v>64</v>
-      </c>
-      <c r="W19" t="s">
-        <v>204</v>
-      </c>
-      <c r="X19" t="s">
+      <c r="V19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="X19" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="Y19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="Z19" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA19">
-        <v>15</v>
-      </c>
-      <c r="AB19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AC19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AD19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF19" t="s">
+      <c r="AF19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AG19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI19" t="s">
+      <c r="AG19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI19" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>207</v>
+      <c r="AJ19" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="A20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E20" t="s">
-        <v>209</v>
-      </c>
       <c r="F20" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" t="s">
-        <v>49</v>
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3381,76 +3346,76 @@
       <c r="S20">
         <v>13262</v>
       </c>
-      <c r="T20" t="s">
+      <c r="T20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V20" t="s">
+      <c r="V20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W20" t="s">
+      <c r="W20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA20">
+        <v>10</v>
+      </c>
+      <c r="AB20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI20" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="X20" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA20">
-        <v>20</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>213</v>
+      <c r="AJ20" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" t="s">
-        <v>214</v>
-      </c>
-      <c r="E21" t="s">
-        <v>215</v>
+      <c r="A21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="F21" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G21">
-        <v>3</v>
-      </c>
-      <c r="H21" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" t="s">
-        <v>49</v>
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3458,76 +3423,74 @@
       <c r="S21">
         <v>13262</v>
       </c>
-      <c r="T21" t="s">
+      <c r="T21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V21" t="s">
+      <c r="V21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W21" t="s">
-        <v>93</v>
-      </c>
-      <c r="X21" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>69</v>
+      <c r="W21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA21">
-        <v>24</v>
-      </c>
-      <c r="AB21" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AC21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AD21" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF21" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>218</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>106</v>
-      </c>
+      <c r="AF21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="AJ21" s="2"/>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" t="s">
-        <v>219</v>
-      </c>
-      <c r="E22" t="s">
-        <v>220</v>
+      <c r="A22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="F22" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G22">
-        <v>3</v>
-      </c>
-      <c r="H22" t="s">
-        <v>157</v>
-      </c>
-      <c r="I22" t="s">
-        <v>49</v>
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3535,76 +3498,76 @@
       <c r="S22">
         <v>13262</v>
       </c>
-      <c r="T22" t="s">
+      <c r="T22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V22" t="s">
+      <c r="V22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W22" t="s">
-        <v>158</v>
-      </c>
-      <c r="X22" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y22" t="s">
+      <c r="W22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z22" t="s">
-        <v>43</v>
+      <c r="Z22" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA22">
         <v>20</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AB22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC22" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD22" t="s">
+      <c r="AC22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF22" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG22" t="s">
+      <c r="AD22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="AG22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH22" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>160</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>222</v>
+      <c r="AH22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" t="s">
-        <v>223</v>
-      </c>
-      <c r="E23" t="s">
-        <v>224</v>
+      <c r="A23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F23" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G23">
-        <v>4</v>
-      </c>
-      <c r="H23" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I23" t="s">
-        <v>42</v>
+      <c r="I23" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -3612,73 +3575,74 @@
       <c r="S23">
         <v>13262</v>
       </c>
-      <c r="T23" t="s">
+      <c r="T23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V23" t="s">
+      <c r="V23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W23" t="s">
-        <v>83</v>
-      </c>
-      <c r="X23" t="s">
-        <v>225</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>69</v>
+      <c r="W23" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA23">
-        <v>40</v>
-      </c>
-      <c r="AB23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC23" t="s">
+      <c r="AC23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD23" t="s">
+      <c r="AD23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF23" t="s">
-        <v>226</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>227</v>
-      </c>
+      <c r="AF23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ23" s="2"/>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E24" t="s">
-        <v>229</v>
+      <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="F24" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G24">
-        <v>4</v>
-      </c>
-      <c r="H24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" t="s">
-        <v>42</v>
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -3686,76 +3650,76 @@
       <c r="S24">
         <v>13262</v>
       </c>
-      <c r="T24" t="s">
+      <c r="T24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V24" t="s">
+      <c r="V24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W24" t="s">
-        <v>109</v>
-      </c>
-      <c r="X24" t="s">
-        <v>230</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z24" t="s">
+      <c r="W24" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z24" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA24">
-        <v>20</v>
-      </c>
-      <c r="AB24" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB24" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AC24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AD24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF24" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>231</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>232</v>
+      <c r="AF24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E25" t="s">
-        <v>234</v>
+      <c r="A25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="F25" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G25">
-        <v>6</v>
-      </c>
-      <c r="H25" t="s">
-        <v>45</v>
-      </c>
-      <c r="I25" t="s">
-        <v>50</v>
+        <v>3</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -3763,75 +3727,75 @@
       <c r="S25">
         <v>13262</v>
       </c>
-      <c r="T25" t="s">
+      <c r="T25" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V25" t="s">
+      <c r="V25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W25" t="s">
-        <v>235</v>
-      </c>
-      <c r="X25" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y25" t="s">
+      <c r="W25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="Z25" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA25">
         <v>20</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AB25" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AC25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="AD25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF25" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>237</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>106</v>
+      <c r="AF25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" t="s">
-        <v>238</v>
-      </c>
-      <c r="E26" t="s">
-        <v>239</v>
+      <c r="A26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="F26" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G26">
-        <v>6</v>
-      </c>
-      <c r="H26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R26">
@@ -3840,75 +3804,75 @@
       <c r="S26">
         <v>13262</v>
       </c>
-      <c r="T26" t="s">
+      <c r="T26" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V26" t="s">
+      <c r="V26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W26" t="s">
-        <v>93</v>
-      </c>
-      <c r="X26" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y26" t="s">
+      <c r="W26" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z26" t="s">
-        <v>69</v>
+      <c r="Z26" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AA26">
-        <v>20</v>
-      </c>
-      <c r="AB26" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AC26" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AD26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF26" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG26" t="s">
+      <c r="AF26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH26" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>242</v>
+      <c r="AH26" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI26" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" t="s">
-        <v>243</v>
-      </c>
-      <c r="E27" t="s">
-        <v>244</v>
+      <c r="A27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="F27" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G27">
-        <v>7</v>
-      </c>
-      <c r="H27" t="s">
-        <v>245</v>
-      </c>
-      <c r="I27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>42</v>
       </c>
       <c r="R27">
@@ -3917,76 +3881,76 @@
       <c r="S27">
         <v>13262</v>
       </c>
-      <c r="T27" t="s">
+      <c r="T27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V27" t="s">
+      <c r="V27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W27" t="s">
-        <v>87</v>
-      </c>
-      <c r="X27" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y27" t="s">
+      <c r="W27" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="Z27" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA27">
         <v>20</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AB27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AC27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AD27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF27" t="s">
-        <v>247</v>
-      </c>
-      <c r="AG27" t="s">
+      <c r="AF27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH27" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>248</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>249</v>
+      <c r="AH27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI27" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" t="s">
-        <v>250</v>
-      </c>
-      <c r="E28" t="s">
-        <v>251</v>
+      <c r="A28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="F28" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G28">
-        <v>9</v>
-      </c>
-      <c r="H28" t="s">
-        <v>191</v>
-      </c>
-      <c r="I28" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -3994,75 +3958,75 @@
       <c r="S28">
         <v>13262</v>
       </c>
-      <c r="T28" t="s">
+      <c r="T28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V28" t="s">
+      <c r="V28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W28" t="s">
-        <v>192</v>
-      </c>
-      <c r="X28" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y28" t="s">
+      <c r="W28" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="Y28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="Z28" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA28">
-        <v>20</v>
-      </c>
-      <c r="AB28" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB28" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC28" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD28" t="s">
+      <c r="AC28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF28" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI28" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>195</v>
+      <c r="AD28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI28" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="AJ28" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" t="s">
-        <v>253</v>
-      </c>
-      <c r="E29" t="s">
-        <v>254</v>
+      <c r="A29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="F29" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G29">
-        <v>10</v>
-      </c>
-      <c r="H29" t="s">
-        <v>138</v>
-      </c>
-      <c r="I29" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R29">
@@ -4071,75 +4035,75 @@
       <c r="S29">
         <v>13262</v>
       </c>
-      <c r="T29" t="s">
+      <c r="T29" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V29" t="s">
+      <c r="V29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W29" t="s">
-        <v>139</v>
-      </c>
-      <c r="X29" t="s">
-        <v>255</v>
-      </c>
-      <c r="Y29" t="s">
+      <c r="W29" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="Z29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA29">
         <v>20</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AB29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AC29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD29" t="s">
+      <c r="AD29" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF29" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI29" t="s">
-        <v>256</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>257</v>
+      <c r="AF29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" t="s">
-        <v>258</v>
-      </c>
-      <c r="E30" t="s">
-        <v>259</v>
+      <c r="A30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="F30" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G30">
-        <v>8</v>
-      </c>
-      <c r="H30" t="s">
+        <v>6</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="2" t="s">
         <v>49</v>
       </c>
       <c r="R30">
@@ -4148,76 +4112,76 @@
       <c r="S30">
         <v>13262</v>
       </c>
-      <c r="T30" t="s">
+      <c r="T30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V30" t="s">
+      <c r="V30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W30" t="s">
+      <c r="W30" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA30">
+        <v>20</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI30" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AJ30" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="X30" t="s">
-        <v>261</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA30">
-        <v>10</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH30" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F31" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4232,19 +4196,19 @@
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA31">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB31" s="2" t="s">
         <v>58</v>
@@ -4256,45 +4220,45 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>267</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F32" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4309,19 +4273,19 @@
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>270</v>
+        <v>76</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="Y32" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA32">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>58</v>
@@ -4333,45 +4297,45 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>272</v>
+        <v>92</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>273</v>
+        <v>186</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>274</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F33" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G33">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4386,19 +4350,19 @@
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="Y33" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="AA33">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>58</v>
@@ -4410,42 +4374,42 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F34" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>49</v>
@@ -4463,16 +4427,16 @@
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="Y34" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA34">
         <v>20</v>
@@ -4481,46 +4445,48 @@
         <v>58</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AJ34" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="AJ34" s="2" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F35" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>49</v>
@@ -4538,19 +4504,19 @@
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AA35">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AB35" s="2" t="s">
         <v>58</v>
@@ -4562,45 +4528,45 @@
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>288</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F36" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4615,19 +4581,19 @@
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="Y36" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="AA36">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>58</v>
@@ -4639,45 +4605,45 @@
         <v>44</v>
       </c>
       <c r="AF36" s="2" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F37" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G37">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>294</v>
+        <v>71</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4692,64 +4658,66 @@
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC37" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD37" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="AJ37" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="AJ37" s="2" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F38" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G38">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>49</v>
@@ -4767,19 +4735,19 @@
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>58</v>
@@ -4791,43 +4759,45 @@
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="AJ38" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="AJ38" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="F39" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -4842,16 +4812,16 @@
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="Y39" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA39">
         <v>20</v>
@@ -4866,37 +4836,39 @@
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AG39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="AJ39" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="AJ39" s="2" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="F40" s="1">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>45</v>
@@ -4917,10 +4889,10 @@
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>309</v>
+        <v>240</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="Y40" s="2" t="s">
         <v>57</v>
@@ -4941,45 +4913,45 @@
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AG40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>311</v>
+        <v>242</v>
       </c>
       <c r="AJ40" s="2" t="s">
-        <v>312</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="F41" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -4994,19 +4966,19 @@
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>315</v>
+        <v>146</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="Y41" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="AA41">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>58</v>
@@ -5018,37 +4990,39 @@
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>272</v>
+        <v>39</v>
       </c>
       <c r="AG41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="AJ41" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="AJ41" s="2" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="F42" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G42">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>61</v>
@@ -5069,16 +5043,16 @@
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>320</v>
+        <v>112</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="Y42" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AA42">
         <v>24</v>
@@ -5093,40 +5067,42 @@
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="AG42" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AJ42" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="AJ42" s="2" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F43" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G43">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>49</v>
@@ -5144,19 +5120,19 @@
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>325</v>
+        <v>194</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="Y43" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA43">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>58</v>
@@ -5168,45 +5144,45 @@
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>272</v>
+        <v>39</v>
       </c>
       <c r="AG43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="AJ43" s="2" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="F44" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>61</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -5221,19 +5197,19 @@
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="Y44" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AA44">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB44" s="2" t="s">
         <v>58</v>
@@ -5245,42 +5221,42 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>333</v>
+        <v>46</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="F45" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>42</v>
@@ -5298,10 +5274,10 @@
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>337</v>
+        <v>76</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>57</v>
@@ -5316,49 +5292,51 @@
         <v>58</v>
       </c>
       <c r="AC45" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AG45" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AJ45" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="AJ45" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="F46" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -5373,19 +5351,19 @@
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>342</v>
+        <v>179</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="Y46" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA46">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB46" s="2" t="s">
         <v>58</v>
@@ -5397,7 +5375,7 @@
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AG46" s="2" t="s">
         <v>40</v>
@@ -5406,31 +5384,33 @@
         <v>47</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AJ46" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="AJ46" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="F47" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>49</v>
@@ -5448,16 +5428,16 @@
         <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="Y47" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AA47">
         <v>24</v>
@@ -5472,45 +5452,45 @@
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AG47" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>348</v>
+        <v>272</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="F48" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5525,10 +5505,10 @@
         <v>37</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>352</v>
+        <v>96</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>57</v>
@@ -5549,42 +5529,42 @@
         <v>44</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AG48" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>355</v>
+        <v>80</v>
       </c>
       <c r="AJ48" s="2" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="F49" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="G49">
         <v>3</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>49</v>
@@ -5602,10 +5582,10 @@
         <v>37</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>359</v>
+        <v>246</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>57</v>
@@ -5614,57 +5594,55 @@
         <v>43</v>
       </c>
       <c r="AA49">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB49" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC49" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD49" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>361</v>
+        <v>47</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="AJ49" s="2" t="s">
-        <v>363</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="AJ49" s="2"/>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="F50" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>61</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -5676,66 +5654,64 @@
         <v>60</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA50">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB50" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC50" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD50" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>41</v>
+        <v>338</v>
       </c>
       <c r="AG50" s="2" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AJ50" s="2" t="s">
-        <v>367</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="AJ50" s="2"/>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="F51" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>45</v>
@@ -5756,16 +5732,16 @@
         <v>37</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="Y51" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z51" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AA51">
         <v>24</v>
@@ -5780,42 +5756,42 @@
         <v>44</v>
       </c>
       <c r="AF51" s="2" t="s">
-        <v>41</v>
+        <v>343</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>371</v>
+        <v>191</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>106</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="F52" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G52">
         <v>8</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>49</v>
@@ -5833,19 +5809,19 @@
         <v>37</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>158</v>
+        <v>347</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z52" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA52">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB52" s="2" t="s">
         <v>58</v>
@@ -5863,30 +5839,30 @@
         <v>41</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>160</v>
+        <v>349</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>222</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="F53" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G53">
         <v>9</v>
@@ -5910,10 +5886,10 @@
         <v>37</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>377</v>
+        <v>257</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>57</v>
@@ -5940,33 +5916,33 @@
         <v>41</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>379</v>
+        <v>259</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>106</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="F54" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>45</v>
@@ -5987,19 +5963,19 @@
         <v>37</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="Y54" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z54" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AA54">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB54" s="2" t="s">
         <v>58</v>
@@ -6017,39 +5993,39 @@
         <v>41</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>371</v>
+        <v>108</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="F55" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -6064,19 +6040,19 @@
         <v>37</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>304</v>
+        <v>86</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>385</v>
+        <v>358</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z55" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AA55">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB55" s="2" t="s">
         <v>58</v>
@@ -6088,43 +6064,45 @@
         <v>44</v>
       </c>
       <c r="AF55" s="2" t="s">
-        <v>41</v>
+        <v>359</v>
       </c>
       <c r="AG55" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="AJ55" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="AJ55" s="2" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="F56" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -6139,10 +6117,10 @@
         <v>37</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="Y56" s="2" t="s">
         <v>57</v>
@@ -6163,19 +6141,250 @@
         <v>44</v>
       </c>
       <c r="AF56" s="2" t="s">
-        <v>67</v>
+        <v>359</v>
       </c>
       <c r="AG56" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH56" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI56" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="AJ56" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46280</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <v>13262</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="X57" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z57" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA57">
+        <v>40</v>
+      </c>
+      <c r="AB57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH57" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI57" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ57" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46280</v>
+      </c>
+      <c r="G58">
+        <v>5</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <v>13262</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z58" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA58">
+        <v>24</v>
+      </c>
+      <c r="AB58" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD58" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI58" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AJ58" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F59" s="1">
+        <v>46280</v>
+      </c>
+      <c r="G59">
+        <v>5</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59">
+        <v>13262</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X59" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="Y59" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA59">
+        <v>20</v>
+      </c>
+      <c r="AB59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF59" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH59" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AI56" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AJ56" s="2" t="s">
-        <v>82</v>
+      <c r="AI59" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ59" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA1C4CB-553C-44FB-AB3F-B1C1864ECDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1EA59E-6365-4A8A-8E76-4B342BF1DD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="371">
   <si>
     <t>Canal</t>
   </si>
@@ -241,30 +241,18 @@
     <t>Octavio Jaimes</t>
   </si>
   <si>
-    <t>Cultura</t>
-  </si>
-  <si>
     <t>Portadas</t>
   </si>
   <si>
     <t>Lorena Rosas</t>
   </si>
   <si>
-    <t>Semot</t>
-  </si>
-  <si>
-    <t>Saderh</t>
-  </si>
-  <si>
     <t>Impresiones locales</t>
   </si>
   <si>
     <t>Segobh</t>
   </si>
   <si>
-    <t>Tizayuca</t>
-  </si>
-  <si>
     <t>PGJEH</t>
   </si>
   <si>
@@ -277,24 +265,9 @@
     <t>Natividad Castrejón Valdez</t>
   </si>
   <si>
-    <t>Salud Mental</t>
-  </si>
-  <si>
-    <t>Tula</t>
-  </si>
-  <si>
-    <t>Salomón Hernández</t>
-  </si>
-  <si>
     <t>SEPH, Ayuntamiento</t>
   </si>
   <si>
-    <t>PGJEH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Semarnath</t>
-  </si>
-  <si>
     <t>Fiestas Patrias</t>
   </si>
   <si>
@@ -313,33 +286,18 @@
     <t>Blanca Soriano</t>
   </si>
   <si>
-    <t>César Martínez</t>
-  </si>
-  <si>
     <t>Gobernador</t>
   </si>
   <si>
     <t>Dulce Castillo</t>
   </si>
   <si>
-    <t>Día del Charro</t>
-  </si>
-  <si>
     <t>Lourdes Naranjo</t>
   </si>
   <si>
-    <t>Sedeco</t>
-  </si>
-  <si>
     <t>Ricardo Calleja</t>
   </si>
   <si>
-    <t>Tlanchinol</t>
-  </si>
-  <si>
-    <t>Ataque Armado</t>
-  </si>
-  <si>
     <t>SEPH, IHE, Gobernador</t>
   </si>
   <si>
@@ -349,823 +307,859 @@
     <t>Carmen Hernández</t>
   </si>
   <si>
-    <t>María Antonieta Islas</t>
-  </si>
-  <si>
     <t>SSH, Presidencia</t>
   </si>
   <si>
-    <t>Hidarte</t>
-  </si>
-  <si>
     <t>Bienestar</t>
   </si>
   <si>
-    <t>Charros y escaramuzas recorren calles céntricas</t>
-  </si>
-  <si>
-    <t>Con motivo de la conmemoración del Día del Charro, charros y escaramuzas recorrieron las calles del centro de Pachuca desde la avenida Revolución hasta el Reloj Monumental, rindiendo homenaje a Roberto López por sus 50 años de trayectoria en la charrería hidalguense.</t>
-  </si>
-  <si>
-    <t>Charros y escaramuzas desfilaron por el centro de Pachuca para celebrar el Día del Charro y homenajear a Roberto López por 50 años de trayectoria.</t>
-  </si>
-  <si>
-    <t>Luis Carlos León</t>
-  </si>
-  <si>
-    <t>Cultura, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Roberto López</t>
-  </si>
-  <si>
-    <t>Propone Julio Menchaca transformar transparencia</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar envió al Congreso de Hidalgo un paquete de iniciativas para actualizar el marco normativo estatal en materia de transparencia, sustituyendo la estructura del Itaih para crear el Subsistema de Transparencia del Estado de Hidalgo integrado al Sistema Nacional.</t>
-  </si>
-  <si>
-    <t>Transparencia</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca presentó al Congreso propuestas para reestructurar los órganos de transparencia y control interno en la entidad.</t>
-  </si>
-  <si>
-    <t>Gustavo Vargas</t>
-  </si>
-  <si>
-    <t>Gobernador, Congreso, Contraloría, Itaipen</t>
-  </si>
-  <si>
     <t>Julio Menchaca Salazar</t>
   </si>
   <si>
-    <t>Piden que el estudio cubra otras especies</t>
-  </si>
-  <si>
-    <t>La Asociación Hidalguense para la Protección de los Animales solicitó ampliar el estudio biológico del tren AIFA-Pachuca en seis municipios para proteger otras especies como murciélagos, conejos, tlacuaches, armadillos y cactáceas además del águila real.</t>
-  </si>
-  <si>
-    <t>Protección Animal</t>
-  </si>
-  <si>
-    <t>Activistas pidieron extender el estudio de impacto ambiental del tren AIFA-Pachuca a más especies de fauna y flora en la franja del proyecto.</t>
-  </si>
-  <si>
-    <t>Semarnath, Presidencia, SICT, Oficialía Mayor</t>
-  </si>
-  <si>
-    <t>Paola Monterrubio</t>
-  </si>
-  <si>
-    <t>Protegen territorio del puma, en Xithi</t>
-  </si>
-  <si>
-    <t>Pobladores y autoridades de Xithi en Tepetitlán recibieron un apoyo de 460 mil pesos para delimitar el territorio habitado por el puma captado en cámaras trampa y evitar incursiones a zonas habitadas o ataques al ganado.</t>
-  </si>
-  <si>
-    <t>Tepetitlán</t>
-  </si>
-  <si>
-    <t>Rescate de especies</t>
-  </si>
-  <si>
-    <t>Ejidatarios de Xithi en Tepetitlán destinaron recursos para el monitoreo y resguardo del hábitat del puma para prevenir conflictos con la población.</t>
-  </si>
-  <si>
-    <t>Rosalía Maldonado</t>
-  </si>
-  <si>
-    <t>Semarnath, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Ana Elsa Castillo Cea</t>
-  </si>
-  <si>
-    <t>Acude artista de Tezontepec a Colombia</t>
-  </si>
-  <si>
-    <t>El artista visual e investigador Javier Acevedo, originario de Tezontepec de Aldama, fue seleccionado para realizar una residencia artística en Colombia para desarrollar su proyecto 'Ensambles viscosos' sobre cuerpos de agua.</t>
-  </si>
-  <si>
-    <t>Tezontepec de Aldama</t>
-  </si>
-  <si>
-    <t>Intercambio Artístico</t>
-  </si>
-  <si>
-    <t>El creador hidalguense Javier Acevedo participará en una residencia artística en Colombia para exponer su obra sobre el territorio y el agua.</t>
-  </si>
-  <si>
-    <t>Javier Acevedo</t>
-  </si>
-  <si>
-    <t>Analizarán con IA problemática vial</t>
-  </si>
-  <si>
-    <t>El gobierno estatal instalará tres cámaras con Inteligencia Artificial en puentes del bulevar Felipe Ángeles para analizar el flujo vehicular y remodelará 34 estaciones del Tuzobús para mejorar el sistema de transporte en Pachuca.</t>
-  </si>
-  <si>
-    <t>Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor aplicará tecnología de IA para evaluar la carga vehicular en el bulevar Felipe Ángeles y proyecta mantenimiento a 34 estaciones del Tuzobús.</t>
-  </si>
-  <si>
     <t>Oficialía Mayor</t>
   </si>
   <si>
-    <t>Oficialía Mayor, Semot, Sitmah</t>
-  </si>
-  <si>
-    <t>Orlando Ángeles Pérez</t>
-  </si>
-  <si>
-    <t>Definirán tarifas para taxi</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte (Semot) alista la definición del tarifario oficial de taxis en Pachuca previo a la Feria San Francisco 2026, recaudando además 190 mil pesos por sanciones por invasión al carril confinado del Tuzobús.</t>
-  </si>
-  <si>
-    <t>Tarifario de taxis</t>
-  </si>
-  <si>
-    <t>La Semot actualizará las tarifas de taxis en Pachuca rumbo a las festividades feriales e informó sobre sanciones aplicadas por invadir el carril del Tuzobús.</t>
-  </si>
-  <si>
-    <t>Semot, Sitmah, Sipdus</t>
-  </si>
-  <si>
-    <t>Lyzbeth Robles Gutiérrez</t>
-  </si>
-  <si>
-    <t>Alcaldías olvidan al campo señala UNTA Hidalgo</t>
-  </si>
-  <si>
-    <t>La dirigencia estatal de la Unión Nacional de Trabajadores Agrícolas (UNTA) acusó a los ayuntamientos hidalguenses de desatender al sector campesino y omitir la asignación de presupuestos para proyectos productivos agropecuarios.</t>
-  </si>
-  <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>La UNTA Hidalgo reprobó que las administraciones municipales no destinen recursos para la reactivación económica y fomento del sector agrícola.</t>
-  </si>
-  <si>
     <t>Alma Leticia Sánchez</t>
   </si>
   <si>
-    <t>Saderh, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Martha López Ríos</t>
-  </si>
-  <si>
-    <t>Charros desfilan en conmemoración de su día</t>
-  </si>
-  <si>
-    <t>Con motivo de la conmemoración del Día del Charro, integrantes de la Asociación de Charros del Estado de Hidalgo desfilaron ataviados con traje típico por las calles del centro de Pachuca desde avenida Revolución hasta el Reloj Monumental, enalteciendo esta tradición declarada Patrimonio Cultural Inmaterial.</t>
-  </si>
-  <si>
-    <t>Integrantes de la Asociación de Charros de Hidalgo desfilaron por el centro de Pachuca para celebrar el Día del Charro y enaltecer la tradición charra.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca envía al Congreso local paquete de reformas en transparencia</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar envió al Congreso de Hidalgo un paquete de reformas para crear 'Transparencia para el Pueblo de Hidalgo' como órgano desconcentrado de la Contraloría y el Subsistema de Transparencia estatal, reorganizando la protección de datos tras la desaparición del ITAIH.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca envió iniciativas al Congreso para reestructurar la transparencia y control interno, creando Transparencia para el Pueblo de Hidalgo.</t>
-  </si>
-  <si>
     <t>Adela Garmez</t>
   </si>
   <si>
-    <t>Gobernador, Congreso, Contraloría, Itaipen, Planeación, TSJEH</t>
-  </si>
-  <si>
-    <t>Comité Estatal de Formación valora propuestas de instrucción docente</t>
-  </si>
-  <si>
-    <t>El Comité Estatal de Formación Continua de Hidalgo analizó la oferta académica del Programa para el Desarrollo Profesional Docente (Prodep) 2026 para fortalecer la capacitación de maestras y maestros de educación básica, con la participación de la coordinadora de Educación Básica, Nancy Adriana León Vite.</t>
-  </si>
-  <si>
     <t>Boletín</t>
   </si>
   <si>
-    <t>Prodep</t>
-  </si>
-  <si>
-    <t>El Comité Estatal de Formación Continua evaluó las acciones formativas del Prodep 2026 para impulsar la profesionalización del magisterio hidalguense.</t>
-  </si>
-  <si>
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>Natividad Castrejón Valdez, Nancy Adriana León Vite, María de Lourdes Reyes Pérez, María del Rosario Ramírez Hernández, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Medirá IA flujo vehicular para solucionar congestionamientos</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo instalará tres cámaras con tecnología de Inteligencia Artificial en puentes del bulevar Felipe Ángeles con una inversión de hasta 600 mil pesos para analizar el tránsito hacia la CDMX y definir soluciones viales. A su vez, la Semot descartó la apertura del carril del Tuzobús al no reducir el tráfico.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor aplicará Inteligencia Artificial para medir el tránsito en el bulevar Felipe Ángeles, mientras la Semot descartó abrir el carril del Tuzobús.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Semot, Sitmah, SICT, Congreso</t>
-  </si>
-  <si>
-    <t>Orlando Ángeles Pérez, Lyzbeth Robles Gutiérrez</t>
-  </si>
-  <si>
-    <t>Prevén entregar este año el nuevo Hospital General</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo prevé concluir este año la transferencia del nuevo Hospital General de Pachuca al IMSS-Bienestar tras dos años de trámites y verificaciones federales. Además, reportó que el Hospital de Actopan lleva más de 90% de avance.</t>
-  </si>
-  <si>
-    <t>Nuevo Hospital General</t>
-  </si>
-  <si>
-    <t>La SSH proyecta entregar este año el nuevo Hospital General de Pachuca al IMSS-Bienestar e informó avances superiores al 90% en el nosocomio de Actopan.</t>
-  </si>
-  <si>
-    <t>SSH, IMSS-Bienestar, Sipdus, Presidencia</t>
-  </si>
-  <si>
     <t>Vanesa Escalante Arroyo</t>
   </si>
   <si>
-    <t>Registra Hidalgo una baja en casos de suicidio</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo reportó más de 40 muertes por suicidio en 2026, lo que representa una baja frente a los 146 casos de 2024 y más de 150 de 2025, manteniendo la atención preventiva en Cecosama y mesas de trabajo municipales.</t>
-  </si>
-  <si>
-    <t>La SSH registró una disminución en fallecimientos por suicidio en Hidalgo durante 2026, reforzando la atención psicológica preventiva en los municipios.</t>
-  </si>
-  <si>
-    <t>SSH, Cecosama, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Gobierno lanzará licitación para remodelar estaciones del Tuzobús</t>
-  </si>
-  <si>
-    <t>La Sipdus emitirá en octubre la licitación para remodelar las 34 estaciones del Tuzobús. Oficialía Mayor reportó que la afluencia subió a más de 91 mil pasajeros diarios y los tiempos de traslado bajaron 30%, mientras que Semot ha recaudado 190 mil pesos por 81 multas por invadir el carril confinado.</t>
-  </si>
-  <si>
-    <t>Rehabilitación estaciones Tuzobús</t>
-  </si>
-  <si>
-    <t>El gobierno estatal licitará la remodelación de 34 estaciones del Tuzobús e informó sobre el incremento de usuarios a 91 mil diarios y sanciones por invadir el carril.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Sipdus, Semot, Sitmah</t>
-  </si>
-  <si>
-    <t>Defiende Semot permanencia del carril confinado</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte (Semot) defendió la permanencia del carril exclusivo del Tuzobús sobre el bulevar Felipe Ángeles, al señalar que su confinamiento permitió elevar la eficiencia operativa del sistema de 75 a 99 por ciento, incrementar el número de usuarios y reducir los siniestros viales. La titular de la dependencia, Lyzbeth Robles Gutiérrez, sostuvo que el carril reservado tiene como prioridad proteger a las más de 60 mil personas que utilizan diariamente la ruta troncal, rechazando que sea el causante del tráfico sobre esa vía.</t>
-  </si>
-  <si>
-    <t>Carril confinado</t>
-  </si>
-  <si>
-    <t>La Semot justificó la vigencia del carril confinado del Tuzobús al argumentar que elevó la eficiencia al 99% y atiende a más de 60 mil usuarios diarios en Pachuca.</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Puértolas</t>
-  </si>
-  <si>
-    <t>Semot, Sitmah, STCH, Presidencia, Sipdus</t>
-  </si>
-  <si>
-    <t>Eficiencia del transporte metropolitano, de 75 a 99%</t>
-  </si>
-  <si>
-    <t>La eficiencia del sistema de transporte metropolitano pasó de 75 a 99 por ciento desde que el gobierno de Hidalgo asumió su operación directamente el pasado 1 de agosto a través del Sitmah. El oficial mayor, Edgar Orlando Ángeles Pérez, detalló que se incorporaron 140 autobuses y 383 operadores certificados, incrementando la afluencia diaria en la ruta troncal y alimentadoras de 68 mil usuarios en junio a 91 mil 923 en septiembre.</t>
-  </si>
-  <si>
-    <t>Afluencia Tuzobús</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor reportó que la operación estatal del transporte metropolitano elevó la eficiencia a 99% y la afluencia de usuarios a cerca de 92 mil diarios.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Sitmah, Semot, Gobernador</t>
-  </si>
-  <si>
-    <t>Prohiben disparos al aire durante el Grito</t>
-  </si>
-  <si>
-    <t>El secretario de Seguridad Pública de Hidalgo, Salvador Cruz Neri, advirtió que no se tolerarán disparos de arma de fuego al aire durante las celebraciones de las Fiestas Patrias, recordando que esta conducta constituye un delito sancionado con hasta dos años de prisión en el Código Penal estatal.</t>
-  </si>
-  <si>
-    <t>La SSPH advirtió que sancionará penalmente los disparos de arma de fuego al aire durante los festejos del Grito de Independencia.</t>
-  </si>
-  <si>
-    <t>SSPH, PGJEH, Segobh</t>
-  </si>
-  <si>
-    <t>Aún pendiente transferencia de hospital</t>
-  </si>
-  <si>
-    <t>La secretaria de Salud de Hidalgo, Vanesa Escalante Arroyo, señaló que el proceso de transferencia del nuevo Hospital General de Pachuca al IMSS-Bienestar continúa pendiente tras dos años de gestiones, esperando concluir las verificaciones federales para su operación.</t>
-  </si>
-  <si>
-    <t>La SSH reportó que sigue en revisión la transferencia del nuevo Hospital General de Pachuca al esquema IMSS-Bienestar.</t>
-  </si>
-  <si>
-    <t>SSH, IMSS-Bienestar, Presidencia</t>
-  </si>
-  <si>
-    <t>Sin puente por fiestas patrias</t>
-  </si>
-  <si>
-    <t>El calendario escolar oficial de la SEP contempla únicamente la suspensión de labores el miércoles 16 de septiembre por las Fiestas Patrias, por lo que las actividades escolares iniciaron de forma regular el martes.</t>
-  </si>
-  <si>
-    <t>El calendario educativo marcó únicamente el 16 de septiembre como suspensión oficial de clases por festejos patrios.</t>
-  </si>
-  <si>
-    <t>SEPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Registran más de 40 suicidios en ocho meses</t>
-  </si>
-  <si>
-    <t>Entre enero y agosto de 2026 Hidalgo acumuló más de 40 fallecimientos por suicidio, reflejando un descenso respecto a años anteriores según datos de la Secretaría de Salud estatal, concentrándose la mayor atención preventiva en jóvenes de 15 a 19 años.</t>
-  </si>
-  <si>
-    <t>La SSH contabilizó más de 40 suicidios en los primeros ocho meses del año, destacando una baja general de casos en la entidad.</t>
-  </si>
-  <si>
     <t>Alejandro Reyes</t>
   </si>
   <si>
-    <t>Más de mil 700 personas acudieron a seis funciones gratuitas de cine en lenguas originarias</t>
-  </si>
-  <si>
-    <t>La muestra itinerante de cine en lenguas originarias congregó a más de mil 700 asistentes durante seis funciones gratuitas en cinco municipios hidalguenses para promover la diversidad lingüística.</t>
-  </si>
-  <si>
-    <t>Cine Comunitario</t>
-  </si>
-  <si>
-    <t>Más de 1,700 espectadores disfrutaron de la muestra de cine en lenguas indígenas en municipios de Hidalgo.</t>
-  </si>
-  <si>
-    <t>La planta Tula de Cruz Azul produce ya 600 toneladas diarias de cemento blanco</t>
-  </si>
-  <si>
-    <t>La fábrica de Cruz Azul en Tula alcanzó una producción diaria de 600 toneladas de cemento blanco y alista el reinicio de líneas de cemento gris, informó Mario Francisco Morán.</t>
-  </si>
-  <si>
-    <t>Cruz Azul</t>
-  </si>
-  <si>
-    <t>La planta de Cruz Azul en Tula reactivó operaciones alcanzando 600 toneladas diarias de cemento blanco.</t>
-  </si>
-  <si>
-    <t>Sedeco, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Mario Francisco Morán</t>
-  </si>
-  <si>
-    <t>El gobernador envía serie de iniciativas al Congreso</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar envió al Congreso local un paquete de iniciativas orientado a actualizar el marco jurídico estatal en materia de transparencia, protección de datos personales, control interno y simplificación administrativa, planteando la creación de Transparencia para el Pueblo de Hidalgo y el Subsistema de Transparencia del Estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca envió un paquete de iniciativas al Congreso para reestructurar el sistema de transparencia estatal y protección de datos tras la extinción del ITAIH.</t>
-  </si>
-  <si>
-    <t>Gobernador, Congreso, Contraloría, Itaipen, Planeación</t>
-  </si>
-  <si>
-    <t>PREPARAN UN ANÁLISIS CON IA DEL TRÁFICO</t>
-  </si>
-  <si>
-    <t>En los próximos 15 días, instalarán tres videocámaras de inteligencia artificial en los puentes del Tecnológico de Monterrey, la Procuraduría de Hidalgo y Matilde, como parte de un análisis del comportamiento vehicular sobre el bulevar Felipe Ángeles; por ahora, continuará en funcionamiento el carril confinado del Tuzobús.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor instalará tres cámaras con IA en el bulevar Felipe Ángeles para evaluar soluciones viales, mientras la Semot descartó la apertura del carril confinado del Tuzobús.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Semot, Sitmah, Congreso, Sipdus</t>
-  </si>
-  <si>
-    <t>Edgar Orlando Ángeles Pérez, Lyzbeth Robles Gutiérrez</t>
-  </si>
-  <si>
-    <t>Le retiran la concesión a una ruta por caso Minero</t>
-  </si>
-  <si>
-    <t>Por carecer de seguro vial, la Secretaría de Movilidad y Transporte de Hidalgo (Semot) le retiró una concesión de transporte a la ruta Tilcuautla-Pachuca, involucrada en el accidente registrado el 20 de mayo de este año en el bulevar Minero, el cual dejó un saldo de una mujer sin vida y a 13 personas lesionadas.</t>
-  </si>
-  <si>
-    <t>Concesiones transporte público</t>
-  </si>
-  <si>
-    <t>La Semot revocó la concesión a la unidad de la ruta Tilcuautla-Pachuca accidentada en el bulevar Minero por no contar con póliza de seguro de viajero.</t>
-  </si>
-  <si>
-    <t>Semot, PGJEH, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Lyzbeth Robles Gutiérrez, Julio N.</t>
-  </si>
-  <si>
-    <t>Copriseh supervisará la venta de alimentos durante fiestas patrias</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo (SSH) y la Copriseh implementarán acciones de vigilancia y fomento sanitario en los 84 municipios de la entidad por medio de sus 12 delegaciones sanitarias durante las Fiestas Patrias 2026, dirigidas a comerciantes y manejadores de alimentos y bebidas.</t>
-  </si>
-  <si>
-    <t>Vigilancia Sanitaria</t>
-  </si>
-  <si>
-    <t>La Copriseh supervisará las condiciones sanitarias de puestos de alimentos y bebidas durante los festejos del Grito de Independencia en los 84 municipios de Hidalgo.</t>
-  </si>
-  <si>
-    <t>SSH, Copriseh, Ayuntamientos, SSPH, PC</t>
-  </si>
-  <si>
-    <t>Alberto Mercado Hernández</t>
-  </si>
-  <si>
-    <t>Charros apoyan tauromaquia ante consulta</t>
-  </si>
-  <si>
-    <t>Los charros de Pachuca manifestaron su respaldo a las corridas de toros ante la consulta sobre la tauromaquia, al considerar que existe una relación histórica y cultural entre la fiesta taurina y la charrería. Gerardo Anselmo Mejía, vicepresidente de la Asociación de Charros de Pachuca, sostuvo que el gremio respalda la tauromaquia.</t>
-  </si>
-  <si>
-    <t>Tauromaquia</t>
-  </si>
-  <si>
-    <t>La Asociación de Charros de Pachuca respaldó la continuidad de la tauromaquia ante la consulta pública, resaltando su hermandad cultural e histórica.</t>
-  </si>
-  <si>
-    <t>Gerardo Anselmo Mejía</t>
-  </si>
-  <si>
-    <t>Desmantelan un taller de regrabado en Pachuca: SSPH</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH), en coordinación con la PGJEH y la Sedena, ejecutó una orden de cateo en un inmueble del fraccionamiento Valle Diamante Plus en Pachuca, desarticulando un taller adaptado para el regrabado y clonación de documentos de identificación vehicular, deteniendo a un hombre (C. A. G. R.).</t>
-  </si>
-  <si>
     <t>Cateo</t>
   </si>
   <si>
-    <t>Fuerzas de seguridad desmantelaron en Pachuca un taller clandestino de clonación de documentos vehiculares y placas robadas, arrestando a un presunto implicado.</t>
-  </si>
-  <si>
     <t>SSPH, PGJEH, Sedena, Presidencia</t>
   </si>
   <si>
-    <t>C. A. G. R.</t>
-  </si>
-  <si>
-    <t>Entregarán hospital a la federación este año</t>
-  </si>
-  <si>
-    <t>Este año se terminará la transferencia del nuevo Hospital General de Pachuca al IMSS-Bienestar, ya que la Secretaría de Infraestructura sigue pasando los reportes sobre la intervención realizada en el inmueble ubicado en San Agustín Tlaxiaca, indicó la titular de la SSH, Vanesa Escalante Arroyo.</t>
-  </si>
-  <si>
-    <t>La SSH prevé concretar este año la transferencia del nuevo Hospital General de Pachuca al sistema IMSS-Bienestar tras revisiones técnicas y entrega de minutas de obra.</t>
-  </si>
-  <si>
-    <t>SSH, IMSS-Bienestar, Sipdus, Contraloría, Presidencia</t>
-  </si>
-  <si>
-    <t>Suicidios en Hidalgo aumentaron 8.2 por ciento en un año</t>
-  </si>
-  <si>
-    <t>En un año, los suicidios en Hidalgo incrementaron 8.2 por ciento; las personas adolescentes y jóvenes de entre 15 y 24 años son el grupo poblacional con más intentos de quitarse la vida, de acuerdo con datos de la Secretaría de Salud estatal (SSH), registrándose 159 casos en 2025 y más de 40 en lo que va de 2026.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo informó un alza del 8.2% en suicidios en 2025 y convocó a mesas de trabajo integrales para atender la salud mental en jóvenes y adolescentes.</t>
-  </si>
-  <si>
-    <t>Inauguran la tienda Hidarte de Tulancingo</t>
-  </si>
-  <si>
-    <t>Este lunes fue inaugurated la tienda Hidarte: Casa de las Artesanías en Tulancingo, ubicada en el Centro Cultural Ricardo Garibay, espacio que expone para su venta productos de 22 artesanas y productores de la región sin cobro de comisiones.</t>
-  </si>
-  <si>
-    <t>La alcaldía de Tulancingo y la Sebiso inauguraron la tienda Hidarte en el Centro Cultural Ricardo Garibay para comercializar piezas de 22 artesanos locales.</t>
-  </si>
-  <si>
-    <t>Mirely Santos</t>
-  </si>
-  <si>
-    <t>Bienestar, Ayuntamiento, Hidarte, Cultura</t>
-  </si>
-  <si>
-    <t>Lorena García Cázares</t>
-  </si>
-  <si>
-    <t>Impulsa Menchaca la creación de nueva estructura de transparencia en Hidalgo</t>
-  </si>
-  <si>
-    <t>Con el objetivo de fortalecer la transparencia y la protección de datos, el gobernador Julio Menchaca Salazar envió una serie de iniciativas al Congreso estatal, además de plantear medidas para fortalecer la simplificación administrativa y la transformación digital. Entre las principales propuestas se encuentra la creación del organismo denominado Transparencia para el Pueblo de Hidalgo, así como del Subsistema de Transparencia del estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca envió iniciativas al Congreso estatal para reestructurar el sistema de transparencia y protección de datos, creando Transparencia para el Pueblo de Hidalgo.</t>
-  </si>
-  <si>
-    <t>“UN MITO” QUE CARRIL CONFINADO DEL TUZOBÚS GENERE TRÁFICO EN FELIPE ÁNGELES; HARÁN ANÁLISIS</t>
-  </si>
-  <si>
-    <t>La secretaria de Movilidad y Transporte del Estado de Hidalgo (Semot), Lizbeth Robles Gutiérrez, calificó como “un mito” que el congestionamiento vehicular sobre el bulevar Felipe Ángeles sea por mantener el carril confinado del Sistema de Transporte Metropolitano (Tuzobús), al señalar que dicha medida ha logrado reducir los registros de siniestros viales, tener mayor eficiencia con el incremento del número de viajes en un 29% y la reducción de los tiempos de traslado de las personas usuarias.</t>
-  </si>
-  <si>
-    <t>La Semot defendió la permanencia del carril confinado del Tuzobús al reducir accidentes y elevar viajes 29%, anunciando el uso de Inteligencia Artificial para evaluar soluciones viales.</t>
-  </si>
-  <si>
-    <t>Semot, Sitmah, STCH, SICT, Presidencia</t>
-  </si>
-  <si>
-    <t>Pierde concesión ruta Tilcuautla-Pachuca involucrada en accidente en Bulevar Minero</t>
-  </si>
-  <si>
-    <t>Por falta de póliza de seguro vigente, le fue retirada la concesión a la ruta del transporte público colectivo Tilcuautla-Pachuca, luego de que una de sus unidades se viera involucrada en el incidente registrado el pasado 20 de mayo sobre el bulevar Minero, en Pachuca, que dejó como saldo una persona sin vida y 17 más lesionadas.</t>
-  </si>
-  <si>
-    <t>La Semot revocó la concesión a la colectiva de la ruta Tilcuautla-Pachuca accidentada en el bulevar Minero tras confirmar que no contaba con póliza de seguro activa.</t>
-  </si>
-  <si>
-    <t>Tizayuca, entre las zonas con mayor riesgo suicida en Hidalgo</t>
-  </si>
-  <si>
-    <t>Tizayuca es identificada como una de las zonas de Hidalgo con mayor riesgo suicida, debido a la presencia de factores como violencia familiar y abandono, así se dio a conocer durante la rueda de prensa con motivo del Día Mundial de la Prevención del Suicidio. La titular de la SSH, Vanesa Escalante Arroyo, explicó que en 2024 se registraron 146 muertes por suicidio y se atendieron 1,020 intentos.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo ubicó a Tizayuca como municipio prioritario por riesgo suicida y violencia familiar, reforzando la atención en los seis centros Cecosama.</t>
-  </si>
-  <si>
-    <t>Vanesa Escalante Arroyo, Yolanda Pérez Martínez</t>
-  </si>
-  <si>
-    <t>A dos años de proceso, avanza transferencia del nuevo Hospital General Pachuca</t>
-  </si>
-  <si>
-    <t>Autoridades del IMSS-Bienestar federal realizaron dos visitas al Hospital General Pachuca, ubicado en San Agustín Tlaxiaca, como parte del proceso para concretar la transferencia del inmueble al Gobierno Federal, informó la secretaria de Salud de Hidalgo, Vanesa Escalante. El trámite para incorporar el hospital lleva alrededor de dos años.</t>
-  </si>
-  <si>
-    <t>La SSH reportó avances en las auditorías de infraestructura para completar la entrega del nuevo Hospital General de Pachuca al sistema IMSS-Bienestar federal.</t>
-  </si>
-  <si>
-    <t>DESMANTELAN CENTRO DE CLONACIÓN DE DOCUMENTACIÓN EN PACHUCA</t>
-  </si>
-  <si>
-    <t>Elementos adscritos a la Secretaría de Seguridad Pública estatal (SSPH) desmantelaron inmueble que estaba adaptado como taller de regrabado y clonación de identificaciones vehiculares en la ciudad de Pachuca. Durante el cateo en Valle Diamante Plus, detuvieron a un hombre identificado como C.A.G.R.</t>
-  </si>
-  <si>
-    <t>Fuerzas estatales y federales aseguraron en Pachuca un taller clandestino de clonación de documentos vehiculares y vehículos robados, arrestando a un sujeto.</t>
-  </si>
-  <si>
-    <t>SEMOT RETIRA CONCESIÓN A COMBI QUE DEJÓ 17 HERIDOS</t>
-  </si>
-  <si>
-    <t>A casi cuatro meses de que una camioneta particular y una unidad del transporte público se vieron involucrados en un accidente sobre el bulevar Minero, en Pachuca, la Secretaría de Movilidad y Transporte (Semot) revocó la concesión a la combi por no contar con seguro vigente.</t>
-  </si>
-  <si>
-    <t>La Semot revocó la concesión a la combi de la ruta Tilcuautla-Pachuca accidentada en el bulevar Minero tras confirmar que no contaba con seguro vehicular activo.</t>
-  </si>
-  <si>
-    <t>TRAS QUEJAS, TAXIS TENDRÁN NUEVA TARIFA EN HIDALGO</t>
-  </si>
-  <si>
-    <t>La próxima semana se dará a conocer la nueva tarifa de los taxis, luego de varios meses de análisis y de múltiples quejas por cobros excesivos, dio a conocer Lyzbeth Robles Gutiérrez, titular de la Secretaría de Movilidad y Transporte (Semot).</t>
-  </si>
-  <si>
-    <t>La Semot anunciará la próxima semana la reestructuración definitiva de las tarifas de taxi en Pachuca para evitar cobros excesivos a usuarios.</t>
-  </si>
-  <si>
-    <t>Semot, Gobernador</t>
-  </si>
-  <si>
-    <t>Lyzbeth Robles Gutiérrez, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>JULIO MENCHACA MANDA AL CONGRESO RELEVO DEL ITAIH</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar envió al Congreso de Hidalgo un paquete de iniciativas para definir cómo operará el nuevo modelo de transparencia y protección de datos personales tras la desaparición del Instituto de Transparencia, Acceso a la Información Pública Gubernamental y Protección de Datos Personales (Itaih).</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca planteó la creación de Transparencia para el Pueblo de Hidalgo y el Subsistema de Transparencia estatal tras la extinción del ITAIH.</t>
-  </si>
-  <si>
-    <t>Luis Godínez</t>
-  </si>
-  <si>
-    <t>ABRIR EL CARRIL CONFINADO NO AMINORARÁ EL TRÁFICO: SEMOT</t>
-  </si>
-  <si>
-    <t>La secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez, consideró que es un 'mito' que el carril confinado del Sistema de Transporte Metropolitano genera tráfico en el sur de Pachuca. En tanto, el oficial mayor, Edgar Orlando Ángeles Pérez, anunció que se instalarán cámaras con inteligencia artificial sobre el bulevar Felipe Ángeles.</t>
-  </si>
-  <si>
-    <t>La Semot sostuvo que el carril exclusivo del Tuzobús protege a más de 91 mil usuarios diarios y Oficialía Mayor probará cámaras con Inteligencia Artificial para medir el tránsito viales.</t>
-  </si>
-  <si>
-    <t>Semot, Sitmah, Oficialía Mayor, PGJEH</t>
-  </si>
-  <si>
-    <t>Lyzbeth Robles Gutiérrez, Edgar Orlando Ángeles Pérez</t>
-  </si>
-  <si>
-    <t>BUSCA SNTE HIDALGO BLINDAR AUTONOMÍA</t>
-  </si>
-  <si>
-    <t>Ante la posibilidad de que el periodo de la actual dirigencia de la sección XV del SNTE en Hidalgo se extienda por un año, el secretario general, Said Vargas Sáenz, argumentó que el propósito es blindar la autonomía sindical para evitar injerencias políticas rumbo a las elecciones de 2027.</t>
-  </si>
-  <si>
-    <t>Dirigencia Partidista</t>
-  </si>
-  <si>
-    <t>El dirigente de la Sección XV del SNTE, Said Vargas, afirmó que la extensión de su gestión busca blindar al sindicato magisterial frente al proceso electoral de 2027.</t>
-  </si>
-  <si>
-    <t>Said Vargas Sáenz</t>
-  </si>
-  <si>
-    <t>REPORTAN 40 SUICIDIOS EN HIDALGO EN LO QUE VA DE 2026</t>
-  </si>
-  <si>
-    <t>La secretaria de Salud en la entidad, Vanesa Escalante Arroyo, dio a conocer que en lo que va del año se han registrado 40 suicidios en Hidalgo, concentrándose la mayor incidencia en adolescentes de 15 a 19 años en municipios metropolitanos.</t>
-  </si>
-  <si>
-    <t>La SSH contabilizó 40 decesos por suicidio en Hidalgo durante 2026 e hizo un llamado a aprovechar la atención psicológica gratuita en los seis centros Cecosama del estado.</t>
-  </si>
-  <si>
-    <t>TRAS 4 AÑOS, NUEVO HOSPITAL GENERAL DE PACHUCA PASARÁ AL IMSS-BIENESTAR</t>
-  </si>
-  <si>
-    <t>A casi cuatro años de su inauguración, la Secretaría de Salud de Hidalgo está por concretar formalmente la transferencia de los servicios del nuevo Hospital General de Pachuca al IMSS-Bienestar federal para su conclusión y puesta en marcha.</t>
-  </si>
-  <si>
-    <t>La SSH afina detalles de las minutas de obra y revisiones técnicas para transferir el nuevo Hospital General de Pachuca al esquema IMSS-Bienestar federal.</t>
-  </si>
-  <si>
-    <t>INAUGURAN LA TIENDA HIDARTE TULANCINGO</t>
-  </si>
-  <si>
-    <t>Con 22 expositores abrió sus puertas la Tienda Hidarte en el Centro Cultural Ricardo Garibay de Tulancingo, impulsada por Sebiso y el gobierno municipal para comercializar piezas artesanales sin cobro de comisión.</t>
-  </si>
-  <si>
-    <t>La Sebiso y la alcaldía de Tulancingo inauguraron la sucursal de Hidarte en el Centro Cultural Garibay para proyectar las creaciones de 22 artesanos locales.</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno, Lorena García Cázares, Minerva Rosales Gayosso, José Antonio Rodríguez Arango</t>
-  </si>
-  <si>
-    <t>DEMANDAN MAYOR SEGURIDAD TRAS EL INCENDIO DE UNIDAD</t>
-  </si>
-  <si>
-    <t>Integrantes de la Asociación Certeza, Progreso y Desarrollo para Todos se reunieron con el alcalde de Tlanchinol, Gabino Hernández Vite, para pedir reforzar la vigilancia tras el incendio intencional de la camioneta de su dirigente, Onésimo Pérez Lara, quien presentó denuncia ante el MP.</t>
-  </si>
-  <si>
-    <t>Integrantes de una organización social de Tlanchinol solicitaron reforzar la seguridad municipal tras el atentado incendiario contra el vehículo de su presidente Onésimo Pérez.</t>
-  </si>
-  <si>
-    <t>Onésimo Pérez Lara, Gabino Hernández Vite</t>
-  </si>
-  <si>
-    <t>Copriseh realizará revisiones de fomento sanitario</t>
-  </si>
-  <si>
-    <t>Con motivo de las fiestas patrias, la Comisión para la Protección contra Riesgos Sanitarios del Estado de Hidalgo (Copriseh) implementará acciones de vigilancia y fomento sanitario en los 84 municipios de la entidad, con el propósito de prevenir riesgos y proteger la salud de la población en establecimientos de alimentos y bebidas.</t>
-  </si>
-  <si>
-    <t>La Copriseh desplegará operativos de fomento y vigilancia sanitaria en puestos de alimentos y bebidas en los 84 municipios por las Fiestas Patrias.</t>
-  </si>
-  <si>
-    <t>SSH, Copriseh, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>PC estatal recomienda evitar el uso de pirotecnia</t>
-  </si>
-  <si>
-    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos del Estado exhortó a la población a evitar el uso de pirotecnia en Fiestas Patrias, destacando que en septiembre las lesiones por quemaduras aumentan 300%. Asimismo, recordó que realizar disparos al aire constituye un delito grave.</t>
-  </si>
-  <si>
-    <t>Pirotecnia</t>
-  </si>
-  <si>
-    <t>Protección Civil de Hidalgo exhortó a suspender la quema de pirotecnia por el incremento del 300% en quemaduras durante septiembre e inhibir disparos al aire.</t>
-  </si>
-  <si>
     <t>Ana Luisa Vega</t>
   </si>
   <si>
-    <t>Segobh, PC, SSPH</t>
-  </si>
-  <si>
-    <t>Remodelarán estaciones de transporte metropolitano</t>
-  </si>
-  <si>
-    <t>El oficial mayor del gobierno estatal, Edgar Orlando Ángeles Pérez, informó que las 34 estaciones del Transporte Metropolitano (Tuzobús) serán remodeladas tras concluir el proyecto ejecutivo, licitándose a finales de septiembre para arrancar en octubre, destacando que el flujo diario subió a 91,923 pasajeros.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor licitará la rehabilitación de las 34 estaciones del Tuzobús en octubre e informó que la afluencia diaria creció 34%, alcanzando los 91,923 usuarios.</t>
-  </si>
-  <si>
     <t>Oscar Raúl Pérez</t>
   </si>
   <si>
-    <t>Edgar Orlando Ángeles Pérez</t>
-  </si>
-  <si>
-    <t>Gabinete de Seguridad, detalló operativos ejecutados en 14 municipios de Hidalgo</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca y el Gabinete de Seguridad reportaron la detención de 24 personas en 14 municipios, el decomiso de 4,521 dosis de narcóticos, armas y vehículos, la desarticulación de narcomenudeo en Tepeapulco y huachicol en Tizayuca y Tepetitlán, la localización de 21 personas desaparecidas y el despliegue de 5 mil policías para Fiestas Patrias.</t>
-  </si>
-  <si>
     <t>Operativo de Seguridad</t>
   </si>
   <si>
-    <t>El Gabinete de Seguridad de Hidalgo informó la captura de 24 personas, decomisos de droga y huachicol en 14 municipios, y el despliegue de 5 mil policías para Fiestas Patrias.</t>
-  </si>
-  <si>
-    <t>SSPH, Gobernador, PGJEH, Gabinete de Seguridad, CBPEH</t>
-  </si>
-  <si>
-    <t>SSPH desmantela local; clonaban identificaciones vehiculares</t>
-  </si>
-  <si>
-    <t>La SSPH, PGJEH y Sedena ejecutaron un cateo en un inmueble del fraccionamiento Valle Diamante Plus en Pachuca, desarticulando un taller de regrabado y clonación de placas, licencias y tarjetas de circulación, arrestando a C. A. G. R..</t>
-  </si>
-  <si>
-    <t>Fuerzas estatales y federales aseguraron en Pachuca un taller clandestino de clonación de placas y documentos vehiculares, arrestando a un presunto implicado.</t>
-  </si>
-  <si>
-    <t>Desfilan charros por calles de Pachuca</t>
-  </si>
-  <si>
-    <t>Cerca de un centenar de charros y escaramuzas tomaron las calles del centro de Pachuca para conmemorar el Día Nacional del Charro. El contingente partió del Estadio Revolución, recorrió avenidas principales como Allende, Matamoros, Guerrero y rodó la explanada del Reloj Monumental antes de concluir en el Lienzo Charro de Pachuca.</t>
-  </si>
-  <si>
-    <t>Charros y escaramuzas desfilaron por las principales calles del centro histórico de Pachuca para conmemorar el Día Nacional del Charro.</t>
-  </si>
-  <si>
-    <t>MEXE SOSTIENE PROTESTA POR MUERTE DE NORMALISTA</t>
-  </si>
-  <si>
-    <t>Estudiantes de la Escuela Normal Rural Luis Villarreal 'El Mexe' mantuvieron una manifestación pacífica en las inmediaciones de la PGJEH en Pachuca para dar seguimiento al caso del homicidio de su compañero. Tras reunirse con autoridades ministeriales, acordaron mesas de trabajo semanales para revisar los avances de la carpeta de investigación.</t>
-  </si>
-  <si>
-    <t>Normalistas de El Mexe protestaron frente a la PGJEH para exigir justicia por el homicidio de un compañero y acordaron reuniones semanales de seguimiento.</t>
-  </si>
-  <si>
     <t>Erick Perales</t>
   </si>
   <si>
-    <t>PGJEH, Presidencia, SEPH</t>
-  </si>
-  <si>
-    <t>Claudia Sheinbaum Pardo, Alejandro Moreno Cárdenas</t>
-  </si>
-  <si>
-    <t>QUITAN CONCESIÓN TRAS ACCIDENTE EN BULEVAR EL MINERO</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte de Hidalgo (Semot) revocó la concesión a una Urvan de la ruta Tilcuautla-Pachuca tras confirmar que circulaba sin póliza de seguro vigente al momento de volcarse sobre el bulevar Minero el pasado 20 de mayo, percance que dejó un saldo de un fallecido y 17 lesionados.</t>
-  </si>
-  <si>
-    <t>La Semot retiró la concesión a la colectivo de la ruta Tilcuautla-Pachuca involucrada en un accidente en el bulevar Minero por no contar con póliza de seguro activa.</t>
-  </si>
-  <si>
-    <t>USARÁN IA PARA RESOLVER TRÁFICO AL SUR DE PACHUCA</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo invertirá hasta 600 mil pesos en la instalación de tres cámaras dotadas con Inteligencia Artificial en puentes peatonales del bulevar Felipe Ángeles para analizar el flujo vehicular en tiempo real hacia la CDMX. Asimismo, la Semot reportó un aumento del 34% en usuarios diarios del Tuzobús.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor colocará tres cámaras con IA en el bulevar Felipe Ángeles para evaluar soluciones viales, reportando además 91 mil usuarios diarios en el Tuzobús.</t>
-  </si>
-  <si>
-    <t>CLONABAN DOCUMENTOS VEHICULARES EN PACHUCA</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH), en coordinación con la PGJEH y la Sedena, cateó y desmanteló una vivienda en el fraccionamiento Valle Diamante Plus en Pachuca adaptada como taller clandestino de clonación de placas, licencias y tarjetas de circulación, arrestando a un hombre (C. A. G. R.).</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad desmantelaron un taller de clonación de placas y documentos vehiculares en Valle Diamante Plus de Pachuca, capturando a un presunto implicado.</t>
-  </si>
-  <si>
-    <t>El edificio de la escuela primaria Aquiles Serdán en Tulancingo deberá ser demolido y reconstruido en su totalidad debido a fallas estructurales severas. El secretario de Educación, Natividad Castrejón, indicó que los trabajos requerirán todo el ciclo escolar 2026-2027 y se evalúan opciones presenciales o híbridas para las clases.</t>
-  </si>
-  <si>
-    <t>La SEPH demolerá y reconstruirá completamente la primaria Aquiles Serdán en Tulancingo tras detectar daños estructurales en el inmueble.</t>
+    <t>Conmemora Menchaca Grito de Independencia con Plaza Juárez llena</t>
+  </si>
+  <si>
+    <t>En un ambiente de fiesta, música, y orgullo patrio, el gobernador Julio Menchaca Salazar, encabezó el Grito de Independencia ante más de 30 mil personas reunidas en Plaza Juárez. Desde el balcón del edificio guinda, el mandatario estatal acompañado de su familia, integrantes de su gabinete, representantes del poder legislativo, judicial, y el alcalde de Pachuca Jorge Reyes, rindió la quinta celebración de su administración, la cual culminó con espectáculo piromusical y la actuación estelar de Carlos Rivera.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca encabezó el Grito de Independencia ante más de 30 mil asistentes en la Plaza Juárez de Pachuca con pirotecnia y eventos musicales.</t>
+  </si>
+  <si>
+    <t>Gobernador, Ayuntamiento, SSPH, Bomberos, Cruz Roja</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Jorge Reyes Hernández, Carlos Rivera</t>
+  </si>
+  <si>
+    <t>REFORMA ELECTORAL PARA GARANTIZAR ALCALDÍAS A MUJERES ERA “LO IDEAL” PARA LA PARIDAD: MENCHACA</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar consideró que la intención de la propuesta de reforma al Código Electoral que planteaba dividir a los 84 municipios en dos bloques de 42 para dejar la mitad a postulaciones exclusivas para mujeres era "lo ideal" para asegurar la paridad que marca la Constitución. Sin embargo, señaló que al no ser incluida durante la aprobación de la reforma en el Congreso local existe el riesgo de que haya menos presidentas municipales en 2027.</t>
+  </si>
+  <si>
+    <t>Reforma Electoral</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca calificó la asignación alfabética de municipios para candidatas como la fórmula ideal de paridad, advirtiendo riesgo de menor representación femenina tras ser excluida por el Congreso.</t>
+  </si>
+  <si>
+    <t>Gobernador, Congreso, IEEH</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Andrés Velázquez Vázquez</t>
+  </si>
+  <si>
+    <t>Desmantelan inmueble usado para comercializar droga en Tepeapulco</t>
+  </si>
+  <si>
+    <t>Elementos de la Secretaría de Seguridad Pública de Hidalgo (SSPH), en coordinación con la PGJEH y la Sedena, ejecutaron un cateo en un inmueble de la colonia Rojo Gómez en Tepeapulco, asegurando 1,073 dosis de presunta droga cristal, 240 dosis de marihuana, un arma de fuego larga, cargadores, tres chalecos tácticos y una báscula de precisión sin registrar personas detenidas.</t>
+  </si>
+  <si>
+    <t>Tepeapulco</t>
+  </si>
+  <si>
+    <t>Operativo conjunto de la SSPH, PGJEH y Ejército desmanteló un centro de distribución de narcóticos en Tepeapulco, asegurando más de 1,300 dosis de droga y armamento.</t>
+  </si>
+  <si>
+    <t>Jornada de 40 horas, sin rechazo de empresarios</t>
+  </si>
+  <si>
+    <t>El sector laboral de Hidalgo se prepara para la reducción paulatina de la jornada laboral de 48 a 40 horas semanales a partir de enero de 2027. El secretario del Trabajo estatal, Oscar Javier González Hernández, informó que no existe resistencia entre el sector empresarial de la entidad y que se mantienen reuniones para planificar la productividad sin afectar sueldos, prestaciones ni derechos laborales.</t>
+  </si>
+  <si>
+    <t>Ley 40 horas</t>
+  </si>
+  <si>
+    <t>El secretario del Trabajo en Hidalgo, Oscar González Hernández, afirmó que no hay rechazo patronal ante la reducción paulatina de la jornada laboral a 40 horas a partir de 2027.</t>
+  </si>
+  <si>
+    <t>STPSH</t>
+  </si>
+  <si>
+    <t>STPSH, Presidencia, INEGI</t>
+  </si>
+  <si>
+    <t>Oscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>Escuelas con solo 6 alumnos en Hidalgo</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública de Hidalgo (SEPH) mantiene 700 escuelas primarias rurales con baja matrícula, algunas con de seis a 13 estudiantes. El secretario Natividad Castrejón Valdez descartó el cierre de planteles y explicó que se realiza una reingeniería de recursos humanos aprovechando plazas liberadas por jubilaciones, mientras el Conafe atiende a 7 mil alumnos en 2,100 centros comunitarios.</t>
+  </si>
+  <si>
+    <t>Infraestructura escolar</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón, aclaró que las 700 primarias rurales con baja matrícula en Hidalgo no serán cerradas y se optimizarán las plazas docentes.</t>
+  </si>
+  <si>
+    <t>Sonia Nochebuena</t>
+  </si>
+  <si>
+    <t>SEPH, Conafe, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Familias disfrutan desfile en Pachuca</t>
+  </si>
+  <si>
+    <t>Miles de familias se congregaron en las calles del Centro Histórico de Pachuca para presenciar el desfile cívico-militar conmemorativo del 216 aniversario del inicio de la Independencia de México, encabezado por el gobernador Julio Menchaca Salazar y la presidenta del DIF Edda Vite. Marcharon 1,800 alumnos de educación básica, 901 de nivel medio y superior, corporaciones policiales, Guardia Nacional, Ejército y asociaciones charras.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca encabezó el desfile cívico-militar del 216 aniversario de la Independencia de México en Pachuca con participación de contingentes escolares y de seguridad.</t>
+  </si>
+  <si>
+    <t>Gobernador, DIFH, SSPH, Sedena, GN, Cruz Roja, Ayuntamientos, Pemex</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Edda Vite Ramos, Salvador Cruz Neri</t>
+  </si>
+  <si>
+    <t>Llama obispo a aclarar la muerte de párroco</t>
+  </si>
+  <si>
+    <t>El obispo de la diócesis de Huejutla, José Acosta, exigió a las autoridades esclarecer el asesinato del sacerdote Román e hizo un llamado urgente a la sociedad hidalguense para consolidar una cultura de paz, tolerancia y reconciliación social para erradicar la violencia.</t>
+  </si>
+  <si>
+    <t>Huejutla</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>El obispo de Huejutla, José Acosta, pidió el esclarecimiento del homicidio del párroco Román y exhortó a la población a promover la reconciliación y la paz.</t>
+  </si>
+  <si>
+    <t>PGJEH, Presidencia</t>
+  </si>
+  <si>
+    <t>José Acosta, Román N.</t>
+  </si>
+  <si>
+    <t>Reportan saldo blanco por fiestas patrias</t>
+  </si>
+  <si>
+    <t>El titular de la SSPH, Salvador Cruz Neri, informó saldo blanco durante las celebraciones patrias en el estado de Hidalgo, destacando ausencia de disparos al aire y pocos decomisos de pirotecnia. Asimismo, aclaró que la Policía Estatal no participó en el cateo realizado por fuerzas federales en La Toscana, Tulancingo.</t>
+  </si>
+  <si>
+    <t>La SSPH informó saldo blanco en los festejos patrios de la entidad y precisó que la corporación no intervino en las diligencias del cateo en Tulancingo.</t>
+  </si>
+  <si>
+    <t>SSPH, Presidencia, Sedena, FGR</t>
+  </si>
+  <si>
+    <t>Iniciará mantenimiento del pisal de Byron Gálvez</t>
+  </si>
+  <si>
+    <t>El próximo 23 de octubre iniciarán los trabajos de mantenimiento del pisal Homenaje a la mujer del mundo, del artista hidalguense Byron Gálvez, donde serán reemplazados los mosaicos faltantes o rotos a lo largo de la explanada ubicada en el Parque Cultural Hidalguense en Pachuca, obra proyectada por la Sipdus con fecha de conclusión al 28 de febrero de 2027.</t>
+  </si>
+  <si>
+    <t>Patrimonio cultural</t>
+  </si>
+  <si>
+    <t>La Sipdus licitó los trabajos de restauración y reemplazo de piezas cerámicas del pisal Homenaje a la mujer del mundo en el Parque Cultural Hidalguense de Pachuca.</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Sipdus, Oficialía Mayor, Gobernador</t>
+  </si>
+  <si>
+    <t>Byron Gálvez, Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>Carecen de Atlas de Riesgos 15 municipios afectados por vaguada</t>
+  </si>
+  <si>
+    <t>Quince de los 28 municipios con mayores afectaciones por lluvias y la vaguada monzónica carecen de un Atlas de Riesgos actualizado, por lo que la Subsecretaría de Protección Civil estatal brindó capacitación a las autoridades locales para elaborar mapas de peligro temporales y alcanzar la cobertura total de los 84 ayuntamientos.</t>
+  </si>
+  <si>
+    <t>Atlas de Riesgos</t>
+  </si>
+  <si>
+    <t>Protección Civil estatal capacitó a 15 ayuntamientos afectados por contingencias climatológicas que carecen de un Atlas de Riesgos actualizado.</t>
+  </si>
+  <si>
+    <t>Segobh, PC, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Para 2027, prevén 500 mdp para contingencias naturales</t>
+  </si>
+  <si>
+    <t>La Secretaría de Hacienda del Estado proyecta etiquetar alrededor de 500 millones de pesos dentro del Paquete Hacendario 2027 para la prevención y atención de contingencias derivadas de desastres naturales en Hidalgo. La titular de la dependencia, María Esther Ramírez Vargas, señaló que el proyecto de presupuesto se entregará al Congreso a más tardar el 19 de noviembre.</t>
+  </si>
+  <si>
+    <t>Presupuesto De Egresos</t>
+  </si>
+  <si>
+    <t>La Secretaría de Hacienda de Hidalgo alista una partida de 500 mdp en el Paquete Hacendario 2027 para la atención de emergencias y fenómenos naturales.</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>Hacienda</t>
+  </si>
+  <si>
+    <t>Hacienda, Gobernador, Congreso, Presidencia</t>
+  </si>
+  <si>
+    <t>María Esther Ramírez Vargas</t>
+  </si>
+  <si>
+    <t>Gobierno afina reunión para lograr pacto electoral</t>
+  </si>
+  <si>
+    <t>El secretario de Gobierno, Guillermo Olivares Reyna, anunció que entablará reuniones con las dirigencias de partidos políticos y autoridades electorales para establecer un pacto de civilidad cívica e institucional previo al arranque oficial del proceso electoral 2027 en diciembre próximo, en el que se renovarán 18 diputaciones locales y 84 ayuntamientos.</t>
+  </si>
+  <si>
+    <t>Proceso electoral</t>
+  </si>
+  <si>
+    <t>La Secretaría de Gobierno convocará a partidos políticos e IEEH para consolidar un pacto de respeto institucional rumbo a las elecciones locales de 2027.</t>
+  </si>
+  <si>
+    <t>Segobh, IEEH, PT, Congreso</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna, Damián Sosa Castelán, María Magdalena González Escalona</t>
+  </si>
+  <si>
+    <t>Para evitar compra de votos, Sebiso blindará programas</t>
+  </si>
+  <si>
+    <t>El titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, confirmó la publicación de las reglas de operación y el cierre oportuno del padrón de beneficiarios a inicios de 2027 para establecer la veda electoral y evitar el uso clientelar o condicionado de los apoyos sociales en los comicios.</t>
+  </si>
+  <si>
+    <t>Programas Del Bienestar</t>
+  </si>
+  <si>
+    <t>La Sebiso implementará un blindaje institucional en sus padrones para impedir el condicionamiento de programas sociales en las elecciones de 2027.</t>
+  </si>
+  <si>
+    <t>Nathali González</t>
+  </si>
+  <si>
+    <t>Bienestar, Gobernador</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Siguen abiertas las investigaciones por destrozos en la SEPH</t>
+  </si>
+  <si>
+    <t>El encargado del despacho de la PGJEH, Francisco Fernández Hasbun, informó que continúan en integración las carpetas de investigación por los daños materiales calculados en 6 millones de pesos causados a la sede de la SEPH por estudiantes de la Escuela Normal Rural El Mexe en febrero pasado, manteniendo además canales de diálogo directo con familiares del joven fallecido.</t>
+  </si>
+  <si>
+    <t>La PGJEH mantiene abiertas las indagatorias por los destrozos en la sede de la SEPH cometidos por estudiantes de El Mexe y da seguimiento a carpetas de investigación.</t>
+  </si>
+  <si>
+    <t>PGJEH, SEPH, Presidencia</t>
+  </si>
+  <si>
+    <t>Francisco Fernández Hasbun, Natividad Castrejón Valdez, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Fortalece IHE la identidad cultural en Ixmiquilpan con Cazadores de saberes</t>
+  </si>
+  <si>
+    <t>El Centro Estatal de Lenguas y Culturas Indígenas (CELCI) del IHE presentó la revista número 22 Cazadores de saberes en la Escuela Primaria Indígena El Nigromante en Ixmiquilpan, obra colectiva elaborada por artesanos, médicos tradicionales y familias para promover el patrimonio cultural e idioma náhuatl y otomí.</t>
+  </si>
+  <si>
+    <t>Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Preservación Lenguas Maternas</t>
+  </si>
+  <si>
+    <t>El IHE y el CELCI entregaron en Ixmiquilpan la edición 22 de la revista Cazadores de saberes para preservar la riqueza cultural de los pueblos indígenas.</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Ortega Sánchez, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Aumenta demanda estatal de atención por metanfetaminas</t>
+  </si>
+  <si>
+    <t>De acuerdo con el informe epidemiológico de los Centros de Integración Juvenil (CIJ Pachuca), las metanfetaminas se consolidaron como la principal droga de impacto en Hidalgo al representar el 63.2% de las solicitudes de tratamiento en el primer semestre de 2026 con 171 casos registrados, desplazando al cannabis y al alcohol.</t>
+  </si>
+  <si>
+    <t>Consumo De Drogas</t>
+  </si>
+  <si>
+    <t>Los CIJ de la Secretaría de Salud reportaron que las metanfetaminas se ubicaron como la causa principal de atención de adicciones en Hidalgo con el 63.2% de los pacientes.</t>
+  </si>
+  <si>
+    <t>BUSCAN BLINDAR LA ELECCIÓN MEDIANTE PACTO DE CIVILIDAD</t>
+  </si>
+  <si>
+    <t>Partidos políticos y aspirantes independientes serán convocados en los próximos días a mesas de trabajo para acordar un pacto de civilidad que regule su participación durante el proceso electoral 2026-2027 en Hidalgo. El secretario de Gobierno, Guillermo Olivares Reyna, adelantó que el llamado incluirá a las fuerzas políticas acreditadas ante los órganos electorales nacionales y estatales, con el propósito de que conozcan y respeten las nuevas disposiciones del Código Electoral de Hidalgo.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Gobierno convocará a partidos políticos y aspirantes independientes a mesas de diálogo para pactar civilidad y respeto a la ley en las elecciones de 2027.</t>
+  </si>
+  <si>
+    <t>Teodoro Santos</t>
+  </si>
+  <si>
+    <t>Segobh, IEEH, TEEH, Congreso</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna</t>
+  </si>
+  <si>
+    <t>REPORTAN SALDO BLANCO EN CELEBRACIONES DE INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>Ante cientos de familias hidalguenses se celebró el desfile conmemorativo por la Independencia de México encabezado por el gobernador Julio Menchaca Salazar, reportando los 84 municipios saldo blanco y tranquilidad durante los festejos patrios.</t>
+  </si>
+  <si>
+    <t>Desfile cívico</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca presidió el desfile cívico-militar en Pachuca, reportando saldo blanco en los 84 municipios durante las Fiestas Patrias.</t>
+  </si>
+  <si>
+    <t>Gobernador, SSPH, Sedena, GN, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Salvador Cruz Neri</t>
+  </si>
+  <si>
+    <t>ARRANCAN OBRAS EN PISAL DEL PARQUE</t>
+  </si>
+  <si>
+    <t>La obra Homenaje a la Mujer del Mundo de Byron Gálvez será intervenida a finales de este mes, informó la Oficialía Mayor. Los trabajos contemplan el reemplazo de mosaicos dañados y restauración de piezas fracturadas.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor y Sipdus iniciarán a finales de septiembre la rehabilitación y reemplazo de mosaicos del pisal de Byron Gálvez en Pachuca.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Sipdus, Cultura, Gobernador</t>
+  </si>
+  <si>
+    <t>Edgar Orlando Ángeles Pérez, Byron Gálvez</t>
+  </si>
+  <si>
+    <t>EN HIDALGO, NI FOSAS CLANDESTINAS NI CASOS DE DESAPARICIÓN FORZADA</t>
+  </si>
+  <si>
+    <t>Hidalgo no registra casos de desaparición forzada, además en los cuatro años del gobierno del estado no se han localizado fosas clandestinas, de acuerdo con la encargada de la Subprocuraduría de Delitos de Género, Desaparición de Personas e Impacto Social, Lorena Cano García. La funcionaria precisó que la mayoría de los expedientes iniciados corresponden a ausencias voluntarias.</t>
+  </si>
+  <si>
+    <t>Desapariciones</t>
+  </si>
+  <si>
+    <t>La PGJEH aclaró que en cuatro años no hay registros de fosas clandestinas ni desaparición forzada en Hidalgo, correspondiendo la mayoría de los casos a ausencias voluntarias.</t>
+  </si>
+  <si>
+    <t>PGJEH, CBPEIH, Presidencia</t>
+  </si>
+  <si>
+    <t>Lorena Cano García</t>
+  </si>
+  <si>
+    <t>SÓLO 22 CONFORMAN FUERZA DE BÚSQUEDA ESTATAL DE PERSONAS</t>
+  </si>
+  <si>
+    <t>La Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEIH) cuenta sólo con alrededor de 22 personas para las acciones de búsqueda en los 84 municipios, apoyándose con corporaciones de Seguridad Pública y la Procuraduría estatal, informó el comisionado Francisco García Reyes.</t>
+  </si>
+  <si>
+    <t>Déficit policial</t>
+  </si>
+  <si>
+    <t>La Comisión de Búsqueda de Personas de Hidalgo opera con un déficit de personal de sólo 22 integrantes para atender a los 84 municipios, apoyándose en la SSPH y la PGJEH.</t>
+  </si>
+  <si>
+    <t>Segobh, CBPEIH, SSPH, PGJEH, Presidencia</t>
+  </si>
+  <si>
+    <t>Francisco García Reyes</t>
+  </si>
+  <si>
+    <t>LLUVIAS AFECTAN LAS VIALIDADES</t>
+  </si>
+  <si>
+    <t>Derivado de las lluvias recientes existen afectaciones a las principales vialidades de Pachuca y de otros puntos de Hidalgo, reconoció el titular de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS), Alejandro Sánchez García, requiriendo reparaciones a las empresas contratistas.</t>
+  </si>
+  <si>
+    <t>Vialidad En Mal Estado</t>
+  </si>
+  <si>
+    <t>La Sipdus reconoció afectaciones en las vialidades principales de Pachuca por las lluvias recientes y requirió a las empresas constructoras reparar los baches y daños en obras públicas.</t>
+  </si>
+  <si>
+    <t>Sipdus, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Alejandro Sánchez García</t>
+  </si>
+  <si>
+    <t>REHABILITARÁN “EL PISAL” EN PACHUCA</t>
+  </si>
+  <si>
+    <t>El gobierno de Hidalgo trabaja desde hace seis meses en la rehabilitación de la obra “Homenaje a la Mujer del Mundo”, de Byron Gálvez, conocida como “El Pisal”, ubicada en el Parque Cultural Hidalguense, informó el titular de la Oficialía Mayor, Edgar Ángeles.</t>
+  </si>
+  <si>
+    <t>El gobierno estatal invertirá en la rehabilitación del pisal de Byron Gálvez en Pachuca, sustituyendo piezas dañadas conforme al diseño original con fecha de término en marzo de 2027.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Sipdus, Cultura</t>
+  </si>
+  <si>
+    <t>REPUVE LLEVA MÓDULO MÓVIL A LOCALIDADES</t>
+  </si>
+  <si>
+    <t>Registrar un vehículo ante el Repuve será más accesible para habitantes de municipios que no cuentan con un módulo fijo, luego de que Hidalgo incorporó una unidad itinerante para realizar gratuitamente la colocación del chip de identificación vehicular.</t>
+  </si>
+  <si>
+    <t>Padrón vehicular</t>
+  </si>
+  <si>
+    <t>La SSPH activó una unidad móvil del Repuve que acudirá a comunidades e itinerarios municipales para instalar chips de registro vehicular sin costo.</t>
+  </si>
+  <si>
+    <t>SSPH, Segobh, Bienestar</t>
+  </si>
+  <si>
+    <t>CONVIERTEN LACTOSUERO EN PRODUCTOS SUSTENTABLES</t>
+  </si>
+  <si>
+    <t>Un residuo de la industria quesera del Valle de Tulancingo se convirtió en materia prima para un proyecto desarrollado por estudiantes del Conalep Tulancingo. Se trata del lactosuero, del que diariamente se generan 492 mil litros en la región y cerca de 72 por ciento se desecha sin tratamiento.</t>
+  </si>
+  <si>
+    <t>Economía Circular</t>
+  </si>
+  <si>
+    <t>Estudiantes del Conalep Tulancingo transformaron mermas de lactosuero en biofertilizantes, ecoladrillos y productos sustentables para combatir la contaminación ambiental.</t>
+  </si>
+  <si>
+    <t>SEPH, Conalep, Semarnath</t>
+  </si>
+  <si>
+    <t>Habrá segunda etapa de obras viales cerca de la glorieta 24 Horas</t>
+  </si>
+  <si>
+    <t>Una segunda etapa de intervención vial en los alrededores de la glorieta del puente atirantado contempla la colocación de nuevas luminarias, adecuaciones en calles aledañas y un carril adicional sobre el bulevar Colosio. Así lo informó Alejandro Sánchez García, secretario de Infraestructura Pública y Desarrollo Urbano Sostenible de Hidalgo (Sipdus), quien explicó que son trabajos complementarios a los realizados en la zona desde 2025.</t>
+  </si>
+  <si>
+    <t>Glorieta 24 Horas</t>
+  </si>
+  <si>
+    <t>La Sipdus alista la segunda etapa de adecuaciones viales, iluminación y carril adicional en las inmediaciones de la glorieta 24 Horas en el bulevar Colosio.</t>
+  </si>
+  <si>
+    <t>REPORTARON SALDO BLANCO DURANTE LAS FIESTAS PATRIAS</t>
+  </si>
+  <si>
+    <t>Los festejos por el Grito de Independencia en las plazas públicas de los 84 municipios de Hidalgo resultaron con saldo blanco, informó el gobernador Julio Menchaca Salazar tras encabezar el desfile cívico militar del 16 de septiembre en Pachuca. Además, el titular de la Secretaría de Seguridad Pública de Hidalgo (SSPH), Salvador Cruz Neri, comentó que no hubo disparos al aire libre y decomisaron poca pirotecnia.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca y la SSPH reportaron saldo blanco en los 84 municipios durante las celebraciones del Grito y desfiles del 16 de septiembre.</t>
+  </si>
+  <si>
+    <t>Gobernador, SSPH, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Familias pachuqueñas disfrutan desfile patrio</t>
+  </si>
+  <si>
+    <t>La jornada comenzó por la mañana en la plaza Constitución, donde el gobernador Julio Menchaca Salazar encabezó la Guardia de Honor y depósito de una ofrenda floral con motivo del 216 aniversario del inicio de la Independencia de México. Apenas un par de horas después, familias pachuqueñas ocuparon las banquetas del Centro Histórico para presenciar el desfile con la participación de 2,701 estudiantes, 150 integrantes del Pentatlón, 750 elementos de seguridad y bomberos, además de corporaciones ecuestres y charras.</t>
+  </si>
+  <si>
+    <t>Crónica</t>
+  </si>
+  <si>
+    <t>Familias de Pachuca presenciaron el desfile del 16 de septiembre en el Centro Histórico con la participación de contingentes escolares, corporaciones de seguridad y agrupaciones de charros.</t>
+  </si>
+  <si>
+    <t>Gobernador, SSPH, Bomberos, PC, Cruz Roja, GN, Sedena, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Anuncian rehabilitación del pisal del Parque Cultural Hidalguense</t>
+  </si>
+  <si>
+    <t>A finales de septiembre iniciará la rehabilitación del pisal ubicado en el Parque Cultural Hidalguense, trabajos que se extenderán hasta marzo de 2027, informó Edgar Orlando Ángeles Pérez, oficial Mayor. Las labores contemplan la sustitución de piezas, por lo que el proveedor ganador de la licitación deberá reponer las faltantes a la medida y con características del diseño original de Byron Gálvez.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor y Sipdus iniciarán la restauración del pisal Homenaje a la Mujer del Mundo en Pachuca, reemplazando mosaicos fracturados hasta marzo de 2027.</t>
+  </si>
+  <si>
+    <t>Hidalgo suma siete muertes maternas este año; superó el registro de 2025</t>
+  </si>
+  <si>
+    <t>Durante la primera semana de septiembre, Hidalgo registró una muerte materna, con la que acumuló siete casos en lo que va del año, cifra que ya superó los seis decesos ocurridos en 2025, de acuerdo con la Secretaría de Salud federal. Al respecto, la titular de la SSH, Vanesa Escalante Arroyo, indicó que reforzarán las campañas de difusión para la prevención sobre signos de alarma en pacientes embarazadas, especialmente por preeclampsia.</t>
+  </si>
+  <si>
+    <t>Salud materna</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud federal reportó siete muertes maternas en Hidalgo durante 2026, superando la cifra total de 2025, ante lo cual la SSH reforzará la prevención de preeclampsia.</t>
+  </si>
+  <si>
+    <t>SSH, IMSS, ISSSTE, IMSS-Bienestar, Presidencia</t>
+  </si>
+  <si>
+    <t>INVESTIGAN ASESINATO DEL SACERDOTE ROMÁN</t>
+  </si>
+  <si>
+    <t>La Procuraduría General de Justicia de Hidalgo (PGJEH) investiga el hallazgo sin vida de un sacerdote en Lolotla, mientras que el Obispado de Huejutla realizó un llamado para que el hecho se esclarezca. La víctima es el presbítero Román de la Cruz Hernández, originario de Mazahuacán, quien ejercía como párroco en la iglesia de Santa Cruz, Huejutla. En el sitio se halló un mensaje presuntamente vinculado a un grupo delictivo.</t>
+  </si>
+  <si>
+    <t>Lolotla</t>
+  </si>
+  <si>
+    <t>La PGJEH investiga el asesinato del sacerdote Román de la Cruz Hernández en Lolotla, mientras el obispado de Huejutla y la CEM demandaron el esclarecimiento de los hechos.</t>
+  </si>
+  <si>
+    <t>Francisco Bautista</t>
+  </si>
+  <si>
+    <t>PGJEH, Presidencia, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Román de la Cruz Hernández, Francisco Ángel Fernández Hasbún, José Hirais Acosta Beltrán</t>
+  </si>
+  <si>
+    <t>CONTINÚA LA PGJEH INVESTIGACIÓN POR MUERTE EN EL MEXE</t>
+  </si>
+  <si>
+    <t>El encargado de la Procuraduría General de Justicia del Estado de Hidalgo (PGJEH), Francisco Fernández Hasbun, descartó órdenes de aprehensión por el hallazgo sin vida de un estudiante de la Normal Rural El Mexe; se reunió con un tío del fallecido para informarle sobre los avances en las indagatorias y confirmó que las carpetas por los destrozos en la SEPH en febrero continúan abiertas.</t>
+  </si>
+  <si>
+    <t>La PGJEH descartó órdenes de aprehensión inmediatas por el homicidio de un alumno de El Mexe tras informar avances a un familiar y mantiene abiertas las carpetas de investigación por destrozos en la SEPH.</t>
+  </si>
+  <si>
+    <t>Francisco Fernández Hasbun, José Antonio Salgado, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>CONTROVERSIAS CONTRA EL RECTOR DE UPP QUEDARON RESUELTAS: SEPH</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, dio a conocer que se aclararon los señalamientos contra el rector de la UPP, Francisco Hernández Jiménez, explicando que cuenta con dos maestrías concluidas en proceso de registro e instruyó a los Órganos Internos de Control verificar los contratos de uniformes universitarios.</t>
+  </si>
+  <si>
+    <t>Irregularidades en escuela</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón, declaró resueltas las dudas sobre el registro académico del rector de la UPP y solicitó auditar la adquisición de uniformes institucionales.</t>
+  </si>
+  <si>
+    <t>SEPH, Contraloría</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Francisco Hernández Jiménez</t>
+  </si>
+  <si>
+    <t>JULIO MENCHACA ENCABEZA EL GRITO DE INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>Al grito de "¡Viva la Transformación!", el gobernador Julio Menchaca Salazar encabezó el acto del 216 Aniversario del inicio de la Independencia de México desde el balcón de Palacio de Gobierno en plaza Juárez ante miles de asistentes, acompañado por representantes del Congreso local y del Tribunal Superior de Justicia, culminando con el concierto de Carlos Rivera.</t>
+  </si>
+  <si>
+    <t>Grito De Independencia</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca vitoreó a los héroes de la Patria y a la transformación de Hidalgo en la plaza Juárez durante la ceremonia del Grito de Independencia.</t>
+  </si>
+  <si>
+    <t>Gobernador, Congreso, TSJEH, Presidencia, Sedena</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Andrés Velázquez Vázquez, Rebeca Stella Aladro Echeverría, Carlos Rivera</t>
+  </si>
+  <si>
+    <t>AUTORIDADES ASEGURAN SALDO BLANCO DURANTE LAS FIESTAS PATRIAS DE 2026</t>
+  </si>
+  <si>
+    <t>Corporaciones de seguridad reportaron un desarrollo tranquilo y con saldo blanco durante los festejos patrios en los 84 municipios de Hidalgo. El secretario de Seguridad, Salvador Cruz Neri, desmintió reportes de detonaciones de arma de fuego, mientras que el alcalde de Pachuca, Jorge Reyes, informó de seis sancionados en el alcoholímetro sin detenidos.</t>
+  </si>
+  <si>
+    <t>La SSPH y la alcaldía de Pachuca confirmaron saldo blanco en las celebraciones patrias de la entidad, reportando decomiso de pirotecnia y seis conductores sancionados en el alcoholímetro.</t>
+  </si>
+  <si>
+    <t>SSPH, Ayuntamiento, PC</t>
+  </si>
+  <si>
+    <t>Salvador Cruz Neri, Jorge Reyes Hernández</t>
+  </si>
+  <si>
+    <t>ATRIBUYE SIPDUS DAÑOS EN VIALIDADES A LLUVIAS</t>
+  </si>
+  <si>
+    <t>El secretario de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus), Alejandro Sánchez García, consideró normales los encharcamientos, baches y daños en obras recién rehabilitadas como los bulevares Minero, Everardo Márquez y Felipe Ángeles debido a las intensas precipitaciones pluviométricas del año, asegurando que las empresas contratistas responderán mediante fianzas de vicios ocultos.</t>
+  </si>
+  <si>
+    <t>El titular de Sipdus, Alejandro Sánchez, justificó las inundaciones y deterioros en calles y bulevares de Pachuca por la carga atípica de lluvias e indicó que las constructoras harán efectivas las garantías de obra.</t>
+  </si>
+  <si>
+    <t>INICIA EN OCTUBRE RESTAURACIÓN DEL PISAL DE PACHUCA</t>
+  </si>
+  <si>
+    <t>El oficial mayor del gobierno estatal, Edgar Orlando Ángeles Pérez, dio a conocer que a inicios de octubre comenzará la intervención del pisal "Homenaje a la Mujer del Mundo" de Byron Gálvez en el Parque Cultural Hidalguense de Pachuca, con una duración proyectada de seis meses y dividido en seis tramos con accesos restringidos temporales.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor y Sipdus licitaron la restauración por etapas del pisal de Byron Gálvez en el Parque Cultural Hidalguense, contemplando seis meses de ejecución a partir de octubre.</t>
+  </si>
+  <si>
+    <t>MÁS DE 4 MIL PARTICIPARON EN EL DESFILE CÍVICO MILITAR</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar presenció el desfile cívico militar conmemorativo del 216 Aniversario de la Independencia de México en el Centro Histórico de Pachuca, donde marcharon 2,701 estudiantes, 150 miembros del Pentatlón, 216 agentes municipales, 750 elementos de la SSPH y Bomberos, Guardia Nacional, Ejército Mexicano y agrupaciones charras.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca encabezó la parada cívico-militar en el centro de Pachuca con la marcha de más de 4 mil alumnos y efectivos de las corporaciones de seguridad.</t>
+  </si>
+  <si>
+    <t>Gobernador, SSPH, Sedena, GN, Cruz Roja, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>REPUNTARON EN HUASCA LOS DELITOS FRAUDE Y LESIONES</t>
+  </si>
+  <si>
+    <t>Datos del SESNSP reflejaron que entre enero y julio de 2026 las denuncias por fraude pasaron de 0 a 9 en Huasca de Ocampo, las lesiones se elevaron de 19 a 26 casos y se contabilizaron 2 homicidios, en contraste con disminuciones en robo y despojo.</t>
+  </si>
+  <si>
+    <t>Huasca</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>El Secretariado Ejecutivo reportó incrementos en las carpetas de investigación por fraude y lesiones en Huasca de Ocampo en el primer semestre.</t>
+  </si>
+  <si>
+    <t>Martha Sáenz</t>
+  </si>
+  <si>
+    <t>RESCATAN SABERES INDÍGENAS</t>
+  </si>
+  <si>
+    <t>El IHE y el CELCI presentaron en la primaria El Nigromante de Ixmiquilpan la edición 22 de la revista Cazadores de saberes para fomentar el conocimiento de las tradiciones y lenguas náhuatl y otomí entre la niñez hidalguense.</t>
+  </si>
+  <si>
+    <t>Autoridades del IHE y del CELCI difundieron en Ixmiquilpan la edición 22 de la revista Cazadores de saberes para preservar la identidad de los pueblos originarios.</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Ortega Sánchez, Julio Menchaca Salazar, Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>SALDO BLANCO EN HIDALGO TRAS FESTEJOS PATRIOS</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, gobernador de Hidalgo, informó que tras las celebraciones por el 216 aniversario de la Independencia de México en los 84 municipios de Hidalgo se registró saldo blanco, destacando el despliegue de 5 mil 580 elementos de seguridad estatal y municipal.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca y la SSPH reportaron saldo blanco en los 84 municipios durante las celebraciones del Grito de Independencia con despliegue de 5,580 elementos.</t>
+  </si>
+  <si>
+    <t>UN TOTAL DE 7 MUERTES MATERNAS EN LA ENTIDAD</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud Federal informó que durante 2026 la entidad registró un total de siete muertes maternas en el sector salud (SSH, IMSS, IMSS-Bienestar y particulares), derivado de hemorragias, trastornos hipertensivos y complicaciones del parto, por lo que la SSH exhortó a llevar control prenatal.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud Federal reportó siete muertes maternas en Hidalgo durante 2026, por lo que las autoridades sanitarias instaron a acudir a revisiones prenatales preventivas.</t>
+  </si>
+  <si>
+    <t>SSH, IMSS, IMSS-Bienestar, Presidencia</t>
+  </si>
+  <si>
+    <t>Concluye el 216 aniversario del inicio de la Independencia</t>
+  </si>
+  <si>
+    <t>Con la participación de más de 5 mil estudiantes, elementos de seguridad, Fuerzas Armadas, cuerpos de emergencia y charros, concluyeron los festejos por el 216 Aniversario de la Independencia en Pachuca con el Desfile Cívico-Militar encabezado por el gobernador Julio Menchaca Salazar.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca encabezó el Desfile Cívico-Militar en el centro de Pachuca con la marcha de más de 5 mil alumnos, efectivos de seguridad y agrupaciones ecuestres.</t>
+  </si>
+  <si>
+    <t>Acercan registro vehicular gratuito a todas las regiones</t>
+  </si>
+  <si>
+    <t>La Secretaría de Gobierno de Hidalgo incorporó una unidad móvil del Registro Público Vehicular (Repuve) para recorrer municipios sin módulo fijo y colocar gratuitamente el chip de identificación vehicular en 15 minutos, fortaleciendo la certeza jurídica y la prevención de delitos.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Gobierno puso en operación un módulo itinerante del Repuve para colocar gratuitamente el chip de registro vehicular en comunidades sin módulos fijos.</t>
+  </si>
+  <si>
+    <t>Segobh, Gobernador, Bienestar</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Guillermo Olivares Reyna</t>
+  </si>
+  <si>
+    <t>Negaron hackeo y vulneración del sistema del C5i de Hidalgo</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo desmintió categóricamente rumores difundidos en redes sociales sobre un supuesto hackeo o vulneración de los sistemas de inteligencia del C5i, confirmando la solidez de sus esquemas cibernéticos e infraestructura tecnológica.</t>
+  </si>
+  <si>
+    <t>Ciberseguridad</t>
+  </si>
+  <si>
+    <t>La SSPH desmintió haber sufrido un hackeo en la plataforma del C5i de Hidalgo, asegurando que los sistemas operan con esquemas de protección cibernética blindados.</t>
+  </si>
+  <si>
+    <t>SSPH, C5i</t>
+  </si>
+  <si>
+    <t>Balacearon y ejecutaron a un sacerdote católico, en Lolotla</t>
+  </si>
+  <si>
+    <t>Vecinos de Lolotla hallaron sin vida al sacerdote católico Román de la Cruz Hernández, de 48 años, párroco de la iglesia de la Santa Cruz en Huejutla, con heridas de arma de fuego y una cartulina con un mensaje amenazante dejada en su espalda a la orilla de la carretera Tetlapaya-Hueyapa. La PGJEH inició carpeta de investigación.</t>
+  </si>
+  <si>
+    <t>El párroco de Huejutla, Román de la Cruz Hernández, fue localizado ejecutado con disparos y un mensaje amenazante a la orilla de la carretera en Lolotla, abriéndose la carpeta de investigación en la PGJEH.</t>
+  </si>
+  <si>
+    <t>PGJEH, SSPH, Presidencia</t>
+  </si>
+  <si>
+    <t>Román de la Cruz Hernández</t>
+  </si>
+  <si>
+    <t>ASEGURAN PUNTO DE VENTA DE NARCÓTICOS</t>
+  </si>
+  <si>
+    <t>Mediante orden de cateo en Ciudad Sahagún, Tepeapulco, elementos de la SSPH, PGJEH y Sedena desmantelaron un centro de distribución de drogas en la colonia Rojo Gómez, decomisando 1,073 dosis de cristal, 240 de marihuana, un arma de fuego larga, chalecos tácticos y básculas de precisión.</t>
+  </si>
+  <si>
+    <t>Operativo conjunto de la SSPH, PGJEH y Ejército Mexicano desarticuló un punto de narcomenudeo en Ciudad Sahagún, asegurando más de 1,300 dosis de narcóticos y armas de fuego.</t>
+  </si>
+  <si>
+    <t>MÁS DE 4 MIL PERSONAS PARTICIPARON EN DESFILE CÍVICO-MILITAR EN PACHUCA</t>
+  </si>
+  <si>
+    <t>Con la participación de estudiantes, elementos de seguridad, cuerpos de emergencia, integrantes de las Fuerzas Armadas y asociaciones de charros, Hidalgo concluyó este miércoles las actividades conmemorativas por el 216 aniversario del Inicio de la Independencia de México con un desfile cívico-militar por las calles del Centro Histórico de Pachuca. El contingente estuvo integrado por 2,701 estudiantes de educación básica, media superior y superior, además de corporaciones de seguridad y rescate.</t>
+  </si>
+  <si>
+    <t>Con la participación de 2,701 estudiantes, corporaciones policiales y militares, concluyeron los festejos patrios en Pachuca con el Desfile Cívico-Militar y saldo blanco estatal.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Román Bernal Díaz</t>
+  </si>
+  <si>
+    <t>Rehabilitación del Pisal Monumental podría concluir en marzo de 2027</t>
+  </si>
+  <si>
+    <t>La rehabilitación y mantenimiento del Pisal Monumental 'Homenaje a la Mujer del Mundo', obra del artista Byron Gálvez ubicada en el Parque Cultural Hidalguense en Pachuca, podría concluir en marzo de 2027, informó el titular de la Oficialía Mayor, Edgar Orlando Ángeles Pérez. El proyecto contempla seis etapas ejecutadas junto con Sipdus para evitar el cierre total del espacio.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor y Sipdus licitarán a finales de septiembre la restauración por seis etapas del pisal de Byron Gálvez en Pachuca, proyectando concluir en marzo de 2027.</t>
+  </si>
+  <si>
+    <t>Demandas de “El Mexe” continuarán en atención durante los próximos años: Castrejón</t>
+  </si>
+  <si>
+    <t>Tras la manifestación de estudiantes de la Normal Rural El Mexe durante el informe de la presidenta Claudia Sheinbaum en Pachuca, el secretario de Educación Pública de Hidalgo, Natividad Castrejón, señaló que se mantendrá el diálogo institucional continuo para atender sus solicitudes educativas e infraestructura.</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón, afirmó que la atención a las peticiones de los normalistas de El Mexe continuará durante los próximos años mediante el subsecretario Daniel Fragoso.</t>
+  </si>
+  <si>
+    <t>SEPH, PGJEH, Presidencia</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Daniel Fragoso Torres, Francisco Fernández Hasbun, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Grandes cantidades de agua están afectando la infraestructura pública: SIPDUS</t>
+  </si>
+  <si>
+    <t>El titular de la SIPDUS, Alejandro Sánchez García, reconoció que las precipitaciones atípicas han afectado las vialidades en Pachuca, destacando que los trabajos de infraestructura realizados han permitido desfogar el agua en cuestión de horas en puntos críticos como el bulevar Minero y Colosio.</t>
+  </si>
+  <si>
+    <t>La Sipdus atribuyó el deterioro de calles y baches en Pachuca a la acumulación de lluvias de la temporada, descartando fallas permanentes en obras recientes.</t>
+  </si>
+  <si>
+    <t>SALDO BLANCO EN HIDALGO DURANTE FESTEJOS PATRIOS</t>
+  </si>
+  <si>
+    <t>La noche del 15 de septiembre transcurrió con saldo blanco en Hidalgo, de acuerdo con el gobernador Julio Menchaca Salazar, quien informó que no se registraron incidentes durante el Grito en los municipios del estado. En Pachuca se detuvieron a seis conductores en el alcoholímetro y se entregó a una menor extraviada sin lesiones.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca y autoridades municipales informaron saldo blanco en las celebraciones patrias de los 84 municipios de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Jorge Reyes Hernández</t>
+  </si>
+  <si>
+    <t>CAMBIAN DE EMPRESA PARA REPARAR EL PISAL DEDICADO A LA MUJER</t>
+  </si>
+  <si>
+    <t>Una empresa distinta a la que elaboró originalmente el Pisal 'Homenaje a la Mujer del Mundo' intervendrá la obra de Byron Gálvez por fracturas y piezas ausentes, informó el Oficial Mayor, Orlando Ángeles Pérez. Explicó que la licitación se emitirá entre septiembre u octubre para concluir en marzo de 2027.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor licitará la intervención del pisal de Byron Gálvez en Pachuca para reponer mosaicos a medida respetando el diseño original.</t>
+  </si>
+  <si>
+    <t>SIN DEMANDAS CONTRA FIRMAS CONSTRUCTORAS POR MALAS OBRAS</t>
+  </si>
+  <si>
+    <t>La Sipdus informó que no mantiene procesos contra empresas por fallas estructurales o baches, ya que las compañías cuentan con fianza por vicios ocultos de un año, reconociendo el titular Alejandro Sánchez que las lluvias atípicas han generado afectaciones temporales en calles y bulevares.</t>
+  </si>
+  <si>
+    <t>El titular de Sipdus descartó litigios contra empresas por baches o socavones al señalar que las lluvias han causado daños y las constructoras aplicarán garantías.</t>
+  </si>
+  <si>
+    <t>IGLESIA CONDENA HOMICIDIO DE SACERDOTE DE HUEJUTLA</t>
+  </si>
+  <si>
+    <t>La Diócesis de Huejutla y la Conferencia del Episcopado Mexicano (CEM) exigieron esclarecer el asesinato del sacerdote Román de la Cruz Hernández, de 48 años, ocurrido en Lolotla, mientras la PGJEH integra la carpeta de investigación correspondiente.</t>
+  </si>
+  <si>
+    <t>La Iglesia católica exigió a las autoridades de Hidalgo esclarecer el homicidio del párroco Román de la Cruz localizado en Lolotla.</t>
+  </si>
+  <si>
+    <t>Román de la Cruz Hernández, José Hirais Acosta Beltrán</t>
+  </si>
+  <si>
+    <t>La escuela primaria Aquiles Serdán en Tulancingo deberá ser demolida y reconstruida en su totalidad por fallas estructurales severas, informó el titular de la SEPH, Natividad Castrejón. Las obras durarán un ciclo escolar completo.</t>
+  </si>
+  <si>
+    <t>La SEPH sustituirá completamente la infraestructura de la primaria Aquiles Serdán en Tulancingo al detectar daños graves en la estructura.</t>
   </si>
 </sst>
 </file>
@@ -1347,8 +1341,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ59" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ59" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ57" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ57" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1780,7 +1774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1930,19 +1924,19 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F2" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1966,19 +1960,19 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>58</v>
@@ -1990,36 +1984,36 @@
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F3" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -2028,7 +2022,7 @@
         <v>61</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2043,19 +2037,19 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>58</v>
@@ -2067,45 +2061,45 @@
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F4" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2120,10 +2114,10 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>57</v>
@@ -2144,42 +2138,40 @@
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AG4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>122</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="AJ4" s="2"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F5" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>49</v>
@@ -2197,19 +2189,19 @@
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="Y5" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>58</v>
@@ -2221,45 +2213,45 @@
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F6" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2274,10 +2266,10 @@
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="Y6" s="2" t="s">
         <v>57</v>
@@ -2286,7 +2278,7 @@
         <v>43</v>
       </c>
       <c r="AA6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>58</v>
@@ -2298,39 +2290,39 @@
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>136</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F7" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>45</v>
@@ -2351,19 +2343,19 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA7">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>58</v>
@@ -2375,45 +2367,45 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="AJ7" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F8" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2428,16 +2420,16 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA8">
         <v>20</v>
@@ -2452,45 +2444,45 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F9" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G9">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>61</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2505,10 +2497,10 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>57</v>
@@ -2517,51 +2509,51 @@
         <v>43</v>
       </c>
       <c r="AA9">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD9" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F10" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>45</v>
@@ -2582,19 +2574,19 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="Y10" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA10">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>58</v>
@@ -2606,43 +2598,45 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ10" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F11" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>61</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2657,19 +2651,19 @@
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA11">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>58</v>
@@ -2681,39 +2675,37 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="AJ11" s="2" t="s">
-        <v>116</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="AJ11" s="2"/>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F12" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>61</v>
@@ -2731,22 +2723,22 @@
         <v>60</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>167</v>
+        <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA12">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>58</v>
@@ -2757,46 +2749,43 @@
       <c r="AD12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AE12" t="s">
-        <v>170</v>
-      </c>
       <c r="AF12" s="2" t="s">
-        <v>41</v>
+        <v>162</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>46</v>
+        <v>163</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F13" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G13">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>49</v>
@@ -2814,19 +2803,19 @@
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Y13" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA13">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>58</v>
@@ -2838,42 +2827,42 @@
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F14" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>49</v>
@@ -2891,19 +2880,19 @@
         <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB14" s="2" t="s">
         <v>58</v>
@@ -2915,45 +2904,45 @@
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F15" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G15">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2968,19 +2957,19 @@
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Y15" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>58</v>
@@ -2992,42 +2981,42 @@
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="AG15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F16" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G16">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>49</v>
@@ -3042,22 +3031,22 @@
         <v>60</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA16">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>58</v>
@@ -3066,48 +3055,51 @@
         <v>38</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>93</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>163</v>
+        <v>41</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>191</v>
+        <v>83</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F17" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3122,19 +3114,19 @@
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA17">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>58</v>
@@ -3146,42 +3138,40 @@
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="AJ17" s="2" t="s">
-        <v>149</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AJ17" s="2"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F18" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>49</v>
@@ -3199,19 +3189,19 @@
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA18">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>58</v>
@@ -3223,39 +3213,39 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AJ18" s="2" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F19" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>45</v>
@@ -3276,25 +3266,25 @@
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD19" s="2" t="s">
         <v>44</v>
@@ -3306,30 +3296,30 @@
         <v>41</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="F20" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -3338,7 +3328,7 @@
         <v>45</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3353,48 +3343,48 @@
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD20" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="AI20" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ20" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="AJ20" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
@@ -3406,10 +3396,10 @@
         <v>212</v>
       </c>
       <c r="F21" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>61</v>
@@ -3430,19 +3420,19 @@
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>58</v>
@@ -3454,37 +3444,39 @@
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="AJ21" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F22" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G22">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>61</v>
@@ -3505,16 +3497,16 @@
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Y22" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA22">
         <v>20</v>
@@ -3523,51 +3515,51 @@
         <v>58</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD22" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="AG22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>101</v>
+        <v>221</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F23" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G23">
         <v>8</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -3582,10 +3574,10 @@
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>59</v>
@@ -3600,7 +3592,7 @@
         <v>58</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD23" s="2" t="s">
         <v>44</v>
@@ -3612,34 +3604,36 @@
         <v>41</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ23" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F24" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G24">
         <v>8</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>49</v>
@@ -3657,19 +3651,19 @@
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB24" s="2" t="s">
         <v>58</v>
@@ -3681,39 +3675,39 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="AG24" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F25" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>61</v>
@@ -3734,25 +3728,25 @@
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>112</v>
+        <v>235</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB25" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>44</v>
@@ -3764,36 +3758,34 @@
         <v>41</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="AJ25" s="2" t="s">
-        <v>116</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="AJ25" s="2"/>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F26" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>49</v>
@@ -3811,19 +3803,19 @@
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA26">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>58</v>
@@ -3835,45 +3827,43 @@
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="AJ26" s="2" t="s">
-        <v>237</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="AJ26" s="2"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F27" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -3888,10 +3878,10 @@
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>57</v>
@@ -3912,39 +3902,39 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F28" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>61</v>
@@ -3965,63 +3955,63 @@
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Y28" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA28">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AB28" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F29" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>45</v>
@@ -4039,13 +4029,13 @@
         <v>60</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>37</v>
+        <v>253</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>252</v>
+        <v>202</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>57</v>
@@ -4054,7 +4044,7 @@
         <v>43</v>
       </c>
       <c r="AA29">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB29" s="2" t="s">
         <v>58</v>
@@ -4066,39 +4056,39 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AG29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>108</v>
+        <v>255</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>254</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F30" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>45</v>
@@ -4119,7 +4109,7 @@
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>257</v>
+        <v>148</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>258</v>
@@ -4128,60 +4118,60 @@
         <v>57</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA30">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB30" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD30" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="AG30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>260</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F31" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4196,19 +4186,19 @@
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA31">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB31" s="2" t="s">
         <v>58</v>
@@ -4220,7 +4210,7 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
@@ -4229,33 +4219,33 @@
         <v>47</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="1">
+        <v>46282</v>
+      </c>
+      <c r="G32">
+        <v>9</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="F32" s="1">
-        <v>46280</v>
-      </c>
-      <c r="G32">
-        <v>8</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>42</v>
@@ -4273,7 +4263,7 @@
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="X32" s="2" t="s">
         <v>267</v>
@@ -4282,10 +4272,10 @@
         <v>57</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA32">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>58</v>
@@ -4297,45 +4287,45 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>92</v>
+        <v>268</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>182</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F33" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G33">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4350,19 +4340,19 @@
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Y33" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA33">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>58</v>
@@ -4374,42 +4364,42 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>271</v>
+        <v>85</v>
       </c>
       <c r="AG33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>272</v>
+        <v>182</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F34" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>49</v>
@@ -4427,16 +4417,16 @@
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>112</v>
+        <v>277</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y34" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA34">
         <v>20</v>
@@ -4451,39 +4441,39 @@
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="AG34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>115</v>
+        <v>279</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>116</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F35" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>45</v>
@@ -4504,16 +4494,16 @@
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA35">
         <v>40</v>
@@ -4528,45 +4518,45 @@
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="AG35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>149</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F36" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4581,10 +4571,10 @@
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="Y36" s="2" t="s">
         <v>57</v>
@@ -4605,42 +4595,42 @@
         <v>44</v>
       </c>
       <c r="AF36" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="AG36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>149</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="F37" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>42</v>
@@ -4658,19 +4648,19 @@
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="Y37" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA37">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>58</v>
@@ -4682,39 +4672,39 @@
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="F38" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>45</v>
@@ -4735,19 +4725,19 @@
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA38">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>58</v>
@@ -4759,39 +4749,39 @@
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="F39" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>45</v>
@@ -4812,19 +4802,19 @@
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>257</v>
+        <v>202</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="Y39" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA39">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB39" s="2" t="s">
         <v>58</v>
@@ -4836,42 +4826,42 @@
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>260</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="F40" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>42</v>
@@ -4889,10 +4879,10 @@
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>240</v>
+        <v>305</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="Y40" s="2" t="s">
         <v>57</v>
@@ -4901,57 +4891,55 @@
         <v>43</v>
       </c>
       <c r="AA40">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC40" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD40" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>39</v>
+        <v>307</v>
       </c>
       <c r="AG40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="AJ40" s="2" t="s">
-        <v>149</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AJ40" s="2"/>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="F41" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -4963,13 +4951,13 @@
         <v>60</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="Y41" s="2" t="s">
         <v>57</v>
@@ -4978,7 +4966,7 @@
         <v>43</v>
       </c>
       <c r="AA41">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>58</v>
@@ -4987,42 +4975,45 @@
         <v>38</v>
       </c>
       <c r="AD41" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>93</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AJ41" s="2" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F42" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>61</v>
@@ -5043,19 +5034,19 @@
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="Y42" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA42">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AB42" s="2" t="s">
         <v>58</v>
@@ -5067,45 +5058,45 @@
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>305</v>
+        <v>99</v>
       </c>
       <c r="AG42" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="AJ42" s="2" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="F43" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -5120,66 +5111,64 @@
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="Y43" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA43">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC43" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD43" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="AG43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="AJ43" s="2" t="s">
-        <v>310</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="AJ43" s="2"/>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F44" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>49</v>
@@ -5197,16 +5186,16 @@
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>313</v>
+        <v>202</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="Y44" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA44">
         <v>20</v>
@@ -5221,45 +5210,45 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>46</v>
+        <v>301</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>315</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F45" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>61</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5274,10 +5263,10 @@
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>57</v>
@@ -5292,48 +5281,48 @@
         <v>58</v>
       </c>
       <c r="AC45" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>186</v>
+        <v>325</v>
       </c>
       <c r="AJ45" s="2" t="s">
-        <v>182</v>
+        <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F46" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G46">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>49</v>
@@ -5351,19 +5340,19 @@
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>179</v>
+        <v>329</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="Y46" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA46">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AB46" s="2" t="s">
         <v>58</v>
@@ -5375,45 +5364,43 @@
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AJ46" s="2" t="s">
-        <v>182</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="AJ46" s="2"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F47" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>48</v>
+        <v>266</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5428,19 +5415,19 @@
         <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="Y47" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA47">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>58</v>
@@ -5452,45 +5439,45 @@
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="F48" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G48">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5508,7 +5495,7 @@
         <v>96</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>57</v>
@@ -5529,42 +5516,40 @@
         <v>44</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ48" s="2" t="s">
-        <v>329</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="AJ48" s="2"/>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F49" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>49</v>
@@ -5582,64 +5567,66 @@
         <v>37</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA49">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AB49" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC49" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD49" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="AJ49" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="AJ49" s="2" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F50" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>49</v>
@@ -5657,19 +5644,19 @@
         <v>37</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>336</v>
+        <v>148</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA50">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB50" s="2" t="s">
         <v>58</v>
@@ -5681,43 +5668,45 @@
         <v>44</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="AG50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AJ50" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="AJ50" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F51" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -5732,19 +5721,19 @@
         <v>37</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="Y51" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z51" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA51">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB51" s="2" t="s">
         <v>58</v>
@@ -5756,45 +5745,45 @@
         <v>44</v>
       </c>
       <c r="AF51" s="2" t="s">
-        <v>343</v>
+        <v>74</v>
       </c>
       <c r="AG51" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>191</v>
+        <v>350</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="F52" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G52">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R52">
         <v>1</v>
@@ -5809,19 +5798,19 @@
         <v>37</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>347</v>
+        <v>225</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z52" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA52">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB52" s="2" t="s">
         <v>58</v>
@@ -5833,42 +5822,42 @@
         <v>44</v>
       </c>
       <c r="AF52" s="2" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>349</v>
+        <v>227</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>116</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F53" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G53">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>49</v>
@@ -5886,19 +5875,19 @@
         <v>37</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>257</v>
+        <v>73</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z53" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA53">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB53" s="2" t="s">
         <v>58</v>
@@ -5910,39 +5899,39 @@
         <v>44</v>
       </c>
       <c r="AF53" s="2" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="AG53" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>260</v>
+        <v>358</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F54" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>45</v>
@@ -5963,16 +5952,16 @@
         <v>37</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="Y54" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z54" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA54">
         <v>20</v>
@@ -5987,42 +5976,42 @@
         <v>44</v>
       </c>
       <c r="AF54" s="2" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>108</v>
+        <v>232</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>109</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F55" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>42</v>
@@ -6040,16 +6029,16 @@
         <v>37</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z55" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA55">
         <v>40</v>
@@ -6064,42 +6053,42 @@
         <v>44</v>
       </c>
       <c r="AF55" s="2" t="s">
-        <v>359</v>
+        <v>101</v>
       </c>
       <c r="AG55" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>360</v>
+        <v>227</v>
       </c>
       <c r="AJ55" s="2" t="s">
-        <v>361</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F56" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>45</v>
+        <v>266</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>42</v>
@@ -6117,19 +6106,19 @@
         <v>37</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Y56" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z56" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AA56">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB56" s="2" t="s">
         <v>58</v>
@@ -6141,45 +6130,45 @@
         <v>44</v>
       </c>
       <c r="AF56" s="2" t="s">
-        <v>359</v>
+        <v>63</v>
       </c>
       <c r="AG56" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH56" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>242</v>
+        <v>140</v>
       </c>
       <c r="AJ56" s="2" t="s">
-        <v>149</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>365</v>
+        <v>69</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F57" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R57">
         <v>1</v>
@@ -6194,19 +6183,19 @@
         <v>37</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Y57" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z57" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AA57">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB57" s="2" t="s">
         <v>58</v>
@@ -6218,173 +6207,19 @@
         <v>44</v>
       </c>
       <c r="AF57" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="AG57" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="AJ57" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F58" s="1">
-        <v>46280</v>
-      </c>
-      <c r="G58">
-        <v>5</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R58">
-        <v>1</v>
-      </c>
-      <c r="S58">
-        <v>13262</v>
-      </c>
-      <c r="T58" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V58" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W58" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="X58" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="Y58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA58">
-        <v>24</v>
-      </c>
-      <c r="AB58" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC58" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF58" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG58" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH58" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI58" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="AJ58" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F59" s="1">
-        <v>46280</v>
-      </c>
-      <c r="G59">
-        <v>5</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="R59">
-        <v>1</v>
-      </c>
-      <c r="S59">
-        <v>13262</v>
-      </c>
-      <c r="T59" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W59" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X59" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="Y59" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA59">
-        <v>20</v>
-      </c>
-      <c r="AB59" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC59" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD59" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF59" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG59" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH59" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI59" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ59" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1EA59E-6365-4A8A-8E76-4B342BF1DD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FCAD75-2417-4976-8A36-A540F901D7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="343">
   <si>
     <t>Canal</t>
   </si>
@@ -235,931 +235,847 @@
     <t>Hidalgo</t>
   </si>
   <si>
+    <t>Octavio Jaimes</t>
+  </si>
+  <si>
+    <t>Portadas</t>
+  </si>
+  <si>
+    <t>Segobh</t>
+  </si>
+  <si>
+    <t>PGJEH</t>
+  </si>
+  <si>
+    <t>Fiestas Patrias</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor</t>
+  </si>
+  <si>
+    <t>Adela Garmez</t>
+  </si>
+  <si>
+    <t>Erick Perales</t>
+  </si>
+  <si>
+    <t>Huejutla</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>Nathali González</t>
+  </si>
+  <si>
+    <t>Lolotla</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Cultura</t>
+  </si>
+  <si>
+    <t>Van a demoler primaria en Tulancingo; edificarán otra</t>
+  </si>
+  <si>
+    <t>Turismo</t>
+  </si>
+  <si>
+    <t>Gustavo Vargas</t>
+  </si>
+  <si>
+    <t>Planeación</t>
+  </si>
+  <si>
+    <t>Tula</t>
+  </si>
+  <si>
+    <t>Carretera En Mal Estado</t>
+  </si>
+  <si>
+    <t>César Martínez</t>
+  </si>
+  <si>
+    <t>Simulacro Sismo</t>
+  </si>
+  <si>
+    <t>Apoyo a personas con discapacidad</t>
+  </si>
+  <si>
+    <t>DIFH</t>
+  </si>
+  <si>
+    <t>PGJEH, SSPH</t>
+  </si>
+  <si>
+    <t>Tezontepec de Aldama</t>
+  </si>
+  <si>
+    <t>Semarnath</t>
+  </si>
+  <si>
+    <t>PGJEH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Lluvias de septiembre dejan deslaves en Tenango</t>
+  </si>
+  <si>
+    <t>El registro de precipitaciones recientes en la entidad ha comenzado a generar diversas afectaciones operativas, entre las que destacan obstrucciones viales por deslaves en Tenango de Doria y acumulación pluvial en Zacualtipán.</t>
+  </si>
+  <si>
+    <t>Tenango de Doria</t>
+  </si>
+  <si>
+    <t>Deslaves por lluvias</t>
+  </si>
+  <si>
+    <t>Precipitaciones provocaron deslave en la carretera Tenango de Doria-Metepec y encharcamientos en Zacualtipán, restableciéndose la circulación tras labores de limpieza.</t>
+  </si>
+  <si>
+    <t>Segobh, IMSS</t>
+  </si>
+  <si>
+    <t>Accidentes y males hepáticos son más letales en hombres</t>
+  </si>
+  <si>
+    <t>Las estadísticas del Inegi correspondientes al primer trimestre de 2026 revelan diferencias significativas en las causas de fallecimiento entre hombres y mujeres en Hidalgo.</t>
+  </si>
+  <si>
+    <t>Prevención De Enfermedades</t>
+  </si>
+  <si>
+    <t>Reporte del Inegi indica que mientras las enfermedades del corazón y diabetes lideran los decesos generales, los hombres registran mayor mortalidad en males hepáticos y accidentes.</t>
+  </si>
+  <si>
+    <t>SSH, Presidencia</t>
+  </si>
+  <si>
+    <t>IP pide homologar trámites para acelerar inversión local</t>
+  </si>
+  <si>
+    <t>El presidente del CCEH, Jorge González Corona, planteó la necesidad de homologar en todos los municipios los requisitos para tramitar licencias de funcionamiento y construcción.</t>
+  </si>
+  <si>
+    <t>Atracción De Inversiones</t>
+  </si>
+  <si>
+    <t>El CCEH propuso estandarizar trámites municipales para agilizar la llegada y consolidación de inversiones privadas en el estado.</t>
+  </si>
+  <si>
+    <t>Sedeco</t>
+  </si>
+  <si>
+    <t>Jorge González Corona</t>
+  </si>
+  <si>
+    <t>Preparan etapa de pavimentación en la vía Cuautepec-Tulancingo</t>
+  </si>
+  <si>
+    <t>SIPDUS publicó la licitación para la tercera etapa de pavimentación hidráulica de la carretera Cuautepec-Tulancingo, proyectando iniciar labores en octubre.</t>
+  </si>
+  <si>
+    <t>Cuautepec</t>
+  </si>
+  <si>
+    <t>Pavimentación hidráulica</t>
+  </si>
+  <si>
+    <t>SIPDUS arrancó la licitación pública para la pavimentación de la carretera Cuautepec-Tulancingo en su tercera fase con inversión mínima de 6.1 mdp.</t>
+  </si>
+  <si>
+    <t>DIFH recibe tres camionetas adaptadas para el traslado de personas con discapacidad</t>
+  </si>
+  <si>
+    <t>Como parte de la entrega de 91 vehículos accesibles y adaptados a los sistemas estatales DIF, la presidenta del Patronato del Sistema DIF Hidalgo, Edda Vite Ramos, recibió tres camionetas destinadas al transporte especializado de personas con discapacidad.</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, presidenta del Patronato del DIF Hidalgo, recibió tres camionetas adaptadas para el transporte especializado de personas con discapacidad hacia servicios de rehabilitación en el CRIH.</t>
+  </si>
+  <si>
+    <t>Veida Martínez Miranda</t>
+  </si>
+  <si>
+    <t>DIFH, CRIH</t>
+  </si>
+  <si>
+    <t>Tuzobús movilizó 1.8 millones de pasajeros durante julio, 6.6% más que en 2025</t>
+  </si>
+  <si>
+    <t>El Sistema de Transporte Metropolitano (Tuzobús) registró un incremento de 6.6% en el número de pasajeros durante julio de 2026 en comparación con 2025, al movilizar a 1.8 millones de usuarios según la ETUP del Inegi.</t>
+  </si>
+  <si>
+    <t>Afluencia Tuzobús</t>
+  </si>
+  <si>
+    <t>Durante julio de 2026, el Tuzobús transportó a 1.8 millones de pasajeros en la Zona Metropolitana de Pachuca, lo que representa un aumento anual del 6.6% según datos del Inegi.</t>
+  </si>
+  <si>
+    <t>Semot</t>
+  </si>
+  <si>
+    <t>Semot, Inegi</t>
+  </si>
+  <si>
+    <t>Costará 1.9 mdp mantenimiento del Cuartel del Arte en Pachuca</t>
+  </si>
+  <si>
+    <t>Los trabajos de mantenimiento del Cuartel del Arte en Pachuca tendrán una inversión de 1.94 millones de pesos tras el fallo de la licitación EO-SIPDUS-N116-2026 emitida por la Sipdus.</t>
+  </si>
+  <si>
+    <t>Licitaciones</t>
+  </si>
+  <si>
+    <t>La Sipdus adjudicó los trabajos de mantenimiento del Cuartel del Arte en Pachuca por 1.94 mdp. La obra durará 152 días e incluye pisos, impermeabilización e iluminación LED bajo supervisión del INAH.</t>
+  </si>
+  <si>
+    <t>Sipdus, INAH</t>
+  </si>
+  <si>
+    <t>UPT celebrará 24 años con jornada llena de actividades académicas y deportivas</t>
+  </si>
+  <si>
+    <t>Del 28 de septiembre al 2 de octubre, la Universidad Politécnica de Tulancingo (UPT) celebrará su 24 aniversario con eventos académicos, culturales, deportivos y de vinculación con el sector productivo.</t>
+  </si>
+  <si>
+    <t>Aniversario Universidades</t>
+  </si>
+  <si>
+    <t>La Universidad Politécnica de Tulancingo festejará su 24 aniversario con eventos académicos y deportivos, destacando la inauguración de laboratorios para Psicología e Ingeniería Textil.</t>
+  </si>
+  <si>
+    <t>SEPH, UPT</t>
+  </si>
+  <si>
+    <t>Tramo carretero en Tenango, sin paso por afectaciones de lluvias</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos informó que, al corte de las 8:00 horas del sábado, no había paso en el tramo carretero Peña Blanca-El Nanthe, en el municipio de Tenango de Doria. La dependencia explicó que el cierre se debe a las afectaciones ocasionadas por las lluvias, por lo que se exhortó a la población a evitar transitar por esa zona y usar vías alternas.</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil de Hidalgo reportó el cierre del tramo carretero Peña Blanca-El Nanthe en Tenango de Doria debido a daños provocados por las lluvias.</t>
+  </si>
+  <si>
+    <t>Protección Civil</t>
+  </si>
+  <si>
+    <t>Hidalgo supera media nacional en consumo de sustancias ilícitas</t>
+  </si>
+  <si>
+    <t>Durante el primer semestre de 2026, el estado de Hidalgo se ubicó por arriba del promedio nacional en las tasas de consumo de, al menos, tres tipos de sustancias ilícitas —metanfetaminas, éxtasis y alucinógenos—, de acuerdo con el Reporte de información epidemiológica del consumo de drogas emitido por los Centros de Integración Juvenil (CIJ). Hidalgo registró 72.3% de consumo alguna vez en la vida de metanfetaminas entre la población atendida.</t>
+  </si>
+  <si>
+    <t>Consumo De Drogas</t>
+  </si>
+  <si>
+    <t>Un informe de los Centros de Integración Juvenil situó a Hidalgo por encima del promedio nacional en el consumo de metanfetaminas, éxtasis y alucinógenos durante el primer semestre de 2026.</t>
+  </si>
+  <si>
+    <t>CIJ</t>
+  </si>
+  <si>
+    <t>La SEP mandata la realización del censo Ejercicios de Integración Académica</t>
+  </si>
+  <si>
+    <t>Tras la publicación de resultados de evaluaciones internacionales que mostraron caídas en matemáticas y lectura, el titular de la SEPH, Natividad Castrejón, informó que buscarán acceder a los datos locales. Recordó que la SEP mandata la realización del censo Ejercicios de Integración Académica a estudiantes de primaria y secundaria para diagnosticar sus niveles de aprendizaje antes de octubre.</t>
+  </si>
+  <si>
+    <t>Mejora educativa</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón, anunció la realización del censo Ejercicios de Integración Académica para diagnosticar el nivel educativo de estudiantes de primaria y secundaria.</t>
+  </si>
+  <si>
+    <t>SEPH, SEP</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>SIPDUS emite fallo para el mantenimiento del Cuartel del Arte</t>
+  </si>
+  <si>
+    <t>Tras declararse desierto un primer procedimiento por falta de interesados, la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS) emitió el fallo de la licitación EO-SIPDUS-N116-2026 correspondiente a la obra de mantenimiento y conservación del Cuartel del Arte en Pachuca, iniciando los trabajos el próximo 2 de octubre.</t>
+  </si>
+  <si>
+    <t>La SIPDUS adjudicó los trabajos de mantenimiento y restauración del Cuartel del Arte en Pachuca mediante la licitación EO-SIPDUS-N116-2026, con inicio programado para el 2 de octubre.</t>
+  </si>
+  <si>
+    <t>Con desfile concluyen festejos patrios en Pachuca</t>
+  </si>
+  <si>
+    <t>Con la participación de más de 4 mil personas entre estudiantes, fuerzas armadas, corporaciones de seguridad y agrupaciones ecuestres, Pachuca cerró las celebraciones por el 216 Aniversario de la Independencia de México. El contingente incluyó 2 mil 700 estudiantes, elementos de la Policía Estatal, Bomberos, Ejército y Guardia Nacional.</t>
+  </si>
+  <si>
+    <t>Crónica</t>
+  </si>
+  <si>
+    <t>Más de 4 mil participantes de instituciones educativas, corporaciones de seguridad y fuerzas armadas formaron parte del desfile conmemorativo del 216 Aniversario de la Independencia en Pachuca.</t>
+  </si>
+  <si>
+    <t>Benjamín H. V.</t>
+  </si>
+  <si>
+    <t>SSPH, Ejército, Guardia Nacional, PIBEH</t>
+  </si>
+  <si>
+    <t>Ocupación hotelera registra disminución en primer semestre</t>
+  </si>
+  <si>
+    <t>La ocupación hotelera en el estado de Hidalgo registró una disminución de 6.4% durante el primer semestre de este año, comparado con el mismo periodo de 2025, según cifras de Datatur de la Secretaría de Turismo del Gobierno federal. Aunque Pachuca se ubicó en las 10 ciudades con mayor ocupación en julio con 66.2%, la presidenta de la Asociación de Hoteles y Moteles, Roxana Vargas Juárez, estimó cerrar el año con 55%.</t>
+  </si>
+  <si>
+    <t>Ocupación Hotelera</t>
+  </si>
+  <si>
+    <t>Cifras del sistema Datatur revelaron una caída del 6.4% en la ocupación hotelera de Hidalgo en el primer semestre de 2026, aunque Pachuca destacó con un 66.2% durante julio.</t>
+  </si>
+  <si>
+    <t>Roxana Vargas Juárez</t>
+  </si>
+  <si>
+    <t>Enfermedades del corazón, principal causa de fallecimientos en la entidad</t>
+  </si>
+  <si>
+    <t>De enero a marzo de 2026 se registraron 1,250 defunciones por enfermedades del corazón en Hidalgo, seguidas de 767 por diabetes mellitus y 568 por tumores malignos, de acuerdo con el INEGI.</t>
+  </si>
+  <si>
+    <t>El Inegi reportó que las afecciones cardiacas, la diabetes y los tumores malignos encabezaron las causas de mortalidad en Hidalgo durante el primer trimestre de 2026, afectando en mayor proporción a los hombres.</t>
+  </si>
+  <si>
+    <t>SSH, Inegi</t>
+  </si>
+  <si>
+    <t>Hidalgo participa en el segundo Simulacro Nacional 2026</t>
+  </si>
+  <si>
+    <t>Con la evacuación de 102 personas en Palacio de Gobierno y la participación de hospitales y comercios, Hidalgo se sumó al segundo Simulacro Nacional 2026 bajo la hipótesis de un sismo de magnitud 7.7.</t>
+  </si>
+  <si>
+    <t>Dependencias estatales, comercios y ciudadanía participaron en el Simulacro Nacional 2026 activando alertas en telefonía móvil y evacuando edificios públicos en Pachuca y Mineral de la Reforma.</t>
+  </si>
+  <si>
+    <t>Berenice Gamboa</t>
+  </si>
+  <si>
+    <t>Segobh, PC, IMSS</t>
+  </si>
+  <si>
+    <t>Reúne tercera Gimnasiada Nacional a más de 5 mil atletas</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, titular de la SEPH, inauguró la tercera Gimnasiada Nacional en la UAEH con la presencia de más de 5 mil deportistas de los 32 estados en nueve disciplinas.</t>
+  </si>
+  <si>
+    <t>Justa Deportiva</t>
+  </si>
+  <si>
+    <t>Más de 5 mil atletas juveniles de todo el país compiten en la tercera Gimnasiada Nacional en Hidalgo para conformar la delegación mexicana que asistirá al Mundial Sub-18 en Brasil.</t>
+  </si>
+  <si>
+    <t>SEPH, UAEH, Gobernador</t>
+  </si>
+  <si>
+    <t>Colonias de Pachuca tendrán baja presión de agua durante cinco días</t>
+  </si>
+  <si>
+    <t>La Caasim alertó sobre una disminución en la presión del suministro de agua potable en las colonias Antonio del Castillo, Morelos, Cuauhtémoc y Centro debido a trabajos de mantenimiento preventivo.</t>
+  </si>
+  <si>
+    <t>Abasto de agua</t>
+  </si>
+  <si>
+    <t>La Caasim informó que debido a obras de mantenimiento realizadas por la empresa Real del Monte, diversas colonias céntricas de Pachuca registrarán baja presión de agua durante cinco días.</t>
+  </si>
+  <si>
+    <t>Sipdus, Caasim</t>
+  </si>
+  <si>
+    <t>Deslaves por lluvias ocasionan cierre carretero en Tenango de Doria</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil ordenó el cierre de la carretera Peña Blanca-El Nanthe en Tenango de Doria a causa de deslaves provocados por las recientes lluvias.</t>
+  </si>
+  <si>
+    <t>Derrumbes y deslaves derivados de lluvias provocaron el cierre del tramo carretero Peña Blanca-El Nanthe en Tenango de Doria, mientras autoridades mantienen vigilancia preventiva en Tepehuacán de Guerrero.</t>
+  </si>
+  <si>
+    <t>Segobh, PC, Sipdus</t>
+  </si>
+  <si>
+    <t>Fortalecen acciones contra enfermedades diarreicas</t>
+  </si>
+  <si>
+    <t>El 94.8% de los casos de enfermedades diarreicas durante 2026, se relacionó con alimentos contaminados, mientras que 65% estuvo asociado con la comida en el hogar, por lo que autoridades sanitarias acordaron reforzar la higiene en la entidad.</t>
+  </si>
+  <si>
+    <t>Vigilancia Epidemiológica</t>
+  </si>
+  <si>
+    <t>Autoridades sanitarias acordaron reforzar las medidas de higiene en Hidalgo debido a que el 94.8% de los casos de enfermedades diarreicas en 2026 se relacionaron con alimentos contaminados.</t>
+  </si>
+  <si>
+    <t>Llevan vacunas antirrábicas a cinco colonias de Pachuca</t>
+  </si>
+  <si>
+    <t>Habitantes de distintos puntos de la capital hidalguense tendrán una opción cercana para proteger a sus animales de compañía contra la rabia. Del 21 al 25 de septiembre se instalarán módulos itinerantes, con atención a perros y gatos desde un mes de edad.</t>
+  </si>
+  <si>
+    <t>Vacunación Antirrábica</t>
+  </si>
+  <si>
+    <t>Del 21 al 25 de septiembre se instalarán módulos itinerantes de vacunación antirrábica para perros y gatos en cinco colonias de Pachuca.</t>
+  </si>
+  <si>
+    <t>SSH, CAIVM</t>
+  </si>
+  <si>
+    <t>Temen menor pasaje con nuevas tarifas</t>
+  </si>
+  <si>
+    <t>Choferes de taxi de la zona metropolitana de Pachuca temen que el próximo ajuste tarifario, anunciado por la Secretaría de Movilidad y Transporte de Hidalgo, reduzca temporalmente el número de pasajeros y beneficie principalmente a los concesionarios, quienes podrían aumentar las cuotas; de acuerdo con testimonios, actualmente pagan entre 400 y 500 pesos diarios por el uso de las unidades y una cantidad similar en gasolina.</t>
+  </si>
+  <si>
+    <t>Tarifario de taxis</t>
+  </si>
+  <si>
+    <t>Taxistas de Pachuca prevén una disminución de pasajeros ante el próximo ajuste tarifario anunciado por la Semoth y afirman que el beneficio será para los concesionarios.</t>
+  </si>
+  <si>
+    <t>Sube el precio de jitomate y cebolla</t>
+  </si>
+  <si>
+    <t>Estos dos productos registraron aumentos en locales fijos, pues el primero pasó de 16 a 30 pesos por kilo, el segundo alcanza los 40 pesos. Los comerciantes atribuyen el alza a las intensas lluvias que afectaron cultivos y redujeron el abasto.</t>
+  </si>
+  <si>
+    <t>Canasta básica</t>
+  </si>
+  <si>
+    <t>El precio del jitomate y la cebolla aumentó en Pachuca debido a las afectaciones por lluvias en cultivos y la disminución del abasto.</t>
+  </si>
+  <si>
+    <t>Alma Leticia Sánchez</t>
+  </si>
+  <si>
+    <t>Prevén taxistas caída en el pasaje</t>
+  </si>
+  <si>
+    <t>El ajuste de tarifas para taxis anunciado por la Secretaría de Movilidad y Transporte de Hidalgo (Semoth) podría reducir el número de pasajeros y beneficiará principalmente a los concesionarios, indicaron choferes de la zona metropolitana de Pachuca, quienes tienen incrementos en las cuotas diarias por el uso de las unidades. Conductores refirieron pagar cuotas diarias de 400 a 500 pesos más combustible y señalaron los costos de refacciones y baches como afectaciones adicionales.</t>
+  </si>
+  <si>
+    <t>Aumento Tarifa De Transporte</t>
+  </si>
+  <si>
+    <t>Choferes de taxi en Pachuca advierten que el nuevo ajuste tarifario incrementará las cuotas de los concesionarios y reducirá la afluencia de pasajeros.</t>
+  </si>
+  <si>
+    <t>Blanca Soriano</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles Gutiérrez, Hugo Islas, Omar Cisneros, Felipe García</t>
+  </si>
+  <si>
+    <t>Reúne Hidalgo a guitarristas en festival</t>
+  </si>
+  <si>
+    <t>La guitarra clásica volverá a tomar distintos escenarios de Hidalgo con la edición 18 del Festival Nacional de Guitarra Ramón Noble, que del lunes 21 al sábado 26 de septiembre reunirá a intérpretes de Guadalajara, Ciudad de México, Monterrey, Texas y nuestra entidad. Durante seis días, el encuentro ofrecerá conciertos, clases magistrales, presentaciones editoriales y actividades académicas en municipios como Tlahuelilpan, Emiliano Zapata, Real del Monte, Mineral de la Reforma y Tepeapulco.</t>
+  </si>
+  <si>
+    <t>Festival Cultural</t>
+  </si>
+  <si>
+    <t>La edición 18 del Festival Nacional de Guitarra Ramón Noble reunirá a intérpretes nacionales e internacionales en diversos municipios de Hidalgo del 21 al 26 de septiembre.</t>
+  </si>
+  <si>
+    <t>Ramón Noble Olivares</t>
+  </si>
+  <si>
+    <t>Ayate, en el uso agrícola y doméstico</t>
+  </si>
+  <si>
+    <t>El ayate de ixtle es un tejido elaborado de manera artesanal por manos de mujeres y hombres que extraen la fibra de maguey de las pencas de este agave en el Valle del Mezquital. El artesano Plácido Claudio destacó que además de herramienta agrícola y ganadera, el ayate se utilizaba tradicionalmente en los hogares como cuna para arrullar a los bebés mientras las madres realizaban labores domésticas.</t>
+  </si>
+  <si>
+    <t>San Salvador</t>
+  </si>
+  <si>
+    <t>Apoyo a artesanos</t>
+  </si>
+  <si>
+    <t>Artesanos del Valle del Mezquital preservan la elaboración del ayate de ixtle, usado tradicionalmente como herramienta de trabajo y cuna en los hogares.</t>
+  </si>
+  <si>
+    <t>Omar Santiago</t>
+  </si>
+  <si>
+    <t>Plácido Claudio</t>
+  </si>
+  <si>
+    <t>Pobladores se reúnen a limpiar ribera de los ríos</t>
+  </si>
+  <si>
+    <t>Aproximadamente 500 pobladores de Tula participaron en una jornada simultánea de limpieza en las riberas de los ríos Rosas y Tula, recolectando basura y desyerbando áreas colindantes. La actividad fue organizada por Semarnat federal y Conagua, en coordinación con el área de Ecología de la alcaldía de Tula de Allende, con el fin de cuidar el medio ambiente y evitar focos de infección.</t>
+  </si>
+  <si>
+    <t>Saneamiento río Tula</t>
+  </si>
+  <si>
+    <t>Cerca de 500 habitantes de Tula participaron en una jornada comunitaria de limpieza y deshierbe en las riberas de los ríos Rosas y Tula.</t>
+  </si>
+  <si>
+    <t>Semarnat, Conagua, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Nayeli Pérez Jiménez, Ismael Gutiérrez</t>
+  </si>
+  <si>
+    <t>Ejecutivo destina 84 mil para limpieza de vidrios en edificios</t>
+  </si>
+  <si>
+    <t>El gobierno del estado destinará casi 500 mil pesos para el lavado de vidrios de las fachadas del palacio de gobierno y las nuevas oficinas de las secretarías de Bienestar e Inclusión Social y de Agricultura. El Corporativo y Asociados AKRAM S.A. de C.V. será el encargado de brindar el servicio por 484 mil 120.20 pesos por un periodo de tres meses. El servicio incluirá personal capacitado en trabajos de altura y equipo especializado.</t>
+  </si>
+  <si>
+    <t>La Oficialía Mayor de Hidalgo adjudicó un contrato por 484 mil pesos a la empresa AKRAM para la limpieza especializada de vidrios en las fachadas del Palacio de Gobierno y dependencias estatales.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Bienestar, Saderh</t>
+  </si>
+  <si>
+    <t>SSPH detiene a expolicía de Tula con armas y droga</t>
+  </si>
+  <si>
+    <t>Elementos de la Secretaría de Seguridad Pública de Hidalgo (SSPH) lograron la detención de Brigham C.B., expolicía municipal de Tula y señalado como presunto líder de un grupo generador de violencia en la región. El sujeto fue asegurado en la avenida Sur a bordo de una camioneta Dodge Ram portando un arma de fuego corta, dos cargadores abastecidos, 460 dosis de hierba con características de marihuana y 117 dosis de cristal, por lo que fue trasladado a Pachuca.</t>
+  </si>
+  <si>
+    <t>Detención</t>
+  </si>
+  <si>
+    <t>La SSPH aprehendió en Tula a Brigham C.B., expolicía municipal identificado como generador de violencia, asegurándole un arma de fuego y centenas de dosis de enervantes.</t>
+  </si>
+  <si>
+    <t>Joselyn Sánchez</t>
+  </si>
+  <si>
+    <t>SSPH</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH, Presidencia</t>
+  </si>
+  <si>
+    <t>Brigham C.B.</t>
+  </si>
+  <si>
+    <t>Destinan 8.5 mdp para dos planes de movilidad</t>
+  </si>
+  <si>
+    <t>El gobierno del estado destinó 8 millones 555 mil pesos para la elaboración del Plan Integral de Movilidad Urbana Sustentable (PIMUS) de los municipios de Huejutla e Ixmiquilpan. La empresa encargada de prestar el servicio es Modelística S.A. de C.V., la cual evaluará los patrones de movilidad, oferta de transporte, vías ciclistas y densidad poblacional de los últimos 20 años para diseñar rutas que optimicen los traslados internos.</t>
+  </si>
+  <si>
+    <t>Movilidad urbana</t>
+  </si>
+  <si>
+    <t>El Gobierno de Hidalgo invierte 8.5 millones de pesos en la elaboración de los Planes Integrales de Movilidad Urbana Sustentable para Huejutla e Ixmiquilpan.</t>
+  </si>
+  <si>
+    <t>Semot, Presidencia</t>
+  </si>
+  <si>
+    <t>Estudio busca preservar una especie endémica de agave</t>
+  </si>
+  <si>
+    <t>Ciencia. Investigación especializada busca preservar una especie endémica de agave en el estado de Hidalgo frente a amenazas de pérdida de hábitat.</t>
+  </si>
+  <si>
+    <t>Conservación Biodiversidad</t>
+  </si>
+  <si>
+    <t>Investigadores desarrollan un proyecto para la conservación y resguardo biológico de una variedad endémica de agave en territorio hidalguense.</t>
+  </si>
+  <si>
+    <t>Citnova, UAEH</t>
+  </si>
+  <si>
+    <t>Padecimientos gastrointestinales 90% por agua y alimentos: SSEH</t>
+  </si>
+  <si>
+    <t>Los alimentos contaminados están relacionados con 94.8% de los casos de Enfermedades Diarreicas Agudas reportadas por la Secretaría de Salud de Hidalgo.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo advierte que más del 90% de los padecimientos gastrointestinales responden a la ingesta de agua o alimentos contaminados.</t>
+  </si>
+  <si>
+    <t>SSH, Copriseh</t>
+  </si>
+  <si>
+    <t>Huejutla concentra 528 mdp en 84 obras</t>
+  </si>
+  <si>
+    <t>Huejutla concentró una inversión de 528 millones de pesos en 84 obras de infraestructura durante los primeros cuatro años de la administración estatal.</t>
+  </si>
+  <si>
+    <t>Obras De Infraestructura</t>
+  </si>
+  <si>
+    <t>El secretario de Contraloría, Álvaro Bardales, informó sobre la inversión de 528 mdp en obras de infraestructura vial y educativa para la Huasteca hidalguense.</t>
+  </si>
+  <si>
+    <t>Contraloría</t>
+  </si>
+  <si>
+    <t>Contraloría, Gobernador</t>
+  </si>
+  <si>
+    <t>Álvaro Bardales, Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Impulsa ITESHU conservación del agave con apoyo del Fondo Hidalgo</t>
+  </si>
+  <si>
+    <t>El ITESHU encabeza un proyecto científico apoyado con 250 mil pesos por el Fondo Hidalgo para la conservación y manejo sustentable del Agave salmiana en zonas semiáridas.</t>
+  </si>
+  <si>
+    <t>Huichapan</t>
+  </si>
+  <si>
+    <t>Investigadores del Tecnológico de Huichapan desarrollan un proyecto sustentable para el rescate y reproducción del Agave salmiana con un estímulo de 250 mil pesos otorgado por el Fondo Hidalgo.</t>
+  </si>
+  <si>
+    <t>Marco Cerón</t>
+  </si>
+  <si>
+    <t>SEPH, ITESHU, Planeación</t>
+  </si>
+  <si>
+    <t>Atentan a mano armada contra hombre en el centro de la capital hidalguense</t>
+  </si>
+  <si>
+    <t>Un hombre perdió la vida tras recibir disparos con arma de fuego en la calle Ramos Arizpe, cerca de El Parián en el centro de Pachuca. Peritos de la PGJEH recabaron nueve casquillos e iniciaron investigaciones.</t>
+  </si>
+  <si>
+    <t>Ataque Armado</t>
+  </si>
+  <si>
+    <t>Un hombre fue asesinado a balazos en la zona centro de Pachuca durante la madrugada. La SSPH desplegó un operativo que permitió la detención de tres presuntos responsables.</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH</t>
+  </si>
+  <si>
+    <t>Detienen a generador de violencia en la zona de Tula de Allende</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) dio a conocer la detención de un hombre armado, en posesión de presunta droga, cuando viajaba a bordo de una camioneta Dodge RAM color azul en el municipio de Tula. De acuerdo con la información difundida por la dependencia, el hombre era líder de un grupo generador de violencia en la región Tula. Durante la revisión le fueron aseguradas un arma de fuego larga, dos cargadores abastecidos, un arma corta, un chaleco táctico, además de 560 dosis de hierba seca con características de la marihuana y 117 dosis de sustancia granulada presuntamente cristal. Por tal motivo, la persona detenida y los objetos fueron puestos a disposición del Ministerio Público.</t>
+  </si>
+  <si>
+    <t>La SSPH detuvo en Tula a un presunto líder generador de violencia armado con un chaleco táctico, dos cargadores y más de 670 dosis de estupefacientes (marihuana y cristal).</t>
+  </si>
+  <si>
+    <t>SSPH, MP</t>
+  </si>
+  <si>
+    <t>Incidencia delictiva se redujo 7%: SESNSP</t>
+  </si>
+  <si>
+    <t>La Procuraduría General de Justicia del Estado de Hidalgo (PGJEH) inició 4 mil 287 carpetas de investigación por diversos delitos cometidos durante agosto, de acuerdo con el Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP). En comparación con julio, la incidencia delictiva disminuyó 7%, con mayor acumulación en delitos patrimoniales (1,567 denuncias).</t>
+  </si>
+  <si>
+    <t>La incidencia delictiva en Hidalgo disminuyó un 7% durante el mes de agosto con 4,287 carpetas de investigación iniciadas por la PGJEH, según datos del SESNSP.</t>
+  </si>
+  <si>
+    <t>PGJEH, Presidencia</t>
+  </si>
+  <si>
+    <t>Concentran 2 municipios la mitad de homicidios</t>
+  </si>
+  <si>
+    <t>Tezontepec de Aldama y Tizayuca fueron los municipios con mayor cantidad de carpetas de investigación por homicidios dolosos durante agosto, acumulando el 50 por ciento de las 12 denuncias iniciadas en la entidad por la PGJEH. Ambas demarcaciones registraron tres homicidios dolosos cada una.</t>
+  </si>
+  <si>
+    <t>Tezontepec de Aldama y Tizayuca concentraron la mitad de los homicidios dolosos registrados en Hidalgo durante el mes de agosto, con tres carpetas de investigación en cada municipio.</t>
+  </si>
+  <si>
+    <t>Raymundo S. G.</t>
+  </si>
+  <si>
+    <t>La crisis del suicidio persiste en Tulancingo en los últimos meses</t>
+  </si>
+  <si>
+    <t>Tulancingo suma al menos seis casos de presuntos suicidios entre enero y septiembre de 2026, incluyendo dos incidentes registrados dentro del Cereso municipal. En respuesta, el Centro de Cultura Emocional de la Familia (CCEF) del DIF Tulancingo puso en marcha talleres de prevención y primeros auxilios psicológicos dirigidos a la población penitenciaria.</t>
+  </si>
+  <si>
+    <t>Suicidio</t>
+  </si>
+  <si>
+    <t>El municipio de Tulancingo contabiliza al menos seis suicidios en 2026, lo que motivó al DIF local a implementar talleres de contención y apoyo psicológico dentro del Cereso y en planteles educativos.</t>
+  </si>
+  <si>
+    <t>María Antonieta Islas</t>
+  </si>
+  <si>
+    <t>DIFH, SSH</t>
+  </si>
+  <si>
+    <t>Teresa Magdiel Bazan Pérez</t>
+  </si>
+  <si>
+    <t>Lolotla, municipio serrano con tres casos mediáticos en los últimos dos años</t>
+  </si>
+  <si>
+    <t>En Lolotla se han registrado tres eventos de seguridad de trascendencia nacional durante la administración de María Díaz Bustos: la desaparición del niño Dorian Kaleb Chiu Arroyo en abril de 2025, el homicidio del sacerdote Román de la Cruz Hernández en la carretera Tolago-Tetlapaya y un caso de maltrato animal.</t>
+  </si>
+  <si>
+    <t>El municipio de Lolotla ha sido escenario de tres hechos de alto impacto social en los últimos dos años, incluyendo la desaparición de un menor y el homicidio de un párroco.</t>
+  </si>
+  <si>
+    <t>Martha Sáenz</t>
+  </si>
+  <si>
+    <t>María Díaz Bustos, Dorian Kaleb Chiu Arroyo, Román de la Cruz Hernández</t>
+  </si>
+  <si>
+    <t>Auto particular impacta colectiva en Pachuca; reportan 6 heridos leves</t>
+  </si>
+  <si>
+    <t>Con relación al siniestro de tránsito ocurrido sobre la vialidad del bulevar el Minero a la altura de una gasolinera en Pachuca, la Semot a través del STCH informa que intervino en el percance y se auxilió a seis heridos leves.</t>
+  </si>
+  <si>
+    <t>Accidente de Transporte Público</t>
+  </si>
+  <si>
+    <t>Un auto particular impactó por alcance a una colectiva de transporte público en el bulevar El Minero en Pachuca, dejando seis personas con lesiones leves que fueron auxiliadas por Semot y Cruz Roja.</t>
+  </si>
+  <si>
+    <t>Semot, STCH, Cruz Roja</t>
+  </si>
+  <si>
+    <t>Bienestar atiende a migrantes y sus familias en Epazoyucan</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social (Sebiso), a través de la Dirección de Atención al Migrante, llevará a Epazoyucan una jornada de atención dirigida a migrantes, familias y repatriados el martes 22 de septiembre.</t>
+  </si>
+  <si>
+    <t>Epazoyucan</t>
+  </si>
+  <si>
+    <t>Atención A Migrantes</t>
+  </si>
+  <si>
+    <t>Sebiso instalará un módulo itinerante en el Auditorio Municipal de Epazoyucan para brindar orientación gratuita sobre visas, pasaportes, doble nacionalidad y el programa Raíces de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Bienestar</t>
+  </si>
+  <si>
+    <t>Detienen en Tulancingo a dos mujeres acusadas de secuestro exprés</t>
+  </si>
+  <si>
+    <t>Policías de Tulancingo intervinieron a dos mujeres por falta administrativa y, al cruzar datos con la PGJEH, descubrieron que contaban con orden de aprehensión por secuestro exprés agravado.</t>
+  </si>
+  <si>
+    <t>Secuestro</t>
+  </si>
+  <si>
+    <t>Personal de la PGJEH cumplimentó una mandamiento judicial contra dos mujeres en Tulancingo tras ser identificadas por mandamientos judiciales pendientes por secuestro exprés.</t>
+  </si>
+  <si>
+    <t>Un ataque a balazos provocó la detención de tres involucrados</t>
+  </si>
+  <si>
+    <t>Sujetos armados atacaron a balazos al conductor de un vehículo en la calle Arizpe del Centro de Pachuca; elementos de seguridad desplegaron operativo y lograron la captura de tres involucrados.</t>
+  </si>
+  <si>
+    <t>Ataque con arma de fuego en las inmediaciones de El Parián en Pachuca movilizó a policías municipales y estatales, logrando la aprehensión de tres presuntos agresores.</t>
+  </si>
+  <si>
+    <t>SSPH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Detienen a líder criminal con armamento y droga en Tula</t>
+  </si>
+  <si>
+    <t>Agentes de la SSPH detuvieron en Tula a un generador de violencia a bordo de una camioneta Dodge RAM, decomisándole un arma larga, arma corta, chaleco táctico y más de 670 dosis de drogas.</t>
+  </si>
+  <si>
+    <t>Operativo de la Secretaría de Seguridad Pública de Hidalgo culminó con la captura de un presunto líder delincuencial operando en la región de Tula de Allende.</t>
+  </si>
+  <si>
+    <t>Hongos en el café</t>
+  </si>
+  <si>
+    <t>Durante un curso de micología en el CITNOVA, la empresa HC Wellness presentó desarrollos alimentarios para incorporar extractos de hongos funcionales con bioactivos y antioxidantes al café.</t>
+  </si>
+  <si>
+    <t>Reportaje</t>
+  </si>
+  <si>
+    <t>Divulgación científica</t>
+  </si>
+  <si>
+    <t>Investigadores y especialistas exponen en el CITNOVA la aplicación de propiedades nutricionales de hongos funcionales en bebidas de consumo cotidiano.</t>
+  </si>
+  <si>
+    <t>Planeación, CITNOVA</t>
+  </si>
+  <si>
+    <t>Obras del Tren AIFA-Pachuca cortan agua a colonias del sur</t>
+  </si>
+  <si>
+    <t>Cerca de 30 vecinos de distintos fraccionamientos de la zona sur de Mineral de la Reforma (Tulipanes, La Colonia, Cipreses, Magisterio y Encinos) bloquearon este domingo la avenida de los Árboles, a la altura de la caseta de Tulipanes, para exigir agua potable luego de que el tandeo previsto no se cumpliera. Los habitantes señalaron que el desabasto se ha prolongado hasta por 15 días y atribuyeron parte de las afectaciones a los trabajos del Tren AIFA-Pachuca por interferencias en la infraestructura de Caasim.</t>
+  </si>
+  <si>
+    <t>Vecinos del sur de Mineral de la Reforma bloquearon la avenida de los Árboles tras cumplir 15 días sin suministro de agua potable, señalando que las obras del Tren AIFA-Pachuca dañaron las redes de distribución de Caasim.</t>
+  </si>
+  <si>
+    <t>Sipdus, Presidencia</t>
+  </si>
+  <si>
+    <t>Durante 2026 van 179 contagios de Covid en Hidalgo</t>
+  </si>
+  <si>
+    <t>Hidalgo acumula 179 casos de Covid-19 durante 2026 y se ubica en el tercer lugar nacional por contagios, de acuerdo con el reporte de la Dirección General de Epidemiología. Asimismo, la entidad ocupa el primer lugar nacional por defunciones asociadas al coronavirus con 15 fallecimientos. La secretaria de Salud de Hidalgo, Vanesa Escalante Arroyo, señaló que los padecimientos crónico-degenerativos sin control y la falta de actualización de esquemas de vacunación incrementan los riesgos.</t>
+  </si>
+  <si>
+    <t>Covid 19</t>
+  </si>
+  <si>
+    <t>Con 179 contagios y 15 defunciones en 2026, Hidalgo se ubica en el primer lugar nacional en mortalidad por Covid-19. La Secretaría de Salud de Hidalgo llamó a mantener al día los esquemas de vacunación.</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>Avanza transferencia del Nuevo Hospital General</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo prevé concretar la transferencia del Nuevo Hospital General de Pachuca al IMSS-Bienestar, informó su titular Vanesa Escalante Arroyo. Autoridades federales realizaron visitas e integran documentación técnica para que el organismo asuma la operación del inmueble que permanece sin funcionar.</t>
+  </si>
+  <si>
+    <t>IMSS Bienestar</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo avanza en las gestiones para transferir el Nuevo Hospital General de Pachuca al esquema IMSS-Bienestar para iniciar su equipamiento y puesta en operación.</t>
+  </si>
+  <si>
+    <t>La escuela primaria Aquiles Serdán de Tulancingo presenta graves daños estructurales, por lo que será demolida y reconstruida totalmente durante el ciclo escolar 2026-2027, según informó el titular de la SEPH, Natividad Castrejón. Se analizan alternativas para reubicar temporalmente a los alumnos en planteles cercanos o modalidades de educación a distancia.</t>
+  </si>
+  <si>
     <t>Reconstrucción de escuela</t>
   </si>
   <si>
-    <t>Octavio Jaimes</t>
-  </si>
-  <si>
-    <t>Portadas</t>
-  </si>
-  <si>
-    <t>Lorena Rosas</t>
+    <t>Por fallas estructurales, la Secretaría de Educación Pública de Hidalgo construirá un nuevo plantel para la primaria Aquiles Serdán en Tulancingo, evaluando sedes temporales para atender al alumnado.</t>
   </si>
   <si>
     <t>Impresiones locales</t>
-  </si>
-  <si>
-    <t>Segobh</t>
-  </si>
-  <si>
-    <t>PGJEH</t>
-  </si>
-  <si>
-    <t>VAN A DEMOLER PRIMARIA EN TULANCINGO; EDIFICARÁN OTRA</t>
-  </si>
-  <si>
-    <t>Veida Martínez Miranda</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>SEPH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Fiestas Patrias</t>
-  </si>
-  <si>
-    <t>Berenice Gamboa</t>
-  </si>
-  <si>
-    <t>SSPH</t>
-  </si>
-  <si>
-    <t>Salvador Cruz Neri</t>
-  </si>
-  <si>
-    <t>El Mexe</t>
-  </si>
-  <si>
-    <t>Blanca Soriano</t>
-  </si>
-  <si>
-    <t>Gobernador</t>
-  </si>
-  <si>
-    <t>Dulce Castillo</t>
-  </si>
-  <si>
-    <t>Lourdes Naranjo</t>
-  </si>
-  <si>
-    <t>Ricardo Calleja</t>
-  </si>
-  <si>
-    <t>SEPH, IHE, Gobernador</t>
-  </si>
-  <si>
-    <t>Marco Cerón</t>
-  </si>
-  <si>
-    <t>Carmen Hernández</t>
-  </si>
-  <si>
-    <t>SSH, Presidencia</t>
-  </si>
-  <si>
-    <t>Bienestar</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor</t>
-  </si>
-  <si>
-    <t>Alma Leticia Sánchez</t>
-  </si>
-  <si>
-    <t>Adela Garmez</t>
-  </si>
-  <si>
-    <t>Boletín</t>
-  </si>
-  <si>
-    <t>Comunicado gubernamental</t>
-  </si>
-  <si>
-    <t>Vanesa Escalante Arroyo</t>
-  </si>
-  <si>
-    <t>Alejandro Reyes</t>
-  </si>
-  <si>
-    <t>Cateo</t>
-  </si>
-  <si>
-    <t>SSPH, PGJEH, Sedena, Presidencia</t>
-  </si>
-  <si>
-    <t>Ana Luisa Vega</t>
-  </si>
-  <si>
-    <t>Oscar Raúl Pérez</t>
-  </si>
-  <si>
-    <t>Operativo de Seguridad</t>
-  </si>
-  <si>
-    <t>Erick Perales</t>
-  </si>
-  <si>
-    <t>Conmemora Menchaca Grito de Independencia con Plaza Juárez llena</t>
-  </si>
-  <si>
-    <t>En un ambiente de fiesta, música, y orgullo patrio, el gobernador Julio Menchaca Salazar, encabezó el Grito de Independencia ante más de 30 mil personas reunidas en Plaza Juárez. Desde el balcón del edificio guinda, el mandatario estatal acompañado de su familia, integrantes de su gabinete, representantes del poder legislativo, judicial, y el alcalde de Pachuca Jorge Reyes, rindió la quinta celebración de su administración, la cual culminó con espectáculo piromusical y la actuación estelar de Carlos Rivera.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca encabezó el Grito de Independencia ante más de 30 mil asistentes en la Plaza Juárez de Pachuca con pirotecnia y eventos musicales.</t>
-  </si>
-  <si>
-    <t>Gobernador, Ayuntamiento, SSPH, Bomberos, Cruz Roja</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Jorge Reyes Hernández, Carlos Rivera</t>
-  </si>
-  <si>
-    <t>REFORMA ELECTORAL PARA GARANTIZAR ALCALDÍAS A MUJERES ERA “LO IDEAL” PARA LA PARIDAD: MENCHACA</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar consideró que la intención de la propuesta de reforma al Código Electoral que planteaba dividir a los 84 municipios en dos bloques de 42 para dejar la mitad a postulaciones exclusivas para mujeres era "lo ideal" para asegurar la paridad que marca la Constitución. Sin embargo, señaló que al no ser incluida durante la aprobación de la reforma en el Congreso local existe el riesgo de que haya menos presidentas municipales en 2027.</t>
-  </si>
-  <si>
-    <t>Reforma Electoral</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca calificó la asignación alfabética de municipios para candidatas como la fórmula ideal de paridad, advirtiendo riesgo de menor representación femenina tras ser excluida por el Congreso.</t>
-  </si>
-  <si>
-    <t>Gobernador, Congreso, IEEH</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Andrés Velázquez Vázquez</t>
-  </si>
-  <si>
-    <t>Desmantelan inmueble usado para comercializar droga en Tepeapulco</t>
-  </si>
-  <si>
-    <t>Elementos de la Secretaría de Seguridad Pública de Hidalgo (SSPH), en coordinación con la PGJEH y la Sedena, ejecutaron un cateo en un inmueble de la colonia Rojo Gómez en Tepeapulco, asegurando 1,073 dosis de presunta droga cristal, 240 dosis de marihuana, un arma de fuego larga, cargadores, tres chalecos tácticos y una báscula de precisión sin registrar personas detenidas.</t>
-  </si>
-  <si>
-    <t>Tepeapulco</t>
-  </si>
-  <si>
-    <t>Operativo conjunto de la SSPH, PGJEH y Ejército desmanteló un centro de distribución de narcóticos en Tepeapulco, asegurando más de 1,300 dosis de droga y armamento.</t>
-  </si>
-  <si>
-    <t>Jornada de 40 horas, sin rechazo de empresarios</t>
-  </si>
-  <si>
-    <t>El sector laboral de Hidalgo se prepara para la reducción paulatina de la jornada laboral de 48 a 40 horas semanales a partir de enero de 2027. El secretario del Trabajo estatal, Oscar Javier González Hernández, informó que no existe resistencia entre el sector empresarial de la entidad y que se mantienen reuniones para planificar la productividad sin afectar sueldos, prestaciones ni derechos laborales.</t>
-  </si>
-  <si>
-    <t>Ley 40 horas</t>
-  </si>
-  <si>
-    <t>El secretario del Trabajo en Hidalgo, Oscar González Hernández, afirmó que no hay rechazo patronal ante la reducción paulatina de la jornada laboral a 40 horas a partir de 2027.</t>
-  </si>
-  <si>
-    <t>STPSH</t>
-  </si>
-  <si>
-    <t>STPSH, Presidencia, INEGI</t>
-  </si>
-  <si>
-    <t>Oscar Javier González Hernández</t>
-  </si>
-  <si>
-    <t>Escuelas con solo 6 alumnos en Hidalgo</t>
-  </si>
-  <si>
-    <t>La Secretaría de Educación Pública de Hidalgo (SEPH) mantiene 700 escuelas primarias rurales con baja matrícula, algunas con de seis a 13 estudiantes. El secretario Natividad Castrejón Valdez descartó el cierre de planteles y explicó que se realiza una reingeniería de recursos humanos aprovechando plazas liberadas por jubilaciones, mientras el Conafe atiende a 7 mil alumnos en 2,100 centros comunitarios.</t>
-  </si>
-  <si>
-    <t>Infraestructura escolar</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón, aclaró que las 700 primarias rurales con baja matrícula en Hidalgo no serán cerradas y se optimizarán las plazas docentes.</t>
-  </si>
-  <si>
-    <t>Sonia Nochebuena</t>
-  </si>
-  <si>
-    <t>SEPH, Conafe, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Familias disfrutan desfile en Pachuca</t>
-  </si>
-  <si>
-    <t>Miles de familias se congregaron en las calles del Centro Histórico de Pachuca para presenciar el desfile cívico-militar conmemorativo del 216 aniversario del inicio de la Independencia de México, encabezado por el gobernador Julio Menchaca Salazar y la presidenta del DIF Edda Vite. Marcharon 1,800 alumnos de educación básica, 901 de nivel medio y superior, corporaciones policiales, Guardia Nacional, Ejército y asociaciones charras.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca encabezó el desfile cívico-militar del 216 aniversario de la Independencia de México en Pachuca con participación de contingentes escolares y de seguridad.</t>
-  </si>
-  <si>
-    <t>Gobernador, DIFH, SSPH, Sedena, GN, Cruz Roja, Ayuntamientos, Pemex</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Edda Vite Ramos, Salvador Cruz Neri</t>
-  </si>
-  <si>
-    <t>Llama obispo a aclarar la muerte de párroco</t>
-  </si>
-  <si>
-    <t>El obispo de la diócesis de Huejutla, José Acosta, exigió a las autoridades esclarecer el asesinato del sacerdote Román e hizo un llamado urgente a la sociedad hidalguense para consolidar una cultura de paz, tolerancia y reconciliación social para erradicar la violencia.</t>
-  </si>
-  <si>
-    <t>Huejutla</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
-    <t>El obispo de Huejutla, José Acosta, pidió el esclarecimiento del homicidio del párroco Román y exhortó a la población a promover la reconciliación y la paz.</t>
-  </si>
-  <si>
-    <t>PGJEH, Presidencia</t>
-  </si>
-  <si>
-    <t>José Acosta, Román N.</t>
-  </si>
-  <si>
-    <t>Reportan saldo blanco por fiestas patrias</t>
-  </si>
-  <si>
-    <t>El titular de la SSPH, Salvador Cruz Neri, informó saldo blanco durante las celebraciones patrias en el estado de Hidalgo, destacando ausencia de disparos al aire y pocos decomisos de pirotecnia. Asimismo, aclaró que la Policía Estatal no participó en el cateo realizado por fuerzas federales en La Toscana, Tulancingo.</t>
-  </si>
-  <si>
-    <t>La SSPH informó saldo blanco en los festejos patrios de la entidad y precisó que la corporación no intervino en las diligencias del cateo en Tulancingo.</t>
-  </si>
-  <si>
-    <t>SSPH, Presidencia, Sedena, FGR</t>
-  </si>
-  <si>
-    <t>Iniciará mantenimiento del pisal de Byron Gálvez</t>
-  </si>
-  <si>
-    <t>El próximo 23 de octubre iniciarán los trabajos de mantenimiento del pisal Homenaje a la mujer del mundo, del artista hidalguense Byron Gálvez, donde serán reemplazados los mosaicos faltantes o rotos a lo largo de la explanada ubicada en el Parque Cultural Hidalguense en Pachuca, obra proyectada por la Sipdus con fecha de conclusión al 28 de febrero de 2027.</t>
-  </si>
-  <si>
-    <t>Patrimonio cultural</t>
-  </si>
-  <si>
-    <t>La Sipdus licitó los trabajos de restauración y reemplazo de piezas cerámicas del pisal Homenaje a la mujer del mundo en el Parque Cultural Hidalguense de Pachuca.</t>
-  </si>
-  <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Sipdus, Oficialía Mayor, Gobernador</t>
-  </si>
-  <si>
-    <t>Byron Gálvez, Orlando Ángeles Pérez</t>
-  </si>
-  <si>
-    <t>Carecen de Atlas de Riesgos 15 municipios afectados por vaguada</t>
-  </si>
-  <si>
-    <t>Quince de los 28 municipios con mayores afectaciones por lluvias y la vaguada monzónica carecen de un Atlas de Riesgos actualizado, por lo que la Subsecretaría de Protección Civil estatal brindó capacitación a las autoridades locales para elaborar mapas de peligro temporales y alcanzar la cobertura total de los 84 ayuntamientos.</t>
-  </si>
-  <si>
-    <t>Atlas de Riesgos</t>
-  </si>
-  <si>
-    <t>Protección Civil estatal capacitó a 15 ayuntamientos afectados por contingencias climatológicas que carecen de un Atlas de Riesgos actualizado.</t>
-  </si>
-  <si>
-    <t>Segobh, PC, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Para 2027, prevén 500 mdp para contingencias naturales</t>
-  </si>
-  <si>
-    <t>La Secretaría de Hacienda del Estado proyecta etiquetar alrededor de 500 millones de pesos dentro del Paquete Hacendario 2027 para la prevención y atención de contingencias derivadas de desastres naturales en Hidalgo. La titular de la dependencia, María Esther Ramírez Vargas, señaló que el proyecto de presupuesto se entregará al Congreso a más tardar el 19 de noviembre.</t>
-  </si>
-  <si>
-    <t>Presupuesto De Egresos</t>
-  </si>
-  <si>
-    <t>La Secretaría de Hacienda de Hidalgo alista una partida de 500 mdp en el Paquete Hacendario 2027 para la atención de emergencias y fenómenos naturales.</t>
-  </si>
-  <si>
-    <t>Socorro Ávila</t>
-  </si>
-  <si>
-    <t>Hacienda</t>
-  </si>
-  <si>
-    <t>Hacienda, Gobernador, Congreso, Presidencia</t>
-  </si>
-  <si>
-    <t>María Esther Ramírez Vargas</t>
-  </si>
-  <si>
-    <t>Gobierno afina reunión para lograr pacto electoral</t>
-  </si>
-  <si>
-    <t>El secretario de Gobierno, Guillermo Olivares Reyna, anunció que entablará reuniones con las dirigencias de partidos políticos y autoridades electorales para establecer un pacto de civilidad cívica e institucional previo al arranque oficial del proceso electoral 2027 en diciembre próximo, en el que se renovarán 18 diputaciones locales y 84 ayuntamientos.</t>
-  </si>
-  <si>
-    <t>Proceso electoral</t>
-  </si>
-  <si>
-    <t>La Secretaría de Gobierno convocará a partidos políticos e IEEH para consolidar un pacto de respeto institucional rumbo a las elecciones locales de 2027.</t>
-  </si>
-  <si>
-    <t>Segobh, IEEH, PT, Congreso</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna, Damián Sosa Castelán, María Magdalena González Escalona</t>
-  </si>
-  <si>
-    <t>Para evitar compra de votos, Sebiso blindará programas</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, confirmó la publicación de las reglas de operación y el cierre oportuno del padrón de beneficiarios a inicios de 2027 para establecer la veda electoral y evitar el uso clientelar o condicionado de los apoyos sociales en los comicios.</t>
-  </si>
-  <si>
-    <t>Programas Del Bienestar</t>
-  </si>
-  <si>
-    <t>La Sebiso implementará un blindaje institucional en sus padrones para impedir el condicionamiento de programas sociales en las elecciones de 2027.</t>
-  </si>
-  <si>
-    <t>Nathali González</t>
-  </si>
-  <si>
-    <t>Bienestar, Gobernador</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>Siguen abiertas las investigaciones por destrozos en la SEPH</t>
-  </si>
-  <si>
-    <t>El encargado del despacho de la PGJEH, Francisco Fernández Hasbun, informó que continúan en integración las carpetas de investigación por los daños materiales calculados en 6 millones de pesos causados a la sede de la SEPH por estudiantes de la Escuela Normal Rural El Mexe en febrero pasado, manteniendo además canales de diálogo directo con familiares del joven fallecido.</t>
-  </si>
-  <si>
-    <t>La PGJEH mantiene abiertas las indagatorias por los destrozos en la sede de la SEPH cometidos por estudiantes de El Mexe y da seguimiento a carpetas de investigación.</t>
-  </si>
-  <si>
-    <t>PGJEH, SEPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Francisco Fernández Hasbun, Natividad Castrejón Valdez, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>Fortalece IHE la identidad cultural en Ixmiquilpan con Cazadores de saberes</t>
-  </si>
-  <si>
-    <t>El Centro Estatal de Lenguas y Culturas Indígenas (CELCI) del IHE presentó la revista número 22 Cazadores de saberes en la Escuela Primaria Indígena El Nigromante en Ixmiquilpan, obra colectiva elaborada por artesanos, médicos tradicionales y familias para promover el patrimonio cultural e idioma náhuatl y otomí.</t>
-  </si>
-  <si>
-    <t>Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Preservación Lenguas Maternas</t>
-  </si>
-  <si>
-    <t>El IHE y el CELCI entregaron en Ixmiquilpan la edición 22 de la revista Cazadores de saberes para preservar la riqueza cultural de los pueblos indígenas.</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Ortega Sánchez, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Aumenta demanda estatal de atención por metanfetaminas</t>
-  </si>
-  <si>
-    <t>De acuerdo con el informe epidemiológico de los Centros de Integración Juvenil (CIJ Pachuca), las metanfetaminas se consolidaron como la principal droga de impacto en Hidalgo al representar el 63.2% de las solicitudes de tratamiento en el primer semestre de 2026 con 171 casos registrados, desplazando al cannabis y al alcohol.</t>
-  </si>
-  <si>
-    <t>Consumo De Drogas</t>
-  </si>
-  <si>
-    <t>Los CIJ de la Secretaría de Salud reportaron que las metanfetaminas se ubicaron como la causa principal de atención de adicciones en Hidalgo con el 63.2% de los pacientes.</t>
-  </si>
-  <si>
-    <t>BUSCAN BLINDAR LA ELECCIÓN MEDIANTE PACTO DE CIVILIDAD</t>
-  </si>
-  <si>
-    <t>Partidos políticos y aspirantes independientes serán convocados en los próximos días a mesas de trabajo para acordar un pacto de civilidad que regule su participación durante el proceso electoral 2026-2027 en Hidalgo. El secretario de Gobierno, Guillermo Olivares Reyna, adelantó que el llamado incluirá a las fuerzas políticas acreditadas ante los órganos electorales nacionales y estatales, con el propósito de que conozcan y respeten las nuevas disposiciones del Código Electoral de Hidalgo.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Gobierno convocará a partidos políticos y aspirantes independientes a mesas de diálogo para pactar civilidad y respeto a la ley en las elecciones de 2027.</t>
-  </si>
-  <si>
-    <t>Teodoro Santos</t>
-  </si>
-  <si>
-    <t>Segobh, IEEH, TEEH, Congreso</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna</t>
-  </si>
-  <si>
-    <t>REPORTAN SALDO BLANCO EN CELEBRACIONES DE INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>Ante cientos de familias hidalguenses se celebró el desfile conmemorativo por la Independencia de México encabezado por el gobernador Julio Menchaca Salazar, reportando los 84 municipios saldo blanco y tranquilidad durante los festejos patrios.</t>
-  </si>
-  <si>
-    <t>Desfile cívico</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca presidió el desfile cívico-militar en Pachuca, reportando saldo blanco en los 84 municipios durante las Fiestas Patrias.</t>
-  </si>
-  <si>
-    <t>Gobernador, SSPH, Sedena, GN, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Salvador Cruz Neri</t>
-  </si>
-  <si>
-    <t>ARRANCAN OBRAS EN PISAL DEL PARQUE</t>
-  </si>
-  <si>
-    <t>La obra Homenaje a la Mujer del Mundo de Byron Gálvez será intervenida a finales de este mes, informó la Oficialía Mayor. Los trabajos contemplan el reemplazo de mosaicos dañados y restauración de piezas fracturadas.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor y Sipdus iniciarán a finales de septiembre la rehabilitación y reemplazo de mosaicos del pisal de Byron Gálvez en Pachuca.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Sipdus, Cultura, Gobernador</t>
-  </si>
-  <si>
-    <t>Edgar Orlando Ángeles Pérez, Byron Gálvez</t>
-  </si>
-  <si>
-    <t>EN HIDALGO, NI FOSAS CLANDESTINAS NI CASOS DE DESAPARICIÓN FORZADA</t>
-  </si>
-  <si>
-    <t>Hidalgo no registra casos de desaparición forzada, además en los cuatro años del gobierno del estado no se han localizado fosas clandestinas, de acuerdo con la encargada de la Subprocuraduría de Delitos de Género, Desaparición de Personas e Impacto Social, Lorena Cano García. La funcionaria precisó que la mayoría de los expedientes iniciados corresponden a ausencias voluntarias.</t>
-  </si>
-  <si>
-    <t>Desapariciones</t>
-  </si>
-  <si>
-    <t>La PGJEH aclaró que en cuatro años no hay registros de fosas clandestinas ni desaparición forzada en Hidalgo, correspondiendo la mayoría de los casos a ausencias voluntarias.</t>
-  </si>
-  <si>
-    <t>PGJEH, CBPEIH, Presidencia</t>
-  </si>
-  <si>
-    <t>Lorena Cano García</t>
-  </si>
-  <si>
-    <t>SÓLO 22 CONFORMAN FUERZA DE BÚSQUEDA ESTATAL DE PERSONAS</t>
-  </si>
-  <si>
-    <t>La Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEIH) cuenta sólo con alrededor de 22 personas para las acciones de búsqueda en los 84 municipios, apoyándose con corporaciones de Seguridad Pública y la Procuraduría estatal, informó el comisionado Francisco García Reyes.</t>
-  </si>
-  <si>
-    <t>Déficit policial</t>
-  </si>
-  <si>
-    <t>La Comisión de Búsqueda de Personas de Hidalgo opera con un déficit de personal de sólo 22 integrantes para atender a los 84 municipios, apoyándose en la SSPH y la PGJEH.</t>
-  </si>
-  <si>
-    <t>Segobh, CBPEIH, SSPH, PGJEH, Presidencia</t>
-  </si>
-  <si>
-    <t>Francisco García Reyes</t>
-  </si>
-  <si>
-    <t>LLUVIAS AFECTAN LAS VIALIDADES</t>
-  </si>
-  <si>
-    <t>Derivado de las lluvias recientes existen afectaciones a las principales vialidades de Pachuca y de otros puntos de Hidalgo, reconoció el titular de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS), Alejandro Sánchez García, requiriendo reparaciones a las empresas contratistas.</t>
-  </si>
-  <si>
-    <t>Vialidad En Mal Estado</t>
-  </si>
-  <si>
-    <t>La Sipdus reconoció afectaciones en las vialidades principales de Pachuca por las lluvias recientes y requirió a las empresas constructoras reparar los baches y daños en obras públicas.</t>
-  </si>
-  <si>
-    <t>Sipdus, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Alejandro Sánchez García</t>
-  </si>
-  <si>
-    <t>REHABILITARÁN “EL PISAL” EN PACHUCA</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo trabaja desde hace seis meses en la rehabilitación de la obra “Homenaje a la Mujer del Mundo”, de Byron Gálvez, conocida como “El Pisal”, ubicada en el Parque Cultural Hidalguense, informó el titular de la Oficialía Mayor, Edgar Ángeles.</t>
-  </si>
-  <si>
-    <t>El gobierno estatal invertirá en la rehabilitación del pisal de Byron Gálvez en Pachuca, sustituyendo piezas dañadas conforme al diseño original con fecha de término en marzo de 2027.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Sipdus, Cultura</t>
-  </si>
-  <si>
-    <t>REPUVE LLEVA MÓDULO MÓVIL A LOCALIDADES</t>
-  </si>
-  <si>
-    <t>Registrar un vehículo ante el Repuve será más accesible para habitantes de municipios que no cuentan con un módulo fijo, luego de que Hidalgo incorporó una unidad itinerante para realizar gratuitamente la colocación del chip de identificación vehicular.</t>
-  </si>
-  <si>
-    <t>Padrón vehicular</t>
-  </si>
-  <si>
-    <t>La SSPH activó una unidad móvil del Repuve que acudirá a comunidades e itinerarios municipales para instalar chips de registro vehicular sin costo.</t>
-  </si>
-  <si>
-    <t>SSPH, Segobh, Bienestar</t>
-  </si>
-  <si>
-    <t>CONVIERTEN LACTOSUERO EN PRODUCTOS SUSTENTABLES</t>
-  </si>
-  <si>
-    <t>Un residuo de la industria quesera del Valle de Tulancingo se convirtió en materia prima para un proyecto desarrollado por estudiantes del Conalep Tulancingo. Se trata del lactosuero, del que diariamente se generan 492 mil litros en la región y cerca de 72 por ciento se desecha sin tratamiento.</t>
-  </si>
-  <si>
-    <t>Economía Circular</t>
-  </si>
-  <si>
-    <t>Estudiantes del Conalep Tulancingo transformaron mermas de lactosuero en biofertilizantes, ecoladrillos y productos sustentables para combatir la contaminación ambiental.</t>
-  </si>
-  <si>
-    <t>SEPH, Conalep, Semarnath</t>
-  </si>
-  <si>
-    <t>Habrá segunda etapa de obras viales cerca de la glorieta 24 Horas</t>
-  </si>
-  <si>
-    <t>Una segunda etapa de intervención vial en los alrededores de la glorieta del puente atirantado contempla la colocación de nuevas luminarias, adecuaciones en calles aledañas y un carril adicional sobre el bulevar Colosio. Así lo informó Alejandro Sánchez García, secretario de Infraestructura Pública y Desarrollo Urbano Sostenible de Hidalgo (Sipdus), quien explicó que son trabajos complementarios a los realizados en la zona desde 2025.</t>
-  </si>
-  <si>
-    <t>Glorieta 24 Horas</t>
-  </si>
-  <si>
-    <t>La Sipdus alista la segunda etapa de adecuaciones viales, iluminación y carril adicional en las inmediaciones de la glorieta 24 Horas en el bulevar Colosio.</t>
-  </si>
-  <si>
-    <t>REPORTARON SALDO BLANCO DURANTE LAS FIESTAS PATRIAS</t>
-  </si>
-  <si>
-    <t>Los festejos por el Grito de Independencia en las plazas públicas de los 84 municipios de Hidalgo resultaron con saldo blanco, informó el gobernador Julio Menchaca Salazar tras encabezar el desfile cívico militar del 16 de septiembre en Pachuca. Además, el titular de la Secretaría de Seguridad Pública de Hidalgo (SSPH), Salvador Cruz Neri, comentó que no hubo disparos al aire libre y decomisaron poca pirotecnia.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca y la SSPH reportaron saldo blanco en los 84 municipios durante las celebraciones del Grito y desfiles del 16 de septiembre.</t>
-  </si>
-  <si>
-    <t>Gobernador, SSPH, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Familias pachuqueñas disfrutan desfile patrio</t>
-  </si>
-  <si>
-    <t>La jornada comenzó por la mañana en la plaza Constitución, donde el gobernador Julio Menchaca Salazar encabezó la Guardia de Honor y depósito de una ofrenda floral con motivo del 216 aniversario del inicio de la Independencia de México. Apenas un par de horas después, familias pachuqueñas ocuparon las banquetas del Centro Histórico para presenciar el desfile con la participación de 2,701 estudiantes, 150 integrantes del Pentatlón, 750 elementos de seguridad y bomberos, además de corporaciones ecuestres y charras.</t>
-  </si>
-  <si>
-    <t>Crónica</t>
-  </si>
-  <si>
-    <t>Familias de Pachuca presenciaron el desfile del 16 de septiembre en el Centro Histórico con la participación de contingentes escolares, corporaciones de seguridad y agrupaciones de charros.</t>
-  </si>
-  <si>
-    <t>Gobernador, SSPH, Bomberos, PC, Cruz Roja, GN, Sedena, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Anuncian rehabilitación del pisal del Parque Cultural Hidalguense</t>
-  </si>
-  <si>
-    <t>A finales de septiembre iniciará la rehabilitación del pisal ubicado en el Parque Cultural Hidalguense, trabajos que se extenderán hasta marzo de 2027, informó Edgar Orlando Ángeles Pérez, oficial Mayor. Las labores contemplan la sustitución de piezas, por lo que el proveedor ganador de la licitación deberá reponer las faltantes a la medida y con características del diseño original de Byron Gálvez.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor y Sipdus iniciarán la restauración del pisal Homenaje a la Mujer del Mundo en Pachuca, reemplazando mosaicos fracturados hasta marzo de 2027.</t>
-  </si>
-  <si>
-    <t>Hidalgo suma siete muertes maternas este año; superó el registro de 2025</t>
-  </si>
-  <si>
-    <t>Durante la primera semana de septiembre, Hidalgo registró una muerte materna, con la que acumuló siete casos en lo que va del año, cifra que ya superó los seis decesos ocurridos en 2025, de acuerdo con la Secretaría de Salud federal. Al respecto, la titular de la SSH, Vanesa Escalante Arroyo, indicó que reforzarán las campañas de difusión para la prevención sobre signos de alarma en pacientes embarazadas, especialmente por preeclampsia.</t>
-  </si>
-  <si>
-    <t>Salud materna</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud federal reportó siete muertes maternas en Hidalgo durante 2026, superando la cifra total de 2025, ante lo cual la SSH reforzará la prevención de preeclampsia.</t>
-  </si>
-  <si>
-    <t>SSH, IMSS, ISSSTE, IMSS-Bienestar, Presidencia</t>
-  </si>
-  <si>
-    <t>INVESTIGAN ASESINATO DEL SACERDOTE ROMÁN</t>
-  </si>
-  <si>
-    <t>La Procuraduría General de Justicia de Hidalgo (PGJEH) investiga el hallazgo sin vida de un sacerdote en Lolotla, mientras que el Obispado de Huejutla realizó un llamado para que el hecho se esclarezca. La víctima es el presbítero Román de la Cruz Hernández, originario de Mazahuacán, quien ejercía como párroco en la iglesia de Santa Cruz, Huejutla. En el sitio se halló un mensaje presuntamente vinculado a un grupo delictivo.</t>
-  </si>
-  <si>
-    <t>Lolotla</t>
-  </si>
-  <si>
-    <t>La PGJEH investiga el asesinato del sacerdote Román de la Cruz Hernández en Lolotla, mientras el obispado de Huejutla y la CEM demandaron el esclarecimiento de los hechos.</t>
-  </si>
-  <si>
-    <t>Francisco Bautista</t>
-  </si>
-  <si>
-    <t>PGJEH, Presidencia, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Román de la Cruz Hernández, Francisco Ángel Fernández Hasbún, José Hirais Acosta Beltrán</t>
-  </si>
-  <si>
-    <t>CONTINÚA LA PGJEH INVESTIGACIÓN POR MUERTE EN EL MEXE</t>
-  </si>
-  <si>
-    <t>El encargado de la Procuraduría General de Justicia del Estado de Hidalgo (PGJEH), Francisco Fernández Hasbun, descartó órdenes de aprehensión por el hallazgo sin vida de un estudiante de la Normal Rural El Mexe; se reunió con un tío del fallecido para informarle sobre los avances en las indagatorias y confirmó que las carpetas por los destrozos en la SEPH en febrero continúan abiertas.</t>
-  </si>
-  <si>
-    <t>La PGJEH descartó órdenes de aprehensión inmediatas por el homicidio de un alumno de El Mexe tras informar avances a un familiar y mantiene abiertas las carpetas de investigación por destrozos en la SEPH.</t>
-  </si>
-  <si>
-    <t>Francisco Fernández Hasbun, José Antonio Salgado, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>CONTROVERSIAS CONTRA EL RECTOR DE UPP QUEDARON RESUELTAS: SEPH</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, dio a conocer que se aclararon los señalamientos contra el rector de la UPP, Francisco Hernández Jiménez, explicando que cuenta con dos maestrías concluidas en proceso de registro e instruyó a los Órganos Internos de Control verificar los contratos de uniformes universitarios.</t>
-  </si>
-  <si>
-    <t>Irregularidades en escuela</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón, declaró resueltas las dudas sobre el registro académico del rector de la UPP y solicitó auditar la adquisición de uniformes institucionales.</t>
-  </si>
-  <si>
-    <t>SEPH, Contraloría</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Francisco Hernández Jiménez</t>
-  </si>
-  <si>
-    <t>JULIO MENCHACA ENCABEZA EL GRITO DE INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>Al grito de "¡Viva la Transformación!", el gobernador Julio Menchaca Salazar encabezó el acto del 216 Aniversario del inicio de la Independencia de México desde el balcón de Palacio de Gobierno en plaza Juárez ante miles de asistentes, acompañado por representantes del Congreso local y del Tribunal Superior de Justicia, culminando con el concierto de Carlos Rivera.</t>
-  </si>
-  <si>
-    <t>Grito De Independencia</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca vitoreó a los héroes de la Patria y a la transformación de Hidalgo en la plaza Juárez durante la ceremonia del Grito de Independencia.</t>
-  </si>
-  <si>
-    <t>Gobernador, Congreso, TSJEH, Presidencia, Sedena</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Andrés Velázquez Vázquez, Rebeca Stella Aladro Echeverría, Carlos Rivera</t>
-  </si>
-  <si>
-    <t>AUTORIDADES ASEGURAN SALDO BLANCO DURANTE LAS FIESTAS PATRIAS DE 2026</t>
-  </si>
-  <si>
-    <t>Corporaciones de seguridad reportaron un desarrollo tranquilo y con saldo blanco durante los festejos patrios en los 84 municipios de Hidalgo. El secretario de Seguridad, Salvador Cruz Neri, desmintió reportes de detonaciones de arma de fuego, mientras que el alcalde de Pachuca, Jorge Reyes, informó de seis sancionados en el alcoholímetro sin detenidos.</t>
-  </si>
-  <si>
-    <t>La SSPH y la alcaldía de Pachuca confirmaron saldo blanco en las celebraciones patrias de la entidad, reportando decomiso de pirotecnia y seis conductores sancionados en el alcoholímetro.</t>
-  </si>
-  <si>
-    <t>SSPH, Ayuntamiento, PC</t>
-  </si>
-  <si>
-    <t>Salvador Cruz Neri, Jorge Reyes Hernández</t>
-  </si>
-  <si>
-    <t>ATRIBUYE SIPDUS DAÑOS EN VIALIDADES A LLUVIAS</t>
-  </si>
-  <si>
-    <t>El secretario de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus), Alejandro Sánchez García, consideró normales los encharcamientos, baches y daños en obras recién rehabilitadas como los bulevares Minero, Everardo Márquez y Felipe Ángeles debido a las intensas precipitaciones pluviométricas del año, asegurando que las empresas contratistas responderán mediante fianzas de vicios ocultos.</t>
-  </si>
-  <si>
-    <t>El titular de Sipdus, Alejandro Sánchez, justificó las inundaciones y deterioros en calles y bulevares de Pachuca por la carga atípica de lluvias e indicó que las constructoras harán efectivas las garantías de obra.</t>
-  </si>
-  <si>
-    <t>INICIA EN OCTUBRE RESTAURACIÓN DEL PISAL DE PACHUCA</t>
-  </si>
-  <si>
-    <t>El oficial mayor del gobierno estatal, Edgar Orlando Ángeles Pérez, dio a conocer que a inicios de octubre comenzará la intervención del pisal "Homenaje a la Mujer del Mundo" de Byron Gálvez en el Parque Cultural Hidalguense de Pachuca, con una duración proyectada de seis meses y dividido en seis tramos con accesos restringidos temporales.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor y Sipdus licitaron la restauración por etapas del pisal de Byron Gálvez en el Parque Cultural Hidalguense, contemplando seis meses de ejecución a partir de octubre.</t>
-  </si>
-  <si>
-    <t>MÁS DE 4 MIL PARTICIPARON EN EL DESFILE CÍVICO MILITAR</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar presenció el desfile cívico militar conmemorativo del 216 Aniversario de la Independencia de México en el Centro Histórico de Pachuca, donde marcharon 2,701 estudiantes, 150 miembros del Pentatlón, 216 agentes municipales, 750 elementos de la SSPH y Bomberos, Guardia Nacional, Ejército Mexicano y agrupaciones charras.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca encabezó la parada cívico-militar en el centro de Pachuca con la marcha de más de 4 mil alumnos y efectivos de las corporaciones de seguridad.</t>
-  </si>
-  <si>
-    <t>Gobernador, SSPH, Sedena, GN, Cruz Roja, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>REPUNTARON EN HUASCA LOS DELITOS FRAUDE Y LESIONES</t>
-  </si>
-  <si>
-    <t>Datos del SESNSP reflejaron que entre enero y julio de 2026 las denuncias por fraude pasaron de 0 a 9 en Huasca de Ocampo, las lesiones se elevaron de 19 a 26 casos y se contabilizaron 2 homicidios, en contraste con disminuciones en robo y despojo.</t>
-  </si>
-  <si>
-    <t>Huasca</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
-    <t>El Secretariado Ejecutivo reportó incrementos en las carpetas de investigación por fraude y lesiones en Huasca de Ocampo en el primer semestre.</t>
-  </si>
-  <si>
-    <t>Martha Sáenz</t>
-  </si>
-  <si>
-    <t>RESCATAN SABERES INDÍGENAS</t>
-  </si>
-  <si>
-    <t>El IHE y el CELCI presentaron en la primaria El Nigromante de Ixmiquilpan la edición 22 de la revista Cazadores de saberes para fomentar el conocimiento de las tradiciones y lenguas náhuatl y otomí entre la niñez hidalguense.</t>
-  </si>
-  <si>
-    <t>Autoridades del IHE y del CELCI difundieron en Ixmiquilpan la edición 22 de la revista Cazadores de saberes para preservar la identidad de los pueblos originarios.</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Ortega Sánchez, Julio Menchaca Salazar, Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>SALDO BLANCO EN HIDALGO TRAS FESTEJOS PATRIOS</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, gobernador de Hidalgo, informó que tras las celebraciones por el 216 aniversario de la Independencia de México en los 84 municipios de Hidalgo se registró saldo blanco, destacando el despliegue de 5 mil 580 elementos de seguridad estatal y municipal.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca y la SSPH reportaron saldo blanco en los 84 municipios durante las celebraciones del Grito de Independencia con despliegue de 5,580 elementos.</t>
-  </si>
-  <si>
-    <t>UN TOTAL DE 7 MUERTES MATERNAS EN LA ENTIDAD</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud Federal informó que durante 2026 la entidad registró un total de siete muertes maternas en el sector salud (SSH, IMSS, IMSS-Bienestar y particulares), derivado de hemorragias, trastornos hipertensivos y complicaciones del parto, por lo que la SSH exhortó a llevar control prenatal.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud Federal reportó siete muertes maternas en Hidalgo durante 2026, por lo que las autoridades sanitarias instaron a acudir a revisiones prenatales preventivas.</t>
-  </si>
-  <si>
-    <t>SSH, IMSS, IMSS-Bienestar, Presidencia</t>
-  </si>
-  <si>
-    <t>Concluye el 216 aniversario del inicio de la Independencia</t>
-  </si>
-  <si>
-    <t>Con la participación de más de 5 mil estudiantes, elementos de seguridad, Fuerzas Armadas, cuerpos de emergencia y charros, concluyeron los festejos por el 216 Aniversario de la Independencia en Pachuca con el Desfile Cívico-Militar encabezado por el gobernador Julio Menchaca Salazar.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca encabezó el Desfile Cívico-Militar en el centro de Pachuca con la marcha de más de 5 mil alumnos, efectivos de seguridad y agrupaciones ecuestres.</t>
-  </si>
-  <si>
-    <t>Acercan registro vehicular gratuito a todas las regiones</t>
-  </si>
-  <si>
-    <t>La Secretaría de Gobierno de Hidalgo incorporó una unidad móvil del Registro Público Vehicular (Repuve) para recorrer municipios sin módulo fijo y colocar gratuitamente el chip de identificación vehicular en 15 minutos, fortaleciendo la certeza jurídica y la prevención de delitos.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Gobierno puso en operación un módulo itinerante del Repuve para colocar gratuitamente el chip de registro vehicular en comunidades sin módulos fijos.</t>
-  </si>
-  <si>
-    <t>Segobh, Gobernador, Bienestar</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Guillermo Olivares Reyna</t>
-  </si>
-  <si>
-    <t>Negaron hackeo y vulneración del sistema del C5i de Hidalgo</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo desmintió categóricamente rumores difundidos en redes sociales sobre un supuesto hackeo o vulneración de los sistemas de inteligencia del C5i, confirmando la solidez de sus esquemas cibernéticos e infraestructura tecnológica.</t>
-  </si>
-  <si>
-    <t>Ciberseguridad</t>
-  </si>
-  <si>
-    <t>La SSPH desmintió haber sufrido un hackeo en la plataforma del C5i de Hidalgo, asegurando que los sistemas operan con esquemas de protección cibernética blindados.</t>
-  </si>
-  <si>
-    <t>SSPH, C5i</t>
-  </si>
-  <si>
-    <t>Balacearon y ejecutaron a un sacerdote católico, en Lolotla</t>
-  </si>
-  <si>
-    <t>Vecinos de Lolotla hallaron sin vida al sacerdote católico Román de la Cruz Hernández, de 48 años, párroco de la iglesia de la Santa Cruz en Huejutla, con heridas de arma de fuego y una cartulina con un mensaje amenazante dejada en su espalda a la orilla de la carretera Tetlapaya-Hueyapa. La PGJEH inició carpeta de investigación.</t>
-  </si>
-  <si>
-    <t>El párroco de Huejutla, Román de la Cruz Hernández, fue localizado ejecutado con disparos y un mensaje amenazante a la orilla de la carretera en Lolotla, abriéndose la carpeta de investigación en la PGJEH.</t>
-  </si>
-  <si>
-    <t>PGJEH, SSPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Román de la Cruz Hernández</t>
-  </si>
-  <si>
-    <t>ASEGURAN PUNTO DE VENTA DE NARCÓTICOS</t>
-  </si>
-  <si>
-    <t>Mediante orden de cateo en Ciudad Sahagún, Tepeapulco, elementos de la SSPH, PGJEH y Sedena desmantelaron un centro de distribución de drogas en la colonia Rojo Gómez, decomisando 1,073 dosis de cristal, 240 de marihuana, un arma de fuego larga, chalecos tácticos y básculas de precisión.</t>
-  </si>
-  <si>
-    <t>Operativo conjunto de la SSPH, PGJEH y Ejército Mexicano desarticuló un punto de narcomenudeo en Ciudad Sahagún, asegurando más de 1,300 dosis de narcóticos y armas de fuego.</t>
-  </si>
-  <si>
-    <t>MÁS DE 4 MIL PERSONAS PARTICIPARON EN DESFILE CÍVICO-MILITAR EN PACHUCA</t>
-  </si>
-  <si>
-    <t>Con la participación de estudiantes, elementos de seguridad, cuerpos de emergencia, integrantes de las Fuerzas Armadas y asociaciones de charros, Hidalgo concluyó este miércoles las actividades conmemorativas por el 216 aniversario del Inicio de la Independencia de México con un desfile cívico-militar por las calles del Centro Histórico de Pachuca. El contingente estuvo integrado por 2,701 estudiantes de educación básica, media superior y superior, además de corporaciones de seguridad y rescate.</t>
-  </si>
-  <si>
-    <t>Con la participación de 2,701 estudiantes, corporaciones policiales y militares, concluyeron los festejos patrios en Pachuca con el Desfile Cívico-Militar y saldo blanco estatal.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Román Bernal Díaz</t>
-  </si>
-  <si>
-    <t>Rehabilitación del Pisal Monumental podría concluir en marzo de 2027</t>
-  </si>
-  <si>
-    <t>La rehabilitación y mantenimiento del Pisal Monumental 'Homenaje a la Mujer del Mundo', obra del artista Byron Gálvez ubicada en el Parque Cultural Hidalguense en Pachuca, podría concluir en marzo de 2027, informó el titular de la Oficialía Mayor, Edgar Orlando Ángeles Pérez. El proyecto contempla seis etapas ejecutadas junto con Sipdus para evitar el cierre total del espacio.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor y Sipdus licitarán a finales de septiembre la restauración por seis etapas del pisal de Byron Gálvez en Pachuca, proyectando concluir en marzo de 2027.</t>
-  </si>
-  <si>
-    <t>Demandas de “El Mexe” continuarán en atención durante los próximos años: Castrejón</t>
-  </si>
-  <si>
-    <t>Tras la manifestación de estudiantes de la Normal Rural El Mexe durante el informe de la presidenta Claudia Sheinbaum en Pachuca, el secretario de Educación Pública de Hidalgo, Natividad Castrejón, señaló que se mantendrá el diálogo institucional continuo para atender sus solicitudes educativas e infraestructura.</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón, afirmó que la atención a las peticiones de los normalistas de El Mexe continuará durante los próximos años mediante el subsecretario Daniel Fragoso.</t>
-  </si>
-  <si>
-    <t>SEPH, PGJEH, Presidencia</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Daniel Fragoso Torres, Francisco Fernández Hasbun, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>Grandes cantidades de agua están afectando la infraestructura pública: SIPDUS</t>
-  </si>
-  <si>
-    <t>El titular de la SIPDUS, Alejandro Sánchez García, reconoció que las precipitaciones atípicas han afectado las vialidades en Pachuca, destacando que los trabajos de infraestructura realizados han permitido desfogar el agua en cuestión de horas en puntos críticos como el bulevar Minero y Colosio.</t>
-  </si>
-  <si>
-    <t>La Sipdus atribuyó el deterioro de calles y baches en Pachuca a la acumulación de lluvias de la temporada, descartando fallas permanentes en obras recientes.</t>
-  </si>
-  <si>
-    <t>SALDO BLANCO EN HIDALGO DURANTE FESTEJOS PATRIOS</t>
-  </si>
-  <si>
-    <t>La noche del 15 de septiembre transcurrió con saldo blanco en Hidalgo, de acuerdo con el gobernador Julio Menchaca Salazar, quien informó que no se registraron incidentes durante el Grito en los municipios del estado. En Pachuca se detuvieron a seis conductores en el alcoholímetro y se entregó a una menor extraviada sin lesiones.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca y autoridades municipales informaron saldo blanco en las celebraciones patrias de los 84 municipios de Hidalgo.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Jorge Reyes Hernández</t>
-  </si>
-  <si>
-    <t>CAMBIAN DE EMPRESA PARA REPARAR EL PISAL DEDICADO A LA MUJER</t>
-  </si>
-  <si>
-    <t>Una empresa distinta a la que elaboró originalmente el Pisal 'Homenaje a la Mujer del Mundo' intervendrá la obra de Byron Gálvez por fracturas y piezas ausentes, informó el Oficial Mayor, Orlando Ángeles Pérez. Explicó que la licitación se emitirá entre septiembre u octubre para concluir en marzo de 2027.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor licitará la intervención del pisal de Byron Gálvez en Pachuca para reponer mosaicos a medida respetando el diseño original.</t>
-  </si>
-  <si>
-    <t>SIN DEMANDAS CONTRA FIRMAS CONSTRUCTORAS POR MALAS OBRAS</t>
-  </si>
-  <si>
-    <t>La Sipdus informó que no mantiene procesos contra empresas por fallas estructurales o baches, ya que las compañías cuentan con fianza por vicios ocultos de un año, reconociendo el titular Alejandro Sánchez que las lluvias atípicas han generado afectaciones temporales en calles y bulevares.</t>
-  </si>
-  <si>
-    <t>El titular de Sipdus descartó litigios contra empresas por baches o socavones al señalar que las lluvias han causado daños y las constructoras aplicarán garantías.</t>
-  </si>
-  <si>
-    <t>IGLESIA CONDENA HOMICIDIO DE SACERDOTE DE HUEJUTLA</t>
-  </si>
-  <si>
-    <t>La Diócesis de Huejutla y la Conferencia del Episcopado Mexicano (CEM) exigieron esclarecer el asesinato del sacerdote Román de la Cruz Hernández, de 48 años, ocurrido en Lolotla, mientras la PGJEH integra la carpeta de investigación correspondiente.</t>
-  </si>
-  <si>
-    <t>La Iglesia católica exigió a las autoridades de Hidalgo esclarecer el homicidio del párroco Román de la Cruz localizado en Lolotla.</t>
-  </si>
-  <si>
-    <t>Román de la Cruz Hernández, José Hirais Acosta Beltrán</t>
-  </si>
-  <si>
-    <t>La escuela primaria Aquiles Serdán en Tulancingo deberá ser demolida y reconstruida en su totalidad por fallas estructurales severas, informó el titular de la SEPH, Natividad Castrejón. Las obras durarán un ciclo escolar completo.</t>
-  </si>
-  <si>
-    <t>La SEPH sustituirá completamente la infraestructura de la primaria Aquiles Serdán en Tulancingo al detectar daños graves en la estructura.</t>
   </si>
 </sst>
 </file>
@@ -1341,8 +1257,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ57" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ57" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ51" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ51" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1774,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1924,28 +1840,28 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F2" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1960,19 +1876,19 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>58</v>
@@ -1984,36 +1900,34 @@
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>106</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="AJ2" s="2"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F3" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -2037,19 +1951,19 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA3">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>58</v>
@@ -2061,42 +1975,40 @@
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>112</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="AJ3" s="2"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F4" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>49</v>
@@ -2114,19 +2026,19 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="AA4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>58</v>
@@ -2138,43 +2050,45 @@
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="AG4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ4" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F5" s="1">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2189,69 +2103,67 @@
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="Y5" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA5">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>123</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="AJ5" s="2"/>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F6" s="1">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2266,16 +2178,16 @@
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="Y6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="AA6">
         <v>20</v>
@@ -2290,39 +2202,37 @@
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="AJ6" s="2"/>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F7" s="1">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>45</v>
@@ -2343,19 +2253,19 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA7">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>58</v>
@@ -2367,45 +2277,43 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ7" s="2" t="s">
-        <v>134</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="AJ7" s="2"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F8" s="1">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2420,19 +2328,19 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA8">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>58</v>
@@ -2444,42 +2352,40 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AJ8" s="2" t="s">
-        <v>141</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AJ8" s="2"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F9" s="1">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>49</v>
@@ -2497,10 +2403,10 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>57</v>
@@ -2509,57 +2415,55 @@
         <v>43</v>
       </c>
       <c r="AA9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD9" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="AJ9" s="2" t="s">
-        <v>76</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AJ9" s="2"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F10" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2574,19 +2478,19 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA10">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>58</v>
@@ -2598,39 +2502,37 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AJ10" s="2" t="s">
-        <v>152</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AJ10" s="2"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="F11" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>61</v>
@@ -2651,16 +2553,16 @@
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="AA11">
         <v>20</v>
@@ -2675,34 +2577,34 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="AJ11" s="2"/>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="F12" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -2711,7 +2613,7 @@
         <v>61</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2726,19 +2628,19 @@
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA12">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>58</v>
@@ -2750,42 +2652,42 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="F13" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>49</v>
@@ -2803,19 +2705,19 @@
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA13">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>58</v>
@@ -2827,42 +2729,40 @@
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AJ13" s="2" t="s">
-        <v>171</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="AJ13" s="2"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F14" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>49</v>
@@ -2877,13 +2777,13 @@
         <v>60</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>174</v>
+        <v>66</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>57</v>
@@ -2892,7 +2792,7 @@
         <v>43</v>
       </c>
       <c r="AA14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB14" s="2" t="s">
         <v>58</v>
@@ -2904,39 +2804,37 @@
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AJ14" s="2" t="s">
-        <v>178</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="AJ14" s="2"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="F15" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>45</v>
@@ -2957,19 +2855,19 @@
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="Y15" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA15">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>58</v>
@@ -2981,45 +2879,45 @@
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="AG15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>182</v>
+        <v>80</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="F16" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>186</v>
+        <v>61</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3031,19 +2929,19 @@
         <v>60</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="AA16">
         <v>20</v>
@@ -3055,51 +2953,46 @@
         <v>38</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ16" s="2" t="s">
-        <v>189</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="AJ16" s="2"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F17" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G17">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3114,19 +3007,19 @@
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA17">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>58</v>
@@ -3138,40 +3031,40 @@
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="AJ17" s="2"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F18" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>49</v>
@@ -3189,19 +3082,19 @@
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>58</v>
@@ -3213,45 +3106,43 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="AJ18" s="2" t="s">
-        <v>199</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="AJ18" s="2"/>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="F19" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3266,19 +3157,19 @@
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA19">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>58</v>
@@ -3290,45 +3181,43 @@
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="AJ19" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="AJ19" s="2"/>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F20" s="1">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3343,19 +3232,19 @@
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA20">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>58</v>
@@ -3367,39 +3256,37 @@
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="AG20" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ20" s="2" t="s">
-        <v>210</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="AJ20" s="2"/>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="F21" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>61</v>
@@ -3420,19 +3307,19 @@
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA21">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>58</v>
@@ -3444,45 +3331,43 @@
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ21" s="2" t="s">
-        <v>216</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AJ21" s="2"/>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="F22" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3497,19 +3382,19 @@
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="AA22">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AB22" s="2" t="s">
         <v>58</v>
@@ -3521,39 +3406,37 @@
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="AG22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="AJ22" s="2" t="s">
-        <v>222</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AJ22" s="2"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="F23" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>45</v>
@@ -3574,25 +3457,25 @@
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>59</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD23" s="2" t="s">
         <v>44</v>
@@ -3604,39 +3487,37 @@
         <v>41</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AJ23" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="AJ23" s="2"/>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="F24" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -3651,19 +3532,19 @@
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA24">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AB24" s="2" t="s">
         <v>58</v>
@@ -3675,45 +3556,43 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="AJ24" s="2" t="s">
-        <v>210</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AJ24" s="2"/>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="F25" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -3728,64 +3607,66 @@
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB25" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="AG25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="AJ25" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="F26" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>49</v>
@@ -3803,10 +3684,10 @@
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="Y26" s="2" t="s">
         <v>59</v>
@@ -3821,46 +3702,48 @@
         <v>58</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="AJ26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="F27" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>45</v>
+        <v>219</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>49</v>
@@ -3878,19 +3761,19 @@
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z27" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA27">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB27" s="2" t="s">
         <v>58</v>
@@ -3902,42 +3785,42 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>65</v>
+        <v>222</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="F28" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>49</v>
@@ -3955,19 +3838,19 @@
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="Y28" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA28">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB28" s="2" t="s">
         <v>58</v>
@@ -3979,45 +3862,45 @@
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AG28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="F29" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -4029,22 +3912,22 @@
         <v>60</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>253</v>
+        <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA29">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AB29" s="2" t="s">
         <v>58</v>
@@ -4056,42 +3939,40 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="AG29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="AJ29" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="AJ29" s="2"/>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="F30" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>49</v>
@@ -4109,69 +3990,69 @@
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA30">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB30" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD30" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>65</v>
+        <v>238</v>
       </c>
       <c r="AG30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>89</v>
+        <v>239</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="F31" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4186,10 +4067,10 @@
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>57</v>
@@ -4198,7 +4079,7 @@
         <v>43</v>
       </c>
       <c r="AA31">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB31" s="2" t="s">
         <v>58</v>
@@ -4210,45 +4091,43 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="AJ31" s="2" t="s">
-        <v>94</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="AJ31" s="2"/>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="F32" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>266</v>
+        <v>61</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4263,19 +4142,19 @@
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA32">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>58</v>
@@ -4287,39 +4166,37 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>268</v>
+        <v>41</v>
       </c>
       <c r="AG32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="AJ32" s="2" t="s">
-        <v>270</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AJ32" s="2"/>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="F33" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>45</v>
@@ -4340,66 +4217,64 @@
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA33">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC33" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD33" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="AG33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="AJ33" s="2" t="s">
-        <v>274</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="AJ33" s="2"/>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="F34" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>49</v>
@@ -4417,13 +4292,13 @@
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>43</v>
@@ -4435,48 +4310,48 @@
         <v>58</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>46</v>
+        <v>260</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="F35" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>49</v>
@@ -4494,19 +4369,19 @@
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA35">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB35" s="2" t="s">
         <v>58</v>
@@ -4518,45 +4393,43 @@
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>39</v>
+        <v>267</v>
       </c>
       <c r="AG35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AJ35" s="2" t="s">
-        <v>286</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="AJ35" s="2"/>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="F36" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4571,19 +4444,19 @@
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>73</v>
+        <v>271</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA36">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>58</v>
@@ -4595,45 +4468,43 @@
         <v>44</v>
       </c>
       <c r="AF36" s="2" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="AG36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="AJ36" s="2" t="s">
-        <v>291</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="AJ36" s="2"/>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="F37" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4648,19 +4519,19 @@
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA37">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>58</v>
@@ -4672,42 +4543,40 @@
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>150</v>
+        <v>239</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AJ37" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="AJ37" s="2"/>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="F38" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>49</v>
@@ -4716,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="S38">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>60</v>
@@ -4725,75 +4594,73 @@
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA38">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="AJ38" s="2" t="s">
-        <v>210</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="AJ38" s="2"/>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="F39" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R39">
         <v>1</v>
       </c>
       <c r="S39">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>60</v>
@@ -4802,19 +4669,19 @@
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA39">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AB39" s="2" t="s">
         <v>58</v>
@@ -4826,42 +4693,42 @@
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>301</v>
+        <v>89</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>88</v>
+        <v>285</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="F40" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>304</v>
+        <v>48</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>42</v>
@@ -4870,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="S40">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>60</v>
@@ -4879,10 +4746,10 @@
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="Y40" s="2" t="s">
         <v>57</v>
@@ -4891,82 +4758,84 @@
         <v>43</v>
       </c>
       <c r="AA40">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC40" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD40" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="AG40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AJ40" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="AJ40" s="2" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="F41" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G41">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>186</v>
+        <v>75</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R41">
         <v>1</v>
       </c>
       <c r="S41">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>60</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z41" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA41">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>58</v>
@@ -4975,51 +4844,45 @@
         <v>38</v>
       </c>
       <c r="AD41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>41</v>
+        <v>296</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AJ41" s="2" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="F42" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G42">
-        <v>5</v>
+        <v>46286</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -5034,19 +4897,19 @@
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>73</v>
+        <v>300</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="Y42" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA42">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB42" s="2" t="s">
         <v>58</v>
@@ -5058,45 +4921,40 @@
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AJ42" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="AJ42" s="2"/>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="F43" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G43">
-        <v>5</v>
+        <v>46286</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -5111,10 +4969,10 @@
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="Y43" s="2" t="s">
         <v>57</v>
@@ -5129,46 +4987,43 @@
         <v>58</v>
       </c>
       <c r="AC43" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD43" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>47</v>
+        <v>308</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="AJ43" s="2"/>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="F44" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G44">
-        <v>5</v>
+        <v>46286</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>49</v>
@@ -5186,19 +5041,19 @@
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>202</v>
+        <v>311</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA44">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB44" s="2" t="s">
         <v>58</v>
@@ -5210,45 +5065,40 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="AJ44" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="AJ44" s="2"/>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="F45" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G45">
-        <v>6</v>
+        <v>46286</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5263,19 +5113,19 @@
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z45" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA45">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB45" s="2" t="s">
         <v>58</v>
@@ -5293,36 +5143,31 @@
         <v>41</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>67</v>
+        <v>239</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="AJ45" s="2" t="s">
-        <v>326</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="AJ45" s="2"/>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F46" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G46">
-        <v>8</v>
+        <v>46286</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>49</v>
@@ -5340,19 +5185,19 @@
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA46">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB46" s="2" t="s">
         <v>58</v>
@@ -5370,37 +5215,34 @@
         <v>41</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>331</v>
+        <v>273</v>
       </c>
       <c r="AJ46" s="2"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="F47" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G47">
-        <v>9</v>
+        <v>46286</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5412,22 +5254,22 @@
         <v>60</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>37</v>
+        <v>322</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>138</v>
+        <v>323</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="Y47" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA47">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>58</v>
@@ -5445,39 +5287,37 @@
         <v>41</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="AJ47" s="2" t="s">
-        <v>336</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="AJ47" s="2"/>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="F48" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G48">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5492,16 +5332,16 @@
         <v>37</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z48" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="AA48">
         <v>20</v>
@@ -5516,43 +5356,43 @@
         <v>44</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>97</v>
+        <v>329</v>
       </c>
       <c r="AJ48" s="2"/>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="F49" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -5567,19 +5407,19 @@
         <v>37</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>202</v>
+        <v>332</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA49">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AB49" s="2" t="s">
         <v>58</v>
@@ -5591,39 +5431,39 @@
         <v>44</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AG49" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>301</v>
+        <v>103</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F50" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>45</v>
@@ -5644,19 +5484,19 @@
         <v>37</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>148</v>
+        <v>337</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AA50">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB50" s="2" t="s">
         <v>58</v>
@@ -5668,45 +5508,45 @@
         <v>44</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AG50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>210</v>
+        <v>334</v>
       </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="F51" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -5721,10 +5561,10 @@
         <v>37</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="Y51" s="2" t="s">
         <v>57</v>
@@ -5745,7 +5585,7 @@
         <v>44</v>
       </c>
       <c r="AF51" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="AG51" s="2" t="s">
         <v>40</v>
@@ -5754,472 +5594,10 @@
         <v>46</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>350</v>
+        <v>46</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F52" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G52">
-        <v>3</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R52">
-        <v>1</v>
-      </c>
-      <c r="S52">
-        <v>13262</v>
-      </c>
-      <c r="T52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W52" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="X52" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y52" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA52">
-        <v>20</v>
-      </c>
-      <c r="AB52" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC52" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF52" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH52" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="AI52" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AJ52" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F53" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G53">
-        <v>2</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R53">
-        <v>1</v>
-      </c>
-      <c r="S53">
-        <v>13262</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W53" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="X53" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y53" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z53" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA53">
-        <v>40</v>
-      </c>
-      <c r="AB53" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC53" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF53" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH53" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI53" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AJ53" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F54" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G54">
-        <v>3</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R54">
-        <v>1</v>
-      </c>
-      <c r="S54">
-        <v>13262</v>
-      </c>
-      <c r="T54" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V54" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W54" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="X54" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="Y54" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA54">
-        <v>20</v>
-      </c>
-      <c r="AB54" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC54" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF54" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH54" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI54" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="AJ54" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F55" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G55">
-        <v>3</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R55">
-        <v>1</v>
-      </c>
-      <c r="S55">
-        <v>13262</v>
-      </c>
-      <c r="T55" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V55" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W55" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="X55" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="Y55" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z55" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA55">
-        <v>40</v>
-      </c>
-      <c r="AB55" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC55" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD55" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF55" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG55" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH55" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI55" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AJ55" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F56" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G56">
-        <v>5</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R56">
-        <v>1</v>
-      </c>
-      <c r="S56">
-        <v>13262</v>
-      </c>
-      <c r="T56" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V56" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W56" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="X56" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="Y56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z56" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA56">
-        <v>40</v>
-      </c>
-      <c r="AB56" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC56" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD56" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG56" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH56" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI56" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AJ56" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F57" s="1">
-        <v>46282</v>
-      </c>
-      <c r="G57">
-        <v>5</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="R57">
-        <v>1</v>
-      </c>
-      <c r="S57">
-        <v>13262</v>
-      </c>
-      <c r="T57" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V57" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W57" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X57" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="Y57" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z57" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA57">
-        <v>20</v>
-      </c>
-      <c r="AB57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD57" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF57" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG57" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI57" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ57" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FCAD75-2417-4976-8A36-A540F901D7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69487F9-1FA4-4AFF-9E14-2682960DD0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="414">
   <si>
     <t>Canal</t>
   </si>
@@ -193,9 +193,6 @@
     <t>SSH</t>
   </si>
   <si>
-    <t>Tulancingo</t>
-  </si>
-  <si>
     <t>Positivo</t>
   </si>
   <si>
@@ -250,9 +247,6 @@
     <t>Fiestas Patrias</t>
   </si>
   <si>
-    <t>Oficialía Mayor</t>
-  </si>
-  <si>
     <t>Adela Garmez</t>
   </si>
   <si>
@@ -262,820 +256,1039 @@
     <t>Huejutla</t>
   </si>
   <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Socorro Ávila</t>
-  </si>
-  <si>
-    <t>Nathali González</t>
-  </si>
-  <si>
     <t>Lolotla</t>
   </si>
   <si>
     <t>Incidencia Delictiva</t>
   </si>
   <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
     <t>Cultura</t>
   </si>
   <si>
-    <t>Van a demoler primaria en Tulancingo; edificarán otra</t>
-  </si>
-  <si>
     <t>Turismo</t>
   </si>
   <si>
-    <t>Gustavo Vargas</t>
-  </si>
-  <si>
     <t>Planeación</t>
   </si>
   <si>
     <t>Tula</t>
   </si>
   <si>
-    <t>Carretera En Mal Estado</t>
-  </si>
-  <si>
-    <t>César Martínez</t>
-  </si>
-  <si>
-    <t>Simulacro Sismo</t>
-  </si>
-  <si>
-    <t>Apoyo a personas con discapacidad</t>
-  </si>
-  <si>
-    <t>DIFH</t>
-  </si>
-  <si>
-    <t>PGJEH, SSPH</t>
-  </si>
-  <si>
-    <t>Tezontepec de Aldama</t>
-  </si>
-  <si>
-    <t>Semarnath</t>
-  </si>
-  <si>
-    <t>PGJEH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Lluvias de septiembre dejan deslaves en Tenango</t>
-  </si>
-  <si>
-    <t>El registro de precipitaciones recientes en la entidad ha comenzado a generar diversas afectaciones operativas, entre las que destacan obstrucciones viales por deslaves en Tenango de Doria y acumulación pluvial en Zacualtipán.</t>
-  </si>
-  <si>
-    <t>Tenango de Doria</t>
-  </si>
-  <si>
-    <t>Deslaves por lluvias</t>
-  </si>
-  <si>
-    <t>Precipitaciones provocaron deslave en la carretera Tenango de Doria-Metepec y encharcamientos en Zacualtipán, restableciéndose la circulación tras labores de limpieza.</t>
-  </si>
-  <si>
-    <t>Segobh, IMSS</t>
-  </si>
-  <si>
-    <t>Accidentes y males hepáticos son más letales en hombres</t>
-  </si>
-  <si>
-    <t>Las estadísticas del Inegi correspondientes al primer trimestre de 2026 revelan diferencias significativas en las causas de fallecimiento entre hombres y mujeres en Hidalgo.</t>
-  </si>
-  <si>
-    <t>Prevención De Enfermedades</t>
-  </si>
-  <si>
-    <t>Reporte del Inegi indica que mientras las enfermedades del corazón y diabetes lideran los decesos generales, los hombres registran mayor mortalidad en males hepáticos y accidentes.</t>
-  </si>
-  <si>
-    <t>SSH, Presidencia</t>
-  </si>
-  <si>
-    <t>IP pide homologar trámites para acelerar inversión local</t>
-  </si>
-  <si>
-    <t>El presidente del CCEH, Jorge González Corona, planteó la necesidad de homologar en todos los municipios los requisitos para tramitar licencias de funcionamiento y construcción.</t>
-  </si>
-  <si>
-    <t>Atracción De Inversiones</t>
-  </si>
-  <si>
-    <t>El CCEH propuso estandarizar trámites municipales para agilizar la llegada y consolidación de inversiones privadas en el estado.</t>
-  </si>
-  <si>
-    <t>Sedeco</t>
-  </si>
-  <si>
-    <t>Jorge González Corona</t>
-  </si>
-  <si>
-    <t>Preparan etapa de pavimentación en la vía Cuautepec-Tulancingo</t>
-  </si>
-  <si>
-    <t>SIPDUS publicó la licitación para la tercera etapa de pavimentación hidráulica de la carretera Cuautepec-Tulancingo, proyectando iniciar labores en octubre.</t>
-  </si>
-  <si>
-    <t>Cuautepec</t>
-  </si>
-  <si>
-    <t>Pavimentación hidráulica</t>
-  </si>
-  <si>
-    <t>SIPDUS arrancó la licitación pública para la pavimentación de la carretera Cuautepec-Tulancingo en su tercera fase con inversión mínima de 6.1 mdp.</t>
-  </si>
-  <si>
-    <t>DIFH recibe tres camionetas adaptadas para el traslado de personas con discapacidad</t>
-  </si>
-  <si>
-    <t>Como parte de la entrega de 91 vehículos accesibles y adaptados a los sistemas estatales DIF, la presidenta del Patronato del Sistema DIF Hidalgo, Edda Vite Ramos, recibió tres camionetas destinadas al transporte especializado de personas con discapacidad.</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos, presidenta del Patronato del DIF Hidalgo, recibió tres camionetas adaptadas para el transporte especializado de personas con discapacidad hacia servicios de rehabilitación en el CRIH.</t>
-  </si>
-  <si>
     <t>Veida Martínez Miranda</t>
   </si>
   <si>
-    <t>DIFH, CRIH</t>
-  </si>
-  <si>
-    <t>Tuzobús movilizó 1.8 millones de pasajeros durante julio, 6.6% más que en 2025</t>
-  </si>
-  <si>
-    <t>El Sistema de Transporte Metropolitano (Tuzobús) registró un incremento de 6.6% en el número de pasajeros durante julio de 2026 en comparación con 2025, al movilizar a 1.8 millones de usuarios según la ETUP del Inegi.</t>
-  </si>
-  <si>
-    <t>Afluencia Tuzobús</t>
-  </si>
-  <si>
-    <t>Durante julio de 2026, el Tuzobús transportó a 1.8 millones de pasajeros en la Zona Metropolitana de Pachuca, lo que representa un aumento anual del 6.6% según datos del Inegi.</t>
-  </si>
-  <si>
     <t>Semot</t>
   </si>
   <si>
-    <t>Semot, Inegi</t>
-  </si>
-  <si>
-    <t>Costará 1.9 mdp mantenimiento del Cuartel del Arte en Pachuca</t>
-  </si>
-  <si>
-    <t>Los trabajos de mantenimiento del Cuartel del Arte en Pachuca tendrán una inversión de 1.94 millones de pesos tras el fallo de la licitación EO-SIPDUS-N116-2026 emitida por la Sipdus.</t>
-  </si>
-  <si>
-    <t>Licitaciones</t>
-  </si>
-  <si>
-    <t>La Sipdus adjudicó los trabajos de mantenimiento del Cuartel del Arte en Pachuca por 1.94 mdp. La obra durará 152 días e incluye pisos, impermeabilización e iluminación LED bajo supervisión del INAH.</t>
-  </si>
-  <si>
-    <t>Sipdus, INAH</t>
-  </si>
-  <si>
-    <t>UPT celebrará 24 años con jornada llena de actividades académicas y deportivas</t>
-  </si>
-  <si>
-    <t>Del 28 de septiembre al 2 de octubre, la Universidad Politécnica de Tulancingo (UPT) celebrará su 24 aniversario con eventos académicos, culturales, deportivos y de vinculación con el sector productivo.</t>
-  </si>
-  <si>
-    <t>Aniversario Universidades</t>
-  </si>
-  <si>
-    <t>La Universidad Politécnica de Tulancingo festejará su 24 aniversario con eventos académicos y deportivos, destacando la inauguración de laboratorios para Psicología e Ingeniería Textil.</t>
-  </si>
-  <si>
-    <t>SEPH, UPT</t>
-  </si>
-  <si>
-    <t>Tramo carretero en Tenango, sin paso por afectaciones de lluvias</t>
-  </si>
-  <si>
-    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos informó que, al corte de las 8:00 horas del sábado, no había paso en el tramo carretero Peña Blanca-El Nanthe, en el municipio de Tenango de Doria. La dependencia explicó que el cierre se debe a las afectaciones ocasionadas por las lluvias, por lo que se exhortó a la población a evitar transitar por esa zona y usar vías alternas.</t>
-  </si>
-  <si>
-    <t>La Subsecretaría de Protección Civil de Hidalgo reportó el cierre del tramo carretero Peña Blanca-El Nanthe en Tenango de Doria debido a daños provocados por las lluvias.</t>
-  </si>
-  <si>
-    <t>Protección Civil</t>
-  </si>
-  <si>
-    <t>Hidalgo supera media nacional en consumo de sustancias ilícitas</t>
-  </si>
-  <si>
-    <t>Durante el primer semestre de 2026, el estado de Hidalgo se ubicó por arriba del promedio nacional en las tasas de consumo de, al menos, tres tipos de sustancias ilícitas —metanfetaminas, éxtasis y alucinógenos—, de acuerdo con el Reporte de información epidemiológica del consumo de drogas emitido por los Centros de Integración Juvenil (CIJ). Hidalgo registró 72.3% de consumo alguna vez en la vida de metanfetaminas entre la población atendida.</t>
-  </si>
-  <si>
-    <t>Consumo De Drogas</t>
-  </si>
-  <si>
-    <t>Un informe de los Centros de Integración Juvenil situó a Hidalgo por encima del promedio nacional en el consumo de metanfetaminas, éxtasis y alucinógenos durante el primer semestre de 2026.</t>
-  </si>
-  <si>
-    <t>CIJ</t>
-  </si>
-  <si>
-    <t>La SEP mandata la realización del censo Ejercicios de Integración Académica</t>
-  </si>
-  <si>
-    <t>Tras la publicación de resultados de evaluaciones internacionales que mostraron caídas en matemáticas y lectura, el titular de la SEPH, Natividad Castrejón, informó que buscarán acceder a los datos locales. Recordó que la SEP mandata la realización del censo Ejercicios de Integración Académica a estudiantes de primaria y secundaria para diagnosticar sus niveles de aprendizaje antes de octubre.</t>
-  </si>
-  <si>
-    <t>Mejora educativa</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón, anunció la realización del censo Ejercicios de Integración Académica para diagnosticar el nivel educativo de estudiantes de primaria y secundaria.</t>
-  </si>
-  <si>
     <t>SEPH, SEP</t>
   </si>
   <si>
     <t>Natividad Castrejón</t>
   </si>
   <si>
-    <t>SIPDUS emite fallo para el mantenimiento del Cuartel del Arte</t>
-  </si>
-  <si>
-    <t>Tras declararse desierto un primer procedimiento por falta de interesados, la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS) emitió el fallo de la licitación EO-SIPDUS-N116-2026 correspondiente a la obra de mantenimiento y conservación del Cuartel del Arte en Pachuca, iniciando los trabajos el próximo 2 de octubre.</t>
-  </si>
-  <si>
-    <t>La SIPDUS adjudicó los trabajos de mantenimiento y restauración del Cuartel del Arte en Pachuca mediante la licitación EO-SIPDUS-N116-2026, con inicio programado para el 2 de octubre.</t>
-  </si>
-  <si>
-    <t>Con desfile concluyen festejos patrios en Pachuca</t>
-  </si>
-  <si>
-    <t>Con la participación de más de 4 mil personas entre estudiantes, fuerzas armadas, corporaciones de seguridad y agrupaciones ecuestres, Pachuca cerró las celebraciones por el 216 Aniversario de la Independencia de México. El contingente incluyó 2 mil 700 estudiantes, elementos de la Policía Estatal, Bomberos, Ejército y Guardia Nacional.</t>
-  </si>
-  <si>
-    <t>Crónica</t>
-  </si>
-  <si>
-    <t>Más de 4 mil participantes de instituciones educativas, corporaciones de seguridad y fuerzas armadas formaron parte del desfile conmemorativo del 216 Aniversario de la Independencia en Pachuca.</t>
-  </si>
-  <si>
-    <t>Benjamín H. V.</t>
-  </si>
-  <si>
-    <t>SSPH, Ejército, Guardia Nacional, PIBEH</t>
-  </si>
-  <si>
-    <t>Ocupación hotelera registra disminución en primer semestre</t>
-  </si>
-  <si>
-    <t>La ocupación hotelera en el estado de Hidalgo registró una disminución de 6.4% durante el primer semestre de este año, comparado con el mismo periodo de 2025, según cifras de Datatur de la Secretaría de Turismo del Gobierno federal. Aunque Pachuca se ubicó en las 10 ciudades con mayor ocupación en julio con 66.2%, la presidenta de la Asociación de Hoteles y Moteles, Roxana Vargas Juárez, estimó cerrar el año con 55%.</t>
-  </si>
-  <si>
-    <t>Ocupación Hotelera</t>
-  </si>
-  <si>
-    <t>Cifras del sistema Datatur revelaron una caída del 6.4% en la ocupación hotelera de Hidalgo en el primer semestre de 2026, aunque Pachuca destacó con un 66.2% durante julio.</t>
-  </si>
-  <si>
-    <t>Roxana Vargas Juárez</t>
-  </si>
-  <si>
-    <t>Enfermedades del corazón, principal causa de fallecimientos en la entidad</t>
-  </si>
-  <si>
-    <t>De enero a marzo de 2026 se registraron 1,250 defunciones por enfermedades del corazón en Hidalgo, seguidas de 767 por diabetes mellitus y 568 por tumores malignos, de acuerdo con el INEGI.</t>
-  </si>
-  <si>
-    <t>El Inegi reportó que las afecciones cardiacas, la diabetes y los tumores malignos encabezaron las causas de mortalidad en Hidalgo durante el primer trimestre de 2026, afectando en mayor proporción a los hombres.</t>
-  </si>
-  <si>
-    <t>SSH, Inegi</t>
-  </si>
-  <si>
-    <t>Hidalgo participa en el segundo Simulacro Nacional 2026</t>
-  </si>
-  <si>
-    <t>Con la evacuación de 102 personas en Palacio de Gobierno y la participación de hospitales y comercios, Hidalgo se sumó al segundo Simulacro Nacional 2026 bajo la hipótesis de un sismo de magnitud 7.7.</t>
-  </si>
-  <si>
-    <t>Dependencias estatales, comercios y ciudadanía participaron en el Simulacro Nacional 2026 activando alertas en telefonía móvil y evacuando edificios públicos en Pachuca y Mineral de la Reforma.</t>
-  </si>
-  <si>
     <t>Berenice Gamboa</t>
   </si>
   <si>
-    <t>Segobh, PC, IMSS</t>
-  </si>
-  <si>
-    <t>Reúne tercera Gimnasiada Nacional a más de 5 mil atletas</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, titular de la SEPH, inauguró la tercera Gimnasiada Nacional en la UAEH con la presencia de más de 5 mil deportistas de los 32 estados en nueve disciplinas.</t>
-  </si>
-  <si>
-    <t>Justa Deportiva</t>
-  </si>
-  <si>
-    <t>Más de 5 mil atletas juveniles de todo el país compiten en la tercera Gimnasiada Nacional en Hidalgo para conformar la delegación mexicana que asistirá al Mundial Sub-18 en Brasil.</t>
-  </si>
-  <si>
-    <t>SEPH, UAEH, Gobernador</t>
-  </si>
-  <si>
-    <t>Colonias de Pachuca tendrán baja presión de agua durante cinco días</t>
-  </si>
-  <si>
-    <t>La Caasim alertó sobre una disminución en la presión del suministro de agua potable en las colonias Antonio del Castillo, Morelos, Cuauhtémoc y Centro debido a trabajos de mantenimiento preventivo.</t>
-  </si>
-  <si>
     <t>Abasto de agua</t>
   </si>
   <si>
-    <t>La Caasim informó que debido a obras de mantenimiento realizadas por la empresa Real del Monte, diversas colonias céntricas de Pachuca registrarán baja presión de agua durante cinco días.</t>
-  </si>
-  <si>
-    <t>Sipdus, Caasim</t>
-  </si>
-  <si>
-    <t>Deslaves por lluvias ocasionan cierre carretero en Tenango de Doria</t>
-  </si>
-  <si>
-    <t>La Subsecretaría de Protección Civil ordenó el cierre de la carretera Peña Blanca-El Nanthe en Tenango de Doria a causa de deslaves provocados por las recientes lluvias.</t>
-  </si>
-  <si>
-    <t>Derrumbes y deslaves derivados de lluvias provocaron el cierre del tramo carretero Peña Blanca-El Nanthe en Tenango de Doria, mientras autoridades mantienen vigilancia preventiva en Tepehuacán de Guerrero.</t>
-  </si>
-  <si>
-    <t>Segobh, PC, Sipdus</t>
-  </si>
-  <si>
-    <t>Fortalecen acciones contra enfermedades diarreicas</t>
-  </si>
-  <si>
-    <t>El 94.8% de los casos de enfermedades diarreicas durante 2026, se relacionó con alimentos contaminados, mientras que 65% estuvo asociado con la comida en el hogar, por lo que autoridades sanitarias acordaron reforzar la higiene en la entidad.</t>
-  </si>
-  <si>
-    <t>Vigilancia Epidemiológica</t>
-  </si>
-  <si>
-    <t>Autoridades sanitarias acordaron reforzar las medidas de higiene en Hidalgo debido a que el 94.8% de los casos de enfermedades diarreicas en 2026 se relacionaron con alimentos contaminados.</t>
-  </si>
-  <si>
-    <t>Llevan vacunas antirrábicas a cinco colonias de Pachuca</t>
-  </si>
-  <si>
-    <t>Habitantes de distintos puntos de la capital hidalguense tendrán una opción cercana para proteger a sus animales de compañía contra la rabia. Del 21 al 25 de septiembre se instalarán módulos itinerantes, con atención a perros y gatos desde un mes de edad.</t>
-  </si>
-  <si>
-    <t>Vacunación Antirrábica</t>
-  </si>
-  <si>
-    <t>Del 21 al 25 de septiembre se instalarán módulos itinerantes de vacunación antirrábica para perros y gatos en cinco colonias de Pachuca.</t>
-  </si>
-  <si>
-    <t>SSH, CAIVM</t>
-  </si>
-  <si>
-    <t>Temen menor pasaje con nuevas tarifas</t>
-  </si>
-  <si>
-    <t>Choferes de taxi de la zona metropolitana de Pachuca temen que el próximo ajuste tarifario, anunciado por la Secretaría de Movilidad y Transporte de Hidalgo, reduzca temporalmente el número de pasajeros y beneficie principalmente a los concesionarios, quienes podrían aumentar las cuotas; de acuerdo con testimonios, actualmente pagan entre 400 y 500 pesos diarios por el uso de las unidades y una cantidad similar en gasolina.</t>
-  </si>
-  <si>
-    <t>Tarifario de taxis</t>
-  </si>
-  <si>
-    <t>Taxistas de Pachuca prevén una disminución de pasajeros ante el próximo ajuste tarifario anunciado por la Semoth y afirman que el beneficio será para los concesionarios.</t>
-  </si>
-  <si>
-    <t>Sube el precio de jitomate y cebolla</t>
-  </si>
-  <si>
-    <t>Estos dos productos registraron aumentos en locales fijos, pues el primero pasó de 16 a 30 pesos por kilo, el segundo alcanza los 40 pesos. Los comerciantes atribuyen el alza a las intensas lluvias que afectaron cultivos y redujeron el abasto.</t>
-  </si>
-  <si>
-    <t>Canasta básica</t>
-  </si>
-  <si>
-    <t>El precio del jitomate y la cebolla aumentó en Pachuca debido a las afectaciones por lluvias en cultivos y la disminución del abasto.</t>
-  </si>
-  <si>
-    <t>Alma Leticia Sánchez</t>
-  </si>
-  <si>
-    <t>Prevén taxistas caída en el pasaje</t>
-  </si>
-  <si>
-    <t>El ajuste de tarifas para taxis anunciado por la Secretaría de Movilidad y Transporte de Hidalgo (Semoth) podría reducir el número de pasajeros y beneficiará principalmente a los concesionarios, indicaron choferes de la zona metropolitana de Pachuca, quienes tienen incrementos en las cuotas diarias por el uso de las unidades. Conductores refirieron pagar cuotas diarias de 400 a 500 pesos más combustible y señalaron los costos de refacciones y baches como afectaciones adicionales.</t>
-  </si>
-  <si>
     <t>Aumento Tarifa De Transporte</t>
   </si>
   <si>
-    <t>Choferes de taxi en Pachuca advierten que el nuevo ajuste tarifario incrementará las cuotas de los concesionarios y reducirá la afluencia de pasajeros.</t>
-  </si>
-  <si>
     <t>Blanca Soriano</t>
   </si>
   <si>
-    <t>Lyzbeth Robles Gutiérrez, Hugo Islas, Omar Cisneros, Felipe García</t>
-  </si>
-  <si>
-    <t>Reúne Hidalgo a guitarristas en festival</t>
-  </si>
-  <si>
-    <t>La guitarra clásica volverá a tomar distintos escenarios de Hidalgo con la edición 18 del Festival Nacional de Guitarra Ramón Noble, que del lunes 21 al sábado 26 de septiembre reunirá a intérpretes de Guadalajara, Ciudad de México, Monterrey, Texas y nuestra entidad. Durante seis días, el encuentro ofrecerá conciertos, clases magistrales, presentaciones editoriales y actividades académicas en municipios como Tlahuelilpan, Emiliano Zapata, Real del Monte, Mineral de la Reforma y Tepeapulco.</t>
-  </si>
-  <si>
     <t>Festival Cultural</t>
   </si>
   <si>
-    <t>La edición 18 del Festival Nacional de Guitarra Ramón Noble reunirá a intérpretes nacionales e internacionales en diversos municipios de Hidalgo del 21 al 26 de septiembre.</t>
-  </si>
-  <si>
-    <t>Ramón Noble Olivares</t>
-  </si>
-  <si>
-    <t>Ayate, en el uso agrícola y doméstico</t>
-  </si>
-  <si>
-    <t>El ayate de ixtle es un tejido elaborado de manera artesanal por manos de mujeres y hombres que extraen la fibra de maguey de las pencas de este agave en el Valle del Mezquital. El artesano Plácido Claudio destacó que además de herramienta agrícola y ganadera, el ayate se utilizaba tradicionalmente en los hogares como cuna para arrullar a los bebés mientras las madres realizaban labores domésticas.</t>
-  </si>
-  <si>
-    <t>San Salvador</t>
-  </si>
-  <si>
     <t>Apoyo a artesanos</t>
   </si>
   <si>
-    <t>Artesanos del Valle del Mezquital preservan la elaboración del ayate de ixtle, usado tradicionalmente como herramienta de trabajo y cuna en los hogares.</t>
-  </si>
-  <si>
-    <t>Omar Santiago</t>
-  </si>
-  <si>
-    <t>Plácido Claudio</t>
-  </si>
-  <si>
-    <t>Pobladores se reúnen a limpiar ribera de los ríos</t>
-  </si>
-  <si>
-    <t>Aproximadamente 500 pobladores de Tula participaron en una jornada simultánea de limpieza en las riberas de los ríos Rosas y Tula, recolectando basura y desyerbando áreas colindantes. La actividad fue organizada por Semarnat federal y Conagua, en coordinación con el área de Ecología de la alcaldía de Tula de Allende, con el fin de cuidar el medio ambiente y evitar focos de infección.</t>
-  </si>
-  <si>
-    <t>Saneamiento río Tula</t>
-  </si>
-  <si>
-    <t>Cerca de 500 habitantes de Tula participaron en una jornada comunitaria de limpieza y deshierbe en las riberas de los ríos Rosas y Tula.</t>
-  </si>
-  <si>
-    <t>Semarnat, Conagua, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Nayeli Pérez Jiménez, Ismael Gutiérrez</t>
-  </si>
-  <si>
-    <t>Ejecutivo destina 84 mil para limpieza de vidrios en edificios</t>
-  </si>
-  <si>
-    <t>El gobierno del estado destinará casi 500 mil pesos para el lavado de vidrios de las fachadas del palacio de gobierno y las nuevas oficinas de las secretarías de Bienestar e Inclusión Social y de Agricultura. El Corporativo y Asociados AKRAM S.A. de C.V. será el encargado de brindar el servicio por 484 mil 120.20 pesos por un periodo de tres meses. El servicio incluirá personal capacitado en trabajos de altura y equipo especializado.</t>
-  </si>
-  <si>
-    <t>La Oficialía Mayor de Hidalgo adjudicó un contrato por 484 mil pesos a la empresa AKRAM para la limpieza especializada de vidrios en las fachadas del Palacio de Gobierno y dependencias estatales.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Bienestar, Saderh</t>
-  </si>
-  <si>
-    <t>SSPH detiene a expolicía de Tula con armas y droga</t>
-  </si>
-  <si>
-    <t>Elementos de la Secretaría de Seguridad Pública de Hidalgo (SSPH) lograron la detención de Brigham C.B., expolicía municipal de Tula y señalado como presunto líder de un grupo generador de violencia en la región. El sujeto fue asegurado en la avenida Sur a bordo de una camioneta Dodge Ram portando un arma de fuego corta, dos cargadores abastecidos, 460 dosis de hierba con características de marihuana y 117 dosis de cristal, por lo que fue trasladado a Pachuca.</t>
-  </si>
-  <si>
-    <t>Detención</t>
-  </si>
-  <si>
-    <t>La SSPH aprehendió en Tula a Brigham C.B., expolicía municipal identificado como generador de violencia, asegurándole un arma de fuego y centenas de dosis de enervantes.</t>
-  </si>
-  <si>
     <t>Joselyn Sánchez</t>
   </si>
   <si>
     <t>SSPH</t>
   </si>
   <si>
-    <t>SSPH, PGJEH, Presidencia</t>
-  </si>
-  <si>
-    <t>Brigham C.B.</t>
-  </si>
-  <si>
-    <t>Destinan 8.5 mdp para dos planes de movilidad</t>
-  </si>
-  <si>
-    <t>El gobierno del estado destinó 8 millones 555 mil pesos para la elaboración del Plan Integral de Movilidad Urbana Sustentable (PIMUS) de los municipios de Huejutla e Ixmiquilpan. La empresa encargada de prestar el servicio es Modelística S.A. de C.V., la cual evaluará los patrones de movilidad, oferta de transporte, vías ciclistas y densidad poblacional de los últimos 20 años para diseñar rutas que optimicen los traslados internos.</t>
-  </si>
-  <si>
-    <t>Movilidad urbana</t>
-  </si>
-  <si>
-    <t>El Gobierno de Hidalgo invierte 8.5 millones de pesos en la elaboración de los Planes Integrales de Movilidad Urbana Sustentable para Huejutla e Ixmiquilpan.</t>
-  </si>
-  <si>
-    <t>Semot, Presidencia</t>
-  </si>
-  <si>
-    <t>Estudio busca preservar una especie endémica de agave</t>
-  </si>
-  <si>
-    <t>Ciencia. Investigación especializada busca preservar una especie endémica de agave en el estado de Hidalgo frente a amenazas de pérdida de hábitat.</t>
-  </si>
-  <si>
-    <t>Conservación Biodiversidad</t>
-  </si>
-  <si>
-    <t>Investigadores desarrollan un proyecto para la conservación y resguardo biológico de una variedad endémica de agave en territorio hidalguense.</t>
-  </si>
-  <si>
-    <t>Citnova, UAEH</t>
-  </si>
-  <si>
-    <t>Padecimientos gastrointestinales 90% por agua y alimentos: SSEH</t>
-  </si>
-  <si>
-    <t>Los alimentos contaminados están relacionados con 94.8% de los casos de Enfermedades Diarreicas Agudas reportadas por la Secretaría de Salud de Hidalgo.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo advierte que más del 90% de los padecimientos gastrointestinales responden a la ingesta de agua o alimentos contaminados.</t>
-  </si>
-  <si>
-    <t>SSH, Copriseh</t>
-  </si>
-  <si>
-    <t>Huejutla concentra 528 mdp en 84 obras</t>
-  </si>
-  <si>
-    <t>Huejutla concentró una inversión de 528 millones de pesos en 84 obras de infraestructura durante los primeros cuatro años de la administración estatal.</t>
-  </si>
-  <si>
-    <t>Obras De Infraestructura</t>
-  </si>
-  <si>
-    <t>El secretario de Contraloría, Álvaro Bardales, informó sobre la inversión de 528 mdp en obras de infraestructura vial y educativa para la Huasteca hidalguense.</t>
-  </si>
-  <si>
-    <t>Contraloría</t>
-  </si>
-  <si>
-    <t>Contraloría, Gobernador</t>
-  </si>
-  <si>
-    <t>Álvaro Bardales, Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Impulsa ITESHU conservación del agave con apoyo del Fondo Hidalgo</t>
-  </si>
-  <si>
-    <t>El ITESHU encabeza un proyecto científico apoyado con 250 mil pesos por el Fondo Hidalgo para la conservación y manejo sustentable del Agave salmiana en zonas semiáridas.</t>
-  </si>
-  <si>
-    <t>Huichapan</t>
-  </si>
-  <si>
-    <t>Investigadores del Tecnológico de Huichapan desarrollan un proyecto sustentable para el rescate y reproducción del Agave salmiana con un estímulo de 250 mil pesos otorgado por el Fondo Hidalgo.</t>
-  </si>
-  <si>
     <t>Marco Cerón</t>
   </si>
   <si>
-    <t>SEPH, ITESHU, Planeación</t>
-  </si>
-  <si>
-    <t>Atentan a mano armada contra hombre en el centro de la capital hidalguense</t>
-  </si>
-  <si>
-    <t>Un hombre perdió la vida tras recibir disparos con arma de fuego en la calle Ramos Arizpe, cerca de El Parián en el centro de Pachuca. Peritos de la PGJEH recabaron nueve casquillos e iniciaron investigaciones.</t>
-  </si>
-  <si>
-    <t>Ataque Armado</t>
-  </si>
-  <si>
-    <t>Un hombre fue asesinado a balazos en la zona centro de Pachuca durante la madrugada. La SSPH desplegó un operativo que permitió la detención de tres presuntos responsables.</t>
-  </si>
-  <si>
-    <t>SSPH, PGJEH</t>
-  </si>
-  <si>
-    <t>Detienen a generador de violencia en la zona de Tula de Allende</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) dio a conocer la detención de un hombre armado, en posesión de presunta droga, cuando viajaba a bordo de una camioneta Dodge RAM color azul en el municipio de Tula. De acuerdo con la información difundida por la dependencia, el hombre era líder de un grupo generador de violencia en la región Tula. Durante la revisión le fueron aseguradas un arma de fuego larga, dos cargadores abastecidos, un arma corta, un chaleco táctico, además de 560 dosis de hierba seca con características de la marihuana y 117 dosis de sustancia granulada presuntamente cristal. Por tal motivo, la persona detenida y los objetos fueron puestos a disposición del Ministerio Público.</t>
-  </si>
-  <si>
-    <t>La SSPH detuvo en Tula a un presunto líder generador de violencia armado con un chaleco táctico, dos cargadores y más de 670 dosis de estupefacientes (marihuana y cristal).</t>
-  </si>
-  <si>
-    <t>SSPH, MP</t>
-  </si>
-  <si>
-    <t>Incidencia delictiva se redujo 7%: SESNSP</t>
-  </si>
-  <si>
-    <t>La Procuraduría General de Justicia del Estado de Hidalgo (PGJEH) inició 4 mil 287 carpetas de investigación por diversos delitos cometidos durante agosto, de acuerdo con el Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP). En comparación con julio, la incidencia delictiva disminuyó 7%, con mayor acumulación en delitos patrimoniales (1,567 denuncias).</t>
-  </si>
-  <si>
-    <t>La incidencia delictiva en Hidalgo disminuyó un 7% durante el mes de agosto con 4,287 carpetas de investigación iniciadas por la PGJEH, según datos del SESNSP.</t>
-  </si>
-  <si>
     <t>PGJEH, Presidencia</t>
   </si>
   <si>
-    <t>Concentran 2 municipios la mitad de homicidios</t>
-  </si>
-  <si>
-    <t>Tezontepec de Aldama y Tizayuca fueron los municipios con mayor cantidad de carpetas de investigación por homicidios dolosos durante agosto, acumulando el 50 por ciento de las 12 denuncias iniciadas en la entidad por la PGJEH. Ambas demarcaciones registraron tres homicidios dolosos cada una.</t>
-  </si>
-  <si>
-    <t>Tezontepec de Aldama y Tizayuca concentraron la mitad de los homicidios dolosos registrados en Hidalgo durante el mes de agosto, con tres carpetas de investigación en cada municipio.</t>
-  </si>
-  <si>
-    <t>Raymundo S. G.</t>
-  </si>
-  <si>
-    <t>La crisis del suicidio persiste en Tulancingo en los últimos meses</t>
-  </si>
-  <si>
-    <t>Tulancingo suma al menos seis casos de presuntos suicidios entre enero y septiembre de 2026, incluyendo dos incidentes registrados dentro del Cereso municipal. En respuesta, el Centro de Cultura Emocional de la Familia (CCEF) del DIF Tulancingo puso en marcha talleres de prevención y primeros auxilios psicológicos dirigidos a la población penitenciaria.</t>
-  </si>
-  <si>
-    <t>Suicidio</t>
-  </si>
-  <si>
-    <t>El municipio de Tulancingo contabiliza al menos seis suicidios en 2026, lo que motivó al DIF local a implementar talleres de contención y apoyo psicológico dentro del Cereso y en planteles educativos.</t>
-  </si>
-  <si>
-    <t>María Antonieta Islas</t>
-  </si>
-  <si>
-    <t>DIFH, SSH</t>
-  </si>
-  <si>
-    <t>Teresa Magdiel Bazan Pérez</t>
-  </si>
-  <si>
-    <t>Lolotla, municipio serrano con tres casos mediáticos en los últimos dos años</t>
-  </si>
-  <si>
-    <t>En Lolotla se han registrado tres eventos de seguridad de trascendencia nacional durante la administración de María Díaz Bustos: la desaparición del niño Dorian Kaleb Chiu Arroyo en abril de 2025, el homicidio del sacerdote Román de la Cruz Hernández en la carretera Tolago-Tetlapaya y un caso de maltrato animal.</t>
-  </si>
-  <si>
-    <t>El municipio de Lolotla ha sido escenario de tres hechos de alto impacto social en los últimos dos años, incluyendo la desaparición de un menor y el homicidio de un párroco.</t>
-  </si>
-  <si>
-    <t>Martha Sáenz</t>
-  </si>
-  <si>
-    <t>María Díaz Bustos, Dorian Kaleb Chiu Arroyo, Román de la Cruz Hernández</t>
-  </si>
-  <si>
-    <t>Auto particular impacta colectiva en Pachuca; reportan 6 heridos leves</t>
-  </si>
-  <si>
-    <t>Con relación al siniestro de tránsito ocurrido sobre la vialidad del bulevar el Minero a la altura de una gasolinera en Pachuca, la Semot a través del STCH informa que intervino en el percance y se auxilió a seis heridos leves.</t>
-  </si>
-  <si>
     <t>Accidente de Transporte Público</t>
   </si>
   <si>
-    <t>Un auto particular impactó por alcance a una colectiva de transporte público en el bulevar El Minero en Pachuca, dejando seis personas con lesiones leves que fueron auxiliadas por Semot y Cruz Roja.</t>
-  </si>
-  <si>
-    <t>Semot, STCH, Cruz Roja</t>
-  </si>
-  <si>
-    <t>Bienestar atiende a migrantes y sus familias en Epazoyucan</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social (Sebiso), a través de la Dirección de Atención al Migrante, llevará a Epazoyucan una jornada de atención dirigida a migrantes, familias y repatriados el martes 22 de septiembre.</t>
-  </si>
-  <si>
-    <t>Epazoyucan</t>
-  </si>
-  <si>
-    <t>Atención A Migrantes</t>
-  </si>
-  <si>
-    <t>Sebiso instalará un módulo itinerante en el Auditorio Municipal de Epazoyucan para brindar orientación gratuita sobre visas, pasaportes, doble nacionalidad y el programa Raíces de Hidalgo.</t>
-  </si>
-  <si>
     <t>Bienestar</t>
   </si>
   <si>
-    <t>Detienen en Tulancingo a dos mujeres acusadas de secuestro exprés</t>
-  </si>
-  <si>
-    <t>Policías de Tulancingo intervinieron a dos mujeres por falta administrativa y, al cruzar datos con la PGJEH, descubrieron que contaban con orden de aprehensión por secuestro exprés agravado.</t>
-  </si>
-  <si>
-    <t>Secuestro</t>
-  </si>
-  <si>
-    <t>Personal de la PGJEH cumplimentó una mandamiento judicial contra dos mujeres en Tulancingo tras ser identificadas por mandamientos judiciales pendientes por secuestro exprés.</t>
-  </si>
-  <si>
-    <t>Un ataque a balazos provocó la detención de tres involucrados</t>
-  </si>
-  <si>
-    <t>Sujetos armados atacaron a balazos al conductor de un vehículo en la calle Arizpe del Centro de Pachuca; elementos de seguridad desplegaron operativo y lograron la captura de tres involucrados.</t>
-  </si>
-  <si>
-    <t>Ataque con arma de fuego en las inmediaciones de El Parián en Pachuca movilizó a policías municipales y estatales, logrando la aprehensión de tres presuntos agresores.</t>
-  </si>
-  <si>
-    <t>SSPH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Detienen a líder criminal con armamento y droga en Tula</t>
-  </si>
-  <si>
-    <t>Agentes de la SSPH detuvieron en Tula a un generador de violencia a bordo de una camioneta Dodge RAM, decomisándole un arma larga, arma corta, chaleco táctico y más de 670 dosis de drogas.</t>
-  </si>
-  <si>
-    <t>Operativo de la Secretaría de Seguridad Pública de Hidalgo culminó con la captura de un presunto líder delincuencial operando en la región de Tula de Allende.</t>
-  </si>
-  <si>
-    <t>Hongos en el café</t>
-  </si>
-  <si>
-    <t>Durante un curso de micología en el CITNOVA, la empresa HC Wellness presentó desarrollos alimentarios para incorporar extractos de hongos funcionales con bioactivos y antioxidantes al café.</t>
-  </si>
-  <si>
-    <t>Reportaje</t>
-  </si>
-  <si>
-    <t>Divulgación científica</t>
-  </si>
-  <si>
-    <t>Investigadores y especialistas exponen en el CITNOVA la aplicación de propiedades nutricionales de hongos funcionales en bebidas de consumo cotidiano.</t>
-  </si>
-  <si>
-    <t>Planeación, CITNOVA</t>
-  </si>
-  <si>
-    <t>Obras del Tren AIFA-Pachuca cortan agua a colonias del sur</t>
-  </si>
-  <si>
-    <t>Cerca de 30 vecinos de distintos fraccionamientos de la zona sur de Mineral de la Reforma (Tulipanes, La Colonia, Cipreses, Magisterio y Encinos) bloquearon este domingo la avenida de los Árboles, a la altura de la caseta de Tulipanes, para exigir agua potable luego de que el tandeo previsto no se cumpliera. Los habitantes señalaron que el desabasto se ha prolongado hasta por 15 días y atribuyeron parte de las afectaciones a los trabajos del Tren AIFA-Pachuca por interferencias en la infraestructura de Caasim.</t>
-  </si>
-  <si>
-    <t>Vecinos del sur de Mineral de la Reforma bloquearon la avenida de los Árboles tras cumplir 15 días sin suministro de agua potable, señalando que las obras del Tren AIFA-Pachuca dañaron las redes de distribución de Caasim.</t>
-  </si>
-  <si>
-    <t>Sipdus, Presidencia</t>
-  </si>
-  <si>
-    <t>Durante 2026 van 179 contagios de Covid en Hidalgo</t>
-  </si>
-  <si>
-    <t>Hidalgo acumula 179 casos de Covid-19 durante 2026 y se ubica en el tercer lugar nacional por contagios, de acuerdo con el reporte de la Dirección General de Epidemiología. Asimismo, la entidad ocupa el primer lugar nacional por defunciones asociadas al coronavirus con 15 fallecimientos. La secretaria de Salud de Hidalgo, Vanesa Escalante Arroyo, señaló que los padecimientos crónico-degenerativos sin control y la falta de actualización de esquemas de vacunación incrementan los riesgos.</t>
-  </si>
-  <si>
-    <t>Covid 19</t>
-  </si>
-  <si>
-    <t>Con 179 contagios y 15 defunciones en 2026, Hidalgo se ubica en el primer lugar nacional en mortalidad por Covid-19. La Secretaría de Salud de Hidalgo llamó a mantener al día los esquemas de vacunación.</t>
-  </si>
-  <si>
-    <t>Vanesa Escalante Arroyo</t>
-  </si>
-  <si>
-    <t>Avanza transferencia del Nuevo Hospital General</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo prevé concretar la transferencia del Nuevo Hospital General de Pachuca al IMSS-Bienestar, informó su titular Vanesa Escalante Arroyo. Autoridades federales realizaron visitas e integran documentación técnica para que el organismo asuma la operación del inmueble que permanece sin funcionar.</t>
-  </si>
-  <si>
-    <t>IMSS Bienestar</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo avanza en las gestiones para transferir el Nuevo Hospital General de Pachuca al esquema IMSS-Bienestar para iniciar su equipamiento y puesta en operación.</t>
-  </si>
-  <si>
-    <t>La escuela primaria Aquiles Serdán de Tulancingo presenta graves daños estructurales, por lo que será demolida y reconstruida totalmente durante el ciclo escolar 2026-2027, según informó el titular de la SEPH, Natividad Castrejón. Se analizan alternativas para reubicar temporalmente a los alumnos en planteles cercanos o modalidades de educación a distancia.</t>
-  </si>
-  <si>
-    <t>Reconstrucción de escuela</t>
-  </si>
-  <si>
-    <t>Por fallas estructurales, la Secretaría de Educación Pública de Hidalgo construirá un nuevo plantel para la primaria Aquiles Serdán en Tulancingo, evaluando sedes temporales para atender al alumnado.</t>
-  </si>
-  <si>
     <t>Impresiones locales</t>
+  </si>
+  <si>
+    <t>Bloquean para exigir obras... serán escuchados</t>
+  </si>
+  <si>
+    <t>Habitantes de comunidades de Zempoala bloquearon ayer la carretera Pachuca-Ciudad Sahagún por varias horas, para exigir la rehabilitación, reconstrucción y nivelación de un puente y un retorno, además de la mejora de los accesos a Santa Cruz, La Trinidad y Buenavista. Al lugar acudió el secretario de Gobierno, Guillermo Olivares, quien se comprometió a una mesa de diálogo y con ello los manifestantes liberaron la vía.</t>
+  </si>
+  <si>
+    <t>Zempoala</t>
+  </si>
+  <si>
+    <t>Bloqueo Carretero</t>
+  </si>
+  <si>
+    <t>Habitantes de Zempoala bloquearon la carretera Pachuca-Ciudad Sahagún exigiendo obras viales y retiraron el cerco tras la mediación del secretario de Gobierno.</t>
+  </si>
+  <si>
+    <t>Maximiliano Pérez</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares</t>
+  </si>
+  <si>
+    <t>Subirán 20% tarifas del servicio de taxi</t>
+  </si>
+  <si>
+    <t>Tras cuatro años, las tarifas de taxis en Hidalgo aumentarán 20%, quedando en 45 pesos la mínima y cuatro pesos el kilómetro adicional, informó la titular de la Secretaría de Movilidad y Transporte, Lyzbeth Robles. Agregó que Pachuca y Mineral de la Reforma serán los primeros municipios en aplicar el ajuste. La tarifa nocturna será de 54 pesos.</t>
+  </si>
+  <si>
+    <t>La Semot anunció un aumento del 20% en las tarifas de taxi en Hidalgo, fijando la tarifa mínima en 45 pesos.</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles</t>
+  </si>
+  <si>
+    <t>Incrementan 20.4% fraudes en la entidad</t>
+  </si>
+  <si>
+    <t>El delito de fraude acumuló mil 648 carpetas de investigación en Hidalgo durante los primeros siete meses del año 2026, 279 más que en el mismo periodo de 2025, lo que representa un crecimiento de 20.4%, según registros estatales del SESNSP.</t>
+  </si>
+  <si>
+    <t>Fraude</t>
+  </si>
+  <si>
+    <t>Entre enero y julio de 2026 se registraron 1,648 carpetas de investigación por fraude en Hidalgo, un aumento del 20.4% respecto al año anterior.</t>
+  </si>
+  <si>
+    <t>Alumnos del ITP se suman a obras federales</t>
+  </si>
+  <si>
+    <t>Estudiantes del Instituto Tecnológico de Pachuca (ITP) se incorporan para realizar su residencia profesional en obras federales estratégicas como el tren México-Querétaro y AIFA-Pachuca, informó el director Miguel Ángel Lee Rodríguez durante la ceremonia por el 55 aniversario de la institución.</t>
+  </si>
+  <si>
+    <t>Proyectos Ferroviarios</t>
+  </si>
+  <si>
+    <t>Estudiantes del Instituto Tecnológico de Pachuca participan en proyectos de infraestructura federal como el Tren México-Querétaro y el Tren AIFA-Pachuca.</t>
+  </si>
+  <si>
+    <t>Sonia Nochebuena</t>
+  </si>
+  <si>
+    <t>SEPH, Congreso, UAEH, Presidencia</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Lee, Rebeca Aladro, Octavio Castillo, Andrés Velázquez, Jorge Reyes</t>
+  </si>
+  <si>
+    <t>Liberan la carretera a Sahagún tras acuerdos</t>
+  </si>
+  <si>
+    <t>Tras varias horas de bloqueo, habitantes de comunidades del municipio de Zempoala liberaron la carretera Pachuca-Ciudad Sahagún, luego de que se acordara una mesa de vecinos para ser atendida por representantes del Gobierno del Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Liberación de carretera</t>
+  </si>
+  <si>
+    <t>Habitantes de Zempoala levantaron el bloqueo sobre la carretera Pachuca-Sahagún tras entablar acuerdos con funcionarios del Gobierno Estatal.</t>
+  </si>
+  <si>
+    <t>Segobh, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares, Francisco Sinuhé Ramírez</t>
+  </si>
+  <si>
+    <t>Protestan por falta de agua</t>
+  </si>
+  <si>
+    <t>Vecinos de Real del Monte se manifestaron ayer por la mañana en las instalaciones de la Comisión de Agua, Alcantarillado y Sistemas Intermunicipales (Caasim) en el centro del Pueblo Mágico para exigir una solución a la falta de agua potable.</t>
+  </si>
+  <si>
+    <t>Mineral del Monte</t>
+  </si>
+  <si>
+    <t>Pobladores de Real del Monte protestaron ante la Caasim exigiendo el restablecimiento del servicio de agua potable en su municipio.</t>
+  </si>
+  <si>
+    <t>Caasim, Sipdus, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Edmundo Tejeda</t>
+  </si>
+  <si>
+    <t>Fraude aumenta 20.4% en Hidalgo</t>
+  </si>
+  <si>
+    <t>El delito de fraude registró un incremento durante los primeros siete meses de 2026 en Hidalgo al acumular mil 648 carpetas de investigación, cifra superior a las mil 369 registradas durante el mismo periodo de 2025 de acuerdo con el SESNSP.</t>
+  </si>
+  <si>
+    <t>En Hidalgo las carpetas de investigación por fraude aumentaron 20.4% entre enero y julio de 2026, concentrando la mayor cantidad de denuncias en marzo y abril.</t>
+  </si>
+  <si>
+    <t>Regularán el uso de celulares en escuelas</t>
+  </si>
+  <si>
+    <t>El uso de celulares en las instituciones educativas de Hidalgo será regulado para mejorar el aprendizaje de los estudiantes y evitar distracciones, tal como se prevé a nivel federal, confirmó la SEPH.</t>
+  </si>
+  <si>
+    <t>Convivencia Escolar</t>
+  </si>
+  <si>
+    <t>La SEPH regulará el uso de teléfonos celulares en planteles de educación básica en coincidencia con los lineamientos federales.</t>
+  </si>
+  <si>
+    <t>SEPH, Presidencia</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón, Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Tutores cierran Cobaeh por falta de electricidad</t>
+  </si>
+  <si>
+    <t>Padres de familia de la comunidad de Tamoyón I, Huejutla, tomaron las instalaciones del plantel Cobaeh Cemsad debido a que un transformador se quemó y dejó sin energía eléctrica a 131 alumnos.</t>
+  </si>
+  <si>
+    <t>Infraestructura escolar</t>
+  </si>
+  <si>
+    <t>Padres de familia cerraron el plantel Cobaeh Cemsad en Huejutla tras la falla de un transformador que dejó sin luz a la escuela.</t>
+  </si>
+  <si>
+    <t>Rubén Juárez</t>
+  </si>
+  <si>
+    <t>SEPH, Cobaeh</t>
+  </si>
+  <si>
+    <t>Iván Lara Tovar, Jesús Flores Ramírez</t>
+  </si>
+  <si>
+    <t>Piden salida del director del ITH</t>
+  </si>
+  <si>
+    <t>Docentes y administrativos del Instituto Tecnológico de Huejutla (ITH) exigen la destitución inmediata del director Evaristo Rogaciano López Hernández por incumplir acuerdos laborales.</t>
+  </si>
+  <si>
+    <t>Exigen destitución de funcionario</t>
+  </si>
+  <si>
+    <t>Personal docente y administrativo del Instituto Tecnológico de Huejutla protestó para demandar la destitución del director del plantel.</t>
+  </si>
+  <si>
+    <t>Evaristo Rogaciano López, Silvestre Téllez Argüelles</t>
+  </si>
+  <si>
+    <t>Prohíben celulares en primaria y secundaria</t>
+  </si>
+  <si>
+    <t>El uso de celulares y tabletas quedará prohibido en las escuelas primarias y secundarias de todo el país a partir del 3 de noviembre, como parte de un acuerdo unánime de las autoridades educativas de las 32 entidades. Los estudiantes pueden llevar sus dispositivos pero deberán mantenerlos guardados.</t>
+  </si>
+  <si>
+    <t>Regulación de dispositivos digitales</t>
+  </si>
+  <si>
+    <t>Autoridades educativas acordaron restringir el uso de celulares y tabletas en escuelas de educación básica a partir del 3 de noviembre.</t>
+  </si>
+  <si>
+    <t>Mauricio Bautista</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum, Natividad Castrejón, Mario Delgado</t>
+  </si>
+  <si>
+    <t>Autorizan aumento de 20% a la tarifa de taxis</t>
+  </si>
+  <si>
+    <t>Esta semana entrará en vigor el alza al banderazo de salida del transporte colectivo individual, el cual tendrá un incremento del 20%, pasando la tarifa de 38 a 45 pesos en Pachuca y Mineral de la Reforma.</t>
+  </si>
+  <si>
+    <t>La Semot autorizó un incremento del 20% en la tarifa de taxis colectivos e individuales, fijando el banderazo mínimo en 45 pesos de forma gradual.</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles Gutiérrez</t>
+  </si>
+  <si>
+    <t>IHE fortalece Educación Inicial con Cada momento cuenta</t>
+  </si>
+  <si>
+    <t>El Instituto Hidalguense de Educación realizó el encuentro Cada momento cuenta para intercambiar experiencias y fortalecer los servicios de Educación Inicial en el desarrollo de las primeras infancias.</t>
+  </si>
+  <si>
+    <t>Boletín</t>
+  </si>
+  <si>
+    <t>Educación inicial</t>
+  </si>
+  <si>
+    <t>El IHE organizó un encuentro de trabajo con personal educativo especializado para intercambiar experiencias y fortalecer la atención integral de las primeras infancias.</t>
+  </si>
+  <si>
+    <t>Comunicado gubernamental</t>
+  </si>
+  <si>
+    <t>SEPH, IHE</t>
+  </si>
+  <si>
+    <t>Nancy León Vite, Leobardo Cano Albarrán, Herlinda Amador Lara</t>
+  </si>
+  <si>
+    <t>Garantiza Semoth transporte hasta las 3 de la mañana durante la feria</t>
+  </si>
+  <si>
+    <t>La Semoth implementará un plan operativo en el transporte metropolitano Tuzobús y colectivo durante la Feria de Pachuca, extendiendo el servicio especial nocturno hasta las 3:00 am.</t>
+  </si>
+  <si>
+    <t>Feria Pachuca</t>
+  </si>
+  <si>
+    <t>La Semot implementará un operativo especial en el Tuzobús y rutas colectivas para ampliar el servicio de transporte hasta las 3:00 horas durante la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>Sancionan a 35 por ofrecer taxi por aplicación</t>
+  </si>
+  <si>
+    <t>Debido a que el servicio de taxi por aplicación no está regulado en Hidalgo, el STCH ha infraccionado a 35 personas por ofrecer dicho servicio de manera irregular.</t>
+  </si>
+  <si>
+    <t>Apps de transporte</t>
+  </si>
+  <si>
+    <t>El STCH sancionó a 35 conductores por prestar servicio de taxi por aplicación no regulado en Hidalgo durante operativos realizados de mayo a septiembre.</t>
+  </si>
+  <si>
+    <t>Semot, STCH</t>
+  </si>
+  <si>
+    <t>Operativo de seguridad deja tres detenidos tras balacera</t>
+  </si>
+  <si>
+    <t>Elementos de seguridad detuvieron a tres personas por su probable participación en una riña y detonación de arma de fuego en un bar de Pachuca; además reportan aseguramiento de drogas e hidrocarburo.</t>
+  </si>
+  <si>
+    <t>Operativo de Seguridad</t>
+  </si>
+  <si>
+    <t>Elementos de seguridad detuvieron a tres personas implicadas en una balacera en un bar de Pachuca, además de asegurar hidrocarburo robado y localizar a 14 personas en la entidad.</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH, Gabinete de Seguridad</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Vecinos bloquean la Pachuca-Sahagún durante cinco horas</t>
+  </si>
+  <si>
+    <t>La carretera Pachuca-Ciudad Sahagún fue liberada luego de más de cinco horas de bloqueo por parte de habitantes de Zempoala, quienes solicitaron atención a la infraestructura vial.</t>
+  </si>
+  <si>
+    <t>Habitantes de Zempoala bloquearon durante cinco horas la carretera Pachuca-Sahagún para exigir obras viales, retirándose tras acordar mesas de trabajo con Segobh.</t>
+  </si>
+  <si>
+    <t>América Castillo</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna</t>
+  </si>
+  <si>
+    <t>Negocian liberación de tres ejidos para Tren México-Querétaro</t>
+  </si>
+  <si>
+    <t>Gobernación y diversas dependencias trabajan en las negociaciones necesarias para liberar el derecho de vía por donde pasará el Tren México-Querétaro en tres ejidos de la región de Tula.</t>
+  </si>
+  <si>
+    <t>Tren México Querétaro</t>
+  </si>
+  <si>
+    <t>Autoridades federales y estatales avanzan en las negociaciones para liberar tres tramos ejidales pendientes en la región de Tula para el proyecto del Tren México-Querétaro.</t>
+  </si>
+  <si>
+    <t>Gobierno</t>
+  </si>
+  <si>
+    <t>SICT, RAN, Segobh</t>
+  </si>
+  <si>
+    <t>Gasury Mota Licona</t>
+  </si>
+  <si>
+    <t>Familiares buscan reclasificar homicidio tras atropellamiento</t>
+  </si>
+  <si>
+    <t>Familiares de Karla y Estrella, estudiantes de la UTSH, buscan que el delito imputado al automovilista ebrio sea reclasificado a homicidio doloso eventual y solicitan 25 mdp como reparación del daño moral.</t>
+  </si>
+  <si>
+    <t>Atropellamiento estudiante</t>
+  </si>
+  <si>
+    <t>Familiares de las estudiantes arrolladas en la UTSH buscan que el delito imputado al conductor ebrio sea reclasificado a homicidio doloso eventual con reparación del daño moral.</t>
+  </si>
+  <si>
+    <t>PGJEH, SEPH</t>
+  </si>
+  <si>
+    <t>David Ramírez</t>
+  </si>
+  <si>
+    <t>Aunque distrae, uso de celular en la escuela no explica rezago</t>
+  </si>
+  <si>
+    <t>La evaluación PISA 2025 confirma que 37% de los estudiantes mexicanos reporta distracciones frecuentes por el uso de celulares en las aulas, aunque en México no se encontró una diferencia estadísticamente significativa en el rendimiento entre alumnos expuestos a distracciones digitales y quienes no las reportaron. En Hidalgo, el secretario de Educación Pública Natividad Castrejón descartó batallas legales y confirmó que se establecerán acuerdos con padres de familia para regular los dispositivos en las escuelas.</t>
+  </si>
+  <si>
+    <t>La prueba PISA 2025 reveló que el 37% de estudiantes mexicanos se distrae con el celular en clases, mientras que en Hidalgo la SEPH descartó amparos y acordará reglas con padres de familia.</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Puértolas</t>
+  </si>
+  <si>
+    <t>Aumenta 20% la tarifa de taxi; Pachuca va primero</t>
+  </si>
+  <si>
+    <t>Derivado de denuncias por cobros excesivos, la Secretaría de Movilidad y Transporte (Semot), encabezada por Lyzbeth Robles Gutiérrez, anunció un incremento del 20% en las tarifas de taxi en Hidalgo, fijando el banderazo inicial en 45 pesos por los primeros 4 kilómetros en Pachuca y Mineral de la Reforma, y 4 pesos por kilómetro adicional.</t>
+  </si>
+  <si>
+    <t>La Semot anunció un incremento del 20% en las tarifas de taxi en Hidalgo, estableciendo un banderazo inicial de 45 pesos en la zona metropolitana de Pachuca.</t>
+  </si>
+  <si>
+    <t>Teodoro Santos</t>
+  </si>
+  <si>
+    <t>Por 7 particulares, últimos choques al transporte público</t>
+  </si>
+  <si>
+    <t>Siete accidentes viales involucrando unidades del transporte público se registraron entre el 1 y el 21 de septiembre en Pachuca y la zona metropolitana, dejando 16 personas lesionadas y un fallecimiento. La Semot atribuyó los percances a maniobras imprudentes de automovilistas particulares.</t>
+  </si>
+  <si>
+    <t>Siete accidentes viales con unidades de transporte público en Pachuca dejaron 16 lesionados y un fallecido entre el 1 y el 21 de septiembre, atribuidos a imprudencias de particulares.</t>
+  </si>
+  <si>
+    <t>Semot, SSPH</t>
+  </si>
+  <si>
+    <t>Garantizan unidades colectivas durante la feria</t>
+  </si>
+  <si>
+    <t>Ante el inicio de la Feria de San Francisco Pachuca 2026, la Semot implementará operativos especiales de transporte público, extendiendo el horario de la Ruta Troncal del Tuzobús hasta las 3:00 am y reforzando la inspección de colectivas y taxis para garantizar tarifas autorizadas.</t>
+  </si>
+  <si>
+    <t>La Semot garantizó servicio especial de transporte colectivo y Tuzobús hasta las 3:00 am durante la Feria de San Francisco Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>Zimapán vive fiesta de música y tradiciones</t>
+  </si>
+  <si>
+    <t>En el municipio de Zimapán se llevó a cabo la Caravana Cultural como parte de las festividades patrias 2026, contando con muestras artísticas, bailes tradicionales y el respaldo de la Secretaría de Cultura de Hidalgo y el alcalde Hermilo Trejo.</t>
+  </si>
+  <si>
+    <t>Zimapán</t>
+  </si>
+  <si>
+    <t>Zimapán celebró su Caravana Cultural 2026 con presentaciones artísticas y música tradicional en el marco de las festividades patrias.</t>
+  </si>
+  <si>
+    <t>Cultura, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Hermilo Trejo</t>
+  </si>
+  <si>
+    <t>El lirio acuático y el deterioro de los lagos...</t>
+  </si>
+  <si>
+    <t>Especialistas, científicos y estudiantes abordarán la problemática del lirio acuático y la degradación de humedales en un congreso ambiental, mientras que autoridades destinaron más de 6 millones de pesos en apoyos para productores agrícolas en Zacualtipán.</t>
+  </si>
+  <si>
+    <t>Zacualtipán</t>
+  </si>
+  <si>
+    <t>Lirio Acuático</t>
+  </si>
+  <si>
+    <t>Especialistas debatirán sobre el impacto del lirio acuático en humedales, en tanto que se entregaron 6 millones de pesos en apoyos agrícolas en Zacualtipán.</t>
+  </si>
+  <si>
+    <t>Saderh</t>
+  </si>
+  <si>
+    <t>Saderh, Semarnath</t>
+  </si>
+  <si>
+    <t>CELULARES EN ESCUELAS, SÓLO PARA TRABAJOS Y EMERGENCIAS</t>
+  </si>
+  <si>
+    <t>Hidalgo se suma al acuerdo del Consejo Nacional de Autoridades Educativas (Conaedu) que establece la restricción del uso de celulares en escuelas de nivel básico, los cuales no podrán ser utilizados dentro del plantel, a menos que tengan una actividad planeada o una emergencia, informó el titular de la SEPH, Natividad Castrejón Valdez.</t>
+  </si>
+  <si>
+    <t>Hidalgo se sumó al acuerdo nacional para restringir el uso de teléfonos celulares en escuelas de educación básica a partir del 3 de noviembre, permitiendo su uso solo en emergencias o actividades planeadas.</t>
+  </si>
+  <si>
+    <t>Lourdes Naranjo</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Separan de su cargo a maestra de secundaria por acoso laboral</t>
+  </si>
+  <si>
+    <t>Tras la pasada manifestación de una docente afuera de la Secundaria Técnica 1 de Pachuca, autoridades educativas informaron que la Secretaría de Contraloría de Hidalgo determinó separarla de sus funciones en esa escuela por acoso laboral tras concluir una investigación interna.</t>
+  </si>
+  <si>
+    <t>Acoso Laboral</t>
+  </si>
+  <si>
+    <t>La Secretaría de Contraloría determinó separar de sus funciones a una maestra de matemáticas de la Secundaria Técnica 1 de Pachuca por incurrir en acoso laboral.</t>
+  </si>
+  <si>
+    <t>SEPH, Contraloría</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Elena C. P.</t>
+  </si>
+  <si>
+    <t>Bloquean por seis horas la Pachuca-Cd. Sahagún</t>
+  </si>
+  <si>
+    <t>Pobladores de Zempoala lograron labores de rehabilitación en caminos y un puente vehicular por parte de los tres órdenes de gobierno, luego de bloquear durante seis horas la carretera Pachuca-Ciudad Sahagún a la altura de La Trinidad para exigir respuesta a sus demandas de infraestructura y agua.</t>
+  </si>
+  <si>
+    <t>Habitantes de Zempoala bloquearon durante seis horas la carretera Pachuca-Sahagún exigiendo obras viales y desabasto de agua; retiraron la protesta tras acordar mesas de trabajo con Segobh.</t>
+  </si>
+  <si>
+    <t>Víctor Valera</t>
+  </si>
+  <si>
+    <t>Segobh, Ayuntamiento, Defensa</t>
+  </si>
+  <si>
+    <t>Familia de joven que murió atropellada pide 25 mdp por daño moral</t>
+  </si>
+  <si>
+    <t>Los familiares y la asesoría jurídica de Karla, la universitaria originaria de Tianguistengo que murió tras un accidente de tránsito causado por un conductor ebrio en Zacualtipán, exigen 25 millones de pesos por concepto de daño moral dentro del proceso penal.</t>
+  </si>
+  <si>
+    <t>Familiares de la estudiante Karla, fallecida tras ser arrollada por un conductor ebrio en Zacualtipán, solicitan una indemnización de 25 mdp por daño moral.</t>
+  </si>
+  <si>
+    <t>Lorena Rosas</t>
+  </si>
+  <si>
+    <t>Pablo Marcelo Coiffer Martínez</t>
+  </si>
+  <si>
+    <t>Habrá cuatro corridas de toros en la feria</t>
+  </si>
+  <si>
+    <t>Cuatro corridas de toros, 24 espectáculos en el Megadomo de las Estrellas y 18 conciertos en el Centro de Espectáculos se presentarán en la Feria San Francisco Pachuca 2026, del 24 de septiembre al 18 de octubre, según informó la Operadora de Eventos.</t>
+  </si>
+  <si>
+    <t>La Operadora de Eventos presentó el programa de la Feria San Francisco Pachuca 2026, destacando cuatro corridas de toros, palenque y teatro del pueblo.</t>
+  </si>
+  <si>
+    <t>Turismo, OEEH, Cultura</t>
+  </si>
+  <si>
+    <t>Marco Antonio Aranzábal Juárez</t>
+  </si>
+  <si>
+    <t>Remodelación de Hidarte tiene un avance de 60 por ciento</t>
+  </si>
+  <si>
+    <t>La remodelación de la tienda Hidarte Pachuca registra un avance de 60 por ciento y se prevé que reabra en enero de 2027, informó Ricardo Gómez Moreno, titular de Sebiso. Los trabajos representan una inversión de alrededor de 12 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Hidarte</t>
+  </si>
+  <si>
+    <t>La reconstrucción de la tienda artesanal Hidarte en Pachuca lleva 60% de avance y prevé su reapertura en enero de 2027 tras invertir 12 mdp.</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Aumentará la tarifa de taxis en la entidad</t>
+  </si>
+  <si>
+    <t>El costo del pasaje en taxis aumentará en los 84 municipios de Hidalgo. La tarifa inicial pasará de 38 a 45 pesos por los primeros cuatro kilómetros en Pachuca y Mineral de la Reforma; posteriormente será oficial el uso del taxímetro digital.</t>
+  </si>
+  <si>
+    <t>La Semot anunció el alza de la tarifa inicial de taxis a 45 pesos por los primeros 4 kilómetros en la zona metropolitana, aplicable en 5 fases en la entidad.</t>
+  </si>
+  <si>
+    <t>Usuarios cuestionan incremento; afectará su bolsillo, señalan</t>
+  </si>
+  <si>
+    <t>El aumento a la tarifa del servicio de taxi en Pachuca y Mineral de la Reforma generó opiniones negativas entre usuarios consultados por El Universal Hidalgo, quienes señalaron que el incremento perjudicará sus bolsillos y exigieron mejorar el servicio.</t>
+  </si>
+  <si>
+    <t>Usuarios de transporte en Pachuca rechazaron el aumento a la tarifa de taxi de 38 a 45 pesos, señalando abusos de los choferes y mala calidad del servicio.</t>
+  </si>
+  <si>
+    <t>Ricardo Calleja</t>
+  </si>
+  <si>
+    <t>María de los Ángeles Rivera, Cristina Benavides, Alfredo Hernández</t>
+  </si>
+  <si>
+    <t>Detuvieron a una pareja con 72 kilogramos de marihuana</t>
+  </si>
+  <si>
+    <t>Elementos de la Secretaría de Seguridad Pública de Hidalgo (SSPH) aseguraron 72 kilogramos de marihuana y 103 dosis de cristal tras la intervención de una camioneta en la localidad Tephé, municipio de Ixmiquilpan, deteniendo a un hombre y una mujer.</t>
+  </si>
+  <si>
+    <t>Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>La Policía Estatal de Hidalgo detuvo a una pareja en Ixmiquilpan en posesión de 72 kilos de marihuana y 103 dosis de cristal.</t>
+  </si>
+  <si>
+    <t>SSPH, C5i</t>
+  </si>
+  <si>
+    <t>R. H. G., M. G. Q. M.</t>
+  </si>
+  <si>
+    <t>Protestan por falta de electricidad en el Cobaeh de Tamoyón I</t>
+  </si>
+  <si>
+    <t>Padres de familia y estudiantes del Cemsad Tamoyón I en Huautla tomaron las instalaciones del plantel como medida de protesta ante la constante falta de energía eléctrica que padecen desde hace cuatro meses.</t>
+  </si>
+  <si>
+    <t>Huautla</t>
+  </si>
+  <si>
+    <t>Padres de familia y alumnos en Huautla tomaron las instalaciones del Cobaeh Cemsad debido a que llevan cuatro meses sin suministro de energía eléctrica.</t>
+  </si>
+  <si>
+    <t>Francisco Bautista</t>
+  </si>
+  <si>
+    <t>Iván Lara Hernández</t>
+  </si>
+  <si>
+    <t>Trabajadores de una secundaria señalan acoso de los padres</t>
+  </si>
+  <si>
+    <t>Personal directivo, docente y administrativo de la Secundaria General 1 Miguel Hidalgo de Actopan colocó una lona pidiendo la intervención de autoridades educativas ante el presunto acoso de la Sociedad de Padres de Familia.</t>
+  </si>
+  <si>
+    <t>Actopan</t>
+  </si>
+  <si>
+    <t>Trabajo bajo protesta</t>
+  </si>
+  <si>
+    <t>Personal docente y directivo de la Secundaria General 1 de Actopan se declaró en trabajo bajo protesta acusando acoso por parte de la mesa de padres de familia.</t>
+  </si>
+  <si>
+    <t>Erika Gutiérrez</t>
+  </si>
+  <si>
+    <t>Siguen 3 líneas de investigación por asesinato de sacerdote</t>
+  </si>
+  <si>
+    <t>La PGJEH cuenta con tres líneas de investigación sobre el homicidio del párroco Román de la Cruz Hernández en Tlanchinol-Lolotla. El procurador Francisco Fernández Hasbun informó sobre avances tras reunirse con el obispo José Hiraís Acosta Beltrán.</t>
+  </si>
+  <si>
+    <t>Exigen esclarecer homicidio</t>
+  </si>
+  <si>
+    <t>La PGJEH reportó la apertura de tres líneas de investigación para esclarecer el homicidio del sacerdote Román de la Cruz Hernández en la Huasteca.</t>
+  </si>
+  <si>
+    <t>Francisco Fernández Hasbun, José Hiraís Acosta Beltrán, Román de la Cruz Hernández</t>
+  </si>
+  <si>
+    <t>Presentan nueva tarifa de taxis</t>
+  </si>
+  <si>
+    <t>La tarifa del servicio de transporte público individual será de 45 pesos para los primeros cuatro kilómetros y por cada kilómetro adicional se cobrarán 4 pesos en una primera etapa para Pachuca y Mineral de la Reforma, reveló la secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez. Los taxis migrarán de forma gradual a taxímetros en un periodo de hasta 120 días.</t>
+  </si>
+  <si>
+    <t>La Semot anunció la nueva tarifa base de taxi en 45 pesos para los primeros cuatro kilómetros en Pachuca y Mineral de la Reforma, con un cobro de 4 pesos por kilómetro adicional y una transición gradual a taxímetros en 120 días.</t>
+  </si>
+  <si>
+    <t>Rutas 47 y 108, con más accidentes de tránsito</t>
+  </si>
+  <si>
+    <t>Entre las calles y bulevares de Pachuca, la prisa por ganar pasaje y la falta de precaución han contribuido a que las rutas 47 y 108 concentren la mayor cantidad de accidentes viales durante 2026. La capital hidalguense registra 27 percances del transporte público en lo que va del año.</t>
+  </si>
+  <si>
+    <t>Pachuca encabeza los accidentes de transporte público en Hidalgo con 27 casos en 2026, destacando las rutas 47 y 108 con cuatro percances cada una debido a exceso de velocidad e imprudencia al conducir.</t>
+  </si>
+  <si>
+    <t>Semot, PGJEH</t>
+  </si>
+  <si>
+    <t>La PGJEH abre dos carpetas por tentativa de feminicidio</t>
+  </si>
+  <si>
+    <t>La Procuraduría General de Justicia del Estado de Hidalgo inició dos carpetas de investigación por tentativa de feminicidio durante 2026 en Metepec y Actopan, de acuerdo con cifras del Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública.</t>
+  </si>
+  <si>
+    <t>Metepec</t>
+  </si>
+  <si>
+    <t>Feminicidio</t>
+  </si>
+  <si>
+    <t>Durante 2026, la PGJEH inició dos carpetas de investigación por tentativa de feminicidio en los municipios de Metepec y Actopan, buscando judicializar los casos para llevar a los responsables ante la justicia.</t>
+  </si>
+  <si>
+    <t>Revisará Semot vigencia de seguro de unidades del transporte público</t>
+  </si>
+  <si>
+    <t>Luego de revocar la concesión a una colectiva involucrada en un accidente en el bulevar Minero por no contar con seguro, la Semot realizará inspecciones gratuitas para verificar que todas las unidades del transporte público tengan póliza vigente o de lo contrario perderán el permiso.</t>
+  </si>
+  <si>
+    <t>Supervisión de Transporte</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte iniciará revisiones a unidades del transporte público para garantizar que cuenten con seguro vigente, advirtiendo que la falta de cobertura provocará la cancelación definitiva de la concesión.</t>
+  </si>
+  <si>
+    <t>Semot, STCH, PGJEH</t>
+  </si>
+  <si>
+    <t>Habrá transporte nocturno por la Feria de San Francisco 2026</t>
+  </si>
+  <si>
+    <t>Como parte del operativo especial de movilidad para la Feria de San Francisco Pachuca 2026, la Semoth confirmó que el Tuzobús, taxis y rutas de combis ofrecerán servicio nocturno especial extendido hasta las 3:00 de la mañana.</t>
+  </si>
+  <si>
+    <t>La Semoth garantizó opciones de transporte nocturno extendido hasta las 03:00 horas durante la Feria de San Francisco 2026 mediante unidades del Tuzobús, taxis y combis.</t>
+  </si>
+  <si>
+    <t>Separan a docente de la Técnica Uno</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón, informó que la Contraloría estatal determinó separar de su cargo a una maestra de matemáticas de la Secundaria Técnica 1 en Pachuca tras resolverse un procedimiento por acoso.</t>
+  </si>
+  <si>
+    <t>La Contraloría de Hidalgo aplicó una sanción para retirar de la Secundaria Técnica 1 de Pachuca a una profesora de matemáticas tras acreditarse una denuncia por acoso.</t>
+  </si>
+  <si>
+    <t>Carmen Hernández</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Elena Cortés</t>
+  </si>
+  <si>
+    <t>Dice SEPH no prohibirá el ingreso de celulares</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, titular de la SEPH, aclaró que no se prohibirá la entrada de teléfonos celulares a planteles de educación básica, pero su uso estará restringido durante la jornada escolar y el receso a actividades estrictamente académicas o emergencias.</t>
+  </si>
+  <si>
+    <t>La SEPH mantendrá una regulación restrictiva sobre el uso de celulares durante las clases y receso en escuelas de educación básica, enfocando la medida como un proceso formativo.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Expondrán 139 artesanos en Feria de San Francisco</t>
+  </si>
+  <si>
+    <t>El secretario de Bienestar e Inclusión Social, Ricardo Gómez Moreno, dio a conocer que 139 artesanos y productores gastronómicos de 50 municipios participarán sin costo en el Pabellón Artesanal de la Feria de San Francisco 2026, espacio remodelado con 6.5 mdp.</t>
+  </si>
+  <si>
+    <t>La Sebiso destinó más de 6.5 millones de pesos a la remodelación del Pabellón Artesanal de la Feria de Pachuca, donde 139 productores expondrán de manera gratuita del 24 de septiembre al 18 de octubre.</t>
+  </si>
+  <si>
+    <t>Fallan 102 de las 167 plantas para tratar aguas sucias</t>
+  </si>
+  <si>
+    <t>Un informe de la CEAA reveló que 102 de las 167 Plantas de Tratamiento de Aguas Residuales en la Huasteca y Sierra permanecen fuera de servicio por falta de mantenimiento, capacitación y cobro de cuotas, desaprovechando 337 litros por segundo de capacidad de saneamiento.</t>
+  </si>
+  <si>
+    <t>PTAR</t>
+  </si>
+  <si>
+    <t>La CEAA reportó que más del 60 por ciento de la infraestructura de saneamiento de aguas residuales en la Huasteca y Sierra de Hidalgo está inactiva debido al abandono y la falta de financiamiento municipal.</t>
+  </si>
+  <si>
+    <t>Salomón Hernández</t>
+  </si>
+  <si>
+    <t>Suma Hidalgo 768 casos de narcomenudeo durante 2026</t>
+  </si>
+  <si>
+    <t>Datos del SESNSP señalan que entre enero y agosto de 2026 se registraron 768 casos de narcomenudeo en los principales municipios de Hidalgo. Pachuca lidera la lista con 139 carpetas, seguida de Tulancingo (65), Mineral de la Reforma (58) y Tizayuca (58).</t>
+  </si>
+  <si>
+    <t>Un reporte estadístico del SESNSP ubicó a Pachuca, Tulancingo, Mineral de la Reforma y Tizayuca como las demarcaciones urbanas con mayor concentración de delitos por venta y posesión de narcomenudeo en la entidad.</t>
+  </si>
+  <si>
+    <t>Luis Godínez</t>
+  </si>
+  <si>
+    <t>PGJEH, Presidencia, SSPH</t>
+  </si>
+  <si>
+    <t>Caso Karla: buscan llevar la acusación por dolo eventual</t>
+  </si>
+  <si>
+    <t>Abogados de la familia de Karla, joven que falleció tras ser atropellada en Zacualtipán, informaron que el Ministerio Público formuló una acusación bajo dolo eventual contra el conductor ebrio, además de solicitar 25 mdp como reparación por daño moral.</t>
+  </si>
+  <si>
+    <t>La representación legal de las estudiantes atropelladas en Zacualtipán busca que el imputado sea juzgado por homicidio con dolo eventual debido al alto grado de ebriedad con el que conducía.</t>
+  </si>
+  <si>
+    <t>Piden padres se normalice el servicio de luz en Cobaeh</t>
+  </si>
+  <si>
+    <t>Padres de familia del Cobaeh Cemsad Tamoyón I en Huautla cerraron las instalaciones del plantel exigiendo el restablecimiento del servicio de energía eléctrica que dejó de funcionar hace cuatro meses, afectando las actividades de 131 alumnos.</t>
+  </si>
+  <si>
+    <t>Un grupo de tutores tomó las instalaciones del plantel Cobaeh en Huautla para presionar a las autoridades a solucionar la falta de luz que padecen los estudiantes desde hace cuatro meses.</t>
+  </si>
+  <si>
+    <t>San Agustín Tlaxiaca activa brigada</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo y el Ayuntamiento de San Agustín Tlaxiaca pusieron en marcha la Brigada contra el Suicidio en las instalaciones del Cobaeh local, promoviendo espacios de orientación y prevención de la salud mental.</t>
+  </si>
+  <si>
+    <t>San Agustín Tlaxiaca</t>
+  </si>
+  <si>
+    <t>Prevención del suicidio</t>
+  </si>
+  <si>
+    <t>La SSH y la alcaldía de San Agustín Tlaxiaca iniciaron las brigadas universitarias de atención psicológica y prevención del suicidio entre la comunidad estudiantil.</t>
+  </si>
+  <si>
+    <t>SSH, SEPH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo, Mario David Medina Hernández</t>
+  </si>
+  <si>
+    <t>IHE impulsa primera infancia</t>
+  </si>
+  <si>
+    <t>El Instituto Hidalguense de Educación llevó a cabo el encuentro estatal 'Cada Momento Cuenta', donde docentes y especialistas intercambiaron propuestas para fortalecer el modelo de Educación Inicial y el desarrollo de la niñez en Hidalgo.</t>
+  </si>
+  <si>
+    <t>El IHE organizó una jornada de trabajo con agentes educativos y personal directivo para evaluar los avances y ampliar la cobertura del programa de Educación Inicial en el estado.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Nancy León Vite, Leobardo Cano Albarrán, Herlinda Amador Lara</t>
+  </si>
+  <si>
+    <t>Tarifa mínima de taxis aumentará a 45 pesos</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte anunció que el banderazo inicial para el servicio de taxis en la zona metropolitana de Pachuca y Mineral de la Reforma aumentará a 45 pesos, con un costo adicional de 4 pesos por kilómetro recorrido.</t>
+  </si>
+  <si>
+    <t>La Semot autorizó el ajuste del 20% a la tarifa de taxi en la zona metropolitana de Pachuca, fijando la tarifa mínima en 45 pesos por los primeros 4 kilómetros.</t>
+  </si>
+  <si>
+    <t>Oscar Raúl Pérez</t>
+  </si>
+  <si>
+    <t>Restringen uso de dispositivos móviles en aulas</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón Valdez, informó que el uso de celulares en las aulas queda restricted en Hidalgo a fines estrictamente pedagógicos o emergencias, en apego a los acuerdos nacionales.</t>
+  </si>
+  <si>
+    <t>La SEPH ratificó la medida de restringir los celulares en aulas de educación básica, permitiendo su uso únicamente bajo supervisión docente y con fines educativos.</t>
+  </si>
+  <si>
+    <t>Ana Luisa Vega</t>
+  </si>
+  <si>
+    <t>Audiencia por triple feminicidio, continuará el jueves</t>
+  </si>
+  <si>
+    <t>El tribunal de enjuiciamiento determinó un receso en el desahogo de pruebas y fijó para este jueves la reanudación de la audiencia por el triple feminicidio ocurrido en Santiago Tulantepec.</t>
+  </si>
+  <si>
+    <t>Santiago Tulantepec</t>
+  </si>
+  <si>
+    <t>Continuará este jueves el juicio oral contra los probables responsables del triple feminicidio en Santiago Tulantepec, donde se prevé la declaración de los imputados.</t>
+  </si>
+  <si>
+    <t>Capturan a pareja con 72 kilos de presunta marihuana</t>
+  </si>
+  <si>
+    <t>Policías estatales detuvieron en el municipio de Ixmiquilpan a un hombre y una mujer en posesión de 72 kilogramos de hierba seca con características de la marihuana valuados en más de 570 mil pesos.</t>
+  </si>
+  <si>
+    <t>La SSPH aseguró un cargamento de 72 kilos de marihuana en Ixmiquilpan y aprehendió a dos personas vinculadas con la transportación del estupefaciente.</t>
+  </si>
+  <si>
+    <t>Abordarán retos del lirio acuático y los humedales</t>
+  </si>
+  <si>
+    <t>El Citnova anunció la realización del Congreso Lirio Acuático, Humedales e Innovación para la Restauración Ambiental los días 24 y 25 de septiembre en Pachuca.</t>
+  </si>
+  <si>
+    <t>Especialistas e investigadores se reunirán en el Citnova para analizar alternativas de aprovechamiento del lirio acuático y conservación de humedales.</t>
+  </si>
+  <si>
+    <t>CITNOVA</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad hace decomiso de 35 mil litros de hidrocarburo</t>
+  </si>
+  <si>
+    <t>El Gabinete de Seguridad de Hidalgo informó sobre el decomiso de 35,038 litros de hidrocarburo robado, la captura de tres personas por altercado con arma de fuego en el centro de Pachuca y saldo blanco en festejos patrios.</t>
+  </si>
+  <si>
+    <t>Combate Al Huachicol</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad de Hidalgo reportó el aseguramiento de más de 35 mil litros de huachicol y la detención de tres presuntos responsables de una riña armada en Pachuca.</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH, Sedena, GN</t>
+  </si>
+  <si>
+    <t>Taxis suben tarifas: banderazo en 45 pesos</t>
+  </si>
+  <si>
+    <t>La tarifa mínima de taxis en la zona metropolitana aumentó 7 pesos, fijando el banderazo en 45 pesos por cuatro kilómetros y 4 pesos por kilómetro adicional.</t>
+  </si>
+  <si>
+    <t>Aumenta 20% la tarifa de taxis en Pachuca y Mineral de la Reforma; el banderazo inicial pasa a 45 pesos con incremento a 4 pesos por kilómetro subsecuente.</t>
+  </si>
+  <si>
+    <t>Piden reclasificar homicidio de una alumna de UTSH</t>
+  </si>
+  <si>
+    <t>Familiares de la estudiante Karla Espinoza Hernández solicitarán la reclasificación del delito de homicidio culposo a doloso por dolo eventual tras el atropellamiento registrado en Zacualtipán.</t>
+  </si>
+  <si>
+    <t>Familiares de estudiante fallecida en Zacualtipán exigen reclasificar la causa penal a dolo eventual argumentando estado de ebriedad del conductor.</t>
+  </si>
+  <si>
+    <t>Diócesis y PGJEH revisan asesinato de eclesiástico</t>
+  </si>
+  <si>
+    <t>La Diócesis de Huejutla y la PGJEH establecieron acuerdos de colaboración para dar seguimiento a las investigaciones por el homicidio del presbítero Román de la Cruz en Lolotla.</t>
+  </si>
+  <si>
+    <t>Procurador y Obispo de Huejutla sostuvieron reunión de trabajo para coordinar avances en la investigación del asesinato del sacerdote Román de la Cruz.</t>
+  </si>
+  <si>
+    <t>Oficial: SEP prohíbe celulares en las aulas</t>
+  </si>
+  <si>
+    <t>La SEPH implementará las directrices nacionales para restringir el uso de teléfonos celulares en salones de educación básica, permitiéndolos sólo con fines pedagógicos planeados.</t>
+  </si>
+  <si>
+    <t>Autoridades educativas en Hidalgo restringirán el uso de dispositivos móviles en planteles de educación básica a actividades con propósito escolar explícito.</t>
+  </si>
+  <si>
+    <t>Sin incidentes en festejos patrios, reporta Seguridad</t>
+  </si>
+  <si>
+    <t>El Gabinete de Seguridad de Hidalgo dio a conocer que el dispositivo implementado durante las celebraciones patrias en Pachuca y municipios concluyó con saldo blanco.</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad de Hidalgo concluyó el operativo de Fiestas Patrias reportando ausencia de incidentes mayores en los 84 municipios.</t>
+  </si>
+  <si>
+    <t>SSPH, Segobh</t>
+  </si>
+  <si>
+    <t>Anuncian aumento del 20% en la tarifa de taxis; ajuste iniciará en Pachuca y La Reforma</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte del estado (Semoth), Lizbeth Robles Gutiérrez, anunció el aumento del 20% en la tarifa del Servicio Público de Transporte Individual (taxi), aplicando inicialmente en Pachuca y Mineral de la Reforma. El banderazo pasa de 38 a 45 pesos por los primeros 4 kilómetros y 4 pesos por kilómetro adicional, contemplando la migración gradual a taxímetros digitales en 120 días.</t>
+  </si>
+  <si>
+    <t>La Semot anunció un aumento del 20% en la tarifa de taxis en Pachuca y Mineral de la Reforma, fijando el costo inicial en 45 pesos por los primeros 4 kilómetros y 4 pesos por kilómetro adicional.</t>
+  </si>
+  <si>
+    <t>Uso de celulares en escuelas solo para emergencias o actividades planeadas: SEPH</t>
+  </si>
+  <si>
+    <t>El titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón Valdez, confirmó que se reforzará la restricción del uso de dispositivos celulares en escuelas de educación básica en la entidad, permitiendo su encendido únicamente para actividades pedagógicas previamente planeadas o ante emergencias justificadas.</t>
+  </si>
+  <si>
+    <t>La SEPH ratificó la restricción del uso de teléfonos celulares en escuelas de educación básica de Hidalgo, condicionando su uso a fines estrictamente educativos o emergencias.</t>
+  </si>
+  <si>
+    <t>Operativos a combis dejan 724 infracciones y 153 unidades aseguradas</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte (Semot) informó que tras la realización de 249 operativos al transporte público colectivo se aplicaron 724 infracciones y se aseguraron 153 unidades por diversas irregularidades, además de verificar la vigencia de las pólizas de seguro de responsabilidad civil.</t>
+  </si>
+  <si>
+    <t>Operativos de la Semot al transporte público colectivo derivaron en 724 infracciones y 153 unidades remitidas al corralón por falta de seguro y otras faltas operativas.</t>
+  </si>
+  <si>
+    <t>Exigen reparación integral tras muerte de Karla y lesiones de Estrella</t>
+  </si>
+  <si>
+    <t>Familiares y representantes legales de Karla y Estrella, estudiantes atropelladas en Zacualtipán, solicitaron que la acusación contra el presunto responsable se mantenga como homicidio con dolo eventual y que se contemple una reparación integral por daño moral estimada en 25 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Abogados de las familias de dos estudiantes universitarias atropelladas en Zacualtipán buscan reclasificar el delito a homicidio con dolo eventual y exigen reparación de daños morales.</t>
+  </si>
+  <si>
+    <t>Participarán 139 artesanos en la Feria San Francisco Hidalgo 2026</t>
+  </si>
+  <si>
+    <t>El titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, informó que 139 artesanos hidalguenses de 50 municipios participarán con espacios gratuitos en el pabellón artesanal y gastronómico de la Feria San Francisco Pachuca Hidalgo 2026, destacando además un 60% de avance en la remodelación de la tienda Hidarte.</t>
+  </si>
+  <si>
+    <t>La Sebiso asignó espacios gratuitos a 139 artesanos de 50 municipios para exponer en la Feria de San Francisco 2026 y reportó avances del 60% en las obras de Hidarte.</t>
+  </si>
+  <si>
+    <t>Siguen tres líneas de investigación por muerte de párroco de Huejutla</t>
+  </si>
+  <si>
+    <t>En reunión entre el encargado del despacho de la PGJEH, Francisco Fernández Hasbun, y el obispo de la Diócesis de Huejutla, José Hiraís Acosta Beltrán, se informó sobre la existencia de tres líneas de investigación abiertas para esclarecer el homicidio del presbítero Román de la Cruz Hernández, hallado en Lolotla el pasado 15 de septiembre.</t>
+  </si>
+  <si>
+    <t>La PGJEH dio a conocer al obispo de Huejutla tres líneas de investigación para dar con los responsables del asesinato del párroco Román de la Cruz Hernández.</t>
+  </si>
+  <si>
+    <t>Román de la Cruz Hernández, José Hiraís Acosta Beltrán, Francisco Fernández Hasbun</t>
+  </si>
+  <si>
+    <t>Aseguran combustible, vehículos y drogas durante operativos en Hidalgo</t>
+  </si>
+  <si>
+    <t>Durante la reunión semanal del gabinete de seguridad encabezada por el gobernador Julio Menchaca Salazar, autoridades informaron sobre el decomiso de más de 35 mil litros de hidrocarburo, 15 vehículos, armas de fuego, chalecos tácticos y más de 70 kilos de mariguana, así como la detención de presuntos delincuentes en varios municipios.</t>
+  </si>
+  <si>
+    <t>Operativos del gabinete de seguridad en Hidalgo permitieron incautar 35 mil litros de combustible robado, armas, enervantes y detener a generadores de violencia en la entidad.</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH, Pemex</t>
   </si>
 </sst>
 </file>
@@ -1257,8 +1470,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ51" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ51" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ70" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ70" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1690,7 +1903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ51"/>
+  <dimension ref="A1:AJ70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1840,10 +2053,10 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>93</v>
@@ -1852,10 +2065,10 @@
         <v>94</v>
       </c>
       <c r="F2" s="1">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>95</v>
@@ -1870,7 +2083,7 @@
         <v>13262</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>37</v>
@@ -1882,16 +2095,16 @@
         <v>97</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AA2">
         <v>20</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>38</v>
@@ -1900,43 +2113,45 @@
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ2" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F3" s="1">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1945,55 +2160,57 @@
         <v>13262</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>102</v>
       </c>
       <c r="Y3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA3">
+        <v>20</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA3">
-        <v>16</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="AC3" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD3" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="AI3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AJ3" s="2"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>104</v>
@@ -2002,16 +2219,16 @@
         <v>105</v>
       </c>
       <c r="F4" s="1">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2020,7 +2237,7 @@
         <v>13262</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>37</v>
@@ -2032,16 +2249,16 @@
         <v>107</v>
       </c>
       <c r="Y4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA4">
+        <v>12</v>
+      </c>
+      <c r="AB4" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA4">
-        <v>24</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="AC4" s="2" t="s">
         <v>38</v>
@@ -2050,45 +2267,43 @@
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="AG4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>109</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="AJ4" s="2"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F5" s="1">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="G5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2097,55 +2312,57 @@
         <v>13262</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA5">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ5" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>115</v>
@@ -2154,16 +2371,16 @@
         <v>116</v>
       </c>
       <c r="F6" s="1">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2172,28 +2389,28 @@
         <v>13262</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V6" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA6">
         <v>20</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC6" s="2" t="s">
         <v>38</v>
@@ -2202,43 +2419,45 @@
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="AI6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AJ6" s="2"/>
+      <c r="AJ6" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F7" s="1">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2247,28 +2466,28 @@
         <v>13262</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Y7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA7">
+        <v>8</v>
+      </c>
+      <c r="AB7" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA7">
-        <v>30</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>38</v>
@@ -2277,43 +2496,45 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AJ7" s="2"/>
+      <c r="AJ7" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F8" s="1">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2322,28 +2543,28 @@
         <v>13262</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="X8" s="2" t="s">
         <v>129</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA8">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC8" s="2" t="s">
         <v>38</v>
@@ -2352,40 +2573,40 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="AJ8" s="2"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="F9" s="1">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>49</v>
@@ -2397,28 +2618,28 @@
         <v>13262</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="X9" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="X9" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="Y9" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA9">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC9" s="2" t="s">
         <v>38</v>
@@ -2427,7 +2648,7 @@
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>40</v>
@@ -2436,16 +2657,18 @@
         <v>46</v>
       </c>
       <c r="AI9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AJ9" s="2"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>136</v>
@@ -2454,13 +2677,13 @@
         <v>137</v>
       </c>
       <c r="F10" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>42</v>
@@ -2472,28 +2695,28 @@
         <v>13262</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA10">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC10" s="2" t="s">
         <v>38</v>
@@ -2502,40 +2725,42 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AJ10" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F11" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>42</v>
@@ -2547,28 +2772,28 @@
         <v>13262</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Y11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA11">
+        <v>12</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA11">
-        <v>20</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="AC11" s="2" t="s">
         <v>38</v>
@@ -2577,43 +2802,45 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AJ11" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F12" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2622,28 +2849,28 @@
         <v>13262</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Y12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA12">
+        <v>20</v>
+      </c>
+      <c r="AB12" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA12">
-        <v>16</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="AC12" s="2" t="s">
         <v>38</v>
@@ -2652,7 +2879,7 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>40</v>
@@ -2661,36 +2888,36 @@
         <v>46</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F13" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2699,28 +2926,28 @@
         <v>13262</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA13">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>38</v>
@@ -2729,43 +2956,45 @@
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ13" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F14" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2774,73 +3003,78 @@
         <v>13262</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA14">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>164</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="AJ14" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F15" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2849,19 +3083,19 @@
         <v>13262</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>43</v>
@@ -2870,7 +3104,7 @@
         <v>16</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC15" s="2" t="s">
         <v>38</v>
@@ -2879,45 +3113,45 @@
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AG15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F16" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -2926,73 +3160,75 @@
         <v>13262</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="Y16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA16">
+        <v>10</v>
+      </c>
+      <c r="AB16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA16">
-        <v>20</v>
-      </c>
-      <c r="AB16" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="AC16" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="AG16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AJ16" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F17" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3001,28 +3237,28 @@
         <v>13262</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="Y17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA17">
+        <v>24</v>
+      </c>
+      <c r="AB17" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA17">
-        <v>30</v>
-      </c>
-      <c r="AB17" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="AC17" s="2" t="s">
         <v>38</v>
@@ -3031,43 +3267,45 @@
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="AJ17" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="F18" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3076,19 +3314,19 @@
         <v>13262</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>43</v>
@@ -3097,7 +3335,7 @@
         <v>20</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC18" s="2" t="s">
         <v>38</v>
@@ -3106,43 +3344,45 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AJ18" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F19" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3151,28 +3391,28 @@
         <v>13262</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC19" s="2" t="s">
         <v>38</v>
@@ -3181,40 +3421,42 @@
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AG19" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ19" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F20" s="1">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>42</v>
@@ -3226,19 +3468,19 @@
         <v>13262</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>96</v>
+        <v>197</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>43</v>
@@ -3247,7 +3489,7 @@
         <v>20</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC20" s="2" t="s">
         <v>38</v>
@@ -3256,7 +3498,7 @@
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="AG20" s="2" t="s">
         <v>40</v>
@@ -3265,34 +3507,36 @@
         <v>64</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="AJ20" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="AJ20" s="2" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="F21" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G21">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3301,28 +3545,28 @@
         <v>13262</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC21" s="2" t="s">
         <v>38</v>
@@ -3331,43 +3575,45 @@
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ21" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F22" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3376,28 +3622,28 @@
         <v>13262</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V22" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC22" s="2" t="s">
         <v>38</v>
@@ -3406,37 +3652,39 @@
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>41</v>
+        <v>208</v>
       </c>
       <c r="AG22" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AJ22" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F23" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>45</v>
@@ -3451,28 +3699,28 @@
         <v>13262</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>199</v>
+        <v>90</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC23" s="2" t="s">
         <v>38</v>
@@ -3487,37 +3735,37 @@
         <v>41</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="AJ23" s="2"/>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F24" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -3526,73 +3774,75 @@
         <v>13262</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD24" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ24" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F25" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -3601,75 +3851,75 @@
         <v>13262</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA25">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="AG25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>124</v>
+        <v>220</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F26" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>45</v>
+        <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -3678,72 +3928,70 @@
         <v>13262</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ26" s="2" t="s">
-        <v>216</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="AJ26" s="2"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F27" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G27">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>49</v>
@@ -3752,31 +4000,31 @@
         <v>1</v>
       </c>
       <c r="S27">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA27">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC27" s="2" t="s">
         <v>38</v>
@@ -3785,75 +4033,75 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F28" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G28">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R28">
         <v>1</v>
       </c>
       <c r="S28">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V28" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA28">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC28" s="2" t="s">
         <v>38</v>
@@ -3862,75 +4110,75 @@
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>85</v>
+        <v>232</v>
       </c>
       <c r="AG28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F29" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R29">
         <v>1</v>
       </c>
       <c r="S29">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA29">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC29" s="2" t="s">
         <v>38</v>
@@ -3939,74 +4187,76 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>68</v>
+        <v>243</v>
       </c>
       <c r="AG29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="AJ29" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F30" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G30">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R30">
         <v>1</v>
       </c>
       <c r="S30">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V30" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="Y30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA30">
+        <v>12</v>
+      </c>
+      <c r="AB30" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA30">
-        <v>20</v>
-      </c>
-      <c r="AB30" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="AC30" s="2" t="s">
         <v>44</v>
       </c>
@@ -4014,75 +4264,75 @@
         <v>44</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AG30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>239</v>
+        <v>64</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F31" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G31">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R31">
         <v>1</v>
       </c>
       <c r="S31">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z31" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA31">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC31" s="2" t="s">
         <v>38</v>
@@ -4091,112 +4341,116 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>68</v>
+        <v>248</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="AJ31" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="AJ31" s="2" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F32" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G32">
         <v>5</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
       <c r="S32">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V32" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD32" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>41</v>
+        <v>248</v>
       </c>
       <c r="AG32" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="AJ32" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="AJ32" s="2" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F33" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>45</v>
@@ -4208,183 +4462,185 @@
         <v>1</v>
       </c>
       <c r="S33">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AA33">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC33" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD33" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>41</v>
+        <v>248</v>
       </c>
       <c r="AG33" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="AJ33" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AJ33" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F34" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R34">
         <v>1</v>
       </c>
       <c r="S34">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA34">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>41</v>
+        <v>266</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>260</v>
+        <v>77</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F35" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R35">
         <v>1</v>
       </c>
       <c r="S35">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Y35" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA35">
+        <v>12</v>
+      </c>
+      <c r="AB35" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="Z35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA35">
-        <v>20</v>
-      </c>
-      <c r="AB35" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="AC35" s="2" t="s">
         <v>38</v>
@@ -4393,40 +4649,42 @@
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>267</v>
+        <v>41</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="AJ35" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="AJ35" s="2" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F36" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>45</v>
+        <v>277</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>42</v>
@@ -4435,22 +4693,22 @@
         <v>1</v>
       </c>
       <c r="S36">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>271</v>
+        <v>138</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>43</v>
@@ -4459,7 +4717,7 @@
         <v>12</v>
       </c>
       <c r="AB36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC36" s="2" t="s">
         <v>38</v>
@@ -4468,73 +4726,75 @@
         <v>44</v>
       </c>
       <c r="AF36" s="2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AG36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>239</v>
+        <v>46</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AJ36" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="AJ36" s="2" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F37" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G37">
         <v>9</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R37">
         <v>1</v>
       </c>
       <c r="S37">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V37" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA37">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC37" s="2" t="s">
         <v>38</v>
@@ -4543,115 +4803,117 @@
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>41</v>
+        <v>286</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>239</v>
+        <v>46</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>277</v>
+        <v>46</v>
       </c>
       <c r="AJ37" s="2"/>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F38" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R38">
         <v>1</v>
       </c>
       <c r="S38">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>76</v>
+        <v>289</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA38">
         <v>20</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>39</v>
+        <v>243</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AJ38" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="AJ38" s="2" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="F39" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>42</v>
@@ -4663,28 +4925,28 @@
         <v>12500</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA39">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB39" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC39" s="2" t="s">
         <v>38</v>
@@ -4699,36 +4961,36 @@
         <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>285</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="F40" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>42</v>
@@ -4740,28 +5002,28 @@
         <v>12500</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>288</v>
+        <v>90</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA40">
         <v>20</v>
       </c>
       <c r="AB40" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC40" s="2" t="s">
         <v>38</v>
@@ -4770,42 +5032,40 @@
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>290</v>
+        <v>39</v>
       </c>
       <c r="AG40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ40" s="2" t="s">
-        <v>292</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="AJ40" s="2"/>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F41" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>42</v>
@@ -4817,28 +5077,28 @@
         <v>12500</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V41" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>76</v>
+        <v>302</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA41">
         <v>12</v>
       </c>
       <c r="AB41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC41" s="2" t="s">
         <v>38</v>
@@ -4847,216 +5107,227 @@
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>296</v>
+        <v>39</v>
       </c>
       <c r="AG41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ41" s="2" t="s">
-        <v>297</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="AJ41" s="2"/>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F42" s="1">
-        <v>46286</v>
+        <v>46287</v>
+      </c>
+      <c r="G42">
+        <v>4</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R42">
         <v>1</v>
       </c>
       <c r="S42">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V42" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA42">
         <v>20</v>
       </c>
       <c r="AB42" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC42" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD42" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="AJ42" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="AJ42" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F43" s="1">
-        <v>46286</v>
+        <v>46287</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>305</v>
+        <v>45</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R43">
         <v>1</v>
       </c>
       <c r="S43">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V43" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>306</v>
+        <v>169</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA43">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB43" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC43" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD43" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>308</v>
+        <v>77</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="AJ43" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="AJ43" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F44" s="1">
-        <v>46286</v>
+        <v>46287</v>
+      </c>
+      <c r="G44">
+        <v>8</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R44">
         <v>1</v>
       </c>
       <c r="S44">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>311</v>
+        <v>236</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA44">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB44" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC44" s="2" t="s">
         <v>38</v>
@@ -5065,61 +5336,66 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>41</v>
+        <v>315</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ44" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="AJ44" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F45" s="1">
-        <v>46286</v>
+        <v>46287</v>
+      </c>
+      <c r="G45">
+        <v>8</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R45">
         <v>1</v>
       </c>
       <c r="S45">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V45" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>271</v>
+        <v>150</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z45" s="2" t="s">
         <v>43</v>
@@ -5128,79 +5404,84 @@
         <v>12</v>
       </c>
       <c r="AB45" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC45" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>41</v>
+        <v>315</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>239</v>
+        <v>46</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ45" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="AJ45" s="2" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F46" s="1">
-        <v>46286</v>
+        <v>46287</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
       <c r="S46">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA46">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB46" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC46" s="2" t="s">
         <v>38</v>
@@ -5209,70 +5490,75 @@
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>41</v>
+        <v>315</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AJ46" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="AJ46" s="2" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F47" s="1">
-        <v>46286</v>
+        <v>46287</v>
+      </c>
+      <c r="G47">
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R47">
         <v>1</v>
       </c>
       <c r="S47">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>322</v>
+        <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA47">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AB47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC47" s="2" t="s">
         <v>38</v>
@@ -5281,40 +5567,40 @@
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>41</v>
+        <v>328</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>325</v>
+        <v>69</v>
       </c>
       <c r="AJ47" s="2"/>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F48" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>42</v>
@@ -5323,31 +5609,31 @@
         <v>1</v>
       </c>
       <c r="S48">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V48" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z48" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AA48">
         <v>20</v>
       </c>
       <c r="AB48" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC48" s="2" t="s">
         <v>38</v>
@@ -5356,40 +5642,40 @@
         <v>44</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>69</v>
+        <v>332</v>
       </c>
       <c r="AG48" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AJ48" s="2"/>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F49" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>61</v>
+        <v>224</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>42</v>
@@ -5398,108 +5684,108 @@
         <v>1</v>
       </c>
       <c r="S49">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V49" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>332</v>
+        <v>197</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z49" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA49">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC49" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD49" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>69</v>
+        <v>332</v>
       </c>
       <c r="AG49" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>334</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>342</v>
+        <v>92</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F50" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>45</v>
+        <v>277</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R50">
         <v>1</v>
       </c>
       <c r="S50">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V50" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>337</v>
+        <v>138</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA50">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC50" s="2" t="s">
         <v>38</v>
@@ -5508,96 +5794,1525 @@
         <v>44</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>69</v>
+        <v>328</v>
       </c>
       <c r="AG50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ50" s="2" t="s">
-        <v>334</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="AJ50" s="2"/>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F51" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G51">
+        <v>19</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F51" s="1">
-        <v>46286</v>
-      </c>
-      <c r="G51">
-        <v>6</v>
-      </c>
-      <c r="H51" s="2" t="s">
+      <c r="I51" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="R51">
         <v>1</v>
       </c>
       <c r="S51">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V51" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z51" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA51">
+        <v>12</v>
+      </c>
+      <c r="AB51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI51" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="AJ51" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F52" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G52">
+        <v>19</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>12500</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA52">
+        <v>16</v>
+      </c>
+      <c r="AB52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH52" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI52" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ52" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F53" s="1">
+        <v>46287</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
+      </c>
+      <c r="S53">
+        <v>13262</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="Y53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA53">
         <v>20</v>
       </c>
-      <c r="AB51" s="2" t="s">
+      <c r="AB53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF53" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="AG53" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ53" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F54" s="1">
+        <v>46287</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+      <c r="S54">
+        <v>13262</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z54" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA54">
+        <v>20</v>
+      </c>
+      <c r="AB54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF54" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="AG54" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH54" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI54" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ54" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F55" s="1">
+        <v>46287</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <v>13262</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA55">
+        <v>12</v>
+      </c>
+      <c r="AB55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC55" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD55" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF55" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG55" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ55" s="2"/>
+    </row>
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F56" s="1">
+        <v>46287</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>13262</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y56" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC51" s="2" t="s">
+      <c r="Z56" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA56">
+        <v>12</v>
+      </c>
+      <c r="AB56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC56" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF51" s="2" t="s">
+      <c r="AD56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH56" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI56" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AJ56" s="2"/>
+    </row>
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46287</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <v>13262</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="X57" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA57">
+        <v>10</v>
+      </c>
+      <c r="AB57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH57" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI57" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="AJ57" s="2"/>
+    </row>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46287</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <v>13262</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="Y58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA58">
+        <v>24</v>
+      </c>
+      <c r="AB58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD58" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH58" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI58" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="AJ58" s="2"/>
+    </row>
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F59" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59">
+        <v>13262</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="X59" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="Y59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z59" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG51" s="2" t="s">
+      <c r="AA59">
+        <v>20</v>
+      </c>
+      <c r="AB59" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF59" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG59" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH51" s="2" t="s">
+      <c r="AH59" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI59" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ59" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F60" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R60">
+        <v>1</v>
+      </c>
+      <c r="S60">
+        <v>13262</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="X60" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="Y60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z60" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA60">
+        <v>16</v>
+      </c>
+      <c r="AB60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG60" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH60" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI60" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ60" s="2"/>
+    </row>
+    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F61" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G61">
+        <v>3</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+      <c r="S61">
+        <v>13262</v>
+      </c>
+      <c r="T61" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="X61" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA61">
+        <v>20</v>
+      </c>
+      <c r="AB61" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC61" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF61" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG61" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ61" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G62">
+        <v>5</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R62">
+        <v>1</v>
+      </c>
+      <c r="S62">
+        <v>13262</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="X62" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="Y62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA62">
+        <v>16</v>
+      </c>
+      <c r="AB62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH62" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AI51" s="2" t="s">
+      <c r="AI62" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ62" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F63" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R63">
+        <v>1</v>
+      </c>
+      <c r="S63">
+        <v>13262</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X63" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="Y63" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA63">
+        <v>12</v>
+      </c>
+      <c r="AB63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF63" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG63" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH63" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI63" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="AJ63" s="2"/>
+    </row>
+    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F64" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R64">
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <v>15000</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="X64" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="Y64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z64" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA64">
+        <v>20</v>
+      </c>
+      <c r="AB64" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF64" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG64" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH64" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI64" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ64" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F65" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <v>15000</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="Y65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z65" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA65">
+        <v>20</v>
+      </c>
+      <c r="AB65" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC65" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG65" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH65" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AJ51" s="2" t="s">
-        <v>150</v>
+      <c r="AI65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ65" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F66" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66">
+        <v>15000</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA66">
+        <v>12</v>
+      </c>
+      <c r="AB66" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG66" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH66" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI66" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ66" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F67" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G67">
+        <v>3</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>15000</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W67" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="X67" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="Y67" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z67" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA67">
+        <v>20</v>
+      </c>
+      <c r="AB67" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF67" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG67" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH67" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI67" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ67" s="2"/>
+    </row>
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F68" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>15000</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="Y68" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z68" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA68">
+        <v>20</v>
+      </c>
+      <c r="AB68" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC68" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF68" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG68" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH68" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI68" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ68" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F69" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G69">
+        <v>4</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69">
+        <v>15000</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W69" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="X69" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="Y69" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z69" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA69">
+        <v>20</v>
+      </c>
+      <c r="AB69" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC69" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD69" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF69" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG69" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH69" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI69" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ69" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F70" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G70">
+        <v>4</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+      <c r="S70">
+        <v>15000</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="Y70" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z70" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA70">
+        <v>24</v>
+      </c>
+      <c r="AB70" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF70" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG70" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH70" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI70" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ70" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF117B0E-71F6-4E71-B2C5-9A916C25EE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A94576E-581E-43F2-BA8B-9756AA6A15EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="333">
   <si>
     <t>Canal</t>
   </si>
@@ -244,78 +244,30 @@
     <t>Adela Garmez</t>
   </si>
   <si>
-    <t>Erick Perales</t>
-  </si>
-  <si>
-    <t>Huejutla</t>
-  </si>
-  <si>
-    <t>Cultura</t>
-  </si>
-  <si>
-    <t>Tula</t>
-  </si>
-  <si>
     <t>Veida Martínez Miranda</t>
   </si>
   <si>
     <t>Semot</t>
   </si>
   <si>
-    <t>Natividad Castrejón</t>
-  </si>
-  <si>
     <t>Aumento Tarifa De Transporte</t>
   </si>
   <si>
     <t>Blanca Soriano</t>
   </si>
   <si>
-    <t>Apoyo a artesanos</t>
-  </si>
-  <si>
     <t>SSPH</t>
   </si>
   <si>
-    <t>Accidente de Transporte Público</t>
-  </si>
-  <si>
-    <t>Bienestar</t>
-  </si>
-  <si>
     <t>Impresiones locales</t>
   </si>
   <si>
     <t>Sonia Nochebuena</t>
   </si>
   <si>
-    <t>SEPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Exigen destitución de funcionario</t>
-  </si>
-  <si>
-    <t>Regulación de dispositivos digitales</t>
-  </si>
-  <si>
-    <t>Lyzbeth Robles Gutiérrez</t>
-  </si>
-  <si>
-    <t>SEPH, IHE</t>
-  </si>
-  <si>
     <t>Apps de transporte</t>
   </si>
   <si>
-    <t>Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Puértolas</t>
-  </si>
-  <si>
-    <t>Cultura, Ayuntamiento</t>
-  </si>
-  <si>
     <t>Lourdes Naranjo</t>
   </si>
   <si>
@@ -325,15 +277,6 @@
     <t>Ricardo Calleja</t>
   </si>
   <si>
-    <t>Francisco Bautista</t>
-  </si>
-  <si>
-    <t>Actopan</t>
-  </si>
-  <si>
-    <t>Erika Gutiérrez</t>
-  </si>
-  <si>
     <t>Carmen Hernández</t>
   </si>
   <si>
@@ -343,655 +286,766 @@
     <t>Ana Luisa Vega</t>
   </si>
   <si>
-    <t>Combate Al Huachicol</t>
-  </si>
-  <si>
-    <t>Respaldaron padres restringir celulares</t>
-  </si>
-  <si>
-    <t>Padres de familia de primarias en Pachuca manifestaron su respaldo a las restricciones del uso de teléfonos celulares en planteles de educación básica, solicitando que la medida aplique también a docentes y se contemplen excepciones en emergencias.</t>
-  </si>
-  <si>
-    <t>Padres de familia en Pachuca apoyan la regulación de celulares en aulas de educación básica pero piden flexibilidad para casos de emergencia.</t>
-  </si>
-  <si>
-    <t>Luana Silva, Diego García, Erika Lara</t>
-  </si>
-  <si>
-    <t>Alumnos cuidarán la salud mental</t>
-  </si>
-  <si>
-    <t>Cerca de 300 estudiantes del CBTIS 222 se capacitaron como promotores de salud mental con la Secretaría de Salud de Hidalgo para identificar factores de riesgo y canalizar oportunamente a sus compañeros.</t>
-  </si>
-  <si>
-    <t>Salud Mental</t>
-  </si>
-  <si>
-    <t>Estudiantes del CBTIS 222 en Pachuca participan en una red de promotores juveniles de salud mental impulsada por la Secretaría de Salud de Hidalgo.</t>
-  </si>
-  <si>
     <t>SSH, SEPH</t>
   </si>
   <si>
-    <t>Vanesa Escalante Arroyo</t>
-  </si>
-  <si>
-    <t>Menchaca liga talento e inversión</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca conmemoró el aniversario de las universidades tecnológicas y politécnicas de Hidalgo, resaltando que la formación profesional de los jóvenes es clave para la atracción de inversiones al estado.</t>
-  </si>
-  <si>
-    <t>Aniversario Universidades</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca encabezó el Aniversario de Universidades Tecnológicas y Politécnicas, enfatizando el compromiso con la educación superior y el fortalecimiento económico.</t>
-  </si>
-  <si>
-    <t>Gobernador</t>
-  </si>
-  <si>
-    <t>Gobernador, SEPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo, Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Abre Artifex exposición de arte en Actopan</t>
-  </si>
-  <si>
-    <t>Abre sus puertas la galería Artifex en Actopan con la exposición de pinturas y obras de arte de los artistas Joel Trejo y Juan Ugalde, promoviendo el acceso cultural a la comunidad.</t>
-  </si>
-  <si>
-    <t>Exposición Artística</t>
-  </si>
-  <si>
-    <t>Abre en Actopan la galería comunitaria Artifex exhibiendo obras pictóricas de artistas plásticos regionales.</t>
-  </si>
-  <si>
-    <t>Omar Santiago</t>
-  </si>
-  <si>
-    <t>Darío Torres Durán, Joel Trejo, Juan Ugalde</t>
-  </si>
-  <si>
-    <t>Entidad avanza en salud, economía y en seguridad</t>
-  </si>
-  <si>
-    <t>El estado de Hidalgo llega a la medición 2026 del Índice de Competitividad Estatal con avances concretos en varios de los indicadores que impactan directamente en la economía y las condiciones de vida de la población, desde una mayor cobertura de internet y mejores resultados en algunos indicadores de salud.</t>
-  </si>
-  <si>
-    <t>Crecimiento Económico</t>
-  </si>
-  <si>
-    <t>El estado de Hidalgo registró avances en el Índice de Competitividad Estatal 2026 en rubros como salud, educación, conectividad e incremento del Producto Interno Bruto.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Con 14 politécnicas forman talento para nuevas generaciones</t>
-  </si>
-  <si>
-    <t>Las universidades tecnológicas y politécnicas de Hidalgo atienden actualmente a más de 33 mil estudiantes y se han convertido en uno de los vínculos entre la formación profesional y las necesidades del sector productivo, en un momento en que el estado reporta inversiones por 147 mil millones de pesos.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca destacó la red de 14 universidades politécnicas y tecnológicas que atienden a más de 33 mil alumnos con 48 laboratorios STEM en la entidad.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Natividad Castrejón, Guadalupe Ortiz Villafaña</t>
-  </si>
-  <si>
-    <t>Piden reducir uso individual de vehículo</t>
-  </si>
-  <si>
-    <t>En el Día Mundial Sin Automóvil, la Secretaría de Movilidad y Transporte de Hidalgo (Semot) llamó a reducir el uso individual del vehículo y fomentar alternativas como el transporte público, bicicletas o caminatas, respetando la jerarquía de movilidad.</t>
-  </si>
-  <si>
-    <t>Movilidad sustentable</t>
-  </si>
-  <si>
-    <t>En el marco del Día Mundial Sin Automóvil, la Semot promovió la reducción del uso de autos particulares y exhortó a priorizar al peatón y al transporte público.</t>
-  </si>
-  <si>
-    <t>Apoyan restricción de celulares</t>
-  </si>
-  <si>
-    <t>La presidenta del Sistema DIF en el estado de Hidalgo, Edda Vite Ramos, se pronunció a favor de la restricción de teléfonos celulares al interior de las instituciones de educación básica tras el acuerdo impulsado por la Secretaría de Educación Pública.</t>
-  </si>
-  <si>
-    <t>La titular del DIF Hidalgo, Edda Vite, respaldó la medida de regular los dispositivos celulares en las aulas para fomentar la convivencia escolar.</t>
-  </si>
-  <si>
-    <t>DIFH</t>
-  </si>
-  <si>
-    <t>DIFH, SEPH</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos</t>
-  </si>
-  <si>
-    <t>Retrocede la entidad siete posiciones en competitividad: IMCO</t>
-  </si>
-  <si>
-    <t>En el Índice de Competitividad Estatal (ICE) 2026, Hidalgo retrocedió siete posiciones respecto al año anterior, posicionándose en el lugar número 21 de las 32 entidades evaluadas por el IMCO con un puntaje de 42.75. El gobernador Julio Menchaca Salazar sostuvo que su administración trabaja para dar resultados.</t>
-  </si>
-  <si>
     <t>Atracción De Inversiones</t>
   </si>
   <si>
-    <t>Hidalgo cayó al lugar 21 nacional en el Índice de Competitividad Estatal 2026 del IMCO. El gobernador Julio Menchaca afirmó que atienden áreas de oportunidad ante limitaciones presupuestales.</t>
-  </si>
-  <si>
-    <t>Gobernador, Sedeco</t>
-  </si>
-  <si>
-    <t>Taxis de Pachuca lucen deteriorados</t>
-  </si>
-  <si>
-    <t>En dos viajes realizados en taxi por Pachuca, El Universal Hidalgo constató unidades con marcado deterioro físico y, en uno de los casos, percepción de olor a alcohol en el interior, además de cobros con tarifas arbitrarias antes de la implementación del nuevo esquema tarifario.</t>
-  </si>
-  <si>
-    <t>Crónica</t>
-  </si>
-  <si>
     <t>Tarifario de taxis</t>
   </si>
   <si>
-    <t>Un recorrido periodístico evidenció el deterioro de las unidades de taxi en Pachuca, operadores conduciendo con olor a alcohol y cobros dispares antes del nuevo tarifario.</t>
-  </si>
-  <si>
-    <t>Hidalgo será sede de la Olimpiada Nacional el próximo año</t>
-  </si>
-  <si>
-    <t>Hidalgo será una de las seis sedes de la Olimpiada Nacional 2027 (ON) y albergará a atletas de todo el país en la Ciudad Deportiva de Alto Rendimiento de Pachuca, según confirmó el titular de la Conade, Rommel Pacheco Marrufo.</t>
-  </si>
-  <si>
     <t>Nacionales Conade</t>
   </si>
   <si>
-    <t>La Conade confirmó que Hidalgo albergará competencias de la Olimpiada Nacional 2027 en la Ciudad Deportiva de Pachuca.</t>
-  </si>
-  <si>
-    <t>Rommel Pacheco Marrufo, Óscar Pérez Rojas, Claudia Sheinbaum</t>
-  </si>
-  <si>
-    <t>Trasladaron vía aérea a menor para que reciba atención médica</t>
-  </si>
-  <si>
-    <t>Un menor de un año originario de Pahactla, Atlapexco, fue trasladado vía aérea desde el Hospital General de la Huasteca hacia el Hospital del Niño DIF en Pachuca tras presentar un cuadro clínico de neumonía y cardiopatía congénita.</t>
-  </si>
-  <si>
-    <t>Atlapexco</t>
-  </si>
-  <si>
-    <t>Traslado Aéreo</t>
-  </si>
-  <si>
-    <t>Autoridades médicas de la SSH e IMSS-Bienestar coordinaron el traslado aéreo de un bebé de un año desde Huejutla al Hospital del Niño DIF en Pachuca.</t>
-  </si>
-  <si>
-    <t>SSH, DIFH, Presidencia</t>
-  </si>
-  <si>
-    <t>Hay 33 mil alumnos en planteles politécnicos y tecnológicos: SEPH</t>
-  </si>
-  <si>
-    <t>Más de 33 mil personas estudian en las ocho universidades tecnológicas y seis politécnicas de Hidalgo, instituciones que conmemoraron 35 y 25 años de creación en un evento encabezado por el gobernador Julio Menchaca Salazar y el titular de la SEPH, Natividad Castrejón Valdez.</t>
-  </si>
-  <si>
-    <t>Las universidades tecnológicas y politécnicas de Hidalgo festejaron sus aniversarios con una matrícula superior a 33 mil alumnos. La eficiencia terminal en educación superior alcanzó 84.5%.</t>
-  </si>
-  <si>
-    <t>SEPH, Gobernador</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Guadalupe Ortiz Villafaña, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Rehabilitación de Casa del Niño DIFH tiene 90% de avance</t>
-  </si>
-  <si>
-    <t>La remodelación de la Casa del Niño del Sistema DIF Hidalgo presenta un 90 por ciento de avance con una inversión cercana a 20 millones de pesos, informó Edda Vite Ramos, presidenta del Patronato del DIFH.</t>
-  </si>
-  <si>
-    <t>Asistencia social</t>
-  </si>
-  <si>
-    <t>La rehabilitación de la Casa del Niño DIFH registra 90% de avance e iniciará la fase de equipamiento e interiorismo con una inversión de 20 mdp.</t>
-  </si>
-  <si>
-    <t>La Contraloría estatal le canceló el registro a seis proveedores</t>
-  </si>
-  <si>
-    <t>La Secretaría de Contraloría de Hidalgo ordenó a dependencias y ayuntamientos abstenerse de contratar a seis personas físicas y morales a las que se les inhabilitó del Padrón de Proveedores por periodos de cinco a seis años tras procedimientos administrativos.</t>
-  </si>
-  <si>
     <t>Padrón de proveedores</t>
   </si>
   <si>
-    <t>La Secretaría de Contraloría sancionó a seis empresas y personas físicas retirándoles el registro de proveedores del estado por hasta seis años.</t>
-  </si>
-  <si>
     <t>Contraloría</t>
   </si>
   <si>
-    <t>Maritza Yazmín Estrada Ortiz, Lizbeth Pedraza Quijada, José Guillermo López Galindo, Laura Flores Méndez</t>
-  </si>
-  <si>
-    <t>Operadores ebrios causan accidentes</t>
-  </si>
-  <si>
-    <t>Choferes de transporte público de Tizayuca provocaron accidentes en estado de ebriedad, dejando un saldo de 13 lesionados al colisionar una colectiva contra un camión de volteo en el acceso a Fuentes de Tizayuca, además de la detención de otros conductores en estado inconveniente.</t>
-  </si>
-  <si>
-    <t>Tizayuca</t>
-  </si>
-  <si>
-    <t>Operadores del transporte público en Tizayuca causaron percances viales al conducir alcoholizados, registrándose 13 personas heridas en el choque de una colectiva.</t>
-  </si>
-  <si>
-    <t>Javier Quezada</t>
-  </si>
-  <si>
-    <t>Semot, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Exigen destitución del director del Tecnológico de Huejutla</t>
-  </si>
-  <si>
-    <t>Docentes y personal administrativo del Instituto Tecnológico de Huejutla se manifestaron con lonas para solicitar la destitución del director Evaristo Rogaciano López Hernández por incumplir acuerdos laborales y exceder el tiempo en el cargo.</t>
-  </si>
-  <si>
-    <t>Personal del Instituto Tecnológico de Huejutla colocó mantas para exigir la salida del director Evaristo Rogaciano López por presunto incumplimiento de acuerdos.</t>
-  </si>
-  <si>
-    <t>Evaristo Rogaciano López Hernández</t>
-  </si>
-  <si>
-    <t>Comienza la reforestación en Alfajayucan</t>
-  </si>
-  <si>
-    <t>La UMA del ejido Xothé inició jornadas de reforestación en el bosque de encino en Alfajayucan con la participación de ocho UMA regionales para favorecer la recarga de mantos acuíferos y preservar la biodiversidad, según informó la Semarnath.</t>
-  </si>
-  <si>
-    <t>Alfajayucan</t>
-  </si>
-  <si>
-    <t>Reforestación</t>
-  </si>
-  <si>
-    <t>Ocho Unidades de Manejo para la Conservación de la Vida Silvestre arrancaron labores de reforestación en Alfajayucan para beneficiar acuíferos locales.</t>
-  </si>
-  <si>
     <t>Semarnath</t>
   </si>
   <si>
-    <t>Semarnath, Semarnat, Profepa</t>
-  </si>
-  <si>
-    <t>Aumenta 14.9 puntos porcentuales la eficiencia terminal en universidades de la entidad</t>
-  </si>
-  <si>
-    <t>La eficiencia terminal en educación superior pasó de 69.6% a 84.5% en los primeros tres años del gobierno de Julio Menchaca Salazar, posicionando a Hidalgo en el sexto lugar nacional según datos de la ANUIES. Durante el 35 aniversario de las universidades tecnológicas y 25 de las politécnicas, se reconoció a más de 33 mil estudiantes.</t>
-  </si>
-  <si>
-    <t>Hidalgo incrementó 14.9 puntos porcentuales su eficiencia terminal en nivel superior durante la administración de Julio Menchaca, ubicándose en sexto lugar nacional.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Menchaca pide a su gabinete prepararse para comparecencias ante el Congreso</t>
-  </si>
-  <si>
-    <t>De cara a las comparecencias de los funcionarios del gabinete estatal ante el Congreso de Hidalgo, el gobernador Julio Menchaca Salazar afirmó que ha solicitado a los secretarios estudiar y prepararse. Asimismo, consideró viable la participación del Oficial Mayor, Edgar Orlando Ángeles Pérez, en la rendición de cuentas.</t>
-  </si>
-  <si>
-    <t>Comparecencias</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca llamó a los integrantes de su gabinete a prepararse para las comparecencias en el Congreso y respaldó la posible asistencia del Oficial Mayor.</t>
-  </si>
-  <si>
-    <t>Gobernador, Congreso, Oficialía Mayor, Segobh</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Edgar Orlando Ángeles Pérez, Rommel Pacheco</t>
-  </si>
-  <si>
-    <t>DIFH destina más de 640 mil pesos a becas PILARES</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos, presidenta del Patronato del Sistema DIF Hidalgo, entregó becas PILARES a 305 usuarios de 17 municipios de la región Pachuca. El programa beneficia a niñas, niños y adolescentes con un apoyo económico único de mil 200 pesos anuales, acumulando una inversión total de 640 mil 500 pesos en la zona.</t>
-  </si>
-  <si>
-    <t>Becas</t>
-  </si>
-  <si>
-    <t>El Sistema DIF Hidalgo distribuyó 640 mil pesos en becas PILARES a 305 estudiantes de 17 municipios para respaldar la economía familiar.</t>
-  </si>
-  <si>
-    <t>La FUTVEH, conforme con la tarifa de taxi</t>
-  </si>
-  <si>
-    <t>Tras la actualización de la tarifa de taxis a 45 pesos para los primeros cuatro kilómetros, el presidente de la Federación de Unión de Trabajadores del Volante del Estado de Hidalgo (FUTVEH), Eleno Arias Pérez, aseguró que están conformes; sin embargo, ellos buscaban que la cuota mínima se estableciera en 50 pesos.</t>
-  </si>
-  <si>
-    <t>Eleno Arias Pérez, líder de la FUTVEH, señaló que el sector está conforme con la tarifa mínima de 45 pesos fijada por la Semot, aunque la propuesta inicial del gremio era de 50 pesos.</t>
-  </si>
-  <si>
-    <t>Semot, FUTVEH</t>
-  </si>
-  <si>
-    <t>Eleno Arias Pérez, Lyzbeth Robles Gutiérrez</t>
-  </si>
-  <si>
-    <t>Buscan ampliar oferta educativa de la EMEH</t>
-  </si>
-  <si>
-    <t>Derivado del proceso de incorporación de la Escuela de Música del Estado de Hidalgo (EMEH) a la Secretaría de Educación Pública estatal, la dependencia trabaja en la creación de un nuevo sistema y una nueva oferta educativa con las características de una universidad politécnica y tecnológica; así lo dio a conocer el subsecretario Daniel Fragoso Torres.</t>
-  </si>
-  <si>
     <t>Oferta educativa</t>
   </si>
   <si>
-    <t>Tras la incorporación de la Escuela de Música del Estado de Hidalgo a la SEPH, se proyecta la creación de la licenciatura en Cinematografía, además de nuevas carreras en la UTVM y un Hospital-Escuela en Zacualtipán.</t>
-  </si>
-  <si>
-    <t>SEPH, EMEH, UTVM</t>
-  </si>
-  <si>
     <t>Daniel Fragoso Torres</t>
   </si>
   <si>
-    <t>Homologan los salarios en las universidades</t>
-  </si>
-  <si>
-    <t>El subsecretario de Educación Media Superior y Superior de Hidalgo, Daniel Fragoso Torres, señaló que, pese a que se logró una homologación salarial entre docentes de universidades politécnicas y tecnológicas, continúa pendiente que el incremento alcance una armonización con las percepciones de institutos tecnológicos federales.</t>
-  </si>
-  <si>
-    <t>Tabulador salarial</t>
-  </si>
-  <si>
-    <t>El subsecretario Daniel Fragoso Torres destacó la homologación de sueldos entre docentes de universidades politécnicas y tecnológicas en Hidalgo, aunque reconoció que subsiste una brecha respecto a tecnológicos federales.</t>
-  </si>
-  <si>
-    <t>Niño lesionado recibe cirugía y evoluciona favorablemente: DIF</t>
-  </si>
-  <si>
-    <t>El niño que resultó lesionado por una llama durante una presentación con una flauta ancestral en la ceremonia de abanderamiento de la delegación estatal de paratletas fue intervenido mediante cirugía plástica y presenta una evolución favorable, informó la presidenta del Patronato del DIF Hidalgo, Edda Vite Ramos.</t>
-  </si>
-  <si>
-    <t>Atención médica</t>
-  </si>
-  <si>
-    <t>La presidenta del Patronato del DIF Hidalgo, Edda Vite Ramos, informó que el niño lesionado en la Ciudad Deportiva de Alto Rendimiento fue operado de manera gratuita en el Hospital del Niño DIF y muestra evolución estable.</t>
-  </si>
-  <si>
-    <t>Lizania Zavala</t>
-  </si>
-  <si>
-    <t>Protestas en informes, parte de la democracia: Menchaca</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, descartó que haya faltado trabajo político y de conciliación a los presidentes municipales de la entidad, luego de las manifestaciones que se registraron durante los informes de algunos alcaldes, considerando que forman parte de la libertad de expresión.</t>
-  </si>
-  <si>
-    <t>Gobernabilidad</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar calificó las protestas registradas durante rendiciones de cuentas municipales como expresiones democráticas e hizo un llamado a conducirse dentro del marco del respeto e integridad.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Yeymi Yadira Solís Zavala, Christian Evanivaldo Martínez Reséndiz</t>
-  </si>
-  <si>
-    <t>Secretarios deben estudiar para rendir cuentas: JMS</t>
-  </si>
-  <si>
-    <t>Para las comparecencias de este año, el gobernador de Hidalgo, Julio Menchaca Salazar, llamó a los titulares de las diferentes secretarías a prepararse y estudiar para que la rendición de cuentas se desarrolle de buena manera ante las y los legisladores, como parte de la glosa del cuarto año.</t>
-  </si>
-  <si>
-    <t>De cara a la glosa del cuarto año de gobierno, Julio Menchaca pidió a los integrantes del gabinete estatal prepararse ampliamente para las comparecencias e indicó un acuerdo para que el Oficial Mayor rinda cuentas ante el Congreso.</t>
-  </si>
-  <si>
-    <t>Gobernador, Oficialía Mayor, Congreso</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Edgar Orlando Ángeles Pérez</t>
-  </si>
-  <si>
-    <t>Entrega el DIF Hidalgo 305 becas Pilares a estudiantes</t>
-  </si>
-  <si>
-    <t>Este martes fueron entregadas las becas Pilares 2026 a 305 usuarias y usuarios de 17 municipios pertenecientes a la región Pachuca. Durante el acto, Edda Vite Ramos afirmó que esta beca contribuye a superar obstáculos y apoyar necesidades como útiles y transporte.</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos entregó apoyos económicos anuales de mil 200 pesos del programa Pilares a 305 niñas, niños y adolescentes de 17 municipios de la zona Pachuca, con un presupuesto invertido de 640 mil pesos.</t>
-  </si>
-  <si>
-    <t>Preparan jornada educativa en Hidalgo</t>
-  </si>
-  <si>
-    <t>Más de 6 mil escuelas de Educación Básica de Hidalgo participarán en la Primera Sesión Ordinaria del Consejo Técnico Escolar (CTE) del ciclo 2026-2027, programada para el próximo 25 de septiembre, con la participación de más de 38 mil figuras educativas.</t>
-  </si>
-  <si>
-    <t>Consejo Técnico</t>
-  </si>
-  <si>
-    <t>Más de 38 mil docentes de 6 mil escuelas de educación básica en Hidalgo participarán el próximo 25 de septiembre en la primera sesión ordinaria del Consejo Técnico Escolar del ciclo lectivo 2026-2027.</t>
-  </si>
-  <si>
-    <t>Nancy Adriana León Vite, Leobardo Cano Albarrán, Bonny Lizeth Rivera Arrieta</t>
-  </si>
-  <si>
-    <t>Reconocen necesidad de actualizar tarifa de taxis</t>
-  </si>
-  <si>
-    <t>El dirigente de la Confederación de Transportistas Metropolitanos de Hidalgo (CTMH), Apolinar Ávila González, estimó que en Tulancingo la tarifa del servicio de taxi no se ha actualizado desde hace más de una década, por lo que respaldó una regulación ajustada.</t>
-  </si>
-  <si>
     <t>Tulancingo</t>
   </si>
   <si>
-    <t>Apolinar Ávila, dirigente de la CTMH, señaló que en Tulancingo el costo del taxi no se actualiza desde hace diez años y adelantó que enviarán un estudio a la Semot para solicitar mesas de ajuste tarifario.</t>
-  </si>
-  <si>
     <t>María Antonieta Islas</t>
   </si>
   <si>
-    <t>Semot, CTMH</t>
-  </si>
-  <si>
-    <t>Apolinar Ávila González, Lyzbeth Robles Gutiérrez</t>
-  </si>
-  <si>
-    <t>Impresos locales</t>
-  </si>
-  <si>
-    <t>Oficial mayor debería comparecer; es decisión del Congreso: Menchaca</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar señaló que el oficial mayor Orlando Ángeles Pérez debería participar en las comparecencias ante el Congreso local para informar sobre las compras estatales. Asimismo, solicitó a los secretarios prepararse para presentar sus informes en octubre y pidió que las manifestaciones ciudadanas por informes municipales se realicen con respeto dentro del orden democrático.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca precisó que el oficial mayor Orlando Ángeles Pérez debería comparecer ante el Congreso para detallar las compras del estado, solicitando además a los secretarios estudiar para sus informes de octubre.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Congreso, Segobh</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Orlando Ángeles Pérez</t>
-  </si>
-  <si>
-    <t>Celebran creación de las politécnicas y tecnológicas</t>
-  </si>
-  <si>
-    <t>En el marco de la conmemoración del 35 aniversario de las universidades tecnológicas y 25 de las politécnicas en el estado, el titular de la SEPH, Natividad Castrejón, resaltó el incremento de la eficiencia terminal de 69.9% a 84.5%, situando a Hidalgo en sexto lugar nacional. Además, se anunció la transición de la Escuela de Música del Estado de Hidalgo (EMEH) al subsistema tecnológico o politécnico.</t>
-  </si>
-  <si>
-    <t>Hidalgo conmemoró el aniversario de sus universidades tecnológicas y politécnicas destacando un aumento de eficiencia terminal al 84.5% y la transición de la EMEH al subsistema tecnológico.</t>
-  </si>
-  <si>
-    <t>SEPH, UTTT, EMEH</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Julio Menchaca Salazar, Daniel Fragoso, Guadalupe Ortiz Villafaña</t>
-  </si>
-  <si>
-    <t>Tesoros Vivos entregará cinco estímulos de 80 mil pesos</t>
-  </si>
-  <si>
-    <t>El Gobierno del Estado de Hidalgo, a través de la Secretaría de Cultura, convoca a postular a personas portadoras de saberes tradicionales al programa Tesoros Vivos. Premio Guardián del Patrimonio Hidalguense 2026, que premiará con una bolsa de 400 mil pesos en cinco estímulos de 80 mil pesos a cultores con trayectoria mínima de 15 años.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura convocó a portadores de saberes tradicionales al programa Tesoros Vivos 2026 para entregar cinco premios de 80 mil pesos.</t>
-  </si>
-  <si>
-    <t>SSH integra equipo de jóvenes para prevenir la salud mental</t>
-  </si>
-  <si>
-    <t>Alrededor de 300 estudiantes del CBTIS 222 se convirtieron en aliados de la prevención de la salud mental bajo la estrategia Cambiando la Narrativa, articulada con la campaña nacional El ABC de las emociones impulsada por la Secretaría de Salud de Hidalgo para identificar conductas de riesgo.</t>
-  </si>
-  <si>
-    <t>Alrededor de 300 estudiantes del CBTIS 222 se capacitaron como aliados en salud mental bajo la estrategia El ABC de las emociones para identificar conductas de riesgo.</t>
-  </si>
-  <si>
-    <t>Diana Reyes Gómez</t>
-  </si>
-  <si>
-    <t>Ya disponibles los resultados de “Titúlate 2026”</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social y el Inhjuve informaron que están disponibles los resultados de la convocatoria Titúlate 2026 para jóvenes en proceso de titulación universitaria, quienes pueden consultar su estatus mediante la CURP en el portal oficial.</t>
-  </si>
-  <si>
-    <t>Apoyo para titulación</t>
-  </si>
-  <si>
-    <t>La Sebiso e Inhjuve publicaron los resultados del programa Titúlate 2026 para apoyar económicamente a egresados universitarios.</t>
-  </si>
-  <si>
-    <t>Sebiso, Inhjuve</t>
-  </si>
-  <si>
-    <t>Ricardo Olvera Molina, Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Brinda DIF becas para apoyar la economía familiar</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos, presidenta del Patronato del Sistema DIF Hidalgo, encabezó la entrega de becas PILARES 2026 a 305 niños y adolescentes de 17 municipios de la región Pachuca, otorgando apoyos anuales de 1,200 pesos con un presupuesto de 640 mil pesos.</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos entregó becas PILARES por 1,200 pesos a 305 estudiantes de 17 municipios de la región Pachuca.</t>
-  </si>
-  <si>
-    <t>Alerta Delegación de Programas para el Bienestar de fraude</t>
-  </si>
-  <si>
-    <t>La Delegación de Programas para el Bienestar en Hidalgo alertó sobre mensajes apócrifos difundidos en WhatsApp donde se pide a beneficiarios actualizar sus datos para presuntamente despojarlos de información personal.</t>
-  </si>
-  <si>
-    <t>Alerta De Fraude</t>
-  </si>
-  <si>
-    <t>La Delegación de Programas para el Bienestar alertó sobre intentos de fraude por WhatsApp que piden actualizar datos a beneficiarios.</t>
-  </si>
-  <si>
-    <t>Resultados del ICE 2026 muestran áreas de oportunidad: Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Ante la caída de Hidalgo en el Índice de Competitividad Estatal 2026 del IMCO al puesto 21, el gobernador Julio Menchaca afirmó que los señalamientos de la oposición se centran en lo negativo, pero su administración atiende los rezagos históricos.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca sostuvo que los resultados del IMCO señalan áreas de oportunidad que se atienden con trabajo presupuestal.</t>
-  </si>
-  <si>
-    <t>IMCO, Gobernador</t>
-  </si>
-  <si>
-    <t>Impresionante operativo policiaco por huachicol en Teocalco</t>
-  </si>
-  <si>
-    <t>Un despliegue de patrullas del Mando Coordinado y Policía Estatal alarmó a pobladores de Teocalco en Tula de Allende por presuntas maniobras ilegales de trasiego de hidrocarburo cerca de ductos de Pemex.</t>
-  </si>
-  <si>
-    <t>Operativo de la SSPH patrulló bodegas y ductos de Pemex en Teocalco, Tula, para combatir el robo de combustible.</t>
-  </si>
-  <si>
-    <t>SSPH, Pemex</t>
-  </si>
-  <si>
-    <t>Salvador Cruz Neri</t>
-  </si>
-  <si>
-    <t>Una colectiva chocó con un tráiler y 12 personas resultaron lesionadas</t>
-  </si>
-  <si>
-    <t>Protección Civil y la Secretaría de Seguridad de Tizayuca atendieron un choque entre una Urvan del transporte público y un tráiler en la México-Pachuca, dejando saldo de 12 pasajeros trasladados a clínicas.</t>
-  </si>
-  <si>
-    <t>Accidente sobre la carretera México-Pachuca entre colectiva y tractocamión dejó 12 heridos en Tizayuca.</t>
-  </si>
-  <si>
-    <t>PC, Cruz Roja</t>
-  </si>
-  <si>
-    <t>Traslado aéreo de bebé, por neumonía y cardiopatía congénita</t>
-  </si>
-  <si>
-    <t>Un bebé de un año gravemente enfermo fue trasladado en el helicóptero Bell 429 desde la Huasteca al Hospital del Niño DIF Pachuca por coordinación de la SSH y Despacho del Gobernador.</t>
-  </si>
-  <si>
-    <t>Coordinación interinstitucional logró el traslado aéreo urgente de un lactante desde Atlapexco hacia el Hospital del Niño DIF.</t>
-  </si>
-  <si>
-    <t>SSH, DIFH</t>
-  </si>
-  <si>
-    <t>GOBERNADOR AVALA QUE COMPAREZCA EL OFICIAL MAYOR</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca consideró viable que el titular de la Oficialía Mayor, Édgar Orlando Ángeles Pérez, comparezca ante el Congreso para rendir cuentas sobre contratos, licitaciones y manejo presupuestal.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca avaló la comparecencia del oficial mayor Édgar Ángeles Pérez ante el Congreso.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor, Congreso</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Édgar Orlando Ángeles Pérez</t>
-  </si>
-  <si>
-    <t>SIN RUTA PARA PERMITIR APP DE TRANSPORTE EN HIDALGO</t>
-  </si>
-  <si>
-    <t>Plataformas como Uber, DiDi e InDrive continúan sin autorización para prestar servicio en Hidalgo al no existir iniciativas legislativas en el Congreso local. Menchaca respaldó la regulación prioritaria a taxis.</t>
-  </si>
-  <si>
-    <t>Congreso y Gobierno de Hidalgo no contemplan reformas para autorizar el servicio de plataformas privadas como Uber o DiDi.</t>
-  </si>
-  <si>
-    <t>Semot, Congreso</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Juan Pablo Escalante Urbán</t>
-  </si>
-  <si>
-    <t>VAN A DEMOLER PRIMARIA EN TULANCINGO; EDIFICARÁN OTRA</t>
-  </si>
-  <si>
-    <t>La SEPH anunció que la primaria Aquiles Serdán de Tulancingo será demolida y edificada de nuevo por daños en su estructura, previendo obras durante el ciclo 2026-2027.</t>
-  </si>
-  <si>
     <t>Reconstrucción de escuela</t>
   </si>
   <si>
-    <t>La SEPH tirará y reconstruirá la primaria Aquiles Serdán en Tulancingo tras diagnosticar fallas de estructura.</t>
+    <t>Nuevas tarifas de taxis ya se aplican</t>
+  </si>
+  <si>
+    <t>Tras la publicación del acuerdo en el Periódico Oficial del Estado de Hidalgo, el aumento de 20% en las tarifas de taxis en Pachuca y Mineral de la Reforma entró en vigor ayer. De acuerdo con el tarifario, un traslado del Reloj Monumental a la Feria tiene un costo de 77 pesos.</t>
+  </si>
+  <si>
+    <t>Entró en vigor el incremento del 20% en las tarifas de taxis para Pachuca y Mineral de la Reforma tras su publicación en el POEH, fijando el banderazo mínimo en 45 pesos.</t>
+  </si>
+  <si>
+    <t>Semot, STCH</t>
+  </si>
+  <si>
+    <t>Desmiente Ice Dreams a la feria de Pachuca</t>
+  </si>
+  <si>
+    <t>La compañía informó que no se presentará en la Feria San Francisco Pachuca 2026 y se deslindó del espectáculo Raíces del Mundo, anunciado en las cuentas oficiales del evento. Señaló que se utilizaron fotografías de sus patinadores sin autorización, algunas alteradas con Inteligencia Artificial.</t>
+  </si>
+  <si>
+    <t>Feria Pachuca</t>
+  </si>
+  <si>
+    <t>La empresa Ice Dreams México aclaró que no participará en la Feria San Francisco Pachuca 2026 y denunció el uso no autorizado de imágenes de sus integrantes en la promoción oficial.</t>
+  </si>
+  <si>
+    <t>Turismo</t>
+  </si>
+  <si>
+    <t>Turismo, OEEH</t>
+  </si>
+  <si>
+    <t>Asesoran a jóvenes para prevenir suicidio</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo reforzó las acciones dirigidas a jóvenes para que puedan identificar conductas de riesgo y construyan redes de apoyo entre compañeros. La estrategia incluye actividades en planteles educativos, mientras que las autoridades difunden las señales de alerta y ponen a disposición la Línea de la Vida.</t>
+  </si>
+  <si>
+    <t>Prevención del suicidio</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo lleva a cabo talleres y capacitaciones en escuelas para prevenir el suicidio juvenil mediante la identificación oportuna de factores de riesgo.</t>
+  </si>
+  <si>
+    <t>Colillas y envases, los residuos predominantes en las costas</t>
+  </si>
+  <si>
+    <t>Millones de kilogramos de basura fueron recogidos y eliminados por voluntarios en regiones costeras de todo el mundo en 2021. De acuerdo con la organización estadounidense sin fines de lucro Ocean Conservancy, la basura en las playas y otros centros recreativos aumenta año con año.</t>
+  </si>
+  <si>
+    <t>Protección ambiental</t>
+  </si>
+  <si>
+    <t>Datos de Ocean Conservancy revelan que las colillas de cigarro, envoltorios de comida y botellas de plástico representan los principales contaminantes recolectados en zonas costeras.</t>
+  </si>
+  <si>
+    <t>Tarifa de agua sube 14.08% en 3 años</t>
+  </si>
+  <si>
+    <t>Del 2023 al 2026 la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (Caasim) ha incrementado en 14.08% el suministro de agua tipo doméstico, cuyo costo mínimo era de 35.81 pesos en 2023 a 54.93 en 2026.</t>
+  </si>
+  <si>
+    <t>Tarifa Caasim</t>
+  </si>
+  <si>
+    <t>La tarifa básica de suministro doméstico de agua potable de Caasim acumula un incremento del 14.08% en tres años en los 14 municipios atendidos.</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Caasim, Sipdus</t>
+  </si>
+  <si>
+    <t>Sin casos activos de barrenador</t>
+  </si>
+  <si>
+    <t>Tras acumular mil 376 contagios de gusano barrenador en animales tras cuatro meses del primer infectado, Hidalgo dejó de figurar entre las entidades con casos activos de esta plaga, de acuerdo con el reporte más reciente del Servicio Nacional de Sanidad, Inocuidad y Calidad Agroalimentaria (Senasica).</t>
+  </si>
+  <si>
+    <t>Gusano barrenador</t>
+  </si>
+  <si>
+    <t>Senasica confirmó que Hidalgo ya no presenta casos activos de gusano barrenador en ganado tras haber registrado 1,376 contagios en meses anteriores.</t>
+  </si>
+  <si>
+    <t>Alma Leticia Sánchez</t>
+  </si>
+  <si>
+    <t>Saderh</t>
+  </si>
+  <si>
+    <t>Senasica, Saderh</t>
+  </si>
+  <si>
+    <t>Por Feria se aplican operativo de transporte</t>
+  </si>
+  <si>
+    <t>Con motivo de la Feria de San Francisco Pachuca Hidalgo 2026, la Secretaría de Movilidad y Transporte de Hidalgo (Semoth) realizará operativos especiales del jueves 24 de septiembre al domingo 18 de octubre, con el objetivo de garantizar la movilidad y un servicio de transporte accesible.</t>
+  </si>
+  <si>
+    <t>Operativo de transporte</t>
+  </si>
+  <si>
+    <t>La Semot puso en marcha operativos de transporte especial y bases temporales de taxis para dar servicio nocturno continuo durante la Feria de Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah, STCH</t>
+  </si>
+  <si>
+    <t>Cobro puede aumentar por el tráfico, choferes</t>
+  </si>
+  <si>
+    <t>Tras la publicación del nuevo tarifario de taxis en el Periódico Oficial del Estado de Hidalgo (POEH), operadores en Pachuca y Mineral de la Reforma pidieron a los usuarios considerar el tiempo que permanecen en el tráfico y a la Secretaría de Movilidad y Transporte (Semoth) aclarar cómo será el proceso para la instalación de los taxímetros físicos.</t>
+  </si>
+  <si>
+    <t>Taxistas de Pachuca señalaron que el tráfico vehicular genera cobros adicionales por minutos de espera y urgieron a la Semot a clarificar la transición hacia taxímetros digitales.</t>
+  </si>
+  <si>
+    <t>Germán Carrasco</t>
+  </si>
+  <si>
+    <t>Continúa retiro de material en la Tenango-Metepec</t>
+  </si>
+  <si>
+    <t>Las labores de atención y supervisión vial se mantienen de manera constante sobre la carretera estatal Tenango-Metepec, previo al Arco de Bienvenida de Tenango de Doria, donde se retira material derivado de deslaves provocados por lluvias. Protección Civil mantiene monitoreo del terreno y pide extremar precauciones.</t>
+  </si>
+  <si>
+    <t>Tenango de Doria</t>
+  </si>
+  <si>
+    <t>Deslaves por lluvias</t>
+  </si>
+  <si>
+    <t>Autoridades y Protección Civil mantienen trabajos con maquinaria pesada en la carretera estatal Tenango-Metepec para retirar el material acumulado por derrumbes tras las recientes lluvias.</t>
+  </si>
+  <si>
+    <t>Nathali González</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Entra en vigor nueva tarifa de taxis; banderazo será de $45</t>
+  </si>
+  <si>
+    <t>El Sistema de Transporte Convencional de Hidalgo publicó en el POEH la actualización de la tarifa del transporte individual (taxi) para Pachuca y Mineral de la Reforma. El banderazo ordinario será de 45 pesos más 4 pesos por kilómetro adicional, con incremento nocturno del 20%. Concesionarios tendrán 120 días para instalar taxímetros digitales.</t>
+  </si>
+  <si>
+    <t>Entró en vigor el incremento tarifario de taxis en Pachuca y Mineral de la Reforma fijando la bajada de bandera en 45 pesos, estableciendo la obligación de implementar taxímetros digitales en 120 días.</t>
+  </si>
+  <si>
+    <t>Portada</t>
+  </si>
+  <si>
+    <t>STCH</t>
+  </si>
+  <si>
+    <t>Hidalgo suma 269 homicidios de enero a agosto de este año</t>
+  </si>
+  <si>
+    <t>El Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública documentó que Hidalgo acumuló 269 homicidios (131 dolosos y 138 culposos) en los primeros ocho meses de 2026. Además, se contabilizaron 6 mil 949 delitos contra la vida e integridad corporal, dos feminicidios y seis secuestros extorsivos.</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>Cifras del SESNSP revelan que Hidalgo acumuló 269 homicidios y dos feminicidios en los primeros ocho meses de 2026, concentrando la mayoría de muertes culposas en percances de tránsito.</t>
+  </si>
+  <si>
+    <t>Dulce Castillo</t>
+  </si>
+  <si>
+    <t>PGJEH</t>
+  </si>
+  <si>
+    <t>SESNSP</t>
+  </si>
+  <si>
+    <t>Sin alza en tres años, la Feria de Pachuca apuesta por patrocinios</t>
+  </si>
+  <si>
+    <t>El titular de la Operadora de Eventos del Estado de Hidalgo, Marco Antonio Aranzábal Juárez, ratificó que el boleto de entrada a la Feria de San Francisco Pachuca 2026 costará 60 pesos por tercer año consecutivo. La sostenibilidad del costo se logró mediante patrocinios privados y concesión del polígono ferial por recintos.</t>
+  </si>
+  <si>
+    <t>La Feria de San Francisco Pachuca 2026 conservará por tercer año consecutivo la tarifa de 60 pesos en su boleto de entrada, financiada mediante esquemas de patrocinio comercial y alianzas estratégicas.</t>
+  </si>
+  <si>
+    <t>OEEH, SSPH, Cofepris, SSH, Profeco, CDHEH</t>
+  </si>
+  <si>
+    <t>Marco Antonio Aranzábal Juárez, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Destruyen huachitúnel en comunidad de Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>El secretario de Gobierno, Guillermo Olivares Reyna, supervisó la destrucción del huachitúnel número 17 en Teocalco, municipio de Tlaxcoapan. La estructura rústica de 143 metros de longitud pasaba por debajo de carreteras y vías de ferrocarril conectando con el poliducto de Pemex. Con esto suman 16 huachitúneles inhabilitados en el sexenio.</t>
+  </si>
+  <si>
+    <t>Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>Huachitúnel</t>
+  </si>
+  <si>
+    <t>Autoridades estatales, federales y Pemex clausuraron un huachitúnel de 143 metros de longitud en Tlaxcoapan, sumando 16 estructuras subterráneas invalidadas durante la presente administración.</t>
+  </si>
+  <si>
+    <t>Joselyn Sánchez</t>
+  </si>
+  <si>
+    <t>Presidencia, Pemex, GN, Sedena, Ferromex, PC</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna, Román Bernal Díaz, Jaime Álvarez Solís, Juan Pablo Velázquez</t>
+  </si>
+  <si>
+    <t>Acción ambiental</t>
+  </si>
+  <si>
+    <t>El ayuntamiento de Pachuca y Semarnath invitan al acopio de pilas y reforestación en la unidad deportiva de la colonia Carlo Rovirosa, de 9:00 a 16:00 horas. ¡Cada pila cuenta, cada acción protege!</t>
+  </si>
+  <si>
+    <t>Boletín</t>
+  </si>
+  <si>
+    <t>El Ayuntamiento de Pachuca y Semarnath invitan a la ciudadanía al acopio de pilas y jornadas de reforestación en la unidad deportiva de la colonia Carlo Rovirosa.</t>
+  </si>
+  <si>
+    <t>Semarnath, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Es oficial, sube 20% tarifa inicial de taxis en la capital</t>
+  </si>
+  <si>
+    <t>Desde ayer 23 de septiembre entró en vigor la nueva tarifa para el transporte público individual, taxi, en Pachuca y Mineral de la Reforma, de acuerdo con el acuerdo publicado por el Sistema de Transporte Convencional de Hidalgo (STCH) en el Periódico Oficial del Estado de Hidalgo. El documento establece una primera etapa de transición con un incremento de 20 por ciento respecto a la tarifa anterior. El banderazo pasó de 38.50 a 45 pesos, correspondiente a los primeros cuatro kilómetros, mientras que el costo por kilómetro adicional aumentó de tres a cuatro pesos, según se informó. Además, se estableció un plazo de 120 días hábiles, a partir del 23 de septiembre, para que los taxis se incorporen al dispositivo físico de taxímetro digital. Este sistema contempla un cobro adicional por tiempo de espera o baja velocidad: un peso por cada 150 metros recorridos en 60 segundos o cuando la unidad circule a menos de 15 kilómetros por hora. De acuerdo con el esquema, este aumento permite elevar el costo de los recorridos cuando las unidades permanecen detenidas o avanzan lentamente debido al tránsito. El STCH sostiene que la medida busca regular las demoras provocadas por congestión vial y tiempos de espera, además de modernizar el servicio. El acuerdo señala que los taxímetros deberán contar con las certificaciones correspondientes y ser instalados por proveedores aprobados por el STCH. Una vez concluido el plazo, la falta de instalación, así como la manipulación o alteración del dispositivo, será motivo de sanciones. A partir de este miércoles, los operadores también deben ajustarse al tarifario oficial, que contempla 12 destinos frecuentes y más de 80 puntos de origen en Pachuca y Mineral de la Reforma. El STCH también reforzó las obligaciones para concesionarios y conductores, entre ellas cobrar las tarifas autorizadas, obtener el tarifario, participar en programas de capacitación, mantener vigente la póliza de seguro y garantizar las condiciones físico-mecánicas de las unidades. Los operadores deberán portar en un sitio visible el tarjetón de conductor, someter las unidades a inspección, mantener libres de obstrucciones los parabrisas y ventanillas y respetar disposiciones sobre iluminación y sonido al interior de los vehículos. El acuerdo también contempla un incremento de 20 por ciento en la tarifa durante el horario nocturno, de las 00:01 a las 04:59 horas. Durante el resto del día, de las 05:00 a las 24:00 horas, se aplicará la tarifa ordinaria. El nuevo esquema también busca reducir la discrecionalidad en el cobro, ya que los operadores deberán sujetarse a las tarifas.</t>
+  </si>
+  <si>
+    <t>Entró en vigor el incremento del 20% en la tarifa inicial de taxis para Pachuca y Mineral de la Reforma, fijando el banderazo mínimo en 45 pesos y otorgando 120 días para la instalación obligatoria de taxímetros digitales.</t>
+  </si>
+  <si>
+    <t>Teodoro Santos</t>
+  </si>
+  <si>
+    <t>Descartan aumento al precio de la tortilla</t>
+  </si>
+  <si>
+    <t>El kilo de tortilla se mantendrá en 25 pesos en el estado de Hidalgo, luego de que la Secretaría de Agricultura y Desarrollo Rural (Sader) señaló que existe suficiente maíz blanco para atender la demanda de la industria y que el reciente incremento en el precio del grano tendría un impacto limitado en el producto final. En las últimas cuatro semanas, la tonelada de maíz registró un aumento de 400 pesos, equivalente a 6 por ciento, pero, de acuerdo con las estimaciones de la dependencia, esto representa una variación aproximada de 28 centavos en el precio de un kilogramo de tortilla. En julio de 2025 fue firmado el Acuerdo Nacional Maíz-Tortilla, con el objetivo de contener incrementos en el precio del alimento. Desde entonces, el valor de la tonelada de maíz llegó a disminuir de alrededor de 6 mil 800 a 5 mil pesos en algunas regiones. Con la llegada del otoño y el inicio de la cosecha, se espera una mayor disponibilidad del grano. La Sader señaló que, al noveno mes del año, los inventarios de maíz blanco permiten cubrir la demanda de la industria, por lo que no existen condiciones para justificar un incremento en el precio de la tortilla. Un recorrido por tortillerías de la zona metropolitana de Pachuca confirmó que el precio se mantiene en 25 pesos por kilo. En algunos mercados también se conserva este costo para las tortillas hechas a mano, debido a que el ajuste en el precio del maíz aún no se refleja de manera significativa en el valor de la masa. La Sader señaló que, al noveno mes del año, los inventarios de maíz blanco permiten cubrir la demanda de la industria, por lo que no existen condiciones para justificar un incremento en el precio de la tortilla. Para finales de octubre comenzará la cosecha nacional del ciclo primavera-verano. La Sader aseguró que hay suficiente maíz blanco para cubrir la demanda de la industria y evitar un alza en el alimento.</t>
+  </si>
+  <si>
+    <t>Canasta básica</t>
+  </si>
+  <si>
+    <t>La Sader descartó un alza en el precio de la tortilla en Hidalgo, confirmando que el costo se mantendrá en 25 pesos por kilogramo gracias al abasto suficiente de maíz blanco en los inventarios nacionales.</t>
+  </si>
+  <si>
+    <t>Miriam Avilés</t>
+  </si>
+  <si>
+    <t>Saderh, Presidencia</t>
+  </si>
+  <si>
+    <t>Incremento a tarifas de taxis entró en vigor</t>
+  </si>
+  <si>
+    <t>Publican acuerdo del STCH en el POEH fijando la tarifa mínima en 45 pesos para Pachuca y Mineral de la Reforma, con la obligación de instalar taxímetros en 120 días.</t>
+  </si>
+  <si>
+    <t>Entra en vigor el nuevo tarifario de taxis en la zona metropolitana de Pachuca estableciendo un banderazo mínimo de 45 pesos e incremento nocturno del 20%.</t>
+  </si>
+  <si>
+    <t>Amarra Hidalgo sede de Olimpiada</t>
+  </si>
+  <si>
+    <t>Hidalgo albergará la competencia Orgullo Nacional 2027, la contienda deportiva infantil y juvenil más importante del país, anunciaron el gobernador Menchaca y Rommel Pacheco.</t>
+  </si>
+  <si>
+    <t>Anuncian que Hidalgo será la sede principal de la Olimpiada Nacional Orgullo Nacional 2027 en coordinación entre el gobierno estatal y la Conade.</t>
+  </si>
+  <si>
+    <t>SEPH, Gobernador, Inhide</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Rommel Pacheco</t>
+  </si>
+  <si>
+    <t>Implementará la SSPH operativo en la Feria</t>
+  </si>
+  <si>
+    <t>La SSPH desplegará un operativo de vigilancia con Policía Estatal, C5i, Bomberos y Tránsito dentro y fuera del recinto ferial San Francisco Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>La SSPH dispondrá un operativo de seguridad permanente con patrullajes, videovigilancia del C5i y módulos de bomberos durante la Feria de San Francisco 2026.</t>
+  </si>
+  <si>
+    <t>SSPH, C5i, Bomberos, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Violencia familiar, el delito más recurrente</t>
+  </si>
+  <si>
+    <t>Pachuca acumuló 854 denuncias por violencia familiar de enero a julio de 2026, superando al fraude y las amenazas, señala reporte del SESNSP analizado por la UAEH.</t>
+  </si>
+  <si>
+    <t>Violencia familiar</t>
+  </si>
+  <si>
+    <t>Reporte del SESNSP ubica a la violencia familiar como el delito de mayor incidencia en Pachuca durante los primeros siete meses del año con 854 carpetas.</t>
+  </si>
+  <si>
+    <t>PGJEH, Presidencia, UAEH</t>
+  </si>
+  <si>
+    <t>Gloria Contreras Jiménez</t>
+  </si>
+  <si>
+    <t>Prevén cambio de modelo para la Escuela de Música</t>
+  </si>
+  <si>
+    <t>La SEPH proyecta integrar a la EMEH dentro del subsistema de universidades politécnicas-tecnológicas al sumar licenciaturas como Cinematografía y posgrados.</t>
+  </si>
+  <si>
+    <t>La SEPH analiza reestructurar el modelo educativo de la Escuela de Música de Hidalgo para incorporarla al sistema de universidades politécnicas y tecnológicas.</t>
+  </si>
+  <si>
+    <t>SEPH, EMEH</t>
+  </si>
+  <si>
+    <t>Huachitúnel de 143 metros, destruido</t>
+  </si>
+  <si>
+    <t>Autoridades federales y estatales destruyeron un túnel huachicolero de 143 metros de largo en Teocalco, Tlaxcoapan. Suman 17 túneles inhabilitados en 2026.</t>
+  </si>
+  <si>
+    <t>Quedó destruido un pasadizo de 143 metros utilizado para el robo de hidrocarburo en Teocalco, Tlaxcoapan, alcanzando 17 túneles inhabilitados de junio a septiembre en Hidalgo.</t>
+  </si>
+  <si>
+    <t>FGR, Pemex, PGJEH, SSPH, Segobh, Ferromex</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna</t>
+  </si>
+  <si>
+    <t>Hidalgo será sede del Campeonato de Boccia 2026 y la Olimpiada Nacional 2027</t>
+  </si>
+  <si>
+    <t>Hidalgo será una de las seis sedes de la Olimpiada Nacional 2027, confirmó Rommel Pacheco, director de la Comisión Nacional de Cultura Física y Deporte (Conade), durante una conferencia de prensa realizada con motivo del anuncio del Campeonato Centroamericano y del Caribe de Boccia 2026. La entidad compartirá la sede de esta justa multidisciplinaria con Coahuila, Veracruz, Tamaulipas, Oaxaca y la UNAM.</t>
+  </si>
+  <si>
+    <t>Rommel Pacheco, titular de la Conade, anunció que Hidalgo albergará la Olimpiada Nacional 2027 y el Campeonato Centroamericano y del Caribe de Boccia 2026.</t>
+  </si>
+  <si>
+    <t>SEPH, Conade, Inhide</t>
+  </si>
+  <si>
+    <t>Rommel Pacheco, Liliana Suárez Carreón</t>
+  </si>
+  <si>
+    <t>Persiste maltrato animal en Hidalgo; judicializan 21 carpetas de investigación</t>
+  </si>
+  <si>
+    <t>Ana Lilia Martínez Hernández, titular de la Unidad Especializada en la Investigación de Delitos en Contra de los Animales, dio a conocer a Síntesis Hidalgo que, de 81 carpetas de investigación integradas por agravios contra animales, 21 han sido judicializadas, de las cuales se han obtenido 14 sentencias condenatorias en municipios como Pachuca, Mineral de la Reforma, Tizayuca y Tula.</t>
+  </si>
+  <si>
+    <t>Maltrato animal</t>
+  </si>
+  <si>
+    <t>La PGJEH ha judicializado 21 carpetas por maltrato animal en Hidalgo y logrado 14 sentencias condenatorias, reportó la Unidad Especializada.</t>
+  </si>
+  <si>
+    <t>Marco Cerón</t>
+  </si>
+  <si>
+    <t>Ana Lilia Martínez Hernández</t>
+  </si>
+  <si>
+    <t>Destruyen túnel ligado al huachicol en Tlaxcoapan; van 17</t>
+  </si>
+  <si>
+    <t>En la localidad de Teocalco, municipio de Tlaxcoapan, el Gabinete de Seguridad asistió a la destrucción de un túnel de 143 metros de longitud relacionado con el robo de hidrocarburo. Con este operativo suman 17 túneles inhabilitados en Hidalgo entre junio y septiembre de 2026, informó el secretario de Gobierno, Guillermo Olivares Reyna.</t>
+  </si>
+  <si>
+    <t>Autoridades estatales y federales destruyeron un huachitúnel de 143 metros en Tlaxcoapan, alcanzando 17 estructuras eliminadas en la entidad.</t>
+  </si>
+  <si>
+    <t>Segobh, FGR, Ferromex, Pemex, PGJEH, SSPH, PC</t>
+  </si>
+  <si>
+    <t>Hidalgo reportó tres secuestros en agosto 2026</t>
+  </si>
+  <si>
+    <t>En agosto, la PGJEH inició tres carpetas de investigación por secuestro (dos extorsivos y un exprés), cifra máxima en 29 meses según datos del SESNSP.</t>
+  </si>
+  <si>
+    <t>Secuestro</t>
+  </si>
+  <si>
+    <t>La PGJEH registró tres carpetas de investigación por secuestro en agosto en Hidalgo, la cifra mensual más alta en 29 meses según el SESNSP.</t>
+  </si>
+  <si>
+    <t>PGJEH, Presidencia</t>
+  </si>
+  <si>
+    <t>Todo listo para el arranque de la feria de San Francisco 2026</t>
+  </si>
+  <si>
+    <t>Las instalaciones de la Feria San Francisco Pachuca 2026 se encuentran preparadas para iniciar 25 días de actividades culturales, gastronómicas y espectáculos.</t>
+  </si>
+  <si>
+    <t>Arranca la Feria San Francisco Pachuca 2026 con espectáculos musicales, muestras artesanales y gastronomía durante 25 días de actividades.</t>
+  </si>
+  <si>
+    <t>Turismo, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Las denuncias por tortura se disparan en un 400 por ciento</t>
+  </si>
+  <si>
+    <t>Las denuncias por tortura en Hidalgo aumentaron 400% en agosto al registrar cinco carpetas de investigación ante la PGJEH, situando a la entidad en el lugar 12 nacional.</t>
+  </si>
+  <si>
+    <t>Tortura</t>
+  </si>
+  <si>
+    <t>Reporte del SESNSP indica que en agosto las denuncias por tortura en Hidalgo crecieron 400% con cinco querellas iniciadas ante la PGJEH.</t>
+  </si>
+  <si>
+    <t>Autoridades advierten que hay un repunte de enfermedades diarreicas</t>
+  </si>
+  <si>
+    <t>Personal de la Jurisdicción Sanitaria 2 advirtió durante sesión del Cojuve que las enfermedades diarreicas registraron un repunte por relajamiento en medidas de higiene.</t>
+  </si>
+  <si>
+    <t>Vigilancia Epidemiológica</t>
+  </si>
+  <si>
+    <t>Autoridades de salud en la región Tulancingo llamaron a reforzar la higiene y lavado de manos ante el incremento de padecimientos diarreicos.</t>
+  </si>
+  <si>
+    <t>Emiten recomendaciones a concesionarios de FUTVEH</t>
+  </si>
+  <si>
+    <t>El dirigente de la FUTVEH informó que emiten recomendaciones a concesionarios para mantener actualizadas las pólizas de seguro del transporte público ante operativos de la Semot.</t>
+  </si>
+  <si>
+    <t>Supervisión de Transporte</t>
+  </si>
+  <si>
+    <t>Dirigencia de transportistas en Pachuca exhorta a permisionarios a vigilar la vigencia de seguros de unidades para evitar sanciones y revocaciones por parte de la Semot.</t>
+  </si>
+  <si>
+    <t>Eleno Arias Pérez</t>
+  </si>
+  <si>
+    <t>Fue cancelado el registro de 6 proveedores y contratistas</t>
+  </si>
+  <si>
+    <t>La Secretaría de Contraloría publicó en el POEH la cancelación del registro e inhabilitación por 5 y 6 años de dos empresas y cuatro personas físicas.</t>
+  </si>
+  <si>
+    <t>Contraloría estatal sancionó e inhabilitó a cinco proveedores y una contratista para impedirles celebrar contratos con ayuntamientos y el gobierno de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Contraloría, SEPH</t>
+  </si>
+  <si>
+    <t>Maritza Yazmín Estrada Ortiz, Lizbeth Pedraza Quijada, Laura Flores Méndez</t>
+  </si>
+  <si>
+    <t>Llegarán a Hidalgo millón y medio de vacunas contra la influenza y el Covid-19</t>
+  </si>
+  <si>
+    <t>La SSH programa la llegada y distribución de 1.5 millones de dosis de vacunas contra influenza y Covid-19 en la entidad para la campaña invernal a partir del 12 de octubre.</t>
+  </si>
+  <si>
+    <t>Campaña de vacunación</t>
+  </si>
+  <si>
+    <t>Sector salud en Hidalgo prepara la aplicación de 1.5 millones de biológicos contra enfermedades respiratorias durante la temporada invernal 2026-2027.</t>
+  </si>
+  <si>
+    <t>SSH, IMSS, ISSSTE, Pemex</t>
+  </si>
+  <si>
+    <t>Investigan irregularidades en programa social para mujeres</t>
+  </si>
+  <si>
+    <t>La Contraloría estatal abrió expediente de verificación física y documental en Xochiatipan ante posible entrega irregular de apoyos del programa social para mujeres.</t>
+  </si>
+  <si>
+    <t>Xochiatipan</t>
+  </si>
+  <si>
+    <t>Auditorías</t>
+  </si>
+  <si>
+    <t>Secretaría de Contraloría indaga denuncia realizada en buzón QR sobre presuntas inconsistencias en el padrón de beneficiarias de Bienestar en Xochiatipan.</t>
+  </si>
+  <si>
+    <t>Salomón Hernández</t>
+  </si>
+  <si>
+    <t>Contraloría, Bienestar, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Briseyda Torres Martínez</t>
+  </si>
+  <si>
+    <t>Padres de familia de primaria exigen cambio del director y la renovación del comité</t>
+  </si>
+  <si>
+    <t>Tutores de la primaria Leona Vicario en Tulancingo se manifestaron afuera del plantel exigiendo cuentas claras del manejo financiero de cuotas y la destitución del director.</t>
+  </si>
+  <si>
+    <t>Quejas padres de familia</t>
+  </si>
+  <si>
+    <t>Manifestación de padres de familia en escuela de Tulancingo solicita la intervención inmediata de las autoridades de la SEPH para renovar la mesa directiva.</t>
+  </si>
+  <si>
+    <t>Tulancingo concentra apoyos para fortalecer actividades del campo</t>
+  </si>
+  <si>
+    <t>La Saderh entregó 8.5 mdp en apoyos agrícolas, crías de peces, huertos familiares y sistemas fotovoltaicos en beneficio de 179 productores hidalguenses.</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>Entrega regional de apoyos a productores del campo en Tulancingo busca dignificar la producción agrícola y acuícola con equipamiento e insumos.</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez</t>
+  </si>
+  <si>
+    <t>Carrera del COBAEH San Ildefonso promueve salud y convivencia juvenil</t>
+  </si>
+  <si>
+    <t>Más de 160 estudiantes de Tepeji del Río se reunieron en la carrera deportiva del Cobaeh enfocada en la activación física e integración escolar.</t>
+  </si>
+  <si>
+    <t>Tepeji del Río</t>
+  </si>
+  <si>
+    <t>Carrera atlética</t>
+  </si>
+  <si>
+    <t>Jornada deportiva estudiantil en Tepeji del Río promovió hábitos saludables y valores de convivencia entre la juventud del subsistema Cobaeh.</t>
+  </si>
+  <si>
+    <t>SEPH, Ayuntamiento, DIFH</t>
+  </si>
+  <si>
+    <t>Suman un total de 23 casos de gusano barrenador en Hidalgo</t>
+  </si>
+  <si>
+    <t>De acuerdo con el Boletín Epidemiológico de la Secretaría de Salud Federal, Hidalgo registra 23 casos de gusano barrenador en humanos en lo que va de 2026, ubicándose en novena posición nacional.</t>
+  </si>
+  <si>
+    <t>Hidalgo suma 23 casos acumulados de miasis por gusano barrenador en humanos durante 2026 sin registrar defunciones.</t>
+  </si>
+  <si>
+    <t>SSH, Presidencia</t>
+  </si>
+  <si>
+    <t>Taxis cobrarán hasta 133 pesos desde la feria</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte publicó el tarifario oficial para traslados desde la Feria Pachuca 2026, fijando cobros de 45 a 133 pesos según el destino.</t>
+  </si>
+  <si>
+    <t>Semot emitió el tabulador oficial de taxis para la Feria de Pachuca 2026 con tarifa mínima de 45 pesos y máxima de 133 a municipios conurbados.</t>
+  </si>
+  <si>
+    <t>Hidalgo, sede de Orgullo Nacional 2027 y del Campeonato Centroamericano de Boccia</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca y Rommel Pacheco, titular de la Conade, anunciaron que Hidalgo albergará la competencia Orgullo Nacional 2027 y el Centroamericano de Boccia 2026.</t>
+  </si>
+  <si>
+    <t>Hidalgo fue confirmado como sede principal de la justa juvenil Orgullo Nacional 2027 y del Campeonato Centroamericano de Boccia 2026.</t>
+  </si>
+  <si>
+    <t>SEPH, Gobernador, Presidencia</t>
+  </si>
+  <si>
+    <t>Entró en vigor el incremento del 20 por ciento a las tarifas del transporte en Pachuca</t>
+  </si>
+  <si>
+    <t>Publicaron en el POEH el acuerdo que autoriza el alza de tarifa inicial de taxi a 45 pesos e inicia la transición progresiva hacia taxímetros digitales.</t>
+  </si>
+  <si>
+    <t>Sube 20% la tarifa de taxis en Pachuca y Mineral de la Reforma con banderazo oficial de 45 pesos publicado en el POEH.</t>
+  </si>
+  <si>
+    <t>Atrae Hidalgo más de 147 mil MDP en inversión privada</t>
+  </si>
+  <si>
+    <t>La Unidad de Planeación y Prospectiva destacó la atracción de 147 mil 697 millones de pesos en capital privado durante la actual administración.</t>
+  </si>
+  <si>
+    <t>Uplaph reportó una cifra acumulada superior a 147 mil mdp en inversión privada consolidada en parques industriales de la entidad.</t>
+  </si>
+  <si>
+    <t>Planeación</t>
+  </si>
+  <si>
+    <t>Planeación, Uplaph</t>
+  </si>
+  <si>
+    <t>Vacunarán a más de 202 mil perros y gatos en la Semana de Reforzamiento Antirrábico</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo aplicará 202 mil dosis de vacuna antirrábica en los 84 municipios durante la jornada de reforzamiento.</t>
+  </si>
+  <si>
+    <t>Vacunación Antirrábica</t>
+  </si>
+  <si>
+    <t>Arrancó la Semana Nacional de vacunación antirrábica en Hidalgo para inmunizar a más de 202 mil mascotas.</t>
+  </si>
+  <si>
+    <t>Padres de familia cierran escuela Leona Vicario y exigen cambio de comité</t>
+  </si>
+  <si>
+    <t>Toman las instalaciones del plantel educativo en Tulancingo exigiendo auditoría al comité de padres y señalando presunto desvío de recursos.</t>
+  </si>
+  <si>
+    <t>Tutores de la primaria Leona Vicario en Tulancingo protestan y cierran la escuela solicitando transparencia en las cuotas escolares.</t>
+  </si>
+  <si>
+    <t>Jesús Riveros</t>
+  </si>
+  <si>
+    <t>Implementa la SSPH operativo especial de vigilancia por la Feria San Francisco Pachuca 2026</t>
+  </si>
+  <si>
+    <t>La Policía Estatal desplegará unidades de vigilancia permanente en zonas comerciales, estacionamientos y escenarios del recinto ferial.</t>
+  </si>
+  <si>
+    <t>Operativo de Seguridad</t>
+  </si>
+  <si>
+    <t>SSPH activó el operativo de prevención y vialidad para resguardar a los visitantes de la Feria de San Francisco en Pachuca.</t>
+  </si>
+  <si>
+    <t>SSPH, C5i</t>
+  </si>
+  <si>
+    <t>Tuzobús modifica operación y anuncia servicio especial nocturno por Feria Pachuca 2026</t>
+  </si>
+  <si>
+    <t>El sistema troncal permitirá paradas especiales en estaciones Vicente Segura y Juan C. Doria y dará servicio nocturno de 23:00 a 03:00 horas.</t>
+  </si>
+  <si>
+    <t>Afluencia Tuzobús</t>
+  </si>
+  <si>
+    <t>Tuzobús extenderá horario con rutas nocturnas de Cetram Téllez a Centro Histórico por la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah</t>
+  </si>
+  <si>
+    <t>Sancionan a 35 personas por ofrecer servicio de taxi mediante aplicación</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte informó sobre infracciones a choferes por operar plataformas digitales no autorizadas en la entidad.</t>
+  </si>
+  <si>
+    <t>Semot aplicó 35 sanciones durante operativos de inspección a unidades que prestaban servicio ejecutivo sin concesión.</t>
+  </si>
+  <si>
+    <t>Descubren y aseguran en Atitalaquia y Teocalco sofisticada red de túneles y tomas clandestinas</t>
+  </si>
+  <si>
+    <t>Fuerzas de seguridad estatales y federales inhabilitaron dos excavaciones de alta tecnología conectadas a ductos de Pemex en la región Tula.</t>
+  </si>
+  <si>
+    <t>Autoridades inhabilitaron dos subterráneos huachicoleros en Atitalaquia y Tlaxcoapan equipados con mangueras de alta presión.</t>
+  </si>
+  <si>
+    <t>Segobh, SSPH, Pemex, FGR</t>
+  </si>
+  <si>
+    <t>Ya es oficial: suben tarifa de los taxis en Pachuca y Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Entran en vigor las nuevas tarifas de transporte individual con banderazo de 45 pesos y recargo del 20% en horario nocturno.</t>
+  </si>
+  <si>
+    <t>Semot oficializó en el periódico oficial las tarifas de taxi para Pachuca con sanciones de hasta 15 mil pesos por cobros indebidos.</t>
+  </si>
+  <si>
+    <t>Garantizan transporte, así como vigilancia y servicio especial nocturno para la Feria San Francisco 2026</t>
+  </si>
+  <si>
+    <t>SSPH y Semot desplegarán operativos coordinados con células de vigilancia y transporte nocturno de 10 pesos durante la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>Autoridades estatales implementarán un despliegue operativo conjunto de seguridad y movilidad para los asistentes a la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>SSPH, Semot, Sitmah, C5i</t>
+  </si>
+  <si>
+    <t>Eliminan túnel de huachicol de 143 metros situado en Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>El Gabinete de Seguridad inhabilitó una excavación subterránea de 143 metros de longitud utilizada para la extracción ilícita de hidrocarburo en Teocalco.</t>
+  </si>
+  <si>
+    <t>Destruyen túnel clandestino en Tlaxcoapan tras peritajes de la FGR en operativo conjunto de seguridad.</t>
+  </si>
+  <si>
+    <t>Segobh, SSPH, FGR</t>
+  </si>
+  <si>
+    <t>Van a demoler primaria Aquiles Serdán en Tulancingo; edificarán otra</t>
+  </si>
+  <si>
+    <t>La SEPH demolerá la primaria Aquiles Serdán en Tulancingo por daños estructurales y reubicará provisionalmente a la plantilla escolar.</t>
+  </si>
+  <si>
+    <t>Educación Pública reconstruirá totalmente la escuela primaria Aquiles Serdán evaluando alternativas de clases híbridas o presenciales.</t>
   </si>
 </sst>
 </file>
@@ -1173,8 +1227,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ45" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ45" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ52" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ52" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1606,7 +1660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ45"/>
+  <dimension ref="A1:AJ52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1756,28 +1810,28 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F2" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1792,19 +1846,19 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>57</v>
@@ -1816,45 +1870,43 @@
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>102</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AJ2" s="2"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F3" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1869,19 +1921,19 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>58</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>57</v>
@@ -1893,42 +1945,40 @@
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="AJ3" s="2"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F4" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>48</v>
@@ -1946,69 +1996,67 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA4">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>115</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="AJ4" s="2"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F5" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2023,10 +2071,10 @@
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="Y5" s="2" t="s">
         <v>58</v>
@@ -2035,7 +2083,7 @@
         <v>43</v>
       </c>
       <c r="AA5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>57</v>
@@ -2047,51 +2095,49 @@
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>121</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="AJ5" s="2"/>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F6" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R6">
         <v>1</v>
       </c>
       <c r="S6">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>59</v>
@@ -2100,31 +2146,31 @@
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="Y6" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>40</v>
@@ -2133,30 +2179,28 @@
         <v>113</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>126</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="AJ6" s="2"/>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F7" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>60</v>
@@ -2168,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="S7">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>59</v>
@@ -2177,10 +2221,10 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>56</v>
@@ -2201,42 +2245,40 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ7" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="AJ7" s="2"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F8" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>48</v>
@@ -2245,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="S8">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>59</v>
@@ -2254,19 +2296,19 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>57</v>
@@ -2278,51 +2320,49 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ8" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="AJ8" s="2"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F9" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R9">
         <v>1</v>
       </c>
       <c r="S9">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>59</v>
@@ -2331,19 +2371,19 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>57</v>
@@ -2355,42 +2395,42 @@
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F10" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>42</v>
@@ -2399,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="S10">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>59</v>
@@ -2408,19 +2448,19 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>57</v>
@@ -2432,39 +2472,37 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="AG10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="AJ10" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AJ10" s="2"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F11" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>45</v>
@@ -2476,25 +2514,25 @@
         <v>1</v>
       </c>
       <c r="S11">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>59</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA11">
         <v>20</v>
@@ -2509,49 +2547,49 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="AJ11" s="2"/>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F12" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R12">
         <v>1</v>
       </c>
       <c r="S12">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>59</v>
@@ -2560,10 +2598,10 @@
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>56</v>
@@ -2572,7 +2610,7 @@
         <v>43</v>
       </c>
       <c r="AA12">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>57</v>
@@ -2584,42 +2622,40 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ12" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="AJ12" s="2"/>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F13" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>48</v>
@@ -2628,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="S13">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>59</v>
@@ -2637,25 +2673,25 @@
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA13">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD13" s="2" t="s">
         <v>44</v>
@@ -2667,34 +2703,36 @@
         <v>41</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AJ13" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F14" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>60</v>
+        <v>157</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>48</v>
@@ -2703,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="S14">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>59</v>
@@ -2712,16 +2750,16 @@
         <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA14">
         <v>24</v>
@@ -2736,39 +2774,39 @@
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F15" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>45</v>
@@ -2780,28 +2818,28 @@
         <v>1</v>
       </c>
       <c r="S15">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>59</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA15">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>57</v>
@@ -2813,39 +2851,37 @@
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ15" s="2" t="s">
-        <v>140</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="AJ15" s="2"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F16" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>45</v>
@@ -2857,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="S16">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>59</v>
@@ -2866,75 +2902,73 @@
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA16">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="AG16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>175</v>
+        <v>66</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="AJ16" s="2" t="s">
-        <v>176</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AJ16" s="2"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F17" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>179</v>
+        <v>45</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>59</v>
@@ -2943,64 +2977,64 @@
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA17">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AJ17" s="2"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F18" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>42</v>
@@ -3018,19 +3052,19 @@
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA18">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>57</v>
@@ -3042,42 +3076,40 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ18" s="2" t="s">
-        <v>186</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AJ18" s="2"/>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F19" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>48</v>
@@ -3095,16 +3127,16 @@
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="Y19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA19">
         <v>20</v>
@@ -3119,40 +3151,42 @@
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>192</v>
+        <v>46</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="AJ19" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F20" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>48</v>
@@ -3161,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="S20">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>59</v>
@@ -3170,19 +3204,19 @@
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA20">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>57</v>
@@ -3194,51 +3228,49 @@
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AG20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH20" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="AI20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ20" s="2" t="s">
-        <v>197</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="AJ20" s="2"/>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F21" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R21">
         <v>1</v>
       </c>
       <c r="S21">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>59</v>
@@ -3247,19 +3279,19 @@
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA21">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>57</v>
@@ -3271,39 +3303,39 @@
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AG21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F22" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>45</v>
@@ -3315,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="S22">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>59</v>
@@ -3324,19 +3356,19 @@
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA22">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB22" s="2" t="s">
         <v>57</v>
@@ -3348,51 +3380,51 @@
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AG22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F23" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R23">
         <v>1</v>
       </c>
       <c r="S23">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>59</v>
@@ -3401,63 +3433,63 @@
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA23">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD23" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="AG23" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F24" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>45</v>
@@ -3469,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="S24">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>59</v>
@@ -3478,16 +3510,16 @@
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="Y24" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA24">
         <v>20</v>
@@ -3502,7 +3534,7 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
@@ -3511,42 +3543,42 @@
         <v>46</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F25" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R25">
         <v>1</v>
       </c>
       <c r="S25">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T25" s="2" t="s">
         <v>59</v>
@@ -3555,66 +3587,66 @@
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA25">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB25" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="AG25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F26" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>48</v>
@@ -3623,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="S26">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>59</v>
@@ -3632,60 +3664,60 @@
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA26">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>227</v>
+        <v>65</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>138</v>
+        <v>219</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>140</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="F27" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -3694,7 +3726,7 @@
         <v>45</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -3709,16 +3741,16 @@
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA27">
         <v>20</v>
@@ -3739,39 +3771,37 @@
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ27" s="2" t="s">
-        <v>232</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="AJ27" s="2"/>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="F28" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -3786,69 +3816,67 @@
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA28">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB28" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="AJ28" s="2" t="s">
-        <v>237</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="AJ28" s="2"/>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="F29" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -3863,19 +3891,19 @@
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA29">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB29" s="2" t="s">
         <v>57</v>
@@ -3887,45 +3915,43 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG29" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ29" s="2" t="s">
-        <v>140</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="AJ29" s="2"/>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F30" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -3940,10 +3966,10 @@
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>58</v>
@@ -3952,7 +3978,7 @@
         <v>43</v>
       </c>
       <c r="AA30">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB30" s="2" t="s">
         <v>57</v>
@@ -3964,45 +3990,43 @@
         <v>44</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="AG30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ30" s="2" t="s">
-        <v>245</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AJ30" s="2"/>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="F31" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G31">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4017,10 +4041,10 @@
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>72</v>
+        <v>239</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>56</v>
@@ -4041,51 +4065,51 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>250</v>
+        <v>39</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>251</v>
+        <v>66</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="F32" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
       <c r="S32">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T32" s="2" t="s">
         <v>59</v>
@@ -4094,16 +4118,16 @@
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="Y32" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA32">
         <v>20</v>
@@ -4118,42 +4142,42 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="F33" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>48</v>
@@ -4162,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="S33">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T33" s="2" t="s">
         <v>59</v>
@@ -4171,19 +4195,19 @@
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>111</v>
+        <v>249</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA33">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>57</v>
@@ -4195,48 +4219,49 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AG33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AJ33" s="2" t="s">
-        <v>263</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AJ33" s="2"/>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="F34" s="1">
-        <v>46288</v>
+        <v>46289</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>60</v>
+        <v>254</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R34">
         <v>1</v>
       </c>
       <c r="S34">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T34" s="2" t="s">
         <v>59</v>
@@ -4245,19 +4270,19 @@
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>74</v>
+        <v>255</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA34">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB34" s="2" t="s">
         <v>57</v>
@@ -4269,46 +4294,51 @@
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ34" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="AJ34" s="2" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="F35" s="1">
-        <v>46288</v>
+        <v>46289</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R35">
         <v>1</v>
       </c>
       <c r="S35">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T35" s="2" t="s">
         <v>59</v>
@@ -4317,10 +4347,10 @@
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>105</v>
+        <v>262</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>56</v>
@@ -4341,39 +4371,40 @@
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ35" s="2" t="s">
-        <v>270</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="AJ35" s="2"/>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F36" s="1">
-        <v>46288</v>
+        <v>46289</v>
+      </c>
+      <c r="G36">
+        <v>8</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>48</v>
@@ -4382,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="S36">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T36" s="2" t="s">
         <v>59</v>
@@ -4391,10 +4422,10 @@
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="Y36" s="2" t="s">
         <v>56</v>
@@ -4403,13 +4434,13 @@
         <v>43</v>
       </c>
       <c r="AA36">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC36" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD36" s="2" t="s">
         <v>44</v>
@@ -4421,33 +4452,36 @@
         <v>41</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>275</v>
+        <v>120</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="F37" s="1">
-        <v>46288</v>
+        <v>46289</v>
+      </c>
+      <c r="G37">
+        <v>8</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>45</v>
+        <v>271</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>48</v>
@@ -4456,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="S37">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T37" s="2" t="s">
         <v>59</v>
@@ -4465,25 +4499,25 @@
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA37">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC37" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD37" s="2" t="s">
         <v>44</v>
@@ -4495,30 +4529,28 @@
         <v>41</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ37" s="2" t="s">
-        <v>140</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="AJ37" s="2"/>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F38" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>60</v>
@@ -4539,19 +4571,19 @@
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>282</v>
+        <v>117</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA38">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>57</v>
@@ -4563,37 +4595,37 @@
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AJ38" s="2"/>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F39" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>49</v>
@@ -4611,10 +4643,10 @@
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="Y39" s="2" t="s">
         <v>56</v>
@@ -4635,42 +4667,40 @@
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AG39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AJ39" s="2" t="s">
-        <v>126</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="AJ39" s="2"/>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F40" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -4685,19 +4715,19 @@
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="Y40" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA40">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>57</v>
@@ -4715,36 +4745,34 @@
         <v>41</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ40" s="2" t="s">
-        <v>292</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="AJ40" s="2"/>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F41" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>179</v>
+        <v>45</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -4759,10 +4787,10 @@
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="Y41" s="2" t="s">
         <v>56</v>
@@ -4777,43 +4805,43 @@
         <v>57</v>
       </c>
       <c r="AC41" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>296</v>
+        <v>94</v>
       </c>
       <c r="AJ41" s="2"/>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F42" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>48</v>
@@ -4831,10 +4859,10 @@
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="Y42" s="2" t="s">
         <v>56</v>
@@ -4861,39 +4889,34 @@
         <v>41</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>47</v>
+        <v>292</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="AJ42" s="2" t="s">
-        <v>126</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="AJ42" s="2"/>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F43" s="1">
-        <v>46288</v>
-      </c>
-      <c r="G43">
-        <v>3</v>
+        <v>46289</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -4908,19 +4931,19 @@
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>200</v>
+        <v>296</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA43">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>57</v>
@@ -4932,45 +4955,40 @@
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="AJ43" s="2" t="s">
-        <v>305</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AJ43" s="2"/>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F44" s="1">
-        <v>46288</v>
-      </c>
-      <c r="G44">
-        <v>3</v>
+        <v>46289</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -4985,10 +5003,10 @@
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>85</v>
+        <v>262</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="Y44" s="2" t="s">
         <v>56</v>
@@ -5009,45 +5027,40 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>65</v>
+        <v>301</v>
       </c>
       <c r="AG44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="AJ44" s="2" t="s">
-        <v>310</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="AJ44" s="2"/>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="F45" s="1">
-        <v>46288</v>
-      </c>
-      <c r="G45">
-        <v>4</v>
+        <v>46289</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5062,10 +5075,10 @@
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>56</v>
@@ -5086,20 +5099,534 @@
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH45" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI45" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ45" s="2"/>
+    </row>
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F46" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R46">
+        <v>1</v>
+      </c>
+      <c r="S46">
+        <v>13262</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA46">
+        <v>16</v>
+      </c>
+      <c r="AB46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI46" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ46" s="2"/>
+    </row>
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F47" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R47">
+        <v>1</v>
+      </c>
+      <c r="S47">
+        <v>13262</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="X47" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="Y47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA47">
+        <v>12</v>
+      </c>
+      <c r="AB47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ47" s="2"/>
+    </row>
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F48" s="1">
+        <v>46289</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R48">
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <v>13262</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA48">
+        <v>24</v>
+      </c>
+      <c r="AB48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC48" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI48" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AJ48" s="2"/>
+    </row>
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F49" s="1">
+        <v>46289</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R49">
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <v>13262</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X49" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z49" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA49">
+        <v>20</v>
+      </c>
+      <c r="AB49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD49" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ49" s="2"/>
+    </row>
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F50" s="1">
+        <v>46289</v>
+      </c>
+      <c r="G50">
+        <v>4</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
+      </c>
+      <c r="S50">
+        <v>13262</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA50">
+        <v>20</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI50" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="AJ50" s="2"/>
+    </row>
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F51" s="1">
+        <v>46289</v>
+      </c>
+      <c r="G51">
+        <v>4</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
+      </c>
+      <c r="S51">
+        <v>13262</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="Y51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z51" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA51">
+        <v>20</v>
+      </c>
+      <c r="AB51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC51" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI51" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="AJ51" s="2"/>
+    </row>
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F52" s="1">
+        <v>46289</v>
+      </c>
+      <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>13262</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA52">
+        <v>16</v>
+      </c>
+      <c r="AB52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC52" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF52" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AG45" s="2" t="s">
+      <c r="AG52" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH45" s="2" t="s">
+      <c r="AH52" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AI45" s="2" t="s">
+      <c r="AI52" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AJ45" s="2" t="s">
-        <v>71</v>
-      </c>
+      <c r="AJ52" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A94576E-581E-43F2-BA8B-9756AA6A15EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3317E19-8A9D-4BC8-B8EC-D570FC15AE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="321">
   <si>
     <t>Canal</t>
   </si>
@@ -244,9 +244,6 @@
     <t>Adela Garmez</t>
   </si>
   <si>
-    <t>Veida Martínez Miranda</t>
-  </si>
-  <si>
     <t>Semot</t>
   </si>
   <si>
@@ -265,9 +262,6 @@
     <t>Sonia Nochebuena</t>
   </si>
   <si>
-    <t>Apps de transporte</t>
-  </si>
-  <si>
     <t>Lourdes Naranjo</t>
   </si>
   <si>
@@ -277,775 +271,745 @@
     <t>Ricardo Calleja</t>
   </si>
   <si>
-    <t>Carmen Hernández</t>
-  </si>
-  <si>
     <t>Oscar Raúl Pérez</t>
   </si>
   <si>
-    <t>Ana Luisa Vega</t>
-  </si>
-  <si>
-    <t>SSH, SEPH</t>
-  </si>
-  <si>
-    <t>Atracción De Inversiones</t>
-  </si>
-  <si>
-    <t>Tarifario de taxis</t>
-  </si>
-  <si>
-    <t>Nacionales Conade</t>
-  </si>
-  <si>
-    <t>Padrón de proveedores</t>
-  </si>
-  <si>
     <t>Contraloría</t>
   </si>
   <si>
-    <t>Semarnath</t>
-  </si>
-  <si>
-    <t>Oferta educativa</t>
-  </si>
-  <si>
-    <t>Daniel Fragoso Torres</t>
-  </si>
-  <si>
     <t>Tulancingo</t>
   </si>
   <si>
-    <t>María Antonieta Islas</t>
-  </si>
-  <si>
     <t>Reconstrucción de escuela</t>
   </si>
   <si>
-    <t>Nuevas tarifas de taxis ya se aplican</t>
-  </si>
-  <si>
-    <t>Tras la publicación del acuerdo en el Periódico Oficial del Estado de Hidalgo, el aumento de 20% en las tarifas de taxis en Pachuca y Mineral de la Reforma entró en vigor ayer. De acuerdo con el tarifario, un traslado del Reloj Monumental a la Feria tiene un costo de 77 pesos.</t>
-  </si>
-  <si>
-    <t>Entró en vigor el incremento del 20% en las tarifas de taxis para Pachuca y Mineral de la Reforma tras su publicación en el POEH, fijando el banderazo mínimo en 45 pesos.</t>
-  </si>
-  <si>
-    <t>Semot, STCH</t>
-  </si>
-  <si>
-    <t>Desmiente Ice Dreams a la feria de Pachuca</t>
-  </si>
-  <si>
-    <t>La compañía informó que no se presentará en la Feria San Francisco Pachuca 2026 y se deslindó del espectáculo Raíces del Mundo, anunciado en las cuentas oficiales del evento. Señaló que se utilizaron fotografías de sus patinadores sin autorización, algunas alteradas con Inteligencia Artificial.</t>
-  </si>
-  <si>
     <t>Feria Pachuca</t>
   </si>
   <si>
-    <t>La empresa Ice Dreams México aclaró que no participará en la Feria San Francisco Pachuca 2026 y denunció el uso no autorizado de imágenes de sus integrantes en la promoción oficial.</t>
-  </si>
-  <si>
     <t>Turismo</t>
   </si>
   <si>
-    <t>Turismo, OEEH</t>
-  </si>
-  <si>
-    <t>Asesoran a jóvenes para prevenir suicidio</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo reforzó las acciones dirigidas a jóvenes para que puedan identificar conductas de riesgo y construyan redes de apoyo entre compañeros. La estrategia incluye actividades en planteles educativos, mientras que las autoridades difunden las señales de alerta y ponen a disposición la Línea de la Vida.</t>
-  </si>
-  <si>
-    <t>Prevención del suicidio</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo lleva a cabo talleres y capacitaciones en escuelas para prevenir el suicidio juvenil mediante la identificación oportuna de factores de riesgo.</t>
-  </si>
-  <si>
-    <t>Colillas y envases, los residuos predominantes en las costas</t>
-  </si>
-  <si>
-    <t>Millones de kilogramos de basura fueron recogidos y eliminados por voluntarios en regiones costeras de todo el mundo en 2021. De acuerdo con la organización estadounidense sin fines de lucro Ocean Conservancy, la basura en las playas y otros centros recreativos aumenta año con año.</t>
-  </si>
-  <si>
-    <t>Protección ambiental</t>
-  </si>
-  <si>
-    <t>Datos de Ocean Conservancy revelan que las colillas de cigarro, envoltorios de comida y botellas de plástico representan los principales contaminantes recolectados en zonas costeras.</t>
-  </si>
-  <si>
-    <t>Tarifa de agua sube 14.08% en 3 años</t>
-  </si>
-  <si>
-    <t>Del 2023 al 2026 la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (Caasim) ha incrementado en 14.08% el suministro de agua tipo doméstico, cuyo costo mínimo era de 35.81 pesos en 2023 a 54.93 en 2026.</t>
-  </si>
-  <si>
-    <t>Tarifa Caasim</t>
-  </si>
-  <si>
-    <t>La tarifa básica de suministro doméstico de agua potable de Caasim acumula un incremento del 14.08% en tres años en los 14 municipios atendidos.</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Caasim, Sipdus</t>
-  </si>
-  <si>
-    <t>Sin casos activos de barrenador</t>
-  </si>
-  <si>
-    <t>Tras acumular mil 376 contagios de gusano barrenador en animales tras cuatro meses del primer infectado, Hidalgo dejó de figurar entre las entidades con casos activos de esta plaga, de acuerdo con el reporte más reciente del Servicio Nacional de Sanidad, Inocuidad y Calidad Agroalimentaria (Senasica).</t>
-  </si>
-  <si>
-    <t>Gusano barrenador</t>
-  </si>
-  <si>
-    <t>Senasica confirmó que Hidalgo ya no presenta casos activos de gusano barrenador en ganado tras haber registrado 1,376 contagios en meses anteriores.</t>
-  </si>
-  <si>
     <t>Alma Leticia Sánchez</t>
   </si>
   <si>
     <t>Saderh</t>
   </si>
   <si>
-    <t>Senasica, Saderh</t>
-  </si>
-  <si>
-    <t>Por Feria se aplican operativo de transporte</t>
-  </si>
-  <si>
-    <t>Con motivo de la Feria de San Francisco Pachuca Hidalgo 2026, la Secretaría de Movilidad y Transporte de Hidalgo (Semoth) realizará operativos especiales del jueves 24 de septiembre al domingo 18 de octubre, con el objetivo de garantizar la movilidad y un servicio de transporte accesible.</t>
-  </si>
-  <si>
-    <t>Operativo de transporte</t>
-  </si>
-  <si>
-    <t>La Semot puso en marcha operativos de transporte especial y bases temporales de taxis para dar servicio nocturno continuo durante la Feria de Pachuca 2026.</t>
-  </si>
-  <si>
-    <t>Semot, Sitmah, STCH</t>
-  </si>
-  <si>
-    <t>Cobro puede aumentar por el tráfico, choferes</t>
-  </si>
-  <si>
-    <t>Tras la publicación del nuevo tarifario de taxis en el Periódico Oficial del Estado de Hidalgo (POEH), operadores en Pachuca y Mineral de la Reforma pidieron a los usuarios considerar el tiempo que permanecen en el tráfico y a la Secretaría de Movilidad y Transporte (Semoth) aclarar cómo será el proceso para la instalación de los taxímetros físicos.</t>
-  </si>
-  <si>
-    <t>Taxistas de Pachuca señalaron que el tráfico vehicular genera cobros adicionales por minutos de espera y urgieron a la Semot a clarificar la transición hacia taxímetros digitales.</t>
-  </si>
-  <si>
-    <t>Germán Carrasco</t>
-  </si>
-  <si>
-    <t>Continúa retiro de material en la Tenango-Metepec</t>
-  </si>
-  <si>
-    <t>Las labores de atención y supervisión vial se mantienen de manera constante sobre la carretera estatal Tenango-Metepec, previo al Arco de Bienvenida de Tenango de Doria, donde se retira material derivado de deslaves provocados por lluvias. Protección Civil mantiene monitoreo del terreno y pide extremar precauciones.</t>
-  </si>
-  <si>
-    <t>Tenango de Doria</t>
-  </si>
-  <si>
-    <t>Deslaves por lluvias</t>
-  </si>
-  <si>
-    <t>Autoridades y Protección Civil mantienen trabajos con maquinaria pesada en la carretera estatal Tenango-Metepec para retirar el material acumulado por derrumbes tras las recientes lluvias.</t>
-  </si>
-  <si>
     <t>Nathali González</t>
   </si>
   <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>Entra en vigor nueva tarifa de taxis; banderazo será de $45</t>
-  </si>
-  <si>
-    <t>El Sistema de Transporte Convencional de Hidalgo publicó en el POEH la actualización de la tarifa del transporte individual (taxi) para Pachuca y Mineral de la Reforma. El banderazo ordinario será de 45 pesos más 4 pesos por kilómetro adicional, con incremento nocturno del 20%. Concesionarios tendrán 120 días para instalar taxímetros digitales.</t>
-  </si>
-  <si>
-    <t>Entró en vigor el incremento tarifario de taxis en Pachuca y Mineral de la Reforma fijando la bajada de bandera en 45 pesos, estableciendo la obligación de implementar taxímetros digitales en 120 días.</t>
-  </si>
-  <si>
-    <t>Portada</t>
-  </si>
-  <si>
-    <t>STCH</t>
-  </si>
-  <si>
-    <t>Hidalgo suma 269 homicidios de enero a agosto de este año</t>
-  </si>
-  <si>
-    <t>El Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública documentó que Hidalgo acumuló 269 homicidios (131 dolosos y 138 culposos) en los primeros ocho meses de 2026. Además, se contabilizaron 6 mil 949 delitos contra la vida e integridad corporal, dos feminicidios y seis secuestros extorsivos.</t>
-  </si>
-  <si>
     <t>Incidencia Delictiva</t>
   </si>
   <si>
-    <t>Cifras del SESNSP revelan que Hidalgo acumuló 269 homicidios y dos feminicidios en los primeros ocho meses de 2026, concentrando la mayoría de muertes culposas en percances de tránsito.</t>
-  </si>
-  <si>
     <t>Dulce Castillo</t>
   </si>
   <si>
     <t>PGJEH</t>
   </si>
   <si>
-    <t>SESNSP</t>
-  </si>
-  <si>
-    <t>Sin alza en tres años, la Feria de Pachuca apuesta por patrocinios</t>
-  </si>
-  <si>
-    <t>El titular de la Operadora de Eventos del Estado de Hidalgo, Marco Antonio Aranzábal Juárez, ratificó que el boleto de entrada a la Feria de San Francisco Pachuca 2026 costará 60 pesos por tercer año consecutivo. La sostenibilidad del costo se logró mediante patrocinios privados y concesión del polígono ferial por recintos.</t>
-  </si>
-  <si>
-    <t>La Feria de San Francisco Pachuca 2026 conservará por tercer año consecutivo la tarifa de 60 pesos en su boleto de entrada, financiada mediante esquemas de patrocinio comercial y alianzas estratégicas.</t>
-  </si>
-  <si>
-    <t>OEEH, SSPH, Cofepris, SSH, Profeco, CDHEH</t>
-  </si>
-  <si>
-    <t>Marco Antonio Aranzábal Juárez, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Destruyen huachitúnel en comunidad de Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>El secretario de Gobierno, Guillermo Olivares Reyna, supervisó la destrucción del huachitúnel número 17 en Teocalco, municipio de Tlaxcoapan. La estructura rústica de 143 metros de longitud pasaba por debajo de carreteras y vías de ferrocarril conectando con el poliducto de Pemex. Con esto suman 16 huachitúneles inhabilitados en el sexenio.</t>
-  </si>
-  <si>
-    <t>Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>Huachitúnel</t>
-  </si>
-  <si>
-    <t>Autoridades estatales, federales y Pemex clausuraron un huachitúnel de 143 metros de longitud en Tlaxcoapan, sumando 16 estructuras subterráneas invalidadas durante la presente administración.</t>
-  </si>
-  <si>
-    <t>Joselyn Sánchez</t>
-  </si>
-  <si>
-    <t>Presidencia, Pemex, GN, Sedena, Ferromex, PC</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna, Román Bernal Díaz, Jaime Álvarez Solís, Juan Pablo Velázquez</t>
-  </si>
-  <si>
-    <t>Acción ambiental</t>
-  </si>
-  <si>
-    <t>El ayuntamiento de Pachuca y Semarnath invitan al acopio de pilas y reforestación en la unidad deportiva de la colonia Carlo Rovirosa, de 9:00 a 16:00 horas. ¡Cada pila cuenta, cada acción protege!</t>
-  </si>
-  <si>
-    <t>Boletín</t>
-  </si>
-  <si>
-    <t>El Ayuntamiento de Pachuca y Semarnath invitan a la ciudadanía al acopio de pilas y jornadas de reforestación en la unidad deportiva de la colonia Carlo Rovirosa.</t>
-  </si>
-  <si>
-    <t>Semarnath, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Es oficial, sube 20% tarifa inicial de taxis en la capital</t>
-  </si>
-  <si>
-    <t>Desde ayer 23 de septiembre entró en vigor la nueva tarifa para el transporte público individual, taxi, en Pachuca y Mineral de la Reforma, de acuerdo con el acuerdo publicado por el Sistema de Transporte Convencional de Hidalgo (STCH) en el Periódico Oficial del Estado de Hidalgo. El documento establece una primera etapa de transición con un incremento de 20 por ciento respecto a la tarifa anterior. El banderazo pasó de 38.50 a 45 pesos, correspondiente a los primeros cuatro kilómetros, mientras que el costo por kilómetro adicional aumentó de tres a cuatro pesos, según se informó. Además, se estableció un plazo de 120 días hábiles, a partir del 23 de septiembre, para que los taxis se incorporen al dispositivo físico de taxímetro digital. Este sistema contempla un cobro adicional por tiempo de espera o baja velocidad: un peso por cada 150 metros recorridos en 60 segundos o cuando la unidad circule a menos de 15 kilómetros por hora. De acuerdo con el esquema, este aumento permite elevar el costo de los recorridos cuando las unidades permanecen detenidas o avanzan lentamente debido al tránsito. El STCH sostiene que la medida busca regular las demoras provocadas por congestión vial y tiempos de espera, además de modernizar el servicio. El acuerdo señala que los taxímetros deberán contar con las certificaciones correspondientes y ser instalados por proveedores aprobados por el STCH. Una vez concluido el plazo, la falta de instalación, así como la manipulación o alteración del dispositivo, será motivo de sanciones. A partir de este miércoles, los operadores también deben ajustarse al tarifario oficial, que contempla 12 destinos frecuentes y más de 80 puntos de origen en Pachuca y Mineral de la Reforma. El STCH también reforzó las obligaciones para concesionarios y conductores, entre ellas cobrar las tarifas autorizadas, obtener el tarifario, participar en programas de capacitación, mantener vigente la póliza de seguro y garantizar las condiciones físico-mecánicas de las unidades. Los operadores deberán portar en un sitio visible el tarjetón de conductor, someter las unidades a inspección, mantener libres de obstrucciones los parabrisas y ventanillas y respetar disposiciones sobre iluminación y sonido al interior de los vehículos. El acuerdo también contempla un incremento de 20 por ciento en la tarifa durante el horario nocturno, de las 00:01 a las 04:59 horas. Durante el resto del día, de las 05:00 a las 24:00 horas, se aplicará la tarifa ordinaria. El nuevo esquema también busca reducir la discrecionalidad en el cobro, ya que los operadores deberán sujetarse a las tarifas.</t>
-  </si>
-  <si>
-    <t>Entró en vigor el incremento del 20% en la tarifa inicial de taxis para Pachuca y Mineral de la Reforma, fijando el banderazo mínimo en 45 pesos y otorgando 120 días para la instalación obligatoria de taxímetros digitales.</t>
-  </si>
-  <si>
-    <t>Teodoro Santos</t>
-  </si>
-  <si>
-    <t>Descartan aumento al precio de la tortilla</t>
-  </si>
-  <si>
-    <t>El kilo de tortilla se mantendrá en 25 pesos en el estado de Hidalgo, luego de que la Secretaría de Agricultura y Desarrollo Rural (Sader) señaló que existe suficiente maíz blanco para atender la demanda de la industria y que el reciente incremento en el precio del grano tendría un impacto limitado en el producto final. En las últimas cuatro semanas, la tonelada de maíz registró un aumento de 400 pesos, equivalente a 6 por ciento, pero, de acuerdo con las estimaciones de la dependencia, esto representa una variación aproximada de 28 centavos en el precio de un kilogramo de tortilla. En julio de 2025 fue firmado el Acuerdo Nacional Maíz-Tortilla, con el objetivo de contener incrementos en el precio del alimento. Desde entonces, el valor de la tonelada de maíz llegó a disminuir de alrededor de 6 mil 800 a 5 mil pesos en algunas regiones. Con la llegada del otoño y el inicio de la cosecha, se espera una mayor disponibilidad del grano. La Sader señaló que, al noveno mes del año, los inventarios de maíz blanco permiten cubrir la demanda de la industria, por lo que no existen condiciones para justificar un incremento en el precio de la tortilla. Un recorrido por tortillerías de la zona metropolitana de Pachuca confirmó que el precio se mantiene en 25 pesos por kilo. En algunos mercados también se conserva este costo para las tortillas hechas a mano, debido a que el ajuste en el precio del maíz aún no se refleja de manera significativa en el valor de la masa. La Sader señaló que, al noveno mes del año, los inventarios de maíz blanco permiten cubrir la demanda de la industria, por lo que no existen condiciones para justificar un incremento en el precio de la tortilla. Para finales de octubre comenzará la cosecha nacional del ciclo primavera-verano. La Sader aseguró que hay suficiente maíz blanco para cubrir la demanda de la industria y evitar un alza en el alimento.</t>
-  </si>
-  <si>
-    <t>Canasta básica</t>
-  </si>
-  <si>
-    <t>La Sader descartó un alza en el precio de la tortilla en Hidalgo, confirmando que el costo se mantendrá en 25 pesos por kilogramo gracias al abasto suficiente de maíz blanco en los inventarios nacionales.</t>
-  </si>
-  <si>
-    <t>Miriam Avilés</t>
-  </si>
-  <si>
-    <t>Saderh, Presidencia</t>
-  </si>
-  <si>
-    <t>Incremento a tarifas de taxis entró en vigor</t>
-  </si>
-  <si>
-    <t>Publican acuerdo del STCH en el POEH fijando la tarifa mínima en 45 pesos para Pachuca y Mineral de la Reforma, con la obligación de instalar taxímetros en 120 días.</t>
-  </si>
-  <si>
-    <t>Entra en vigor el nuevo tarifario de taxis en la zona metropolitana de Pachuca estableciendo un banderazo mínimo de 45 pesos e incremento nocturno del 20%.</t>
-  </si>
-  <si>
-    <t>Amarra Hidalgo sede de Olimpiada</t>
-  </si>
-  <si>
-    <t>Hidalgo albergará la competencia Orgullo Nacional 2027, la contienda deportiva infantil y juvenil más importante del país, anunciaron el gobernador Menchaca y Rommel Pacheco.</t>
-  </si>
-  <si>
-    <t>Anuncian que Hidalgo será la sede principal de la Olimpiada Nacional Orgullo Nacional 2027 en coordinación entre el gobierno estatal y la Conade.</t>
-  </si>
-  <si>
-    <t>SEPH, Gobernador, Inhide</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Rommel Pacheco</t>
-  </si>
-  <si>
-    <t>Implementará la SSPH operativo en la Feria</t>
-  </si>
-  <si>
-    <t>La SSPH desplegará un operativo de vigilancia con Policía Estatal, C5i, Bomberos y Tránsito dentro y fuera del recinto ferial San Francisco Pachuca 2026.</t>
-  </si>
-  <si>
-    <t>La SSPH dispondrá un operativo de seguridad permanente con patrullajes, videovigilancia del C5i y módulos de bomberos durante la Feria de San Francisco 2026.</t>
-  </si>
-  <si>
-    <t>SSPH, C5i, Bomberos, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Violencia familiar, el delito más recurrente</t>
-  </si>
-  <si>
-    <t>Pachuca acumuló 854 denuncias por violencia familiar de enero a julio de 2026, superando al fraude y las amenazas, señala reporte del SESNSP analizado por la UAEH.</t>
-  </si>
-  <si>
-    <t>Violencia familiar</t>
-  </si>
-  <si>
-    <t>Reporte del SESNSP ubica a la violencia familiar como el delito de mayor incidencia en Pachuca durante los primeros siete meses del año con 854 carpetas.</t>
-  </si>
-  <si>
-    <t>PGJEH, Presidencia, UAEH</t>
-  </si>
-  <si>
-    <t>Gloria Contreras Jiménez</t>
-  </si>
-  <si>
-    <t>Prevén cambio de modelo para la Escuela de Música</t>
-  </si>
-  <si>
-    <t>La SEPH proyecta integrar a la EMEH dentro del subsistema de universidades politécnicas-tecnológicas al sumar licenciaturas como Cinematografía y posgrados.</t>
-  </si>
-  <si>
-    <t>La SEPH analiza reestructurar el modelo educativo de la Escuela de Música de Hidalgo para incorporarla al sistema de universidades politécnicas y tecnológicas.</t>
-  </si>
-  <si>
-    <t>SEPH, EMEH</t>
-  </si>
-  <si>
-    <t>Huachitúnel de 143 metros, destruido</t>
-  </si>
-  <si>
-    <t>Autoridades federales y estatales destruyeron un túnel huachicolero de 143 metros de largo en Teocalco, Tlaxcoapan. Suman 17 túneles inhabilitados en 2026.</t>
-  </si>
-  <si>
-    <t>Quedó destruido un pasadizo de 143 metros utilizado para el robo de hidrocarburo en Teocalco, Tlaxcoapan, alcanzando 17 túneles inhabilitados de junio a septiembre en Hidalgo.</t>
-  </si>
-  <si>
-    <t>FGR, Pemex, PGJEH, SSPH, Segobh, Ferromex</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna</t>
-  </si>
-  <si>
-    <t>Hidalgo será sede del Campeonato de Boccia 2026 y la Olimpiada Nacional 2027</t>
-  </si>
-  <si>
-    <t>Hidalgo será una de las seis sedes de la Olimpiada Nacional 2027, confirmó Rommel Pacheco, director de la Comisión Nacional de Cultura Física y Deporte (Conade), durante una conferencia de prensa realizada con motivo del anuncio del Campeonato Centroamericano y del Caribe de Boccia 2026. La entidad compartirá la sede de esta justa multidisciplinaria con Coahuila, Veracruz, Tamaulipas, Oaxaca y la UNAM.</t>
-  </si>
-  <si>
-    <t>Rommel Pacheco, titular de la Conade, anunció que Hidalgo albergará la Olimpiada Nacional 2027 y el Campeonato Centroamericano y del Caribe de Boccia 2026.</t>
-  </si>
-  <si>
-    <t>SEPH, Conade, Inhide</t>
-  </si>
-  <si>
-    <t>Rommel Pacheco, Liliana Suárez Carreón</t>
-  </si>
-  <si>
-    <t>Persiste maltrato animal en Hidalgo; judicializan 21 carpetas de investigación</t>
-  </si>
-  <si>
-    <t>Ana Lilia Martínez Hernández, titular de la Unidad Especializada en la Investigación de Delitos en Contra de los Animales, dio a conocer a Síntesis Hidalgo que, de 81 carpetas de investigación integradas por agravios contra animales, 21 han sido judicializadas, de las cuales se han obtenido 14 sentencias condenatorias en municipios como Pachuca, Mineral de la Reforma, Tizayuca y Tula.</t>
-  </si>
-  <si>
     <t>Maltrato animal</t>
   </si>
   <si>
-    <t>La PGJEH ha judicializado 21 carpetas por maltrato animal en Hidalgo y logrado 14 sentencias condenatorias, reportó la Unidad Especializada.</t>
-  </si>
-  <si>
     <t>Marco Cerón</t>
   </si>
   <si>
-    <t>Ana Lilia Martínez Hernández</t>
-  </si>
-  <si>
-    <t>Destruyen túnel ligado al huachicol en Tlaxcoapan; van 17</t>
-  </si>
-  <si>
-    <t>En la localidad de Teocalco, municipio de Tlaxcoapan, el Gabinete de Seguridad asistió a la destrucción de un túnel de 143 metros de longitud relacionado con el robo de hidrocarburo. Con este operativo suman 17 túneles inhabilitados en Hidalgo entre junio y septiembre de 2026, informó el secretario de Gobierno, Guillermo Olivares Reyna.</t>
-  </si>
-  <si>
-    <t>Autoridades estatales y federales destruyeron un huachitúnel de 143 metros en Tlaxcoapan, alcanzando 17 estructuras eliminadas en la entidad.</t>
-  </si>
-  <si>
-    <t>Segobh, FGR, Ferromex, Pemex, PGJEH, SSPH, PC</t>
-  </si>
-  <si>
-    <t>Hidalgo reportó tres secuestros en agosto 2026</t>
-  </si>
-  <si>
-    <t>En agosto, la PGJEH inició tres carpetas de investigación por secuestro (dos extorsivos y un exprés), cifra máxima en 29 meses según datos del SESNSP.</t>
-  </si>
-  <si>
     <t>Secuestro</t>
   </si>
   <si>
-    <t>La PGJEH registró tres carpetas de investigación por secuestro en agosto en Hidalgo, la cifra mensual más alta en 29 meses según el SESNSP.</t>
-  </si>
-  <si>
     <t>PGJEH, Presidencia</t>
   </si>
   <si>
-    <t>Todo listo para el arranque de la feria de San Francisco 2026</t>
-  </si>
-  <si>
-    <t>Las instalaciones de la Feria San Francisco Pachuca 2026 se encuentran preparadas para iniciar 25 días de actividades culturales, gastronómicas y espectáculos.</t>
-  </si>
-  <si>
-    <t>Arranca la Feria San Francisco Pachuca 2026 con espectáculos musicales, muestras artesanales y gastronomía durante 25 días de actividades.</t>
-  </si>
-  <si>
     <t>Turismo, Ayuntamiento</t>
   </si>
   <si>
-    <t>Las denuncias por tortura se disparan en un 400 por ciento</t>
-  </si>
-  <si>
-    <t>Las denuncias por tortura en Hidalgo aumentaron 400% en agosto al registrar cinco carpetas de investigación ante la PGJEH, situando a la entidad en el lugar 12 nacional.</t>
-  </si>
-  <si>
-    <t>Tortura</t>
-  </si>
-  <si>
-    <t>Reporte del SESNSP indica que en agosto las denuncias por tortura en Hidalgo crecieron 400% con cinco querellas iniciadas ante la PGJEH.</t>
-  </si>
-  <si>
-    <t>Autoridades advierten que hay un repunte de enfermedades diarreicas</t>
-  </si>
-  <si>
-    <t>Personal de la Jurisdicción Sanitaria 2 advirtió durante sesión del Cojuve que las enfermedades diarreicas registraron un repunte por relajamiento en medidas de higiene.</t>
-  </si>
-  <si>
     <t>Vigilancia Epidemiológica</t>
   </si>
   <si>
-    <t>Autoridades de salud en la región Tulancingo llamaron a reforzar la higiene y lavado de manos ante el incremento de padecimientos diarreicos.</t>
-  </si>
-  <si>
-    <t>Emiten recomendaciones a concesionarios de FUTVEH</t>
-  </si>
-  <si>
-    <t>El dirigente de la FUTVEH informó que emiten recomendaciones a concesionarios para mantener actualizadas las pólizas de seguro del transporte público ante operativos de la Semot.</t>
-  </si>
-  <si>
-    <t>Supervisión de Transporte</t>
-  </si>
-  <si>
-    <t>Dirigencia de transportistas en Pachuca exhorta a permisionarios a vigilar la vigencia de seguros de unidades para evitar sanciones y revocaciones por parte de la Semot.</t>
-  </si>
-  <si>
-    <t>Eleno Arias Pérez</t>
-  </si>
-  <si>
-    <t>Fue cancelado el registro de 6 proveedores y contratistas</t>
-  </si>
-  <si>
-    <t>La Secretaría de Contraloría publicó en el POEH la cancelación del registro e inhabilitación por 5 y 6 años de dos empresas y cuatro personas físicas.</t>
-  </si>
-  <si>
-    <t>Contraloría estatal sancionó e inhabilitó a cinco proveedores y una contratista para impedirles celebrar contratos con ayuntamientos y el gobierno de Hidalgo.</t>
-  </si>
-  <si>
-    <t>Contraloría, SEPH</t>
-  </si>
-  <si>
-    <t>Maritza Yazmín Estrada Ortiz, Lizbeth Pedraza Quijada, Laura Flores Méndez</t>
-  </si>
-  <si>
-    <t>Llegarán a Hidalgo millón y medio de vacunas contra la influenza y el Covid-19</t>
-  </si>
-  <si>
-    <t>La SSH programa la llegada y distribución de 1.5 millones de dosis de vacunas contra influenza y Covid-19 en la entidad para la campaña invernal a partir del 12 de octubre.</t>
-  </si>
-  <si>
-    <t>Campaña de vacunación</t>
-  </si>
-  <si>
-    <t>Sector salud en Hidalgo prepara la aplicación de 1.5 millones de biológicos contra enfermedades respiratorias durante la temporada invernal 2026-2027.</t>
-  </si>
-  <si>
-    <t>SSH, IMSS, ISSSTE, Pemex</t>
-  </si>
-  <si>
-    <t>Investigan irregularidades en programa social para mujeres</t>
-  </si>
-  <si>
-    <t>La Contraloría estatal abrió expediente de verificación física y documental en Xochiatipan ante posible entrega irregular de apoyos del programa social para mujeres.</t>
-  </si>
-  <si>
-    <t>Xochiatipan</t>
-  </si>
-  <si>
-    <t>Auditorías</t>
-  </si>
-  <si>
-    <t>Secretaría de Contraloría indaga denuncia realizada en buzón QR sobre presuntas inconsistencias en el padrón de beneficiarias de Bienestar en Xochiatipan.</t>
-  </si>
-  <si>
     <t>Salomón Hernández</t>
   </si>
   <si>
-    <t>Contraloría, Bienestar, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Briseyda Torres Martínez</t>
-  </si>
-  <si>
-    <t>Padres de familia de primaria exigen cambio del director y la renovación del comité</t>
-  </si>
-  <si>
-    <t>Tutores de la primaria Leona Vicario en Tulancingo se manifestaron afuera del plantel exigiendo cuentas claras del manejo financiero de cuotas y la destitución del director.</t>
-  </si>
-  <si>
-    <t>Quejas padres de familia</t>
-  </si>
-  <si>
-    <t>Manifestación de padres de familia en escuela de Tulancingo solicita la intervención inmediata de las autoridades de la SEPH para renovar la mesa directiva.</t>
-  </si>
-  <si>
-    <t>Tulancingo concentra apoyos para fortalecer actividades del campo</t>
-  </si>
-  <si>
-    <t>La Saderh entregó 8.5 mdp en apoyos agrícolas, crías de peces, huertos familiares y sistemas fotovoltaicos en beneficio de 179 productores hidalguenses.</t>
-  </si>
-  <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>Entrega regional de apoyos a productores del campo en Tulancingo busca dignificar la producción agrícola y acuícola con equipamiento e insumos.</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez</t>
-  </si>
-  <si>
-    <t>Carrera del COBAEH San Ildefonso promueve salud y convivencia juvenil</t>
-  </si>
-  <si>
-    <t>Más de 160 estudiantes de Tepeji del Río se reunieron en la carrera deportiva del Cobaeh enfocada en la activación física e integración escolar.</t>
-  </si>
-  <si>
-    <t>Tepeji del Río</t>
-  </si>
-  <si>
-    <t>Carrera atlética</t>
-  </si>
-  <si>
-    <t>Jornada deportiva estudiantil en Tepeji del Río promovió hábitos saludables y valores de convivencia entre la juventud del subsistema Cobaeh.</t>
-  </si>
-  <si>
-    <t>SEPH, Ayuntamiento, DIFH</t>
-  </si>
-  <si>
-    <t>Suman un total de 23 casos de gusano barrenador en Hidalgo</t>
-  </si>
-  <si>
-    <t>De acuerdo con el Boletín Epidemiológico de la Secretaría de Salud Federal, Hidalgo registra 23 casos de gusano barrenador en humanos en lo que va de 2026, ubicándose en novena posición nacional.</t>
-  </si>
-  <si>
-    <t>Hidalgo suma 23 casos acumulados de miasis por gusano barrenador en humanos durante 2026 sin registrar defunciones.</t>
-  </si>
-  <si>
-    <t>SSH, Presidencia</t>
-  </si>
-  <si>
-    <t>Taxis cobrarán hasta 133 pesos desde la feria</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte publicó el tarifario oficial para traslados desde la Feria Pachuca 2026, fijando cobros de 45 a 133 pesos según el destino.</t>
-  </si>
-  <si>
-    <t>Semot emitió el tabulador oficial de taxis para la Feria de Pachuca 2026 con tarifa mínima de 45 pesos y máxima de 133 a municipios conurbados.</t>
-  </si>
-  <si>
-    <t>Hidalgo, sede de Orgullo Nacional 2027 y del Campeonato Centroamericano de Boccia</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca y Rommel Pacheco, titular de la Conade, anunciaron que Hidalgo albergará la competencia Orgullo Nacional 2027 y el Centroamericano de Boccia 2026.</t>
-  </si>
-  <si>
-    <t>Hidalgo fue confirmado como sede principal de la justa juvenil Orgullo Nacional 2027 y del Campeonato Centroamericano de Boccia 2026.</t>
-  </si>
-  <si>
-    <t>SEPH, Gobernador, Presidencia</t>
-  </si>
-  <si>
-    <t>Entró en vigor el incremento del 20 por ciento a las tarifas del transporte en Pachuca</t>
-  </si>
-  <si>
-    <t>Publicaron en el POEH el acuerdo que autoriza el alza de tarifa inicial de taxi a 45 pesos e inicia la transición progresiva hacia taxímetros digitales.</t>
-  </si>
-  <si>
-    <t>Sube 20% la tarifa de taxis en Pachuca y Mineral de la Reforma con banderazo oficial de 45 pesos publicado en el POEH.</t>
-  </si>
-  <si>
-    <t>Atrae Hidalgo más de 147 mil MDP en inversión privada</t>
-  </si>
-  <si>
-    <t>La Unidad de Planeación y Prospectiva destacó la atracción de 147 mil 697 millones de pesos en capital privado durante la actual administración.</t>
-  </si>
-  <si>
-    <t>Uplaph reportó una cifra acumulada superior a 147 mil mdp en inversión privada consolidada en parques industriales de la entidad.</t>
-  </si>
-  <si>
     <t>Planeación</t>
   </si>
   <si>
-    <t>Planeación, Uplaph</t>
-  </si>
-  <si>
-    <t>Vacunarán a más de 202 mil perros y gatos en la Semana de Reforzamiento Antirrábico</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo aplicará 202 mil dosis de vacuna antirrábica en los 84 municipios durante la jornada de reforzamiento.</t>
-  </si>
-  <si>
-    <t>Vacunación Antirrábica</t>
-  </si>
-  <si>
-    <t>Arrancó la Semana Nacional de vacunación antirrábica en Hidalgo para inmunizar a más de 202 mil mascotas.</t>
-  </si>
-  <si>
-    <t>Padres de familia cierran escuela Leona Vicario y exigen cambio de comité</t>
-  </si>
-  <si>
-    <t>Toman las instalaciones del plantel educativo en Tulancingo exigiendo auditoría al comité de padres y señalando presunto desvío de recursos.</t>
-  </si>
-  <si>
-    <t>Tutores de la primaria Leona Vicario en Tulancingo protestan y cierran la escuela solicitando transparencia en las cuotas escolares.</t>
-  </si>
-  <si>
-    <t>Jesús Riveros</t>
-  </si>
-  <si>
-    <t>Implementa la SSPH operativo especial de vigilancia por la Feria San Francisco Pachuca 2026</t>
-  </si>
-  <si>
-    <t>La Policía Estatal desplegará unidades de vigilancia permanente en zonas comerciales, estacionamientos y escenarios del recinto ferial.</t>
-  </si>
-  <si>
-    <t>Operativo de Seguridad</t>
-  </si>
-  <si>
-    <t>SSPH activó el operativo de prevención y vialidad para resguardar a los visitantes de la Feria de San Francisco en Pachuca.</t>
-  </si>
-  <si>
-    <t>SSPH, C5i</t>
-  </si>
-  <si>
-    <t>Tuzobús modifica operación y anuncia servicio especial nocturno por Feria Pachuca 2026</t>
-  </si>
-  <si>
-    <t>El sistema troncal permitirá paradas especiales en estaciones Vicente Segura y Juan C. Doria y dará servicio nocturno de 23:00 a 03:00 horas.</t>
-  </si>
-  <si>
-    <t>Afluencia Tuzobús</t>
-  </si>
-  <si>
-    <t>Tuzobús extenderá horario con rutas nocturnas de Cetram Téllez a Centro Histórico por la Feria de Pachuca.</t>
-  </si>
-  <si>
-    <t>Semot, Sitmah</t>
-  </si>
-  <si>
-    <t>Sancionan a 35 personas por ofrecer servicio de taxi mediante aplicación</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte informó sobre infracciones a choferes por operar plataformas digitales no autorizadas en la entidad.</t>
-  </si>
-  <si>
-    <t>Semot aplicó 35 sanciones durante operativos de inspección a unidades que prestaban servicio ejecutivo sin concesión.</t>
-  </si>
-  <si>
-    <t>Descubren y aseguran en Atitalaquia y Teocalco sofisticada red de túneles y tomas clandestinas</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad estatales y federales inhabilitaron dos excavaciones de alta tecnología conectadas a ductos de Pemex en la región Tula.</t>
-  </si>
-  <si>
-    <t>Autoridades inhabilitaron dos subterráneos huachicoleros en Atitalaquia y Tlaxcoapan equipados con mangueras de alta presión.</t>
-  </si>
-  <si>
-    <t>Segobh, SSPH, Pemex, FGR</t>
-  </si>
-  <si>
-    <t>Ya es oficial: suben tarifa de los taxis en Pachuca y Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Entran en vigor las nuevas tarifas de transporte individual con banderazo de 45 pesos y recargo del 20% en horario nocturno.</t>
-  </si>
-  <si>
-    <t>Semot oficializó en el periódico oficial las tarifas de taxi para Pachuca con sanciones de hasta 15 mil pesos por cobros indebidos.</t>
-  </si>
-  <si>
-    <t>Garantizan transporte, así como vigilancia y servicio especial nocturno para la Feria San Francisco 2026</t>
-  </si>
-  <si>
-    <t>SSPH y Semot desplegarán operativos coordinados con células de vigilancia y transporte nocturno de 10 pesos durante la Feria de Pachuca.</t>
-  </si>
-  <si>
-    <t>Autoridades estatales implementarán un despliegue operativo conjunto de seguridad y movilidad para los asistentes a la Feria de Pachuca.</t>
-  </si>
-  <si>
-    <t>SSPH, Semot, Sitmah, C5i</t>
-  </si>
-  <si>
-    <t>Eliminan túnel de huachicol de 143 metros situado en Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>El Gabinete de Seguridad inhabilitó una excavación subterránea de 143 metros de longitud utilizada para la extracción ilícita de hidrocarburo en Teocalco.</t>
-  </si>
-  <si>
-    <t>Destruyen túnel clandestino en Tlaxcoapan tras peritajes de la FGR en operativo conjunto de seguridad.</t>
-  </si>
-  <si>
-    <t>Segobh, SSPH, FGR</t>
-  </si>
-  <si>
-    <t>Van a demoler primaria Aquiles Serdán en Tulancingo; edificarán otra</t>
-  </si>
-  <si>
-    <t>La SEPH demolerá la primaria Aquiles Serdán en Tulancingo por daños estructurales y reubicará provisionalmente a la plantilla escolar.</t>
-  </si>
-  <si>
-    <t>Educación Pública reconstruirá totalmente la escuela primaria Aquiles Serdán evaluando alternativas de clases híbridas o presenciales.</t>
+    <t>Magda Acuña</t>
+  </si>
+  <si>
+    <t>Nosocomio de mil 617 mdp, sin funcionar</t>
+  </si>
+  <si>
+    <t>El inmueble del nuevo Hospital General de Pachuca permanece sin operación, con basura y daños visibles, mientras la Secretaría de Salud estatal indicó que está en proceso de transferencia a la federación.</t>
+  </si>
+  <si>
+    <t>IMSS Bienestar</t>
+  </si>
+  <si>
+    <t>A cuatro años de su inauguración, el nuevo Hospital General de Pachuca no ha sido recibido por el IMSS-Bienestar y continúa cerrado.</t>
+  </si>
+  <si>
+    <t>SSH, IMSS-Bienestar</t>
+  </si>
+  <si>
+    <t>Omar Fayad Meneses</t>
+  </si>
+  <si>
+    <t>Feria recibió a sus primeros visitantes</t>
+  </si>
+  <si>
+    <t>Visitantes de municipios como Zapotlán, Tetepango y Pachuca acudieron a la apertura del recinto ferial a partir de las 13:00 horas para disfrutar de las atracciones y del concierto del grupo Bronco.</t>
+  </si>
+  <si>
+    <t>Con la apertura de pabellones y ambiente festivo, inició la Feria San Francisco Pachuca 2026 registrando la llegada de familias desde el primer día.</t>
+  </si>
+  <si>
+    <t>Casimiro Márquez Reyes</t>
+  </si>
+  <si>
+    <t>Taxis que incumplan tarifa serán sancionados</t>
+  </si>
+  <si>
+    <t>Tras la publicación del tarifario en el POEH con un costo mínimo de 45 pesos, autoridades estatales y municipales coordinarán operativos para vigilar que los conductores respeten las tarifas oficiales.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca advirtió sanciones y la posible retirada de concesiones a taxistas que cobren tarifas superiores a las autorizadas.</t>
+  </si>
+  <si>
+    <t>Semot, SSPH, Gobernador</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Distribuyen recursos a empresarios</t>
+  </si>
+  <si>
+    <t>Beneficiarios de 74 municipios recibieron 25 mil pesos cada uno para fortalecer microempresas de giros comerciales, de servicios y producción artesanal en la entidad.</t>
+  </si>
+  <si>
+    <t>Apoyo a emprendedores</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca entregó 760 apoyos económicos del programa Emprendiendo paso a paso 2026 por un total de 20 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Gobernador</t>
+  </si>
+  <si>
+    <t>Gobernador, Sedeco, IHCE</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Carlos Henkel Escorza</t>
+  </si>
+  <si>
+    <t>Respaldan obra de Caasim en el Ramón G. Bonfil</t>
+  </si>
+  <si>
+    <t>A pesar de las molestias temporales por polvo y tráfico, locatarios señalaron que la obra resolverá el desabasto de agua que padecían desde hace 15 días en la colonia Santa Julia.</t>
+  </si>
+  <si>
+    <t>Infraestructura Hidráulica</t>
+  </si>
+  <si>
+    <t>Comerciantes del bulevar Ramón G. Bonfil manifestaron su respaldo a los trabajos de sustitución de tubería de agua potable realizados por Caasim.</t>
+  </si>
+  <si>
+    <t>Sipdus, Caasim</t>
+  </si>
+  <si>
+    <t>Eusebio Fidel Orta</t>
+  </si>
+  <si>
+    <t>Educación analiza riesgos de IA en emociones de niños y jóvenes</t>
+  </si>
+  <si>
+    <t>El impacto de la inteligencia artificial en las emociones de niños y docentes fue uno de los temas centrales del encuentro estatal 'Voces que transforman', organizado por la Secretaría de Educación Pública de Hidalgo para evaluar los algoritmos y la inclusión digital.</t>
+  </si>
+  <si>
+    <t>Educación socioemocional</t>
+  </si>
+  <si>
+    <t>La SEPH realizó el encuentro 'Voces que transforman' para evaluar el impacto de la inteligencia artificial y los algoritmos digitales en la salud emocional de los estudiantes.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón, Xóchitl García</t>
+  </si>
+  <si>
+    <t>Buscan ampliación de capacidades para uso de la tecnología</t>
+  </si>
+  <si>
+    <t>La inteligencia artificial y la ciberseguridad comienzan a ocupar un espacio estratégico en Hidalgo con la búsqueda de alianzas entre instituciones educativas y actores especializados. La DESCTI sostuvo un encuentro con la Embajada de Estados Unidos.</t>
+  </si>
+  <si>
+    <t>Innovación tecnológica</t>
+  </si>
+  <si>
+    <t>La DESCTI sostuvo una reunión con la Embajada de Estados Unidos para fortalecer alianzas estratégicas en ciberseguridad e inteligencia artificial.</t>
+  </si>
+  <si>
+    <t>Planeación, DESCTI</t>
+  </si>
+  <si>
+    <t>Alejandro Franco Segura, Andrew Chapman</t>
+  </si>
+  <si>
+    <t>¡Pequeños guerreros! ¿Y si una consulta a tiempo pudiera cambiar una historia?</t>
+  </si>
+  <si>
+    <t>Dorado, informarnos sobre el cáncer infantil nos ayuda a reconocer la importancia de la atención oportuna. En septiembre, Mes Dorado, se fomenta la concienciación y consulta oportuna para salvar vidas de niños.</t>
+  </si>
+  <si>
+    <t>Cáncer Infantil</t>
+  </si>
+  <si>
+    <t>En el marco del Mes Dorado, autoridades de salud enfatizan la importancia de la detección oportuna y consulta médica a tiempo del cáncer infantil.</t>
+  </si>
+  <si>
+    <t>Empresas buscarán talento en Empleotón</t>
+  </si>
+  <si>
+    <t>Personas con discapacidad, adultos mayores y mujeres que buscan reincorporarse al mercado laboral tendrán el próximo 9 de octubre una jornada de empleo con participación de más de 15 empresas en la Feria Nacional de Empleo para Grupos Vulnerables.</t>
+  </si>
+  <si>
+    <t>Feria De Empleo</t>
+  </si>
+  <si>
+    <t>La STPSH anunció la celebración de la Feria Nacional de Empleo para Grupos Vulnerables con la participación de más de 15 empresas oferentes.</t>
+  </si>
+  <si>
+    <t>STPSH</t>
+  </si>
+  <si>
+    <t>Oscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>Destinan 19 mdp a emprendedores</t>
+  </si>
+  <si>
+    <t>Para quienes tuvieron que enfrentar las afectaciones de la vaguada monzónica, el apoyo llega como una posibilidad de recuperación. El gobernador Julio Menchaca Salazar defendió la decisión de entregar recursos directamente a los beneficiarios del programa Emprendiendo paso a paso.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca entregó 760 apoyos del programa Emprendiendo Paso a Paso, destinando especial atención a personas afectadas por contingencias climáticas.</t>
+  </si>
+  <si>
+    <t>Gobernador, Sedeco</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Carlos Henkel Escorza, Alejandra Hernández</t>
+  </si>
+  <si>
+    <t>Fijan tarifas de taxis en hasta $133 al salir de feria</t>
+  </si>
+  <si>
+    <t>Salir de la Feria San Francisco Pachuca en taxi tendrá un costo de entre 45 y 133 pesos, dependiendo del destino, de acuerdo con el tarifario público emitido por la Secretaría de Movilidad y Transporte. La tarifa mínima será de 45 pesos para destinos cercanos.</t>
+  </si>
+  <si>
+    <t>Tarifario Feria Pachuca</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad fijó el tabulador de tarifas para el servicio de taxis desde las instalaciones de la Feria de San Francisco, con costos de $45 a $133 según el destino.</t>
+  </si>
+  <si>
+    <t>El Hijo del Santo</t>
+  </si>
+  <si>
+    <t>Hay más de 42 mil víctimas de delitos</t>
+  </si>
+  <si>
+    <t>Hidalgo registró 42 mil 457 víctimas de delitos del fuero común entre enero y agosto de este año, de acuerdo con el Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública. Las lesiones lideran con 8,051 casos.</t>
+  </si>
+  <si>
+    <t>Un informe del SESNSP reporta 42,457 víctimas de delitos en Hidalgo entre enero y agosto de 2026, destacando lesiones y violencia familiar entre los más recurrentes.</t>
+  </si>
+  <si>
+    <t>FASP reporta avances en indicadores</t>
+  </si>
+  <si>
+    <t>El Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública dio a conocer los indicadores del primer trimestre del Fondo de Aportaciones para la Seguridad Pública (FASP), con un avance de 43.8 por ciento.</t>
+  </si>
+  <si>
+    <t>FASP</t>
+  </si>
+  <si>
+    <t>El Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública reportó un avance del 43.8% en los indicadores del Fondo de Aportaciones para la Seguridad Pública.</t>
+  </si>
+  <si>
+    <t>Segobh, SSPH</t>
+  </si>
+  <si>
+    <t>PIBEH suma 229 policías con bachillerato</t>
+  </si>
+  <si>
+    <t>Doscientos veintinueve elementos de la Policía Industrial Bancaria del Estado de Hidalgo concluyeron su educación media superior mediante el programa Mi Prepa Digital, permitiendo certificar a 130 trabajadores.</t>
+  </si>
+  <si>
+    <t>Capacitación policial</t>
+  </si>
+  <si>
+    <t>La Policía Industrial Bancaria de Hidalgo certificó a 229 elementos en educación media superior mediante el programa Mi Prepa Digital.</t>
+  </si>
+  <si>
+    <t>SSPH, PIBEH</t>
+  </si>
+  <si>
+    <t>Escuelas de Huejutla se preparan para Xantolo 2026</t>
+  </si>
+  <si>
+    <t>Las escuelas de Huejutla comenzaron a prepararse para su participación en el Xantolo 2026, con actividades que incluirán exposiciones, demostraciones de cuadrillas y manifestaciones relacionadas con el Día de Muertos.</t>
+  </si>
+  <si>
+    <t>Huejutla</t>
+  </si>
+  <si>
+    <t>Xantolo</t>
+  </si>
+  <si>
+    <t>Planteles educativos de Huejutla iniciaron ensayos de cuadrillas de disfrazados y preparación de altares rumbo a las festividades tradicionales del Xantolo 2026.</t>
+  </si>
+  <si>
+    <t>SEPH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Hidalgo llevará su cultura a Tlaxkallan</t>
+  </si>
+  <si>
+    <t>El son huasteco, las danzas, los carnavales y la artesanía hidalguense llegarán este viernes al Palacio de Cultura de Tlaxcala, donde Hidalgo participa como estado invitado en el Festival Tlaxcallan 2026.</t>
+  </si>
+  <si>
+    <t>Exposición cultural</t>
+  </si>
+  <si>
+    <t>Más de 300 agentes culturales, danzantes y artesanos de Hidalgo participarán como estado invitado en el Festival Tlaxcallan 2026.</t>
+  </si>
+  <si>
+    <t>Cultura</t>
+  </si>
+  <si>
+    <t>Entregan 760 apoyos a emprendedores; 191 afectados por vaguada</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar realizó la entrega de 760 apoyos del programa Emprendiendo Paso a Paso 2026, de los cuales 191 fueron para afectados por la vaguada monzónica de octubre del año pasado. Carlos Henkel Escorza, titular de Sedeco, explicó que se destinaron 20 millones de pesos.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca entregó 760 apoyos de 25 mil pesos del programa Emprendiendo Paso a Paso 2026, beneficiando a emprendedores y afectados por lluvias en 23 municipios.</t>
+  </si>
+  <si>
+    <t>Sedeco</t>
+  </si>
+  <si>
+    <t>Sedeco, IHCE, Gobernador</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Carlos Henkel Escorza, Carlos Martín Pérez Quijano</t>
+  </si>
+  <si>
+    <t>Estacionamiento: $150</t>
+  </si>
+  <si>
+    <t>La Operadora de Eventos de Hidalgo confirmó que la tarifa oficial del estacionamiento de la Feria de Pachuca es de 150 pesos, advirtiendo que no debe cobrarse en vía pública.</t>
+  </si>
+  <si>
+    <t>La OEEH estableció una cuota fija de 150 pesos para el estacionamiento ferial y coordinará operativos viales con la Semot y policía municipal.</t>
+  </si>
+  <si>
+    <t>Turismo, OEEH, Semot</t>
+  </si>
+  <si>
+    <t>Tras dos años, dan fecha para fallo por triple feminicidio en Tulantepec</t>
+  </si>
+  <si>
+    <t>Los Juzgados de Control fijaron para el 8 de octubre el fallo definitivo por el triple feminicidio de dos hermanas y una amiga ocurrido en Santiago Tulantepec en julio de 2024. Los tres imputados rechazaron declarar en la última audiencia.</t>
+  </si>
+  <si>
+    <t>Santiago Tulantepec</t>
+  </si>
+  <si>
+    <t>Feminicidio</t>
+  </si>
+  <si>
+    <t>Juez emitirá sentencia el 8 de octubre por el caso de triple feminicidio en Santiago Tulantepec; familiares de las víctimas exigen la pena máxima.</t>
+  </si>
+  <si>
+    <t>PGJEH, TSJEH</t>
+  </si>
+  <si>
+    <t>Sandra Sauza</t>
+  </si>
+  <si>
+    <t>Arranca la Feria San Francisco; hoy la inauguran</t>
+  </si>
+  <si>
+    <t>Abrió sus puertas la Feria San Francisco, al sur de la ciudad, en donde se espera que la gente acuda a los conciertos masivos, así como a los pabellones gastronómico y cultural. El recinto estará vigilado con policía estatal y municipal para seguridad de los visitantes.</t>
+  </si>
+  <si>
+    <t>Abrió sus puertas la Feria San Francisco Pachuca 2026 con un dispositivo de seguridad conjunta entre la policía estatal y municipal para resguardar a los asistentes.</t>
+  </si>
+  <si>
+    <t>Turismo, SSPH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Taxistas de Pachuca ignoran nuevas tarifas</t>
+  </si>
+  <si>
+    <t>Conductores de taxi de la zona metropolitana de Pachuca ignoran el nuevo tarifario publicado en el Periódico Oficial del Estado de Hidalgo y continúan cobrando según su propio criterio, cobrando montos de entre 70 y 150 pesos.</t>
+  </si>
+  <si>
+    <t>Un sondeo de El Universal Hidalgo constató que choferes de taxi en Pachuca no respetan el banderazo oficial de 45 pesos publicado en el POEH y aplican tarifas arbitrarias.</t>
+  </si>
+  <si>
+    <t>Aplican el aumento en Tizayuca aunque aún no les corresponde</t>
+  </si>
+  <si>
+    <t>Usuarios del transporte público en Tizayuca denunciaron que taxistas locales ya cobran el banderazo de 45 pesos en trayectos cortos sin contar con la autorización de la Semot, ya que el municipio pertenece a la fase III del ajuste.</t>
+  </si>
+  <si>
+    <t>Tizayuca</t>
+  </si>
+  <si>
+    <t>Pasajeros de Tizayuca señalaron cobros indebidos de 45 y 50 pesos por parte de taxistas, a pesar de que el incremento autorizado por la Semot aún no aplica en la demarcación.</t>
+  </si>
+  <si>
+    <t>Javier Quezada</t>
+  </si>
+  <si>
+    <t>Semot, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles Gutiérrez</t>
+  </si>
+  <si>
+    <t>Julio Menchaca advierte de sanciones por cobros excesivos</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar advirtió que habrá medidas enérgicas y sanciones contra los taxistas que no respeten el tarifario autorizado, recordando que la falta de seguro o cobros excesivos pueden derivar en la revocación de concesiones.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca instó a la norma tarifaria en el transporte e informó que la autoridad aplicará sanciones severas a los choferes que cobren de más.</t>
+  </si>
+  <si>
+    <t>Gobernador, Semot</t>
+  </si>
+  <si>
+    <t>Entregaron 760 apoyos para emprendedores</t>
+  </si>
+  <si>
+    <t>Un total de 760 personas recibieron apoyos económicos de 25 mil pesos mediante el programa Emprendiendo Paso a Paso 2026 del IHCE; 191 beneficiarios son emprendedores de 21 municipios afectados por la vaguada monzónica del año pasado.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca encabezó la entrega de 19 mdp en apoyos directos de 25 mil pesos a 760 emprendedores del estado a través del IHCE.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Carlos Pérez Quijano</t>
+  </si>
+  <si>
+    <t>Sedentarismo cognitivo, principal riesgo de la IA en las aulas, alertan</t>
+  </si>
+  <si>
+    <t>Durante el Encuentro Estatal para la Mejora Educativa organizado por la SEPH, la especialista Cimenna Chao Rebolledo advirtió que el uso acrítico de Inteligencia Artificial generativa provoca sustitución de la lectura y sedentarismo cognitivo en alumnos.</t>
+  </si>
+  <si>
+    <t>Regulación de dispositivos digitales</t>
+  </si>
+  <si>
+    <t>Especialista de la Ibero expuso en foro de la SEPH sobre los riesgos pedagógicos y socioemocionales de ceder el juicio crítico a herramientas de inteligencia artificial.</t>
+  </si>
+  <si>
+    <t>Cimenna Chao Rebolledo</t>
+  </si>
+  <si>
+    <t>Condenan a dos secuestradores a 50 años</t>
+  </si>
+  <si>
+    <t>La UECS de la PGJEH logró sentencia condenatoria de 50 años de prisión contra dos hombres identificados como J. C. M. F. y A. S. Z. por el secuestro agravado de un comerciante de autos en Progreso de Obregón.</t>
+  </si>
+  <si>
+    <t>Progreso</t>
+  </si>
+  <si>
+    <t>Tribunal dictó sentencia de 50 años de cárcel y pago de reparación de daño a dos plagiarios capturados tras rescatar a una víctima en Progreso de Obregón.</t>
+  </si>
+  <si>
+    <t>PGJEH, UECS</t>
+  </si>
+  <si>
+    <t>En Atracciones Grupo García, 'Me late subirme a los juegos' en la feria 2026</t>
+  </si>
+  <si>
+    <t>En el marco de su 95 aniversario, Atracciones Grupo García instaló más de 20 juegos mecánicos, promociones en la tarjeta MásXMás y acceso gratuito para personas con discapacidad en la Feria San Francisco Pachuca.</t>
+  </si>
+  <si>
+    <t>Grupo García dio a conocer las atracciones familiares y promociones especiales disponibles durante la Feria de Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>Turismo, Otros</t>
+  </si>
+  <si>
+    <t>Los canes con dueño causan ocho de cada 10 agresiones</t>
+  </si>
+  <si>
+    <t>El coordinador de Zoonosis de Tulancingo, Hugo Montiel Díaz, dio a conocer durante la sesión de Vigilancia Epidemiológica que el 80% de mordeduras registradas provienen de perros que tienen propietario pero permanecen sueltos.</t>
+  </si>
+  <si>
+    <t>Autoridades sanitarias de Tulancingo alertaron que la mayoría de los ataques caninos reportados semanalmente corresponden a mascotas con dueño descuidadas en la vía pública.</t>
+  </si>
+  <si>
+    <t>Mirely Santos</t>
+  </si>
+  <si>
+    <t>SSH, IMSS, ISSSTE</t>
+  </si>
+  <si>
+    <t>Hugo Montiel Díaz</t>
+  </si>
+  <si>
+    <t>Exigen esclarecer muerte de perros</t>
+  </si>
+  <si>
+    <t>El Comité Delegacional de Mascotas de Huejutla informó que existen dos carpetas de investigación ante la PGJEH por el envenenamiento y muerte de siete caninos en la colonia Parque de Poblamiento.</t>
+  </si>
+  <si>
+    <t>Vecinos y protectores de animales en Huejutla exigieron justicia y celeridad en las denuncias penales iniciadas tras el hallazgo de perros sin vida por presunto envenenamiento.</t>
+  </si>
+  <si>
+    <t>Francisco Bautista</t>
+  </si>
+  <si>
+    <t>PGJEH, Ayuntamiento, UAEH</t>
+  </si>
+  <si>
+    <t>Programa estatal beneficia a 760 emprendedores de Hidalgo</t>
+  </si>
+  <si>
+    <t>Un total de 760 emprendedores de 74 municipios de Hidalgo recibieron apoyos de 25 mil pesos mediante el programa Emprendiendo paso a paso 2026, con una bolsa de 20 millones de pesos. El beneficio incluyó a 191 emprendedores de 21 municipios afectados por la vaguada monzónica de 2025.</t>
+  </si>
+  <si>
+    <t>Un total de 760 emprendedores hidalguenses recibieron apoyos de 25 mil pesos a través del programa Emprendiendo paso a paso 2026.</t>
+  </si>
+  <si>
+    <t>Berenice Gamboa</t>
+  </si>
+  <si>
+    <t>Sedeco, Gobernador</t>
+  </si>
+  <si>
+    <t>Reforzarán cumplimiento de tarifas de taxis durante la Feria de San Francisco Pachuca</t>
+  </si>
+  <si>
+    <t>Tras la publicación de las nuevas tarifas para el servicio de taxi en la zona metropolitana y de las tarifas especiales con motivo de la Feria de San Francisco Pachuca 2026, el gobernador Julio Menchaca anunció una vigilancia coordinada entre Semot, SSPH y municipios para garantizar su cumplimiento.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca anunció vigilancia coordinada para vigilar el cobro justo de las tarifas de taxis durante la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>Semot, Gobernador, SSPH</t>
+  </si>
+  <si>
+    <t>Dan 50 años de prisión a dos presuntos secuestradores de Progreso</t>
+  </si>
+  <si>
+    <t>Un tribunal de enjuiciamiento dictó fallo condenatorio de 50 años de prisión contra dos sujetos (J.C.M.F. y A.S.Z.) que simularon comprar un vehículo para secuestrar al propietario de un lote de autos en Progreso de Obregón y exigir 600 mil pesos a su familia.</t>
+  </si>
+  <si>
+    <t>Sentencian a 50 años de cárcel a dos secuestradores que privaron de la libertad a un comerciante de autos en Progreso.</t>
+  </si>
+  <si>
+    <t>Claudia Ávila</t>
+  </si>
+  <si>
+    <t>Cuantifican daños en 40 mil pesos en el Parque Cultural</t>
+  </si>
+  <si>
+    <t>El vehículo que se impactó contra diversos elementos del Parque Cultural Hidalguense, tras las fiestas patrias, dejó daños estimados en 40 mil pesos, informó el gobernador Julio Menchaca Salazar. Señaló que las afectaciones serán reparadas mediante el seguro de la unidad.</t>
+  </si>
+  <si>
+    <t>Rehabilitación de espacios públicos</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca informó que los daños causados por un vehículo en el Parque Cultural Hidalguense ascienden a 40 mil pesos y serán cubiertos por el seguro del automóvil.</t>
+  </si>
+  <si>
+    <t>Erick Perales</t>
+  </si>
+  <si>
+    <t>Gobernador, PGJEH</t>
+  </si>
+  <si>
+    <t>Impulsan recuperación de negocios en Hidalgo</t>
+  </si>
+  <si>
+    <t>Un total de 760 personas emprendedoras de 74 municipios recibieron 25 mil pesos cada una para impulsar o fortalecer su proyecto. Del total, 191 apoyos fueron destinados a emprendedores de 21 municipios afectados por la vaguada monzónica.</t>
+  </si>
+  <si>
+    <t>El gobierno del estado entregó 760 apoyos económicos de 25 mil pesos a emprendedores hidalguenses, de los cuales 191 se destinaron a afectados por la vaguada monzónica.</t>
+  </si>
+  <si>
+    <t>Carlos Henkel Escorza, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Bronco enciende el arranque de la Feria</t>
+  </si>
+  <si>
+    <t>La Feria de San Francisco Pachuca 2026 abrió sus puertas este jueves 24 de septiembre con ambiente tranquilo y presentación estelar del grupo Bronco en el Teatro del Pueblo. La inauguración oficial se llevará a cabo este viernes con la presencia del gobernador Julio Menchaca y operativo con 60 elementos de seguridad.</t>
+  </si>
+  <si>
+    <t>La Feria San Francisco Pachuca 2026 inició actividades con la presentación de Bronco y despliegue de seguridad municipal, previo a la inauguración oficial a cargo del gobernador Julio Menchaca.</t>
+  </si>
+  <si>
+    <t>Turismo, Gobernador, Ayuntamiento, SSPH</t>
+  </si>
+  <si>
+    <t>Alumnos del Mexe bloquean autopista para ejercer presión</t>
+  </si>
+  <si>
+    <t>Estudiantes de la Escuela Normal Rural "El Mexe" tomaron por segundo día consecutivo la caseta de San Alejo sobre la autopista México-Tuxpan, permitiendo el paso vehicular a cambio de aportaciones voluntarias, para exigir diálogo con la Presidencia respecto a la investigación del homicidio de un compañero y la restitución del plantel.</t>
+  </si>
+  <si>
+    <t>Protesta estudiantil</t>
+  </si>
+  <si>
+    <t>Normalistas de El Mexe tomaron la caseta de San Alejo en la autopista México-Tuxpan por segundo día consecutivo para solicitar una mesa de diálogo con el Gobierno Federal.</t>
+  </si>
+  <si>
+    <t>SEPH, Presidencia</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Van a demoler primaria en Tulancingo; edificarán otra</t>
+  </si>
+  <si>
+    <t>La escuela primaria Aquiles Serdán de Tulancingo presenta fallas estructurales graves por lo que deberá ser demolida y reconstruida totalmente durante el ciclo escolar 2026-2027, según confirmó el secretario de Educación Pública de Hidalgo, Natividad Castrejón. Se analizan alternativas para reubicar temporalmente a los alumnos en planteles cercanos o modalidades de educación a distancia.</t>
+  </si>
+  <si>
+    <t>La SEPH demolerá y reconstruirá la primaria Aquiles Serdán en Tulancingo debido a daños estructurales, evaluando sedes temporales para atender al alumnado durante el ciclo 2026-2027.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Retirarán concesiones a transportistas que incumplan la ley</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar advirtió que las concesiones de los transportistas que no cumplan con la ley y el esquema tarifario serán retiradas, priorizando la seguridad e integridad de los usuarios.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca advirtió que retirará concesiones a transportistas que violen la ley o abusen de las nuevas tarifas de transporte público.</t>
+  </si>
+  <si>
+    <t>Semot, Gobernador</t>
+  </si>
+  <si>
+    <t>Entregó Gobierno del Estado apoyos del programa Emprendiendo Paso a Paso 2026</t>
+  </si>
+  <si>
+    <t>Durante la entrega simbólica de 760 apoyos del programa Emprendiendo paso a paso 2026, el gobernador Julio Menchaca refrendó el compromiso de generar bienestar en los 84 municipios, entregando 25 mil pesos a cada emprendedor.</t>
+  </si>
+  <si>
+    <t>El Gobierno de Hidalgo entregó estímulos de 25 mil pesos a 760 personas emprendedoras, respaldando proyectos productivos y a familias afectadas por la vaguada monzónica.</t>
+  </si>
+  <si>
+    <t>Sedeco, IHCE</t>
+  </si>
+  <si>
+    <t>Otorgarán 500 becas de excelencia</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Pachuca abrió la convocatoria 2026 de la Beca Municipal a la Excelencia Académica para otorgar 500 becas a estudiantes de primarias públicas de Pachuca con promedio mínimo de 9.5.</t>
+  </si>
+  <si>
+    <t>Becas</t>
+  </si>
+  <si>
+    <t>El DIF Pachuca lanzó la convocatoria para la Beca Municipal a la Excelencia Académica, beneficiando a 500 alumnos de primaria pública con alto desempeño escolar.</t>
+  </si>
+  <si>
+    <t>DIFH</t>
+  </si>
+  <si>
+    <t>DIFH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Por un secuestro, dos hombres pasarán 50 años en la prisión</t>
+  </si>
+  <si>
+    <t>La UECS de la PGJEH obtuvo sentencia de 50 años de prisión contra dos imputados por secuestro agravado en Progreso de Obregón tras fingir interés en comprar un vehículo en 2024.</t>
+  </si>
+  <si>
+    <t>Tribunal dictó condena de 50 años de cárcel a dos secuestradores procesados por la UECS tras privar de la libertad a un comerciante en Progreso de Obregón.</t>
+  </si>
+  <si>
+    <t>Francisco Villeda</t>
+  </si>
+  <si>
+    <t>Se vigilará que taxis respeten las nuevas tarifas: Gobernador</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, aseguró que habrá revisiones coordinadas entre la Semot, la SSPH y los ayuntamientos para evitar cobros no permitidos en el servicio de taxi tras el ajuste tarifario en Pachuca y Mineral de la Reforma.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca advirtió sanciones y retiro de concesiones a taxistas que realicen cobros excesivos fuera del tarifario oficial de 45 pesos por los primeros 4 km.</t>
+  </si>
+  <si>
+    <t>Gobernador, Semot, SSPH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Lyzbeth Robles</t>
+  </si>
+  <si>
+    <t>Repararán los daños en el Parque Cultural Hidalguense, aseguran</t>
+  </si>
+  <si>
+    <t>El responsable de los daños al Parque Cultural Hidalguense Ben Gurión pagó 40 mil pesos y se repararán los desperfectos, confirmó el gobernador Julio Menchaca. Explicó que se trató de un menor de edad que confundió el freno con el acelerador.</t>
+  </si>
+  <si>
+    <t>Un menor de edad responsable de causar destrozos vehiculares en áreas verdes del Parque Ben Gurión cubrió 40 mil pesos para reparar las afectaciones.</t>
+  </si>
+  <si>
+    <t>Estacionamiento de la feria cuesta $150</t>
+  </si>
+  <si>
+    <t>El estacionamiento oficial de la Feria San Francisco Pachuca Hidalgo 2026 tendrá una cuota única de 150 pesos por vehículo por tiempo libre, tarifa que también aplicará en el espacio habilitado en la Plaza de Toros Vicente Segura.</t>
+  </si>
+  <si>
+    <t>Autoridades fijaron en 150 pesos el cobro por tiempo libre en el estacionamiento oficial del recinto ferial y la Plaza de Toros durante la Feria de Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>Jorge Reyes Hernández</t>
+  </si>
+  <si>
+    <t>Naranja subsiste entre plagas y bajos precios</t>
+  </si>
+  <si>
+    <t>Productores citrícolas de la Huasteca hidalguense enfrentan afectaciones del 30% por la plaga del dragón amarillo (HLB) y sequías, aunado a variaciones de precios en el mercado regional.</t>
+  </si>
+  <si>
+    <t>Control de plagas</t>
+  </si>
+  <si>
+    <t>La producción de más de 5 mil hectáreas de naranja en la Huasteca hidalguense enfrenta severas pérdidas por el dragón amarillo y sequía.</t>
+  </si>
+  <si>
+    <t>Antíoco Aquino Leyva, Napoleón González</t>
+  </si>
+  <si>
+    <t>Supervisarán la calidad y peso del cacao y azúcar destinados al Xantolo</t>
+  </si>
+  <si>
+    <t>La Contraloría de Hidalgo inspeccionará el almacenamiento y distribución de 135 mil paquetes de cacao y azúcar en 22 municipios de la Huasteca para las festividades del Xantolo.</t>
+  </si>
+  <si>
+    <t>Entrega De Cacao</t>
+  </si>
+  <si>
+    <t>Inspectores estatales verificarán que los paquetes de cacao y azúcar para el Xantolo cumplan con el peso exacto de un kilo antes de entregarse a las familias.</t>
+  </si>
+  <si>
+    <t>Contraloría, Bienestar</t>
+  </si>
+  <si>
+    <t>Briseyda Torres</t>
   </si>
 </sst>
 </file>
@@ -1227,8 +1191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ52" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ52" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ47" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ47" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1660,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ52"/>
+  <dimension ref="A1:AJ47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1810,22 +1774,25 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
       <c r="D2" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F2" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>45</v>
@@ -1846,19 +1813,19 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>62</v>
       </c>
       <c r="AA2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>57</v>
@@ -1870,43 +1837,48 @@
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AJ2" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F3" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1921,19 +1893,19 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="AA3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>57</v>
@@ -1945,43 +1917,48 @@
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ3" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
       <c r="D4" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F4" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -1996,67 +1973,72 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ4" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
       <c r="D5" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2071,19 +2053,19 @@
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>57</v>
@@ -2095,43 +2077,48 @@
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ5" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F6" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2146,19 +2133,19 @@
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA6">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>57</v>
@@ -2170,43 +2157,48 @@
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AJ6" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>95</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F7" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2221,10 +2213,10 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>56</v>
@@ -2245,37 +2237,42 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ7" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>95</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>45</v>
@@ -2296,19 +2293,19 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>57</v>
@@ -2320,43 +2317,48 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AJ8" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F9" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2371,19 +2373,19 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA9">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>57</v>
@@ -2395,45 +2397,46 @@
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AJ9" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AJ9" s="2"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F10" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2448,10 +2451,10 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="Y10" s="2" t="s">
         <v>58</v>
@@ -2466,49 +2469,54 @@
         <v>57</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD10" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AJ10" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F11" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2523,16 +2531,16 @@
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA11">
         <v>20</v>
@@ -2547,43 +2555,48 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="AJ11" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F12" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G12">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2598,10 +2611,10 @@
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>56</v>
@@ -2610,7 +2623,7 @@
         <v>43</v>
       </c>
       <c r="AA12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>57</v>
@@ -2622,43 +2635,48 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ12" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F13" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G13">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2673,25 +2691,25 @@
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA13">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD13" s="2" t="s">
         <v>44</v>
@@ -2703,36 +2721,37 @@
         <v>41</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AJ13" s="2" t="s">
-        <v>154</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AJ13" s="2"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F14" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G14">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>157</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>48</v>
@@ -2750,52 +2769,53 @@
         <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA14">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB14" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>160</v>
+        <v>41</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH14" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AJ14" s="2" t="s">
         <v>162</v>
       </c>
+      <c r="AJ14" s="2"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
       <c r="D15" s="2" t="s">
         <v>163</v>
       </c>
@@ -2803,13 +2823,13 @@
         <v>164</v>
       </c>
       <c r="F15" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>48</v>
@@ -2824,10 +2844,10 @@
         <v>59</v>
       </c>
       <c r="V15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W15" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>166</v>
@@ -2839,13 +2859,13 @@
         <v>43</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD15" s="2" t="s">
         <v>44</v>
@@ -2857,7 +2877,7 @@
         <v>41</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="AI15" s="2" t="s">
         <v>167</v>
@@ -2866,11 +2886,14 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
       <c r="D16" s="2" t="s">
         <v>168</v>
       </c>
@@ -2878,16 +2901,16 @@
         <v>169</v>
       </c>
       <c r="F16" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -2902,19 +2925,19 @@
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>57</v>
@@ -2926,40 +2949,43 @@
         <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>171</v>
+        <v>41</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="AJ16" s="2"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
       <c r="D17" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F17" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>48</v>
@@ -2977,10 +3003,10 @@
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>58</v>
@@ -2989,7 +3015,7 @@
         <v>43</v>
       </c>
       <c r="AA17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>57</v>
@@ -3001,49 +3027,52 @@
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AJ17" s="2"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F18" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
       <c r="S18">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>59</v>
@@ -3052,16 +3081,16 @@
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="AA18">
         <v>20</v>
@@ -3076,49 +3105,54 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AJ18" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F19" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R19">
         <v>1</v>
       </c>
       <c r="S19">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>59</v>
@@ -3127,75 +3161,76 @@
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA19">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="AJ19" s="2" t="s">
-        <v>185</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="AJ19" s="2"/>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F20" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R20">
         <v>1</v>
       </c>
       <c r="S20">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>59</v>
@@ -3204,19 +3239,19 @@
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA20">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>57</v>
@@ -3228,49 +3263,52 @@
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AJ20" s="2"/>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="C21" t="s">
+        <v>195</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F21" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R21">
         <v>1</v>
       </c>
       <c r="S21">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>59</v>
@@ -3279,16 +3317,16 @@
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA21">
         <v>20</v>
@@ -3303,51 +3341,52 @@
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="AJ21" s="2" t="s">
-        <v>195</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="AJ21" s="2"/>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="C22" t="s">
+        <v>195</v>
+      </c>
       <c r="D22" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F22" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R22">
         <v>1</v>
       </c>
       <c r="S22">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>59</v>
@@ -3356,19 +3395,19 @@
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA22">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB22" s="2" t="s">
         <v>57</v>
@@ -3386,45 +3425,46 @@
         <v>40</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="AJ22" s="2" t="s">
-        <v>87</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="AJ22" s="2"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="C23" t="s">
+        <v>195</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F23" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R23">
         <v>1</v>
       </c>
       <c r="S23">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>59</v>
@@ -3433,19 +3473,19 @@
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA23">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>57</v>
@@ -3457,51 +3497,54 @@
         <v>44</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>74</v>
+        <v>207</v>
       </c>
       <c r="AG23" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>195</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F24" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R24">
         <v>1</v>
       </c>
       <c r="S24">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>59</v>
@@ -3510,19 +3553,19 @@
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA24">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB24" s="2" t="s">
         <v>57</v>
@@ -3534,51 +3577,54 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>209</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>195</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F25" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R25">
         <v>1</v>
       </c>
       <c r="S25">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T25" s="2" t="s">
         <v>59</v>
@@ -3587,16 +3633,16 @@
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>212</v>
+        <v>113</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Y25" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA25">
         <v>20</v>
@@ -3611,51 +3657,54 @@
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>214</v>
+        <v>72</v>
       </c>
       <c r="AG25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>195</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F26" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R26">
         <v>1</v>
       </c>
       <c r="S26">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>59</v>
@@ -3664,19 +3713,19 @@
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA26">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>57</v>
@@ -3688,51 +3737,54 @@
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>219</v>
+        <v>46</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
+        <v>195</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F27" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R27">
         <v>1</v>
       </c>
       <c r="S27">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>59</v>
@@ -3741,19 +3793,19 @@
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>222</v>
+        <v>89</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA27">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB27" s="2" t="s">
         <v>57</v>
@@ -3765,37 +3817,40 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AG27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AJ27" s="2"/>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>195</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F28" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>45</v>
@@ -3807,7 +3862,7 @@
         <v>1</v>
       </c>
       <c r="S28">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>59</v>
@@ -3816,19 +3871,19 @@
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA28">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB28" s="2" t="s">
         <v>57</v>
@@ -3846,43 +3901,46 @@
         <v>41</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AJ28" s="2"/>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>195</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F29" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R29">
         <v>1</v>
       </c>
       <c r="S29">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T29" s="2" t="s">
         <v>59</v>
@@ -3891,10 +3949,10 @@
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>56</v>
@@ -3915,40 +3973,45 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>39</v>
+        <v>235</v>
       </c>
       <c r="AG29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AJ29" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="C30" t="s">
+        <v>195</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F30" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>42</v>
@@ -3957,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="S30">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>59</v>
@@ -3966,10 +4029,10 @@
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>58</v>
@@ -3978,52 +4041,55 @@
         <v>43</v>
       </c>
       <c r="AA30">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB30" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD30" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>89</v>
+        <v>241</v>
       </c>
       <c r="AG30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>47</v>
+        <v>242</v>
       </c>
       <c r="AJ30" s="2"/>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>195</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F31" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>48</v>
@@ -4032,7 +4098,7 @@
         <v>1</v>
       </c>
       <c r="S31">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>59</v>
@@ -4041,16 +4107,16 @@
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>239</v>
+        <v>113</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA31">
         <v>20</v>
@@ -4065,51 +4131,54 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>39</v>
+        <v>246</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>66</v>
+        <v>247</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>241</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>195</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F32" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
       <c r="S32">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T32" s="2" t="s">
         <v>59</v>
@@ -4118,16 +4187,16 @@
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Y32" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA32">
         <v>20</v>
@@ -4142,42 +4211,45 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>76</v>
+        <v>246</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>246</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>195</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F33" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G33">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>48</v>
@@ -4186,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="S33">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T33" s="2" t="s">
         <v>59</v>
@@ -4195,19 +4267,19 @@
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>249</v>
+        <v>89</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA33">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>57</v>
@@ -4219,49 +4291,52 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AG33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="AJ33" s="2"/>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
+      </c>
+      <c r="C34" t="s">
+        <v>255</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F34" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>254</v>
+        <v>45</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R34">
         <v>1</v>
       </c>
       <c r="S34">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T34" s="2" t="s">
         <v>59</v>
@@ -4270,75 +4345,78 @@
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA34">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB34" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>259</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
+      </c>
+      <c r="C35" t="s">
+        <v>255</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F35" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R35">
         <v>1</v>
       </c>
       <c r="S35">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T35" s="2" t="s">
         <v>59</v>
@@ -4347,10 +4425,10 @@
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>56</v>
@@ -4371,40 +4449,45 @@
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ35" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="AJ35" s="2" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>255</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F36" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>48</v>
@@ -4413,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="S36">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T36" s="2" t="s">
         <v>59</v>
@@ -4422,25 +4505,25 @@
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Y36" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA36">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC36" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD36" s="2" t="s">
         <v>44</v>
@@ -4452,45 +4535,48 @@
         <v>41</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>120</v>
+        <v>269</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>268</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
+      </c>
+      <c r="C37" t="s">
+        <v>255</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F37" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>271</v>
+        <v>76</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R37">
         <v>1</v>
       </c>
       <c r="S37">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T37" s="2" t="s">
         <v>59</v>
@@ -4517,16 +4603,16 @@
         <v>57</v>
       </c>
       <c r="AC37" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD37" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH37" s="2" t="s">
         <v>46</v>
@@ -4534,29 +4620,37 @@
       <c r="AI37" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="AJ37" s="2"/>
+      <c r="AJ37" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
+        <v>255</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F38" s="1">
-        <v>46289</v>
+        <v>46290</v>
+      </c>
+      <c r="G38">
+        <v>6</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R38">
         <v>1</v>
@@ -4571,19 +4665,19 @@
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA38">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>57</v>
@@ -4595,34 +4689,39 @@
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AJ38" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="AJ38" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="C39" t="s">
+        <v>255</v>
+      </c>
       <c r="D39" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F39" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>45</v>
@@ -4643,10 +4742,10 @@
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y39" s="2" t="s">
         <v>56</v>
@@ -4667,37 +4766,42 @@
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AG39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ39" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="AJ39" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="C40" t="s">
+        <v>255</v>
+      </c>
       <c r="D40" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F40" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>48</v>
@@ -4715,19 +4819,19 @@
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y40" s="2" t="s">
         <v>56</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA40">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>57</v>
@@ -4745,34 +4849,39 @@
         <v>41</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AJ40" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="AJ40" s="2" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="C41" t="s">
+        <v>255</v>
+      </c>
       <c r="D41" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F41" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -4787,61 +4896,64 @@
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>67</v>
+        <v>290</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z41" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA41">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC41" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>66</v>
+        <v>292</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>94</v>
+        <v>293</v>
       </c>
       <c r="AJ41" s="2"/>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="C42" t="s">
+        <v>255</v>
+      </c>
       <c r="D42" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F42" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>60</v>
+        <v>225</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>48</v>
@@ -4859,10 +4971,10 @@
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Y42" s="2" t="s">
         <v>56</v>
@@ -4889,40 +5001,46 @@
         <v>41</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>292</v>
+        <v>86</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>293</v>
+        <v>227</v>
       </c>
       <c r="AJ42" s="2"/>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="C43" t="s">
+        <v>297</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F43" s="1">
-        <v>46289</v>
+        <v>46290</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R43">
         <v>1</v>
       </c>
       <c r="S43">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T43" s="2" t="s">
         <v>59</v>
@@ -4931,19 +5049,19 @@
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>296</v>
+        <v>66</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AA43">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>57</v>
@@ -4955,46 +5073,54 @@
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ43" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="AJ43" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="C44" t="s">
+        <v>297</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F44" s="1">
-        <v>46289</v>
+        <v>46290</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R44">
         <v>1</v>
       </c>
       <c r="S44">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T44" s="2" t="s">
         <v>59</v>
@@ -5003,19 +5129,19 @@
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA44">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB44" s="2" t="s">
         <v>57</v>
@@ -5027,46 +5153,54 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>301</v>
+        <v>39</v>
       </c>
       <c r="AG44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ44" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="AJ44" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="C45" t="s">
+        <v>297</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F45" s="1">
-        <v>46289</v>
+        <v>46290</v>
+      </c>
+      <c r="G45">
+        <v>7</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R45">
         <v>1</v>
       </c>
       <c r="S45">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>59</v>
@@ -5075,10 +5209,10 @@
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>304</v>
+        <v>152</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>56</v>
@@ -5105,40 +5239,48 @@
         <v>41</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="AJ45" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="AJ45" s="2" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="C46" t="s">
+        <v>297</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F46" s="1">
-        <v>46289</v>
+        <v>46290</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
       <c r="S46">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T46" s="2" t="s">
         <v>59</v>
@@ -5147,19 +5289,19 @@
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA46">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AB46" s="2" t="s">
         <v>57</v>
@@ -5171,46 +5313,54 @@
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AJ46" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AJ46" s="2" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="C47" t="s">
+        <v>297</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F47" s="1">
-        <v>46289</v>
+        <v>46290</v>
+      </c>
+      <c r="G47">
+        <v>6</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R47">
         <v>1</v>
       </c>
       <c r="S47">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>59</v>
@@ -5219,414 +5369,44 @@
         <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>72</v>
+        <v>317</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA47">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AC47" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD47" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ47" s="2"/>
-    </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F48" s="1">
-        <v>46289</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R48">
-        <v>1</v>
-      </c>
-      <c r="S48">
-        <v>13262</v>
-      </c>
-      <c r="T48" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V48" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W48" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="X48" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y48" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z48" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA48">
-        <v>24</v>
-      </c>
-      <c r="AB48" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF48" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG48" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH48" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI48" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="AJ48" s="2"/>
-    </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="AJ47" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F49" s="1">
-        <v>46289</v>
-      </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R49">
-        <v>1</v>
-      </c>
-      <c r="S49">
-        <v>13262</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W49" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="X49" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="Y49" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z49" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA49">
-        <v>20</v>
-      </c>
-      <c r="AB49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC49" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF49" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG49" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH49" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI49" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ49" s="2"/>
-    </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F50" s="1">
-        <v>46289</v>
-      </c>
-      <c r="G50">
-        <v>4</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R50">
-        <v>1</v>
-      </c>
-      <c r="S50">
-        <v>13262</v>
-      </c>
-      <c r="T50" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="X50" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="Y50" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA50">
-        <v>20</v>
-      </c>
-      <c r="AB50" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC50" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF50" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG50" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH50" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI50" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="AJ50" s="2"/>
-    </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F51" s="1">
-        <v>46289</v>
-      </c>
-      <c r="G51">
-        <v>4</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R51">
-        <v>1</v>
-      </c>
-      <c r="S51">
-        <v>13262</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W51" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="X51" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="Y51" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z51" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA51">
-        <v>20</v>
-      </c>
-      <c r="AB51" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC51" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF51" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG51" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH51" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI51" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="AJ51" s="2"/>
-    </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F52" s="1">
-        <v>46289</v>
-      </c>
-      <c r="G52">
-        <v>4</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R52">
-        <v>1</v>
-      </c>
-      <c r="S52">
-        <v>13262</v>
-      </c>
-      <c r="T52" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W52" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="X52" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="Y52" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA52">
-        <v>16</v>
-      </c>
-      <c r="AB52" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC52" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF52" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG52" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ52" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3317E19-8A9D-4BC8-B8EC-D570FC15AE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FBBE8D-BA7F-4D41-94B2-E590C6A6040C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="390">
   <si>
     <t>Canal</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Neutro</t>
   </si>
   <si>
-    <t>El Sol de Hidalgo</t>
-  </si>
-  <si>
     <t>El Universal Hidalgo</t>
   </si>
   <si>
@@ -250,24 +247,15 @@
     <t>Aumento Tarifa De Transporte</t>
   </si>
   <si>
-    <t>Blanca Soriano</t>
-  </si>
-  <si>
     <t>SSPH</t>
   </si>
   <si>
     <t>Impresiones locales</t>
   </si>
   <si>
-    <t>Sonia Nochebuena</t>
-  </si>
-  <si>
     <t>Lourdes Naranjo</t>
   </si>
   <si>
-    <t>Lorena Rosas</t>
-  </si>
-  <si>
     <t>Ricardo Calleja</t>
   </si>
   <si>
@@ -289,12 +277,6 @@
     <t>Turismo</t>
   </si>
   <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Alma Leticia Sánchez</t>
-  </si>
-  <si>
     <t>Saderh</t>
   </si>
   <si>
@@ -310,9 +292,6 @@
     <t>PGJEH</t>
   </si>
   <si>
-    <t>Maltrato animal</t>
-  </si>
-  <si>
     <t>Marco Cerón</t>
   </si>
   <si>
@@ -322,694 +301,922 @@
     <t>PGJEH, Presidencia</t>
   </si>
   <si>
-    <t>Turismo, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Vigilancia Epidemiológica</t>
-  </si>
-  <si>
-    <t>Salomón Hernández</t>
-  </si>
-  <si>
     <t>Planeación</t>
   </si>
   <si>
     <t>Magda Acuña</t>
   </si>
   <si>
-    <t>Nosocomio de mil 617 mdp, sin funcionar</t>
-  </si>
-  <si>
-    <t>El inmueble del nuevo Hospital General de Pachuca permanece sin operación, con basura y daños visibles, mientras la Secretaría de Salud estatal indicó que está en proceso de transferencia a la federación.</t>
-  </si>
-  <si>
-    <t>IMSS Bienestar</t>
-  </si>
-  <si>
-    <t>A cuatro años de su inauguración, el nuevo Hospital General de Pachuca no ha sido recibido por el IMSS-Bienestar y continúa cerrado.</t>
-  </si>
-  <si>
-    <t>SSH, IMSS-Bienestar</t>
-  </si>
-  <si>
-    <t>Omar Fayad Meneses</t>
-  </si>
-  <si>
-    <t>Feria recibió a sus primeros visitantes</t>
-  </si>
-  <si>
-    <t>Visitantes de municipios como Zapotlán, Tetepango y Pachuca acudieron a la apertura del recinto ferial a partir de las 13:00 horas para disfrutar de las atracciones y del concierto del grupo Bronco.</t>
-  </si>
-  <si>
-    <t>Con la apertura de pabellones y ambiente festivo, inició la Feria San Francisco Pachuca 2026 registrando la llegada de familias desde el primer día.</t>
-  </si>
-  <si>
-    <t>Casimiro Márquez Reyes</t>
-  </si>
-  <si>
-    <t>Taxis que incumplan tarifa serán sancionados</t>
-  </si>
-  <si>
-    <t>Tras la publicación del tarifario en el POEH con un costo mínimo de 45 pesos, autoridades estatales y municipales coordinarán operativos para vigilar que los conductores respeten las tarifas oficiales.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca advirtió sanciones y la posible retirada de concesiones a taxistas que cobren tarifas superiores a las autorizadas.</t>
-  </si>
-  <si>
-    <t>Semot, SSPH, Gobernador</t>
-  </si>
-  <si>
     <t>Julio Menchaca Salazar</t>
   </si>
   <si>
-    <t>Distribuyen recursos a empresarios</t>
-  </si>
-  <si>
-    <t>Beneficiarios de 74 municipios recibieron 25 mil pesos cada uno para fortalecer microempresas de giros comerciales, de servicios y producción artesanal en la entidad.</t>
-  </si>
-  <si>
-    <t>Apoyo a emprendedores</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca entregó 760 apoyos económicos del programa Emprendiendo paso a paso 2026 por un total de 20 millones de pesos.</t>
-  </si>
-  <si>
     <t>Gobernador</t>
   </si>
   <si>
-    <t>Gobernador, Sedeco, IHCE</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Carlos Henkel Escorza</t>
-  </si>
-  <si>
-    <t>Respaldan obra de Caasim en el Ramón G. Bonfil</t>
-  </si>
-  <si>
-    <t>A pesar de las molestias temporales por polvo y tráfico, locatarios señalaron que la obra resolverá el desabasto de agua que padecían desde hace 15 días en la colonia Santa Julia.</t>
-  </si>
-  <si>
-    <t>Infraestructura Hidráulica</t>
-  </si>
-  <si>
-    <t>Comerciantes del bulevar Ramón G. Bonfil manifestaron su respaldo a los trabajos de sustitución de tubería de agua potable realizados por Caasim.</t>
-  </si>
-  <si>
-    <t>Sipdus, Caasim</t>
-  </si>
-  <si>
-    <t>Eusebio Fidel Orta</t>
-  </si>
-  <si>
-    <t>Educación analiza riesgos de IA en emociones de niños y jóvenes</t>
-  </si>
-  <si>
-    <t>El impacto de la inteligencia artificial en las emociones de niños y docentes fue uno de los temas centrales del encuentro estatal 'Voces que transforman', organizado por la Secretaría de Educación Pública de Hidalgo para evaluar los algoritmos y la inclusión digital.</t>
-  </si>
-  <si>
-    <t>Educación socioemocional</t>
-  </si>
-  <si>
-    <t>La SEPH realizó el encuentro 'Voces que transforman' para evaluar el impacto de la inteligencia artificial y los algoritmos digitales en la salud emocional de los estudiantes.</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón, Xóchitl García</t>
-  </si>
-  <si>
-    <t>Buscan ampliación de capacidades para uso de la tecnología</t>
-  </si>
-  <si>
-    <t>La inteligencia artificial y la ciberseguridad comienzan a ocupar un espacio estratégico en Hidalgo con la búsqueda de alianzas entre instituciones educativas y actores especializados. La DESCTI sostuvo un encuentro con la Embajada de Estados Unidos.</t>
-  </si>
-  <si>
-    <t>Innovación tecnológica</t>
-  </si>
-  <si>
-    <t>La DESCTI sostuvo una reunión con la Embajada de Estados Unidos para fortalecer alianzas estratégicas en ciberseguridad e inteligencia artificial.</t>
-  </si>
-  <si>
-    <t>Planeación, DESCTI</t>
-  </si>
-  <si>
-    <t>Alejandro Franco Segura, Andrew Chapman</t>
-  </si>
-  <si>
-    <t>¡Pequeños guerreros! ¿Y si una consulta a tiempo pudiera cambiar una historia?</t>
-  </si>
-  <si>
-    <t>Dorado, informarnos sobre el cáncer infantil nos ayuda a reconocer la importancia de la atención oportuna. En septiembre, Mes Dorado, se fomenta la concienciación y consulta oportuna para salvar vidas de niños.</t>
-  </si>
-  <si>
-    <t>Cáncer Infantil</t>
-  </si>
-  <si>
-    <t>En el marco del Mes Dorado, autoridades de salud enfatizan la importancia de la detección oportuna y consulta médica a tiempo del cáncer infantil.</t>
-  </si>
-  <si>
-    <t>Empresas buscarán talento en Empleotón</t>
-  </si>
-  <si>
-    <t>Personas con discapacidad, adultos mayores y mujeres que buscan reincorporarse al mercado laboral tendrán el próximo 9 de octubre una jornada de empleo con participación de más de 15 empresas en la Feria Nacional de Empleo para Grupos Vulnerables.</t>
-  </si>
-  <si>
-    <t>Feria De Empleo</t>
-  </si>
-  <si>
-    <t>La STPSH anunció la celebración de la Feria Nacional de Empleo para Grupos Vulnerables con la participación de más de 15 empresas oferentes.</t>
-  </si>
-  <si>
-    <t>STPSH</t>
-  </si>
-  <si>
-    <t>Oscar Javier González Hernández</t>
-  </si>
-  <si>
-    <t>Destinan 19 mdp a emprendedores</t>
-  </si>
-  <si>
-    <t>Para quienes tuvieron que enfrentar las afectaciones de la vaguada monzónica, el apoyo llega como una posibilidad de recuperación. El gobernador Julio Menchaca Salazar defendió la decisión de entregar recursos directamente a los beneficiarios del programa Emprendiendo paso a paso.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca entregó 760 apoyos del programa Emprendiendo Paso a Paso, destinando especial atención a personas afectadas por contingencias climáticas.</t>
-  </si>
-  <si>
-    <t>Gobernador, Sedeco</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Carlos Henkel Escorza, Alejandra Hernández</t>
-  </si>
-  <si>
-    <t>Fijan tarifas de taxis en hasta $133 al salir de feria</t>
-  </si>
-  <si>
-    <t>Salir de la Feria San Francisco Pachuca en taxi tendrá un costo de entre 45 y 133 pesos, dependiendo del destino, de acuerdo con el tarifario público emitido por la Secretaría de Movilidad y Transporte. La tarifa mínima será de 45 pesos para destinos cercanos.</t>
-  </si>
-  <si>
-    <t>Tarifario Feria Pachuca</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad fijó el tabulador de tarifas para el servicio de taxis desde las instalaciones de la Feria de San Francisco, con costos de $45 a $133 según el destino.</t>
-  </si>
-  <si>
-    <t>El Hijo del Santo</t>
-  </si>
-  <si>
-    <t>Hay más de 42 mil víctimas de delitos</t>
-  </si>
-  <si>
-    <t>Hidalgo registró 42 mil 457 víctimas de delitos del fuero común entre enero y agosto de este año, de acuerdo con el Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública. Las lesiones lideran con 8,051 casos.</t>
-  </si>
-  <si>
-    <t>Un informe del SESNSP reporta 42,457 víctimas de delitos en Hidalgo entre enero y agosto de 2026, destacando lesiones y violencia familiar entre los más recurrentes.</t>
-  </si>
-  <si>
-    <t>FASP reporta avances en indicadores</t>
-  </si>
-  <si>
-    <t>El Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública dio a conocer los indicadores del primer trimestre del Fondo de Aportaciones para la Seguridad Pública (FASP), con un avance de 43.8 por ciento.</t>
-  </si>
-  <si>
-    <t>FASP</t>
-  </si>
-  <si>
-    <t>El Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública reportó un avance del 43.8% en los indicadores del Fondo de Aportaciones para la Seguridad Pública.</t>
-  </si>
-  <si>
-    <t>Segobh, SSPH</t>
-  </si>
-  <si>
-    <t>PIBEH suma 229 policías con bachillerato</t>
-  </si>
-  <si>
-    <t>Doscientos veintinueve elementos de la Policía Industrial Bancaria del Estado de Hidalgo concluyeron su educación media superior mediante el programa Mi Prepa Digital, permitiendo certificar a 130 trabajadores.</t>
-  </si>
-  <si>
     <t>Capacitación policial</t>
   </si>
   <si>
-    <t>La Policía Industrial Bancaria de Hidalgo certificó a 229 elementos en educación media superior mediante el programa Mi Prepa Digital.</t>
-  </si>
-  <si>
-    <t>SSPH, PIBEH</t>
-  </si>
-  <si>
-    <t>Escuelas de Huejutla se preparan para Xantolo 2026</t>
-  </si>
-  <si>
-    <t>Las escuelas de Huejutla comenzaron a prepararse para su participación en el Xantolo 2026, con actividades que incluirán exposiciones, demostraciones de cuadrillas y manifestaciones relacionadas con el Día de Muertos.</t>
-  </si>
-  <si>
     <t>Huejutla</t>
   </si>
   <si>
     <t>Xantolo</t>
   </si>
   <si>
-    <t>Planteles educativos de Huejutla iniciaron ensayos de cuadrillas de disfrazados y preparación de altares rumbo a las festividades tradicionales del Xantolo 2026.</t>
-  </si>
-  <si>
-    <t>SEPH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Hidalgo llevará su cultura a Tlaxkallan</t>
-  </si>
-  <si>
-    <t>El son huasteco, las danzas, los carnavales y la artesanía hidalguense llegarán este viernes al Palacio de Cultura de Tlaxcala, donde Hidalgo participa como estado invitado en el Festival Tlaxcallan 2026.</t>
-  </si>
-  <si>
     <t>Exposición cultural</t>
   </si>
   <si>
-    <t>Más de 300 agentes culturales, danzantes y artesanos de Hidalgo participarán como estado invitado en el Festival Tlaxcallan 2026.</t>
-  </si>
-  <si>
     <t>Cultura</t>
   </si>
   <si>
-    <t>Entregan 760 apoyos a emprendedores; 191 afectados por vaguada</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar realizó la entrega de 760 apoyos del programa Emprendiendo Paso a Paso 2026, de los cuales 191 fueron para afectados por la vaguada monzónica de octubre del año pasado. Carlos Henkel Escorza, titular de Sedeco, explicó que se destinaron 20 millones de pesos.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca entregó 760 apoyos de 25 mil pesos del programa Emprendiendo Paso a Paso 2026, beneficiando a emprendedores y afectados por lluvias en 23 municipios.</t>
-  </si>
-  <si>
     <t>Sedeco</t>
   </si>
   <si>
-    <t>Sedeco, IHCE, Gobernador</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Carlos Henkel Escorza, Carlos Martín Pérez Quijano</t>
-  </si>
-  <si>
-    <t>Estacionamiento: $150</t>
-  </si>
-  <si>
-    <t>La Operadora de Eventos de Hidalgo confirmó que la tarifa oficial del estacionamiento de la Feria de Pachuca es de 150 pesos, advirtiendo que no debe cobrarse en vía pública.</t>
-  </si>
-  <si>
-    <t>La OEEH estableció una cuota fija de 150 pesos para el estacionamiento ferial y coordinará operativos viales con la Semot y policía municipal.</t>
-  </si>
-  <si>
-    <t>Turismo, OEEH, Semot</t>
-  </si>
-  <si>
-    <t>Tras dos años, dan fecha para fallo por triple feminicidio en Tulantepec</t>
-  </si>
-  <si>
-    <t>Los Juzgados de Control fijaron para el 8 de octubre el fallo definitivo por el triple feminicidio de dos hermanas y una amiga ocurrido en Santiago Tulantepec en julio de 2024. Los tres imputados rechazaron declarar en la última audiencia.</t>
-  </si>
-  <si>
-    <t>Santiago Tulantepec</t>
-  </si>
-  <si>
-    <t>Feminicidio</t>
-  </si>
-  <si>
-    <t>Juez emitirá sentencia el 8 de octubre por el caso de triple feminicidio en Santiago Tulantepec; familiares de las víctimas exigen la pena máxima.</t>
-  </si>
-  <si>
-    <t>PGJEH, TSJEH</t>
-  </si>
-  <si>
     <t>Sandra Sauza</t>
   </si>
   <si>
-    <t>Arranca la Feria San Francisco; hoy la inauguran</t>
-  </si>
-  <si>
-    <t>Abrió sus puertas la Feria San Francisco, al sur de la ciudad, en donde se espera que la gente acuda a los conciertos masivos, así como a los pabellones gastronómico y cultural. El recinto estará vigilado con policía estatal y municipal para seguridad de los visitantes.</t>
-  </si>
-  <si>
-    <t>Abrió sus puertas la Feria San Francisco Pachuca 2026 con un dispositivo de seguridad conjunta entre la policía estatal y municipal para resguardar a los asistentes.</t>
-  </si>
-  <si>
-    <t>Turismo, SSPH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Taxistas de Pachuca ignoran nuevas tarifas</t>
-  </si>
-  <si>
-    <t>Conductores de taxi de la zona metropolitana de Pachuca ignoran el nuevo tarifario publicado en el Periódico Oficial del Estado de Hidalgo y continúan cobrando según su propio criterio, cobrando montos de entre 70 y 150 pesos.</t>
-  </si>
-  <si>
-    <t>Un sondeo de El Universal Hidalgo constató que choferes de taxi en Pachuca no respetan el banderazo oficial de 45 pesos publicado en el POEH y aplican tarifas arbitrarias.</t>
-  </si>
-  <si>
-    <t>Aplican el aumento en Tizayuca aunque aún no les corresponde</t>
-  </si>
-  <si>
-    <t>Usuarios del transporte público en Tizayuca denunciaron que taxistas locales ya cobran el banderazo de 45 pesos en trayectos cortos sin contar con la autorización de la Semot, ya que el municipio pertenece a la fase III del ajuste.</t>
-  </si>
-  <si>
-    <t>Tizayuca</t>
-  </si>
-  <si>
-    <t>Pasajeros de Tizayuca señalaron cobros indebidos de 45 y 50 pesos por parte de taxistas, a pesar de que el incremento autorizado por la Semot aún no aplica en la demarcación.</t>
-  </si>
-  <si>
-    <t>Javier Quezada</t>
-  </si>
-  <si>
-    <t>Semot, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Lyzbeth Robles Gutiérrez</t>
-  </si>
-  <si>
-    <t>Julio Menchaca advierte de sanciones por cobros excesivos</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar advirtió que habrá medidas enérgicas y sanciones contra los taxistas que no respeten el tarifario autorizado, recordando que la falta de seguro o cobros excesivos pueden derivar en la revocación de concesiones.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca instó a la norma tarifaria en el transporte e informó que la autoridad aplicará sanciones severas a los choferes que cobren de más.</t>
-  </si>
-  <si>
-    <t>Gobernador, Semot</t>
-  </si>
-  <si>
-    <t>Entregaron 760 apoyos para emprendedores</t>
-  </si>
-  <si>
-    <t>Un total de 760 personas recibieron apoyos económicos de 25 mil pesos mediante el programa Emprendiendo Paso a Paso 2026 del IHCE; 191 beneficiarios son emprendedores de 21 municipios afectados por la vaguada monzónica del año pasado.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca encabezó la entrega de 19 mdp en apoyos directos de 25 mil pesos a 760 emprendedores del estado a través del IHCE.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Carlos Pérez Quijano</t>
-  </si>
-  <si>
-    <t>Sedentarismo cognitivo, principal riesgo de la IA en las aulas, alertan</t>
-  </si>
-  <si>
-    <t>Durante el Encuentro Estatal para la Mejora Educativa organizado por la SEPH, la especialista Cimenna Chao Rebolledo advirtió que el uso acrítico de Inteligencia Artificial generativa provoca sustitución de la lectura y sedentarismo cognitivo en alumnos.</t>
-  </si>
-  <si>
-    <t>Regulación de dispositivos digitales</t>
-  </si>
-  <si>
-    <t>Especialista de la Ibero expuso en foro de la SEPH sobre los riesgos pedagógicos y socioemocionales de ceder el juicio crítico a herramientas de inteligencia artificial.</t>
-  </si>
-  <si>
-    <t>Cimenna Chao Rebolledo</t>
-  </si>
-  <si>
-    <t>Condenan a dos secuestradores a 50 años</t>
-  </si>
-  <si>
-    <t>La UECS de la PGJEH logró sentencia condenatoria de 50 años de prisión contra dos hombres identificados como J. C. M. F. y A. S. Z. por el secuestro agravado de un comerciante de autos en Progreso de Obregón.</t>
-  </si>
-  <si>
-    <t>Progreso</t>
-  </si>
-  <si>
-    <t>Tribunal dictó sentencia de 50 años de cárcel y pago de reparación de daño a dos plagiarios capturados tras rescatar a una víctima en Progreso de Obregón.</t>
-  </si>
-  <si>
     <t>PGJEH, UECS</t>
   </si>
   <si>
-    <t>En Atracciones Grupo García, 'Me late subirme a los juegos' en la feria 2026</t>
-  </si>
-  <si>
-    <t>En el marco de su 95 aniversario, Atracciones Grupo García instaló más de 20 juegos mecánicos, promociones en la tarjeta MásXMás y acceso gratuito para personas con discapacidad en la Feria San Francisco Pachuca.</t>
-  </si>
-  <si>
-    <t>Grupo García dio a conocer las atracciones familiares y promociones especiales disponibles durante la Feria de Pachuca 2026.</t>
-  </si>
-  <si>
-    <t>Turismo, Otros</t>
-  </si>
-  <si>
-    <t>Los canes con dueño causan ocho de cada 10 agresiones</t>
-  </si>
-  <si>
-    <t>El coordinador de Zoonosis de Tulancingo, Hugo Montiel Díaz, dio a conocer durante la sesión de Vigilancia Epidemiológica que el 80% de mordeduras registradas provienen de perros que tienen propietario pero permanecen sueltos.</t>
-  </si>
-  <si>
-    <t>Autoridades sanitarias de Tulancingo alertaron que la mayoría de los ataques caninos reportados semanalmente corresponden a mascotas con dueño descuidadas en la vía pública.</t>
-  </si>
-  <si>
-    <t>Mirely Santos</t>
-  </si>
-  <si>
-    <t>SSH, IMSS, ISSSTE</t>
-  </si>
-  <si>
-    <t>Hugo Montiel Díaz</t>
-  </si>
-  <si>
-    <t>Exigen esclarecer muerte de perros</t>
-  </si>
-  <si>
-    <t>El Comité Delegacional de Mascotas de Huejutla informó que existen dos carpetas de investigación ante la PGJEH por el envenenamiento y muerte de siete caninos en la colonia Parque de Poblamiento.</t>
-  </si>
-  <si>
-    <t>Vecinos y protectores de animales en Huejutla exigieron justicia y celeridad en las denuncias penales iniciadas tras el hallazgo de perros sin vida por presunto envenenamiento.</t>
-  </si>
-  <si>
-    <t>Francisco Bautista</t>
-  </si>
-  <si>
-    <t>PGJEH, Ayuntamiento, UAEH</t>
-  </si>
-  <si>
-    <t>Programa estatal beneficia a 760 emprendedores de Hidalgo</t>
-  </si>
-  <si>
-    <t>Un total de 760 emprendedores de 74 municipios de Hidalgo recibieron apoyos de 25 mil pesos mediante el programa Emprendiendo paso a paso 2026, con una bolsa de 20 millones de pesos. El beneficio incluyó a 191 emprendedores de 21 municipios afectados por la vaguada monzónica de 2025.</t>
-  </si>
-  <si>
-    <t>Un total de 760 emprendedores hidalguenses recibieron apoyos de 25 mil pesos a través del programa Emprendiendo paso a paso 2026.</t>
-  </si>
-  <si>
     <t>Berenice Gamboa</t>
   </si>
   <si>
     <t>Sedeco, Gobernador</t>
   </si>
   <si>
-    <t>Reforzarán cumplimiento de tarifas de taxis durante la Feria de San Francisco Pachuca</t>
-  </si>
-  <si>
-    <t>Tras la publicación de las nuevas tarifas para el servicio de taxi en la zona metropolitana y de las tarifas especiales con motivo de la Feria de San Francisco Pachuca 2026, el gobernador Julio Menchaca anunció una vigilancia coordinada entre Semot, SSPH y municipios para garantizar su cumplimiento.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca anunció vigilancia coordinada para vigilar el cobro justo de las tarifas de taxis durante la Feria de Pachuca.</t>
-  </si>
-  <si>
-    <t>Semot, Gobernador, SSPH</t>
-  </si>
-  <si>
-    <t>Dan 50 años de prisión a dos presuntos secuestradores de Progreso</t>
-  </si>
-  <si>
-    <t>Un tribunal de enjuiciamiento dictó fallo condenatorio de 50 años de prisión contra dos sujetos (J.C.M.F. y A.S.Z.) que simularon comprar un vehículo para secuestrar al propietario de un lote de autos en Progreso de Obregón y exigir 600 mil pesos a su familia.</t>
-  </si>
-  <si>
-    <t>Sentencian a 50 años de cárcel a dos secuestradores que privaron de la libertad a un comerciante de autos en Progreso.</t>
-  </si>
-  <si>
     <t>Claudia Ávila</t>
   </si>
   <si>
-    <t>Cuantifican daños en 40 mil pesos en el Parque Cultural</t>
-  </si>
-  <si>
-    <t>El vehículo que se impactó contra diversos elementos del Parque Cultural Hidalguense, tras las fiestas patrias, dejó daños estimados en 40 mil pesos, informó el gobernador Julio Menchaca Salazar. Señaló que las afectaciones serán reparadas mediante el seguro de la unidad.</t>
-  </si>
-  <si>
-    <t>Rehabilitación de espacios públicos</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca informó que los daños causados por un vehículo en el Parque Cultural Hidalguense ascienden a 40 mil pesos y serán cubiertos por el seguro del automóvil.</t>
-  </si>
-  <si>
     <t>Erick Perales</t>
   </si>
   <si>
-    <t>Gobernador, PGJEH</t>
-  </si>
-  <si>
-    <t>Impulsan recuperación de negocios en Hidalgo</t>
-  </si>
-  <si>
-    <t>Un total de 760 personas emprendedoras de 74 municipios recibieron 25 mil pesos cada una para impulsar o fortalecer su proyecto. Del total, 191 apoyos fueron destinados a emprendedores de 21 municipios afectados por la vaguada monzónica.</t>
-  </si>
-  <si>
-    <t>El gobierno del estado entregó 760 apoyos económicos de 25 mil pesos a emprendedores hidalguenses, de los cuales 191 se destinaron a afectados por la vaguada monzónica.</t>
-  </si>
-  <si>
-    <t>Carlos Henkel Escorza, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Bronco enciende el arranque de la Feria</t>
-  </si>
-  <si>
-    <t>La Feria de San Francisco Pachuca 2026 abrió sus puertas este jueves 24 de septiembre con ambiente tranquilo y presentación estelar del grupo Bronco en el Teatro del Pueblo. La inauguración oficial se llevará a cabo este viernes con la presencia del gobernador Julio Menchaca y operativo con 60 elementos de seguridad.</t>
-  </si>
-  <si>
-    <t>La Feria San Francisco Pachuca 2026 inició actividades con la presentación de Bronco y despliegue de seguridad municipal, previo a la inauguración oficial a cargo del gobernador Julio Menchaca.</t>
-  </si>
-  <si>
-    <t>Turismo, Gobernador, Ayuntamiento, SSPH</t>
-  </si>
-  <si>
-    <t>Alumnos del Mexe bloquean autopista para ejercer presión</t>
-  </si>
-  <si>
-    <t>Estudiantes de la Escuela Normal Rural "El Mexe" tomaron por segundo día consecutivo la caseta de San Alejo sobre la autopista México-Tuxpan, permitiendo el paso vehicular a cambio de aportaciones voluntarias, para exigir diálogo con la Presidencia respecto a la investigación del homicidio de un compañero y la restitución del plantel.</t>
-  </si>
-  <si>
-    <t>Protesta estudiantil</t>
-  </si>
-  <si>
-    <t>Normalistas de El Mexe tomaron la caseta de San Alejo en la autopista México-Tuxpan por segundo día consecutivo para solicitar una mesa de diálogo con el Gobierno Federal.</t>
-  </si>
-  <si>
-    <t>SEPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Claudia Sheinbaum</t>
-  </si>
-  <si>
     <t>Van a demoler primaria en Tulancingo; edificarán otra</t>
   </si>
   <si>
-    <t>La escuela primaria Aquiles Serdán de Tulancingo presenta fallas estructurales graves por lo que deberá ser demolida y reconstruida totalmente durante el ciclo escolar 2026-2027, según confirmó el secretario de Educación Pública de Hidalgo, Natividad Castrejón. Se analizan alternativas para reubicar temporalmente a los alumnos en planteles cercanos o modalidades de educación a distancia.</t>
-  </si>
-  <si>
-    <t>La SEPH demolerá y reconstruirá la primaria Aquiles Serdán en Tulancingo debido a daños estructurales, evaluando sedes temporales para atender al alumnado durante el ciclo 2026-2027.</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Retirarán concesiones a transportistas que incumplan la ley</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar advirtió que las concesiones de los transportistas que no cumplan con la ley y el esquema tarifario serán retiradas, priorizando la seguridad e integridad de los usuarios.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca advirtió que retirará concesiones a transportistas que violen la ley o abusen de las nuevas tarifas de transporte público.</t>
-  </si>
-  <si>
-    <t>Semot, Gobernador</t>
-  </si>
-  <si>
-    <t>Entregó Gobierno del Estado apoyos del programa Emprendiendo Paso a Paso 2026</t>
-  </si>
-  <si>
-    <t>Durante la entrega simbólica de 760 apoyos del programa Emprendiendo paso a paso 2026, el gobernador Julio Menchaca refrendó el compromiso de generar bienestar en los 84 municipios, entregando 25 mil pesos a cada emprendedor.</t>
-  </si>
-  <si>
-    <t>El Gobierno de Hidalgo entregó estímulos de 25 mil pesos a 760 personas emprendedoras, respaldando proyectos productivos y a familias afectadas por la vaguada monzónica.</t>
-  </si>
-  <si>
-    <t>Sedeco, IHCE</t>
-  </si>
-  <si>
-    <t>Otorgarán 500 becas de excelencia</t>
-  </si>
-  <si>
-    <t>El Sistema DIF Pachuca abrió la convocatoria 2026 de la Beca Municipal a la Excelencia Académica para otorgar 500 becas a estudiantes de primarias públicas de Pachuca con promedio mínimo de 9.5.</t>
-  </si>
-  <si>
-    <t>Becas</t>
-  </si>
-  <si>
-    <t>El DIF Pachuca lanzó la convocatoria para la Beca Municipal a la Excelencia Académica, beneficiando a 500 alumnos de primaria pública con alto desempeño escolar.</t>
-  </si>
-  <si>
-    <t>DIFH</t>
-  </si>
-  <si>
-    <t>DIFH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Por un secuestro, dos hombres pasarán 50 años en la prisión</t>
-  </si>
-  <si>
-    <t>La UECS de la PGJEH obtuvo sentencia de 50 años de prisión contra dos imputados por secuestro agravado en Progreso de Obregón tras fingir interés en comprar un vehículo en 2024.</t>
-  </si>
-  <si>
-    <t>Tribunal dictó condena de 50 años de cárcel a dos secuestradores procesados por la UECS tras privar de la libertad a un comerciante en Progreso de Obregón.</t>
-  </si>
-  <si>
     <t>Francisco Villeda</t>
   </si>
   <si>
-    <t>Se vigilará que taxis respeten las nuevas tarifas: Gobernador</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, aseguró que habrá revisiones coordinadas entre la Semot, la SSPH y los ayuntamientos para evitar cobros no permitidos en el servicio de taxi tras el ajuste tarifario en Pachuca y Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca advirtió sanciones y retiro de concesiones a taxistas que realicen cobros excesivos fuera del tarifario oficial de 45 pesos por los primeros 4 km.</t>
-  </si>
-  <si>
-    <t>Gobernador, Semot, SSPH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Lyzbeth Robles</t>
-  </si>
-  <si>
-    <t>Repararán los daños en el Parque Cultural Hidalguense, aseguran</t>
-  </si>
-  <si>
-    <t>El responsable de los daños al Parque Cultural Hidalguense Ben Gurión pagó 40 mil pesos y se repararán los desperfectos, confirmó el gobernador Julio Menchaca. Explicó que se trató de un menor de edad que confundió el freno con el acelerador.</t>
-  </si>
-  <si>
-    <t>Un menor de edad responsable de causar destrozos vehiculares en áreas verdes del Parque Ben Gurión cubrió 40 mil pesos para reparar las afectaciones.</t>
-  </si>
-  <si>
-    <t>Estacionamiento de la feria cuesta $150</t>
-  </si>
-  <si>
-    <t>El estacionamiento oficial de la Feria San Francisco Pachuca Hidalgo 2026 tendrá una cuota única de 150 pesos por vehículo por tiempo libre, tarifa que también aplicará en el espacio habilitado en la Plaza de Toros Vicente Segura.</t>
-  </si>
-  <si>
-    <t>Autoridades fijaron en 150 pesos el cobro por tiempo libre en el estacionamiento oficial del recinto ferial y la Plaza de Toros durante la Feria de Pachuca 2026.</t>
-  </si>
-  <si>
-    <t>Jorge Reyes Hernández</t>
-  </si>
-  <si>
-    <t>Naranja subsiste entre plagas y bajos precios</t>
-  </si>
-  <si>
-    <t>Productores citrícolas de la Huasteca hidalguense enfrentan afectaciones del 30% por la plaga del dragón amarillo (HLB) y sequías, aunado a variaciones de precios en el mercado regional.</t>
-  </si>
-  <si>
-    <t>Control de plagas</t>
-  </si>
-  <si>
-    <t>La producción de más de 5 mil hectáreas de naranja en la Huasteca hidalguense enfrenta severas pérdidas por el dragón amarillo y sequía.</t>
-  </si>
-  <si>
-    <t>Antíoco Aquino Leyva, Napoleón González</t>
-  </si>
-  <si>
-    <t>Supervisarán la calidad y peso del cacao y azúcar destinados al Xantolo</t>
-  </si>
-  <si>
-    <t>La Contraloría de Hidalgo inspeccionará el almacenamiento y distribución de 135 mil paquetes de cacao y azúcar en 22 municipios de la Huasteca para las festividades del Xantolo.</t>
-  </si>
-  <si>
-    <t>Entrega De Cacao</t>
-  </si>
-  <si>
-    <t>Inspectores estatales verificarán que los paquetes de cacao y azúcar para el Xantolo cumplan con el peso exacto de un kilo antes de entregarse a las familias.</t>
-  </si>
-  <si>
-    <t>Contraloría, Bienestar</t>
-  </si>
-  <si>
-    <t>Briseyda Torres</t>
+    <t>Saquean en el estado 2.5 toneladas de cactáceas con carácter de protección</t>
+  </si>
+  <si>
+    <t>Entre abril y septiembre fueron decomisadas 43 biznagas burras con un peso de 2 mil 555.5 kilos, además de 155 ejemplares o partes de garambullo; Cardonal y San Salvador, los blancos.</t>
+  </si>
+  <si>
+    <t>Cardonal</t>
+  </si>
+  <si>
+    <t>Conservación Biodiversidad</t>
+  </si>
+  <si>
+    <t>Autoridades ambientales decomisaron 2.5 toneladas de cactáceas protegidas en Cardonal y San Salvador, e integraron un dictamen pericial por delito ambiental.</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Puértolas</t>
+  </si>
+  <si>
+    <t>Semarnath</t>
+  </si>
+  <si>
+    <t>Semarnath, Profepa, FGR</t>
+  </si>
+  <si>
+    <t>Entre batucadas, arranca la Feria San Francisco</t>
+  </si>
+  <si>
+    <t>A ritmo de música, gastronomía y artesanías, la Feria de Pachuca abrió sus puertas para recibir a los visitantes con la presencia del gobernador Julio Menchaca Salazar.</t>
+  </si>
+  <si>
+    <t>Se inauguró formalmente la Feria San Francisco Pachuca 2026 con espectáculos musicales, muestra gastronómica y oferta artesanal.</t>
+  </si>
+  <si>
+    <t>Teodoro Santos</t>
+  </si>
+  <si>
+    <t>Turismo, Gobernador</t>
+  </si>
+  <si>
+    <t>Certifican intérpretes de náhuatl en Hidalgo</t>
+  </si>
+  <si>
+    <t>Personas hablantes de náhuatl en Hidalgo podrán participar en un proceso de certificación como intérpretes y traductores para fortalecer la procuración de justicia.</t>
+  </si>
+  <si>
+    <t>Certificación de intérpretes</t>
+  </si>
+  <si>
+    <t>La CEDSPI abrió la convocatoria de certificación para intérpretes de la lengua náhuatl para apoyar procedimientos de procuración de justicia.</t>
+  </si>
+  <si>
+    <t>Planeación, CEDSPI</t>
+  </si>
+  <si>
+    <t>Aseguran a tigrillo desnutrido y con maltrato en la Huasteca</t>
+  </si>
+  <si>
+    <t>Una cría de tigrillo desnutrida y con las garras cortadas fue rescatada en Calnali y trasladada a la Unidad de Rehabilitación de Fauna de Pachuca tras denuncia ante la Profepa.</t>
+  </si>
+  <si>
+    <t>Rescate Animal</t>
+  </si>
+  <si>
+    <t>Un ejemplar de tigrillo rescatado en Calnali recibe atención médica en Pachuca por desnutrición tras la intervención de la Profepa.</t>
+  </si>
+  <si>
+    <t>Semarnath, Profepa</t>
+  </si>
+  <si>
+    <t>Dan 11 años a hombre por robo de carga</t>
+  </si>
+  <si>
+    <t>Un juez dictó sentencia de 11 años y tres meses de prisión contra un hombre por el robo de un tractocamión acoplado a una caja seca en Tepeji del Río.</t>
+  </si>
+  <si>
+    <t>Tepeji del Río</t>
+  </si>
+  <si>
+    <t>Sentencia</t>
+  </si>
+  <si>
+    <t>Sentencian a más de 11 años de cárcel a un sujeto por el robo con violencia de transporte de carga en Tepeji del Río.</t>
+  </si>
+  <si>
+    <t>PGJEH, FGR</t>
+  </si>
+  <si>
+    <t>Inauguran la Feria San Francisco Pachuca Hidalgo 2026</t>
+  </si>
+  <si>
+    <t>Autoridades estatales inauguraron formalmente la Feria San Francisco Pachuca Hidalgo 2026 con diversas atracciones y pabellones.</t>
+  </si>
+  <si>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>Inicia el registro para el programa Pensión Mujeres Bienestar</t>
+  </si>
+  <si>
+    <t>Arrancó el registro para la Pensión Mujeres Bienestar en la entidad para beneficiar a adultas mayores de 60 a 64 años.</t>
+  </si>
+  <si>
+    <t>Pensión Mujeres Bienestar</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>Bienestar</t>
+  </si>
+  <si>
+    <t>Sancionarán a taxis que no respeten tarifario en la Feria</t>
+  </si>
+  <si>
+    <t>La Semot advirtió que aplicará sanciones strictly a choferes de taxi que cobren de más durante las festividades feriales.</t>
+  </si>
+  <si>
+    <t>Interiores</t>
+  </si>
+  <si>
+    <t>Atienden deslaves en la región Otomí-Tepehua tras lluvias</t>
+  </si>
+  <si>
+    <t>Cuadrillas de protección civil y obras públicas remueven escombros por deslaves causados por lluvias en la sierra Otomí-Tepehua.</t>
+  </si>
+  <si>
+    <t>Tenango de Doria</t>
+  </si>
+  <si>
+    <t>Deslaves por lluvias</t>
+  </si>
+  <si>
+    <t>Aseguran huachitúnel con conexión a toma clandestina en Atitalaquia</t>
+  </si>
+  <si>
+    <t>Fuerzas de seguridad localizaron e inhabilitaron un huachitúnel conectado a ductos de Pemex en Atitalaquia.</t>
+  </si>
+  <si>
+    <t>Atitalaquia</t>
+  </si>
+  <si>
+    <t>Huachitúnel</t>
+  </si>
+  <si>
+    <t>Hidalgo participará en el Encuentro Nacional de Arte y Cultura 2026</t>
+  </si>
+  <si>
+    <t>Delegación cultural de Hidalgo representará al estado en el Encuentro Nacional de Arte y Cultura 2026.</t>
+  </si>
+  <si>
+    <t>Reportan saldo blanco en primeras horas del operativo de la Feria</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo reportó saldo blanco en el inicio del despliegue operativo en el recinto ferial.</t>
+  </si>
+  <si>
+    <t>Operativo de Seguridad</t>
+  </si>
+  <si>
+    <t>Autoridades estatales e inauguraron oficialmente la Feria San Francisco Pachuca Hidalgo 2026 con un amplio programa de actividades culturales, comerciales y de entretenimiento para toda la familia.</t>
+  </si>
+  <si>
+    <t>Autoridades estatales e inauguraron oficialmente la Feria San Francisco Pachuca Hidalgo 2026 con actividades culturales y de entretenimiento.</t>
+  </si>
+  <si>
+    <t>Veida Martínez Miranda</t>
+  </si>
+  <si>
+    <t>Inicia el registro para el programa Pensión Mujeres Bienestar en Hidalgo</t>
+  </si>
+  <si>
+    <t>Arrancó en la entidad el registro de beneficiarias para el programa federal Pensión Mujeres Bienestar, destinado a otorgar apoyos económicos directos a adultas mayores de 60 a 64 años de edad.</t>
+  </si>
+  <si>
+    <t>Arrancó en Hidalgo el registro de beneficiarias para el programa federal Pensión Mujeres Bienestar destinado a adultas mayores.</t>
+  </si>
+  <si>
+    <t>Sancionarán a taxis que cobren tarifas excesivas durante la Feria de Pachuca</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte advirtió sobre sanciones administrativas y posible retiro de concesiones a taxistas que alteren o incrementen injustificadamente las tarifas autorizadas hacia el recinto ferial.</t>
+  </si>
+  <si>
+    <t>La Semot advirtió sanciones y retiro de concesiones a transportistas que cobren tarifas excesivas durante la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>Destruyen huachitúnel de 143 metros en Tlaxcoapan; suman 17 asegurados</t>
+  </si>
+  <si>
+    <t>Fuerzas de seguridad estatales y federales inhabilitaron un pasaje subterráneo de 143 metros de longitud que conectaba directamente con tomas clandestinas para la sustracción ilegal de combustible en Tlaxcoapan.</t>
+  </si>
+  <si>
+    <t>Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>Fuerzas de seguridad inhabilitaron un túnel de 143 metros utilizado para la extracción ilegal de hidrocarburo en Tlaxcoapan.</t>
+  </si>
+  <si>
+    <t>Segobh, SSPH, PGJEH</t>
+  </si>
+  <si>
+    <t>Aumentan a 23 los casos de gusano barrenador en el ganado hidalguense</t>
+  </si>
+  <si>
+    <t>La Secretaría de Agricultura y Desarrollo Rural confirmó la detección de 23 casos activos de infestación por gusano barrenador en ganado bovino de la entidad, manteniendo controles sanitarios estrictos.</t>
+  </si>
+  <si>
+    <t>Gusano barrenador</t>
+  </si>
+  <si>
+    <t>La Saderh confirmó el incremento a 23 casos detectados de gusano barrenador en ganado bovino en diversos municipios hidalguenses.</t>
+  </si>
+  <si>
+    <t>Reportan saldo blanco en el inicio de la Feria San Francisco Pachuca 2026</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo informó saldo blanco durante la jornada inaugural del recinto ferial tras implementar un riguroso dispositivo de vigilancia interinstitucional.</t>
+  </si>
+  <si>
+    <t>La SSPH reportó saldo blanco tras la implementación de operativos de vigilancia en el arranque de la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>Investigan desvío de recursos en administración municipal anterior de Tula</t>
+  </si>
+  <si>
+    <t>La Contraloría indaga un presunto desvío de recursos financieros cometido durante la gestión municipal anterior en Tula.</t>
+  </si>
+  <si>
+    <t>Tula</t>
+  </si>
+  <si>
+    <t>Desvío de recursos</t>
+  </si>
+  <si>
+    <t>Joselyn Sánchez</t>
+  </si>
+  <si>
+    <t>Plantean reforestación masiva en zonas afectadas por sequía en la Huasteca</t>
+  </si>
+  <si>
+    <t>Ambientalistas y dependencias promueven plan de reforestación masiva en la Huasteca hidalguense para mitigar la sequía.</t>
+  </si>
+  <si>
+    <t>Protección ambiental</t>
+  </si>
+  <si>
+    <t>Productores de café en Otomí-Tepehua prevén buena cosecha pese a lluvias</t>
+  </si>
+  <si>
+    <t>Cafeticultores de la región Otomí-Tepehua estiman buen rendimiento en la cosecha del ciclo actual.</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>Presentan exposición fotográfica sobre la historia de Pachuca</t>
+  </si>
+  <si>
+    <t>Inauguraron galería fotográfica que reúne imágenes históricas sobre la evolución urbana de la capital hidalguense.</t>
+  </si>
+  <si>
+    <t>Desmantelan toma clandestina de hidrocarburo en Cuautepec</t>
+  </si>
+  <si>
+    <t>Elementos estatales y federales inhabilitaron una toma clandestina en un ducto de Pemex ubicado en Cuautepec.</t>
+  </si>
+  <si>
+    <t>Cuautepec</t>
+  </si>
+  <si>
+    <t>Combate Al Huachicol</t>
+  </si>
+  <si>
+    <t>Investigan presunto desvío de recursos en la administración anterior de Tula</t>
+  </si>
+  <si>
+    <t>La Secretaría de la Contraloría abrió expedientes de investigación para esclarecer posibles inconsistencias y desvío de fondos públicos detectados en las arcas del gobierno municipal previo de Tula de Allende.</t>
+  </si>
+  <si>
+    <t>Contraloría del estado inició auditorías e investigaciones por presuntas irregularidades financieras en la gestión previa de Tula.</t>
+  </si>
+  <si>
+    <t>Contraloría, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Plantean programa de reforestación masiva en la Huasteca hidalguense</t>
+  </si>
+  <si>
+    <t>Autoridades de Medio Ambiente y Medio Rural impulsan la siembra masiva de árboles en municipios de la Huasteca para recuperar áreas afectadas por la deforestación y frenar los efectos de la sequía prolongada.</t>
+  </si>
+  <si>
+    <t>Semarnath planteó un esquema de reforestación masiva para contrarrestar la sequía y erosión en la Huasteca.</t>
+  </si>
+  <si>
+    <t>Productores de café de la región Otomí-Tepehua prevén buena producción</t>
+  </si>
+  <si>
+    <t>Agricultores de café en la zona serrana manifestaron expectativas favorables de cosecha para el ciclo actual, beneficiados por las lluvias recientes en los municipios de la región Otomí-Tepehua.</t>
+  </si>
+  <si>
+    <t>Cafetaleros de la región Otomí-Tepehua estiman incremento en el rendimiento de sus cultivos beneficiados por las lluvias.</t>
+  </si>
+  <si>
+    <t>Desmantelan toma clandestina de combustible en municipio de Cuautepec</t>
+  </si>
+  <si>
+    <t>Fuerzas de seguridad aseguraron una excavación e inhabilitaron una toma clandestina conectada a poliductos de Pemex en la zona rural de Cuautepec de Hinojosa, recuperando contenedores con gasolina.</t>
+  </si>
+  <si>
+    <t>Autoridades estatales inhabilitaron una toma clandestina conectada a ductos e incautaron contenedores con combustible en Cuautepec.</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH</t>
+  </si>
+  <si>
+    <t>Sentencian a cinco por secuestro; les dan hasta 87 años</t>
+  </si>
+  <si>
+    <t>Un Tribunal de Enjuiciamiento dictó condenas de hasta 87 años de prisión contra cinco personas por secuestro agravado cometido en Zapotlán de Juárez.</t>
+  </si>
+  <si>
+    <t>Zapotlán</t>
+  </si>
+  <si>
+    <t>Investigaciones de la UECS permitieron obtener sentencias condenatorias de hasta 87 años contra cinco secuestradores en Zapotlán.</t>
+  </si>
+  <si>
+    <t>Alejandro Reyes</t>
+  </si>
+  <si>
+    <t>Hallan en Pachuca 20 mil 900 litros de combustible</t>
+  </si>
+  <si>
+    <t>Agentes de la SSPH y la PGJEH aseguraron 20 mil 900 litros de hidrocarburo ilícito en un inmueble de Santiago Tlapacoya, Pachuca.</t>
+  </si>
+  <si>
+    <t>Cateo coordinado en Santiago Tlapacoya culminó con el decomiso de casi 21 mil litros de combustible y contenedores de alta presión.</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH, Sedena</t>
+  </si>
+  <si>
+    <t>Carpetas por privación ilegal de libertad supera 500 en 8 meses</t>
+  </si>
+  <si>
+    <t>Hidalgo registró 537 carpetas de investigación por el delito de privación ilegal de la libertad entre enero y agosto de 2026 según el SESNSP.</t>
+  </si>
+  <si>
+    <t>Cifras del Secretariado Ejecutivo revelan más de 500 denuncias por privación de la libertad en Hidalgo durante los primeros ocho meses del año.</t>
+  </si>
+  <si>
+    <t>Localizan cadáver en Tezontepec; van dos en una semana</t>
+  </si>
+  <si>
+    <t>El cuerpo de un hombre fue hallado en el canal de aguas negras de Viejo Requena en Tezontepec de Aldama, sumando dos hallazgos similares.</t>
+  </si>
+  <si>
+    <t>Tezontepec de Aldama</t>
+  </si>
+  <si>
+    <t>Localización de cuerpo</t>
+  </si>
+  <si>
+    <t>Cuerpos de seguridad y rescate rescataron el cadáver de un hombre no identificado en aguas negras de Tezontepec de Aldama.</t>
+  </si>
+  <si>
+    <t>PGJEH, Bomberos</t>
+  </si>
+  <si>
+    <t>Prevén reducir el tráfico con trenes y obras viales</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca destacó avances en la edificación del tren AIFA-Pachuca y proyectos de conectividad vial para agilizar la movilidad.</t>
+  </si>
+  <si>
+    <t>Proyectos Ferroviarios</t>
+  </si>
+  <si>
+    <t>Obras del tren México-Pachuca registran 45% de avance, proyectando conclusión de trabajos principales hacia 2027.</t>
+  </si>
+  <si>
+    <t>Gobernador, Presidencia</t>
+  </si>
+  <si>
+    <t>Mexicana e Hidalgo refuerzan conexión</t>
+  </si>
+  <si>
+    <t>La llegada de aeronaves Embraer 190 a Mexicana de Aviación potenciará la conectividad aérea de Hidalgo a través del AIFA.</t>
+  </si>
+  <si>
+    <t>Aeropuerto</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo estatal resalta que la expansión de Mexicana de Aviación impulsará la afluencia turística e industrial hidalguense.</t>
+  </si>
+  <si>
+    <t>Turismo, Presidencia</t>
+  </si>
+  <si>
+    <t>Elizabeth Quintanar Gómez</t>
+  </si>
+  <si>
+    <t>Taxistas se pronuncian por banderazo de 50 pesos</t>
+  </si>
+  <si>
+    <t>Operadores de taxi de Pachuca y Mineral de la Reforma se manifestaron en contra de las tarifas ajustadas y pidieron una tarifa mínima de 50 pesos.</t>
+  </si>
+  <si>
+    <t>Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Taxistas metropolitanos argumentan incrementos en insumos y gasolina para solicitar que la tarifa base suba de 45 a 50 pesos.</t>
+  </si>
+  <si>
+    <t>Amplían opciones de educación superior</t>
+  </si>
+  <si>
+    <t>El PIBEH y la Universidad CNCI firmaron un convenio para permitir que agentes policiacos y sus familias cursen licenciaturas y maestrías en línea.</t>
+  </si>
+  <si>
+    <t>Oferta educativa</t>
+  </si>
+  <si>
+    <t>Convenio educativo facilitará la profesionalización universitaria de elementos de la Policía Industrial Bancaria de Hidalgo.</t>
+  </si>
+  <si>
+    <t>SSPH, PIBEH, SEPH</t>
+  </si>
+  <si>
+    <t>Francisco Martínez Gómez, Benjamín Arcos Hughes</t>
+  </si>
+  <si>
+    <t>Investigan cómo hacer más resistente el cultivo de maíz</t>
+  </si>
+  <si>
+    <t>El ITESHU y el CIMMYT desarrollan ensayos en Huichapan para probar maíz nativo y de conservación resistente a sequías y heladas.</t>
+  </si>
+  <si>
+    <t>Huichapan</t>
+  </si>
+  <si>
+    <t>Investigación académica</t>
+  </si>
+  <si>
+    <t>Investigadores del Tecnológico de Huichapan colaboran con el CIMMYT para optimizar la productividad agrícola frente al cambio climático.</t>
+  </si>
+  <si>
+    <t>SEPH, ITESHU, Saderh</t>
+  </si>
+  <si>
+    <t>Raúl Olvera García</t>
+  </si>
+  <si>
+    <t>Gobernador entrega obras de pavimentación e infraestructura hidráulica en Pachuca</t>
+  </si>
+  <si>
+    <t>El gobernador entregó obras de pavimentación y red hidráulica para mejorar la movilidad y servicios en colonias de Pachuca.</t>
+  </si>
+  <si>
+    <t>Obras De Infraestructura</t>
+  </si>
+  <si>
+    <t>Vinculan a proceso a tres personas por narcomenudeo en Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>La PGJEH obtuvo la vinculación a proceso de tres presuntos distribuidores de droga detenidos en cateo.</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>Anuncian programa cultural de las festividades del Xantolo en la Huasteca</t>
+  </si>
+  <si>
+    <t>Presentaron la agenda de actividades culturales y de la tradición del Xantolo 2026 en municipios huastecos.</t>
+  </si>
+  <si>
+    <t>Recuperan dos vehículos con reporte de robo mediante arcos carreteros</t>
+  </si>
+  <si>
+    <t>Sistemas de videovigilancia y arcos carreteros permitieron la localización y recuperación de dos autos robados.</t>
+  </si>
+  <si>
+    <t>Videovigilancia</t>
+  </si>
+  <si>
+    <t>Entregan obras de pavimentación e infraestructura hidráulica en Pachuca</t>
+  </si>
+  <si>
+    <t>El Poder Ejecutivo estatal inauguró obras de pavimentación con concreto hidráulico y renovación de drenaje pluvial en colonias de Pachuca para mitigar los problemas recurrentes de encharcamientos e inundaciones.</t>
+  </si>
+  <si>
+    <t>El Gobernador entregó obras de pavimentación e infraestructura hidráulica para mitigar inundaciones en colonias de Pachuca.</t>
+  </si>
+  <si>
+    <t>Gobernador, Sipdus</t>
+  </si>
+  <si>
+    <t>Vinculan a proceso a tres probables responsables de narcomenudeo</t>
+  </si>
+  <si>
+    <t>La Procuraduría General de Justicia del Estado de Hidalgo logró la vinculación a proceso de tres personas detenidas en posesión de narcóticos durante operativos realizados en Mineral de la Reforma.</t>
+  </si>
+  <si>
+    <t>PGJEH obtuvo la vinculación a proceso de tres imputados por delitos contra la salud en Mineral de la Reforma.</t>
+  </si>
+  <si>
+    <t>PGJEH, SSPH</t>
+  </si>
+  <si>
+    <t>Presentan el programa cultural y festividades del Xantolo 2026 en la Huasteca</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura del gobierno estatal presentó la agenda artística, cuadrillas de disfrazados e itinerario gastronómico para la celebración de las fiestas tradicionales del Xantolo 2026 en Huejutla.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura dio a conocer el programa oficial y actividades artísticas para el Xantolo 2026 en la Huasteca.</t>
+  </si>
+  <si>
+    <t>Cultura, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Taxistas de Pachuca piden tarifa mínima de 50 pesos</t>
+  </si>
+  <si>
+    <t>Un grupo de taxistas independientes de Pachuca solicitaron que la tarifa mínima del servicio sea de 50 pesos, en lugar de los 45 pesos establecidos por la Semot, al considerar el tráfico y costos operativos.</t>
+  </si>
+  <si>
+    <t>Conductores independientes de taxi en Pachuca pidieron valorar distancias y tiempos de recorrido para fijar un cobro mínimo de 50 pesos frente al nuevo tarifario estatal.</t>
+  </si>
+  <si>
+    <t>Semarnath acopiará baterías en la Unidad Deportiva de Pachuca</t>
+  </si>
+  <si>
+    <t>La Semarnath realizará el próximo viernes 2 de octubre una jornada de acopio de pilas usadas y reforestación en la Unidad Deportiva Municipal de Pachuca.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Medio Ambiente estatal recolectará baterías en desuso y promoverá la plantación de árboles en la Unidad Deportiva de Pachuca el 2 de octubre.</t>
+  </si>
+  <si>
+    <t>Semarnath, Gobernador</t>
+  </si>
+  <si>
+    <t>Mónica Patricia Mixtega Trejo, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Acercan servicios de salud a 9 municipios</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo informó que las brigadas médicas han acercado más de 28 mil 200 acciones de salud gratuitas en nueve municipios de la entidad.</t>
+  </si>
+  <si>
+    <t>Acaxochitlán</t>
+  </si>
+  <si>
+    <t>Jornada de salud</t>
+  </si>
+  <si>
+    <t>La SSH desplegó jornadas médicas itinerantes en nueve municipios hidalguenses, ofreciendo consultas de especialidad, pruebas diagnósticas y apoyos funcionales.</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante</t>
+  </si>
+  <si>
+    <t>Aumentan lesiones y corrupción de menores contra mujeres en Hidalgo</t>
+  </si>
+  <si>
+    <t>En ocho meses, en Hidalgo incrementó la incidencia en los delitos de lesiones dolosas, culposas y corrupción de menores contra mujeres, reveló el reporte mensual del SESNSP.</t>
+  </si>
+  <si>
+    <t>Cifras del SESNSP ubican a Hidalgo entre los estados con mayor repunte en lesiones y corrupción de menores contra mujeres de enero a agosto de 2026.</t>
+  </si>
+  <si>
+    <t>Inició construcción de una planta de Hi-Ref, en Villa de Tezontepec</t>
+  </si>
+  <si>
+    <t>Sedeco encabezó la colocación de la primera piedra de la planta italiana Hi-Ref en Villa de Tezontepec, con una inversión de 200 millones de pesos y 320 empleos.</t>
+  </si>
+  <si>
+    <t>Villa de Tezontepec</t>
+  </si>
+  <si>
+    <t>Atracción De Inversiones</t>
+  </si>
+  <si>
+    <t>Inició la edificación de la primera planta de la empresa Hi-Ref en México, especializada en climatización de centros de datos en Villa de Tezontepec.</t>
+  </si>
+  <si>
+    <t>Carlos Henkel Escorza</t>
+  </si>
+  <si>
+    <t>En Atracciones Grupo García, "Me late subirme a los juegos"</t>
+  </si>
+  <si>
+    <t>Atracciones Grupo García llega a la Feria San Francisco Pachuca 2026 con más de 20 atracciones mecánicas, tarjetas con saldo extra y acceso gratuito para personas con discapacidad.</t>
+  </si>
+  <si>
+    <t>Grupo García ofrece promociones e instalaciones accesibles para personas con discapacidad durante la Feria San Francisco Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>Incautaron 20 mil litros de hidrocarburo</t>
+  </si>
+  <si>
+    <t>La SSPH desmanteló un predio utilizado para almacenar combustible ilegal en la localidad Santiago Tlapacoya de Pachuca, hallando 20 mil 900 litros de hidrocarburo.</t>
+  </si>
+  <si>
+    <t>Operativo coordinado entre SSPH, PGJEH y Sedena permitió el aseguramiento de más de 20 mil litros de huachicol y contenedores en Santiago Tlapacoya.</t>
+  </si>
+  <si>
+    <t>PIBEH firmó un convenio para dar educación a elementos</t>
+  </si>
+  <si>
+    <t>La Policía Industrial Bancaria del Estado de Hidalgo firmó un convenio de colaboración con la Universidad CNCI para ofrecer licenciaturas y maestrías en línea a sus elementos.</t>
+  </si>
+  <si>
+    <t>La PIBEH y la Universidad CNCI acordaron esquemas de profesionalización académica en línea para el personal policial y sus familias.</t>
+  </si>
+  <si>
+    <t>SSPH, Gobernador</t>
+  </si>
+  <si>
+    <t>Francisco Martínez Gómez, Benjamín Arcos Hughes, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Rectores de Hidalgo, entre la academia y la función pública</t>
+  </si>
+  <si>
+    <t>Análisis sobre el perfil profesional de los rectores de instituciones de educación superior en Hidalgo, quienes se dividen entre trayectorias académicas y cargos públicos.</t>
+  </si>
+  <si>
+    <t>Perfil académico</t>
+  </si>
+  <si>
+    <t>Reportaje que analiza las trayectorias de los rectores de las universidades e institutos politécnicos de la entidad.</t>
+  </si>
+  <si>
+    <t>Carmen Hernández</t>
+  </si>
+  <si>
+    <t>Brenda Flores, Pablo Elías Vargas González</t>
+  </si>
+  <si>
+    <t>Taxistas piden que banderazo sea de 50 pesos</t>
+  </si>
+  <si>
+    <t>Choferes de taxi en Pachuca manifiestan su inconformidad con la tarifa fijada por la Semot y solicitan que el banderazo inicial sea de 50 pesos debido al tráfico y costos.</t>
+  </si>
+  <si>
+    <t>Operadores de taxi solicitan un ajuste al banderazo tarifario a 50 pesos para compensar tiempos perdidos en el tráfico y gastos de operación.</t>
+  </si>
+  <si>
+    <t>En ocho meses, 461 asaltos en Pachuca</t>
+  </si>
+  <si>
+    <t>Entre enero y agosto de 2026, Pachuca acumuló 461 asaltos en negocios, transporte público y transeúntes, promediando casi dos casos diarios según el SESNSP.</t>
+  </si>
+  <si>
+    <t>Cifras del SESNSP revelan 461 asaltos en Pachuca en los primeros ocho meses del año, siendo los comercios los más afectados con 290 denuncias.</t>
+  </si>
+  <si>
+    <t>Luis Godínez</t>
+  </si>
+  <si>
+    <t>PGJEH, Presidencia, SESNSP</t>
+  </si>
+  <si>
+    <t>La violación a la intimidad sexual subió 32 por ciento</t>
+  </si>
+  <si>
+    <t>Las denuncias por violación a la intimidad sexual en Hidalgo incrementaron un 32% durante agosto, acumulando 33 carpetas de investigación ante la PGJEH.</t>
+  </si>
+  <si>
+    <t>Violencia digital</t>
+  </si>
+  <si>
+    <t>Las denuncias por delitos contra la intimidad sexual crecieron 32 por ciento en agosto en Hidalgo, encabezando Pachuca las querellas.</t>
+  </si>
+  <si>
+    <t>PGJEH, SESNSP</t>
+  </si>
+  <si>
+    <t>Dicen no a incremento en taxis de Atotonilco</t>
+  </si>
+  <si>
+    <t>Taxistas de Atotonilco el Grande señalaron la dificultad de socializar y aplicar el aumento del 20% a la tarifa del pasaje entre la población local.</t>
+  </si>
+  <si>
+    <t>Atotonilco el Grande</t>
+  </si>
+  <si>
+    <t>Operadores de taxi de Atotonilco expresan complicaciones para aplicar la nueva tarifa autorizada por el rechazo de los usuarios.</t>
+  </si>
+  <si>
+    <t>Martha Sáenz</t>
+  </si>
+  <si>
+    <t>Demanda colectivo revisar el caso de Martínez Cervantes</t>
+  </si>
+  <si>
+    <t>Integrantes del Movimiento No al Basurero exigieron durante el desfile de Atitalaquia revisar la situación jurídica del activista Óscar Martínez.</t>
+  </si>
+  <si>
+    <t>Derechos humanos</t>
+  </si>
+  <si>
+    <t>Manifestantes solicitaron respeto al debido proceso y presunción de inocencia para el activista Óscar Martínez Cervantes detenido recientemente.</t>
+  </si>
+  <si>
+    <t>Magda Olguín</t>
+  </si>
+  <si>
+    <t>Segobh, PGJEH</t>
+  </si>
+  <si>
+    <t>Óscar Martínez Cervantes, Rodrigo Ángeles</t>
+  </si>
+  <si>
+    <t>Taxistas piden nuevo aumento; usuarios exigen que se respeten las tarifas</t>
+  </si>
+  <si>
+    <t>A menos de una semana de que entrara en vigor la actualización de tarifas del transporte público individual en la zona metropolitana de Pachuca, chóferes de taxi solicitaron elevar el cobro mínimo de 45 a 50 pesos, argumentando congestionamiento vial y cuotas elevadas de concesionarios, mientras que usuarios exigen que se respeten los precios oficiales y la Semoth advirtió sanciones.</t>
+  </si>
+  <si>
+    <t>Reportaje</t>
+  </si>
+  <si>
+    <t>Taxistas de Pachuca solicitan elevar la tarifa mínima a 50 pesos mientras usuarios demandan respeto al tarifario oficial de 45 pesos y Semoth mantiene operativos de vigilancia.</t>
+  </si>
+  <si>
+    <t>Semot, STCH, Gobernador</t>
+  </si>
+  <si>
+    <t>SSH lleva Brigadas Médicas a Acaxochitlán</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo implementó jornadas de atención médica en Acaxochitlán, sumando nueve municipios beneficiados y más de 28 mil 200 acciones de medicina general, pediatría, ginecología y odontología.</t>
+  </si>
+  <si>
+    <t>Jornada médica</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo despliega brigadas médicas en Acaxochitlán para la detección oportuna de padecimientos.</t>
+  </si>
+  <si>
+    <t>SSH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Incautan 20 mil 900 litros de combustible</t>
+  </si>
+  <si>
+    <t>La SSPH en coordinación con la PGJEH y Sedena ejecutó una orden de cateo en Santiago Tlapacoya, Pachuca, donde aseguró 20,900 litros de hidrocarburo robado, 32 contenedores de mil litros y 200 metros de manguera.</t>
+  </si>
+  <si>
+    <t>Operativo conjunto de la SSPH y PGJEH en Santiago Tlapacoya logra el aseguramiento de casi 21 mil litros de huachicol.</t>
+  </si>
+  <si>
+    <t>Hallan cadáver en canal de aguas negras y en fiesta hieren a uno</t>
+  </si>
+  <si>
+    <t>Autoridades hallaron el cadáver de un hombre flotando en las aguas del canal San Gabriel en Tezontepec de Aldama, mientras que en Tlaxcoapan un sujeto resultó gravemente herido de bala durante una fiesta infantil.</t>
+  </si>
+  <si>
+    <t>Jornada violenta en la región de Tula deja el hallazgo de un cuerpo en canal de aguas negras y un baleado en Tlaxcoapan.</t>
+  </si>
+  <si>
+    <t>Hidalgo gana otras 2 medallas</t>
+  </si>
+  <si>
+    <t>Atletas hidalguenses conquistaron oro y plata en paranatación durante la Paralimpiada Nacional 2026 gracias a las actuaciones de Emiliano Pérez López y Melani Yamileth Ávila Trujillo.</t>
+  </si>
+  <si>
+    <t>Paranacionales Conade</t>
+  </si>
+  <si>
+    <t>Delegación de Hidalgo suma medallas de oro y plata en paranatación durante la Paralimpiada Nacional 2026.</t>
+  </si>
+  <si>
+    <t>SEPH, Inhide</t>
+  </si>
+  <si>
+    <t>Emiliano Pérez López, Melani Yamileth Ávila Trujillo, Oscar Pérez</t>
+  </si>
+  <si>
+    <t>Vuelca unidad operativa del Tuzobús</t>
+  </si>
+  <si>
+    <t>Una camioneta asignada a la Unidad de Vigilancia Operativa del Sistema de Transporte Metropolitano protagonizó un percance sobre el bulevar Felipe Ángeles, a la altura de la estación Vicente Segura. El vehículo terminó volcado sobre el camellón tras salir de su trayectoria por una supuesta falla mecánica. Los dos ocupantes resultaron ilesos.</t>
+  </si>
+  <si>
+    <t>Accidente de vehículo oficial</t>
+  </si>
+  <si>
+    <t>Una camioneta de la Unidad de Vigilancia Operativa del Tuzobús volcó en el bulevar Felipe Ángeles por una falla mecánica, sin dejar personas lesionadas.</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah</t>
+  </si>
+  <si>
+    <t>Supervisarán a diario juegos mecánicos en la Feria de Pachuca</t>
+  </si>
+  <si>
+    <t>Los 40 juegos mecánicos instalados en la Feria San Francisco Pachuca Hidalgo 2026 deberán contar con un dictamen favorable de Protección Civil y serán inspeccionados diariamente antes de recibir visitantes, como parte de las medidas preventivas para reducir riesgos durante los 25 días de actividades.</t>
+  </si>
+  <si>
+    <t>Protección Civil realizará inspecciones diarias a los 40 juegos mecánicos de la Feria de Pachuca para garantizar la seguridad de los asistentes.</t>
+  </si>
+  <si>
+    <t>Segobh, PC, Turismo</t>
+  </si>
+  <si>
+    <t>Román Bernal Díaz</t>
+  </si>
+  <si>
+    <t>Firma italiana arranca construcción de planta en Hidalgo</t>
+  </si>
+  <si>
+    <t>La empresa italiana Hi-Ref S.p.A. inició la construcción de su nueva planta en Villa de Tezontepec, proyecto que representa su primera instalación productiva en México y fuera de Italia, con una inversión de 200 millones de pesos y la generación de 320 empleos directos e indirectos para fabricar sistemas de climatización de precisión.</t>
+  </si>
+  <si>
+    <t>Hi-Ref S.p.A. colocó la primera piedra de su planta en Villa de Tezontepec con una inversión de 200 mdp para la producción de sistemas de refrigeración de centros de datos.</t>
+  </si>
+  <si>
+    <t>Carlos Henkel Escorza, Julio Menchaca Salazar, Alberto Salmistraro, Fabio Poletto, Alejandra Castellanos García, Lorenzo Vianello</t>
+  </si>
+  <si>
+    <t>Trabajadores del volante exigen modificar tarifas</t>
+  </si>
+  <si>
+    <t>Taxistas independientes de Pachuca y Mineral de la Reforma pidieron participar en la definición de las tarifas de transporte y propusieron establecer un cobro mínimo de 50 pesos. Cuestionaron que la Semoth tomara decisiones sin consultar al gremio.</t>
+  </si>
+  <si>
+    <t>Taxistas independientes de la zona metropolitana de Pachuca solicitaron ser consultados para fijar el tarifario de transporte y plantearon un cobro mínimo de 50 pesos.</t>
+  </si>
+  <si>
+    <t>Leonardo Cruz</t>
+  </si>
+  <si>
+    <t>Descarta el Secretario de Gobierno conflicto religioso en Huasteca</t>
+  </si>
+  <si>
+    <t>El secretario de Gobierno de Hidalgo, Guillermo Olivares Reyna, descartó que exista un conflicto religioso en la Huasteca tras el asesinato del sacerdote Román de la Cruz Hernández en Lolotla, e informó que la PGJEH mantiene estrecha comunicación con la Diócesis de Huejutla para esclarecer el crimen.</t>
+  </si>
+  <si>
+    <t>Lolotla</t>
+  </si>
+  <si>
+    <t>Exigen esclarecer homicidio</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna rechazó tensiones religiosas en la Huasteca tras el homicidio del párroco Román de la Cruz y afirmó avances en la investigación de la PGJEH.</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna, Román de la Cruz Hernández</t>
+  </si>
+  <si>
+    <t>La escuela primaria Aquiles Serdán de Tulancingo presenta fallas estructurales graves por lo que será demolida y reconstruida totalmente durante el ciclo escolar 2026-2027. El titular de la SEPH, Natividad Castrejón, indicó que se buscan opciones temporales para impartir clases presenciales o virtuales.</t>
+  </si>
+  <si>
+    <t>La SEPH demolerá y reconstruirá la primaria Aquiles Serdán en Tulancingo por daños en su infraestructura, evaluando la reubicación temporal del alumnado.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón</t>
   </si>
 </sst>
 </file>
@@ -1191,8 +1398,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ47" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ47" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ69" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ69" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1624,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ47"/>
+  <dimension ref="A1:AJ69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1774,28 +1981,28 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F2" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>42</v>
@@ -1807,28 +2014,28 @@
         <v>13262</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA2">
         <v>24</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>38</v>
@@ -1837,42 +2044,40 @@
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>101</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="AJ2" s="2"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F3" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>45</v>
@@ -1887,28 +2092,28 @@
         <v>13262</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA3">
         <v>20</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC3" s="2" t="s">
         <v>38</v>
@@ -1917,48 +2122,48 @@
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F4" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -1967,72 +2172,70 @@
         <v>13262</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="AJ4" s="2"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F5" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>45</v>
@@ -2047,28 +2250,28 @@
         <v>13262</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA5">
         <v>20</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC5" s="2" t="s">
         <v>38</v>
@@ -2077,45 +2280,43 @@
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>117</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="AJ5" s="2"/>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F6" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>48</v>
@@ -2127,28 +2328,28 @@
         <v>13262</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V6" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC6" s="2" t="s">
         <v>44</v>
@@ -2157,39 +2358,37 @@
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH6" s="2" t="s">
         <v>80</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>123</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AJ6" s="2"/>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F7" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -2204,31 +2403,31 @@
         <v>1</v>
       </c>
       <c r="S7">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="Y7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA7">
+        <v>24</v>
+      </c>
+      <c r="AB7" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA7">
-        <v>20</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>38</v>
@@ -2237,78 +2436,76 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ7" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AJ7" s="2"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F8" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R8">
         <v>1</v>
       </c>
       <c r="S8">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA8">
         <v>16</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC8" s="2" t="s">
         <v>38</v>
@@ -2317,78 +2514,76 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ8" s="2" t="s">
-        <v>134</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AJ8" s="2"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F9" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R9">
         <v>1</v>
       </c>
       <c r="S9">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC9" s="2" t="s">
         <v>38</v>
@@ -2397,156 +2592,154 @@
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AJ9" s="2"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F10" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G10">
         <v>4</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R10">
         <v>1</v>
       </c>
       <c r="S10">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z10" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="X10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="AA10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD10" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ10" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="AJ10" s="2"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F11" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R11">
         <v>1</v>
       </c>
       <c r="S11">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>147</v>
       </c>
       <c r="Y11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA11">
+        <v>24</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA11">
-        <v>20</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC11" s="2" t="s">
         <v>38</v>
@@ -2555,30 +2748,28 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AJ11" s="2" t="s">
-        <v>149</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="AJ11" s="2"/>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>150</v>
@@ -2587,10 +2778,10 @@
         <v>151</v>
       </c>
       <c r="F12" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>45</v>
@@ -2602,31 +2793,31 @@
         <v>1</v>
       </c>
       <c r="S12">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA12">
+        <v>16</v>
+      </c>
+      <c r="AB12" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA12">
-        <v>20</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC12" s="2" t="s">
         <v>38</v>
@@ -2641,306 +2832,304 @@
         <v>41</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ12" s="2" t="s">
-        <v>154</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="AJ12" s="2"/>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F13" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G13">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R13">
         <v>1</v>
       </c>
       <c r="S13">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA13">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD13" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="AJ13" s="2"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F14" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R14">
         <v>1</v>
       </c>
       <c r="S14">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="AJ14" s="2"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F15" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R15">
         <v>1</v>
       </c>
       <c r="S15">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD15" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="AJ15" s="2"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F16" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R16">
         <v>1</v>
       </c>
       <c r="S16">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>171</v>
+        <v>65</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC16" s="2" t="s">
         <v>38</v>
@@ -2949,154 +3138,154 @@
         <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="AJ16" s="2"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F17" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G17">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>60</v>
+        <v>166</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>178</v>
+        <v>62</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="AJ17" s="2"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F18" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
       <c r="S18">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="Y18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA18">
+        <v>16</v>
+      </c>
+      <c r="AB18" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA18">
-        <v>20</v>
-      </c>
-      <c r="AB18" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC18" s="2" t="s">
         <v>38</v>
@@ -3105,42 +3294,40 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ18" s="2" t="s">
-        <v>184</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="AJ18" s="2"/>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F19" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G19">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>45</v>
@@ -3152,109 +3339,109 @@
         <v>1</v>
       </c>
       <c r="S19">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="AG19" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="AJ19" s="2"/>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F20" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G20">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R20">
         <v>1</v>
       </c>
       <c r="S20">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA20">
         <v>20</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC20" s="2" t="s">
         <v>38</v>
@@ -3263,76 +3450,76 @@
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="AG20" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>194</v>
+        <v>71</v>
       </c>
       <c r="AJ20" s="2"/>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="F21" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R21">
         <v>1</v>
       </c>
       <c r="S21">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA21">
         <v>20</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC21" s="2" t="s">
         <v>38</v>
@@ -3341,76 +3528,76 @@
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AJ21" s="2"/>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="F22" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R22">
         <v>1</v>
       </c>
       <c r="S22">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V22" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>66</v>
+        <v>186</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="Y22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA22">
+        <v>16</v>
+      </c>
+      <c r="AB22" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA22">
-        <v>20</v>
-      </c>
-      <c r="AB22" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC22" s="2" t="s">
         <v>38</v>
@@ -3419,76 +3606,76 @@
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AG22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="AJ22" s="2"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F23" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>205</v>
+        <v>45</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R23">
         <v>1</v>
       </c>
       <c r="S23">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA23">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC23" s="2" t="s">
         <v>38</v>
@@ -3497,45 +3684,43 @@
         <v>44</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>207</v>
+        <v>41</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ23" s="2" t="s">
-        <v>209</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="AJ23" s="2"/>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="F24" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>49</v>
@@ -3544,31 +3729,31 @@
         <v>1</v>
       </c>
       <c r="S24">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA24">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC24" s="2" t="s">
         <v>38</v>
@@ -3577,78 +3762,76 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="AJ24" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="AJ24" s="2"/>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="F25" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R25">
         <v>1</v>
       </c>
       <c r="S25">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA25">
         <v>20</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC25" s="2" t="s">
         <v>38</v>
@@ -3657,45 +3840,43 @@
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="AG25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ25" s="2" t="s">
-        <v>217</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AJ25" s="2"/>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="F26" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>49</v>
@@ -3704,31 +3885,31 @@
         <v>1</v>
       </c>
       <c r="S26">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA26">
         <v>16</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC26" s="2" t="s">
         <v>38</v>
@@ -3737,78 +3918,76 @@
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ26" s="2" t="s">
-        <v>222</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AJ26" s="2"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="F27" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R27">
         <v>1</v>
       </c>
       <c r="S27">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>89</v>
+        <v>186</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA27">
         <v>16</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC27" s="2" t="s">
         <v>38</v>
@@ -3817,76 +3996,76 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="AG27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="AJ27" s="2"/>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="F28" s="1">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="G28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R28">
         <v>1</v>
       </c>
       <c r="S28">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V28" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA28">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC28" s="2" t="s">
         <v>38</v>
@@ -3895,46 +4074,46 @@
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="AJ28" s="2"/>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="F29" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>76</v>
+        <v>209</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -3943,28 +4122,28 @@
         <v>13262</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA29">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC29" s="2" t="s">
         <v>38</v>
@@ -3973,48 +4152,46 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="AG29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="AJ29" s="2" t="s">
-        <v>237</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="AJ29" s="2"/>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="F30" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -4023,19 +4200,19 @@
         <v>13262</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V30" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>87</v>
+        <v>192</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>43</v>
@@ -4044,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="AB30" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC30" s="2" t="s">
         <v>38</v>
@@ -4053,76 +4230,76 @@
         <v>44</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>241</v>
+        <v>41</v>
       </c>
       <c r="AG30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="AJ30" s="2"/>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="F31" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R31">
         <v>1</v>
       </c>
       <c r="S31">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AA31">
         <v>20</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC31" s="2" t="s">
         <v>38</v>
@@ -4131,78 +4308,76 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>182</v>
+        <v>80</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="AJ31" s="2" t="s">
-        <v>117</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="AJ31" s="2"/>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="F32" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>45</v>
+        <v>221</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
       <c r="S32">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V32" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>66</v>
+        <v>222</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="Y32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA32">
+        <v>16</v>
+      </c>
+      <c r="AB32" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA32">
-        <v>20</v>
-      </c>
-      <c r="AB32" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC32" s="2" t="s">
         <v>38</v>
@@ -4211,45 +4386,43 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>246</v>
+        <v>101</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="AJ32" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="AJ32" s="2"/>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="F33" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>48</v>
@@ -4258,22 +4431,22 @@
         <v>1</v>
       </c>
       <c r="S33">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>89</v>
+        <v>227</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>43</v>
@@ -4282,7 +4455,7 @@
         <v>20</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC33" s="2" t="s">
         <v>38</v>
@@ -4291,46 +4464,48 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="AG33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI33" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="AJ33" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AI33" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="AJ33" s="2"/>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="F34" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -4339,19 +4514,19 @@
         <v>13262</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>43</v>
@@ -4360,57 +4535,57 @@
         <v>12</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>110</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="F35" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -4419,72 +4594,70 @@
         <v>13262</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA35">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB35" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC35" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD35" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="AJ35" s="2" t="s">
-        <v>265</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="AJ35" s="2"/>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="F36" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>45</v>
@@ -4499,31 +4672,31 @@
         <v>13262</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="Y36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA36">
+        <v>12</v>
+      </c>
+      <c r="AB36" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="Z36" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA36">
-        <v>20</v>
-      </c>
-      <c r="AB36" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="AC36" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD36" s="2" t="s">
         <v>44</v>
@@ -4535,42 +4708,42 @@
         <v>41</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>110</v>
+        <v>245</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="F37" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4579,28 +4752,28 @@
         <v>13262</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V37" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA37">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB37" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC37" s="2" t="s">
         <v>38</v>
@@ -4609,45 +4782,45 @@
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH37" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="F38" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G38">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>49</v>
@@ -4656,31 +4829,31 @@
         <v>1</v>
       </c>
       <c r="S38">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="Y38" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA38">
+        <v>24</v>
+      </c>
+      <c r="AB38" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA38">
-        <v>16</v>
-      </c>
-      <c r="AB38" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>38</v>
@@ -4689,42 +4862,43 @@
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ38" s="2" t="s">
-        <v>279</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AJ38" s="2"/>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="F39" s="1">
-        <v>46290</v>
+        <v>46293</v>
+      </c>
+      <c r="G39">
+        <v>17</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>49</v>
@@ -4733,31 +4907,31 @@
         <v>1</v>
       </c>
       <c r="S39">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="AA39">
         <v>20</v>
       </c>
       <c r="AB39" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC39" s="2" t="s">
         <v>38</v>
@@ -4766,75 +4940,76 @@
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AG39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AJ39" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="AJ39" s="2"/>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="F40" s="1">
-        <v>46290</v>
+        <v>46293</v>
+      </c>
+      <c r="G40">
+        <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R40">
         <v>1</v>
       </c>
       <c r="S40">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA40">
         <v>20</v>
       </c>
       <c r="AB40" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC40" s="2" t="s">
         <v>38</v>
@@ -4843,150 +5018,154 @@
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AJ40" s="2" t="s">
-        <v>217</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="AJ40" s="2"/>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="F41" s="1">
-        <v>46290</v>
+        <v>46293</v>
+      </c>
+      <c r="G41">
+        <v>20</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R41">
         <v>1</v>
       </c>
       <c r="S41">
-        <v>13262</v>
+        <v>10000</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V41" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA41">
         <v>16</v>
       </c>
       <c r="AB41" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC41" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>292</v>
+        <v>66</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>293</v>
+        <v>66</v>
       </c>
       <c r="AJ41" s="2"/>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>255</v>
+        <v>94</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="F42" s="1">
-        <v>46290</v>
+        <v>46293</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R42">
         <v>1</v>
       </c>
       <c r="S42">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V42" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>89</v>
+        <v>255</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="Y42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA42">
+        <v>24</v>
+      </c>
+      <c r="AB42" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA42">
-        <v>20</v>
-      </c>
-      <c r="AB42" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC42" s="2" t="s">
         <v>38</v>
@@ -4995,43 +5174,43 @@
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>227</v>
+        <v>267</v>
       </c>
       <c r="AJ42" s="2"/>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>297</v>
+        <v>94</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="F43" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>49</v>
@@ -5040,31 +5219,31 @@
         <v>1</v>
       </c>
       <c r="S43">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V43" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="AA43">
         <v>20</v>
       </c>
       <c r="AB43" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC43" s="2" t="s">
         <v>38</v>
@@ -5073,45 +5252,43 @@
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="AG43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="AJ43" s="2" t="s">
-        <v>302</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="AJ43" s="2"/>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>297</v>
+        <v>94</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="F44" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>49</v>
@@ -5120,31 +5297,31 @@
         <v>1</v>
       </c>
       <c r="S44">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>258</v>
+        <v>90</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AA44">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB44" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC44" s="2" t="s">
         <v>38</v>
@@ -5153,78 +5330,76 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="AG44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="AJ44" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="AJ44" s="2"/>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>297</v>
+        <v>94</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="F45" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R45">
         <v>1</v>
       </c>
       <c r="S45">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V45" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z45" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA45">
         <v>20</v>
       </c>
       <c r="AB45" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC45" s="2" t="s">
         <v>38</v>
@@ -5233,78 +5408,76 @@
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ45" s="2" t="s">
-        <v>309</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="AJ45" s="2"/>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>297</v>
+        <v>94</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="F46" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
       <c r="S46">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>312</v>
+        <v>183</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="Y46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA46">
+        <v>12</v>
+      </c>
+      <c r="AB46" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA46">
-        <v>24</v>
-      </c>
-      <c r="AB46" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AC46" s="2" t="s">
         <v>38</v>
@@ -5313,45 +5486,45 @@
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>297</v>
+        <v>94</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>316</v>
+        <v>285</v>
       </c>
       <c r="F47" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="G47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>170</v>
+        <v>286</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>48</v>
@@ -5360,31 +5533,31 @@
         <v>1</v>
       </c>
       <c r="S47">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA47">
         <v>20</v>
       </c>
       <c r="AB47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC47" s="2" t="s">
         <v>38</v>
@@ -5393,19 +5566,1744 @@
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ47" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F48" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R48">
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <v>13262</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA48">
+        <v>16</v>
+      </c>
+      <c r="AB48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC48" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF48" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG48" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ48" s="2"/>
+    </row>
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F49" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R49">
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <v>13262</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="X49" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y49" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z49" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA49">
+        <v>20</v>
+      </c>
+      <c r="AB49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD49" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH49" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AG47" s="2" t="s">
+      <c r="AI49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ49" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F50" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G50">
+        <v>6</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
+      </c>
+      <c r="S50">
+        <v>13262</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA50">
+        <v>12</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ50" s="2"/>
+    </row>
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F51" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G51">
+        <v>7</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
+      </c>
+      <c r="S51">
+        <v>13262</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA51">
+        <v>20</v>
+      </c>
+      <c r="AB51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC51" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH51" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI51" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AJ51" s="2"/>
+    </row>
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F52" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G52">
+        <v>7</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>13262</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z52" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA52">
+        <v>16</v>
+      </c>
+      <c r="AB52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC52" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI52" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AJ52" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" t="s">
+        <v>101</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F53" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G53">
+        <v>4</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
+      </c>
+      <c r="S53">
+        <v>12500</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA53">
+        <v>20</v>
+      </c>
+      <c r="AB53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF53" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="AG53" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH47" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI47" s="2" t="s">
+      <c r="AH53" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI53" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ53" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F54" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G54">
+        <v>6</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+      <c r="S54">
+        <v>12500</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA54">
+        <v>20</v>
+      </c>
+      <c r="AB54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF54" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG54" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ54" s="2"/>
+    </row>
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" t="s">
+        <v>101</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="AJ47" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>320</v>
+      </c>
+      <c r="F55" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G55">
+        <v>9</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <v>12500</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA55">
+        <v>20</v>
+      </c>
+      <c r="AB55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC55" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD55" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF55" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AG55" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH55" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI55" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AJ55" s="2"/>
+    </row>
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F56" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G56">
+        <v>9</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>12500</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA56">
+        <v>16</v>
+      </c>
+      <c r="AB56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC56" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF56" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG56" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI56" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AJ56" s="2"/>
+    </row>
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" t="s">
+        <v>101</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G57">
+        <v>5</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <v>12500</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X57" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA57">
+        <v>12</v>
+      </c>
+      <c r="AB57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF57" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="AG57" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ57" s="2"/>
+    </row>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G58">
+        <v>9</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <v>12500</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="Y58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA58">
+        <v>16</v>
+      </c>
+      <c r="AB58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD58" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF58" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="AG58" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH58" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI58" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AJ58" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F59" s="1">
+        <v>46293</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59">
+        <v>13262</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X59" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z59" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA59">
+        <v>24</v>
+      </c>
+      <c r="AB59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF59" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH59" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI59" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="AJ59" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" t="s">
+        <v>98</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F60" s="1">
+        <v>46293</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R60">
+        <v>1</v>
+      </c>
+      <c r="S60">
+        <v>13262</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="X60" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y60" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA60">
+        <v>20</v>
+      </c>
+      <c r="AB60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH60" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI60" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="AJ60" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F61" s="1">
+        <v>46293</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+      <c r="S61">
+        <v>13262</v>
+      </c>
+      <c r="T61" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="X61" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="Y61" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA61">
+        <v>20</v>
+      </c>
+      <c r="AB61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC61" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH61" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI61" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AJ61" s="2"/>
+    </row>
+    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46293</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R62">
+        <v>1</v>
+      </c>
+      <c r="S62">
+        <v>13262</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="X62" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA62">
+        <v>20</v>
+      </c>
+      <c r="AB62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH62" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI62" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AJ62" s="2"/>
+    </row>
+    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F63" s="1">
+        <v>46293</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R63">
+        <v>1</v>
+      </c>
+      <c r="S63">
+        <v>13262</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="X63" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y63" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA63">
+        <v>20</v>
+      </c>
+      <c r="AB63" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH63" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI63" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="AJ63" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C64" t="s">
+        <v>98</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F64" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R64">
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <v>13262</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="X64" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z64" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA64">
+        <v>16</v>
+      </c>
+      <c r="AB64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH64" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI64" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="AJ64" s="2"/>
+    </row>
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C65" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F65" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <v>13262</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y65" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA65">
+        <v>20</v>
+      </c>
+      <c r="AB65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC65" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF65" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG65" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH65" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI65" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="AJ65" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66" t="s">
+        <v>98</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F66" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G66">
+        <v>3</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66">
+        <v>13262</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA66">
+        <v>20</v>
+      </c>
+      <c r="AB66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH66" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI66" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ66" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F67" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G67">
+        <v>4</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>13262</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W67" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X67" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="Y67" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA67">
+        <v>20</v>
+      </c>
+      <c r="AB67" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF67" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG67" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH67" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI67" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ67" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" t="s">
+        <v>98</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F68" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G68">
+        <v>5</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>13262</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Y68" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA68">
+        <v>12</v>
+      </c>
+      <c r="AB68" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH68" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI68" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AJ68" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" t="s">
+        <v>98</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F69" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G69">
+        <v>6</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69">
+        <v>13262</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W69" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X69" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="Y69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z69" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA69">
+        <v>16</v>
+      </c>
+      <c r="AB69" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC69" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD69" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF69" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG69" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ69" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios GitHub\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FBBE8D-BA7F-4D41-94B2-E590C6A6040C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380C0757-EB25-4AC3-866D-7429FC55B986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla1" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="504">
   <si>
     <t>Canal</t>
   </si>
@@ -238,9 +238,6 @@
     <t>Segobh</t>
   </si>
   <si>
-    <t>Adela Garmez</t>
-  </si>
-  <si>
     <t>Semot</t>
   </si>
   <si>
@@ -322,9 +319,6 @@
     <t>Xantolo</t>
   </si>
   <si>
-    <t>Exposición cultural</t>
-  </si>
-  <si>
     <t>Cultura</t>
   </si>
   <si>
@@ -445,18 +439,9 @@
     <t>Inauguran la Feria San Francisco Pachuca Hidalgo 2026</t>
   </si>
   <si>
-    <t>Autoridades estatales inauguraron formalmente la Feria San Francisco Pachuca Hidalgo 2026 con diversas atracciones y pabellones.</t>
-  </si>
-  <si>
     <t>Principal</t>
   </si>
   <si>
-    <t>Inicia el registro para el programa Pensión Mujeres Bienestar</t>
-  </si>
-  <si>
-    <t>Arrancó el registro para la Pensión Mujeres Bienestar en la entidad para beneficiar a adultas mayores de 60 a 64 años.</t>
-  </si>
-  <si>
     <t>Pensión Mujeres Bienestar</t>
   </si>
   <si>
@@ -466,51 +451,18 @@
     <t>Bienestar</t>
   </si>
   <si>
-    <t>Sancionarán a taxis que no respeten tarifario en la Feria</t>
-  </si>
-  <si>
-    <t>La Semot advirtió que aplicará sanciones strictly a choferes de taxi que cobren de más durante las festividades feriales.</t>
-  </si>
-  <si>
     <t>Interiores</t>
   </si>
   <si>
-    <t>Atienden deslaves en la región Otomí-Tepehua tras lluvias</t>
-  </si>
-  <si>
-    <t>Cuadrillas de protección civil y obras públicas remueven escombros por deslaves causados por lluvias en la sierra Otomí-Tepehua.</t>
-  </si>
-  <si>
     <t>Tenango de Doria</t>
   </si>
   <si>
-    <t>Deslaves por lluvias</t>
-  </si>
-  <si>
-    <t>Aseguran huachitúnel con conexión a toma clandestina en Atitalaquia</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad localizaron e inhabilitaron un huachitúnel conectado a ductos de Pemex en Atitalaquia.</t>
-  </si>
-  <si>
     <t>Atitalaquia</t>
   </si>
   <si>
     <t>Huachitúnel</t>
   </si>
   <si>
-    <t>Hidalgo participará en el Encuentro Nacional de Arte y Cultura 2026</t>
-  </si>
-  <si>
-    <t>Delegación cultural de Hidalgo representará al estado en el Encuentro Nacional de Arte y Cultura 2026.</t>
-  </si>
-  <si>
-    <t>Reportan saldo blanco en primeras horas del operativo de la Feria</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo reportó saldo blanco en el inicio del despliegue operativo en el recinto ferial.</t>
-  </si>
-  <si>
     <t>Operativo de Seguridad</t>
   </si>
   <si>
@@ -577,12 +529,6 @@
     <t>La SSPH reportó saldo blanco tras la implementación de operativos de vigilancia en el arranque de la Feria de Pachuca.</t>
   </si>
   <si>
-    <t>Investigan desvío de recursos en administración municipal anterior de Tula</t>
-  </si>
-  <si>
-    <t>La Contraloría indaga un presunto desvío de recursos financieros cometido durante la gestión municipal anterior en Tula.</t>
-  </si>
-  <si>
     <t>Tula</t>
   </si>
   <si>
@@ -592,36 +538,12 @@
     <t>Joselyn Sánchez</t>
   </si>
   <si>
-    <t>Plantean reforestación masiva en zonas afectadas por sequía en la Huasteca</t>
-  </si>
-  <si>
-    <t>Ambientalistas y dependencias promueven plan de reforestación masiva en la Huasteca hidalguense para mitigar la sequía.</t>
-  </si>
-  <si>
     <t>Protección ambiental</t>
   </si>
   <si>
-    <t>Productores de café en Otomí-Tepehua prevén buena cosecha pese a lluvias</t>
-  </si>
-  <si>
-    <t>Cafeticultores de la región Otomí-Tepehua estiman buen rendimiento en la cosecha del ciclo actual.</t>
-  </si>
-  <si>
     <t>Apoyo Al Agro</t>
   </si>
   <si>
-    <t>Presentan exposición fotográfica sobre la historia de Pachuca</t>
-  </si>
-  <si>
-    <t>Inauguraron galería fotográfica que reúne imágenes históricas sobre la evolución urbana de la capital hidalguense.</t>
-  </si>
-  <si>
-    <t>Desmantelan toma clandestina de hidrocarburo en Cuautepec</t>
-  </si>
-  <si>
-    <t>Elementos estatales y federales inhabilitaron una toma clandestina en un ducto de Pemex ubicado en Cuautepec.</t>
-  </si>
-  <si>
     <t>Cuautepec</t>
   </si>
   <si>
@@ -808,39 +730,12 @@
     <t>Raúl Olvera García</t>
   </si>
   <si>
-    <t>Gobernador entrega obras de pavimentación e infraestructura hidráulica en Pachuca</t>
-  </si>
-  <si>
-    <t>El gobernador entregó obras de pavimentación y red hidráulica para mejorar la movilidad y servicios en colonias de Pachuca.</t>
-  </si>
-  <si>
     <t>Obras De Infraestructura</t>
   </si>
   <si>
-    <t>Vinculan a proceso a tres personas por narcomenudeo en Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>La PGJEH obtuvo la vinculación a proceso de tres presuntos distribuidores de droga detenidos en cateo.</t>
-  </si>
-  <si>
     <t>Combate Al Narcomenudeo</t>
   </si>
   <si>
-    <t>Anuncian programa cultural de las festividades del Xantolo en la Huasteca</t>
-  </si>
-  <si>
-    <t>Presentaron la agenda de actividades culturales y de la tradición del Xantolo 2026 en municipios huastecos.</t>
-  </si>
-  <si>
-    <t>Recuperan dos vehículos con reporte de robo mediante arcos carreteros</t>
-  </si>
-  <si>
-    <t>Sistemas de videovigilancia y arcos carreteros permitieron la localización y recuperación de dos autos robados.</t>
-  </si>
-  <si>
-    <t>Videovigilancia</t>
-  </si>
-  <si>
     <t>Entregan obras de pavimentación e infraestructura hidráulica en Pachuca</t>
   </si>
   <si>
@@ -1217,6 +1112,453 @@
   </si>
   <si>
     <t>Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>Gobernador inaugura la Feria de San Francisco 2026</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar cortó el listón inaugural de la Feria de San Francisco Pachuca Hidalgo 2026 y develó la placa tras la remodelación del Pabellón Artesanal, que contó con una inversión superior a 6 mdp y reúne a artesanos de 53 municipios.</t>
+  </si>
+  <si>
+    <t>Feria de San Francisco</t>
+  </si>
+  <si>
+    <t>Julio Menchaca puso en marcha la Feria de San Francisco Pachuca 2026 e inauguró las obras de rehabilitación del Pabellón Artesanal.</t>
+  </si>
+  <si>
+    <t>Gobernador, Turismo, Bienestar, DIFH, OEEH</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Edda Vite Ramos, Rebeca Aladro Echeverría, Ricardo Gómez Moreno, Marco Antonio Aranzábal Juárez, Elizabeth Quintanar Gómez</t>
+  </si>
+  <si>
+    <t>Semot realiza operativos para supervisar a choferes</t>
+  </si>
+  <si>
+    <t>La Semot inició operativos de vigilancia y supervisión en Pachuca y Mineral de la Reforma para verificar el cumplimiento del tarifario de transporte individual publicado el 23 de septiembre y las condiciones de las unidades.</t>
+  </si>
+  <si>
+    <t>Tarifario de taxis</t>
+  </si>
+  <si>
+    <t>Inspectoría del transporte supervisa la aplicación del tarifario actualizado y el estado de las unidades de taxi en la zona metropolitana de Pachuca.</t>
+  </si>
+  <si>
+    <t>Semot, STCH</t>
+  </si>
+  <si>
+    <t>Crece uso de notarías entre personas de 30 a 40 años</t>
+  </si>
+  <si>
+    <t>Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios de Hidalgo, informó que hasta el 40% de los trámites testamentarios en septiembre son realizados por personas de entre 30 y 40 años, rompiendo tabúes en la planeación patrimonial.</t>
+  </si>
+  <si>
+    <t>Trámites notariales</t>
+  </si>
+  <si>
+    <t>Jóvenes de 30 a 40 años representan ya el 40% de las personas que tramitan su testamento durante el mes de septiembre en Hidalgo.</t>
+  </si>
+  <si>
+    <t>Colegio de Notarios de Hidalgo</t>
+  </si>
+  <si>
+    <t>Pedro Luis Noble Monterrubio</t>
+  </si>
+  <si>
+    <t>Sedeco busca incrementar hasta 15% becas de estancias productivas</t>
+  </si>
+  <si>
+    <t>Horacio Ríos Cano, subsecretario de Fomento Económico, señaló que la Sedeco pretende elevar entre 10 y 15% las becas de los programas Transformando con la Juventud y Tu Experiencia Transforma para el paquete fiscal 2027.</t>
+  </si>
+  <si>
+    <t>Programa de empleo</t>
+  </si>
+  <si>
+    <t>La Sedeco solicitará un aumento presupuestal para ampliar la cobertura de sus programas de becas productivas para jóvenes y adultos mayores.</t>
+  </si>
+  <si>
+    <t>Sedeco, Hacienda, Congreso</t>
+  </si>
+  <si>
+    <t>Horacio Ríos Cano</t>
+  </si>
+  <si>
+    <t>Gobierno federal destina más de 40 mdp para CBTis de Tizayuca</t>
+  </si>
+  <si>
+    <t>Se publicó en el DOF el convenio para la ampliación y equipamiento del CBTis número 293 en Tizayuca por un monto de 40.9 millones de pesos provenientes del programa FAM Potenciado.</t>
+  </si>
+  <si>
+    <t>Tizayuca</t>
+  </si>
+  <si>
+    <t>Infraestructura educativa</t>
+  </si>
+  <si>
+    <t>El DOF publicó el convenio por 40.9 mdp para las obras de ampliación y equipamiento integral del plantel CBTis 293 en Tizayuca.</t>
+  </si>
+  <si>
+    <t>SEPH, SEP, Inhife, SICT, Inifed</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Invitan desde Puebla al próximo Festival Internacional del Paste</t>
+  </si>
+  <si>
+    <t>El Consejo Regulador del Patrimonio Cultural de Real del Monte presentó en Puebla la edición 18º del Festival Internacional del Paste, que se celebrará del 9 al 11 de octubre con la elaboración del paste más grande del país (250 kg).</t>
+  </si>
+  <si>
+    <t>Mineral del Monte</t>
+  </si>
+  <si>
+    <t>Festival Gastronómico</t>
+  </si>
+  <si>
+    <t>Real del Monte promocionó la edición 18º del Festival Internacional del Paste en Puebla, destacando las actividades culturales del 9 al 11 de octubre.</t>
+  </si>
+  <si>
+    <t>Turismo, Corepac</t>
+  </si>
+  <si>
+    <t>Rosa María Durán Mejía</t>
+  </si>
+  <si>
+    <t>De la mano de su abuelo nació el amor de Raúl Guerrero por el pulque</t>
+  </si>
+  <si>
+    <t>Perfil sobre Raúl Guerrero Bustamante, fundador de "El Beso de Mayahuel" en Huasca de Ocampo y promotor de la cultura del maguey y el pulque a través del Congreso Nacional del Maguey y el Pulque.</t>
+  </si>
+  <si>
+    <t>Huasca de Ocampo</t>
+  </si>
+  <si>
+    <t>Perfil</t>
+  </si>
+  <si>
+    <t>Semblanza sobre la trayectoria de Raúl Guerrero en la divulgación de la cultura pulquera y la creación del concepto de neopulquería en Huasca.</t>
+  </si>
+  <si>
+    <t>Raúl Guerrero Bustamante</t>
+  </si>
+  <si>
+    <t>Guitarra, voz y nuevas canciones: Erich y Daniel Quien llegan a Pachuca</t>
+  </si>
+  <si>
+    <t>Los cantautores Erich y Daniel Quien se presentan este domingo 27 de septiembre en "Entre Caníbales" en Pachuca dentro de su gira acústica en la que interpretan sus nuevos temas.</t>
+  </si>
+  <si>
+    <t>Evento cultural</t>
+  </si>
+  <si>
+    <t>Erich y Daniel Quien traen su gira acústica e íntima a Pachuca con presentaciones este domingo en el foro Entre Caníbales.</t>
+  </si>
+  <si>
+    <t>América Castillo</t>
+  </si>
+  <si>
+    <t>Erich, Daniel Quien</t>
+  </si>
+  <si>
+    <t>Recomendaciones Literarias</t>
+  </si>
+  <si>
+    <t>En el marco del Día Internacional de la Traducción se recomiendan tres de las obras literarias más traducidas en el mundo: El Principito de Antoine de Saint-Exupéry, Testamento de Taras Shevchenko y Las aventuras de Pinocho de Carlo Collodi.</t>
+  </si>
+  <si>
+    <t>Literatura</t>
+  </si>
+  <si>
+    <t>Recomendación de las tres obras literarias más traducidas a nivel mundial en el marco del Día Internacional de la Traducción.</t>
+  </si>
+  <si>
+    <t>Antoine de Saint-Exupéry, Taras Shevchenko, Carlo Collodi</t>
+  </si>
+  <si>
+    <t>Paran obras de ampliación de la vía México-Tuxpan</t>
+  </si>
+  <si>
+    <t>Ejidatarios de la localidad de Mimila detuvieron las obras de ampliación a cuatro carriles de la carretera México-Tuxpan a la altura del km 89.9 (tramo Pitula-San Alejo) exigiendo indemnización justa por la afectación a sus tierras agrarias.</t>
+  </si>
+  <si>
+    <t>Manifestaciones</t>
+  </si>
+  <si>
+    <t>Ejidatarios de Mimila frenaron la maquinaria de los trabajos de ampliación de la México-Tuxpan en demanda del pago de indemnizaciones por sus predios.</t>
+  </si>
+  <si>
+    <t>SICT</t>
+  </si>
+  <si>
+    <t>SICT, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Lorena García Cázares</t>
+  </si>
+  <si>
+    <t>Impresos locales</t>
+  </si>
+  <si>
+    <t>Reconocen expansión aérea de Mexicana en el AIFA</t>
+  </si>
+  <si>
+    <t>La secretaria de Turismo de Hidalgo, Elizabeth Quintanar Gómez, asistió al Aeropuerto Internacional Felipe Ángeles (AIFA) para la incorporación de la décima aeronave Embraer 190-E2 a la flota de Mexicana. La funcionaria señaló que este hecho fortalece la conectividad aérea y abre oportunidades para el turismo regional.</t>
+  </si>
+  <si>
+    <t>Zumpango</t>
+  </si>
+  <si>
+    <t>Conectividad Aérea</t>
+  </si>
+  <si>
+    <t>La secretaria de Turismo de Hidalgo asistió a la incorporación de la décima aeronave Embraer de Mexicana en el AIFA, destacando el fortalecimiento de la conectividad y el turismo.</t>
+  </si>
+  <si>
+    <t>Turismo, Mexicana de Aviación, AIFA</t>
+  </si>
+  <si>
+    <t>Elizabeth Quintanar Gómez, Julio Menchaca Salazar, Leobardo Ávila Bojórquez</t>
+  </si>
+  <si>
+    <t>Incrementa en hasta 20% valor de predios en la ZMP</t>
+  </si>
+  <si>
+    <t>En el último año, el incremento en el valor por metro cuadrado de los predios en la zona metropolitana de Pachuca alcanzó porcentajes de hasta 20%, siendo las colonias con mayor alza San Cayetano y Mineral del Monte sobre el Corredor de la Montaña, de acuerdo con la séptima edición de la Guía Inmobiliaria de Coparmex.</t>
+  </si>
+  <si>
+    <t>Sector Inmobiliario</t>
+  </si>
+  <si>
+    <t>La séptima Guía Inmobiliaria de Coparmex reportó un incremento de hasta 20% en el valor por metro cuadrado de predios en la zona metropolitana de Pachuca.</t>
+  </si>
+  <si>
+    <t>Coparmex, Colegio de Valuadores Multidisciplinarios de Hidalgo</t>
+  </si>
+  <si>
+    <t>Rodrigo Canseco Puente</t>
+  </si>
+  <si>
+    <t>Hidalgo baja tasa de fecundidad entre niñas y adolescentes</t>
+  </si>
+  <si>
+    <t>El Consejo Estatal de Población informó que Hidalgo ocupa el segundo lugar nacional en la reducción de tasas de fecundidad en menores de 10 a 14 años (-24%), y una disminución del 36% en el grupo de 15 a 19 años entre 2018 y 2023, como resultado de la Estrategia Hidalguense para la Prevención del Embarazo en Adolescentes (EHPEA).</t>
+  </si>
+  <si>
+    <t>Prevención de embarazo adolescente</t>
+  </si>
+  <si>
+    <t>Hidalgo se colocó en segundo lugar nacional en reducción de fecundidad adolescente en el rango de 10 a 14 años, registrando también una baja del 36% en jóvenes de 15 a 19 años.</t>
+  </si>
+  <si>
+    <t>Coespo</t>
+  </si>
+  <si>
+    <t>Coespo, GEPEA, SSH, SEPH</t>
+  </si>
+  <si>
+    <t>Solo una empresa interesada en adecuar antiguo Palacio para la Escuela de Música</t>
+  </si>
+  <si>
+    <t>La empresa RSK Edificación Especializada S.A. de C.V. presentó la única propuesta económica por 20 millones 590 mil 282 pesos en la licitación EO-SIPDUS-N129-2026 convocada por Sipdus para la adecuación del antiguo Palacio de Gobierno como nueva sede de la Escuela de Música del Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Licitaciones</t>
+  </si>
+  <si>
+    <t>Con una oferta superior a los 20 mdp, RSK Edificación Especializada fue la única empresa participante en el concurso para remodelar el antiguo Palacio de Gobierno en Pachuca.</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Sipdus, SEPH, EMEH</t>
+  </si>
+  <si>
+    <t>Daniel Fragoso Torres</t>
+  </si>
+  <si>
+    <t>Disminuyen los casos activos de gusano barrenador del ganado</t>
+  </si>
+  <si>
+    <t>Los casos activos de gusano barrenador del ganado en Hidalgo disminuyeron de 97 a 30 al corte del 26 de septiembre. La entidad acumula 1,376 casos en 2026, concentrándose la mayor incidencia actual en Acatlán, Atotonilco el Grande y San Salvador.</t>
+  </si>
+  <si>
+    <t>Sanidad Animal</t>
+  </si>
+  <si>
+    <t>Reporte de Sader y Senasica revela una caída de 97 a 30 casos activos de gusano barrenador en ganado hidalguense.</t>
+  </si>
+  <si>
+    <t>Sader, Senasica</t>
+  </si>
+  <si>
+    <t>El Enmascarado de Plata: 109 años del nacimiento de una leyenda</t>
+  </si>
+  <si>
+    <t>Reseña conmemorativa por los 109 años del nacimiento de Rodolfo Guzmán Huerta, El Santo, nacido el 23 de septiembre de 1917 en Tulancingo, recordando su trayectoria icónica en la lucha libre y el cine mexicano.</t>
+  </si>
+  <si>
+    <t>Efeméride / Lucha Libre</t>
+  </si>
+  <si>
+    <t>Homenaje a la leyenda de la lucha libre Rodolfo Guzmán Huerta "El Santo" al cumplirse 109 años de su natalicio en Tulancingo.</t>
+  </si>
+  <si>
+    <t>Benjamín H. V.</t>
+  </si>
+  <si>
+    <t>Rodolfo Guzmán Huerta, Jesús Lomelí, Black Shadow, Espanto I, Murciélago Velázquez, Bobby Bonales, Perro Aguayo, José G. Cruz</t>
+  </si>
+  <si>
+    <t>Tulancingo abre diálogo comunitario con Congreso Conexiones Culturales</t>
+  </si>
+  <si>
+    <t>El Foro TAC en Tulancingo será sede el 3 de octubre de la jornada del 2º Congreso Internacional "Conexiones Culturales", que del 1 al 11 de octubre reunirá a más de 100 agentes culturales de Hidalgo, México y 10 países para abordar la gestión, activación comunitaria y formación de públicos.</t>
+  </si>
+  <si>
+    <t>Evento Cultural</t>
+  </si>
+  <si>
+    <t>Tulancingo albergará una de las sedes principales del 2º Congreso Internacional Conexiones Culturales para reflexionar sobre la gestión comunitaria y el desarrollo de recintos culturales.</t>
+  </si>
+  <si>
+    <t>Alejandro Baillet</t>
+  </si>
+  <si>
+    <t>Cultura, Emprendedores Culturales e Industrias Creativas A.C., Cultivarte Patrimonio Vivo A.C.</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Osorio Hernández, Tania Galindo, Gisela Gutiérrez, Beatrice Valdés, Miguel Ángel Servín Trujillo, Daniel Rivera, Isaac Ortega</t>
+  </si>
+  <si>
+    <t>Crecen fallecimientos por covid-19; suman 16 casos</t>
+  </si>
+  <si>
+    <t>Los reportes de la Secretaría de Salud federal muestran que entre la semana 36 y la semana 37 las defunciones acumuladas por covid-19 en Hidalgo pasaron de 15 a 16, mientras que los casos confirmados subieron de 179 a 183 con un porcentaje de positividad del 4.5%.</t>
+  </si>
+  <si>
+    <t>Covid 19</t>
+  </si>
+  <si>
+    <t>Hidalgo acumuló 16 decesos y 183 casos confirmados de covid-19 en el último reporte epidemiológico federal.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud federal, SSH</t>
+  </si>
+  <si>
+    <t>Empresa italiana invierte $200 millones para abrir planta en Hidalgo</t>
+  </si>
+  <si>
+    <t>La empresa italiana Hi-Ref S.p.A. inició la construcción de su primera planta fuera de Italia en Villa de Tezontepec con una inversión de 200 millones de pesos y la generación de 320 nuevos empleos, especializada en climatización de precisión para centros de datos e inteligencia artificial.</t>
+  </si>
+  <si>
+    <t>Inversión privada</t>
+  </si>
+  <si>
+    <t>Hi-Ref S.p.A. colocó la primera piedra de su planta de sistemas de climatización en Villa de Tezontepec, invirtiendo 200 mdp y creando 320 empleos.</t>
+  </si>
+  <si>
+    <t>Sedeco, Embajada de Italia, Cámara de Comercio Italiana</t>
+  </si>
+  <si>
+    <t>Carlos Henkel Escorza, Alberto Salmistraro, Fabio Poletto, Alejandra Castellanos García, Valentina Valente, Lorenzo Vianello</t>
+  </si>
+  <si>
+    <t>Taxistas de Pachuca piden elevar a 50 pesos la tarifa mínima</t>
+  </si>
+  <si>
+    <t>Operadores de taxi independientes en Pachuca manifestaron su inconformidad con el ajuste tarifario a 45 pesos e insistieron en que el cobro mínimo debe subir a 50 pesos debido a altos costos de gasolina, cuotas de alquiler y tiempos perdidos en el tráfico.</t>
+  </si>
+  <si>
+    <t>Chóferes de taxi independientes señalan que el ajuste tarifario a 45 pesos es insuficiente y solicitan fijar en 50 pesos la tarifa mínima de arranque.</t>
+  </si>
+  <si>
+    <t>Localizan vivas a 5 adolescentes reportadas como desaparecidas</t>
+  </si>
+  <si>
+    <t>La Comisión de Búsqueda de Personas del Estado de Hidalgo logró la localización con vida de cinco adolescentes reportadas como desaparecidas en los últimos cuatro días, en acciones coordinadas con la Ciudad de México y el Estado de México.</t>
+  </si>
+  <si>
+    <t>Búsqueda de personas</t>
+  </si>
+  <si>
+    <t>Tras operativos interinstitucionales, la CBPEH ubicó sanas y salvas a cinco menores reportadas como ausentes voluntarias por conflictos familiares.</t>
+  </si>
+  <si>
+    <t>CBPEH, C5i</t>
+  </si>
+  <si>
+    <t>José Francisco García Reyes</t>
+  </si>
+  <si>
+    <t>Escolaridad logra alcanzar los 10 años en promedio</t>
+  </si>
+  <si>
+    <t>De acuerdo con los indicadores del Segundo Informe de Gobierno, la población hidalguense de 15 años y más alcanzó una escolaridad promedio de 10 años, lo que garantiza que concluyen la educación básica e ingresan al nivel medio superior.</t>
+  </si>
+  <si>
+    <t>Nivel educativo</t>
+  </si>
+  <si>
+    <t>Hidalgo eleva el promedio de escolaridad de su población a 10 años de estudio, ubicándose en el primer año de preparatoria o bachillerato.</t>
+  </si>
+  <si>
+    <t>SEPH, Gobierno de Hidalgo</t>
+  </si>
+  <si>
+    <t>Fuera de control, plaga de mosco Culex en la presa Endhó</t>
+  </si>
+  <si>
+    <t>Ana Elsa Castillo Sea, alcaldesa de Tepetitlán, denunció que la plaga del mosco Culex volvió a salirse de control debido a que el lirio acuático cubre entre 85% y 90% de la presa Endhó y Conagua no ha enviado las máquinas cosechadoras prometidas.</t>
+  </si>
+  <si>
+    <t>Tepetitlán</t>
+  </si>
+  <si>
+    <t>Problema ambiental</t>
+  </si>
+  <si>
+    <t>La presidenta municipal de Tepetitlán advierte la presencia masiva de mosco Culex y retrasos en la llegada de barcos cosechadores de Conagua para retirar el lirio de la presa Endhó.</t>
+  </si>
+  <si>
+    <t>Conagua, Semarnath, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Ana Elsa Castillo Sea, Mayela Godínez Alarcón</t>
+  </si>
+  <si>
+    <t>Azares de vuelta: la memoria hecha poema</t>
+  </si>
+  <si>
+    <t>Reseña del libro "Azares de vuelta" de la poeta Dulce María Sardiñas Izaguirre, poemario que reúne vivencias, duelos, recuerdos de juventud y reflexiones autobiográficas escritas entre 1987 y 1990.</t>
+  </si>
+  <si>
+    <t>Reseña literaria</t>
+  </si>
+  <si>
+    <t>La autora Dulce María Sardiñas comparte la bitácora emocional que compone su poemario autobiográfico Azares de vuelta.</t>
+  </si>
+  <si>
+    <t>Angélica Ruiz</t>
+  </si>
+  <si>
+    <t>Dulce María Sardiñas Izaguirre</t>
+  </si>
+  <si>
+    <t>Quintanar prevé alza en turismo debido a la feria</t>
+  </si>
+  <si>
+    <t>Elizabeth Quintanar Gómez, secretaria de Turismo estatal, destacó que la Feria de San Francisco Pachuca 2026 impulsará la ocupación hotelera en la capital y municipios vecinos como Mineral de la Reforma, Mineral del Monte y Mineral del Chico.</t>
+  </si>
+  <si>
+    <t>Afluencia Turística</t>
+  </si>
+  <si>
+    <t>Turismo estatal proyecta alta demanda en hospedaje en el Corredor de la Montaña y Pachuca con motivo de la cartelera de espectáculos de la feria anual.</t>
+  </si>
+  <si>
+    <t>Turismo, OEEH</t>
   </si>
 </sst>
 </file>
@@ -1398,8 +1740,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ69" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ69" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ78" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ78" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1831,45 +2173,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AJ78"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="81.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="81.1796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="22.1796875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="15" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="81.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1979,30 +2321,30 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>102</v>
+        <v>328</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>329</v>
       </c>
       <c r="F2" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>42</v>
@@ -2020,19 +2362,19 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>105</v>
+        <v>330</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>106</v>
+        <v>331</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>56</v>
@@ -2044,40 +2386,40 @@
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>109</v>
+        <v>332</v>
       </c>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>333</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>334</v>
       </c>
       <c r="F3" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>45</v>
@@ -2098,10 +2440,10 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>112</v>
+        <v>335</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>55</v>
@@ -2122,45 +2464,45 @@
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>114</v>
+        <v>336</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>86</v>
+        <v>337</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>115</v>
+        <v>338</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>116</v>
+        <v>339</v>
       </c>
       <c r="F4" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>59</v>
+        <v>260</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>48</v>
@@ -2178,25 +2520,25 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>117</v>
+        <v>261</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>118</v>
+        <v>340</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>44</v>
@@ -2208,40 +2550,42 @@
         <v>41</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AJ4" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
+        <v>342</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>121</v>
+        <v>343</v>
       </c>
       <c r="F5" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2256,10 +2600,10 @@
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>123</v>
+        <v>344</v>
       </c>
       <c r="Y5" s="2" t="s">
         <v>55</v>
@@ -2280,46 +2624,48 @@
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ5" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>345</v>
+      </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>125</v>
+        <v>346</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>126</v>
+        <v>347</v>
       </c>
       <c r="F6" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>127</v>
+        <v>348</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2334,10 +2680,10 @@
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>128</v>
+        <v>349</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>129</v>
+        <v>350</v>
       </c>
       <c r="Y6" s="2" t="s">
         <v>57</v>
@@ -2346,7 +2692,7 @@
         <v>43</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>56</v>
@@ -2364,37 +2710,39 @@
         <v>41</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ6" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>132</v>
+        <v>352</v>
       </c>
       <c r="F7" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>49</v>
@@ -2403,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="S7">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>58</v>
@@ -2412,19 +2760,19 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>132</v>
+        <v>353</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA7">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>56</v>
@@ -2436,43 +2784,45 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ7" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>354</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>134</v>
+        <v>275</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>135</v>
+        <v>276</v>
       </c>
       <c r="F8" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>49</v>
@@ -2481,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="S8">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>58</v>
@@ -2490,19 +2840,19 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>135</v>
+        <v>278</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>56</v>
@@ -2514,52 +2864,54 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ8" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>280</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>139</v>
+        <v>281</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="F9" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R9">
         <v>1</v>
       </c>
       <c r="S9">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>58</v>
@@ -2568,16 +2920,16 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>140</v>
+        <v>283</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA9">
         <v>20</v>
@@ -2592,52 +2944,52 @@
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AJ9" s="2"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>142</v>
+        <v>284</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="F10" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R10">
         <v>1</v>
       </c>
       <c r="S10">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>58</v>
@@ -2646,19 +2998,19 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>143</v>
+        <v>286</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>56</v>
@@ -2670,52 +3022,52 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="AG10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>62</v>
+        <v>288</v>
       </c>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>289</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="F11" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G11">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R11">
         <v>1</v>
       </c>
       <c r="S11">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>58</v>
@@ -2724,19 +3076,19 @@
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>147</v>
+        <v>292</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>56</v>
@@ -2748,52 +3100,52 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>62</v>
+        <v>293</v>
       </c>
       <c r="AJ11" s="2"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>150</v>
+        <v>294</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>151</v>
+        <v>295</v>
       </c>
       <c r="F12" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G12">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>45</v>
+        <v>296</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R12">
         <v>1</v>
       </c>
       <c r="S12">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>58</v>
@@ -2802,19 +3154,19 @@
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>151</v>
+        <v>297</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>56</v>
@@ -2826,52 +3178,52 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>41</v>
+        <v>298</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="AJ12" s="2"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>152</v>
+        <v>299</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>153</v>
+        <v>300</v>
       </c>
       <c r="F13" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R13">
         <v>1</v>
       </c>
       <c r="S13">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>58</v>
@@ -2880,19 +3232,19 @@
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>154</v>
+        <v>301</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>153</v>
+        <v>302</v>
       </c>
       <c r="Y13" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>56</v>
@@ -2904,52 +3256,54 @@
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AI13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ13" s="2"/>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="F14" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R14">
         <v>1</v>
       </c>
       <c r="S14">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>58</v>
@@ -2958,13 +3312,13 @@
         <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>61</v>
@@ -2982,52 +3336,52 @@
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="AJ14" s="2"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>158</v>
+        <v>244</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="F15" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R15">
         <v>1</v>
       </c>
       <c r="S15">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>58</v>
@@ -3036,19 +3390,19 @@
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA15">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>56</v>
@@ -3060,52 +3414,54 @@
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ15" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="F16" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>251</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R16">
         <v>1</v>
       </c>
       <c r="S16">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>58</v>
@@ -3114,19 +3470,19 @@
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>65</v>
+        <v>252</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA16">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>56</v>
@@ -3138,52 +3494,54 @@
         <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ16" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>254</v>
+      </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="F17" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>58</v>
@@ -3192,19 +3550,19 @@
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>56</v>
@@ -3216,52 +3574,52 @@
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AJ17" s="2"/>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="F18" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>59</v>
+        <v>260</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
       <c r="S18">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>58</v>
@@ -3270,19 +3628,19 @@
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>171</v>
+        <v>261</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>172</v>
+        <v>262</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA18">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>56</v>
@@ -3294,52 +3652,54 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ18" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>263</v>
+      </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>173</v>
+        <v>264</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>174</v>
+        <v>265</v>
       </c>
       <c r="F19" s="1">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R19">
         <v>1</v>
       </c>
       <c r="S19">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>58</v>
@@ -3348,19 +3708,19 @@
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>175</v>
+        <v>266</v>
       </c>
       <c r="Y19" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA19">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>56</v>
@@ -3372,52 +3732,52 @@
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AJ19" s="2"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>177</v>
+        <v>268</v>
       </c>
       <c r="F20" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R20">
         <v>1</v>
       </c>
       <c r="S20">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>58</v>
@@ -3426,13 +3786,13 @@
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>177</v>
+        <v>269</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>61</v>
@@ -3450,52 +3810,52 @@
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="AJ20" s="2"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>182</v>
+        <v>271</v>
       </c>
       <c r="F21" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R21">
         <v>1</v>
       </c>
       <c r="S21">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>58</v>
@@ -3504,10 +3864,10 @@
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>183</v>
+        <v>87</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>57</v>
@@ -3516,7 +3876,7 @@
         <v>61</v>
       </c>
       <c r="AA21">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>56</v>
@@ -3528,52 +3888,54 @@
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ21" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>274</v>
+      </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>184</v>
+        <v>355</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>185</v>
+        <v>356</v>
       </c>
       <c r="F22" s="1">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="G22">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R22">
         <v>1</v>
       </c>
       <c r="S22">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>58</v>
@@ -3582,19 +3944,19 @@
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>186</v>
+        <v>357</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>185</v>
+        <v>358</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA22">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AB22" s="2" t="s">
         <v>56</v>
@@ -3606,52 +3968,54 @@
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AG22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ22" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>360</v>
+      </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>361</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>188</v>
+        <v>362</v>
       </c>
       <c r="F23" s="1">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="G23">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R23">
         <v>1</v>
       </c>
       <c r="S23">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>58</v>
@@ -3660,19 +4024,19 @@
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>91</v>
+        <v>363</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>188</v>
+        <v>364</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA23">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>56</v>
@@ -3690,46 +4054,48 @@
         <v>41</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ23" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>189</v>
+        <v>366</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>190</v>
+        <v>367</v>
       </c>
       <c r="F24" s="1">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R24">
         <v>1</v>
       </c>
       <c r="S24">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>58</v>
@@ -3738,19 +4104,19 @@
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>192</v>
+        <v>368</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>190</v>
+        <v>369</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA24">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB24" s="2" t="s">
         <v>56</v>
@@ -3762,52 +4128,54 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AI24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ24" s="2"/>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>193</v>
+        <v>372</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>194</v>
+        <v>373</v>
       </c>
       <c r="F25" s="1">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R25">
         <v>1</v>
       </c>
       <c r="S25">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T25" s="2" t="s">
         <v>58</v>
@@ -3816,19 +4184,19 @@
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>179</v>
+        <v>374</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>195</v>
+        <v>375</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA25">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB25" s="2" t="s">
         <v>56</v>
@@ -3840,52 +4208,54 @@
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="AG25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AJ25" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>377</v>
+      </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>197</v>
+        <v>378</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>198</v>
+        <v>379</v>
       </c>
       <c r="F26" s="1">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>380</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R26">
         <v>1</v>
       </c>
       <c r="S26">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>58</v>
@@ -3894,76 +4264,78 @@
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>183</v>
+        <v>381</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>199</v>
+        <v>382</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA26">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ26" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>384</v>
+      </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>200</v>
+        <v>385</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>201</v>
+        <v>386</v>
       </c>
       <c r="F27" s="1">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>387</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R27">
         <v>1</v>
       </c>
       <c r="S27">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>58</v>
@@ -3972,16 +4344,16 @@
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>186</v>
+        <v>388</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>202</v>
+        <v>389</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA27">
         <v>16</v>
@@ -3996,73 +4368,75 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ27" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
+        <v>391</v>
+      </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>203</v>
+        <v>392</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>204</v>
+        <v>393</v>
       </c>
       <c r="F28" s="1">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>394</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R28">
         <v>1</v>
       </c>
       <c r="S28">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>58</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>192</v>
+        <v>395</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>205</v>
+        <v>396</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA28">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB28" s="2" t="s">
         <v>56</v>
@@ -4074,43 +4448,45 @@
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AG28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ28" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AI28" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="AJ28" s="2"/>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>207</v>
+        <v>398</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>208</v>
+        <v>399</v>
       </c>
       <c r="F29" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>48</v>
@@ -4128,10 +4504,10 @@
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>210</v>
+        <v>401</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>55</v>
@@ -4140,7 +4516,7 @@
         <v>43</v>
       </c>
       <c r="AA29">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AB29" s="2" t="s">
         <v>56</v>
@@ -4152,40 +4528,42 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>211</v>
+        <v>402</v>
       </c>
       <c r="AG29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ29" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>212</v>
+        <v>404</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>213</v>
+        <v>405</v>
       </c>
       <c r="F30" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>45</v>
@@ -4206,10 +4584,10 @@
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>192</v>
+        <v>406</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>214</v>
+        <v>407</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>57</v>
@@ -4218,7 +4596,7 @@
         <v>43</v>
       </c>
       <c r="AA30">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AB30" s="2" t="s">
         <v>56</v>
@@ -4236,37 +4614,39 @@
         <v>41</v>
       </c>
       <c r="AH30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ30" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AI30" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ30" s="2"/>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="B31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>216</v>
+        <v>409</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>217</v>
+        <v>410</v>
       </c>
       <c r="F31" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>42</v>
@@ -4284,16 +4664,16 @@
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>218</v>
+        <v>412</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA31">
         <v>20</v>
@@ -4308,46 +4688,48 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>80</v>
+        <v>413</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ31" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="AJ31" s="2" t="s">
+        <v>415</v>
+      </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>219</v>
+        <v>417</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>220</v>
+        <v>418</v>
       </c>
       <c r="F32" s="1">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>221</v>
+        <v>419</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4362,19 +4744,19 @@
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>222</v>
+        <v>420</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>223</v>
+        <v>421</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA32">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>56</v>
@@ -4386,46 +4768,48 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="AG32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AJ32" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="AJ32" s="2" t="s">
+        <v>423</v>
+      </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>225</v>
+        <v>424</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>226</v>
+        <v>425</v>
       </c>
       <c r="F33" s="1">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4440,16 +4824,16 @@
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>227</v>
+        <v>426</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>228</v>
+        <v>427</v>
       </c>
       <c r="Y33" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA33">
         <v>20</v>
@@ -4464,45 +4848,45 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="AG33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>229</v>
+        <v>428</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>86</v>
+        <v>429</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>231</v>
+        <v>431</v>
       </c>
       <c r="F34" s="1">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>48</v>
@@ -4520,25 +4904,25 @@
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>232</v>
+        <v>432</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>233</v>
+        <v>433</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA34">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB34" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD34" s="2" t="s">
         <v>44</v>
@@ -4550,42 +4934,40 @@
         <v>41</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="AJ34" s="2" t="s">
-        <v>235</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="AJ34" s="2"/>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>236</v>
+        <v>436</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>237</v>
+        <v>437</v>
       </c>
       <c r="F35" s="1">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>238</v>
+        <v>45</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -4600,67 +4982,69 @@
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>65</v>
+        <v>438</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>239</v>
+        <v>439</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA35">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB35" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC35" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD35" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="AG35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>64</v>
+        <v>440</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ35" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="AJ35" s="2" t="s">
+        <v>442</v>
+      </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>240</v>
+        <v>443</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>241</v>
+        <v>444</v>
       </c>
       <c r="F36" s="1">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>48</v>
@@ -4678,69 +5062,67 @@
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>242</v>
+        <v>445</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA36">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC36" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD36" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF36" s="2" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="AJ36" s="2" t="s">
-        <v>245</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="AJ36" s="2"/>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>246</v>
+        <v>448</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>247</v>
+        <v>449</v>
       </c>
       <c r="F37" s="1">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="G37">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>248</v>
+        <v>71</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>48</v>
@@ -4755,13 +5137,13 @@
         <v>58</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>249</v>
+        <v>450</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>250</v>
+        <v>451</v>
       </c>
       <c r="Y37" s="2" t="s">
         <v>55</v>
@@ -4770,7 +5152,7 @@
         <v>43</v>
       </c>
       <c r="AA37">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>56</v>
@@ -4782,54 +5164,54 @@
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>41</v>
+        <v>452</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>251</v>
+        <v>90</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>252</v>
+        <v>453</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>253</v>
+        <v>454</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>254</v>
+        <v>455</v>
       </c>
       <c r="F38" s="1">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R38">
         <v>1</v>
       </c>
       <c r="S38">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>58</v>
@@ -4838,19 +5220,19 @@
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>255</v>
+        <v>456</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>254</v>
+        <v>457</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA38">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>56</v>
@@ -4862,52 +5244,54 @@
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>63</v>
+        <v>458</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ38" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="AJ38" s="2" t="s">
+        <v>460</v>
+      </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>256</v>
+        <v>461</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>257</v>
+        <v>462</v>
       </c>
       <c r="F39" s="1">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="G39">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>238</v>
+        <v>59</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R39">
         <v>1</v>
       </c>
       <c r="S39">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>58</v>
@@ -4916,16 +5300,16 @@
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>258</v>
+        <v>463</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>257</v>
+        <v>464</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA39">
         <v>20</v>
@@ -4940,52 +5324,52 @@
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>80</v>
+        <v>465</v>
       </c>
       <c r="AJ39" s="2"/>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>259</v>
+        <v>466</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>260</v>
+        <v>467</v>
       </c>
       <c r="F40" s="1">
         <v>46293</v>
       </c>
       <c r="G40">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>89</v>
+        <v>260</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R40">
         <v>1</v>
       </c>
       <c r="S40">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>58</v>
@@ -4994,16 +5378,16 @@
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>90</v>
+        <v>468</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>260</v>
+        <v>469</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA40">
         <v>20</v>
@@ -5012,58 +5396,60 @@
         <v>56</v>
       </c>
       <c r="AC40" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD40" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ40" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="AJ40" s="2" t="s">
+        <v>471</v>
+      </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>261</v>
+        <v>472</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>262</v>
+        <v>473</v>
       </c>
       <c r="F41" s="1">
         <v>46293</v>
       </c>
       <c r="G41">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R41">
         <v>1</v>
       </c>
       <c r="S41">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>58</v>
@@ -5072,19 +5458,19 @@
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>263</v>
+        <v>363</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>262</v>
+        <v>474</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA41">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>56</v>
@@ -5096,52 +5482,52 @@
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AG41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>66</v>
+        <v>365</v>
       </c>
       <c r="AJ41" s="2"/>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>265</v>
+        <v>476</v>
       </c>
       <c r="F42" s="1">
         <v>46293</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R42">
         <v>1</v>
       </c>
       <c r="S42">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>58</v>
@@ -5150,19 +5536,19 @@
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>255</v>
+        <v>477</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>266</v>
+        <v>478</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA42">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB42" s="2" t="s">
         <v>56</v>
@@ -5174,52 +5560,54 @@
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="AG42" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ42" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="AJ42" s="2" t="s">
+        <v>480</v>
+      </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>268</v>
+        <v>481</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>269</v>
+        <v>482</v>
       </c>
       <c r="F43" s="1">
         <v>46293</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>238</v>
+        <v>59</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R43">
         <v>1</v>
       </c>
       <c r="S43">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T43" s="2" t="s">
         <v>58</v>
@@ -5228,16 +5616,16 @@
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>258</v>
+        <v>483</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>270</v>
+        <v>484</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA43">
         <v>20</v>
@@ -5252,52 +5640,52 @@
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AG43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>271</v>
+        <v>485</v>
       </c>
       <c r="AJ43" s="2"/>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>272</v>
+        <v>486</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>273</v>
+        <v>487</v>
       </c>
       <c r="F44" s="1">
         <v>46293</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>89</v>
+        <v>488</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R44">
         <v>1</v>
       </c>
       <c r="S44">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T44" s="2" t="s">
         <v>58</v>
@@ -5306,16 +5694,16 @@
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>90</v>
+        <v>489</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>274</v>
+        <v>490</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA44">
         <v>20</v>
@@ -5324,52 +5712,54 @@
         <v>56</v>
       </c>
       <c r="AC44" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD44" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="AG44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AJ44" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="AJ44" s="2" t="s">
+        <v>492</v>
+      </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>276</v>
+        <v>493</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>277</v>
+        <v>494</v>
       </c>
       <c r="F45" s="1">
         <v>46293</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5381,22 +5771,22 @@
         <v>58</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>65</v>
+        <v>495</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>278</v>
+        <v>496</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z45" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA45">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AB45" s="2" t="s">
         <v>56</v>
@@ -5408,40 +5798,42 @@
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>69</v>
+        <v>497</v>
       </c>
       <c r="AG45" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ45" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="AJ45" s="2" t="s">
+        <v>498</v>
+      </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>279</v>
+        <v>499</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="F46" s="1">
         <v>46293</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>45</v>
@@ -5462,19 +5854,19 @@
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>183</v>
+        <v>501</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>281</v>
+        <v>502</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA46">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB46" s="2" t="s">
         <v>56</v>
@@ -5486,48 +5878,48 @@
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>283</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>284</v>
+        <v>100</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>285</v>
+        <v>101</v>
       </c>
       <c r="F47" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>286</v>
+        <v>102</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5542,19 +5934,19 @@
         <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>287</v>
+        <v>103</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>288</v>
+        <v>104</v>
       </c>
       <c r="Y47" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA47">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>56</v>
@@ -5566,48 +5958,46 @@
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ47" s="2" t="s">
-        <v>289</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="AJ47" s="2"/>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>291</v>
+        <v>109</v>
       </c>
       <c r="F48" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5622,19 +6012,19 @@
         <v>37</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>292</v>
+        <v>110</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z48" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA48">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB48" s="2" t="s">
         <v>56</v>
@@ -5646,43 +6036,45 @@
         <v>44</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="AG48" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ48" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="AJ48" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>293</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>294</v>
+        <v>114</v>
       </c>
       <c r="F49" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G49">
         <v>6</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>295</v>
+        <v>59</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>48</v>
@@ -5700,25 +6092,25 @@
         <v>37</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>296</v>
+        <v>115</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>297</v>
+        <v>116</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA49">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB49" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC49" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD49" s="2" t="s">
         <v>44</v>
@@ -5730,36 +6122,34 @@
         <v>41</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ49" s="2" t="s">
-        <v>298</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="AJ49" s="2"/>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>299</v>
+        <v>118</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>300</v>
+        <v>119</v>
       </c>
       <c r="F50" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>45</v>
@@ -5780,19 +6170,19 @@
         <v>37</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>301</v>
+        <v>121</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA50">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB50" s="2" t="s">
         <v>56</v>
@@ -5810,37 +6200,37 @@
         <v>41</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="AJ50" s="2"/>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>302</v>
+        <v>123</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>303</v>
+        <v>124</v>
       </c>
       <c r="F51" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>48</v>
@@ -5858,25 +6248,25 @@
         <v>37</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>304</v>
+        <v>127</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z51" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA51">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AB51" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC51" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD51" s="2" t="s">
         <v>44</v>
@@ -5888,37 +6278,37 @@
         <v>41</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="AJ51" s="2"/>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>305</v>
+        <v>181</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>306</v>
+        <v>182</v>
       </c>
       <c r="F52" s="1">
         <v>46293</v>
       </c>
       <c r="G52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>48</v>
@@ -5936,19 +6326,19 @@
         <v>37</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>307</v>
+        <v>184</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z52" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA52">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AB52" s="2" t="s">
         <v>56</v>
@@ -5960,54 +6350,52 @@
         <v>44</v>
       </c>
       <c r="AF52" s="2" t="s">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH52" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ52" s="2"/>
+    </row>
+    <row r="53" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AI52" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="AJ52" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="B53" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>310</v>
+        <v>186</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>311</v>
+        <v>187</v>
       </c>
       <c r="F53" s="1">
         <v>46293</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R53">
         <v>1</v>
       </c>
       <c r="S53">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T53" s="2" t="s">
         <v>58</v>
@@ -6016,19 +6404,19 @@
         <v>37</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>312</v>
+        <v>166</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>313</v>
+        <v>188</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z53" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA53">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB53" s="2" t="s">
         <v>56</v>
@@ -6040,45 +6428,43 @@
         <v>44</v>
       </c>
       <c r="AF53" s="2" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="AG53" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ53" s="2" t="s">
-        <v>315</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="AJ53" s="2"/>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>316</v>
+        <v>190</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>317</v>
+        <v>191</v>
       </c>
       <c r="F54" s="1">
         <v>46293</v>
       </c>
       <c r="G54">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>42</v>
@@ -6087,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="S54">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T54" s="2" t="s">
         <v>58</v>
@@ -6096,10 +6482,10 @@
         <v>37</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>318</v>
+        <v>192</v>
       </c>
       <c r="Y54" s="2" t="s">
         <v>55</v>
@@ -6120,43 +6506,43 @@
         <v>44</v>
       </c>
       <c r="AF54" s="2" t="s">
-        <v>39</v>
+        <v>185</v>
       </c>
       <c r="AG54" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="AJ54" s="2"/>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>319</v>
+        <v>193</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>320</v>
+        <v>194</v>
       </c>
       <c r="F55" s="1">
         <v>46293</v>
       </c>
       <c r="G55">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>45</v>
+        <v>195</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>42</v>
@@ -6165,7 +6551,7 @@
         <v>1</v>
       </c>
       <c r="S55">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T55" s="2" t="s">
         <v>58</v>
@@ -6174,19 +6560,19 @@
         <v>37</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>321</v>
+        <v>197</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA55">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB55" s="2" t="s">
         <v>56</v>
@@ -6198,52 +6584,52 @@
         <v>44</v>
       </c>
       <c r="AF55" s="2" t="s">
-        <v>322</v>
+        <v>99</v>
       </c>
       <c r="AG55" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>323</v>
+        <v>198</v>
       </c>
       <c r="AJ55" s="2"/>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>324</v>
+        <v>199</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="F56" s="1">
         <v>46293</v>
       </c>
       <c r="G56">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R56">
         <v>1</v>
       </c>
       <c r="S56">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>58</v>
@@ -6252,19 +6638,19 @@
         <v>37</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>326</v>
+        <v>201</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>327</v>
+        <v>202</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA56">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB56" s="2" t="s">
         <v>56</v>
@@ -6276,52 +6662,54 @@
         <v>44</v>
       </c>
       <c r="AF56" s="2" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="AG56" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH56" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AJ56" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="AJ56" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>329</v>
+        <v>204</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>330</v>
+        <v>205</v>
       </c>
       <c r="F57" s="1">
         <v>46293</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>331</v>
+        <v>45</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R57">
         <v>1</v>
       </c>
       <c r="S57">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T57" s="2" t="s">
         <v>58</v>
@@ -6330,10 +6718,10 @@
         <v>37</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>65</v>
+        <v>206</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>332</v>
+        <v>207</v>
       </c>
       <c r="Y57" s="2" t="s">
         <v>57</v>
@@ -6348,49 +6736,51 @@
         <v>56</v>
       </c>
       <c r="AC57" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF57" s="2" t="s">
-        <v>333</v>
+        <v>41</v>
       </c>
       <c r="AG57" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ57" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="AJ57" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>334</v>
+        <v>210</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>335</v>
+        <v>211</v>
       </c>
       <c r="F58" s="1">
         <v>46293</v>
       </c>
       <c r="G58">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>148</v>
+        <v>212</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>42</v>
@@ -6399,7 +6789,7 @@
         <v>1</v>
       </c>
       <c r="S58">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T58" s="2" t="s">
         <v>58</v>
@@ -6408,10 +6798,10 @@
         <v>37</v>
       </c>
       <c r="W58" s="2" t="s">
-        <v>336</v>
+        <v>64</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>337</v>
+        <v>213</v>
       </c>
       <c r="Y58" s="2" t="s">
         <v>57</v>
@@ -6426,51 +6816,52 @@
         <v>56</v>
       </c>
       <c r="AC58" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD58" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF58" s="2" t="s">
-        <v>338</v>
+        <v>185</v>
       </c>
       <c r="AG58" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH58" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AJ58" s="2" t="s">
-        <v>340</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="AJ58" s="2"/>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>341</v>
+        <v>214</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>342</v>
+        <v>215</v>
       </c>
       <c r="F59" s="1">
         <v>46293</v>
       </c>
+      <c r="G59">
+        <v>6</v>
+      </c>
       <c r="H59" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -6482,69 +6873,72 @@
         <v>58</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>343</v>
+        <v>37</v>
       </c>
       <c r="W59" s="2" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>344</v>
+        <v>217</v>
       </c>
       <c r="Y59" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z59" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA59">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB59" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC59" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD59" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF59" s="2" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="AG59" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH59" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>345</v>
+        <v>218</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>86</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>346</v>
+        <v>220</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>347</v>
+        <v>221</v>
       </c>
       <c r="F60" s="1">
         <v>46293</v>
       </c>
+      <c r="G60">
+        <v>7</v>
+      </c>
       <c r="H60" s="2" t="s">
-        <v>286</v>
+        <v>222</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>48</v>
@@ -6562,10 +6956,10 @@
         <v>37</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>348</v>
+        <v>223</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>349</v>
+        <v>224</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>55</v>
@@ -6592,30 +6986,30 @@
         <v>41</v>
       </c>
       <c r="AH60" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>350</v>
+        <v>225</v>
       </c>
       <c r="AJ60" s="2" t="s">
-        <v>289</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>351</v>
+        <v>306</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="F61" s="1">
         <v>46293</v>
@@ -6624,7 +7018,7 @@
         <v>45</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -6636,22 +7030,22 @@
         <v>58</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="W61" s="2" t="s">
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="Y61" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z61" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA61">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB61" s="2" t="s">
         <v>56</v>
@@ -6663,43 +7057,45 @@
         <v>44</v>
       </c>
       <c r="AF61" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="AG61" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH61" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI61" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="AJ61" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="AI61" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ61" s="2"/>
-    </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="F62" s="1">
         <v>46293</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -6714,10 +7110,10 @@
         <v>37</v>
       </c>
       <c r="W62" s="2" t="s">
-        <v>222</v>
+        <v>313</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>356</v>
+        <v>314</v>
       </c>
       <c r="Y62" s="2" t="s">
         <v>55</v>
@@ -6744,28 +7140,30 @@
         <v>41</v>
       </c>
       <c r="AH62" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="AI62" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AJ62" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="AJ62" s="2" t="s">
+        <v>254</v>
+      </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="F63" s="1">
         <v>46293</v>
@@ -6789,10 +7187,10 @@
         <v>37</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>359</v>
+        <v>166</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="Y63" s="2" t="s">
         <v>55</v>
@@ -6819,39 +7217,34 @@
         <v>41</v>
       </c>
       <c r="AH63" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AI63" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="AJ63" s="2" t="s">
-        <v>362</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="AJ63" s="2"/>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
       <c r="F64" s="1">
         <v>46293</v>
       </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
       <c r="H64" s="2" t="s">
-        <v>45</v>
+        <v>195</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>42</v>
@@ -6869,19 +7262,19 @@
         <v>37</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>365</v>
+        <v>196</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="Y64" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z64" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA64">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB64" s="2" t="s">
         <v>56</v>
@@ -6899,35 +7292,32 @@
         <v>41</v>
       </c>
       <c r="AH64" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="AI64" s="2" t="s">
-        <v>367</v>
+        <v>236</v>
       </c>
       <c r="AJ64" s="2"/>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>368</v>
+        <v>322</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="F65" s="1">
         <v>46293</v>
       </c>
-      <c r="G65">
-        <v>2</v>
-      </c>
       <c r="H65" s="2" t="s">
         <v>45</v>
       </c>
@@ -6947,10 +7337,10 @@
         <v>37</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="Y65" s="2" t="s">
         <v>55</v>
@@ -6971,54 +7361,54 @@
         <v>44</v>
       </c>
       <c r="AF65" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="AG65" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH65" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AI65" s="2" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="AJ65" s="2" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>373</v>
+        <v>129</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>374</v>
+        <v>139</v>
       </c>
       <c r="F66" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>295</v>
+        <v>45</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R66">
         <v>1</v>
       </c>
       <c r="S66">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T66" s="2" t="s">
         <v>58</v>
@@ -7027,16 +7417,16 @@
         <v>37</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>375</v>
+        <v>140</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="Z66" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA66">
         <v>20</v>
@@ -7051,54 +7441,52 @@
         <v>44</v>
       </c>
       <c r="AF66" s="2" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="AG66" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH66" s="2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AI66" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ66" s="2" t="s">
-        <v>376</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="AJ66" s="2"/>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>377</v>
+        <v>142</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>378</v>
+        <v>143</v>
       </c>
       <c r="F67" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R67">
         <v>1</v>
       </c>
       <c r="S67">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>58</v>
@@ -7107,16 +7495,16 @@
         <v>37</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>379</v>
+        <v>144</v>
       </c>
       <c r="Y67" s="2" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="Z67" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA67">
         <v>20</v>
@@ -7131,45 +7519,43 @@
         <v>44</v>
       </c>
       <c r="AF67" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="AG67" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH67" s="2" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="AI67" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ67" s="2" t="s">
-        <v>380</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AJ67" s="2"/>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>381</v>
+        <v>145</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>382</v>
+        <v>146</v>
       </c>
       <c r="F68" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>383</v>
+        <v>45</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>49</v>
@@ -7178,7 +7564,7 @@
         <v>1</v>
       </c>
       <c r="S68">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>58</v>
@@ -7187,69 +7573,67 @@
         <v>37</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>384</v>
+        <v>64</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>385</v>
+        <v>147</v>
       </c>
       <c r="Y68" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z68" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA68">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB68" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC68" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD68" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF68" s="2" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="AG68" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH68" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AI68" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AJ68" s="2" t="s">
-        <v>386</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="AJ68" s="2"/>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C69" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>387</v>
+        <v>149</v>
       </c>
       <c r="F69" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="G69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>49</v>
@@ -7258,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="S69">
-        <v>13262</v>
+        <v>15000</v>
       </c>
       <c r="T69" s="2" t="s">
         <v>58</v>
@@ -7267,19 +7651,19 @@
         <v>37</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>388</v>
+        <v>151</v>
       </c>
       <c r="Y69" s="2" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="Z69" s="2" t="s">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="AA69">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB69" s="2" t="s">
         <v>56</v>
@@ -7291,20 +7675,720 @@
         <v>44</v>
       </c>
       <c r="AF69" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG69" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH69" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="AI69" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ69" s="2" t="s">
-        <v>389</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="AJ69" s="2"/>
+    </row>
+    <row r="70" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" t="s">
+        <v>92</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F70" s="1">
+        <v>46291</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+      <c r="S70">
+        <v>15000</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y70" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z70" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA70">
+        <v>16</v>
+      </c>
+      <c r="AB70" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF70" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG70" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH70" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI70" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ70" s="2"/>
+    </row>
+    <row r="71" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" t="s">
+        <v>92</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F71" s="1">
+        <v>46291</v>
+      </c>
+      <c r="G71">
+        <v>3</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R71">
+        <v>1</v>
+      </c>
+      <c r="S71">
+        <v>15000</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W71" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="X71" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y71" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z71" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA71">
+        <v>16</v>
+      </c>
+      <c r="AB71" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF71" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG71" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH71" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI71" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ71" s="2"/>
+    </row>
+    <row r="72" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" t="s">
+        <v>92</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F72" s="1">
+        <v>46292</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72">
+        <v>15000</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y72" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z72" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA72">
+        <v>20</v>
+      </c>
+      <c r="AB72" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF72" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG72" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH72" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ72" s="2"/>
+    </row>
+    <row r="73" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" t="s">
+        <v>92</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F73" s="1">
+        <v>46292</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+      <c r="S73">
+        <v>15000</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W73" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="X73" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y73" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z73" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA73">
+        <v>16</v>
+      </c>
+      <c r="AB73" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC73" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF73" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG73" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH73" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI73" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ73" s="2"/>
+    </row>
+    <row r="74" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" s="1">
+        <v>46292</v>
+      </c>
+      <c r="G74">
+        <v>3</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R74">
+        <v>1</v>
+      </c>
+      <c r="S74">
+        <v>15000</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="X74" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y74" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z74" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA74">
+        <v>16</v>
+      </c>
+      <c r="AB74" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC74" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF74" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG74" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH74" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI74" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ74" s="2"/>
+    </row>
+    <row r="75" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F75" s="1">
+        <v>46292</v>
+      </c>
+      <c r="G75">
+        <v>3</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R75">
+        <v>1</v>
+      </c>
+      <c r="S75">
+        <v>15000</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W75" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X75" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y75" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z75" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA75">
+        <v>20</v>
+      </c>
+      <c r="AB75" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF75" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG75" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH75" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI75" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AJ75" s="2"/>
+    </row>
+    <row r="76" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" t="s">
+        <v>92</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F76" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R76">
+        <v>1</v>
+      </c>
+      <c r="S76">
+        <v>15000</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="X76" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y76" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z76" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA76">
+        <v>24</v>
+      </c>
+      <c r="AB76" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF76" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG76" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH76" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI76" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="AJ76" s="2"/>
+    </row>
+    <row r="77" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F77" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G77">
+        <v>3</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+      <c r="S77">
+        <v>15000</v>
+      </c>
+      <c r="T77" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W77" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="X77" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y77" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z77" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA77">
+        <v>20</v>
+      </c>
+      <c r="AB77" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF77" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG77" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH77" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI77" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="AJ77" s="2"/>
+    </row>
+    <row r="78" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F78" s="1">
+        <v>46293</v>
+      </c>
+      <c r="G78">
+        <v>3</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+      <c r="S78">
+        <v>15000</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="X78" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y78" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z78" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA78">
+        <v>20</v>
+      </c>
+      <c r="AB78" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC78" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD78" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF78" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG78" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH78" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI78" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ78" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FBBE8D-BA7F-4D41-94B2-E590C6A6040C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B80C9D-6A50-4811-B826-A60C50996539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="421">
   <si>
     <t>Canal</t>
   </si>
@@ -238,15 +238,9 @@
     <t>Segobh</t>
   </si>
   <si>
-    <t>Adela Garmez</t>
-  </si>
-  <si>
     <t>Semot</t>
   </si>
   <si>
-    <t>Aumento Tarifa De Transporte</t>
-  </si>
-  <si>
     <t>SSPH</t>
   </si>
   <si>
@@ -256,12 +250,6 @@
     <t>Lourdes Naranjo</t>
   </si>
   <si>
-    <t>Ricardo Calleja</t>
-  </si>
-  <si>
-    <t>Oscar Raúl Pérez</t>
-  </si>
-  <si>
     <t>Contraloría</t>
   </si>
   <si>
@@ -280,27 +268,12 @@
     <t>Saderh</t>
   </si>
   <si>
-    <t>Nathali González</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
     <t>Dulce Castillo</t>
   </si>
   <si>
     <t>PGJEH</t>
   </si>
   <si>
-    <t>Marco Cerón</t>
-  </si>
-  <si>
-    <t>Secuestro</t>
-  </si>
-  <si>
-    <t>PGJEH, Presidencia</t>
-  </si>
-  <si>
     <t>Planeación</t>
   </si>
   <si>
@@ -310,39 +283,18 @@
     <t>Julio Menchaca Salazar</t>
   </si>
   <si>
-    <t>Gobernador</t>
-  </si>
-  <si>
-    <t>Capacitación policial</t>
-  </si>
-  <si>
     <t>Huejutla</t>
   </si>
   <si>
-    <t>Xantolo</t>
-  </si>
-  <si>
-    <t>Exposición cultural</t>
-  </si>
-  <si>
     <t>Cultura</t>
   </si>
   <si>
-    <t>Sedeco</t>
-  </si>
-  <si>
     <t>Sandra Sauza</t>
   </si>
   <si>
-    <t>PGJEH, UECS</t>
-  </si>
-  <si>
     <t>Berenice Gamboa</t>
   </si>
   <si>
-    <t>Sedeco, Gobernador</t>
-  </si>
-  <si>
     <t>Claudia Ávila</t>
   </si>
   <si>
@@ -355,868 +307,1009 @@
     <t>Francisco Villeda</t>
   </si>
   <si>
-    <t>Saquean en el estado 2.5 toneladas de cactáceas con carácter de protección</t>
-  </si>
-  <si>
-    <t>Entre abril y septiembre fueron decomisadas 43 biznagas burras con un peso de 2 mil 555.5 kilos, además de 155 ejemplares o partes de garambullo; Cardonal y San Salvador, los blancos.</t>
-  </si>
-  <si>
-    <t>Cardonal</t>
-  </si>
-  <si>
-    <t>Conservación Biodiversidad</t>
-  </si>
-  <si>
-    <t>Autoridades ambientales decomisaron 2.5 toneladas de cactáceas protegidas en Cardonal y San Salvador, e integraron un dictamen pericial por delito ambiental.</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Puértolas</t>
-  </si>
-  <si>
     <t>Semarnath</t>
   </si>
   <si>
-    <t>Semarnath, Profepa, FGR</t>
-  </si>
-  <si>
-    <t>Entre batucadas, arranca la Feria San Francisco</t>
-  </si>
-  <si>
-    <t>A ritmo de música, gastronomía y artesanías, la Feria de Pachuca abrió sus puertas para recibir a los visitantes con la presencia del gobernador Julio Menchaca Salazar.</t>
-  </si>
-  <si>
-    <t>Se inauguró formalmente la Feria San Francisco Pachuca 2026 con espectáculos musicales, muestra gastronómica y oferta artesanal.</t>
-  </si>
-  <si>
-    <t>Teodoro Santos</t>
-  </si>
-  <si>
-    <t>Turismo, Gobernador</t>
-  </si>
-  <si>
-    <t>Certifican intérpretes de náhuatl en Hidalgo</t>
-  </si>
-  <si>
-    <t>Personas hablantes de náhuatl en Hidalgo podrán participar en un proceso de certificación como intérpretes y traductores para fortalecer la procuración de justicia.</t>
-  </si>
-  <si>
-    <t>Certificación de intérpretes</t>
-  </si>
-  <si>
-    <t>La CEDSPI abrió la convocatoria de certificación para intérpretes de la lengua náhuatl para apoyar procedimientos de procuración de justicia.</t>
-  </si>
-  <si>
-    <t>Planeación, CEDSPI</t>
-  </si>
-  <si>
-    <t>Aseguran a tigrillo desnutrido y con maltrato en la Huasteca</t>
-  </si>
-  <si>
-    <t>Una cría de tigrillo desnutrida y con las garras cortadas fue rescatada en Calnali y trasladada a la Unidad de Rehabilitación de Fauna de Pachuca tras denuncia ante la Profepa.</t>
-  </si>
-  <si>
-    <t>Rescate Animal</t>
-  </si>
-  <si>
-    <t>Un ejemplar de tigrillo rescatado en Calnali recibe atención médica en Pachuca por desnutrición tras la intervención de la Profepa.</t>
-  </si>
-  <si>
-    <t>Semarnath, Profepa</t>
-  </si>
-  <si>
-    <t>Dan 11 años a hombre por robo de carga</t>
-  </si>
-  <si>
-    <t>Un juez dictó sentencia de 11 años y tres meses de prisión contra un hombre por el robo de un tractocamión acoplado a una caja seca en Tepeji del Río.</t>
-  </si>
-  <si>
-    <t>Tepeji del Río</t>
-  </si>
-  <si>
-    <t>Sentencia</t>
-  </si>
-  <si>
-    <t>Sentencian a más de 11 años de cárcel a un sujeto por el robo con violencia de transporte de carga en Tepeji del Río.</t>
-  </si>
-  <si>
-    <t>PGJEH, FGR</t>
-  </si>
-  <si>
-    <t>Inauguran la Feria San Francisco Pachuca Hidalgo 2026</t>
-  </si>
-  <si>
-    <t>Autoridades estatales inauguraron formalmente la Feria San Francisco Pachuca Hidalgo 2026 con diversas atracciones y pabellones.</t>
-  </si>
-  <si>
-    <t>Principal</t>
-  </si>
-  <si>
-    <t>Inicia el registro para el programa Pensión Mujeres Bienestar</t>
-  </si>
-  <si>
-    <t>Arrancó el registro para la Pensión Mujeres Bienestar en la entidad para beneficiar a adultas mayores de 60 a 64 años.</t>
-  </si>
-  <si>
-    <t>Pensión Mujeres Bienestar</t>
-  </si>
-  <si>
-    <t>Socorro Ávila</t>
-  </si>
-  <si>
     <t>Bienestar</t>
   </si>
   <si>
-    <t>Sancionarán a taxis que no respeten tarifario en la Feria</t>
-  </si>
-  <si>
-    <t>La Semot advirtió que aplicará sanciones strictly a choferes de taxi que cobren de más durante las festividades feriales.</t>
-  </si>
-  <si>
-    <t>Interiores</t>
-  </si>
-  <si>
-    <t>Atienden deslaves en la región Otomí-Tepehua tras lluvias</t>
-  </si>
-  <si>
-    <t>Cuadrillas de protección civil y obras públicas remueven escombros por deslaves causados por lluvias en la sierra Otomí-Tepehua.</t>
-  </si>
-  <si>
-    <t>Tenango de Doria</t>
-  </si>
-  <si>
-    <t>Deslaves por lluvias</t>
-  </si>
-  <si>
-    <t>Aseguran huachitúnel con conexión a toma clandestina en Atitalaquia</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad localizaron e inhabilitaron un huachitúnel conectado a ductos de Pemex en Atitalaquia.</t>
-  </si>
-  <si>
     <t>Atitalaquia</t>
   </si>
   <si>
-    <t>Huachitúnel</t>
-  </si>
-  <si>
-    <t>Hidalgo participará en el Encuentro Nacional de Arte y Cultura 2026</t>
-  </si>
-  <si>
-    <t>Delegación cultural de Hidalgo representará al estado en el Encuentro Nacional de Arte y Cultura 2026.</t>
-  </si>
-  <si>
-    <t>Reportan saldo blanco en primeras horas del operativo de la Feria</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo reportó saldo blanco en el inicio del despliegue operativo en el recinto ferial.</t>
-  </si>
-  <si>
-    <t>Operativo de Seguridad</t>
-  </si>
-  <si>
-    <t>Autoridades estatales e inauguraron oficialmente la Feria San Francisco Pachuca Hidalgo 2026 con un amplio programa de actividades culturales, comerciales y de entretenimiento para toda la familia.</t>
-  </si>
-  <si>
-    <t>Autoridades estatales e inauguraron oficialmente la Feria San Francisco Pachuca Hidalgo 2026 con actividades culturales y de entretenimiento.</t>
-  </si>
-  <si>
-    <t>Veida Martínez Miranda</t>
-  </si>
-  <si>
-    <t>Inicia el registro para el programa Pensión Mujeres Bienestar en Hidalgo</t>
-  </si>
-  <si>
-    <t>Arrancó en la entidad el registro de beneficiarias para el programa federal Pensión Mujeres Bienestar, destinado a otorgar apoyos económicos directos a adultas mayores de 60 a 64 años de edad.</t>
-  </si>
-  <si>
-    <t>Arrancó en Hidalgo el registro de beneficiarias para el programa federal Pensión Mujeres Bienestar destinado a adultas mayores.</t>
-  </si>
-  <si>
-    <t>Sancionarán a taxis que cobren tarifas excesivas durante la Feria de Pachuca</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte advirtió sobre sanciones administrativas y posible retiro de concesiones a taxistas que alteren o incrementen injustificadamente las tarifas autorizadas hacia el recinto ferial.</t>
-  </si>
-  <si>
-    <t>La Semot advirtió sanciones y retiro de concesiones a transportistas que cobren tarifas excesivas durante la Feria de Pachuca.</t>
-  </si>
-  <si>
-    <t>Destruyen huachitúnel de 143 metros en Tlaxcoapan; suman 17 asegurados</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad estatales y federales inhabilitaron un pasaje subterráneo de 143 metros de longitud que conectaba directamente con tomas clandestinas para la sustracción ilegal de combustible en Tlaxcoapan.</t>
-  </si>
-  <si>
-    <t>Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad inhabilitaron un túnel de 143 metros utilizado para la extracción ilegal de hidrocarburo en Tlaxcoapan.</t>
-  </si>
-  <si>
-    <t>Segobh, SSPH, PGJEH</t>
-  </si>
-  <si>
-    <t>Aumentan a 23 los casos de gusano barrenador en el ganado hidalguense</t>
-  </si>
-  <si>
-    <t>La Secretaría de Agricultura y Desarrollo Rural confirmó la detección de 23 casos activos de infestación por gusano barrenador en ganado bovino de la entidad, manteniendo controles sanitarios estrictos.</t>
-  </si>
-  <si>
-    <t>Gusano barrenador</t>
-  </si>
-  <si>
-    <t>La Saderh confirmó el incremento a 23 casos detectados de gusano barrenador en ganado bovino en diversos municipios hidalguenses.</t>
-  </si>
-  <si>
-    <t>Reportan saldo blanco en el inicio de la Feria San Francisco Pachuca 2026</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo informó saldo blanco durante la jornada inaugural del recinto ferial tras implementar un riguroso dispositivo de vigilancia interinstitucional.</t>
-  </si>
-  <si>
-    <t>La SSPH reportó saldo blanco tras la implementación de operativos de vigilancia en el arranque de la Feria de Pachuca.</t>
-  </si>
-  <si>
-    <t>Investigan desvío de recursos en administración municipal anterior de Tula</t>
-  </si>
-  <si>
-    <t>La Contraloría indaga un presunto desvío de recursos financieros cometido durante la gestión municipal anterior en Tula.</t>
-  </si>
-  <si>
-    <t>Tula</t>
-  </si>
-  <si>
-    <t>Desvío de recursos</t>
-  </si>
-  <si>
-    <t>Joselyn Sánchez</t>
-  </si>
-  <si>
-    <t>Plantean reforestación masiva en zonas afectadas por sequía en la Huasteca</t>
-  </si>
-  <si>
-    <t>Ambientalistas y dependencias promueven plan de reforestación masiva en la Huasteca hidalguense para mitigar la sequía.</t>
-  </si>
-  <si>
-    <t>Protección ambiental</t>
-  </si>
-  <si>
-    <t>Productores de café en Otomí-Tepehua prevén buena cosecha pese a lluvias</t>
-  </si>
-  <si>
-    <t>Cafeticultores de la región Otomí-Tepehua estiman buen rendimiento en la cosecha del ciclo actual.</t>
-  </si>
-  <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>Presentan exposición fotográfica sobre la historia de Pachuca</t>
-  </si>
-  <si>
-    <t>Inauguraron galería fotográfica que reúne imágenes históricas sobre la evolución urbana de la capital hidalguense.</t>
-  </si>
-  <si>
-    <t>Desmantelan toma clandestina de hidrocarburo en Cuautepec</t>
-  </si>
-  <si>
-    <t>Elementos estatales y federales inhabilitaron una toma clandestina en un ducto de Pemex ubicado en Cuautepec.</t>
-  </si>
-  <si>
-    <t>Cuautepec</t>
-  </si>
-  <si>
     <t>Combate Al Huachicol</t>
   </si>
   <si>
-    <t>Investigan presunto desvío de recursos en la administración anterior de Tula</t>
-  </si>
-  <si>
-    <t>La Secretaría de la Contraloría abrió expedientes de investigación para esclarecer posibles inconsistencias y desvío de fondos públicos detectados en las arcas del gobierno municipal previo de Tula de Allende.</t>
-  </si>
-  <si>
-    <t>Contraloría del estado inició auditorías e investigaciones por presuntas irregularidades financieras en la gestión previa de Tula.</t>
-  </si>
-  <si>
-    <t>Contraloría, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Plantean programa de reforestación masiva en la Huasteca hidalguense</t>
-  </si>
-  <si>
-    <t>Autoridades de Medio Ambiente y Medio Rural impulsan la siembra masiva de árboles en municipios de la Huasteca para recuperar áreas afectadas por la deforestación y frenar los efectos de la sequía prolongada.</t>
-  </si>
-  <si>
-    <t>Semarnath planteó un esquema de reforestación masiva para contrarrestar la sequía y erosión en la Huasteca.</t>
-  </si>
-  <si>
-    <t>Productores de café de la región Otomí-Tepehua prevén buena producción</t>
-  </si>
-  <si>
-    <t>Agricultores de café en la zona serrana manifestaron expectativas favorables de cosecha para el ciclo actual, beneficiados por las lluvias recientes en los municipios de la región Otomí-Tepehua.</t>
-  </si>
-  <si>
-    <t>Cafetaleros de la región Otomí-Tepehua estiman incremento en el rendimiento de sus cultivos beneficiados por las lluvias.</t>
-  </si>
-  <si>
-    <t>Desmantelan toma clandestina de combustible en municipio de Cuautepec</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad aseguraron una excavación e inhabilitaron una toma clandestina conectada a poliductos de Pemex en la zona rural de Cuautepec de Hinojosa, recuperando contenedores con gasolina.</t>
-  </si>
-  <si>
-    <t>Autoridades estatales inhabilitaron una toma clandestina conectada a ductos e incautaron contenedores con combustible en Cuautepec.</t>
-  </si>
-  <si>
     <t>SSPH, PGJEH</t>
   </si>
   <si>
-    <t>Sentencian a cinco por secuestro; les dan hasta 87 años</t>
-  </si>
-  <si>
-    <t>Un Tribunal de Enjuiciamiento dictó condenas de hasta 87 años de prisión contra cinco personas por secuestro agravado cometido en Zapotlán de Juárez.</t>
-  </si>
-  <si>
-    <t>Zapotlán</t>
-  </si>
-  <si>
-    <t>Investigaciones de la UECS permitieron obtener sentencias condenatorias de hasta 87 años contra cinco secuestradores en Zapotlán.</t>
-  </si>
-  <si>
     <t>Alejandro Reyes</t>
   </si>
   <si>
-    <t>Hallan en Pachuca 20 mil 900 litros de combustible</t>
-  </si>
-  <si>
-    <t>Agentes de la SSPH y la PGJEH aseguraron 20 mil 900 litros de hidrocarburo ilícito en un inmueble de Santiago Tlapacoya, Pachuca.</t>
-  </si>
-  <si>
-    <t>Cateo coordinado en Santiago Tlapacoya culminó con el decomiso de casi 21 mil litros de combustible y contenedores de alta presión.</t>
-  </si>
-  <si>
-    <t>SSPH, PGJEH, Sedena</t>
-  </si>
-  <si>
-    <t>Carpetas por privación ilegal de libertad supera 500 en 8 meses</t>
-  </si>
-  <si>
-    <t>Hidalgo registró 537 carpetas de investigación por el delito de privación ilegal de la libertad entre enero y agosto de 2026 según el SESNSP.</t>
-  </si>
-  <si>
-    <t>Cifras del Secretariado Ejecutivo revelan más de 500 denuncias por privación de la libertad en Hidalgo durante los primeros ocho meses del año.</t>
-  </si>
-  <si>
-    <t>Localizan cadáver en Tezontepec; van dos en una semana</t>
-  </si>
-  <si>
-    <t>El cuerpo de un hombre fue hallado en el canal de aguas negras de Viejo Requena en Tezontepec de Aldama, sumando dos hallazgos similares.</t>
-  </si>
-  <si>
-    <t>Tezontepec de Aldama</t>
-  </si>
-  <si>
-    <t>Localización de cuerpo</t>
-  </si>
-  <si>
-    <t>Cuerpos de seguridad y rescate rescataron el cadáver de un hombre no identificado en aguas negras de Tezontepec de Aldama.</t>
-  </si>
-  <si>
-    <t>PGJEH, Bomberos</t>
-  </si>
-  <si>
-    <t>Prevén reducir el tráfico con trenes y obras viales</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca destacó avances en la edificación del tren AIFA-Pachuca y proyectos de conectividad vial para agilizar la movilidad.</t>
-  </si>
-  <si>
     <t>Proyectos Ferroviarios</t>
   </si>
   <si>
-    <t>Obras del tren México-Pachuca registran 45% de avance, proyectando conclusión de trabajos principales hacia 2027.</t>
-  </si>
-  <si>
-    <t>Gobernador, Presidencia</t>
-  </si>
-  <si>
-    <t>Mexicana e Hidalgo refuerzan conexión</t>
-  </si>
-  <si>
-    <t>La llegada de aeronaves Embraer 190 a Mexicana de Aviación potenciará la conectividad aérea de Hidalgo a través del AIFA.</t>
-  </si>
-  <si>
-    <t>Aeropuerto</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo estatal resalta que la expansión de Mexicana de Aviación impulsará la afluencia turística e industrial hidalguense.</t>
-  </si>
-  <si>
-    <t>Turismo, Presidencia</t>
-  </si>
-  <si>
     <t>Elizabeth Quintanar Gómez</t>
   </si>
   <si>
-    <t>Taxistas se pronuncian por banderazo de 50 pesos</t>
-  </si>
-  <si>
-    <t>Operadores de taxi de Pachuca y Mineral de la Reforma se manifestaron en contra de las tarifas ajustadas y pidieron una tarifa mínima de 50 pesos.</t>
-  </si>
-  <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Taxistas metropolitanos argumentan incrementos en insumos y gasolina para solicitar que la tarifa base suba de 45 a 50 pesos.</t>
-  </si>
-  <si>
-    <t>Amplían opciones de educación superior</t>
-  </si>
-  <si>
-    <t>El PIBEH y la Universidad CNCI firmaron un convenio para permitir que agentes policiacos y sus familias cursen licenciaturas y maestrías en línea.</t>
-  </si>
-  <si>
-    <t>Oferta educativa</t>
-  </si>
-  <si>
-    <t>Convenio educativo facilitará la profesionalización universitaria de elementos de la Policía Industrial Bancaria de Hidalgo.</t>
-  </si>
-  <si>
-    <t>SSPH, PIBEH, SEPH</t>
-  </si>
-  <si>
-    <t>Francisco Martínez Gómez, Benjamín Arcos Hughes</t>
-  </si>
-  <si>
-    <t>Investigan cómo hacer más resistente el cultivo de maíz</t>
-  </si>
-  <si>
-    <t>El ITESHU y el CIMMYT desarrollan ensayos en Huichapan para probar maíz nativo y de conservación resistente a sequías y heladas.</t>
-  </si>
-  <si>
-    <t>Huichapan</t>
-  </si>
-  <si>
-    <t>Investigación académica</t>
-  </si>
-  <si>
-    <t>Investigadores del Tecnológico de Huichapan colaboran con el CIMMYT para optimizar la productividad agrícola frente al cambio climático.</t>
-  </si>
-  <si>
-    <t>SEPH, ITESHU, Saderh</t>
-  </si>
-  <si>
-    <t>Raúl Olvera García</t>
-  </si>
-  <si>
-    <t>Gobernador entrega obras de pavimentación e infraestructura hidráulica en Pachuca</t>
-  </si>
-  <si>
-    <t>El gobernador entregó obras de pavimentación y red hidráulica para mejorar la movilidad y servicios en colonias de Pachuca.</t>
-  </si>
-  <si>
-    <t>Obras De Infraestructura</t>
-  </si>
-  <si>
-    <t>Vinculan a proceso a tres personas por narcomenudeo en Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>La PGJEH obtuvo la vinculación a proceso de tres presuntos distribuidores de droga detenidos en cateo.</t>
-  </si>
-  <si>
     <t>Combate Al Narcomenudeo</t>
   </si>
   <si>
-    <t>Anuncian programa cultural de las festividades del Xantolo en la Huasteca</t>
-  </si>
-  <si>
-    <t>Presentaron la agenda de actividades culturales y de la tradición del Xantolo 2026 en municipios huastecos.</t>
-  </si>
-  <si>
-    <t>Recuperan dos vehículos con reporte de robo mediante arcos carreteros</t>
-  </si>
-  <si>
-    <t>Sistemas de videovigilancia y arcos carreteros permitieron la localización y recuperación de dos autos robados.</t>
-  </si>
-  <si>
-    <t>Videovigilancia</t>
-  </si>
-  <si>
-    <t>Entregan obras de pavimentación e infraestructura hidráulica en Pachuca</t>
-  </si>
-  <si>
-    <t>El Poder Ejecutivo estatal inauguró obras de pavimentación con concreto hidráulico y renovación de drenaje pluvial en colonias de Pachuca para mitigar los problemas recurrentes de encharcamientos e inundaciones.</t>
-  </si>
-  <si>
-    <t>El Gobernador entregó obras de pavimentación e infraestructura hidráulica para mitigar inundaciones en colonias de Pachuca.</t>
-  </si>
-  <si>
-    <t>Gobernador, Sipdus</t>
-  </si>
-  <si>
-    <t>Vinculan a proceso a tres probables responsables de narcomenudeo</t>
-  </si>
-  <si>
-    <t>La Procuraduría General de Justicia del Estado de Hidalgo logró la vinculación a proceso de tres personas detenidas en posesión de narcóticos durante operativos realizados en Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>PGJEH obtuvo la vinculación a proceso de tres imputados por delitos contra la salud en Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>PGJEH, SSPH</t>
-  </si>
-  <si>
-    <t>Presentan el programa cultural y festividades del Xantolo 2026 en la Huasteca</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura del gobierno estatal presentó la agenda artística, cuadrillas de disfrazados e itinerario gastronómico para la celebración de las fiestas tradicionales del Xantolo 2026 en Huejutla.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura dio a conocer el programa oficial y actividades artísticas para el Xantolo 2026 en la Huasteca.</t>
-  </si>
-  <si>
-    <t>Cultura, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Taxistas de Pachuca piden tarifa mínima de 50 pesos</t>
-  </si>
-  <si>
-    <t>Un grupo de taxistas independientes de Pachuca solicitaron que la tarifa mínima del servicio sea de 50 pesos, en lugar de los 45 pesos establecidos por la Semot, al considerar el tráfico y costos operativos.</t>
-  </si>
-  <si>
-    <t>Conductores independientes de taxi en Pachuca pidieron valorar distancias y tiempos de recorrido para fijar un cobro mínimo de 50 pesos frente al nuevo tarifario estatal.</t>
-  </si>
-  <si>
-    <t>Semarnath acopiará baterías en la Unidad Deportiva de Pachuca</t>
-  </si>
-  <si>
-    <t>La Semarnath realizará el próximo viernes 2 de octubre una jornada de acopio de pilas usadas y reforestación en la Unidad Deportiva Municipal de Pachuca.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Medio Ambiente estatal recolectará baterías en desuso y promoverá la plantación de árboles en la Unidad Deportiva de Pachuca el 2 de octubre.</t>
-  </si>
-  <si>
-    <t>Semarnath, Gobernador</t>
-  </si>
-  <si>
-    <t>Mónica Patricia Mixtega Trejo, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Acercan servicios de salud a 9 municipios</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo informó que las brigadas médicas han acercado más de 28 mil 200 acciones de salud gratuitas en nueve municipios de la entidad.</t>
-  </si>
-  <si>
-    <t>Acaxochitlán</t>
-  </si>
-  <si>
-    <t>Jornada de salud</t>
-  </si>
-  <si>
-    <t>La SSH desplegó jornadas médicas itinerantes en nueve municipios hidalguenses, ofreciendo consultas de especialidad, pruebas diagnósticas y apoyos funcionales.</t>
-  </si>
-  <si>
-    <t>Vanesa Escalante</t>
-  </si>
-  <si>
-    <t>Aumentan lesiones y corrupción de menores contra mujeres en Hidalgo</t>
-  </si>
-  <si>
-    <t>En ocho meses, en Hidalgo incrementó la incidencia en los delitos de lesiones dolosas, culposas y corrupción de menores contra mujeres, reveló el reporte mensual del SESNSP.</t>
-  </si>
-  <si>
-    <t>Cifras del SESNSP ubican a Hidalgo entre los estados con mayor repunte en lesiones y corrupción de menores contra mujeres de enero a agosto de 2026.</t>
-  </si>
-  <si>
-    <t>Inició construcción de una planta de Hi-Ref, en Villa de Tezontepec</t>
-  </si>
-  <si>
-    <t>Sedeco encabezó la colocación de la primera piedra de la planta italiana Hi-Ref en Villa de Tezontepec, con una inversión de 200 millones de pesos y 320 empleos.</t>
-  </si>
-  <si>
-    <t>Villa de Tezontepec</t>
-  </si>
-  <si>
-    <t>Atracción De Inversiones</t>
-  </si>
-  <si>
-    <t>Inició la edificación de la primera planta de la empresa Hi-Ref en México, especializada en climatización de centros de datos en Villa de Tezontepec.</t>
-  </si>
-  <si>
-    <t>Carlos Henkel Escorza</t>
-  </si>
-  <si>
-    <t>En Atracciones Grupo García, "Me late subirme a los juegos"</t>
-  </si>
-  <si>
-    <t>Atracciones Grupo García llega a la Feria San Francisco Pachuca 2026 con más de 20 atracciones mecánicas, tarjetas con saldo extra y acceso gratuito para personas con discapacidad.</t>
-  </si>
-  <si>
-    <t>Grupo García ofrece promociones e instalaciones accesibles para personas con discapacidad durante la Feria San Francisco Pachuca 2026.</t>
-  </si>
-  <si>
-    <t>Incautaron 20 mil litros de hidrocarburo</t>
-  </si>
-  <si>
-    <t>La SSPH desmanteló un predio utilizado para almacenar combustible ilegal en la localidad Santiago Tlapacoya de Pachuca, hallando 20 mil 900 litros de hidrocarburo.</t>
-  </si>
-  <si>
-    <t>Operativo coordinado entre SSPH, PGJEH y Sedena permitió el aseguramiento de más de 20 mil litros de huachicol y contenedores en Santiago Tlapacoya.</t>
-  </si>
-  <si>
-    <t>PIBEH firmó un convenio para dar educación a elementos</t>
-  </si>
-  <si>
-    <t>La Policía Industrial Bancaria del Estado de Hidalgo firmó un convenio de colaboración con la Universidad CNCI para ofrecer licenciaturas y maestrías en línea a sus elementos.</t>
-  </si>
-  <si>
-    <t>La PIBEH y la Universidad CNCI acordaron esquemas de profesionalización académica en línea para el personal policial y sus familias.</t>
-  </si>
-  <si>
-    <t>SSPH, Gobernador</t>
-  </si>
-  <si>
-    <t>Francisco Martínez Gómez, Benjamín Arcos Hughes, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Rectores de Hidalgo, entre la academia y la función pública</t>
-  </si>
-  <si>
-    <t>Análisis sobre el perfil profesional de los rectores de instituciones de educación superior en Hidalgo, quienes se dividen entre trayectorias académicas y cargos públicos.</t>
-  </si>
-  <si>
-    <t>Perfil académico</t>
-  </si>
-  <si>
-    <t>Reportaje que analiza las trayectorias de los rectores de las universidades e institutos politécnicos de la entidad.</t>
-  </si>
-  <si>
     <t>Carmen Hernández</t>
   </si>
   <si>
-    <t>Brenda Flores, Pablo Elías Vargas González</t>
-  </si>
-  <si>
-    <t>Taxistas piden que banderazo sea de 50 pesos</t>
-  </si>
-  <si>
-    <t>Choferes de taxi en Pachuca manifiestan su inconformidad con la tarifa fijada por la Semot y solicitan que el banderazo inicial sea de 50 pesos debido al tráfico y costos.</t>
-  </si>
-  <si>
-    <t>Operadores de taxi solicitan un ajuste al banderazo tarifario a 50 pesos para compensar tiempos perdidos en el tráfico y gastos de operación.</t>
-  </si>
-  <si>
-    <t>En ocho meses, 461 asaltos en Pachuca</t>
-  </si>
-  <si>
-    <t>Entre enero y agosto de 2026, Pachuca acumuló 461 asaltos en negocios, transporte público y transeúntes, promediando casi dos casos diarios según el SESNSP.</t>
-  </si>
-  <si>
-    <t>Cifras del SESNSP revelan 461 asaltos en Pachuca en los primeros ocho meses del año, siendo los comercios los más afectados con 290 denuncias.</t>
-  </si>
-  <si>
-    <t>Luis Godínez</t>
-  </si>
-  <si>
-    <t>PGJEH, Presidencia, SESNSP</t>
-  </si>
-  <si>
-    <t>La violación a la intimidad sexual subió 32 por ciento</t>
-  </si>
-  <si>
-    <t>Las denuncias por violación a la intimidad sexual en Hidalgo incrementaron un 32% durante agosto, acumulando 33 carpetas de investigación ante la PGJEH.</t>
-  </si>
-  <si>
-    <t>Violencia digital</t>
-  </si>
-  <si>
-    <t>Las denuncias por delitos contra la intimidad sexual crecieron 32 por ciento en agosto en Hidalgo, encabezando Pachuca las querellas.</t>
-  </si>
-  <si>
     <t>PGJEH, SESNSP</t>
   </si>
   <si>
-    <t>Dicen no a incremento en taxis de Atotonilco</t>
-  </si>
-  <si>
-    <t>Taxistas de Atotonilco el Grande señalaron la dificultad de socializar y aplicar el aumento del 20% a la tarifa del pasaje entre la población local.</t>
-  </si>
-  <si>
-    <t>Atotonilco el Grande</t>
-  </si>
-  <si>
-    <t>Operadores de taxi de Atotonilco expresan complicaciones para aplicar la nueva tarifa autorizada por el rechazo de los usuarios.</t>
-  </si>
-  <si>
     <t>Martha Sáenz</t>
   </si>
   <si>
-    <t>Demanda colectivo revisar el caso de Martínez Cervantes</t>
-  </si>
-  <si>
-    <t>Integrantes del Movimiento No al Basurero exigieron durante el desfile de Atitalaquia revisar la situación jurídica del activista Óscar Martínez.</t>
-  </si>
-  <si>
-    <t>Derechos humanos</t>
-  </si>
-  <si>
-    <t>Manifestantes solicitaron respeto al debido proceso y presunción de inocencia para el activista Óscar Martínez Cervantes detenido recientemente.</t>
-  </si>
-  <si>
-    <t>Magda Olguín</t>
-  </si>
-  <si>
-    <t>Segobh, PGJEH</t>
-  </si>
-  <si>
-    <t>Óscar Martínez Cervantes, Rodrigo Ángeles</t>
-  </si>
-  <si>
-    <t>Taxistas piden nuevo aumento; usuarios exigen que se respeten las tarifas</t>
-  </si>
-  <si>
-    <t>A menos de una semana de que entrara en vigor la actualización de tarifas del transporte público individual en la zona metropolitana de Pachuca, chóferes de taxi solicitaron elevar el cobro mínimo de 45 a 50 pesos, argumentando congestionamiento vial y cuotas elevadas de concesionarios, mientras que usuarios exigen que se respeten los precios oficiales y la Semoth advirtió sanciones.</t>
-  </si>
-  <si>
     <t>Reportaje</t>
   </si>
   <si>
-    <t>Taxistas de Pachuca solicitan elevar la tarifa mínima a 50 pesos mientras usuarios demandan respeto al tarifario oficial de 45 pesos y Semoth mantiene operativos de vigilancia.</t>
-  </si>
-  <si>
-    <t>Semot, STCH, Gobernador</t>
-  </si>
-  <si>
-    <t>SSH lleva Brigadas Médicas a Acaxochitlán</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo implementó jornadas de atención médica en Acaxochitlán, sumando nueve municipios beneficiados y más de 28 mil 200 acciones de medicina general, pediatría, ginecología y odontología.</t>
-  </si>
-  <si>
-    <t>Jornada médica</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo despliega brigadas médicas en Acaxochitlán para la detección oportuna de padecimientos.</t>
-  </si>
-  <si>
-    <t>SSH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Incautan 20 mil 900 litros de combustible</t>
-  </si>
-  <si>
-    <t>La SSPH en coordinación con la PGJEH y Sedena ejecutó una orden de cateo en Santiago Tlapacoya, Pachuca, donde aseguró 20,900 litros de hidrocarburo robado, 32 contenedores de mil litros y 200 metros de manguera.</t>
-  </si>
-  <si>
-    <t>Operativo conjunto de la SSPH y PGJEH en Santiago Tlapacoya logra el aseguramiento de casi 21 mil litros de huachicol.</t>
-  </si>
-  <si>
-    <t>Hallan cadáver en canal de aguas negras y en fiesta hieren a uno</t>
-  </si>
-  <si>
-    <t>Autoridades hallaron el cadáver de un hombre flotando en las aguas del canal San Gabriel en Tezontepec de Aldama, mientras que en Tlaxcoapan un sujeto resultó gravemente herido de bala durante una fiesta infantil.</t>
-  </si>
-  <si>
-    <t>Jornada violenta en la región de Tula deja el hallazgo de un cuerpo en canal de aguas negras y un baleado en Tlaxcoapan.</t>
-  </si>
-  <si>
-    <t>Hidalgo gana otras 2 medallas</t>
-  </si>
-  <si>
-    <t>Atletas hidalguenses conquistaron oro y plata en paranatación durante la Paralimpiada Nacional 2026 gracias a las actuaciones de Emiliano Pérez López y Melani Yamileth Ávila Trujillo.</t>
-  </si>
-  <si>
-    <t>Paranacionales Conade</t>
-  </si>
-  <si>
-    <t>Delegación de Hidalgo suma medallas de oro y plata en paranatación durante la Paralimpiada Nacional 2026.</t>
-  </si>
-  <si>
-    <t>SEPH, Inhide</t>
-  </si>
-  <si>
-    <t>Emiliano Pérez López, Melani Yamileth Ávila Trujillo, Oscar Pérez</t>
-  </si>
-  <si>
-    <t>Vuelca unidad operativa del Tuzobús</t>
-  </si>
-  <si>
-    <t>Una camioneta asignada a la Unidad de Vigilancia Operativa del Sistema de Transporte Metropolitano protagonizó un percance sobre el bulevar Felipe Ángeles, a la altura de la estación Vicente Segura. El vehículo terminó volcado sobre el camellón tras salir de su trayectoria por una supuesta falla mecánica. Los dos ocupantes resultaron ilesos.</t>
-  </si>
-  <si>
-    <t>Accidente de vehículo oficial</t>
-  </si>
-  <si>
-    <t>Una camioneta de la Unidad de Vigilancia Operativa del Tuzobús volcó en el bulevar Felipe Ángeles por una falla mecánica, sin dejar personas lesionadas.</t>
-  </si>
-  <si>
-    <t>Semot, Sitmah</t>
-  </si>
-  <si>
-    <t>Supervisarán a diario juegos mecánicos en la Feria de Pachuca</t>
-  </si>
-  <si>
-    <t>Los 40 juegos mecánicos instalados en la Feria San Francisco Pachuca Hidalgo 2026 deberán contar con un dictamen favorable de Protección Civil y serán inspeccionados diariamente antes de recibir visitantes, como parte de las medidas preventivas para reducir riesgos durante los 25 días de actividades.</t>
-  </si>
-  <si>
-    <t>Protección Civil realizará inspecciones diarias a los 40 juegos mecánicos de la Feria de Pachuca para garantizar la seguridad de los asistentes.</t>
-  </si>
-  <si>
-    <t>Segobh, PC, Turismo</t>
-  </si>
-  <si>
-    <t>Román Bernal Díaz</t>
-  </si>
-  <si>
-    <t>Firma italiana arranca construcción de planta en Hidalgo</t>
-  </si>
-  <si>
-    <t>La empresa italiana Hi-Ref S.p.A. inició la construcción de su nueva planta en Villa de Tezontepec, proyecto que representa su primera instalación productiva en México y fuera de Italia, con una inversión de 200 millones de pesos y la generación de 320 empleos directos e indirectos para fabricar sistemas de climatización de precisión.</t>
-  </si>
-  <si>
-    <t>Hi-Ref S.p.A. colocó la primera piedra de su planta en Villa de Tezontepec con una inversión de 200 mdp para la producción de sistemas de refrigeración de centros de datos.</t>
-  </si>
-  <si>
-    <t>Carlos Henkel Escorza, Julio Menchaca Salazar, Alberto Salmistraro, Fabio Poletto, Alejandra Castellanos García, Lorenzo Vianello</t>
-  </si>
-  <si>
-    <t>Trabajadores del volante exigen modificar tarifas</t>
-  </si>
-  <si>
-    <t>Taxistas independientes de Pachuca y Mineral de la Reforma pidieron participar en la definición de las tarifas de transporte y propusieron establecer un cobro mínimo de 50 pesos. Cuestionaron que la Semoth tomara decisiones sin consultar al gremio.</t>
-  </si>
-  <si>
-    <t>Taxistas independientes de la zona metropolitana de Pachuca solicitaron ser consultados para fijar el tarifario de transporte y plantearon un cobro mínimo de 50 pesos.</t>
-  </si>
-  <si>
-    <t>Leonardo Cruz</t>
-  </si>
-  <si>
-    <t>Descarta el Secretario de Gobierno conflicto religioso en Huasteca</t>
-  </si>
-  <si>
-    <t>El secretario de Gobierno de Hidalgo, Guillermo Olivares Reyna, descartó que exista un conflicto religioso en la Huasteca tras el asesinato del sacerdote Román de la Cruz Hernández en Lolotla, e informó que la PGJEH mantiene estrecha comunicación con la Diócesis de Huejutla para esclarecer el crimen.</t>
-  </si>
-  <si>
-    <t>Lolotla</t>
-  </si>
-  <si>
-    <t>Exigen esclarecer homicidio</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna rechazó tensiones religiosas en la Huasteca tras el homicidio del párroco Román de la Cruz y afirmó avances en la investigación de la PGJEH.</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna, Román de la Cruz Hernández</t>
-  </si>
-  <si>
-    <t>La escuela primaria Aquiles Serdán de Tulancingo presenta fallas estructurales graves por lo que será demolida y reconstruida totalmente durante el ciclo escolar 2026-2027. El titular de la SEPH, Natividad Castrejón, indicó que se buscan opciones temporales para impartir clases presenciales o virtuales.</t>
-  </si>
-  <si>
-    <t>La SEPH demolerá y reconstruirá la primaria Aquiles Serdán en Tulancingo por daños en su infraestructura, evaluando la reubicación temporal del alumnado.</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón</t>
+    <t>Destacan récord de empleo y ruta hacia las 40 horas</t>
+  </si>
+  <si>
+    <t>El secretario del Trabajo reportó 60.7 millones de personas ocupadas en agosto y una recuperación del salario mínimo real del 154%, avanzando hacia la reducción gradual de la jornada laboral.</t>
+  </si>
+  <si>
+    <t>CDMX</t>
+  </si>
+  <si>
+    <t>Periódico impreso</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Ley 40 horas</t>
+  </si>
+  <si>
+    <t>La STPS informó sobre la cifra récord de empleos y el esquema gradual para disminuir la jornada de trabajo de 48 a 40 horas.</t>
+  </si>
+  <si>
+    <t>Mauricio Bautista</t>
+  </si>
+  <si>
+    <t>STPSH</t>
+  </si>
+  <si>
+    <t>Presidencia de la República</t>
+  </si>
+  <si>
+    <t>Marath Bolaños</t>
+  </si>
+  <si>
+    <t>Gobierno renovará la nave antigua del pabellón artesanal</t>
+  </si>
+  <si>
+    <t>La Sebiso proyecta para 2027 la modernización de la nave vieja del pabellón artesanal en la Feria Pachuca con una inversión estimada menor a 6 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Sebiso anunció la remodelación integral del pabellón artesanal antiguo de la Feria de Pachuca para corregir fallas eléctricas y de infraestructura.</t>
+  </si>
+  <si>
+    <t>Fonart, OEEH</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Baja tarifa de estacionamiento en la Feria de San Francisco</t>
+  </si>
+  <si>
+    <t>La OEEH informó la reducción del costo de estacionamiento de 150 a 120 pesos en el recinto ferial tras peticiones ciudadanas; reportan 55 mil visitantes con saldo blanco.</t>
+  </si>
+  <si>
+    <t>La concesionaria del estacionamiento de la Feria de Pachuca ajustó su tarifa a 120 pesos, registrando gran afluencia en atracciones.</t>
+  </si>
+  <si>
+    <t>SSPH, Protección Civil, Cruz Roja</t>
+  </si>
+  <si>
+    <t>Marco Antonio Aranzábal Juárez</t>
+  </si>
+  <si>
+    <t>Hidalgo es cuarto lugar nacional en filmaciones</t>
+  </si>
+  <si>
+    <t>Hidalgo acumuló 101 producciones audiovisuales filmadas en su territorio sin otorgar incentivos económicos, impulsando el turismo de pantalla y la economía local.</t>
+  </si>
+  <si>
+    <t>Producción audiovisual</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo destacó la atracción de 101 proyectos cinematográficos y de televisión en el estado gracias a facilidades logísticas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública</t>
+  </si>
+  <si>
+    <t>El Sol de Hidalgo</t>
+  </si>
+  <si>
+    <t>Apuesta Menchaca por coordinación interestatal</t>
+  </si>
+  <si>
+    <t>Durante la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad, el gobernador Julio Menchaca refrendó el compromiso de Hidalgo para fortalecer el trabajo conjunto con la Federación, estados vecinos y municipios para garantizar la seguridad.</t>
+  </si>
+  <si>
+    <t>Coordinación interestatal</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca refrendó el compromiso de Hidalgo para fortalecer la coordinación con la Federación y estados vecinos en materia de seguridad.</t>
+  </si>
+  <si>
+    <t>Nota principal</t>
+  </si>
+  <si>
+    <t>Blanca Soriano</t>
+  </si>
+  <si>
+    <t>Gobierno</t>
+  </si>
+  <si>
+    <t>Gobierno, Presidencia, SSPH</t>
+  </si>
+  <si>
+    <t>Exponen talento artesanal</t>
+  </si>
+  <si>
+    <t>Artesanas de Tenango de Doria y Chilcuautla participan en el Pabellón Artesanal de la Feria San Francisco Pachuca 2026 para exhibir y comercializar sus bordados y productos tradicionales.</t>
+  </si>
+  <si>
+    <t>Apoyo a artesanos</t>
+  </si>
+  <si>
+    <t>Artesanas hidalguenses exhiben y comercializan sus creaciones en el Pabellón Artesanal de la Feria San Francisco Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>DIFH</t>
+  </si>
+  <si>
+    <t>DIFH, Turismo</t>
+  </si>
+  <si>
+    <t>Angélica María Benito, Romana San Pedro</t>
+  </si>
+  <si>
+    <t>Estacionamiento en feria baja su precio</t>
+  </si>
+  <si>
+    <t>Atendiendo sugerencias del público, la empresa concesionaria del estacionamiento de la Feria Pachuca 2026 redujo el costo de cobro por vehículo de 150 a 120 pesos.</t>
+  </si>
+  <si>
+    <t>Tarifario Feria Pachuca</t>
+  </si>
+  <si>
+    <t>La tarifa del estacionamiento de la Feria San Francisco Pachuca disminuyó de 150 a 120 pesos tras atender solicitudes de los usuarios.</t>
+  </si>
+  <si>
+    <t>OEEH, Turismo</t>
+  </si>
+  <si>
+    <t>Pide Protección Civil ubicar salidas</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil emitió recomendaciones preventivas para los asistentes a la Feria Pachuca 2026, destacando la importancia de ubicar salidas de emergencia.</t>
+  </si>
+  <si>
+    <t>Prevención De Riesgos</t>
+  </si>
+  <si>
+    <t>Protección Civil de Hidalgo emitió una serie de recomendaciones para garantizar la seguridad de las familias en la Feria Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>Gustavo Vargas</t>
+  </si>
+  <si>
+    <t>Segobh, PC</t>
+  </si>
+  <si>
+    <t>Huasca: 25 años como Pueblo Mágico</t>
+  </si>
+  <si>
+    <t>Huasca de Ocampo conmemorará un cuarto de siglo de haber sido distinguido como el primer Pueblo Mágico de México con un programa de eventos culturales y gastronómicos.</t>
+  </si>
+  <si>
+    <t>Huasca</t>
+  </si>
+  <si>
+    <t>Pueblos Mágicos</t>
+  </si>
+  <si>
+    <t>El municipio de Huasca festejara 25 años de su acreditación como el primer Pueblo Mágico del país.</t>
+  </si>
+  <si>
+    <t>Obras de trenes extienden oportunidades económicas</t>
+  </si>
+  <si>
+    <t>El titular de la Uplaph destacó que la infraestructura ferroviaria impulsará el desarrollo regional, enfatizando la importancia de un crecimiento urbano ordenado.</t>
+  </si>
+  <si>
+    <t>Planeación estatal resalta la oportunidad de detonar polos de desarrollo mediante las obras de interconexión ferroviaria.</t>
+  </si>
+  <si>
+    <t>Planeación, Uplaph</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas</t>
+  </si>
+  <si>
+    <t>Buscan a jóvenes en Tlanchinol</t>
+  </si>
+  <si>
+    <t>La PGJEH difundió alertas institucionales para dar con el paradero de dos menores de 15 años vistos por última vez en el municipio de Tlanchinol.</t>
+  </si>
+  <si>
+    <t>Tlanchinol</t>
+  </si>
+  <si>
+    <t>Desapariciones</t>
+  </si>
+  <si>
+    <t>Autoridades solicitaron colaboración social para la pronta localización de dos adolescentes en Tlanchinol.</t>
+  </si>
+  <si>
+    <t>Rubén Juárez</t>
+  </si>
+  <si>
+    <t>Dulce Gabriela Hernández de la Cruz, Cristian Jovany Hernández Hernández</t>
+  </si>
+  <si>
+    <t>Destrucción de túneles; nueva era del combate al huachicol</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca afirmó que el aseguramiento y destrucción de túneles usados para el robo de combustible representa un hecho histórico en Hidalgo. Entre junio y septiembre de 2026 han sido eliminados 17 túneles en trabajo coordinado con la Sedena y Guardia Nacional.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca destaca la eliminación de 17 túneles huachicoleros en Hidalgo entre junio y septiembre de 2026 como una acción sin precedente.</t>
+  </si>
+  <si>
+    <t>Equipo Milenio</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo, Sedena, Guardia Nacional, Pemex, FGR</t>
+  </si>
+  <si>
+    <t>Vende terreno 9 veces más caro a empresa sancionada</t>
+  </si>
+  <si>
+    <t>La senadora priista Carolina Viggiano Austria compró en 2011 un terreno de 7.16 hectáreas en Zempoala por 2 millones de pesos y lo vendió en 2018 por 17.9 millones a JERGUI, empresa de los hermanos Segura Zerecero sancionada por la Contraloría.</t>
+  </si>
+  <si>
+    <t>Zempoala</t>
+  </si>
+  <si>
+    <t>Investigación por corrupción</t>
+  </si>
+  <si>
+    <t>Documentos revelan que Carolina Viggiano vendió un predio en Zempoala por 17.9 mdp a la empresa JERGUI, que obtuvo contratos estatales y fue sancionada por la Contraloría.</t>
+  </si>
+  <si>
+    <t>Contraloría, PRI</t>
+  </si>
+  <si>
+    <t>Carolina Viggiano Austria, Omar Guillermo Segura Zerecero, Enrique Segura Zerecero, Nidia Segura Zerecero</t>
+  </si>
+  <si>
+    <t>Asisten a la Feria San Francisco más de 55 mil en 4 días</t>
+  </si>
+  <si>
+    <t>Más de 55 mil personas han acudido a la Feria San Francisco Pachuca Hidalgo durante sus primeros cuatro días de actividades. El circo, espectáculo sobre hielo, lucha libre y actividades infantiles concentran la mayor afluencia.</t>
+  </si>
+  <si>
+    <t>La Feria San Francisco Pachuca registra una afluencia superior a los 55 mil visitantes en sus primeros cuatro días con saldo blanco en el palenque y ocupación hotelera del 64%.</t>
+  </si>
+  <si>
+    <t>OEEH</t>
+  </si>
+  <si>
+    <t>OEEH, Turismo, Bienestar</t>
+  </si>
+  <si>
+    <t>Marco Antonio Aranzábal Juárez, Elizabeth Quintanar Gómez, Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Artesanos alcanzan 6 mdp por comercio en el recinto</t>
+  </si>
+  <si>
+    <t>Artesanos que participan en la Feria San Francisco aumentaron sus ventas de menos de 800 mil pesos al inicio de la administración a 6 millones de pesos actualizados. El gobierno estatal invirtió más de 6.5 mdp para remodelar el pabellón artesanal.</t>
+  </si>
+  <si>
+    <t>Ventas de artesanos en la Feria San Francisco se elevan a 6 mdp tras la remodelación del pabellón artesanal con una inversión estatal de 6.5 mdp.</t>
+  </si>
+  <si>
+    <t>Bienestar, OEEH</t>
+  </si>
+  <si>
+    <t>Marco Antonio Aranzábal Juárez, Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Operadora de Eventos dejó cifra roja; ahora devuelve hasta 6 mdp</t>
+  </si>
+  <si>
+    <t>La Operadora de Eventos del Estado de Hidalgo pasó de operar con números rojos y adeudos a devolver más de 6 millones de pesos al cierre de cada año al gobierno estatal gracias a la autosuficiencia y regularización comercial.</t>
+  </si>
+  <si>
+    <t>Finanzas públicas</t>
+  </si>
+  <si>
+    <t>La OEEH se consolidó como un organismo autosuficiente financiero que regresa más de 6 mdp anuales a las arcas del estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>OEEH, Secretaría de Finanzas</t>
+  </si>
+  <si>
+    <t>Violación a intimidad registra 239 carpetas</t>
+  </si>
+  <si>
+    <t>Hidalgo se ubica entre los 12 estados del país con mayor número de carpetas de investigación por violación a la intimidad sexual al acumular 239 denuncias entre enero y agosto de 2026. Pachuca encabeza la lista municipal con 56 carpetas.</t>
+  </si>
+  <si>
+    <t>Violencia De Género</t>
+  </si>
+  <si>
+    <t>Hidalgo acumula 239 carpetas de investigación por violación a la intimidad sexual en 56 municipios de la entidad, liderando Pachuca y Tizayuca.</t>
+  </si>
+  <si>
+    <t>Resaltan coordinación contra los criminales</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca afirmó que el aseguramiento de túneles huachicoleros representa un hecho histórico. Entre junio y septiembre de 2026 se eliminaron 17 túneles en trabajo coordinado con Sedena, Guardia Nacional, Pemex y FGR.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca resalta la estrategia coordinada con fuerzas federales para destruir 17 túneles usados para el robo de combustible a Pemex en Hidalgo.</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo, Sedena, Guardia Nacional, Pemex, FGR, PGJEH, SSPH</t>
+  </si>
+  <si>
+    <t>Huasca, 25 años como el primer Pueblo Mágico</t>
+  </si>
+  <si>
+    <t>Huasca de Ocampo celebrará sus 25 años como el primer Pueblo Mágico de México el próximo 5 de octubre con un programa de actividades culturales, gastronómicas y artesanales junto a los 9 destinos hidalguenses.</t>
+  </si>
+  <si>
+    <t>Huasca de Ocampo</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo anuncia los festejos conmemorativos por el 25 aniversario del nombramiento de Huasca de Ocampo como el primer Pueblo Mágico del país.</t>
+  </si>
+  <si>
+    <t>El estado obtiene presencia nacional con 101 filmaciones</t>
+  </si>
+  <si>
+    <t>Hidalgo se ubica en el cuarto lugar nacional en actividad cinematográfica con 101 proyectos filmados en su territorio, ofreciendo facilidades logísticas, acompañamiento institucional y seguridad a las productoras.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo destaca que Hidalgo se posicionó en cuarto lugar nacional de filmaciones cinematográficas y televisivas con 101 proyectos.</t>
+  </si>
+  <si>
+    <t>Siete muertes maternas en nueve meses</t>
+  </si>
+  <si>
+    <t>Durante los primeros nueve meses de 2026, Hidalgo acumula siete muertes maternas registradas en municipios como Zempoala, Tula, Tasquillo, Pacula, Jaltocán, Acatlán y Tulancingo, superando la cifra de 2025.</t>
+  </si>
+  <si>
+    <t>Salud pública</t>
+  </si>
+  <si>
+    <t>Hidalgo suma siete fallecimientos de mujeres por causas maternas entre enero y septiembre de 2026, según el reporte semanal de la Secretaría de Salud federal.</t>
+  </si>
+  <si>
+    <t>Breve</t>
+  </si>
+  <si>
+    <t>SSH, Salud Federal</t>
+  </si>
+  <si>
+    <t>Acuerdan trabajo coordinado en seguridad</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca participó en la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad junto con autoridades de Edomex, Guerrero, Morelos y CDMX para reforzar la estrategia regional.</t>
+  </si>
+  <si>
+    <t>Gobierno, Segobh, SSPH</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Evelyn Salgado Pineda, Delfina Gómez Álvarez, Margarita González Saravia, Clara Brugada Molina</t>
+  </si>
+  <si>
+    <t>Huasca: un cuarto de siglo como primer Pueblo Mágico</t>
+  </si>
+  <si>
+    <t>El municipio de Huasca de Ocampo celebrará 25 años como el primer Pueblo Mágico de México con un programa de actividades culturales, artesanales y gastronómicas en octubre.</t>
+  </si>
+  <si>
+    <t>Lorena Rosas</t>
+  </si>
+  <si>
+    <t>Turismo, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Elizabeth Quintanar Gómez, Josefina Rodríguez Zamora</t>
+  </si>
+  <si>
+    <t>Baja a 120 pesos estacionamiento de la feria</t>
+  </si>
+  <si>
+    <t>Tras solicitudes de la OEEH ante inconformidades de los asistentes, la empresa concesionaria del estacionamiento de la Feria de Pachuca redujo su tarifa de 150 a 120 pesos.</t>
+  </si>
+  <si>
+    <t>OEEH, PGJEH</t>
+  </si>
+  <si>
+    <t>Rehabilitarán antigua nave de la feria el próximo año: Sebiso</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social proyecta para 2027 una intervención integral en la antigua nave de la Feria de Pachuca para renovar pisos, estructura y sistema eléctrico.</t>
+  </si>
+  <si>
+    <t>Bienestar, Sipdus</t>
+  </si>
+  <si>
+    <t>Buscan 75 enfermeros trabajar en Alemania; hay 30 vacantes abiertas</t>
+  </si>
+  <si>
+    <t>La STPSH coordina la jornada nacional de reclutamiento laboral para enfermeros que buscan laborar en Alemania, registrando 75 aspirantes para 30 plazas disponibles.</t>
+  </si>
+  <si>
+    <t>Movilidad laboral</t>
+  </si>
+  <si>
+    <t>Oscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>Clausuran túnel y cinco tomas clandestinas</t>
+  </si>
+  <si>
+    <t>Operativos del Gabinete de Seguridad de Hidalgo en Atitalaquia, Pachuca y la región Tula-Tepeji permitieron el aseguramiento de un huachitúnel, cinco tomas clandestinas y 20 mil litros de combustible.</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad, Pemex, SSPH</t>
+  </si>
+  <si>
+    <t>Detienen en Argentina a hija de Gerardo Sosa</t>
+  </si>
+  <si>
+    <t>Ana Carmen Sosa Cravioto fue detenida en un aeropuerto de Mendoza, Argentina, en atención a una alerta roja de Interpol relacionada con una investigación de la FGR por lavado de dinero.</t>
+  </si>
+  <si>
+    <t>Gerardo Sosa</t>
+  </si>
+  <si>
+    <t>Víctor Valera</t>
+  </si>
+  <si>
+    <t>FGR, UAEH, Interpol</t>
+  </si>
+  <si>
+    <t>Gerardo Sosa Castelán</t>
+  </si>
+  <si>
+    <t>Fortalecen atención médica con Ecosistema Digital en Salud</t>
+  </si>
+  <si>
+    <t>Los 18 hospitales del IMSS Bienestar en Hidalgo implementaron la plataforma Pheds y el módulo Moce para digitalizar historiales clínicos y agilizar expedientes de pacientes.</t>
+  </si>
+  <si>
+    <t>IMSS Bienestar</t>
+  </si>
+  <si>
+    <t>SSH, IMSS Bienestar</t>
+  </si>
+  <si>
+    <t>Mireya Gutiérrez García</t>
+  </si>
+  <si>
+    <t>Hidalgo suma siete denuncias por aborto en lo que va del año</t>
+  </si>
+  <si>
+    <t>Colectivas feministas exigieron garantizar la no criminalización de las mujeres en Hidalgo tras registrarse siete carpetas de investigación por el delito de aborto en 2026.</t>
+  </si>
+  <si>
+    <t>Aborto</t>
+  </si>
+  <si>
+    <t>PGJEH, SSH</t>
+  </si>
+  <si>
+    <t>Preparan Expo Oliva 2026 este fin de semana, en Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Productores de la comunidad El Olivo en Ixmiquilpan anunciaron la Expo Oliva 2026 con recorridos a huertos, catas de aceite extra virgen y conferencias técnicas.</t>
+  </si>
+  <si>
+    <t>Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Expo Agroalimentaria</t>
+  </si>
+  <si>
+    <t>Erika Gutiérrez</t>
+  </si>
+  <si>
+    <t>Saderh, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Capturan a 2 por posesión de dogas en Actopan</t>
+  </si>
+  <si>
+    <t>Seguridad Pública de Actopan y la Policía estatal aprehendieron a una mujer y un menor de edad a bordo de una motocicleta portando 27 dosis de presunto cristal.</t>
+  </si>
+  <si>
+    <t>Actopan</t>
+  </si>
+  <si>
+    <t>Realizan operativo vs. violencia de género</t>
+  </si>
+  <si>
+    <t>Elementos de seguridad de Tizayuca, Temascalapa y Zumpango implementaron el operativo Violeta Red Segura en limites territoriales para prevenir agresiones en transporte público.</t>
+  </si>
+  <si>
+    <t>Tizayuca</t>
+  </si>
+  <si>
+    <t>Javier Quezada</t>
+  </si>
+  <si>
+    <t>SSPH, Segobh</t>
+  </si>
+  <si>
+    <t>Menchaca destaca combate al huachicol en reunión interestatal de paz y seguridad</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar participó en la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad en Morelos, destacando las acciones para combatir el robo de combustible que afecta a 22 municipios por donde atraviesan más de 900 kilómetros de ductos de Pemex.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca refrendó el compromiso de Hidalgo en la Séptima Reunión Interestatal de Seguridad para combatir el huachicol en los 22 municipios afectados por ductos de Pemex.</t>
+  </si>
+  <si>
+    <t>Veida Miranda</t>
+  </si>
+  <si>
+    <t>Gobierno, Pemex</t>
+  </si>
+  <si>
+    <t>Feria San Francisco supera 55 mil visitantes; baja costo de estacionamiento</t>
+  </si>
+  <si>
+    <t>Tras inconformidades ciudadanas, la tarifa de estacionamiento en la Feria San Francisco Pachuca 2026 bajó de 150 a 120 pesos en tiempo libre. El director de la OEEH reportó más de 55 mil visitantes en los primeros cuatro días y saldo blanco.</t>
+  </si>
+  <si>
+    <t>La OEEH anunció la reducción del costo de estacionamiento en la Feria Pachuca a 120 pesos tras quejas de usuarios; además reportan 55 mil visitantes con saldo blanco.</t>
+  </si>
+  <si>
+    <t>A más de 5 años de la despenalización, persisten barreras para el aborto seguro en Hidalgo</t>
+  </si>
+  <si>
+    <t>Organizaciones civiles advierten que persisten deficiencias en las instituciones públicas que dificultan el acceso efectivo y seguro al aborto en Hidalgo, citando falta de insumos, personal capacitado y estigmas en municipios del norte del estado.</t>
+  </si>
+  <si>
+    <t>A cinco años de la despenalización del aborto en Hidalgo, la organización SEIINAC señala que persisten barreras de salud, falta de insumos y estigmas en municipios del norte.</t>
+  </si>
+  <si>
+    <t>SSH, SEIINAC</t>
+  </si>
+  <si>
+    <t>Lizeth Clavellina</t>
+  </si>
+  <si>
+    <t>Detienen en Argentina a hija de Gerardo Sosa Castelán</t>
+  </si>
+  <si>
+    <t>Ana Carmen Sosa Cravioto, hija de Gerardo Sosa Castelán, fue detenida en el aeropuerto de Mendoza, Argentina, debido a una notificación roja de la Interpol por delincuencia organizada y operaciones con recursos de procedencia ilícita.</t>
+  </si>
+  <si>
+    <t>Autoridades argentinas arrestaron a la hija de Gerardo Sosa Castelán en el aeropuerto de Mendoza por ficha roja de Interpol; seguirá el proceso bajo prisión domiciliaria.</t>
+  </si>
+  <si>
+    <t>UAEH, FGR, Interpol</t>
+  </si>
+  <si>
+    <t>Ana Carmen Sosa Cravioto, Gerardo Sosa Castelán</t>
+  </si>
+  <si>
+    <t>La entidad, entre los estados con más hurtos a taxi, suman 68 casos</t>
+  </si>
+  <si>
+    <t>Hidalgo se ubicó en el séptimo lugar nacional por cantidad de denuncias de robo a transporte público individual durante agosto con cinco carpetas, acumulando 68 querellas en lo que va del año.</t>
+  </si>
+  <si>
+    <t>Robo de taxi</t>
+  </si>
+  <si>
+    <t>Cifras del SESNSP situaron a Hidalgo en el séptimo lugar nacional en robos a taxis con 68 carpetas de investigación acumuladas en 2026.</t>
+  </si>
+  <si>
+    <t>Revisan la elección sindical municipal</t>
+  </si>
+  <si>
+    <t>El Tribunal de Arbitraje analiza la documentación de la elección en el SUTSMP de Pachuca para determinar si otorga la toma de nota a la planilla azul encabezada por Irma María de Jesús López Arroyo.</t>
+  </si>
+  <si>
+    <t>SUTSMP</t>
+  </si>
+  <si>
+    <t>La STPSH informó que el Tribunal de Arbitraje revisa la legalidad del proceso electivo del sindicato de Pachuca previo a otorgar la toma de nota a la planilla ganadora.</t>
+  </si>
+  <si>
+    <t>Lizania Zavala</t>
+  </si>
+  <si>
+    <t>STPSH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Óscar Javier González Hernández, Irma María de Jesús López Arroyo, Pablo Anaya García</t>
+  </si>
+  <si>
+    <t>Hidalgo, entre los estados con tarifa fija para los taxis</t>
+  </si>
+  <si>
+    <t>Con la actualización a 45 pesos para la tarifa mínima, Hidalgo se ubica entre las pocas entidades del centro del país con esquema definido, destacando por ser la única sin plataformas digitales como Uber o DiDi.</t>
+  </si>
+  <si>
+    <t>Tarifario de taxis</t>
+  </si>
+  <si>
+    <t>Hidalgo cuenta con un esquema de tarifa fija de 45 pesos para transporte individual, situándose como la única entidad de la región sin servicio de plataformas digitales.</t>
+  </si>
+  <si>
+    <t>Coloca STPSH a trabajadores en Canadá, EU y otros estados</t>
+  </si>
+  <si>
+    <t>El titular de la STPSH, Óscar Javier González, reportó la vinculación laboral de 3 mil 400 hidalguenses en Canadá, 39 en Estados Unidos y más de 3 mil en otras entidades federativas.</t>
+  </si>
+  <si>
+    <t>La Secretaría del Trabajo estatal destacó la colocación de miles de trabajadores hidalguenses en el extranjero y diversos estados del país mediante programas de movilidad laboral.</t>
+  </si>
+  <si>
+    <t>Óscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>Anuncia la OEEH la disminución del costo en el estacionamiento</t>
+  </si>
+  <si>
+    <t>Tras escuchar comentarios del público, la OEEH acordó con la concesionaria reducir de 150 a 120 pesos la tarifa por tiempo libre del estacionamiento de la Feria de San Francisco 2026.</t>
+  </si>
+  <si>
+    <t>La Operadora de Eventos de Hidalgo informó la reducción de la tarifa del estacionamiento ferial a 120 pesos tras acuerdos con la empresa prestadora del servicio.</t>
+  </si>
+  <si>
+    <t>Turismo, OEEH</t>
+  </si>
+  <si>
+    <t>Coordinación es la respuesta para paz y seguridad</t>
+  </si>
+  <si>
+    <t>En la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad, el gobernador Julio Menchaca reiteró la alianza con el gobierno federal y estados vecinos para inhibir el delito e impulsar el combate al huachicol.</t>
+  </si>
+  <si>
+    <t>Durante la reunión interestatal de seguridad en Morelos, el gobernador Menchaca destacó las acciones coordinadas para la detección de huachitúneles e inhibición de delitos.</t>
+  </si>
+  <si>
+    <t>Gobierno, Sedena, GN, Pemex</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Delfina Gómez Álvarez, Clara Brugada Molina, Margarita González Saravia, Evelyn Salgado Pineda</t>
+  </si>
+  <si>
+    <t>Exploran la perforación de pozo para Atotonilco</t>
+  </si>
+  <si>
+    <t>La SIPDUS realiza estudios de exploración en La Cañada, Atotonilco de Tula, para determinar la viabilidad de perforar un nuevo pozo que refuerce la red hídrica local.</t>
+  </si>
+  <si>
+    <t>Atotonilco de Tula</t>
+  </si>
+  <si>
+    <t>Perforación de pozo</t>
+  </si>
+  <si>
+    <t>La Sipdus inició pruebas de prospección hidráulica en Atotonilco de Tula para evaluar la factibilidad de perforar un pozo de agua potable.</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Advierten disminución de nutrias en la Huasteca</t>
+  </si>
+  <si>
+    <t>Ambientalistas alertan sobre la drástica reducción de avistamientos del perro de agua en ríos de la Huasteca debido a la contaminación, cacería desmedida y alteración de cauces.</t>
+  </si>
+  <si>
+    <t>Atlapexco</t>
+  </si>
+  <si>
+    <t>Conservación de especies</t>
+  </si>
+  <si>
+    <t>Grupos ecologistas advierten sobre el riesgo de desaparición de la nutria de río en cauces de la Huasteca por la degradación ambiental y cacería.</t>
+  </si>
+  <si>
+    <t>Salomón Hernández</t>
+  </si>
+  <si>
+    <t>Eusebio León</t>
+  </si>
+  <si>
+    <t>Vecinos llevan a la PGJEH las anomalías en un bulevar</t>
+  </si>
+  <si>
+    <t>Colonos del bulevar López Mateos en Huejutla solicitaron avances sobre la denuncia interpuesta ante la PGJEH por presuntas anomalías en el asfaltado ejecutado en el gobierno de Daniel Andrade.</t>
+  </si>
+  <si>
+    <t>Vecinos de Huejutla dieron seguimiento a la denuncia contra la administración del exalcalde Daniel Andrade por la mala calidad y deficiencias técnicas en la pavimentación del bulevar López Mateos.</t>
+  </si>
+  <si>
+    <t>PGJEH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Briseyda Torres, Daniel Andrade Zurutuza</t>
+  </si>
+  <si>
+    <t>Esperan taxistas que se aplique el ajuste de los costos del servicio</t>
+  </si>
+  <si>
+    <t>Concesionarios del transporte público en la Huasteca esperan que la Semot autorice el nuevo tarifario antes del Xantolo para incluir colonias de reciente creación.</t>
+  </si>
+  <si>
+    <t>Cuerpos de transporte individual en Huejutla solicitaron la pronta actualización del tarifario regional ante el alza en refacciones e insumos operacionales.</t>
+  </si>
+  <si>
+    <t>José Almeyda, Gregorio Zamora Ramírez</t>
+  </si>
+  <si>
+    <t>Huasca conmemorará 25 años como Pueblo Mágico</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo anunció que Huasca celebrará un cuarto de siglo con el nombramiento de primer Pueblo Mágico de México con proyecciones de videomapping y muestras artesanales.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo de Hidalgo presentó el programa conmemorativo por los 25 años de Huasca como el primer Pueblo Mágico del país.</t>
+  </si>
+  <si>
+    <t>Plantan 2 mil árboles en jornada ambiental de Mineral del Chico</t>
+  </si>
+  <si>
+    <t>Voluntarios de la empresa Henkel y el Geoparque Comarca Minera sembraron dos mil árboles en El Cedral como parte de una jornada de geoeducación y reforestación.</t>
+  </si>
+  <si>
+    <t>Mineral del Chico</t>
+  </si>
+  <si>
+    <t>Reforestación</t>
+  </si>
+  <si>
+    <t>Una brigada ambiental del Geoparque Comarca Minera y la iniciativa privada plantó dos mil árboles en ejidos de Mineral del Chico.</t>
+  </si>
+  <si>
+    <t>Realiza IHE Congreso Estatal</t>
+  </si>
+  <si>
+    <t>El Instituto Hidalguense de Educación llevó a cabo el primer Congreso Estatal "Juntos por la Convivencia Escolar" enfocado en prevenir la violencia y promover ambientes seguros.</t>
+  </si>
+  <si>
+    <t>Convivencia Escolar</t>
+  </si>
+  <si>
+    <t>El IHE reunió a especialistas y comunidades educativas en un congreso estatal orientado a erradicar la violencia y fomentar valores de respeto en los planteles.</t>
+  </si>
+  <si>
+    <t>SEPH, IHE, CDHEH, Segobh, PGJEH</t>
+  </si>
+  <si>
+    <t>Coordinación de estados, para la paz y seguridad</t>
+  </si>
+  <si>
+    <t>En el marco de la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad entre autoridades de Hidalgo, Estado de México, Ciudad de México, Guerrero y Morelos, el gobernador Julio Menchaca Salazar renovó el compromiso de trabajar en colaboración.</t>
+  </si>
+  <si>
+    <t>En la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad, el gobernador Julio Menchaca renovó el compromiso para trabajar con la federación y estados vecinos.</t>
+  </si>
+  <si>
+    <t>Gobierno, Sedena, Guardia Nacional</t>
+  </si>
+  <si>
+    <t>Gabinete de seguridad anunció resultados de la semana</t>
+  </si>
+  <si>
+    <t>Un túnel localizado, 5 tomas clandestinas clausuradas y más de 20 mil litros de combustible recuperados fue resultado de operativos del Gabinete de Seguridad de Hidalgo en combate al robo de hidrocarburo.</t>
+  </si>
+  <si>
+    <t>El Gabinete de Seguridad de Hidalgo informó sobre la localización de un túnel, la clausura de cinco tomas clandestinas y la recuperación de más de 20 mil litros de hidrocarburo.</t>
+  </si>
+  <si>
+    <t>Cayó en Argentina hija de Gerardo Sosa, iba a volar a Chile</t>
+  </si>
+  <si>
+    <t>En el aeropuerto de Ciudad Mendoza, Argentina, fue asegurada la empresaria mexicana Ana Carmen S. C., hija de Gerardo Sosa Castelán, ex rector de la UAEH, quien contaba con ficha roja de la Interpol.</t>
+  </si>
+  <si>
+    <t>Ana Carmen S. C., hija del exrector de la UAEH Gerardo Sosa Castelán, fue detenida en Argentina tras contar con ficha roja de Interpol por delincuencia organizada y lavado de dinero.</t>
+  </si>
+  <si>
+    <t>PGJEH, UAEH, Interpol</t>
+  </si>
+  <si>
+    <t>Ana Carmen S. C., Gerardo Sosa Castelán</t>
+  </si>
+  <si>
+    <t>Aseguran a 3 sujetos por robo a negocio</t>
+  </si>
+  <si>
+    <t>Como resultado de las acciones de combate al delito efectuadas por la SSPH, se logró la detención de tres hombres por su participación en el asalto a una tienda de alimento para mascotas en Epazoyucan.</t>
+  </si>
+  <si>
+    <t>Epazoyucan</t>
+  </si>
+  <si>
+    <t>Robo a comercio</t>
+  </si>
+  <si>
+    <t>Elementos de la SSPH apresaron a tres hombres que asaltaron una tienda de alimentos para mascotas en Epazoyucan tras una persecución apoyada por el C5i.</t>
+  </si>
+  <si>
+    <t>SSPH, C5i</t>
+  </si>
+  <si>
+    <t>Reconocen a Hidalgo por atracción de casas productoras</t>
+  </si>
+  <si>
+    <t>La titular de la Secretaría de Turismo de Hidalgo, Elizabeth Quintanar, informó que Hidalgo fue reconocido a nivel nacional por la atracción de casas productoras para la grabación de proyectos cinematográficos.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo destacó que Hidalgo se ubica en el cuarto lugar nacional con 101 producciones cinematográficas y audiovisuales filmadas en la entidad.</t>
+  </si>
+  <si>
+    <t>Ana Luisa Vega</t>
+  </si>
+  <si>
+    <t>Presentarán proyecto para remodelar la Nave Antigua de la Feria</t>
+  </si>
+  <si>
+    <t>El titular de la Sebiso, Ricardo Gómez Moreno, adelantó que en breve presentarán un proyecto para la remodelación de la Nave Antigua del recinto ferial para albergar a artesanos en 2027.</t>
+  </si>
+  <si>
+    <t>La Sebiso proyecta la modernización de la Nave Antigua del recinto ferial para albergar a los artesanos participantes en la Feria Pachuca 2027.</t>
+  </si>
+  <si>
+    <t>Saldo blanco en los primeros días de Feria</t>
+  </si>
+  <si>
+    <t>A cuatro días del inicio de la Feria San Francisco Pachuca Hidalgo 2026, se reporta saldo blanco y una afluencia de alrededor de 55 mil visitantes, informó Marco Antonio Aranzábal Juárez.</t>
+  </si>
+  <si>
+    <t>La OEEH reportó saldo blanco y más de 55 mil visitantes en los primeros cuatro días de la Feria Pachuca 2026, además de reducir el costo de estacionamiento a 120 pesos.</t>
+  </si>
+  <si>
+    <t>Oscar Raúl Pérez Cabrera</t>
+  </si>
+  <si>
+    <t>Hidalgo llevará música, danza y fotografía a Tamaulipas</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, titular de la Secretaría de Cultura, informó que Hidalgo participará como estado invitado en el trigésimo tercer Festival Internacional en la Costa del Seno Mexicano.</t>
+  </si>
+  <si>
+    <t>Festival Cultural</t>
+  </si>
+  <si>
+    <t>Hidalgo participará como estado invitado en el Festival Internacional en la Costa del Seno Mexicano en Tamaulipas con agrupaciones de música, danza y muestras fotográficas.</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar</t>
+  </si>
+  <si>
+    <t>Trabajadores del sector salud piden cambio de jefa jurisdiccional</t>
+  </si>
+  <si>
+    <t>Ante diversos casos de acoso laboral y hostigamiento, empleados de la Jurisdicción Sanitaria de Apan, dependiente de la SSH, realizan su jornada laboral bajo protesta contra Edith Carolina Espinoza Jiménez.</t>
+  </si>
+  <si>
+    <t>Apan</t>
+  </si>
+  <si>
+    <t>Acoso Laboral</t>
+  </si>
+  <si>
+    <t>Trabajadores sindicalizados del sector salud en Apan protestaron pacíficamente exigiendo la destitución de la jefa jurisdiccional por presuntos actos de acoso laboral.</t>
+  </si>
+  <si>
+    <t>Abel Ricardo Flores</t>
+  </si>
+  <si>
+    <t>SSH, SNTSA</t>
+  </si>
+  <si>
+    <t>Edith Carolina Espinoza Jiménez, Sonia Ocampo Chapa</t>
+  </si>
+  <si>
+    <t>Detienen en Sudamérica a la hija de Gerardo Sosa</t>
+  </si>
+  <si>
+    <t>Ana Carmen Sosa Cravioto, hija del exrector de la UAEH Gerardo Sosa Castelán, fue detenida en Mendoza, Argentina, tras activarse una alerta roja de Interpol solicitada por autoridades mexicanas por delincuencia organizada y lavado de dinero.</t>
+  </si>
+  <si>
+    <t>La hija del exrector Gerardo Sosa Castelán fue detenida en Argentina tras activarse una orden de aprehensión e Interpol por delincuencia organizada.</t>
+  </si>
+  <si>
+    <t>PGJEH, FGR, UAEH</t>
+  </si>
+  <si>
+    <t>Ana Carmen Sosa Cravioto, Gerardo Sosa Castelán, Adriana Sosa Cravioto</t>
+  </si>
+  <si>
+    <t>Feria de San Francisco 2026 supera los 50 mil visitantes</t>
+  </si>
+  <si>
+    <t>La Feria San Francisco Hidalgo 2026 registró una afluencia de alrededor de 55 mil visitantes durante sus primeros cuatro días, destacando el Pabellón Artesanal con más de 140 artesanas y artesanos, reportando saldo blanco.</t>
+  </si>
+  <si>
+    <t>La Feria San Francisco Pachuca 2026 registró más de 55 mil asistentes en sus primeros cuatro días con alta actividad artesanal y saldo blanco.</t>
+  </si>
+  <si>
+    <t>Turismo, OEEH, Protección Civil</t>
+  </si>
+  <si>
+    <t>Marco Antonio Aranzábal Juárez, Jorge Alberto Reyes Hernández</t>
+  </si>
+  <si>
+    <t>Bajan 30 pesos a estacionamiento tras quejas</t>
+  </si>
+  <si>
+    <t>Las quejas por el costo del estacionamiento de la Feria llevaron a la Operadora de Eventos del Estado de Hidalgo a reducir la tarifa de 150 a 120 pesos e implementar operativos contra cobros irregulares.</t>
+  </si>
+  <si>
+    <t>La OEEH ajustó a 120 pesos la tarifa del estacionamiento ferial tras inconformidades de los usuarios.</t>
+  </si>
+  <si>
+    <t>Turismo, OEEH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Turismo descarta fuga de visitantes por tráfico</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo de Hidalgo descartó que las obras y el tráfico en la carretera México-Pachuca disminuyan la llegada de visitantes, destacando el flujo en la ocupación hotelera.</t>
+  </si>
+  <si>
+    <t>Afluencia Turística</t>
+  </si>
+  <si>
+    <t>La Secturh rechazó afectaciones turísticas por congestionamiento vial ante la alta ocupación en hoteles de la capital.</t>
+  </si>
+  <si>
+    <t>Recolectarán baterías en jornada de reforestación</t>
+  </si>
+  <si>
+    <t>La Semarnath realizará una jornada de acopio de pilas usadas y plantación de árboles en la Unidad Deportiva Municipal de Pachuca para dar destino adecuado a estos residuos.</t>
+  </si>
+  <si>
+    <t>Semarnath coordinará el viernes una campaña ambiental en Pachuca combinando recolección de pilas y siembra de árboles.</t>
+  </si>
+  <si>
+    <t>Semarnath, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Celebrará Huasca su 25 aniversario como Pueblo Mágico</t>
+  </si>
+  <si>
+    <t>Huasca de Ocampo conmemorará 25 años como Pueblo Mágico con eventos culturales y turísticos. La Secretaría de Turismo destacó además el posicionamiento del estado en producciones audiovisuales.</t>
+  </si>
+  <si>
+    <t>Huasca de Ocampo celebrará sus 25 años como el primer Pueblo Mágico de México con un programa festivo el 5 de octubre.</t>
+  </si>
+  <si>
+    <t>Por severas fallas estructurales, la primaria Aquiles Serdán en Tulancingo será demolida y edificada nuevamente en su totalidad, informó el titular de la SEPH Natividad Castrejón.</t>
+  </si>
+  <si>
+    <t>La SEPH reconstruirá íntegramente la primaria Aquiles Serdán por daños estructurales, evaluando reubicación de alumnos.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez</t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1361,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1310,7 +1403,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1398,34 +1491,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ69" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ69" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ67" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ67" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{656C5EAC-6AE7-4849-A2CB-07D90F39D8FD}" uniqueName="Medio_o_cuenta" name="Medio o cuenta" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{656C5EAC-6AE7-4849-A2CB-07D90F39D8FD}" uniqueName="Medio_o_cuenta" name="Medio o cuenta" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Medio_o_cuenta" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{67E4BBBE-D5C7-4FB1-A4CA-49BC94A0014E}" uniqueName="Usuario" name="Usuario">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Usuario" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96739AB4-7016-49C1-A1BC-122CE2056C09}" uniqueName="Titular" name="Titular" dataDxfId="18">
+    <tableColumn id="4" xr3:uid="{96739AB4-7016-49C1-A1BC-122CE2056C09}" uniqueName="Titular" name="Titular" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Titular" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{96B49FFA-3FAF-4446-9C9C-4866BA6A2CFB}" uniqueName="Contenido" name="Contenido" dataDxfId="17">
+    <tableColumn id="5" xr3:uid="{96B49FFA-3FAF-4446-9C9C-4866BA6A2CFB}" uniqueName="Contenido" name="Contenido" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Contenido" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F6615099-82A7-46E7-8B6C-46F5B1BCE0A4}" uniqueName="Fecha_de_publicacion" name="Fecha de publicación" dataDxfId="16">
+    <tableColumn id="6" xr3:uid="{F6615099-82A7-46E7-8B6C-46F5B1BCE0A4}" uniqueName="Fecha_de_publicacion" name="Fecha de publicación" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Fecha_de_publicacion" xmlDataType="date"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{960471FD-DEDC-402B-89FF-237BDB7E7712}" uniqueName="Liga" name="Liga">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Liga" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E3552A04-EE44-46D2-8061-2515AB7BF199}" uniqueName="Municipio" name="Municipio" dataDxfId="15">
+    <tableColumn id="8" xr3:uid="{E3552A04-EE44-46D2-8061-2515AB7BF199}" uniqueName="Municipio" name="Municipio" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Municipio" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2E6348A9-8A06-40E0-9039-3BE83BFEF10B}" uniqueName="Sentimiento_de_la_fuente" name="Sentimiento de la fuente" dataDxfId="14">
+    <tableColumn id="9" xr3:uid="{2E6348A9-8A06-40E0-9039-3BE83BFEF10B}" uniqueName="Sentimiento_de_la_fuente" name="Sentimiento de la fuente" dataDxfId="0">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Sentimiento_de_la_fuente" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{81F2E10D-4242-4A14-AE44-001E3C95FD39}" uniqueName="Tipo_de_publicacion" name="Tipo de publicación">
@@ -1458,55 +1551,55 @@
     <tableColumn id="19" xr3:uid="{09AE5EC7-6FA9-43B0-A953-BEB3738329E3}" uniqueName="Alcance_del_medio" name="Alcance del medio">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Alcance_del_medio" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{D7B2A113-9CC6-4BD4-8DF1-12AA7233AD96}" uniqueName="Unidad_del_alcance" name="Unidad del alcance" dataDxfId="13">
+    <tableColumn id="20" xr3:uid="{D7B2A113-9CC6-4BD4-8DF1-12AA7233AD96}" uniqueName="Unidad_del_alcance" name="Unidad del alcance" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Unidad_del_alcance" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{FBC61DAD-43EE-4F79-B045-4EC08F4350F2}" uniqueName="Impresiones" name="Impresiones">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Impresiones" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{E0F7175B-4E19-404A-85B3-D6F0C20CC4D8}" uniqueName="Genero_periodistico" name="Género periodístico" dataDxfId="12">
+    <tableColumn id="22" xr3:uid="{E0F7175B-4E19-404A-85B3-D6F0C20CC4D8}" uniqueName="Genero_periodistico" name="Género periodístico" dataDxfId="19">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Genero_periodistico" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{956A34F7-46A2-4FD2-B124-47F0DBD8C47B}" uniqueName="Tema_segun_la_fuente" name="Tema según la fuente" dataDxfId="11">
+    <tableColumn id="23" xr3:uid="{956A34F7-46A2-4FD2-B124-47F0DBD8C47B}" uniqueName="Tema_segun_la_fuente" name="Tema según la fuente" dataDxfId="18">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Tema_segun_la_fuente" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{A3443871-377E-4A30-8E3B-7FFA77E0DA55}" uniqueName="Sintesis" name="Síntesis" dataDxfId="10">
+    <tableColumn id="24" xr3:uid="{A3443871-377E-4A30-8E3B-7FFA77E0DA55}" uniqueName="Sintesis" name="Síntesis" dataDxfId="17">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Sintesis" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{5CF69F18-4F87-4056-B7CB-8945726A582A}" uniqueName="Jerarquia_de_la_nota" name="Jerarquía de la nota" dataDxfId="9">
+    <tableColumn id="25" xr3:uid="{5CF69F18-4F87-4056-B7CB-8945726A582A}" uniqueName="Jerarquia_de_la_nota" name="Jerarquía de la nota" dataDxfId="16">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Jerarquia_de_la_nota" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{BDAD3553-B5A7-4B33-B6A0-00158FE22B29}" uniqueName="Posicion" name="Posición" dataDxfId="8">
+    <tableColumn id="26" xr3:uid="{BDAD3553-B5A7-4B33-B6A0-00158FE22B29}" uniqueName="Posicion" name="Posición" dataDxfId="15">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Posicion" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="27" xr3:uid="{6713D1B4-03D8-492E-A805-B8B5E516E754}" uniqueName="Dimension" name="Dimensión">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Dimension" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{5E754D76-EE28-46CE-8759-FFE60C1CFF67}" uniqueName="Unidad_de_la_dimension" name="Unidad de la dimensión" dataDxfId="7">
+    <tableColumn id="28" xr3:uid="{5E754D76-EE28-46CE-8759-FFE60C1CFF67}" uniqueName="Unidad_de_la_dimension" name="Unidad de la dimensión" dataDxfId="14">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Unidad_de_la_dimension" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{8F595EB9-9F69-41D2-AC23-2C7879D9977B}" uniqueName="Con_fotografia" name="Con fotografía" dataDxfId="6">
+    <tableColumn id="29" xr3:uid="{8F595EB9-9F69-41D2-AC23-2C7879D9977B}" uniqueName="Con_fotografia" name="Con fotografía" dataDxfId="13">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Con_fotografia" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{C61CD4D8-3A8E-4A69-A10B-40B4A2B273E1}" uniqueName="Es_replica" name="Es réplica" dataDxfId="5">
+    <tableColumn id="30" xr3:uid="{C61CD4D8-3A8E-4A69-A10B-40B4A2B273E1}" uniqueName="Es_replica" name="Es réplica" dataDxfId="12">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Es_replica" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="31" xr3:uid="{E10CC2EC-300C-4A5F-8203-51C284C389EC}" uniqueName="Medio_de_origen" name="Medio de origen">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Medio_de_origen" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{DF96E63A-F235-4F77-B4AE-FB19B55C217B}" uniqueName="Autor" name="Autor" dataDxfId="4">
+    <tableColumn id="32" xr3:uid="{DF96E63A-F235-4F77-B4AE-FB19B55C217B}" uniqueName="Autor" name="Autor" dataDxfId="11">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Autor" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{D92A8CD3-00A9-49C9-B24E-82388577C54B}" uniqueName="Tipo_de_autor" name="Tipo de autor" dataDxfId="3">
+    <tableColumn id="33" xr3:uid="{D92A8CD3-00A9-49C9-B24E-82388577C54B}" uniqueName="Tipo_de_autor" name="Tipo de autor" dataDxfId="10">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Tipo_de_autor" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{80C3EC21-4CF3-46E5-BBFE-1CD4F7309933}" uniqueName="Dependencia" name="Dependencia" dataDxfId="2">
+    <tableColumn id="34" xr3:uid="{80C3EC21-4CF3-46E5-BBFE-1CD4F7309933}" uniqueName="Dependencia" name="Dependencia" dataDxfId="9">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Dependencia" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{CB1B386E-9E24-4408-8CFA-E4A2B48CA015}" uniqueName="Dependencias_mencionadas" name="Dependencias mencionadas" dataDxfId="1">
+    <tableColumn id="35" xr3:uid="{CB1B386E-9E24-4408-8CFA-E4A2B48CA015}" uniqueName="Dependencias_mencionadas" name="Dependencias mencionadas" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Dependencias_mencionadas" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{A3ED4D4F-6580-49D2-A119-2DFA36DD9925}" uniqueName="Actores_mencionados" name="Actores mencionados" dataDxfId="0">
+    <tableColumn id="36" xr3:uid="{A3ED4D4F-6580-49D2-A119-2DFA36DD9925}" uniqueName="Actores_mencionados" name="Actores mencionados" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Actores_mencionados" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -1831,7 +1924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ69"/>
+  <dimension ref="A1:AJ67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1981,31 +2074,55 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46294</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="K2">
+        <v>13262</v>
+      </c>
+      <c r="L2" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="1">
-        <v>46291</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>42</v>
+      <c r="M2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>103</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -2020,52 +2137,54 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="Y2" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA2">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AJ2" s="2"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>110</v>
@@ -2074,10 +2193,10 @@
         <v>111</v>
       </c>
       <c r="F3" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>45</v>
@@ -2085,6 +2204,30 @@
       <c r="I3" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="J3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3">
+        <v>13262</v>
+      </c>
+      <c r="L3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N3" t="s">
+        <v>103</v>
+      </c>
+      <c r="O3" t="s">
+        <v>103</v>
+      </c>
+      <c r="P3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>103</v>
+      </c>
       <c r="R3">
         <v>1</v>
       </c>
@@ -2098,7 +2241,7 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>112</v>
@@ -2122,30 +2265,30 @@
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AI3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>115</v>
@@ -2154,17 +2297,41 @@
         <v>116</v>
       </c>
       <c r="F4" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="J4" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4">
+        <v>13262</v>
+      </c>
+      <c r="L4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M4" t="s">
+        <v>103</v>
+      </c>
+      <c r="N4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P4" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>103</v>
+      </c>
       <c r="R4">
         <v>1</v>
       </c>
@@ -2178,10 +2345,10 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X4" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>57</v>
@@ -2190,40 +2357,42 @@
         <v>43</v>
       </c>
       <c r="AA4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="AI4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AJ4" s="2"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>120</v>
@@ -2232,10 +2401,10 @@
         <v>121</v>
       </c>
       <c r="F5" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>45</v>
@@ -2243,6 +2412,30 @@
       <c r="I5" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="J5" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5">
+        <v>13262</v>
+      </c>
+      <c r="L5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M5" t="s">
+        <v>103</v>
+      </c>
+      <c r="N5" t="s">
+        <v>103</v>
+      </c>
+      <c r="O5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>103</v>
+      </c>
       <c r="R5">
         <v>1</v>
       </c>
@@ -2265,7 +2458,7 @@
         <v>55</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA5">
         <v>20</v>
@@ -2280,43 +2473,45 @@
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="AI5" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AJ5" s="2"/>
+      <c r="AJ5" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F6" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>48</v>
@@ -2340,70 +2535,72 @@
         <v>129</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ6" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F7" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
       <c r="S7">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>58</v>
@@ -2412,19 +2609,19 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>56</v>
@@ -2436,52 +2633,54 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ7" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F8" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R8">
         <v>1</v>
       </c>
       <c r="S8">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>58</v>
@@ -2490,19 +2689,19 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA8">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>56</v>
@@ -2514,37 +2713,39 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ8" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F9" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G9">
         <v>4</v>
@@ -2559,7 +2760,7 @@
         <v>1</v>
       </c>
       <c r="S9">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>58</v>
@@ -2568,19 +2769,19 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA9">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>56</v>
@@ -2592,52 +2793,52 @@
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="AJ9" s="2"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F10" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R10">
         <v>1</v>
       </c>
       <c r="S10">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>58</v>
@@ -2646,19 +2847,19 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="Y10" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>56</v>
@@ -2670,52 +2871,54 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AG10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AJ10" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F11" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G11">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R11">
         <v>1</v>
       </c>
       <c r="S11">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>58</v>
@@ -2724,76 +2927,78 @@
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AJ11" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="F12" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G12">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R12">
         <v>1</v>
       </c>
       <c r="S12">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>58</v>
@@ -2802,19 +3007,19 @@
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>56</v>
@@ -2826,73 +3031,78 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ12" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="F13" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R13">
         <v>1</v>
       </c>
       <c r="S13">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U13">
+        <v>39786</v>
+      </c>
       <c r="V13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>56</v>
@@ -2904,67 +3114,72 @@
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ13" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="F14" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>45</v>
+        <v>176</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R14">
         <v>1</v>
       </c>
       <c r="S14">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U14">
+        <v>39786</v>
+      </c>
       <c r="V14" s="2" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>61</v>
@@ -2976,79 +3191,84 @@
         <v>56</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ14" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="F15" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R15">
         <v>1</v>
       </c>
       <c r="S15">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U15">
+        <v>39786</v>
+      </c>
       <c r="V15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>56</v>
@@ -3060,37 +3280,39 @@
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ15" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="F16" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -3099,109 +3321,117 @@
         <v>45</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R16">
         <v>1</v>
       </c>
       <c r="S16">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U16">
+        <v>39786</v>
+      </c>
       <c r="V16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ16" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="F17" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U17">
+        <v>39786</v>
+      </c>
       <c r="V17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA17">
         <v>20</v>
@@ -3210,157 +3440,165 @@
         <v>56</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AJ17" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="F18" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
       <c r="S18">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U18">
+        <v>39786</v>
+      </c>
       <c r="V18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA18">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD18" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ18" s="2"/>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="F19" s="1">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R19">
         <v>1</v>
       </c>
       <c r="S19">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U19">
+        <v>39786</v>
+      </c>
       <c r="V19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA19">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>56</v>
@@ -3372,88 +3610,93 @@
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ19" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="F20" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R20">
         <v>1</v>
       </c>
       <c r="S20">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U20">
+        <v>39786</v>
+      </c>
       <c r="V20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA20">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD20" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH20" s="2" t="s">
         <v>71</v>
@@ -3461,59 +3704,64 @@
       <c r="AI20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AJ20" s="2"/>
+      <c r="AJ20" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="F21" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R21">
         <v>1</v>
       </c>
       <c r="S21">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U21">
+        <v>39786</v>
+      </c>
       <c r="V21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>183</v>
+        <v>122</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA21">
         <v>20</v>
@@ -3522,157 +3770,165 @@
         <v>56</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD21" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ21" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="F22" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G22">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R22">
         <v>1</v>
       </c>
       <c r="S22">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U22">
+        <v>39786</v>
+      </c>
       <c r="V22" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>57</v>
+        <v>216</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA22">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AB22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD22" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="AG22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c r="AJ22" s="2"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="F23" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G23">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R23">
         <v>1</v>
       </c>
       <c r="S23">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U23">
+        <v>39786</v>
+      </c>
       <c r="V23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA23">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>56</v>
@@ -3690,67 +3946,72 @@
         <v>41</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ23" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="F24" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R24">
         <v>1</v>
       </c>
       <c r="S24">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U24">
+        <v>39786</v>
+      </c>
       <c r="V24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA24">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB24" s="2" t="s">
         <v>56</v>
@@ -3762,73 +4023,78 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ24" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="F25" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R25">
         <v>1</v>
       </c>
       <c r="S25">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T25" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U25">
+        <v>39786</v>
+      </c>
       <c r="V25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA25">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB25" s="2" t="s">
         <v>56</v>
@@ -3840,7 +4106,7 @@
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AG25" s="2" t="s">
         <v>40</v>
@@ -3849,142 +4115,152 @@
         <v>71</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AJ25" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="F26" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R26">
         <v>1</v>
       </c>
       <c r="S26">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U26">
+        <v>39786</v>
+      </c>
       <c r="V26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="Y26" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ26" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="F27" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R27">
         <v>1</v>
       </c>
       <c r="S27">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U27">
+        <v>39786</v>
+      </c>
       <c r="V27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA27">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB27" s="2" t="s">
         <v>56</v>
@@ -3996,70 +4272,75 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ27" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="F28" s="1">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R28">
         <v>1</v>
       </c>
       <c r="S28">
-        <v>15000</v>
+        <v>13262</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U28">
+        <v>39786</v>
+      </c>
       <c r="V28" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>192</v>
+        <v>89</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA28">
         <v>20</v>
@@ -4074,46 +4355,48 @@
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>66</v>
+        <v>239</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="AJ28" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="AJ28" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="F29" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -4124,23 +4407,26 @@
       <c r="T29" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U29">
+        <v>39786</v>
+      </c>
       <c r="V29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA29">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB29" s="2" t="s">
         <v>56</v>
@@ -4152,40 +4438,42 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="AG29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ29" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="F30" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>45</v>
@@ -4202,14 +4490,17 @@
       <c r="T30" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U30">
+        <v>39786</v>
+      </c>
       <c r="V30" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>57</v>
@@ -4218,7 +4509,7 @@
         <v>43</v>
       </c>
       <c r="AA30">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB30" s="2" t="s">
         <v>56</v>
@@ -4236,34 +4527,36 @@
         <v>41</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ30" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="AJ30" s="2" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="F31" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>59</v>
@@ -4280,23 +4573,26 @@
       <c r="T31" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U31">
+        <v>39786</v>
+      </c>
       <c r="V31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z31" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA31">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB31" s="2" t="s">
         <v>56</v>
@@ -4308,46 +4604,48 @@
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ31" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="AJ31" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="F32" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4358,14 +4656,17 @@
       <c r="T32" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U32">
+        <v>39786</v>
+      </c>
       <c r="V32" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="Y32" s="2" t="s">
         <v>57</v>
@@ -4374,7 +4675,7 @@
         <v>43</v>
       </c>
       <c r="AA32">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>56</v>
@@ -4386,43 +4687,45 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>101</v>
+        <v>260</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AJ32" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="AJ32" s="2" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="F33" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>45</v>
+        <v>264</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>48</v>
@@ -4436,23 +4739,26 @@
       <c r="T33" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U33">
+        <v>39786</v>
+      </c>
       <c r="V33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>227</v>
+        <v>94</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA33">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>56</v>
@@ -4464,45 +4770,45 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>113</v>
+        <v>260</v>
       </c>
       <c r="AG33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>229</v>
+        <v>90</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>86</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="F34" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>45</v>
+        <v>267</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>48</v>
@@ -4516,14 +4822,17 @@
       <c r="T34" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U34">
+        <v>39786</v>
+      </c>
       <c r="V34" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="Y34" s="2" t="s">
         <v>57</v>
@@ -4538,54 +4847,57 @@
         <v>56</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>41</v>
+        <v>268</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="F35" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>238</v>
+        <v>59</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="J35" t="s">
+        <v>102</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -4596,68 +4908,73 @@
       <c r="T35" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U35">
+        <v>39786</v>
+      </c>
       <c r="V35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA35">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB35" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC35" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD35" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="AG35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ35" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="AJ35" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="F36" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>45</v>
@@ -4665,6 +4982,9 @@
       <c r="I36" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="J36" t="s">
+        <v>102</v>
+      </c>
       <c r="R36">
         <v>1</v>
       </c>
@@ -4674,76 +4994,82 @@
       <c r="T36" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U36">
+        <v>39786</v>
+      </c>
       <c r="V36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>242</v>
+        <v>143</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA36">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC36" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD36" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF36" s="2" t="s">
-        <v>41</v>
+        <v>273</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>245</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="F37" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G37">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>248</v>
+        <v>59</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="J37" t="s">
+        <v>102</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4754,20 +5080,23 @@
       <c r="T37" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U37">
+        <v>39786</v>
+      </c>
       <c r="V37" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="Y37" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA37">
         <v>20</v>
@@ -4782,201 +5111,212 @@
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="F38" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="J38" t="s">
+        <v>102</v>
       </c>
       <c r="R38">
         <v>1</v>
       </c>
       <c r="S38">
-        <v>10000</v>
+        <v>13262</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U38">
+        <v>39786</v>
+      </c>
       <c r="V38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA38">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ38" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="AJ38" s="2" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
         <v>85</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="F39" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G39">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>238</v>
+        <v>59</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R39">
         <v>1</v>
       </c>
       <c r="S39">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U39">
+        <v>37500</v>
+      </c>
       <c r="V39" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="Y39" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA39">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB39" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC39" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD39" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AG39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="AJ39" s="2"/>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C40" t="s">
         <v>85</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="F40" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G40">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>49</v>
@@ -4985,73 +5325,78 @@
         <v>1</v>
       </c>
       <c r="S40">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U40">
+        <v>37500</v>
+      </c>
       <c r="V40" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>90</v>
+        <v>294</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="Y40" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AA40">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC40" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD40" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="AG40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ40" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="AJ40" s="2" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C41" t="s">
         <v>85</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="F41" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G41">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>45</v>
@@ -5063,28 +5408,31 @@
         <v>1</v>
       </c>
       <c r="S41">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U41">
+        <v>37500</v>
+      </c>
       <c r="V41" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA41">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>56</v>
@@ -5096,73 +5444,76 @@
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AG41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ41" s="2"/>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="F42" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R42">
         <v>1</v>
       </c>
       <c r="S42">
-        <v>15000</v>
+        <v>12500</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U42">
+        <v>37500</v>
+      </c>
       <c r="V42" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA42">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AB42" s="2" t="s">
         <v>56</v>
@@ -5174,73 +5525,78 @@
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>96</v>
+        <v>296</v>
       </c>
       <c r="AG42" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ42" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="AJ42" s="2" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="F43" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>238</v>
+        <v>45</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R43">
         <v>1</v>
       </c>
       <c r="S43">
-        <v>15000</v>
+        <v>12500</v>
       </c>
       <c r="T43" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U43">
+        <v>37500</v>
+      </c>
       <c r="V43" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>258</v>
+        <v>143</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA43">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>56</v>
@@ -5252,70 +5608,75 @@
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="AG43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AJ43" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="AJ43" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="F44" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G44">
         <v>3</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R44">
         <v>1</v>
       </c>
       <c r="S44">
-        <v>15000</v>
+        <v>12500</v>
       </c>
       <c r="T44" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U44">
+        <v>37500</v>
+      </c>
       <c r="V44" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="AA44">
         <v>20</v>
@@ -5330,148 +5691,156 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AJ44" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="AJ44" s="2" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="F45" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>45</v>
+        <v>318</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R45">
         <v>1</v>
       </c>
       <c r="S45">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U45">
+        <v>37500</v>
+      </c>
       <c r="V45" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>65</v>
+        <v>319</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z45" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA45">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB45" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC45" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>64</v>
+        <v>321</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>64</v>
+        <v>321</v>
       </c>
       <c r="AJ45" s="2"/>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>279</v>
+        <v>322</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="F46" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>45</v>
+        <v>324</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
       <c r="S46">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T46" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U46">
+        <v>37500</v>
+      </c>
       <c r="V46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>183</v>
+        <v>325</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>281</v>
+        <v>326</v>
       </c>
       <c r="Y46" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA46">
         <v>12</v>
@@ -5486,155 +5855,161 @@
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>282</v>
+        <v>86</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="F47" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R47">
         <v>1</v>
       </c>
       <c r="S47">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U47">
+        <v>37500</v>
+      </c>
       <c r="V47" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>287</v>
+        <v>177</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA47">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC47" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD47" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>47</v>
+        <v>332</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="F48" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R48">
         <v>1</v>
       </c>
       <c r="S48">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T48" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U48">
+        <v>37500</v>
+      </c>
       <c r="V48" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>78</v>
+        <v>301</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA48">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB48" s="2" t="s">
         <v>56</v>
@@ -5646,43 +6021,45 @@
         <v>44</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>68</v>
+        <v>327</v>
       </c>
       <c r="AG48" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ48" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="AJ48" s="2" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="F49" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>295</v>
+        <v>154</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>48</v>
@@ -5691,19 +6068,22 @@
         <v>1</v>
       </c>
       <c r="S49">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T49" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U49">
+        <v>37500</v>
+      </c>
       <c r="V49" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>296</v>
+        <v>155</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>55</v>
@@ -5724,45 +6104,45 @@
         <v>44</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ49" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="AI49" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ49" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="F50" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>48</v>
@@ -5771,28 +6151,31 @@
         <v>1</v>
       </c>
       <c r="S50">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T50" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U50">
+        <v>37500</v>
+      </c>
       <c r="V50" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>74</v>
+        <v>344</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA50">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AB50" s="2" t="s">
         <v>56</v>
@@ -5804,40 +6187,40 @@
         <v>44</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="AG50" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AJ50" s="2"/>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>303</v>
+        <v>347</v>
       </c>
       <c r="F51" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>45</v>
@@ -5849,25 +6232,28 @@
         <v>1</v>
       </c>
       <c r="S51">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T51" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U51">
+        <v>37500</v>
+      </c>
       <c r="V51" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>192</v>
+        <v>348</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>304</v>
+        <v>349</v>
       </c>
       <c r="Y51" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z51" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA51">
         <v>20</v>
@@ -5888,37 +6274,37 @@
         <v>41</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>215</v>
+        <v>350</v>
       </c>
       <c r="AJ51" s="2"/>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="F52" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G52">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>48</v>
@@ -5936,19 +6322,19 @@
         <v>37</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA52">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB52" s="2" t="s">
         <v>56</v>
@@ -5966,48 +6352,48 @@
         <v>41</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>309</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="F53" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R53">
         <v>1</v>
       </c>
       <c r="S53">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T53" s="2" t="s">
         <v>58</v>
@@ -6016,19 +6402,19 @@
         <v>37</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>312</v>
+        <v>89</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z53" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA53">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB53" s="2" t="s">
         <v>56</v>
@@ -6040,45 +6426,45 @@
         <v>44</v>
       </c>
       <c r="AF53" s="2" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="AG53" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>315</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>316</v>
+        <v>358</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>317</v>
+        <v>359</v>
       </c>
       <c r="F54" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G54">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>42</v>
@@ -6087,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="S54">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T54" s="2" t="s">
         <v>58</v>
@@ -6096,16 +6482,16 @@
         <v>37</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>65</v>
+        <v>243</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="Y54" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z54" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA54">
         <v>20</v>
@@ -6120,52 +6506,54 @@
         <v>44</v>
       </c>
       <c r="AF54" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ54" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="AJ54" s="2" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="F55" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G55">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>45</v>
+        <v>365</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R55">
         <v>1</v>
       </c>
       <c r="S55">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T55" s="2" t="s">
         <v>58</v>
@@ -6174,76 +6562,76 @@
         <v>37</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>321</v>
+        <v>367</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA55">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB55" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC55" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD55" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF55" s="2" t="s">
-        <v>322</v>
+        <v>41</v>
       </c>
       <c r="AG55" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>323</v>
+        <v>368</v>
       </c>
       <c r="AJ55" s="2"/>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="F56" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G56">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R56">
         <v>1</v>
       </c>
       <c r="S56">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>58</v>
@@ -6252,19 +6640,19 @@
         <v>37</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>326</v>
+        <v>122</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA56">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB56" s="2" t="s">
         <v>56</v>
@@ -6276,52 +6664,54 @@
         <v>44</v>
       </c>
       <c r="AF56" s="2" t="s">
-        <v>39</v>
+        <v>372</v>
       </c>
       <c r="AG56" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH56" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AJ56" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AJ56" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="F57" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G57">
         <v>5</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>331</v>
+        <v>45</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R57">
         <v>1</v>
       </c>
       <c r="S57">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T57" s="2" t="s">
         <v>58</v>
@@ -6330,76 +6720,78 @@
         <v>37</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>332</v>
+        <v>375</v>
       </c>
       <c r="Y57" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z57" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA57">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB57" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC57" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF57" s="2" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="AG57" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ57" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="AJ57" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>335</v>
+        <v>377</v>
       </c>
       <c r="F58" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G58">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R58">
         <v>1</v>
       </c>
       <c r="S58">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T58" s="2" t="s">
         <v>58</v>
@@ -6408,10 +6800,10 @@
         <v>37</v>
       </c>
       <c r="W58" s="2" t="s">
-        <v>336</v>
+        <v>143</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="Y58" s="2" t="s">
         <v>57</v>
@@ -6420,57 +6812,60 @@
         <v>43</v>
       </c>
       <c r="AA58">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB58" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC58" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD58" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF58" s="2" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="AG58" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH58" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="AJ58" s="2" t="s">
-        <v>340</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="F59" s="1">
-        <v>46293</v>
+        <v>46294</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -6482,72 +6877,75 @@
         <v>58</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>343</v>
+        <v>37</v>
       </c>
       <c r="W59" s="2" t="s">
-        <v>65</v>
+        <v>382</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="Y59" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z59" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA59">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB59" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC59" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD59" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF59" s="2" t="s">
-        <v>70</v>
+        <v>379</v>
       </c>
       <c r="AG59" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH59" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>86</v>
+        <v>384</v>
       </c>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>346</v>
+        <v>385</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="F60" s="1">
-        <v>46293</v>
+        <v>46294</v>
+      </c>
+      <c r="G60">
+        <v>6</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>286</v>
+        <v>387</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -6562,69 +6960,72 @@
         <v>37</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA60">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB60" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC60" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD60" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF60" s="2" t="s">
-        <v>41</v>
+        <v>390</v>
       </c>
       <c r="AG60" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH60" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="AJ60" s="2" t="s">
-        <v>289</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>351</v>
+        <v>393</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="F61" s="1">
-        <v>46293</v>
+        <v>46294</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -6639,16 +7040,16 @@
         <v>37</v>
       </c>
       <c r="W61" s="2" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>353</v>
+        <v>395</v>
       </c>
       <c r="Y61" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z61" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA61">
         <v>20</v>
@@ -6669,37 +7070,42 @@
         <v>41</v>
       </c>
       <c r="AH61" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AI61" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ61" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="AJ61" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="F62" s="1">
-        <v>46293</v>
+        <v>46294</v>
+      </c>
+      <c r="G62">
+        <v>3</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>221</v>
+        <v>45</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -6714,16 +7120,16 @@
         <v>37</v>
       </c>
       <c r="W62" s="2" t="s">
-        <v>222</v>
+        <v>70</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="Y62" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z62" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA62">
         <v>20</v>
@@ -6744,31 +7150,36 @@
         <v>41</v>
       </c>
       <c r="AH62" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AI62" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AJ62" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="AJ62" s="2" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>357</v>
+        <v>403</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>358</v>
+        <v>404</v>
       </c>
       <c r="F63" s="1">
-        <v>46293</v>
+        <v>46294</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>45</v>
@@ -6789,19 +7200,19 @@
         <v>37</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>359</v>
+        <v>143</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="Y63" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z63" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA63">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB63" s="2" t="s">
         <v>56</v>
@@ -6813,48 +7224,48 @@
         <v>44</v>
       </c>
       <c r="AF63" s="2" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="AG63" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH63" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="AI63" s="2" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="AJ63" s="2" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="F64" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R64">
         <v>1</v>
@@ -6869,10 +7280,10 @@
         <v>37</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="Y64" s="2" t="s">
         <v>55</v>
@@ -6881,7 +7292,7 @@
         <v>61</v>
       </c>
       <c r="AA64">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB64" s="2" t="s">
         <v>56</v>
@@ -6899,34 +7310,36 @@
         <v>41</v>
       </c>
       <c r="AH64" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="AI64" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="AJ64" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AJ64" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>369</v>
+        <v>412</v>
       </c>
       <c r="F65" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>45</v>
@@ -6947,19 +7360,19 @@
         <v>37</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>74</v>
+        <v>344</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="Y65" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z65" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA65">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB65" s="2" t="s">
         <v>56</v>
@@ -6971,45 +7384,43 @@
         <v>44</v>
       </c>
       <c r="AF65" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="AG65" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH65" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="AI65" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="AJ65" s="2" t="s">
-        <v>372</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="AJ65" s="2"/>
     </row>
     <row r="66" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
       <c r="F66" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>295</v>
+        <v>154</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>48</v>
@@ -7027,19 +7438,19 @@
         <v>37</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>296</v>
+        <v>155</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>375</v>
+        <v>417</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA66">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB66" s="2" t="s">
         <v>56</v>
@@ -7057,42 +7468,42 @@
         <v>41</v>
       </c>
       <c r="AH66" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI66" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="AJ66" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="AI66" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ66" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="67" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>377</v>
+        <v>84</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>378</v>
+        <v>418</v>
       </c>
       <c r="F67" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R67">
         <v>1</v>
@@ -7107,10 +7518,10 @@
         <v>37</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="Y67" s="2" t="s">
         <v>55</v>
@@ -7131,179 +7542,19 @@
         <v>44</v>
       </c>
       <c r="AF67" s="2" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="AG67" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH67" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="AI67" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="AJ67" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C68" t="s">
-        <v>98</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F68" s="1">
-        <v>46293</v>
-      </c>
-      <c r="G68">
-        <v>5</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R68">
-        <v>1</v>
-      </c>
-      <c r="S68">
-        <v>13262</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="X68" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="Y68" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA68">
-        <v>12</v>
-      </c>
-      <c r="AB68" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF68" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG68" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH68" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI68" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AJ68" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C69" t="s">
-        <v>98</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F69" s="1">
-        <v>46293</v>
-      </c>
-      <c r="G69">
-        <v>6</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R69">
-        <v>1</v>
-      </c>
-      <c r="S69">
-        <v>13262</v>
-      </c>
-      <c r="T69" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V69" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W69" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="X69" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="Y69" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA69">
-        <v>16</v>
-      </c>
-      <c r="AB69" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC69" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD69" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF69" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AG69" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH69" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI69" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ69" s="2" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B80C9D-6A50-4811-B826-A60C50996539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48405831-94E8-4101-A2C1-4AE4715D4867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="390">
   <si>
     <t>Canal</t>
   </si>
@@ -244,12 +244,6 @@
     <t>SSPH</t>
   </si>
   <si>
-    <t>Impresiones locales</t>
-  </si>
-  <si>
-    <t>Lourdes Naranjo</t>
-  </si>
-  <si>
     <t>Contraloría</t>
   </si>
   <si>
@@ -283,9 +277,6 @@
     <t>Julio Menchaca Salazar</t>
   </si>
   <si>
-    <t>Huejutla</t>
-  </si>
-  <si>
     <t>Cultura</t>
   </si>
   <si>
@@ -313,132 +304,27 @@
     <t>Bienestar</t>
   </si>
   <si>
-    <t>Atitalaquia</t>
-  </si>
-  <si>
     <t>Combate Al Huachicol</t>
   </si>
   <si>
     <t>SSPH, PGJEH</t>
   </si>
   <si>
-    <t>Alejandro Reyes</t>
-  </si>
-  <si>
-    <t>Proyectos Ferroviarios</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar Gómez</t>
-  </si>
-  <si>
     <t>Combate Al Narcomenudeo</t>
   </si>
   <si>
     <t>Carmen Hernández</t>
   </si>
   <si>
-    <t>PGJEH, SESNSP</t>
-  </si>
-  <si>
-    <t>Martha Sáenz</t>
-  </si>
-  <si>
-    <t>Reportaje</t>
-  </si>
-  <si>
-    <t>Destacan récord de empleo y ruta hacia las 40 horas</t>
-  </si>
-  <si>
-    <t>El secretario del Trabajo reportó 60.7 millones de personas ocupadas en agosto y una recuperación del salario mínimo real del 154%, avanzando hacia la reducción gradual de la jornada laboral.</t>
-  </si>
-  <si>
-    <t>CDMX</t>
-  </si>
-  <si>
-    <t>Periódico impreso</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Ley 40 horas</t>
-  </si>
-  <si>
-    <t>La STPS informó sobre la cifra récord de empleos y el esquema gradual para disminuir la jornada de trabajo de 48 a 40 horas.</t>
-  </si>
-  <si>
-    <t>Mauricio Bautista</t>
-  </si>
-  <si>
-    <t>STPSH</t>
-  </si>
-  <si>
-    <t>Presidencia de la República</t>
-  </si>
-  <si>
-    <t>Marath Bolaños</t>
-  </si>
-  <si>
-    <t>Gobierno renovará la nave antigua del pabellón artesanal</t>
-  </si>
-  <si>
-    <t>La Sebiso proyecta para 2027 la modernización de la nave vieja del pabellón artesanal en la Feria Pachuca con una inversión estimada menor a 6 millones de pesos.</t>
-  </si>
-  <si>
-    <t>Sebiso anunció la remodelación integral del pabellón artesanal antiguo de la Feria de Pachuca para corregir fallas eléctricas y de infraestructura.</t>
-  </si>
-  <si>
-    <t>Fonart, OEEH</t>
-  </si>
-  <si>
     <t>Ricardo Gómez Moreno</t>
   </si>
   <si>
-    <t>Baja tarifa de estacionamiento en la Feria de San Francisco</t>
-  </si>
-  <si>
-    <t>La OEEH informó la reducción del costo de estacionamiento de 150 a 120 pesos en el recinto ferial tras peticiones ciudadanas; reportan 55 mil visitantes con saldo blanco.</t>
-  </si>
-  <si>
-    <t>La concesionaria del estacionamiento de la Feria de Pachuca ajustó su tarifa a 120 pesos, registrando gran afluencia en atracciones.</t>
-  </si>
-  <si>
-    <t>SSPH, Protección Civil, Cruz Roja</t>
-  </si>
-  <si>
-    <t>Marco Antonio Aranzábal Juárez</t>
-  </si>
-  <si>
-    <t>Hidalgo es cuarto lugar nacional en filmaciones</t>
-  </si>
-  <si>
-    <t>Hidalgo acumuló 101 producciones audiovisuales filmadas en su territorio sin otorgar incentivos económicos, impulsando el turismo de pantalla y la economía local.</t>
-  </si>
-  <si>
-    <t>Producción audiovisual</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo destacó la atracción de 101 proyectos cinematográficos y de televisión en el estado gracias a facilidades logísticas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública</t>
-  </si>
-  <si>
     <t>El Sol de Hidalgo</t>
   </si>
   <si>
-    <t>Apuesta Menchaca por coordinación interestatal</t>
-  </si>
-  <si>
-    <t>Durante la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad, el gobernador Julio Menchaca refrendó el compromiso de Hidalgo para fortalecer el trabajo conjunto con la Federación, estados vecinos y municipios para garantizar la seguridad.</t>
-  </si>
-  <si>
     <t>Coordinación interestatal</t>
   </si>
   <si>
-    <t>El gobernador Julio Menchaca refrendó el compromiso de Hidalgo para fortalecer la coordinación con la Federación y estados vecinos en materia de seguridad.</t>
-  </si>
-  <si>
     <t>Nota principal</t>
   </si>
   <si>
@@ -448,868 +334,889 @@
     <t>Gobierno</t>
   </si>
   <si>
-    <t>Gobierno, Presidencia, SSPH</t>
-  </si>
-  <si>
-    <t>Exponen talento artesanal</t>
-  </si>
-  <si>
-    <t>Artesanas de Tenango de Doria y Chilcuautla participan en el Pabellón Artesanal de la Feria San Francisco Pachuca 2026 para exhibir y comercializar sus bordados y productos tradicionales.</t>
-  </si>
-  <si>
-    <t>Apoyo a artesanos</t>
-  </si>
-  <si>
-    <t>Artesanas hidalguenses exhiben y comercializan sus creaciones en el Pabellón Artesanal de la Feria San Francisco Pachuca 2026.</t>
-  </si>
-  <si>
-    <t>DIFH</t>
-  </si>
-  <si>
-    <t>DIFH, Turismo</t>
-  </si>
-  <si>
-    <t>Angélica María Benito, Romana San Pedro</t>
-  </si>
-  <si>
-    <t>Estacionamiento en feria baja su precio</t>
-  </si>
-  <si>
-    <t>Atendiendo sugerencias del público, la empresa concesionaria del estacionamiento de la Feria Pachuca 2026 redujo el costo de cobro por vehículo de 150 a 120 pesos.</t>
-  </si>
-  <si>
-    <t>Tarifario Feria Pachuca</t>
-  </si>
-  <si>
-    <t>La tarifa del estacionamiento de la Feria San Francisco Pachuca disminuyó de 150 a 120 pesos tras atender solicitudes de los usuarios.</t>
-  </si>
-  <si>
-    <t>OEEH, Turismo</t>
-  </si>
-  <si>
-    <t>Pide Protección Civil ubicar salidas</t>
-  </si>
-  <si>
-    <t>La Subsecretaría de Protección Civil emitió recomendaciones preventivas para los asistentes a la Feria Pachuca 2026, destacando la importancia de ubicar salidas de emergencia.</t>
-  </si>
-  <si>
     <t>Prevención De Riesgos</t>
   </si>
   <si>
-    <t>Protección Civil de Hidalgo emitió una serie de recomendaciones para garantizar la seguridad de las familias en la Feria Pachuca 2026.</t>
-  </si>
-  <si>
-    <t>Gustavo Vargas</t>
-  </si>
-  <si>
-    <t>Segobh, PC</t>
-  </si>
-  <si>
-    <t>Huasca: 25 años como Pueblo Mágico</t>
-  </si>
-  <si>
-    <t>Huasca de Ocampo conmemorará un cuarto de siglo de haber sido distinguido como el primer Pueblo Mágico de México con un programa de eventos culturales y gastronómicos.</t>
-  </si>
-  <si>
-    <t>Huasca</t>
-  </si>
-  <si>
-    <t>Pueblos Mágicos</t>
-  </si>
-  <si>
-    <t>El municipio de Huasca festejara 25 años de su acreditación como el primer Pueblo Mágico del país.</t>
-  </si>
-  <si>
-    <t>Obras de trenes extienden oportunidades económicas</t>
-  </si>
-  <si>
-    <t>El titular de la Uplaph destacó que la infraestructura ferroviaria impulsará el desarrollo regional, enfatizando la importancia de un crecimiento urbano ordenado.</t>
-  </si>
-  <si>
-    <t>Planeación estatal resalta la oportunidad de detonar polos de desarrollo mediante las obras de interconexión ferroviaria.</t>
-  </si>
-  <si>
-    <t>Planeación, Uplaph</t>
-  </si>
-  <si>
     <t>Miguel Ángel Tello Vargas</t>
   </si>
   <si>
-    <t>Buscan a jóvenes en Tlanchinol</t>
-  </si>
-  <si>
-    <t>La PGJEH difundió alertas institucionales para dar con el paradero de dos menores de 15 años vistos por última vez en el municipio de Tlanchinol.</t>
-  </si>
-  <si>
     <t>Tlanchinol</t>
   </si>
   <si>
     <t>Desapariciones</t>
   </si>
   <si>
-    <t>Autoridades solicitaron colaboración social para la pronta localización de dos adolescentes en Tlanchinol.</t>
-  </si>
-  <si>
     <t>Rubén Juárez</t>
   </si>
   <si>
-    <t>Dulce Gabriela Hernández de la Cruz, Cristian Jovany Hernández Hernández</t>
-  </si>
-  <si>
-    <t>Destrucción de túneles; nueva era del combate al huachicol</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca afirmó que el aseguramiento y destrucción de túneles usados para el robo de combustible representa un hecho histórico en Hidalgo. Entre junio y septiembre de 2026 han sido eliminados 17 túneles en trabajo coordinado con la Sedena y Guardia Nacional.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca destaca la eliminación de 17 túneles huachicoleros en Hidalgo entre junio y septiembre de 2026 como una acción sin precedente.</t>
-  </si>
-  <si>
-    <t>Equipo Milenio</t>
-  </si>
-  <si>
-    <t>Gobierno de Hidalgo, Sedena, Guardia Nacional, Pemex, FGR</t>
-  </si>
-  <si>
-    <t>Vende terreno 9 veces más caro a empresa sancionada</t>
-  </si>
-  <si>
-    <t>La senadora priista Carolina Viggiano Austria compró en 2011 un terreno de 7.16 hectáreas en Zempoala por 2 millones de pesos y lo vendió en 2018 por 17.9 millones a JERGUI, empresa de los hermanos Segura Zerecero sancionada por la Contraloría.</t>
-  </si>
-  <si>
-    <t>Zempoala</t>
-  </si>
-  <si>
-    <t>Investigación por corrupción</t>
-  </si>
-  <si>
-    <t>Documentos revelan que Carolina Viggiano vendió un predio en Zempoala por 17.9 mdp a la empresa JERGUI, que obtuvo contratos estatales y fue sancionada por la Contraloría.</t>
-  </si>
-  <si>
-    <t>Contraloría, PRI</t>
-  </si>
-  <si>
-    <t>Carolina Viggiano Austria, Omar Guillermo Segura Zerecero, Enrique Segura Zerecero, Nidia Segura Zerecero</t>
-  </si>
-  <si>
-    <t>Asisten a la Feria San Francisco más de 55 mil en 4 días</t>
-  </si>
-  <si>
-    <t>Más de 55 mil personas han acudido a la Feria San Francisco Pachuca Hidalgo durante sus primeros cuatro días de actividades. El circo, espectáculo sobre hielo, lucha libre y actividades infantiles concentran la mayor afluencia.</t>
-  </si>
-  <si>
-    <t>La Feria San Francisco Pachuca registra una afluencia superior a los 55 mil visitantes en sus primeros cuatro días con saldo blanco en el palenque y ocupación hotelera del 64%.</t>
-  </si>
-  <si>
-    <t>OEEH</t>
-  </si>
-  <si>
-    <t>OEEH, Turismo, Bienestar</t>
-  </si>
-  <si>
-    <t>Marco Antonio Aranzábal Juárez, Elizabeth Quintanar Gómez, Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>Artesanos alcanzan 6 mdp por comercio en el recinto</t>
-  </si>
-  <si>
-    <t>Artesanos que participan en la Feria San Francisco aumentaron sus ventas de menos de 800 mil pesos al inicio de la administración a 6 millones de pesos actualizados. El gobierno estatal invirtió más de 6.5 mdp para remodelar el pabellón artesanal.</t>
-  </si>
-  <si>
-    <t>Ventas de artesanos en la Feria San Francisco se elevan a 6 mdp tras la remodelación del pabellón artesanal con una inversión estatal de 6.5 mdp.</t>
-  </si>
-  <si>
-    <t>Bienestar, OEEH</t>
-  </si>
-  <si>
-    <t>Marco Antonio Aranzábal Juárez, Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>Operadora de Eventos dejó cifra roja; ahora devuelve hasta 6 mdp</t>
-  </si>
-  <si>
-    <t>La Operadora de Eventos del Estado de Hidalgo pasó de operar con números rojos y adeudos a devolver más de 6 millones de pesos al cierre de cada año al gobierno estatal gracias a la autosuficiencia y regularización comercial.</t>
-  </si>
-  <si>
-    <t>Finanzas públicas</t>
-  </si>
-  <si>
-    <t>La OEEH se consolidó como un organismo autosuficiente financiero que regresa más de 6 mdp anuales a las arcas del estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>OEEH, Secretaría de Finanzas</t>
-  </si>
-  <si>
-    <t>Violación a intimidad registra 239 carpetas</t>
-  </si>
-  <si>
-    <t>Hidalgo se ubica entre los 12 estados del país con mayor número de carpetas de investigación por violación a la intimidad sexual al acumular 239 denuncias entre enero y agosto de 2026. Pachuca encabeza la lista municipal con 56 carpetas.</t>
-  </si>
-  <si>
-    <t>Violencia De Género</t>
-  </si>
-  <si>
-    <t>Hidalgo acumula 239 carpetas de investigación por violación a la intimidad sexual en 56 municipios de la entidad, liderando Pachuca y Tizayuca.</t>
-  </si>
-  <si>
-    <t>Resaltan coordinación contra los criminales</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca afirmó que el aseguramiento de túneles huachicoleros representa un hecho histórico. Entre junio y septiembre de 2026 se eliminaron 17 túneles en trabajo coordinado con Sedena, Guardia Nacional, Pemex y FGR.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca resalta la estrategia coordinada con fuerzas federales para destruir 17 túneles usados para el robo de combustible a Pemex en Hidalgo.</t>
-  </si>
-  <si>
-    <t>Gobierno de Hidalgo, Sedena, Guardia Nacional, Pemex, FGR, PGJEH, SSPH</t>
-  </si>
-  <si>
-    <t>Huasca, 25 años como el primer Pueblo Mágico</t>
-  </si>
-  <si>
-    <t>Huasca de Ocampo celebrará sus 25 años como el primer Pueblo Mágico de México el próximo 5 de octubre con un programa de actividades culturales, gastronómicas y artesanales junto a los 9 destinos hidalguenses.</t>
-  </si>
-  <si>
-    <t>Huasca de Ocampo</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo anuncia los festejos conmemorativos por el 25 aniversario del nombramiento de Huasca de Ocampo como el primer Pueblo Mágico del país.</t>
-  </si>
-  <si>
-    <t>El estado obtiene presencia nacional con 101 filmaciones</t>
-  </si>
-  <si>
-    <t>Hidalgo se ubica en el cuarto lugar nacional en actividad cinematográfica con 101 proyectos filmados en su territorio, ofreciendo facilidades logísticas, acompañamiento institucional y seguridad a las productoras.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo destaca que Hidalgo se posicionó en cuarto lugar nacional de filmaciones cinematográficas y televisivas con 101 proyectos.</t>
-  </si>
-  <si>
-    <t>Siete muertes maternas en nueve meses</t>
-  </si>
-  <si>
-    <t>Durante los primeros nueve meses de 2026, Hidalgo acumula siete muertes maternas registradas en municipios como Zempoala, Tula, Tasquillo, Pacula, Jaltocán, Acatlán y Tulancingo, superando la cifra de 2025.</t>
-  </si>
-  <si>
-    <t>Salud pública</t>
-  </si>
-  <si>
-    <t>Hidalgo suma siete fallecimientos de mujeres por causas maternas entre enero y septiembre de 2026, según el reporte semanal de la Secretaría de Salud federal.</t>
-  </si>
-  <si>
-    <t>Breve</t>
-  </si>
-  <si>
-    <t>SSH, Salud Federal</t>
-  </si>
-  <si>
-    <t>Acuerdan trabajo coordinado en seguridad</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca participó en la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad junto con autoridades de Edomex, Guerrero, Morelos y CDMX para reforzar la estrategia regional.</t>
-  </si>
-  <si>
-    <t>Gobierno, Segobh, SSPH</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Evelyn Salgado Pineda, Delfina Gómez Álvarez, Margarita González Saravia, Clara Brugada Molina</t>
-  </si>
-  <si>
-    <t>Huasca: un cuarto de siglo como primer Pueblo Mágico</t>
-  </si>
-  <si>
-    <t>El municipio de Huasca de Ocampo celebrará 25 años como el primer Pueblo Mágico de México con un programa de actividades culturales, artesanales y gastronómicas en octubre.</t>
-  </si>
-  <si>
     <t>Lorena Rosas</t>
   </si>
   <si>
-    <t>Turismo, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar Gómez, Josefina Rodríguez Zamora</t>
-  </si>
-  <si>
-    <t>Baja a 120 pesos estacionamiento de la feria</t>
-  </si>
-  <si>
-    <t>Tras solicitudes de la OEEH ante inconformidades de los asistentes, la empresa concesionaria del estacionamiento de la Feria de Pachuca redujo su tarifa de 150 a 120 pesos.</t>
-  </si>
-  <si>
-    <t>OEEH, PGJEH</t>
-  </si>
-  <si>
-    <t>Rehabilitarán antigua nave de la feria el próximo año: Sebiso</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social proyecta para 2027 una intervención integral en la antigua nave de la Feria de Pachuca para renovar pisos, estructura y sistema eléctrico.</t>
-  </si>
-  <si>
-    <t>Bienestar, Sipdus</t>
-  </si>
-  <si>
-    <t>Buscan 75 enfermeros trabajar en Alemania; hay 30 vacantes abiertas</t>
-  </si>
-  <si>
-    <t>La STPSH coordina la jornada nacional de reclutamiento laboral para enfermeros que buscan laborar en Alemania, registrando 75 aspirantes para 30 plazas disponibles.</t>
-  </si>
-  <si>
-    <t>Movilidad laboral</t>
-  </si>
-  <si>
-    <t>Oscar Javier González Hernández</t>
-  </si>
-  <si>
-    <t>Clausuran túnel y cinco tomas clandestinas</t>
-  </si>
-  <si>
-    <t>Operativos del Gabinete de Seguridad de Hidalgo en Atitalaquia, Pachuca y la región Tula-Tepeji permitieron el aseguramiento de un huachitúnel, cinco tomas clandestinas y 20 mil litros de combustible.</t>
-  </si>
-  <si>
     <t>Gabinete de Seguridad</t>
   </si>
   <si>
-    <t>Gabinete de Seguridad, Pemex, SSPH</t>
-  </si>
-  <si>
-    <t>Detienen en Argentina a hija de Gerardo Sosa</t>
-  </si>
-  <si>
-    <t>Ana Carmen Sosa Cravioto fue detenida en un aeropuerto de Mendoza, Argentina, en atención a una alerta roja de Interpol relacionada con una investigación de la FGR por lavado de dinero.</t>
-  </si>
-  <si>
-    <t>Gerardo Sosa</t>
-  </si>
-  <si>
-    <t>Víctor Valera</t>
-  </si>
-  <si>
-    <t>FGR, UAEH, Interpol</t>
-  </si>
-  <si>
-    <t>Gerardo Sosa Castelán</t>
-  </si>
-  <si>
-    <t>Fortalecen atención médica con Ecosistema Digital en Salud</t>
-  </si>
-  <si>
-    <t>Los 18 hospitales del IMSS Bienestar en Hidalgo implementaron la plataforma Pheds y el módulo Moce para digitalizar historiales clínicos y agilizar expedientes de pacientes.</t>
-  </si>
-  <si>
-    <t>IMSS Bienestar</t>
-  </si>
-  <si>
-    <t>SSH, IMSS Bienestar</t>
-  </si>
-  <si>
-    <t>Mireya Gutiérrez García</t>
-  </si>
-  <si>
-    <t>Hidalgo suma siete denuncias por aborto en lo que va del año</t>
-  </si>
-  <si>
-    <t>Colectivas feministas exigieron garantizar la no criminalización de las mujeres en Hidalgo tras registrarse siete carpetas de investigación por el delito de aborto en 2026.</t>
-  </si>
-  <si>
-    <t>Aborto</t>
-  </si>
-  <si>
-    <t>PGJEH, SSH</t>
-  </si>
-  <si>
-    <t>Preparan Expo Oliva 2026 este fin de semana, en Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Productores de la comunidad El Olivo en Ixmiquilpan anunciaron la Expo Oliva 2026 con recorridos a huertos, catas de aceite extra virgen y conferencias técnicas.</t>
-  </si>
-  <si>
     <t>Ixmiquilpan</t>
   </si>
   <si>
-    <t>Expo Agroalimentaria</t>
-  </si>
-  <si>
-    <t>Erika Gutiérrez</t>
-  </si>
-  <si>
-    <t>Saderh, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Capturan a 2 por posesión de dogas en Actopan</t>
-  </si>
-  <si>
-    <t>Seguridad Pública de Actopan y la Policía estatal aprehendieron a una mujer y un menor de edad a bordo de una motocicleta portando 27 dosis de presunto cristal.</t>
-  </si>
-  <si>
     <t>Actopan</t>
   </si>
   <si>
-    <t>Realizan operativo vs. violencia de género</t>
-  </si>
-  <si>
-    <t>Elementos de seguridad de Tizayuca, Temascalapa y Zumpango implementaron el operativo Violeta Red Segura en limites territoriales para prevenir agresiones en transporte público.</t>
-  </si>
-  <si>
-    <t>Tizayuca</t>
-  </si>
-  <si>
     <t>Javier Quezada</t>
   </si>
   <si>
-    <t>SSPH, Segobh</t>
-  </si>
-  <si>
-    <t>Menchaca destaca combate al huachicol en reunión interestatal de paz y seguridad</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar participó en la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad en Morelos, destacando las acciones para combatir el robo de combustible que afecta a 22 municipios por donde atraviesan más de 900 kilómetros de ductos de Pemex.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca refrendó el compromiso de Hidalgo en la Séptima Reunión Interestatal de Seguridad para combatir el huachicol en los 22 municipios afectados por ductos de Pemex.</t>
-  </si>
-  <si>
     <t>Veida Miranda</t>
   </si>
   <si>
-    <t>Gobierno, Pemex</t>
-  </si>
-  <si>
-    <t>Feria San Francisco supera 55 mil visitantes; baja costo de estacionamiento</t>
-  </si>
-  <si>
-    <t>Tras inconformidades ciudadanas, la tarifa de estacionamiento en la Feria San Francisco Pachuca 2026 bajó de 150 a 120 pesos en tiempo libre. El director de la OEEH reportó más de 55 mil visitantes en los primeros cuatro días y saldo blanco.</t>
-  </si>
-  <si>
-    <t>La OEEH anunció la reducción del costo de estacionamiento en la Feria Pachuca a 120 pesos tras quejas de usuarios; además reportan 55 mil visitantes con saldo blanco.</t>
-  </si>
-  <si>
-    <t>A más de 5 años de la despenalización, persisten barreras para el aborto seguro en Hidalgo</t>
-  </si>
-  <si>
-    <t>Organizaciones civiles advierten que persisten deficiencias en las instituciones públicas que dificultan el acceso efectivo y seguro al aborto en Hidalgo, citando falta de insumos, personal capacitado y estigmas en municipios del norte del estado.</t>
-  </si>
-  <si>
-    <t>A cinco años de la despenalización del aborto en Hidalgo, la organización SEIINAC señala que persisten barreras de salud, falta de insumos y estigmas en municipios del norte.</t>
-  </si>
-  <si>
-    <t>SSH, SEIINAC</t>
-  </si>
-  <si>
-    <t>Lizeth Clavellina</t>
-  </si>
-  <si>
-    <t>Detienen en Argentina a hija de Gerardo Sosa Castelán</t>
-  </si>
-  <si>
-    <t>Ana Carmen Sosa Cravioto, hija de Gerardo Sosa Castelán, fue detenida en el aeropuerto de Mendoza, Argentina, debido a una notificación roja de la Interpol por delincuencia organizada y operaciones con recursos de procedencia ilícita.</t>
-  </si>
-  <si>
-    <t>Autoridades argentinas arrestaron a la hija de Gerardo Sosa Castelán en el aeropuerto de Mendoza por ficha roja de Interpol; seguirá el proceso bajo prisión domiciliaria.</t>
-  </si>
-  <si>
-    <t>UAEH, FGR, Interpol</t>
-  </si>
-  <si>
-    <t>Ana Carmen Sosa Cravioto, Gerardo Sosa Castelán</t>
-  </si>
-  <si>
-    <t>La entidad, entre los estados con más hurtos a taxi, suman 68 casos</t>
-  </si>
-  <si>
-    <t>Hidalgo se ubicó en el séptimo lugar nacional por cantidad de denuncias de robo a transporte público individual durante agosto con cinco carpetas, acumulando 68 querellas en lo que va del año.</t>
-  </si>
-  <si>
-    <t>Robo de taxi</t>
-  </si>
-  <si>
-    <t>Cifras del SESNSP situaron a Hidalgo en el séptimo lugar nacional en robos a taxis con 68 carpetas de investigación acumuladas en 2026.</t>
-  </si>
-  <si>
-    <t>Revisan la elección sindical municipal</t>
-  </si>
-  <si>
-    <t>El Tribunal de Arbitraje analiza la documentación de la elección en el SUTSMP de Pachuca para determinar si otorga la toma de nota a la planilla azul encabezada por Irma María de Jesús López Arroyo.</t>
-  </si>
-  <si>
-    <t>SUTSMP</t>
-  </si>
-  <si>
-    <t>La STPSH informó que el Tribunal de Arbitraje revisa la legalidad del proceso electivo del sindicato de Pachuca previo a otorgar la toma de nota a la planilla ganadora.</t>
-  </si>
-  <si>
-    <t>Lizania Zavala</t>
-  </si>
-  <si>
-    <t>STPSH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Óscar Javier González Hernández, Irma María de Jesús López Arroyo, Pablo Anaya García</t>
-  </si>
-  <si>
-    <t>Hidalgo, entre los estados con tarifa fija para los taxis</t>
-  </si>
-  <si>
-    <t>Con la actualización a 45 pesos para la tarifa mínima, Hidalgo se ubica entre las pocas entidades del centro del país con esquema definido, destacando por ser la única sin plataformas digitales como Uber o DiDi.</t>
-  </si>
-  <si>
     <t>Tarifario de taxis</t>
   </si>
   <si>
-    <t>Hidalgo cuenta con un esquema de tarifa fija de 45 pesos para transporte individual, situándose como la única entidad de la región sin servicio de plataformas digitales.</t>
-  </si>
-  <si>
-    <t>Coloca STPSH a trabajadores en Canadá, EU y otros estados</t>
-  </si>
-  <si>
-    <t>El titular de la STPSH, Óscar Javier González, reportó la vinculación laboral de 3 mil 400 hidalguenses en Canadá, 39 en Estados Unidos y más de 3 mil en otras entidades federativas.</t>
-  </si>
-  <si>
-    <t>La Secretaría del Trabajo estatal destacó la colocación de miles de trabajadores hidalguenses en el extranjero y diversos estados del país mediante programas de movilidad laboral.</t>
-  </si>
-  <si>
-    <t>Óscar Javier González Hernández</t>
-  </si>
-  <si>
-    <t>Anuncia la OEEH la disminución del costo en el estacionamiento</t>
-  </si>
-  <si>
-    <t>Tras escuchar comentarios del público, la OEEH acordó con la concesionaria reducir de 150 a 120 pesos la tarifa por tiempo libre del estacionamiento de la Feria de San Francisco 2026.</t>
-  </si>
-  <si>
-    <t>La Operadora de Eventos de Hidalgo informó la reducción de la tarifa del estacionamiento ferial a 120 pesos tras acuerdos con la empresa prestadora del servicio.</t>
-  </si>
-  <si>
-    <t>Turismo, OEEH</t>
-  </si>
-  <si>
-    <t>Coordinación es la respuesta para paz y seguridad</t>
-  </si>
-  <si>
-    <t>En la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad, el gobernador Julio Menchaca reiteró la alianza con el gobierno federal y estados vecinos para inhibir el delito e impulsar el combate al huachicol.</t>
-  </si>
-  <si>
-    <t>Durante la reunión interestatal de seguridad en Morelos, el gobernador Menchaca destacó las acciones coordinadas para la detección de huachitúneles e inhibición de delitos.</t>
-  </si>
-  <si>
-    <t>Gobierno, Sedena, GN, Pemex</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Delfina Gómez Álvarez, Clara Brugada Molina, Margarita González Saravia, Evelyn Salgado Pineda</t>
-  </si>
-  <si>
-    <t>Exploran la perforación de pozo para Atotonilco</t>
-  </si>
-  <si>
-    <t>La SIPDUS realiza estudios de exploración en La Cañada, Atotonilco de Tula, para determinar la viabilidad de perforar un nuevo pozo que refuerce la red hídrica local.</t>
-  </si>
-  <si>
-    <t>Atotonilco de Tula</t>
-  </si>
-  <si>
-    <t>Perforación de pozo</t>
-  </si>
-  <si>
-    <t>La Sipdus inició pruebas de prospección hidráulica en Atotonilco de Tula para evaluar la factibilidad de perforar un pozo de agua potable.</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Advierten disminución de nutrias en la Huasteca</t>
-  </si>
-  <si>
-    <t>Ambientalistas alertan sobre la drástica reducción de avistamientos del perro de agua en ríos de la Huasteca debido a la contaminación, cacería desmedida y alteración de cauces.</t>
-  </si>
-  <si>
-    <t>Atlapexco</t>
-  </si>
-  <si>
     <t>Conservación de especies</t>
   </si>
   <si>
-    <t>Grupos ecologistas advierten sobre el riesgo de desaparición de la nutria de río en cauces de la Huasteca por la degradación ambiental y cacería.</t>
-  </si>
-  <si>
-    <t>Salomón Hernández</t>
-  </si>
-  <si>
-    <t>Eusebio León</t>
-  </si>
-  <si>
-    <t>Vecinos llevan a la PGJEH las anomalías en un bulevar</t>
-  </si>
-  <si>
-    <t>Colonos del bulevar López Mateos en Huejutla solicitaron avances sobre la denuncia interpuesta ante la PGJEH por presuntas anomalías en el asfaltado ejecutado en el gobierno de Daniel Andrade.</t>
-  </si>
-  <si>
-    <t>Vecinos de Huejutla dieron seguimiento a la denuncia contra la administración del exalcalde Daniel Andrade por la mala calidad y deficiencias técnicas en la pavimentación del bulevar López Mateos.</t>
-  </si>
-  <si>
     <t>PGJEH, Ayuntamiento</t>
   </si>
   <si>
-    <t>Briseyda Torres, Daniel Andrade Zurutuza</t>
-  </si>
-  <si>
-    <t>Esperan taxistas que se aplique el ajuste de los costos del servicio</t>
-  </si>
-  <si>
-    <t>Concesionarios del transporte público en la Huasteca esperan que la Semot autorice el nuevo tarifario antes del Xantolo para incluir colonias de reciente creación.</t>
-  </si>
-  <si>
-    <t>Cuerpos de transporte individual en Huejutla solicitaron la pronta actualización del tarifario regional ante el alza en refacciones e insumos operacionales.</t>
-  </si>
-  <si>
-    <t>José Almeyda, Gregorio Zamora Ramírez</t>
-  </si>
-  <si>
-    <t>Huasca conmemorará 25 años como Pueblo Mágico</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo anunció que Huasca celebrará un cuarto de siglo con el nombramiento de primer Pueblo Mágico de México con proyecciones de videomapping y muestras artesanales.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo de Hidalgo presentó el programa conmemorativo por los 25 años de Huasca como el primer Pueblo Mágico del país.</t>
-  </si>
-  <si>
-    <t>Plantan 2 mil árboles en jornada ambiental de Mineral del Chico</t>
-  </si>
-  <si>
-    <t>Voluntarios de la empresa Henkel y el Geoparque Comarca Minera sembraron dos mil árboles en El Cedral como parte de una jornada de geoeducación y reforestación.</t>
-  </si>
-  <si>
-    <t>Mineral del Chico</t>
-  </si>
-  <si>
-    <t>Reforestación</t>
-  </si>
-  <si>
-    <t>Una brigada ambiental del Geoparque Comarca Minera y la iniciativa privada plantó dos mil árboles en ejidos de Mineral del Chico.</t>
-  </si>
-  <si>
-    <t>Realiza IHE Congreso Estatal</t>
-  </si>
-  <si>
-    <t>El Instituto Hidalguense de Educación llevó a cabo el primer Congreso Estatal "Juntos por la Convivencia Escolar" enfocado en prevenir la violencia y promover ambientes seguros.</t>
-  </si>
-  <si>
     <t>Convivencia Escolar</t>
   </si>
   <si>
-    <t>El IHE reunió a especialistas y comunidades educativas en un congreso estatal orientado a erradicar la violencia y fomentar valores de respeto en los planteles.</t>
-  </si>
-  <si>
-    <t>SEPH, IHE, CDHEH, Segobh, PGJEH</t>
-  </si>
-  <si>
-    <t>Coordinación de estados, para la paz y seguridad</t>
-  </si>
-  <si>
-    <t>En el marco de la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad entre autoridades de Hidalgo, Estado de México, Ciudad de México, Guerrero y Morelos, el gobernador Julio Menchaca Salazar renovó el compromiso de trabajar en colaboración.</t>
-  </si>
-  <si>
-    <t>En la Séptima Reunión de Coordinación Interestatal de Paz y Seguridad, el gobernador Julio Menchaca renovó el compromiso para trabajar con la federación y estados vecinos.</t>
-  </si>
-  <si>
-    <t>Gobierno, Sedena, Guardia Nacional</t>
-  </si>
-  <si>
-    <t>Gabinete de seguridad anunció resultados de la semana</t>
-  </si>
-  <si>
-    <t>Un túnel localizado, 5 tomas clandestinas clausuradas y más de 20 mil litros de combustible recuperados fue resultado de operativos del Gabinete de Seguridad de Hidalgo en combate al robo de hidrocarburo.</t>
-  </si>
-  <si>
-    <t>El Gabinete de Seguridad de Hidalgo informó sobre la localización de un túnel, la clausura de cinco tomas clandestinas y la recuperación de más de 20 mil litros de hidrocarburo.</t>
-  </si>
-  <si>
-    <t>Cayó en Argentina hija de Gerardo Sosa, iba a volar a Chile</t>
-  </si>
-  <si>
-    <t>En el aeropuerto de Ciudad Mendoza, Argentina, fue asegurada la empresaria mexicana Ana Carmen S. C., hija de Gerardo Sosa Castelán, ex rector de la UAEH, quien contaba con ficha roja de la Interpol.</t>
-  </si>
-  <si>
-    <t>Ana Carmen S. C., hija del exrector de la UAEH Gerardo Sosa Castelán, fue detenida en Argentina tras contar con ficha roja de Interpol por delincuencia organizada y lavado de dinero.</t>
-  </si>
-  <si>
-    <t>PGJEH, UAEH, Interpol</t>
-  </si>
-  <si>
-    <t>Ana Carmen S. C., Gerardo Sosa Castelán</t>
-  </si>
-  <si>
-    <t>Aseguran a 3 sujetos por robo a negocio</t>
-  </si>
-  <si>
-    <t>Como resultado de las acciones de combate al delito efectuadas por la SSPH, se logró la detención de tres hombres por su participación en el asalto a una tienda de alimento para mascotas en Epazoyucan.</t>
-  </si>
-  <si>
-    <t>Epazoyucan</t>
-  </si>
-  <si>
-    <t>Robo a comercio</t>
-  </si>
-  <si>
-    <t>Elementos de la SSPH apresaron a tres hombres que asaltaron una tienda de alimentos para mascotas en Epazoyucan tras una persecución apoyada por el C5i.</t>
-  </si>
-  <si>
-    <t>SSPH, C5i</t>
-  </si>
-  <si>
-    <t>Reconocen a Hidalgo por atracción de casas productoras</t>
-  </si>
-  <si>
-    <t>La titular de la Secretaría de Turismo de Hidalgo, Elizabeth Quintanar, informó que Hidalgo fue reconocido a nivel nacional por la atracción de casas productoras para la grabación de proyectos cinematográficos.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo destacó que Hidalgo se ubica en el cuarto lugar nacional con 101 producciones cinematográficas y audiovisuales filmadas en la entidad.</t>
-  </si>
-  <si>
     <t>Ana Luisa Vega</t>
   </si>
   <si>
-    <t>Presentarán proyecto para remodelar la Nave Antigua de la Feria</t>
-  </si>
-  <si>
-    <t>El titular de la Sebiso, Ricardo Gómez Moreno, adelantó que en breve presentarán un proyecto para la remodelación de la Nave Antigua del recinto ferial para albergar a artesanos en 2027.</t>
-  </si>
-  <si>
-    <t>La Sebiso proyecta la modernización de la Nave Antigua del recinto ferial para albergar a los artesanos participantes en la Feria Pachuca 2027.</t>
-  </si>
-  <si>
-    <t>Saldo blanco en los primeros días de Feria</t>
-  </si>
-  <si>
-    <t>A cuatro días del inicio de la Feria San Francisco Pachuca Hidalgo 2026, se reporta saldo blanco y una afluencia de alrededor de 55 mil visitantes, informó Marco Antonio Aranzábal Juárez.</t>
-  </si>
-  <si>
-    <t>La OEEH reportó saldo blanco y más de 55 mil visitantes en los primeros cuatro días de la Feria Pachuca 2026, además de reducir el costo de estacionamiento a 120 pesos.</t>
-  </si>
-  <si>
-    <t>Oscar Raúl Pérez Cabrera</t>
-  </si>
-  <si>
-    <t>Hidalgo llevará música, danza y fotografía a Tamaulipas</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, titular de la Secretaría de Cultura, informó que Hidalgo participará como estado invitado en el trigésimo tercer Festival Internacional en la Costa del Seno Mexicano.</t>
-  </si>
-  <si>
-    <t>Festival Cultural</t>
-  </si>
-  <si>
-    <t>Hidalgo participará como estado invitado en el Festival Internacional en la Costa del Seno Mexicano en Tamaulipas con agrupaciones de música, danza y muestras fotográficas.</t>
-  </si>
-  <si>
     <t>Neyda Naranjo Baltazar</t>
   </si>
   <si>
-    <t>Trabajadores del sector salud piden cambio de jefa jurisdiccional</t>
-  </si>
-  <si>
-    <t>Ante diversos casos de acoso laboral y hostigamiento, empleados de la Jurisdicción Sanitaria de Apan, dependiente de la SSH, realizan su jornada laboral bajo protesta contra Edith Carolina Espinoza Jiménez.</t>
-  </si>
-  <si>
-    <t>Apan</t>
-  </si>
-  <si>
-    <t>Acoso Laboral</t>
-  </si>
-  <si>
-    <t>Trabajadores sindicalizados del sector salud en Apan protestaron pacíficamente exigiendo la destitución de la jefa jurisdiccional por presuntos actos de acoso laboral.</t>
-  </si>
-  <si>
-    <t>Abel Ricardo Flores</t>
-  </si>
-  <si>
-    <t>SSH, SNTSA</t>
-  </si>
-  <si>
-    <t>Edith Carolina Espinoza Jiménez, Sonia Ocampo Chapa</t>
-  </si>
-  <si>
-    <t>Detienen en Sudamérica a la hija de Gerardo Sosa</t>
-  </si>
-  <si>
-    <t>Ana Carmen Sosa Cravioto, hija del exrector de la UAEH Gerardo Sosa Castelán, fue detenida en Mendoza, Argentina, tras activarse una alerta roja de Interpol solicitada por autoridades mexicanas por delincuencia organizada y lavado de dinero.</t>
-  </si>
-  <si>
-    <t>La hija del exrector Gerardo Sosa Castelán fue detenida en Argentina tras activarse una orden de aprehensión e Interpol por delincuencia organizada.</t>
-  </si>
-  <si>
-    <t>PGJEH, FGR, UAEH</t>
-  </si>
-  <si>
-    <t>Ana Carmen Sosa Cravioto, Gerardo Sosa Castelán, Adriana Sosa Cravioto</t>
-  </si>
-  <si>
-    <t>Feria de San Francisco 2026 supera los 50 mil visitantes</t>
-  </si>
-  <si>
-    <t>La Feria San Francisco Hidalgo 2026 registró una afluencia de alrededor de 55 mil visitantes durante sus primeros cuatro días, destacando el Pabellón Artesanal con más de 140 artesanas y artesanos, reportando saldo blanco.</t>
-  </si>
-  <si>
-    <t>La Feria San Francisco Pachuca 2026 registró más de 55 mil asistentes en sus primeros cuatro días con alta actividad artesanal y saldo blanco.</t>
-  </si>
-  <si>
-    <t>Turismo, OEEH, Protección Civil</t>
-  </si>
-  <si>
-    <t>Marco Antonio Aranzábal Juárez, Jorge Alberto Reyes Hernández</t>
-  </si>
-  <si>
-    <t>Bajan 30 pesos a estacionamiento tras quejas</t>
-  </si>
-  <si>
-    <t>Las quejas por el costo del estacionamiento de la Feria llevaron a la Operadora de Eventos del Estado de Hidalgo a reducir la tarifa de 150 a 120 pesos e implementar operativos contra cobros irregulares.</t>
-  </si>
-  <si>
-    <t>La OEEH ajustó a 120 pesos la tarifa del estacionamiento ferial tras inconformidades de los usuarios.</t>
-  </si>
-  <si>
-    <t>Turismo, OEEH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Turismo descarta fuga de visitantes por tráfico</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo de Hidalgo descartó que las obras y el tráfico en la carretera México-Pachuca disminuyan la llegada de visitantes, destacando el flujo en la ocupación hotelera.</t>
-  </si>
-  <si>
-    <t>Afluencia Turística</t>
-  </si>
-  <si>
-    <t>La Secturh rechazó afectaciones turísticas por congestionamiento vial ante la alta ocupación en hoteles de la capital.</t>
-  </si>
-  <si>
-    <t>Recolectarán baterías en jornada de reforestación</t>
-  </si>
-  <si>
-    <t>La Semarnath realizará una jornada de acopio de pilas usadas y plantación de árboles en la Unidad Deportiva Municipal de Pachuca para dar destino adecuado a estos residuos.</t>
-  </si>
-  <si>
-    <t>Semarnath coordinará el viernes una campaña ambiental en Pachuca combinando recolección de pilas y siembra de árboles.</t>
-  </si>
-  <si>
-    <t>Semarnath, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Celebrará Huasca su 25 aniversario como Pueblo Mágico</t>
-  </si>
-  <si>
-    <t>Huasca de Ocampo conmemorará 25 años como Pueblo Mágico con eventos culturales y turísticos. La Secretaría de Turismo destacó además el posicionamiento del estado en producciones audiovisuales.</t>
-  </si>
-  <si>
-    <t>Huasca de Ocampo celebrará sus 25 años como el primer Pueblo Mágico de México con un programa festivo el 5 de octubre.</t>
-  </si>
-  <si>
-    <t>Por severas fallas estructurales, la primaria Aquiles Serdán en Tulancingo será demolida y edificada nuevamente en su totalidad, informó el titular de la SEPH Natividad Castrejón.</t>
-  </si>
-  <si>
-    <t>La SEPH reconstruirá íntegramente la primaria Aquiles Serdán por daños estructurales, evaluando reubicación de alumnos.</t>
-  </si>
-  <si>
     <t>Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Impresos locales</t>
+  </si>
+  <si>
+    <t>Rehabilitación del Jardín Colón costará 5.3 mdp</t>
+  </si>
+  <si>
+    <t>Con un plazo de 185 días naturales, el gobierno del estado arrancó la rehabilitación del Jardín Colón en Pachuca con una inversión superior a los 5.3 millones de pesos a través de SIPDUS, contemplando pisos, iluminación y áreas verdes.</t>
+  </si>
+  <si>
+    <t>Rehabilitación de espacios públicos</t>
+  </si>
+  <si>
+    <t>Arrancaron los trabajos de rehabilitación integral del Jardín Colón en Pachuca con una inversión estatal de 5.3 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Fernanda Huerta</t>
+  </si>
+  <si>
+    <t>Supervisará Protección Civil puestos semifijos</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos de Hidalgo supervisará 120 puestos de comerciantes y artesanos en la plaza Aniceto Ortega y el atrio de la Parroquia de San Francisco para la Feria Tradicional.</t>
+  </si>
+  <si>
+    <t>Protección Civil estatal inspeccionará 120 puestos semifijos de comerciantes y artesanos instalados por la Feria San Francisco Pachuca.</t>
+  </si>
+  <si>
+    <t>Segobh, Protección Civil</t>
+  </si>
+  <si>
+    <t>Fortalecen alianzas en reunión NODESS</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar inauguró en la UPMH de Tolcayuca el Encuentro Nacional NODESS 2026, reuniendo a productores, cooperativas y emprendedores para impulsar la economía social y solidaria.</t>
+  </si>
+  <si>
+    <t>Tolcayuca</t>
+  </si>
+  <si>
+    <t>Economía social</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca encabezó la inauguración del Encuentro Nacional NODESS 2026 para fortalecer proyectos productivos e impulsar el desarrollo económico regional.</t>
+  </si>
+  <si>
+    <t>Gobierno, Sedeco, UPMH, INAES</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Carlos Henkel Escorza, Catalina Monreal Pérez</t>
+  </si>
+  <si>
+    <t>Descarta Julio Menchaca una nueva alza a tarifa de taxis</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca descartó autorizar un nuevo incremento a la tarifa de taxis en Hidalgo tras peticiones de concesionarios, señalando que la tarifa ajustada recientemente a 45 pesos busca proteger la economía de las familias.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca descartó incrementar nuevamente la tarifa mínima de taxis en Pachuca y la zona metropolitana.</t>
+  </si>
+  <si>
+    <t>Gobernador</t>
+  </si>
+  <si>
+    <t>Gobernador, Semot</t>
+  </si>
+  <si>
+    <t>Continúan los cobros excesivos de taxistas</t>
+  </si>
+  <si>
+    <t>A una semana de la entrada en vigor del nuevo tarifario, usuarios de la zona metropolitana de Pachuca denunciaron que la mayoría de conductores de taxi ignoran las tarifas oficiales e imponen cobros de hasta 150 pesos hacia la Feria.</t>
+  </si>
+  <si>
+    <t>Abusos taxistas</t>
+  </si>
+  <si>
+    <t>Usuarios de transporte en Pachuca acusaron que taxistas continúan aplicando cobros arbitrarios por encima del tarifario autorizado por la Semot.</t>
+  </si>
+  <si>
+    <t>Claudia Ángeles</t>
+  </si>
+  <si>
+    <t>El Maye resguarda más de 50 biznagas</t>
+  </si>
+  <si>
+    <t>El comisariado ejidal de El Maye en Ixmiquilpan informó que en el cerro de la localidad habitan más de 50 biznagas protegidas, destacando un ejemplar gigante que supera los dos metros de altura.</t>
+  </si>
+  <si>
+    <t>Ejidatarios de El Maye en Ixmiquilpan resguardan un núcleo natural con más de 50 biznagas gigantes protegidas contra la extracción ilegal.</t>
+  </si>
+  <si>
+    <t>Omar Santiago</t>
+  </si>
+  <si>
+    <t>Alfonso Rodríguez</t>
+  </si>
+  <si>
+    <t>El Yathé podría dar dos cosechas al año</t>
+  </si>
+  <si>
+    <t>Representantes agrícolas informaron que la presa El Yathé en Alfajayucan, con capacidad para almacenar 44.3 millones de m3 de agua, permitirá beneficiar a 4 mil hectáreas de riego y garantizar hasta dos cosechas anuales.</t>
+  </si>
+  <si>
+    <t>Alfajayucan</t>
+  </si>
+  <si>
+    <t>Presa Yathé</t>
+  </si>
+  <si>
+    <t>La puesta en operación del canal de interconexión en la presa El Yathé diversificará la producción agrícola en la región del Valle del Mezquital.</t>
+  </si>
+  <si>
+    <t>Saderh, Conagua</t>
+  </si>
+  <si>
+    <t>Antonio Nava</t>
+  </si>
+  <si>
+    <t>La caída del puente-vado afecta la economía familiar</t>
+  </si>
+  <si>
+    <t>El colapso del puente-vado del río Calabozo en Huautla dejó incomunicadas a 18 comunidades por quinta ocasión, obligando a los pobladores a pagar fletes de hasta 600 pesos para trasladar alimentos y productos.</t>
+  </si>
+  <si>
+    <t>Huautla</t>
+  </si>
+  <si>
+    <t>Colapso de puente</t>
+  </si>
+  <si>
+    <t>Habitantes de 18 localidades de Huautla enfrentan afectaciones económicas tras el colapso del puente-vado sobre el río Calabozo.</t>
+  </si>
+  <si>
+    <t>Regional</t>
+  </si>
+  <si>
+    <t>Sipdus, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Hidalgo analizará creación de policía metropolitana</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar informó que durante la séptima Reunión de Coordinación Interestatal de Paz y Seguridad se planteó la necesidad de crear una policía metropolitana para atender la seguridad en áreas limítrofes.</t>
+  </si>
+  <si>
+    <t>Durante la Reunión de Coordinación Interestatal se propuso la creación de una policía metropolitana coordinada con la Guardia Nacional y policías estatales.</t>
+  </si>
+  <si>
+    <t>Adela Garmez</t>
+  </si>
+  <si>
+    <t>Gobierno, SSPH, Segobh</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Clara Brugada</t>
+  </si>
+  <si>
+    <t>Descarta atender petición de taxistas</t>
+  </si>
+  <si>
+    <t>Julio Menchaca descartó que la Secretaría de Movilidad y Transporte atienda la petición de taxistas que solicitaron fijar en 50 pesos la tarifa mínima en Pachuca.</t>
+  </si>
+  <si>
+    <t>El gobernador descartó autorizar el aumento a 50 pesos en la tarifa mínima de taxis solicitada por un grupo de conductores en Pachuca.</t>
+  </si>
+  <si>
+    <t>Interiores</t>
+  </si>
+  <si>
+    <t>Semot, Gobernador</t>
+  </si>
+  <si>
+    <t>IHE realiza congreso estatal Juntos por la Convivencia Escolar</t>
+  </si>
+  <si>
+    <t>El Instituto Hidalguense de Educación organizó un espacio de diálogo y formación con especialistas para promover entornos escolares seguros y prevenir la violencia.</t>
+  </si>
+  <si>
+    <t>Comunidades educativas y especialistas abordaron estrategias para construir ambientes seguros, inclusivos y respetuosos en las escuelas hidalguenses.</t>
+  </si>
+  <si>
+    <t>SEPH, CDHEH, PGJEH, Sipinna</t>
+  </si>
+  <si>
+    <t>Margarita Maricarmen Mandujano Cerrilla, Martín Pérez Sierra</t>
+  </si>
+  <si>
+    <t>Unos 50 regidores y funcionarios reintegran dinero por doble pago</t>
+  </si>
+  <si>
+    <t>El contralor estatal Álvaro Bardales informó que cerca de 50 servidores públicos ya devolvieron recursos tras detectarse nombramientos con doble sueldo.</t>
+  </si>
+  <si>
+    <t>Reintegración de recursos</t>
+  </si>
+  <si>
+    <t>Contraloría del Estado reportó avances en la regularización de casi mil funcionarios detectados con percepciones dobles en ayuntamientos y dependencias.</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>Contraloría, SEPH, SSH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Álvaro Bardales Ramírez</t>
+  </si>
+  <si>
+    <t>Celebran encuentro nacional para impulsar la economía social</t>
+  </si>
+  <si>
+    <t>En la UPMH se realizó el Encuentro Nacional de Nodess para promover esquemas productivos sustentables e integradores en Hidalgo y el país.</t>
+  </si>
+  <si>
+    <t>Zapotlán</t>
+  </si>
+  <si>
+    <t>Hidalgo destaca a nivel nacional con 20 Nodos de Impulso a la Economía Social instalados en 28 municipios para acompañar a productores locales.</t>
+  </si>
+  <si>
+    <t>Sedeco</t>
+  </si>
+  <si>
+    <t>Sedeco, SEPH, Presidencia</t>
+  </si>
+  <si>
+    <t>Carlos Henkel Escorza, Catalina Monreal Pérez</t>
+  </si>
+  <si>
+    <t>Sebiso sumará a cerca de 11 mil beneficiarios a programas sociales</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno informó que 11 mil personas se incorporarán a padrones de la Sebiso, priorizando municipios vulnerables y apoyo artesanal.</t>
+  </si>
+  <si>
+    <t>Programas Del Bienestar</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar ampliará la cobertura de apoyos sociales en Hidalgo sin requerir ampliación presupuestal extraordinaria.</t>
+  </si>
+  <si>
+    <t>IHE y Casio México evalúan uso de tecnología para fortalecer enseñanza de las matemáticas</t>
+  </si>
+  <si>
+    <t>IHE y Casio México analizaron los alcances del Proyecto Piloto CASIO Educación México en secundarias generales para optimizar tiempos de aprendizaje.</t>
+  </si>
+  <si>
+    <t>Innovación tecnológica</t>
+  </si>
+  <si>
+    <t>Evaluación del programa piloto tecnológico implementado por el IHE e iniciativa privada para la enseñanza didáctica de matemáticas en escuelas públicas.</t>
+  </si>
+  <si>
+    <t>Celebrarán en California quinta edición del Festival de la Barbacoa y el Ximbó</t>
+  </si>
+  <si>
+    <t>Migrantes hidalguenses organizan el Festival del Ximbó y la Barbacoa en Santa Rosa, California, promoviendo la gastronomía estatal con apoyo de Sebiso.</t>
+  </si>
+  <si>
+    <t>Atención A Migrantes</t>
+  </si>
+  <si>
+    <t>El gobierno de Hidalgo apoyará con 100 mil pesos y acompañamiento la realización del festival gastronómico hidalguense en Estados Unidos.</t>
+  </si>
+  <si>
+    <t>Presentan acervos históricos en los Diálogos del Patrimonio</t>
+  </si>
+  <si>
+    <t>Documentos desde 1553 hasta la época moderna forman parte del patrimonio documental resguardado por los poderes del estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Patrimonio cultural</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura expuso los avances en digitalización y conservación de los acervos históricos de los poderes Ejecutivo, Legislativo y Judicial.</t>
+  </si>
+  <si>
+    <t>Cultura, TSJEH, Congreso</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, Luis Francisco Sánchez Fonseca, José Vergara Vergara</t>
+  </si>
+  <si>
+    <t>IHE fortalece Educación Inicial con Cada momento cuenta</t>
+  </si>
+  <si>
+    <t>El IHE reunió a personal docente y autoridades en el encuentro 'Cada momento cuenta' para consolidar estrategias de atención integral a la primera infancia.</t>
+  </si>
+  <si>
+    <t>Educación inicial</t>
+  </si>
+  <si>
+    <t>Jornada de capacitación para fortalecer vínculos afectivos y la atención centrada en el desarrollo infantil organizada por el IHE.</t>
+  </si>
+  <si>
+    <t>Nancy León Vite</t>
+  </si>
+  <si>
+    <t>Prevén 19.2 mdp para restaurar tres estaciones de ferrocarril</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura destinará 19.2 mdp para la restauración de estaciones ferroviarias en Cuautepec, Santiago Tulantepec y Tula para convertirlas en centros culturales.</t>
+  </si>
+  <si>
+    <t>Cuautepec</t>
+  </si>
+  <si>
+    <t>Estaciones ferroviarias</t>
+  </si>
+  <si>
+    <t>Proyectos aprobados por el INAH permitirán la rehabilitación de tres antiguas estaciones de tren en Hidalgo para su rescate y difusión artística.</t>
+  </si>
+  <si>
+    <t>Cultura, Semarnath, Presidencia</t>
+  </si>
+  <si>
+    <t>La entidad registra 24 casos de miasis humana</t>
+  </si>
+  <si>
+    <t>Reporte de Vigilancia Epidemiológica confirma 24 contagios acumulados de gusano barrenador en Hidalgo, manteniendo protocolos de supervisión activa.</t>
+  </si>
+  <si>
+    <t>Gusano barrenador</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud reportó la presencia de 24 casos de miasis humana por Cochliomyia hominivorax en territorio estatal.</t>
+  </si>
+  <si>
+    <t>Nathali González</t>
+  </si>
+  <si>
+    <t>SSH, Presidencia</t>
+  </si>
+  <si>
+    <t>Tiene Hidalgo alto nivel de calidad en reporte financiero</t>
+  </si>
+  <si>
+    <t>La SHCP ubicó a Hidalgo en el tercer lugar nacional con 98.71 puntos en el Índice de Calidad de la Información sobre el destino y ejercicio de recursos federales transferidos en el segundo trimestre de 2026.</t>
+  </si>
+  <si>
+    <t>Recursos federales</t>
+  </si>
+  <si>
+    <t>La Secretaría de Hacienda y Crédito Público ubicó a Hidalgo en el tercer lugar nacional por su cumplimiento de 98.71 puntos en el Índice de Calidad de la Información de recursos federales.</t>
+  </si>
+  <si>
+    <t>Hacienda</t>
+  </si>
+  <si>
+    <t>Ven en empresas sociales clave contra la migración</t>
+  </si>
+  <si>
+    <t>Para evitar la migración y arraigar a las personas con un modo de vida digno, el INAES y la Secretaría de Economía de Hidalgo apoyan a cooperativas y empresas sociales con equipamiento de hasta 200 mil pesos.</t>
+  </si>
+  <si>
+    <t>El INAES y la Secretaría de Economía destacaron que más de 400 Nodess y apoyos a cooperativas en Tolcayuca ayudan a arraigar la población e inhibir la migración.</t>
+  </si>
+  <si>
+    <t>Miriam Avilés</t>
+  </si>
+  <si>
+    <t>Sedeco, Presidencia</t>
+  </si>
+  <si>
+    <t>Catalina Monreal, Carlos Henkel</t>
+  </si>
+  <si>
+    <t>Destaca Tello apertura comercial y atracción de inversión al estado</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas, titular de la Uplaph, destacó que la incorporación de la región Tula a la ZMVM representa una gran oportunidad comercial y de atracción de inversiones sin generar conflicto ambiental.</t>
+  </si>
+  <si>
+    <t>Tula</t>
+  </si>
+  <si>
+    <t>Atracción De Inversiones</t>
+  </si>
+  <si>
+    <t>El titular de la Uplaph resaltó la oportunidad que representa incorporar a Tula a la Zona Metropolitana del Valle de México para acelerar la atracción de inversiones.</t>
+  </si>
+  <si>
+    <t>Planeación, Pemex, CFE</t>
+  </si>
+  <si>
+    <t>Adecuan lineamientos en educación media superior por pantallas</t>
+  </si>
+  <si>
+    <t>Daniel Fragoso Torres, subsecretario de Educación Media Superior y Superior, informó sobre las adecuaciones normativas en las escuelas de Hidalgo para aplicar los lineamientos federales sobre uso responsable de celulares en aulas.</t>
+  </si>
+  <si>
+    <t>Regulación de dispositivos digitales</t>
+  </si>
+  <si>
+    <t>La SEPH realiza adecuaciones para cumplir con la disposición federal que regula el uso de pantallas y teléfonos inteligentes durante clases en educación básica y media superior.</t>
+  </si>
+  <si>
+    <t>SEPH, Presidencia</t>
+  </si>
+  <si>
+    <t>Daniel Fragoso Torres</t>
+  </si>
+  <si>
+    <t>Estudian crear corporación metropolitana</t>
+  </si>
+  <si>
+    <t>Hidalgo y entidades del centro del país analizan la creación de una Policía Metropolitana y un C5 Metropolitano para reforzar la seguridad en zonas limítrofes.</t>
+  </si>
+  <si>
+    <t>Metropolitana</t>
+  </si>
+  <si>
+    <t>Gobernadores de la zona centro acordaron analizar en un próximo encuentro la propuesta para homologar operaciones de seguridad en áreas confluentes.</t>
+  </si>
+  <si>
+    <t>Gobierno, Guardia Nacional</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Clara Brugada Molina</t>
+  </si>
+  <si>
+    <t>Rechazan modificación a las tarifas de los taxis</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca descartó ajustar la tarifa de 45 pesos para los primeros 4 km del servicio de taxi en Pachuca, señalando que representa un equilibrio económico.</t>
+  </si>
+  <si>
+    <t>El Ejecutivo estatal reiteró que la tarifa publicada en el POEH para los taxis busca proteger el bolsillo de las familias sin perjudicar al gremio.</t>
+  </si>
+  <si>
+    <t>Semot, OEEH</t>
+  </si>
+  <si>
+    <t>Están en revisión 100 casos de plazas dobles</t>
+  </si>
+  <si>
+    <t>La Secretaría de Contraloría mantiene abiertos entre 90 y 100 expedientes de funcionarios que percibían dobles salarios en dependencias educativas, de salud y alcaldías.</t>
+  </si>
+  <si>
+    <t>Doble Plaza</t>
+  </si>
+  <si>
+    <t>El contralor Álvaro Bardales informó que 900 de mil casos identificados de pagos dobles ya concluyeron con licencias, renuncias o devoluciones de dinero.</t>
+  </si>
+  <si>
+    <t>Contraloría, SEPH, SSH</t>
+  </si>
+  <si>
+    <t>Hidalgo, en el top 3 de calidad de la información financiera</t>
+  </si>
+  <si>
+    <t>La SHCP reconoció a Hidalgo con 98.71 puntos entre los tres estados con mejor nivel de reporte en el Índice de Calidad de la Información del SRFT.</t>
+  </si>
+  <si>
+    <t>Hidalgo superó por casi 15 puntos la media nacional de transparencia en la rendición de cuentas de aportaciones y convenios federales.</t>
+  </si>
+  <si>
+    <t>Hacienda, Presidencia</t>
+  </si>
+  <si>
+    <t>Policía estatal detuvo a dos por presunto narcomenudeo</t>
+  </si>
+  <si>
+    <t>La SSPH aprehendió a dos personas en operativos realizados en Tlahuelilpan y San Bartolo Tutotepec con dosis de marihuana y cristal.</t>
+  </si>
+  <si>
+    <t>Tlahuelilpan</t>
+  </si>
+  <si>
+    <t>Agentes estatales decomisaron más de 600 dosis de presuntos estupefacientes y detuvieron a dos implicados que fueron puestos a disposición del MP.</t>
+  </si>
+  <si>
+    <t>Evacúan a estudiantes del CEB de Juan C. Doria por un arma de fuego</t>
+  </si>
+  <si>
+    <t>Alrededor de 500 alumnos fueron desalojados de sus aulas en Pachuca luego de que una estudiante reportara que un compañero traía un arma.</t>
+  </si>
+  <si>
+    <t>Alumno Armado</t>
+  </si>
+  <si>
+    <t>Autoridades escolares y policías aplicaron el protocolo preventivo evacuando 18 aulas del CEB 5/4 tras una alerta por arma de fuego.</t>
+  </si>
+  <si>
+    <t>SEPH, SSPH</t>
+  </si>
+  <si>
+    <t>Otra vez, derrumbe de vado deja incomunicadas a 18 localidades</t>
+  </si>
+  <si>
+    <t>Crecida del río Calabozo en Huautla destruyó el vado provisional entre Tamoyón I y II, dejando sin paso vehicular a 18 comunidades de la zona.</t>
+  </si>
+  <si>
+    <t>Precipitaciones causaron por quinta ocasión la caída del vado en el río Calabozo, suspendiéndose cruces y paso de embarcaciones por seguridad.</t>
+  </si>
+  <si>
+    <t>Francisco Bautista</t>
+  </si>
+  <si>
+    <t>Hay dos denuncias por desaparición de restos</t>
+  </si>
+  <si>
+    <t>La PGJEH integra dos carpetas de investigación tras la sustracción de restos humanos reportada en el panteón municipal San Miguel de Tulancingo.</t>
+  </si>
+  <si>
+    <t>Localización De Restos</t>
+  </si>
+  <si>
+    <t>El ayuntamiento de Tulancingo promovió una investigación formal en conjunto con familiares para esclarecer la profanación en el camposanto.</t>
+  </si>
+  <si>
+    <t>Mirely Santos</t>
+  </si>
+  <si>
+    <t>Alberto Santuario</t>
+  </si>
+  <si>
+    <t>Hidalgo destaca a nivel nacional en calidad de la información financiera</t>
+  </si>
+  <si>
+    <t>La Secretaría de Hacienda y Crédito Público (SHCP) reconoció al estado de Hidalgo por el nivel alcanzado en materia de calidad de la información reportada mediante el Sistema de Recursos Federales Transferidos (SRFT). Hidalgo se ubicó entre las tres entidades con mayor puntuación a nivel nacional en el Índice de Calidad de la Información (ICI), con 98.71 puntos, superando por 14.96 puntos la media nacional.</t>
+  </si>
+  <si>
+    <t>La SHCP reconoció a Hidalgo por ubicarse en el top 3 nacional del Índice de Calidad de la Información financiera con 98.71 puntos.</t>
+  </si>
+  <si>
+    <t>Hacienda, SHCP</t>
+  </si>
+  <si>
+    <t>Proponen crear una Policía Metropolitana entre Hidalgo y estados vecinos</t>
+  </si>
+  <si>
+    <t>Durante la Séptima Reunión Interestatal de Coordinación por la Paz y Seguridad, la jefa de Gobierno de la Ciudad de México propuso crear una Policía Metropolitana entre Hidalgo y estados limítrofes para fortalecer la seguridad en zonas fronterizas. En el encuentro, el gobernador Julio Menchaca destacó la inhabilitación de 19 túneles y el aseguramiento de más de 7 millones de litros de huachicol.</t>
+  </si>
+  <si>
+    <t>En la reunión interestatal de seguridad se propuso crear una Policía Metropolitana entre Hidalgo y estados vecinos; Menchaca resaltó el decomiso de 7 millones de litros de huachicol.</t>
+  </si>
+  <si>
+    <t>Gobierno, Gabinete de Seguridad, Guardia Nacional, SSPH</t>
+  </si>
+  <si>
+    <t>De mil casos de trabajadores con doble ingreso, cerca de 100 continúan bajo revisión</t>
+  </si>
+  <si>
+    <t>El secretario de la Contraloría, Álvaro Bardales Ramírez, informó que cerca de 100 de casi mil casos de servidores públicos que cobraban doble sueldo estatal y municipal siguen bajo investigación. Señaló que más de 900 personas tramitaron licencia a tiempo y alrededor de 50 reembolsaron el dinero cobrado indebidamente.</t>
+  </si>
+  <si>
+    <t>La Contraloría de Hidalgo mantiene bajo revisión 100 expedientes de trabajadores con doble remuneración pública, mientras 50 personas reembolsaron el dinero.</t>
+  </si>
+  <si>
+    <t>Menchaca descarta ajuste la tarifa de taxis ante petición de incremento</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar rechazó la petición de taxistas independientes de incrementar la tarifa de 45 a 50 o 55 pesos, ratificando que el ajuste acordado de 45 pesos es equilibrado y no afectará la economía de la ciudadanía.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca descartó incrementar la tarifa de taxis a 50 pesos como solicitaban conductores independientes, sosteniendo la tarifa autorizada de 45 pesos.</t>
+  </si>
+  <si>
+    <t>Gobernador, Semot, STCH</t>
+  </si>
+  <si>
+    <t>Logra Hidalgo alto nivel en información financiera</t>
+  </si>
+  <si>
+    <t>La Secretaría de Hacienda y Crédito Público (SHCP) reconoció al estado de Hidalgo al obtener 98.71 puntos en el Índice de Calidad de la Información (ICI), ubicándose entre los tres primeros lugares a nivel nacional junto con Nuevo León y Querétaro.</t>
+  </si>
+  <si>
+    <t>La SHCP posicionó a Hidalgo en el tercer lugar nacional en transparencia y calidad de reporte de recursos federales transferidos.</t>
+  </si>
+  <si>
+    <t>SHCP, Gobierno</t>
+  </si>
+  <si>
+    <t>Descarta Julio Menchaca nuevo aumento a tarifa de taxis</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar descartó abrir una nueva mesa de negociación tras fijarse la tarifa mínima en 45 pesos, señalando que la medida busca un equilibrio económico.</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo rechazó la solicitud de choferes independientes de subir a 50 pesos el pasaje mínimo de taxi.</t>
+  </si>
+  <si>
+    <t>Oscar Raúl Pérez</t>
+  </si>
+  <si>
+    <t>Celebrarán festival Internacional de la Barbacoa y el Ximbo</t>
+  </si>
+  <si>
+    <t>La quinta edición del Festival Internacional de la Barbacoa y el Ximbo se realizará el 11 de octubre en Santa Rosa, California, con apoyo de Sebiso.</t>
+  </si>
+  <si>
+    <t>Migrantes hidalguenses en California realizarán la quinta edición del festival gastronómico con un respaldo de 100 mil pesos de Sebiso.</t>
+  </si>
+  <si>
+    <t>Sebiso</t>
+  </si>
+  <si>
+    <t>Nelly Tello</t>
+  </si>
+  <si>
+    <t>Reportan 29 donaciones de órganos en la entidad, 10 fueron multiorgánicas</t>
+  </si>
+  <si>
+    <t>El Ceetra informó que en lo que va de 2026 se han concretado 29 donaciones de órganos en Hidalgo, permitiendo obtener 66 órganos y tejidos con apoyo de traslados aéreos.</t>
+  </si>
+  <si>
+    <t>Donación De Órganos</t>
+  </si>
+  <si>
+    <t>En el marco del Día Mundial del Corazón, la SSH y el Ceetra destacaron la procuración de un corazón y dos riñones en el Hospital 36 del IMSS Pachuca.</t>
+  </si>
+  <si>
+    <t>Ceetra, IMSS, SSH</t>
+  </si>
+  <si>
+    <t>Carlos Ávila Zúñiga, Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>Tras deslaves, agentes de policía estatal liberan carretera de Tlanchinol</t>
+  </si>
+  <si>
+    <t>Cuadrillas de la SSPH y personal municipal removieron escombros de deslaves provocados por lluvias en la vía federal México-Tampico para restablecer el paso.</t>
+  </si>
+  <si>
+    <t>Deslaves por lluvias</t>
+  </si>
+  <si>
+    <t>Policías estatales y cuadrillas de Obras Públicas desbloquearon tres tramos afectados por derrumbes en la carretera a Tlanchinol.</t>
+  </si>
+  <si>
+    <t>SSPH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Evitan que más de 700 dosis de drogas llegaran a las calles</t>
+  </si>
+  <si>
+    <t>Elementos de la SSPH detuvieron a una mujer en Tlahuelilpan con 609 dosis de enervantes y a un hombre en San Bartolo Tutotepec con 128 dosis y báscula.</t>
+  </si>
+  <si>
+    <t>Patrullajes de la Policía Estatal en Tlahuelilpan y San Bartolo Tutotepec derivaron en el aseguramiento de dos narcomenudistas y más de 700 dosis de marihuana y cristal.</t>
+  </si>
+  <si>
+    <t>Hidalgo gana 12 medallas al cerrar el primer bloque de Paralimpiada Nacional 2026</t>
+  </si>
+  <si>
+    <t>La delegación hidalguense cosechó 3 oros, 5 platas y 4 bronces en natación adaptada y boccia durante la competencia nacional de la Conade.</t>
+  </si>
+  <si>
+    <t>Paranacionales Conade</t>
+  </si>
+  <si>
+    <t>Paratletas de Hidalgo destacaron en la Paralimpiada Nacional CONADE 2026 con 12 preseas en pruebas de para natación y boccia.</t>
+  </si>
+  <si>
+    <t>Inhide, Conade</t>
+  </si>
+  <si>
+    <t>Melani Yamileth Ávila Trujillo, Luis Antonio Cano Torres, Cristian Yahel Solís Rangel, Ethan Leonardo Miranda Rubio</t>
+  </si>
+  <si>
+    <t>Menchaca apaga taxímetro; banderazo se queda en $45</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar descartó un nuevo aumento a la tarifa de taxis, por lo que el cobro mínimo de 45 pesos se mantendrá para los primeros kilómetros en la zona metropolitana de Pachuca. Ante la propuesta de operadores independientes para elevar el mínimo a 50 pesos, el mandatario señaló que no habrá una segunda modificación y sostuvo que el ajuste de 38 a 45 pesos fue acordado con la Semoth.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca rechazó la solicitud de un grupo independiente de taxistas para subir la tarifa mínima a 50 pesos, ratificando que el cobro se mantendrá en 45 pesos.</t>
+  </si>
+  <si>
+    <t>Entrega Estado buenas cuentas a la Federación</t>
+  </si>
+  <si>
+    <t>Hidalgo se ubicó entre los tres primeros lugares del país en el Índice de Calidad de la Información (ICI), correspondiente al segundo trimestre de 2026, con 98.71 puntos, informó la Secretaría de Hacienda y Crédito Público (SHCP). El indicador evalúa la información reportada por las 32 entidades sobre aportaciones federales, subsidios y convenios.</t>
+  </si>
+  <si>
+    <t>Hidalgo obtuvo una calificación de 98.71 puntos en el Índice de Calidad de la Información de la SHCP, colocándose entre las tres entidades mejor evaluadas del país en transparencia financiera.</t>
+  </si>
+  <si>
+    <t>Ponen tras las rejas a 65 huachicoleros</t>
+  </si>
+  <si>
+    <t>En Hidalgo se han inhabilitado 19 túneles para extraer hidrocarburo durante la actual administración, informó el gobernador Julio Menchaca Salazar. Añadió que 65 personas han sido detenidas por delitos relacionados con el robo de combustible; de ellas, 40 son identificadas como generadoras de violencia y objetivos prioritarios del gobierno federal.</t>
+  </si>
+  <si>
+    <t>El gobierno de Hidalgo reportó la clausura de 19 huachitúneles y la detención de 65 personas ligadas al robo de hidrocarburos, de las cuales 40 eran consideradas objetivos prioritarios.</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad, Sedena, GN, FGR</t>
+  </si>
+  <si>
+    <t>Sin rastro de 72 en Valle de Tulancingo</t>
+  </si>
+  <si>
+    <t>Durante 2026, en el Valle de Tulancingo se han activado 72 fichas de búsqueda de personas desaparecidas, de acuerdo con registros de la PGJEH, la Comisión de Búsqueda y Alerta Amber. Tulancingo de Bravo concentra 56 fichas (31 hombres y 25 mujeres), Cuautepec 7, Santiago Tulantepec 4, Acaxochitlán 4 y Acatlán 1.</t>
+  </si>
+  <si>
+    <t>Autoridades estatales registran 72 fichas de búsqueda activadas en el Valle de Tulancingo en lo que va del año, donde predomina la incidencia en Tulancingo de Bravo con 56 personas no localizadas.</t>
+  </si>
+  <si>
+    <t>Karen Aicitel Lira</t>
+  </si>
+  <si>
+    <t>PGJEH, CBPEH</t>
+  </si>
+  <si>
+    <t>Paloma Hernández Vázquez, Iván Ramírez León</t>
+  </si>
+  <si>
+    <t>La escuela primaria Aquiles Serdán, de Tulancingo, presenta daños estructurales, por lo cual será demolida y reconstruida totalmente durante el ciclo escolar 2026-2027, informó el titular de la SEPH, Natividad Castrejón. Se buscan alternativas presenciales o en línea mientras se llevan a cabo las obras.</t>
+  </si>
+  <si>
+    <t>La SEPH demolerá y volverá a edificar la primaria Aquiles Serdán en Tulancingo tras detectar fallas estructurales, gestionando espacios temporales para impartir clases al alumnado.</t>
+  </si>
+  <si>
+    <t>Sigue revisión a 90 de casi mil funcionarios "dobleteros"</t>
+  </si>
+  <si>
+    <t>La Secretaría de Contraloría de Hidalgo redujo a 90 los casos pendientes en la revisión de servidores públicos que recibían doble sueldo al trabajar simultáneamente en dependencias estatales y ayuntamientos.</t>
+  </si>
+  <si>
+    <t>Contraloría estatal informó que de un padrón inicial de mil trabajadores con doble remuneración, unos 50 ya reembolsaron recursos y solo restan 90 en revisión.</t>
+  </si>
+  <si>
+    <t>Luis Godínez</t>
+  </si>
+  <si>
+    <t>Descartan ajustes a la tarifa de los taxis</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar descartó un incremento a la tarifa de taxis de 45 pesos en Pachuca, señalando que la tarifa acordada es equilibrada para no afectar a la ciudadanía.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca confirmó que el banderazo de salida para taxis se mantendrá en 45 pesos pese a solicitudes de transportistas para elevarlo a 50 o 55 pesos.</t>
+  </si>
+  <si>
+    <t>Reforzarán seguridad en la Feria de Pachuca tras derribo de vallas</t>
+  </si>
+  <si>
+    <t>Tras el derribo de vallas e ingreso masivo durante las presentaciones musicales en la Feria de San Francisco, el gobernador Julio Menchaca anunció el reforzamiento de medidas de seguridad.</t>
+  </si>
+  <si>
+    <t>Autoridades estatales reforzarán la seguridad y control de acceso en el recinto ferial de Pachuca para prevenir aglomeraciones de riesgo.</t>
+  </si>
+  <si>
+    <t>Turismo, SSPH, Protección Civil</t>
+  </si>
+  <si>
+    <t>Crecimiento de huachicoleo, por complicidad de autoridades: JMS</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar afirmó que el crecimiento del robo de combustible en administraciones pasadas contó con la complicidad de autoridades locales y federales, destacando la inhabilitación de 19 túneles en su gobierno.</t>
+  </si>
+  <si>
+    <t>El ejecutivo estatal informó sobre la detención de 65 personas y la clausura de 19 túneles huachicoleros durante la actual administración.</t>
+  </si>
+  <si>
+    <t>Gobernador, Gabinete de Seguridad</t>
+  </si>
+  <si>
+    <t>Adultos mayores hidalguenses se reúnen con sus familiares en EU</t>
+  </si>
+  <si>
+    <t>La Dirección General de Atención al Migrante de Hidalgo gestionó cerca de 250 visas para que adultos mayores puedan reencontrarse con sus familias en Estados Unidos.</t>
+  </si>
+  <si>
+    <t>El programa Raíces de Hidalgo concretó 250 trámites de visa en lo que va del año para reunificación familiar de adultos mayores en el extranjero.</t>
+  </si>
+  <si>
+    <t>Manuel Aranda Montero</t>
+  </si>
+  <si>
+    <t>Celebrarán el quinto Festival Internacional de Barbacoa y Ximbó</t>
+  </si>
+  <si>
+    <t>Hidalguenses en el extranjero organizarán la quinta edición del Festival Internacional de Barbacoa y Ximbó en California para promocionar la gastronomía del estado.</t>
+  </si>
+  <si>
+    <t>Festival Gastronómico</t>
+  </si>
+  <si>
+    <t>Migrantes hidalguenses realizarán en Estados Unidos el Quinto Festival Internacional de Barbacoa y Ximbó con la participación de cocineros tradicionales.</t>
+  </si>
+  <si>
+    <t>Turismo, Bienestar</t>
+  </si>
+  <si>
+    <t>Accidentes viales dejan en tan solo dos meses 12 muertos y 14 lesionados</t>
+  </si>
+  <si>
+    <t>Un recuento de Criterio reveló que en los últimos dos meses se han registrado 12 víctimas mortales por accidentes de tránsito en Hidalgo, la mitad motociclistas.</t>
+  </si>
+  <si>
+    <t>Accidente Vial</t>
+  </si>
+  <si>
+    <t>Los percances automovilísticos y de motocicletas en Pachuca, Tepeji y Tula dejaron un saldo trágico de 12 decesos en un periodo de sesenta días.</t>
+  </si>
+  <si>
+    <t>Región Tula concentra 19 proyectos federales</t>
+  </si>
+  <si>
+    <t>El titular de la Unidad de Planeación, Miguel Tello Vargas, destacó que la zona de Tula concentra 19 obras estratégicas como Viviendas para el Bienestar y el Tren México-Querétaro.</t>
+  </si>
+  <si>
+    <t>Proyectos Federales</t>
+  </si>
+  <si>
+    <t>Planeación estatal instó a municipios de la región Tula a preparar infraestructura turística y servicios para aprovechar los desarrollos federales en marcha.</t>
+  </si>
+  <si>
+    <t>Abigail García Torres</t>
+  </si>
+  <si>
+    <t>Planeación, Presidencia</t>
+  </si>
+  <si>
+    <t>Hidalgo responde en la Paralimpiada</t>
+  </si>
+  <si>
+    <t>La delegación hidalguense conquistó 12 medallas en el primer bloque de disciplinas de la Paralimpiada Nacional 2026 y continúa participación en la segunda etapa.</t>
+  </si>
+  <si>
+    <t>Atletas de Hidalgo lograron 12 preseas en pruebas de natación y atletismo adaptado durante los Paranacionales Conade 2026.</t>
+  </si>
+  <si>
+    <t>SEPH, Inhide</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1268,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1403,7 +1310,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1491,34 +1398,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ67" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ67" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ58" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ58" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{656C5EAC-6AE7-4849-A2CB-07D90F39D8FD}" uniqueName="Medio_o_cuenta" name="Medio o cuenta" dataDxfId="5">
+    <tableColumn id="2" xr3:uid="{656C5EAC-6AE7-4849-A2CB-07D90F39D8FD}" uniqueName="Medio_o_cuenta" name="Medio o cuenta" dataDxfId="19">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Medio_o_cuenta" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{67E4BBBE-D5C7-4FB1-A4CA-49BC94A0014E}" uniqueName="Usuario" name="Usuario">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Usuario" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96739AB4-7016-49C1-A1BC-122CE2056C09}" uniqueName="Titular" name="Titular" dataDxfId="4">
+    <tableColumn id="4" xr3:uid="{96739AB4-7016-49C1-A1BC-122CE2056C09}" uniqueName="Titular" name="Titular" dataDxfId="18">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Titular" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{96B49FFA-3FAF-4446-9C9C-4866BA6A2CFB}" uniqueName="Contenido" name="Contenido" dataDxfId="3">
+    <tableColumn id="5" xr3:uid="{96B49FFA-3FAF-4446-9C9C-4866BA6A2CFB}" uniqueName="Contenido" name="Contenido" dataDxfId="17">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Contenido" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F6615099-82A7-46E7-8B6C-46F5B1BCE0A4}" uniqueName="Fecha_de_publicacion" name="Fecha de publicación" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{F6615099-82A7-46E7-8B6C-46F5B1BCE0A4}" uniqueName="Fecha_de_publicacion" name="Fecha de publicación" dataDxfId="16">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Fecha_de_publicacion" xmlDataType="date"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{960471FD-DEDC-402B-89FF-237BDB7E7712}" uniqueName="Liga" name="Liga">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Liga" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E3552A04-EE44-46D2-8061-2515AB7BF199}" uniqueName="Municipio" name="Municipio" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{E3552A04-EE44-46D2-8061-2515AB7BF199}" uniqueName="Municipio" name="Municipio" dataDxfId="15">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Municipio" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2E6348A9-8A06-40E0-9039-3BE83BFEF10B}" uniqueName="Sentimiento_de_la_fuente" name="Sentimiento de la fuente" dataDxfId="0">
+    <tableColumn id="9" xr3:uid="{2E6348A9-8A06-40E0-9039-3BE83BFEF10B}" uniqueName="Sentimiento_de_la_fuente" name="Sentimiento de la fuente" dataDxfId="14">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Sentimiento_de_la_fuente" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{81F2E10D-4242-4A14-AE44-001E3C95FD39}" uniqueName="Tipo_de_publicacion" name="Tipo de publicación">
@@ -1551,55 +1458,55 @@
     <tableColumn id="19" xr3:uid="{09AE5EC7-6FA9-43B0-A953-BEB3738329E3}" uniqueName="Alcance_del_medio" name="Alcance del medio">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Alcance_del_medio" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{D7B2A113-9CC6-4BD4-8DF1-12AA7233AD96}" uniqueName="Unidad_del_alcance" name="Unidad del alcance" dataDxfId="20">
+    <tableColumn id="20" xr3:uid="{D7B2A113-9CC6-4BD4-8DF1-12AA7233AD96}" uniqueName="Unidad_del_alcance" name="Unidad del alcance" dataDxfId="13">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Unidad_del_alcance" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{FBC61DAD-43EE-4F79-B045-4EC08F4350F2}" uniqueName="Impresiones" name="Impresiones">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Impresiones" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{E0F7175B-4E19-404A-85B3-D6F0C20CC4D8}" uniqueName="Genero_periodistico" name="Género periodístico" dataDxfId="19">
+    <tableColumn id="22" xr3:uid="{E0F7175B-4E19-404A-85B3-D6F0C20CC4D8}" uniqueName="Genero_periodistico" name="Género periodístico" dataDxfId="12">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Genero_periodistico" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{956A34F7-46A2-4FD2-B124-47F0DBD8C47B}" uniqueName="Tema_segun_la_fuente" name="Tema según la fuente" dataDxfId="18">
+    <tableColumn id="23" xr3:uid="{956A34F7-46A2-4FD2-B124-47F0DBD8C47B}" uniqueName="Tema_segun_la_fuente" name="Tema según la fuente" dataDxfId="11">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Tema_segun_la_fuente" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{A3443871-377E-4A30-8E3B-7FFA77E0DA55}" uniqueName="Sintesis" name="Síntesis" dataDxfId="17">
+    <tableColumn id="24" xr3:uid="{A3443871-377E-4A30-8E3B-7FFA77E0DA55}" uniqueName="Sintesis" name="Síntesis" dataDxfId="10">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Sintesis" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{5CF69F18-4F87-4056-B7CB-8945726A582A}" uniqueName="Jerarquia_de_la_nota" name="Jerarquía de la nota" dataDxfId="16">
+    <tableColumn id="25" xr3:uid="{5CF69F18-4F87-4056-B7CB-8945726A582A}" uniqueName="Jerarquia_de_la_nota" name="Jerarquía de la nota" dataDxfId="9">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Jerarquia_de_la_nota" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{BDAD3553-B5A7-4B33-B6A0-00158FE22B29}" uniqueName="Posicion" name="Posición" dataDxfId="15">
+    <tableColumn id="26" xr3:uid="{BDAD3553-B5A7-4B33-B6A0-00158FE22B29}" uniqueName="Posicion" name="Posición" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Posicion" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="27" xr3:uid="{6713D1B4-03D8-492E-A805-B8B5E516E754}" uniqueName="Dimension" name="Dimensión">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Dimension" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{5E754D76-EE28-46CE-8759-FFE60C1CFF67}" uniqueName="Unidad_de_la_dimension" name="Unidad de la dimensión" dataDxfId="14">
+    <tableColumn id="28" xr3:uid="{5E754D76-EE28-46CE-8759-FFE60C1CFF67}" uniqueName="Unidad_de_la_dimension" name="Unidad de la dimensión" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Unidad_de_la_dimension" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{8F595EB9-9F69-41D2-AC23-2C7879D9977B}" uniqueName="Con_fotografia" name="Con fotografía" dataDxfId="13">
+    <tableColumn id="29" xr3:uid="{8F595EB9-9F69-41D2-AC23-2C7879D9977B}" uniqueName="Con_fotografia" name="Con fotografía" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Con_fotografia" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{C61CD4D8-3A8E-4A69-A10B-40B4A2B273E1}" uniqueName="Es_replica" name="Es réplica" dataDxfId="12">
+    <tableColumn id="30" xr3:uid="{C61CD4D8-3A8E-4A69-A10B-40B4A2B273E1}" uniqueName="Es_replica" name="Es réplica" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Es_replica" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="31" xr3:uid="{E10CC2EC-300C-4A5F-8203-51C284C389EC}" uniqueName="Medio_de_origen" name="Medio de origen">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Medio_de_origen" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{DF96E63A-F235-4F77-B4AE-FB19B55C217B}" uniqueName="Autor" name="Autor" dataDxfId="11">
+    <tableColumn id="32" xr3:uid="{DF96E63A-F235-4F77-B4AE-FB19B55C217B}" uniqueName="Autor" name="Autor" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Autor" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{D92A8CD3-00A9-49C9-B24E-82388577C54B}" uniqueName="Tipo_de_autor" name="Tipo de autor" dataDxfId="10">
+    <tableColumn id="33" xr3:uid="{D92A8CD3-00A9-49C9-B24E-82388577C54B}" uniqueName="Tipo_de_autor" name="Tipo de autor" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Tipo_de_autor" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{80C3EC21-4CF3-46E5-BBFE-1CD4F7309933}" uniqueName="Dependencia" name="Dependencia" dataDxfId="9">
+    <tableColumn id="34" xr3:uid="{80C3EC21-4CF3-46E5-BBFE-1CD4F7309933}" uniqueName="Dependencia" name="Dependencia" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Dependencia" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{CB1B386E-9E24-4408-8CFA-E4A2B48CA015}" uniqueName="Dependencias_mencionadas" name="Dependencias mencionadas" dataDxfId="8">
+    <tableColumn id="35" xr3:uid="{CB1B386E-9E24-4408-8CFA-E4A2B48CA015}" uniqueName="Dependencias_mencionadas" name="Dependencias mencionadas" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Dependencias_mencionadas" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{A3ED4D4F-6580-49D2-A119-2DFA36DD9925}" uniqueName="Actores_mencionados" name="Actores mencionados" dataDxfId="7">
+    <tableColumn id="36" xr3:uid="{A3ED4D4F-6580-49D2-A119-2DFA36DD9925}" uniqueName="Actores_mencionados" name="Actores mencionados" dataDxfId="0">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Actores_mencionados" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -1924,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ67"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -2074,56 +1981,32 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F2" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2">
-        <v>13262</v>
-      </c>
-      <c r="L2" t="s">
-        <v>103</v>
-      </c>
-      <c r="M2" t="s">
-        <v>103</v>
-      </c>
-      <c r="N2" t="s">
-        <v>103</v>
-      </c>
-      <c r="O2" t="s">
-        <v>103</v>
-      </c>
-      <c r="P2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>103</v>
-      </c>
       <c r="R2">
         <v>1</v>
       </c>
@@ -2137,31 +2020,31 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
@@ -2170,30 +2053,30 @@
         <v>107</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F3" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -2202,31 +2085,7 @@
         <v>45</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K3">
-        <v>13262</v>
-      </c>
-      <c r="L3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M3" t="s">
-        <v>103</v>
-      </c>
-      <c r="N3" t="s">
-        <v>103</v>
-      </c>
-      <c r="O3" t="s">
-        <v>103</v>
-      </c>
-      <c r="P3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2241,19 +2100,19 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>56</v>
@@ -2265,73 +2124,47 @@
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>114</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="AJ3" s="2"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F4" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4">
-        <v>13262</v>
-      </c>
-      <c r="L4" t="s">
-        <v>103</v>
-      </c>
-      <c r="M4" t="s">
-        <v>103</v>
-      </c>
-      <c r="N4" t="s">
-        <v>103</v>
-      </c>
-      <c r="O4" t="s">
-        <v>103</v>
-      </c>
-      <c r="P4" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>103</v>
-      </c>
       <c r="R4">
         <v>1</v>
       </c>
@@ -2345,19 +2178,19 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>56</v>
@@ -2369,72 +2202,48 @@
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AG4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F5" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5">
-        <v>13262</v>
-      </c>
-      <c r="L5" t="s">
-        <v>103</v>
-      </c>
-      <c r="M5" t="s">
-        <v>103</v>
-      </c>
-      <c r="N5" t="s">
-        <v>103</v>
-      </c>
-      <c r="O5" t="s">
-        <v>103</v>
-      </c>
-      <c r="P5" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2449,72 +2258,72 @@
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA5">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F6" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2529,69 +2338,69 @@
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA6">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F7" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>48</v>
@@ -2609,19 +2418,19 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>56</v>
@@ -2633,45 +2442,45 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="AJ7" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F8" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>48</v>
@@ -2689,10 +2498,10 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>57</v>
@@ -2701,7 +2510,7 @@
         <v>43</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>56</v>
@@ -2713,48 +2522,48 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F9" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2769,16 +2578,16 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="AA9">
         <v>12</v>
@@ -2793,46 +2602,48 @@
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AJ9" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F10" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2847,19 +2658,19 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>56</v>
@@ -2871,48 +2682,48 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="AG10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F11" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2927,19 +2738,19 @@
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="AA11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>56</v>
@@ -2951,48 +2762,48 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="AI11" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="AJ11" s="2" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F12" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -3007,19 +2818,19 @@
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="AA12">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>56</v>
@@ -3031,48 +2842,48 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>167</v>
+        <v>41</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F13" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -3083,26 +2894,23 @@
       <c r="T13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U13">
-        <v>39786</v>
-      </c>
       <c r="V13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA13">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>56</v>
@@ -3114,48 +2922,48 @@
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="F14" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -3166,23 +2974,20 @@
       <c r="T14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U14">
-        <v>39786</v>
-      </c>
       <c r="V14" s="2" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>61</v>
+        <v>169</v>
       </c>
       <c r="AA14">
         <v>20</v>
@@ -3191,51 +2996,51 @@
         <v>56</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="F15" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>48</v>
@@ -3249,26 +3054,23 @@
       <c r="T15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U15">
-        <v>39786</v>
-      </c>
       <c r="V15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="AA15">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>56</v>
@@ -3280,45 +3082,45 @@
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>186</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F16" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>48</v>
@@ -3332,32 +3134,29 @@
       <c r="T16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U16">
-        <v>39786</v>
-      </c>
       <c r="V16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="AA16">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>44</v>
@@ -3369,39 +3168,37 @@
         <v>41</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="AJ16" s="2" t="s">
-        <v>191</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="AJ16" s="2"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F17" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>48</v>
@@ -3415,26 +3212,23 @@
       <c r="T17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U17">
-        <v>39786</v>
-      </c>
       <c r="V17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="AA17">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>56</v>
@@ -3446,48 +3240,46 @@
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AJ17" s="2" t="s">
-        <v>119</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="AJ17" s="2"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F18" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3498,26 +3290,23 @@
       <c r="T18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U18">
-        <v>39786</v>
-      </c>
       <c r="V18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="AA18">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>56</v>
@@ -3529,43 +3318,45 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AJ18" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F19" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>48</v>
@@ -3579,76 +3370,73 @@
       <c r="T19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U19">
-        <v>39786</v>
-      </c>
       <c r="V19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="AA19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="AG19" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>77</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F20" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>48</v>
@@ -3662,79 +3450,76 @@
       <c r="T20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U20">
-        <v>39786</v>
-      </c>
       <c r="V20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>155</v>
+        <v>216</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="AA20">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD20" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="AJ20" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F21" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3745,23 +3530,20 @@
       <c r="T21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U21">
-        <v>39786</v>
-      </c>
       <c r="V21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA21">
         <v>20</v>
@@ -3770,54 +3552,52 @@
         <v>56</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD21" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ21" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="AJ21" s="2"/>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="F22" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3828,32 +3608,29 @@
       <c r="T22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U22">
-        <v>39786</v>
-      </c>
       <c r="V22" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AB22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD22" s="2" t="s">
         <v>44</v>
@@ -3865,37 +3642,37 @@
         <v>41</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="AJ22" s="2"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F23" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>48</v>
@@ -3909,26 +3686,23 @@
       <c r="T23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U23">
-        <v>39786</v>
-      </c>
       <c r="V23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA23">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>56</v>
@@ -3940,45 +3714,45 @@
         <v>44</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>41</v>
+        <v>233</v>
       </c>
       <c r="AG23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F24" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>48</v>
@@ -3992,23 +3766,20 @@
       <c r="T24" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U24">
-        <v>39786</v>
-      </c>
       <c r="V24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>155</v>
+        <v>239</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="Y24" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA24">
         <v>20</v>
@@ -4023,48 +3794,48 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>226</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F25" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -4075,17 +3846,14 @@
       <c r="T25" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U25">
-        <v>39786</v>
-      </c>
       <c r="V25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>143</v>
+        <v>244</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="Y25" s="2" t="s">
         <v>57</v>
@@ -4100,51 +3868,51 @@
         <v>56</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="AG25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F26" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>48</v>
@@ -4158,79 +3926,76 @@
       <c r="T26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U26">
-        <v>39786</v>
-      </c>
       <c r="V26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA26">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>224</v>
+        <v>100</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>114</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="F27" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -4241,17 +4006,14 @@
       <c r="T27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U27">
-        <v>39786</v>
-      </c>
       <c r="V27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>235</v>
+        <v>106</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>57</v>
@@ -4272,48 +4034,48 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>236</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="F28" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -4324,23 +4086,20 @@
       <c r="T28" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U28">
-        <v>39786</v>
-      </c>
       <c r="V28" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>89</v>
+        <v>260</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="Y28" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA28">
         <v>20</v>
@@ -4355,48 +4114,48 @@
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>239</v>
+        <v>65</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="F29" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -4407,23 +4166,20 @@
       <c r="T29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U29">
-        <v>39786</v>
-      </c>
       <c r="V29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA29">
         <v>20</v>
@@ -4438,45 +4194,43 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>244</v>
+        <v>41</v>
       </c>
       <c r="AG29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="AJ29" s="2" t="s">
-        <v>246</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="AJ29" s="2"/>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="F30" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>45</v>
+        <v>269</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>48</v>
@@ -4490,17 +4244,14 @@
       <c r="T30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U30">
-        <v>39786</v>
-      </c>
       <c r="V30" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>249</v>
+        <v>87</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>57</v>
@@ -4515,7 +4266,7 @@
         <v>56</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD30" s="2" t="s">
         <v>44</v>
@@ -4527,39 +4278,37 @@
         <v>41</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AJ30" s="2" t="s">
-        <v>251</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AJ30" s="2"/>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="F31" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>42</v>
@@ -4573,17 +4322,14 @@
       <c r="T31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U31">
-        <v>39786</v>
-      </c>
       <c r="V31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>57</v>
@@ -4598,54 +4344,52 @@
         <v>56</v>
       </c>
       <c r="AC31" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD31" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="AJ31" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="AJ31" s="2"/>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="F32" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G32">
         <v>9</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4656,17 +4400,14 @@
       <c r="T32" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U32">
-        <v>39786</v>
-      </c>
       <c r="V32" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="Y32" s="2" t="s">
         <v>57</v>
@@ -4687,48 +4428,46 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="AG32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="AJ32" s="2" t="s">
-        <v>260</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="AJ32" s="2"/>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="F33" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G33">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>264</v>
+        <v>66</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4739,17 +4478,14 @@
       <c r="T33" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U33">
-        <v>39786</v>
-      </c>
       <c r="V33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>94</v>
+        <v>282</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="Y33" s="2" t="s">
         <v>57</v>
@@ -4770,45 +4506,45 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="AG33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="F34" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G34">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>267</v>
+        <v>59</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>48</v>
@@ -4822,26 +4558,23 @@
       <c r="T34" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U34">
-        <v>39786</v>
-      </c>
       <c r="V34" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA34">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB34" s="2" t="s">
         <v>56</v>
@@ -4853,39 +4586,37 @@
         <v>44</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>268</v>
+        <v>105</v>
       </c>
       <c r="AG34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>64</v>
+        <v>229</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="AJ34" s="2" t="s">
-        <v>268</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AJ34" s="2"/>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="F35" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -4896,9 +4627,6 @@
       <c r="I35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J35" t="s">
-        <v>102</v>
-      </c>
       <c r="R35">
         <v>1</v>
       </c>
@@ -4908,17 +4636,14 @@
       <c r="T35" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U35">
-        <v>39786</v>
-      </c>
       <c r="V35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>55</v>
@@ -4939,51 +4664,48 @@
         <v>44</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="AG35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="F36" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G36">
         <v>2</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J36" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4994,26 +4716,23 @@
       <c r="T36" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U36">
-        <v>39786</v>
-      </c>
       <c r="V36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>143</v>
+        <v>260</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA36">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>56</v>
@@ -5025,51 +4744,48 @@
         <v>44</v>
       </c>
       <c r="AF36" s="2" t="s">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="AG36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="F37" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J37" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -5080,26 +4796,23 @@
       <c r="T37" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U37">
-        <v>39786</v>
-      </c>
       <c r="V37" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="Y37" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA37">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>56</v>
@@ -5111,51 +4824,45 @@
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AG37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>282</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="F38" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G38">
-        <v>3</v>
+        <v>46295</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J38" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="R38">
         <v>1</v>
@@ -5166,181 +4873,166 @@
       <c r="T38" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U38">
-        <v>39786</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA38">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AJ38" s="2" t="s">
-        <v>287</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="AJ38" s="2"/>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="F39" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G39">
-        <v>4</v>
+        <v>46295</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R39">
         <v>1</v>
       </c>
       <c r="S39">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U39">
-        <v>37500</v>
-      </c>
       <c r="V39" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>290</v>
+        <v>106</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA39">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB39" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC39" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD39" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>39</v>
+        <v>308</v>
       </c>
       <c r="AG39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AJ39" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="AJ39" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="F40" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G40">
-        <v>6</v>
+        <v>46295</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R40">
         <v>1</v>
       </c>
       <c r="S40">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U40">
-        <v>37500</v>
-      </c>
       <c r="V40" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>294</v>
+        <v>200</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="Y40" s="2" t="s">
         <v>57</v>
@@ -5349,7 +5041,7 @@
         <v>43</v>
       </c>
       <c r="AA40">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>56</v>
@@ -5361,75 +5053,69 @@
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>296</v>
+        <v>111</v>
       </c>
       <c r="AG40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="AJ40" s="2" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="F41" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G41">
-        <v>6</v>
+        <v>46295</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R41">
         <v>1</v>
       </c>
       <c r="S41">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U41">
-        <v>37500</v>
-      </c>
       <c r="V41" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="Y41" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA41">
         <v>20</v>
@@ -5444,43 +5130,42 @@
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ41" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="AJ41" s="2" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="F42" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G42">
-        <v>6</v>
+        <v>46295</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>48</v>
@@ -5489,31 +5174,28 @@
         <v>1</v>
       </c>
       <c r="S42">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U42">
-        <v>37500</v>
-      </c>
       <c r="V42" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA42">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB42" s="2" t="s">
         <v>56</v>
@@ -5525,45 +5207,40 @@
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ42" s="2" t="s">
-        <v>306</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="AJ42" s="2"/>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F43" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G43">
-        <v>8</v>
+        <v>46295</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>45</v>
+        <v>269</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>48</v>
@@ -5572,31 +5249,28 @@
         <v>1</v>
       </c>
       <c r="S43">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T43" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U43">
-        <v>37500</v>
-      </c>
       <c r="V43" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA43">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>56</v>
@@ -5608,45 +5282,40 @@
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="AJ43" s="2" t="s">
-        <v>119</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AJ43" s="2"/>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="F44" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G44">
-        <v>3</v>
+        <v>46295</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>48</v>
@@ -5655,28 +5324,25 @@
         <v>1</v>
       </c>
       <c r="S44">
-        <v>12500</v>
+        <v>13262</v>
       </c>
       <c r="T44" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U44">
-        <v>37500</v>
-      </c>
       <c r="V44" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="Y44" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA44">
         <v>20</v>
@@ -5697,150 +5363,152 @@
         <v>41</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="F45" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>318</v>
+        <v>45</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R45">
         <v>1</v>
       </c>
       <c r="S45">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>58</v>
       </c>
       <c r="U45">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="V45" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>319</v>
+        <v>106</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z45" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA45">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB45" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC45" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD45" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>321</v>
+        <v>134</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AJ45" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="AJ45" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="F46" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>324</v>
+        <v>59</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
       <c r="S46">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="T46" s="2" t="s">
         <v>58</v>
       </c>
       <c r="U46">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>325</v>
+        <v>227</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="Y46" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA46">
         <v>12</v>
@@ -5855,152 +5523,150 @@
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>327</v>
+        <v>41</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>86</v>
+        <v>229</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AJ46" s="2" t="s">
-        <v>328</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="AJ46" s="2"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="F47" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G47">
         <v>4</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R47">
         <v>1</v>
       </c>
       <c r="S47">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>58</v>
       </c>
       <c r="U47">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA47">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC47" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD47" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>327</v>
+        <v>60</v>
       </c>
       <c r="AG47" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>333</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F48" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R48">
         <v>1</v>
       </c>
       <c r="S48">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="T48" s="2" t="s">
         <v>58</v>
       </c>
       <c r="U48">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="V48" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>301</v>
+        <v>98</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>55</v>
@@ -6021,75 +5687,75 @@
         <v>44</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="AG48" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>63</v>
+        <v>348</v>
       </c>
       <c r="AJ48" s="2" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>338</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="F49" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R49">
         <v>1</v>
       </c>
       <c r="S49">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="T49" s="2" t="s">
         <v>58</v>
       </c>
       <c r="U49">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="V49" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA49">
         <v>20</v>
@@ -6104,48 +5770,48 @@
         <v>44</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AG49" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C50" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="F50" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>343</v>
+        <v>45</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -6163,70 +5829,72 @@
         <v>37</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA50">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB50" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC50" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD50" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>97</v>
+        <v>355</v>
       </c>
       <c r="AG50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AJ50" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="AJ50" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C51" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="F51" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G51">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -6244,16 +5912,16 @@
         <v>37</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>348</v>
+        <v>106</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="Y51" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z51" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AA51">
         <v>20</v>
@@ -6268,153 +5936,161 @@
         <v>44</v>
       </c>
       <c r="AF51" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="AJ51" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="AJ51" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
         <v>82</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="F52" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G52">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T52" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U52">
+        <v>37500</v>
+      </c>
       <c r="V52" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z52" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA52">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB52" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC52" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD52" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF52" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
         <v>82</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F53" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G53">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R53">
         <v>1</v>
       </c>
       <c r="S53">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T53" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U53">
+        <v>37500</v>
+      </c>
       <c r="V53" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z53" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA53">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB53" s="2" t="s">
         <v>56</v>
@@ -6426,75 +6102,78 @@
         <v>44</v>
       </c>
       <c r="AF53" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG53" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>239</v>
+        <v>134</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>240</v>
+        <v>366</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C54" t="s">
         <v>82</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F54" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G54">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R54">
         <v>1</v>
       </c>
       <c r="S54">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T54" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U54">
+        <v>37500</v>
+      </c>
       <c r="V54" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z54" s="2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AA54">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB54" s="2" t="s">
         <v>56</v>
@@ -6506,45 +6185,45 @@
         <v>44</v>
       </c>
       <c r="AF54" s="2" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>361</v>
+        <v>84</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C55" t="s">
         <v>82</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="F55" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G55">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>365</v>
+        <v>45</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>48</v>
@@ -6553,19 +6232,22 @@
         <v>1</v>
       </c>
       <c r="S55">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T55" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U55">
+        <v>37500</v>
+      </c>
       <c r="V55" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>57</v>
@@ -6580,70 +6262,73 @@
         <v>56</v>
       </c>
       <c r="AC55" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD55" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF55" s="2" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="AG55" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="AJ55" s="2"/>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C56" t="s">
         <v>82</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F56" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G56">
         <v>4</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R56">
         <v>1</v>
       </c>
       <c r="S56">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U56">
+        <v>37500</v>
+      </c>
       <c r="V56" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>122</v>
+        <v>378</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="Y56" s="2" t="s">
         <v>55</v>
@@ -6664,45 +6349,43 @@
         <v>44</v>
       </c>
       <c r="AF56" s="2" t="s">
-        <v>372</v>
+        <v>39</v>
       </c>
       <c r="AG56" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH56" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ56" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AJ56" s="2"/>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C57" t="s">
         <v>82</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F57" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>48</v>
@@ -6711,19 +6394,22 @@
         <v>1</v>
       </c>
       <c r="S57">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T57" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U57">
+        <v>37500</v>
+      </c>
       <c r="V57" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>70</v>
+        <v>382</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="Y57" s="2" t="s">
         <v>55</v>
@@ -6738,48 +6424,48 @@
         <v>56</v>
       </c>
       <c r="AC57" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF57" s="2" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AG57" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>190</v>
+        <v>385</v>
       </c>
       <c r="AJ57" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C58" t="s">
         <v>82</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="F58" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>45</v>
@@ -6791,771 +6477,54 @@
         <v>1</v>
       </c>
       <c r="S58">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T58" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U58">
+        <v>37500</v>
+      </c>
       <c r="V58" s="2" t="s">
         <v>37</v>
       </c>
       <c r="W58" s="2" t="s">
-        <v>143</v>
+        <v>330</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA58">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB58" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC58" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD58" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF58" s="2" t="s">
-        <v>379</v>
+        <v>41</v>
       </c>
       <c r="AG58" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH58" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="AJ58" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F59" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G59">
-        <v>2</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R59">
-        <v>1</v>
-      </c>
-      <c r="S59">
-        <v>13262</v>
-      </c>
-      <c r="T59" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W59" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="X59" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y59" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA59">
-        <v>16</v>
-      </c>
-      <c r="AB59" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC59" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD59" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF59" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AG59" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH59" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI59" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ59" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F60" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G60">
-        <v>6</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R60">
-        <v>1</v>
-      </c>
-      <c r="S60">
-        <v>13262</v>
-      </c>
-      <c r="T60" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V60" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W60" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="X60" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="Y60" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA60">
-        <v>12</v>
-      </c>
-      <c r="AB60" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC60" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD60" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF60" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AG60" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH60" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI60" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AJ60" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C61" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F61" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G61">
-        <v>2</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R61">
-        <v>1</v>
-      </c>
-      <c r="S61">
-        <v>13262</v>
-      </c>
-      <c r="T61" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W61" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="X61" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="Y61" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z61" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA61">
-        <v>20</v>
-      </c>
-      <c r="AB61" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC61" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD61" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF61" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG61" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH61" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI61" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AJ61" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C62" t="s">
-        <v>82</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F62" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G62">
-        <v>3</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R62">
-        <v>1</v>
-      </c>
-      <c r="S62">
-        <v>13262</v>
-      </c>
-      <c r="T62" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W62" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="X62" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="Y62" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z62" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA62">
-        <v>20</v>
-      </c>
-      <c r="AB62" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC62" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD62" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF62" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG62" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH62" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI62" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="AJ62" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C63" t="s">
-        <v>82</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F63" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G63">
-        <v>3</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R63">
-        <v>1</v>
-      </c>
-      <c r="S63">
-        <v>13262</v>
-      </c>
-      <c r="T63" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W63" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="X63" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="Y63" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA63">
-        <v>12</v>
-      </c>
-      <c r="AB63" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC63" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD63" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF63" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG63" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH63" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI63" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AJ63" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C64" t="s">
-        <v>82</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F64" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G64">
-        <v>4</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R64">
-        <v>1</v>
-      </c>
-      <c r="S64">
-        <v>13262</v>
-      </c>
-      <c r="T64" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V64" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W64" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="X64" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="Y64" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z64" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA64">
-        <v>20</v>
-      </c>
-      <c r="AB64" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC64" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF64" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG64" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH64" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI64" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ64" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C65" t="s">
-        <v>82</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F65" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G65">
-        <v>5</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R65">
-        <v>1</v>
-      </c>
-      <c r="S65">
-        <v>13262</v>
-      </c>
-      <c r="T65" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W65" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="X65" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="Y65" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z65" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA65">
-        <v>12</v>
-      </c>
-      <c r="AB65" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD65" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF65" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG65" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH65" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI65" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AJ65" s="2"/>
-    </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C66" t="s">
-        <v>82</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F66" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G66">
-        <v>5</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R66">
-        <v>1</v>
-      </c>
-      <c r="S66">
-        <v>13262</v>
-      </c>
-      <c r="T66" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V66" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W66" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="X66" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="Y66" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA66">
-        <v>12</v>
-      </c>
-      <c r="AB66" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD66" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF66" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG66" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH66" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI66" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="AJ66" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C67" t="s">
-        <v>82</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F67" s="1">
-        <v>46294</v>
-      </c>
-      <c r="G67">
-        <v>5</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R67">
-        <v>1</v>
-      </c>
-      <c r="S67">
-        <v>13262</v>
-      </c>
-      <c r="T67" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V67" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W67" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="X67" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="Y67" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA67">
-        <v>20</v>
-      </c>
-      <c r="AB67" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC67" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD67" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF67" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AG67" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH67" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI67" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ67" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="AJ58" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48405831-94E8-4101-A2C1-4AE4715D4867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE63221-BF70-45EA-B4A3-8DDA92EE4644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="342">
   <si>
     <t>Canal</t>
   </si>
@@ -235,988 +235,844 @@
     <t>Portadas</t>
   </si>
   <si>
+    <t>Semot</t>
+  </si>
+  <si>
+    <t>SSPH</t>
+  </si>
+  <si>
+    <t>Tulancingo</t>
+  </si>
+  <si>
+    <t>Reconstrucción de escuela</t>
+  </si>
+  <si>
+    <t>Saderh</t>
+  </si>
+  <si>
+    <t>Dulce Castillo</t>
+  </si>
+  <si>
+    <t>PGJEH</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Cultura</t>
+  </si>
+  <si>
+    <t>Van a demoler primaria en Tulancingo; edificarán otra</t>
+  </si>
+  <si>
+    <t>Semarnath</t>
+  </si>
+  <si>
+    <t>Bienestar</t>
+  </si>
+  <si>
+    <t>El Sol de Hidalgo</t>
+  </si>
+  <si>
+    <t>Gobierno</t>
+  </si>
+  <si>
+    <t>Rubén Juárez</t>
+  </si>
+  <si>
+    <t>Lorena Rosas</t>
+  </si>
+  <si>
+    <t>Veida Miranda</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>PGJEH, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Gobernador</t>
+  </si>
+  <si>
+    <t>Adela Garmez</t>
+  </si>
+  <si>
+    <t>Tula</t>
+  </si>
+  <si>
+    <t>Mirely Santos</t>
+  </si>
+  <si>
+    <t>Oscar Raúl Pérez</t>
+  </si>
+  <si>
+    <t>Luis Godínez</t>
+  </si>
+  <si>
+    <t>Accidente Vial</t>
+  </si>
+  <si>
+    <t>Rosalía Maldonado</t>
+  </si>
+  <si>
+    <t>Producción agrícola</t>
+  </si>
+  <si>
+    <t>Gustavo Vargas</t>
+  </si>
+  <si>
+    <t>Alejandro Reyes</t>
+  </si>
+  <si>
+    <t>Adopción De Menores</t>
+  </si>
+  <si>
+    <t>DIFH</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>Accidente de Transporte Público</t>
+  </si>
+  <si>
+    <t>Lizania Zavala</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Laura Karina Ramírez Jiménez</t>
+  </si>
+  <si>
+    <t>Breve</t>
+  </si>
+  <si>
+    <t>Omitlán</t>
+  </si>
+  <si>
+    <t>Investigación por corrupción</t>
+  </si>
+  <si>
+    <t>Impresiones locales</t>
+  </si>
+  <si>
+    <t>Emmanuel Villarreal</t>
+  </si>
+  <si>
+    <t>Buscan garantía en seguridad y respeto al voto en elección 2027</t>
+  </si>
+  <si>
+    <t>Tras el inicio del proceso electoral federal, dirigentes de partidos políticos en Hidalgo sostuvieron una reunión de trabajo con el secretario de Gobierno, Guillermo Olivares Reyna, para acordar esquemas de seguridad y paz.</t>
+  </si>
+  <si>
+    <t>Proceso electoral</t>
+  </si>
+  <si>
+    <t>Dirigentes partidistas acordaron mantener reuniones mensuales con la Secretaría de Gobierno para prevenir conflictos y garantizar un ambiente de paz en las elecciones.</t>
+  </si>
+  <si>
+    <t>Interiores</t>
+  </si>
+  <si>
+    <t>Teodoro Santos</t>
+  </si>
+  <si>
     <t>Segobh</t>
   </si>
   <si>
-    <t>Semot</t>
-  </si>
-  <si>
-    <t>SSPH</t>
-  </si>
-  <si>
-    <t>Contraloría</t>
-  </si>
-  <si>
-    <t>Tulancingo</t>
-  </si>
-  <si>
-    <t>Reconstrucción de escuela</t>
-  </si>
-  <si>
-    <t>Feria Pachuca</t>
-  </si>
-  <si>
-    <t>Turismo</t>
-  </si>
-  <si>
-    <t>Saderh</t>
-  </si>
-  <si>
-    <t>Dulce Castillo</t>
-  </si>
-  <si>
-    <t>PGJEH</t>
+    <t>Gobierno, PRD, Nueva Alianza, MC</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna, Margarita Ramos Villeda, Juana María Márquez Parrasales, Juan Ignacio Samperio Montaño</t>
+  </si>
+  <si>
+    <t>PGJEH, de las seis sin autonomía en el país</t>
+  </si>
+  <si>
+    <t>El Censo Nacional de Procuración de Justicia Estatal del Inegi ubica a la Procuraduría de Hidalgo entre las seis dependencias del país que no son un órgano constitucional autónomo.</t>
+  </si>
+  <si>
+    <t>Transición a Fiscalía</t>
+  </si>
+  <si>
+    <t>Hidalgo avanza en un 80% en el proceso de transición hacia la Fiscalía General de Justicia, órgano que contará con plena autonomía constitucional.</t>
+  </si>
+  <si>
+    <t>PGJEH, Congreso</t>
+  </si>
+  <si>
+    <t>Francisco Fernández</t>
+  </si>
+  <si>
+    <t>SEPH activa protocolo por arma en un escuela</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública de Hidalgo activó el protocolo institucional tras el hallazgo de un objeto presuntamente peligroso en la mochila de un estudiante en Huasca de Ocampo.</t>
+  </si>
+  <si>
+    <t>Huasca</t>
+  </si>
+  <si>
+    <t>Alumno Armado</t>
+  </si>
+  <si>
+    <t>La SEPH implementó medidas de prevención y resguardo en una secundaria de Huasca tras detectar un objeto no permitido entre las pertenencias de un alumno.</t>
+  </si>
+  <si>
+    <t>Miriam Avilés</t>
+  </si>
+  <si>
+    <t>Invierten 10 mil mdp en el parque industrial</t>
+  </si>
+  <si>
+    <t>El titular de la Unidad de Planeación y Prospectiva, Miguel Ángel Tello Vargas, detalló la inversión federal para consolidar el Polo de Desarrollo Económico Reserva Zapotlán.</t>
+  </si>
+  <si>
+    <t>Zapotlán</t>
+  </si>
+  <si>
+    <t>Parque industrial</t>
+  </si>
+  <si>
+    <t>El gobierno confirmó una bolsa superior a 10 mil mdp para obras de infraestructura carretera y ferroviaria en el Parque Industrial de Zapotlán.</t>
   </si>
   <si>
     <t>Planeación</t>
   </si>
   <si>
-    <t>Magda Acuña</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Cultura</t>
+    <t>Planeación, Presidencia</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas</t>
+  </si>
+  <si>
+    <t>Entregan el Premio Estatal de la Juventud 2026</t>
+  </si>
+  <si>
+    <t>Dieciocho jóvenes hidalguenses fueron galardonados con el Premio Estatal de la Juventud 2026 en una ceremonia encabezada por el gobernador Julio Menchaca Salazar.</t>
+  </si>
+  <si>
+    <t>Premio Estatal De La Juventud</t>
+  </si>
+  <si>
+    <t>El gobernador entregó reconocimientos y apoyos por más de 6.2 mdp a jóvenes destacados por su trayectoria y aportaciones sociales en Hidalgo.</t>
+  </si>
+  <si>
+    <t>Priorizan apoyos para usuarias de Centros LIBRE</t>
+  </si>
+  <si>
+    <t>Usuarias de los Centros LIBRE recibirán prioridad en la entrega de apoyos económicos del gobierno estatal, además de atención médica y jurídica gratuita del Instituto Hidalguense de las Mujeres.</t>
+  </si>
+  <si>
+    <t>Apoyo A La Mujer</t>
+  </si>
+  <si>
+    <t>El gobierno del estado fortalece la atención a mujeres vulnerables otorgando preferencia a usuarias de los Centros LIBRE en los programas sociales.</t>
+  </si>
+  <si>
+    <t>Invierten 2.1 mdp en techado para Cobach</t>
+  </si>
+  <si>
+    <t>Durante una gira de trabajo por San Felipe Orizatlán, autoridades educativas iniciaron las obras de un techado para la cancha deportiva del Cobaeh Ahuatitla.</t>
+  </si>
+  <si>
+    <t>San Felipe Orizatlán</t>
+  </si>
+  <si>
+    <t>Infraestructura escolar</t>
+  </si>
+  <si>
+    <t>La SEPH puso en marcha obras de infraestructura escolar en planteles de educación media y básica en San Felipe Orizatlán.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>Francisco Villeda</t>
+  </si>
+  <si>
+    <t>Concreta DIFH tres nuevas adopciones; suman 61 en 4 años</t>
+  </si>
+  <si>
+    <t>En los últimos cuatro años, el Sistema para el Desarrollo Integral de la Familia de Hidalgo (DIFH) ha formalizado la adopción de 61 niñas, niños y adolescentes a través del programa Puentes de Amor, incluyendo tres menores con alguna discapacidad.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo ha formalizado 61 adopciones en cuatro años a través del programa Puentes de Amor, sumando tres nuevas familias integradas.</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Ricardo Alvizo Contreras, Laura Karina Ramírez Jiménez</t>
+  </si>
+  <si>
+    <t>Invierten 6.2 mdp en programas sociales para las juventudes</t>
+  </si>
+  <si>
+    <t>Durante la entrega del Premio Estatal de la Juventud 2026, las autoridades informaron sobre la inversión de 6.2 millones de pesos en diversos esquemas de apoyo para jóvenes en Hidalgo.</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo destinó 6.2 millones de pesos en programas del IHJ y entregó galardones del Premio Estatal de la Juventud 2026.</t>
+  </si>
+  <si>
+    <t>Sebiso, IHJ, Gobierno</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno, Ricardo Olvera Molina, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Cultura prepara etiqueta para garantizar autenticidad de obras</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura estatal diseña un sello distintivo en conjunto con la federación para certificar las piezas elaboradas manualmente por artesanos hidalguenses.</t>
+  </si>
+  <si>
+    <t>Padrón de artesanos</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo crea una etiqueta oficial de autenticidad para proteger el trabajo de artesanos locales frente a revendedores.</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar</t>
+  </si>
+  <si>
+    <t>Van 26 personas con miasis por barrenador</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo mantiene acciones de vigilancia epidemiológica ante la presencia del gusano barrenador, el cual ha afectado a 26 personas en la entidad sin registrar defunciones. Además, atienden demandas en la presa Endhó y previenen el suicidio.</t>
+  </si>
+  <si>
+    <t>Vigilancia Epidemiológica</t>
+  </si>
+  <si>
+    <t>La SSH reportó 26 casos dados de alta de gusano barrenador en Hidalgo e intensificó acciones sanitarias en la presa Endhó y programas de prevención del suicidio.</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Maximiliano Pérez</t>
+  </si>
+  <si>
+    <t>SSH, Cenaprece</t>
+  </si>
+  <si>
+    <t>Reconocen a 18 jóvenes en Hidalgo</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar presidió la entrega del Premio Estatal de la Juventud 2026, con el que fueron reconocidos 18 jóvenes por su trayectoria y aportaciones en áreas académicas, científicas, culturales, de emprendimiento e inclusión social.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca entregó el Premio Estatal de la Juventud 2026 a 18 jóvenes destacados y resaltó la inversión de 6.2 mdp en programas para las juventudes.</t>
+  </si>
+  <si>
+    <t>Blanca Soriano</t>
+  </si>
+  <si>
+    <t>Gobierno, IHJ, Sebiso, Semoth, Caasim, SICT</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Luis Ricardo Olvera Molina, Flor María Bautista Álvarez, Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Llevan la innovación y soluciones a Expociencias</t>
+  </si>
+  <si>
+    <t>Estudiantes del Colegio de Estudios Científicos y Tecnológicos del Estado de Hidalgo (CECYTEH) presentaron 10 proyectos de ciencia y tecnología aplicados a problemáticas locales durante la Expociencias Hidalgo 2026.</t>
+  </si>
+  <si>
+    <t>Innovación tecnológica</t>
+  </si>
+  <si>
+    <t>Alumnos del CECYTEH destacaron en la Expociencias Hidalgo 2026 al presentar 10 proyectos enfocados en resolver problemas locales mediante ciencia y tecnología.</t>
+  </si>
+  <si>
+    <t>SEPH, UAEH</t>
+  </si>
+  <si>
+    <t>Daniel Cruz Campos</t>
+  </si>
+  <si>
+    <t>DIF concreta otras tres adopciones</t>
+  </si>
+  <si>
+    <t>Tres menores de edad iniciaron una nueva etapa de vida al integrarse legalmente a sus familias adoptivas durante el evento "Un puente de amor", encabezado por Edda Vite Ramos, presidenta del Patronato del Sistema DIF Hidalgo.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo concretó la adopción de tres menores mediante el programa "Un puente de amor", alcanzando 62 adopciones durante la presente administración estatal.</t>
+  </si>
+  <si>
+    <t>Abren registro para Bono de Discapacidad</t>
+  </si>
+  <si>
+    <t>La Sección 15 del Sindicato Nacional de Trabajadores de la Educación (SNTE) abrió el proceso de selección para otorgar el denominado Bono de Discapacidad a trabajadores de la educación en activo o a sus hijos que viven con alguna condición especial.</t>
+  </si>
+  <si>
+    <t>Apoyo a personas con discapacidad</t>
+  </si>
+  <si>
+    <t>La Sección 15 del SNTE convocó a docentes en activo a registrarse para obtener el Bono de Discapacidad para trabajadores o sus hijos con alguna condición especial.</t>
+  </si>
+  <si>
+    <t>SEPH, SNTE, ISSSTE, IMSS, DIFH</t>
+  </si>
+  <si>
+    <t>Said Vargas Sáenz</t>
+  </si>
+  <si>
+    <t>Verifican los que salen a otras zonas de Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Automovilistas de Ixmiquilpan acuden a realizar la verificación vehicular en la unidad móvil de la comunidad de Dios Padre principalmente cuando requieren trasladarse a Pachuca, Tula, Querétaro o Puebla por ser un requisito obligatorio.</t>
+  </si>
+  <si>
+    <t>Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Verificación vehicular</t>
+  </si>
+  <si>
+    <t>El verificentro móvil de Ixmiquilpan atiende prioritariamente a conductores que necesitan viajar a otros municipios o estados donde la verificación es exigida.</t>
+  </si>
+  <si>
+    <t>Regional</t>
+  </si>
+  <si>
+    <t>Omar Santiago</t>
+  </si>
+  <si>
+    <t>Luis David Alamilla Zúñiga</t>
+  </si>
+  <si>
+    <t>Aprovechar el lirio no es la solución</t>
+  </si>
+  <si>
+    <t>El ambientalista Carlos Álvarez Flores señaló que buscar un aprovechamiento permanente del lirio acuático en la presa Endhó es un contrasentido, pues la prioridad debe ser frenar la contaminación del agua y realizar tratamientos efectivos.</t>
+  </si>
+  <si>
+    <t>Lirio Acuático</t>
+  </si>
+  <si>
+    <t>El especialista Carlos Álvarez afirmó que la prioridad en la presa Endhó debe ser eliminar la contaminación del agua en lugar de enfocarse únicamente en cosechar el lirio.</t>
+  </si>
+  <si>
+    <t>Semarnath, Conagua, Citnova</t>
+  </si>
+  <si>
+    <t>Carlos Álvarez Flores, Hugo García Reyes</t>
+  </si>
+  <si>
+    <t>Cerca de 6 toneladas de café anuales</t>
+  </si>
+  <si>
+    <t>Productores de café de la Huasteca hidalguense cosechan alrededor de 6 mil toneladas anuales, pero enfrentan afectaciones por el cambio climático y la roya, por lo que solicitan mayor asesoría técnica y apoyos para comercializar su producto a precios justos.</t>
+  </si>
+  <si>
+    <t>Huazalingo</t>
+  </si>
+  <si>
+    <t>Cafetaleros de la Huasteca hidalguense pidieron asesoría comercial y apoyos para combatir la roya y lograr precios competitivos para sus cosechas.</t>
+  </si>
+  <si>
+    <t>Saderh, Sader</t>
+  </si>
+  <si>
+    <t>Rosendo Hernández Castillo, Jorge Rocha Reyes</t>
   </si>
   <si>
     <t>Sandra Sauza</t>
   </si>
   <si>
+    <t>Lirio acuático se apodera de la presa Javier Rojo Gómez</t>
+  </si>
+  <si>
+    <t>A casi dos años de que pobladores de comunidades aledañas a la presa Javier Rojo Gómez en Alfajayucan denunciaran la plaga de lirio que cubre más de 90% del embalse y genera mosco Culex, la problemática persiste sin que las autoridades municipales hayan logrado retirar la planta.</t>
+  </si>
+  <si>
+    <t>Alfajayucan</t>
+  </si>
+  <si>
+    <t>Pobladores de Alfajayucan denunciaron que el lirio acuático cubre más de 90% de la presa Javier Rojo Gómez y genera plaga de mosco Culex sin acciones efectivas de retiro.</t>
+  </si>
+  <si>
+    <t>Erika Gutiérrez</t>
+  </si>
+  <si>
+    <t>Semarnath, Conagua, Cenaprece</t>
+  </si>
+  <si>
+    <t>Julio Agustín Cruz Tovar</t>
+  </si>
+  <si>
+    <t>Estatal dejaría secretaría para competir en 2027</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar confirmó que un integrante de su gabinete estatal evalúa dejar su cargo de secretario para participar en el proceso electoral de 2027, señalando que quien busque competir debe asumir los riesgos correspondientes.</t>
+  </si>
+  <si>
+    <t>Aspirantes</t>
+  </si>
+  <si>
+    <t>Un secretario del gabinete del gobernador Julio Menchaca evalúa dejar su cargo para buscar una candidatura en las elecciones de 2027.</t>
+  </si>
+  <si>
+    <t>Ricardo Calleja</t>
+  </si>
+  <si>
+    <t>Imputaciones aumentaron 13% en un año en la entidad</t>
+  </si>
+  <si>
+    <t>Durante 2025, la PGJEH formuló imputación a 5 mil 302 personas, de las cuales 4 mil 791 fueron vinculadas a proceso, lo que representó un incremento del 13% respecto al año anterior, según datos del Censo Nacional de Procuración de Justicia del Inegi.</t>
+  </si>
+  <si>
+    <t>Procuración de Justicia</t>
+  </si>
+  <si>
+    <t>Las imputaciones formuladas por el Ministerio Público en Hidalgo crecieron 13% en 2025 al alcanzar 5 mil 302 casos, según el Inegi.</t>
+  </si>
+  <si>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>PGJEH, Inegi, FGR</t>
+  </si>
+  <si>
+    <t>Han sido adoptados en Hidalgo 3 menores con discapacidad en 4 años</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo ha concretado 61 adopciones en los últimos cuatro años, de las cuales tres corresponden a menores con alguna discapacidad, como el caso de Elías Gabriel, de dos años y dos meses con acondroplasia, quien fue integrado a su nueva familia.</t>
+  </si>
+  <si>
+    <t>El DIF Hidalgo sumó 61 adopciones en cuatro años, entre ellas tres menores con discapacidad, restituyendo su derecho a integrarse a un hogar.</t>
+  </si>
+  <si>
+    <t>Laura Karina Ramírez Jiménez</t>
+  </si>
+  <si>
+    <t>Menchaca entregó el Premio de la Juventud</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar encabezó la entrega del Premio Estatal de la Juventud 2026 a 18 galardonados y otorgó apoyos sociales a 667 jóvenes, destacando un incremento presupuestal del 360% en programas sociales durante su administración.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca reconoció a 18 galardonados del Premio Estatal de la Juventud 2026 y entregó programas sociales con inversión de 6.2 mdp.</t>
+  </si>
+  <si>
+    <t>Gobierno, Sebiso, IHJ</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Ricardo Gómez Moreno, Luis Ricardo Olvera Molina, Flor María Bautista Álvarez</t>
+  </si>
+  <si>
+    <t>Estudiante desarrolla dron para reforestación</t>
+  </si>
+  <si>
+    <t>José de Jesús Rivas Ángeles, estudiante del Conalep Hidalgo, desarrolló Agrofly, un proyecto que adapta un dron para mapear terrenos y dispersar cápsulas de semillas endémicas en zonas forestales de difícil acceso afectadas por tala o incendios.</t>
+  </si>
+  <si>
+    <t>Estudiante del Conalep Hidalgo creó Agrofly, un dron diseñado para reforestar mediante dispersión aérea de semillas en zonas boscosas de difícil acceso.</t>
+  </si>
+  <si>
+    <t>Conalep</t>
+  </si>
+  <si>
+    <t>José de Jesús Rivas Ángeles</t>
+  </si>
+  <si>
+    <t>Decomisaron un arma en secundaria de Huasca</t>
+  </si>
+  <si>
+    <t>Un arma de fuego y cartuchos fueron decomisados a un estudiante de 13 años durante un operativo de revisión en la secundaria Teodomiro Manzano en Huasca de Ocampo, provocando la activación de protocolos de la SEPH e investigaciones de autoridades.</t>
+  </si>
+  <si>
+    <t>Autoridades decomisaron un arma de fuego a un alumno de secundaria en Huasca de Ocampo; la SEPH activó protocolos de seguridad e investigación.</t>
+  </si>
+  <si>
+    <t>Transporte público suma dos accidentes</t>
+  </si>
+  <si>
+    <t>Dos percances viales del transporte público se registraron en la región Tulancingo en menos de una semana, dejando saldo de un chofer fallecido tras sufrir un infarto al volante y tres pasajeros lesionados.</t>
+  </si>
+  <si>
+    <t>Dos accidentes de colectivas en la región Tulancingo dejaron un conductor sin vida y tres personas heridas.</t>
+  </si>
+  <si>
+    <t>Semot, Cruz Roja</t>
+  </si>
+  <si>
+    <t>Hubo 2 ingresos de armas a escuelas en una semana</t>
+  </si>
+  <si>
+    <t>Tras el caso detectado en la secundaria general Teodomiro Manzano en Huasca de Ocampo, la SEPH activó protocolos institucionales para salvaguardar a la comunidad escolar. Además, en esta semana se reportó la evacuación preventiva del Centro de Estudios de Bachillerato Prof. Rafael Ramírez en Pachuca por un incidente similar.</t>
+  </si>
+  <si>
+    <t>La SEPH activó protocolos de seguridad por el hallazgo de armas de fuego en planteles educativos de Huasca y Pachuca, exhortando a los padres de familia a supervisar los objetos de los alumnos.</t>
+  </si>
+  <si>
+    <t>Carmen Hernández</t>
+  </si>
+  <si>
+    <t>Alista un secretario de Hidalgo posible candidatura para 2027</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar reveló que un miembro de su gabinete le manifestó su interés por competir en el proceso electoral de 2027. El mandatario indicó que quien decida participar deberá renunciar a su cargo y comparecer ante el Congreso local, dejando en claro que no habrá posibilidad de reincorporación si no obtiene la candidatura.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca confirmó que un integrante de su gabinete evalúa postularse en 2027 y aclaró que de aceptar la contienda deberá dejar su puesto definitivamente antes de las comparecencias.</t>
+  </si>
+  <si>
+    <t>Gobierno, Congreso, Morena</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Edgar Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>Descarta JMS al Chico para las Casas del Bienestar</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca descartó construir Viviendas del Bienestar en la cabecera municipal de Mineral del Chico debido a la falta de espacio, sugiriendo que podrían ubicarse en localidades como La Estanzuela, Benito Juárez o Carboneras. Mencionó que la Semot, Caasim y Sipdus trabajan en las rutas y servicios requeridos para estos desarrollos.</t>
+  </si>
+  <si>
+    <t>Mineral del Chico</t>
+  </si>
+  <si>
+    <t>Proyectos Federales</t>
+  </si>
+  <si>
+    <t>Julio Menchaca aclaró que la escasez de terrenos impide edificar Casas del Bienestar en la cabecera de Mineral del Chico, por lo que se evalúa realizarlas en comunidades alejadas.</t>
+  </si>
+  <si>
+    <t>Gobernador, Semot, Caasim, Sipdus, Presidencia</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>DIF estatal entrega tres niños a sus familias adoptivas</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo celebró el evento 'Adopción, un puente de amor', en el que tres menores —entre ellos Elías Gabriel, de dos años, que vive con acondroplasia, y dos recién nacidos— se integraron legalmente a sus nuevas familias en el Centro Pilares de Pachuca. Con esta entrega, suman 61 adopciones en lo que va de la administración estatal.</t>
+  </si>
+  <si>
+    <t>El DIF Hidalgo integró a tres menores a sus familias adoptivas como parte del programa Un puente de amor, alcanzando 61 procesos de adopción concretados durante el gobierno actual.</t>
+  </si>
+  <si>
+    <t>Suben 40 por ciento denuncias por robos</t>
+  </si>
+  <si>
+    <t>De acuerdo con el Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública, las denuncias por robo en sus diversas modalidades crecieron un 40 por ciento en Mineral del Monte entre enero y agosto de 2026, pasando de 30 carpetas en 2025 a 50 en el presente año. Asimismo, se reportó un incremento en las investigaciones por lesiones y narcomenudeo.</t>
+  </si>
+  <si>
+    <t>Mineral del Monte</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>Las carpetas de investigación por robo en Mineral del Monte aumentaron 40% durante los primeros ocho meses de 2026 en comparación con 2025, de acuerdo con cifras del SESNSP.</t>
+  </si>
+  <si>
+    <t>Martha Sáenz</t>
+  </si>
+  <si>
+    <t>SSPH, PGJEH</t>
+  </si>
+  <si>
+    <t>Vinculan a proceso a exalcalde de Omitlán de Juárez por peculado</t>
+  </si>
+  <si>
+    <t>En audiencia privada celebrada en los juzgados de Pachuca, la jueza Karina Vértiz Marín vinculó a proceso al exalcalde de Omitlán de Juárez, Jorge Martín Borbolla Calderón, por el delito de peculado. Se le investiga por la venta desproporcionada de un predio municipal de 39 mil metros cuadrados en 21 millones de pesos, cuando su valor comercial oscila entre 49 y 64 millones.</t>
+  </si>
+  <si>
+    <t>El exalcalde Jorge Martín Borbolla Calderón fue vinculado a proceso por peculado tras la venta presuntamente subvaluada de un terreno municipal donado para fines de interés social.</t>
+  </si>
+  <si>
+    <t>Jorge Martín Borbolla Calderón, Karina Vértiz Marín, Martha Belem Oliver González</t>
+  </si>
+  <si>
+    <t>Cambios viales generan molestias entre habitantes y automovilistas</t>
+  </si>
+  <si>
+    <t>Los cierres de accesos y la habilitación de rutas alternas por las obras del nuevo puente de La Romera en Tepeji del Río han provocado inconformidad entre vecinos y conductores. La obra contempla una inversión y un plazo de ejecución de 245 días para agilizar la conectividad entre Tianguistengo y El Cerrito.</t>
+  </si>
+  <si>
+    <t>Tepeji del Río</t>
+  </si>
+  <si>
+    <t>Obras De Infraestructura</t>
+  </si>
+  <si>
+    <t>Habitantes de Tepeji del Río externaron su inconformidad por los cortes a la circulación vial derivados de la edificación del nuevo puente vehicular en la zona de La Romera.</t>
+  </si>
+  <si>
+    <t>Abigail García Torres</t>
+  </si>
+  <si>
+    <t>Sipdus, Ayuntamiento, INAH</t>
+  </si>
+  <si>
+    <t>Claudia Ávila</t>
+  </si>
+  <si>
+    <t>Menchaca Salazar respalda a la juventud hidalguense</t>
+  </si>
+  <si>
+    <t>Como un reconocimiento y respaldo a las y los jóvenes hidalguenses, el gobernador Julio Menchaca Salazar encabezó la entrega del Premio Estatal de la Juventud 2026 y programas sociales para 667 beneficiarios, gracias a la inversión de seis millones 200 mil pesos.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca entregó el Premio Estatal de la Juventud 2026 y programas sociales en beneficio de 667 jóvenes hidalguenses con una inversión de 6.2 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Flor María Bautista Álvarez, Ricardo Gómez Moreno, Luis Ricardo Olvera Molina</t>
+  </si>
+  <si>
+    <t>Funcionarios estatales analizan irse de candidatos</t>
+  </si>
+  <si>
+    <t>Integrantes del gobierno de Hidalgo analizan dejar sus cargos para buscar una candidatura en el proceso electoral de 2027, reconoció Julio Menchaca Salazar, gobernador de Hidalgo, advirtiendo que no podrán regresar a sus puestos.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca confirmó que miembros de su gabinete evalúan buscar candidaturas para 2027 y recalcó que quienes decidan competir no podrán reincorporarse a sus cargos.</t>
+  </si>
+  <si>
+    <t>Gobernador, Morena, Congreso</t>
+  </si>
+  <si>
+    <t>Con operativo Mochila, detectan arma en Secundaria de Huasca</t>
+  </si>
+  <si>
+    <t>Durante la implementación del Operativo Mochila en la Escuela Secundaria General Teodomiro Manzano del municipio de Huasca de Ocampo, autoridades detectaron un arma de fuego y cartuchos al interior de la mochila de un alumno.</t>
+  </si>
+  <si>
+    <t>Autoridades decomisaron un arma de fuego y cartuchos a un estudiante durante el Operativo Mochila en una secundaria de Huasca de Ocampo; la SEPH activó protocolos escolares.</t>
+  </si>
+  <si>
+    <t>Páginas interiores</t>
+  </si>
+  <si>
+    <t>Supervisan unidades de transporte público</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte de Hidalgo dio a conocer que el personal del Sistema de Transporte Convencional mantiene labores de vigilancia y supervisión en Tolcayuca, Huejutla, Tulancingo, Mineral de la Reforma y Pachuca.</t>
+  </si>
+  <si>
+    <t>Supervisión de Transporte</t>
+  </si>
+  <si>
+    <t>La Semot realizó operativos de inspección a unidades de transporte público en cinco municipios de Hidalgo para garantizar el cumplimiento de la Ley de Movilidad.</t>
+  </si>
+  <si>
+    <t>Semot, STCH</t>
+  </si>
+  <si>
+    <t>Motociclista pierde la vida tras una carambola en la México-Pachuca</t>
+  </si>
+  <si>
+    <t>Una mañana mortal fue la de este jueves sobre la Autopista México-Pachuca, donde se registró una carambola a la altura de Ecatepec que dejó como saldo preliminar a un motociclista sin vida y cuantiosos daños materiales.</t>
+  </si>
+  <si>
+    <t>Un motociclista falleció tras una carambola ocurrida en el kilómetro 14 de la autopista México-Pachuca a la altura de Ecatepec, provocando severas afectaciones viales.</t>
+  </si>
+  <si>
+    <t>1 secretario de Hidalgo analiza participar en proceso electoral de 2027</t>
+  </si>
+  <si>
+    <t>Un integrante del gabinete del gobernador Julio Menchaca Salazar analiza participar en el proceso interno de Morena rumbo a las elecciones de 2027, situación que podría derivar en su salida anticipada de la administración estatal, confirmó el mandatario. El gobernador señaló que si el funcionario decide contender deberá ajustar sus tiempos y adelantar su comparecencia ante el Congreso de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Un titular de secretaría del gobierno de Hidalgo analiza registrarse en la convocatoria interna de Morena rumbo a los comicios de 2027, por lo que tendría que adelantar su comparecencia ante el Congreso local y separarse de su cargo.</t>
+  </si>
+  <si>
+    <t>Erick Perales</t>
+  </si>
+  <si>
+    <t>Gobierno, Morena, Congreso</t>
+  </si>
+  <si>
+    <t>16 adolescentes permanecen en proceso de adopción, a través del DIF en Hidalgo</t>
+  </si>
+  <si>
+    <t>El programa "Puente de Amor" del Sistema DIF Hidalgo ha concretado 61 adopciones en los últimos cuatro años, mientras que 16 adolescentes permanecen en proceso sin que hasta ahora se hayan encontrado familias interesadas. La presidenta del Patronato, Edda Vite Ramos, y la procuradora Laura Karina Ramírez Jiménez explicaron que las principales dificultades se deben a situaciones de discapacidad, grupos de hermanos o edad avanzada.</t>
+  </si>
+  <si>
+    <t>El programa "Puente de Amor" del DIF Hidalgo registra 61 adopciones concluidas sin revocación; actualmente 13 familias cuentan con certificado de idoneidad y 16 adolescentes con alguna condición de discapacidad o mayor edad buscan integrarse a un hogar.</t>
+  </si>
+  <si>
+    <t>Repartieron 6.2 mdp en apoyos para 667 jóvenes hidalguenses</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca encabezó la entrega del Premio Estatal de la Juventud 2026 y beneficios económicos para 667 jóvenes hidalguenses con una inversión de 6.2 millones de pesos. El secretario de Bienestar e Inclusión Social, Ricardo Gómez Moreno, detalló que se entregaron bolsas y recursos mediante programas como Jóvenes Embajadores, Transformando Emprendedores y Titúlate.</t>
+  </si>
+  <si>
+    <t>El gobierno estatal dispersó 6.2 millones de pesos a 667 jóvenes hidalguenses mediante el Premio Estatal de la Juventud 2026 y los programas Jóvenes Embajadores, Transformando Emprendedores y Titúlate.</t>
+  </si>
+  <si>
+    <t>Bienestar, Gobierno</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Ricardo Gómez Moreno, Luis Ricardo Olvera Molina</t>
+  </si>
+  <si>
+    <t>La escuela primaria Aquiles Serdán de Tulancingo será demolida y reconstruida totalmente debido a graves daños estructurales. El titular de la SEPH, Natividad Castrejón, explicó que las obras abarcarán todo el ciclo escolar 2026-2027 y los alumnos tomarán clases en sedes temporales o en modalidad híbrida/virtual mientras se concluye el nuevo plantel.</t>
+  </si>
+  <si>
+    <t>La SEPH anunció la demolición y sustitución completa de la primaria Aquiles Serdán en Tulancingo por daños estructurales, reubicando temporalmente a los alumnos para el ciclo escolar 2026-2027.</t>
+  </si>
+  <si>
+    <t>DIFH concreta 61 adopciones en cuatro años; 16 adolescentes en espera</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo concretó la adopción de 61 niñas, niños y adolescentes a través del programa "Puente de Amor", durante los cuatro años de la actual administración. Este jueves primero de octubre, tres menores fueron integrados a sus nuevas familias: Elías Gabriel, de dos años y dos meses con acondroplasia, y Leonel, de 21 días de nacido. La titular de la Procuraduría de Protección a Niñas, Niños, Adolescentes y la Familia, Laura Karina Ramírez Jiménez, explicó que el proceso certificado dura seis meses. Edda Vite Ramos informó que actualmente hay 16 adolescentes susceptibles de adopción pero sin familias interesadas por presentar alguna condición de discapacidad física, motriz o intelectual.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo ha concretado la adopción de 61 menores en cuatro años mediante el programa "Puente de Amor", integrando a tres niños a nuevos hogares el 1 de octubre, mientras 16 adolescentes con discapacidad siguen en espera.</t>
+  </si>
+  <si>
+    <t>Menchaca confirma que un integrante de su gabinete analiza contender en las elecciones de 2027</t>
+  </si>
+  <si>
+    <t>Un integrante del gabinete estatal analiza participar en el proceso electoral de 2027, confirmó el gobernador de Hidalgo, Julio Menchaca Salazar. Aunque no reveló el nombre, indicó que se trata de un titular de secretaría quien deberá adelantar su comparecencia ante el Congreso local en caso de separarse de su cargo.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar confirmó que un secretario de su gabinete evalúa contender en los comicios de 2027, precisando que deberá adelantar su comparecencia antes de dejar el cargo.</t>
+  </si>
+  <si>
+    <t>Gobernador, Congreso</t>
+  </si>
+  <si>
+    <t>Reconocen a 18 jóvenes con el Premio Estatal de la Juventud 2026</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar encabezó la entrega del Premio Estatal de la Juventud 2026 y programas sociales para 667 beneficiarios, con una inversión de 6.2 millones de pesos. El secretario de Bienestar e Inclusión Social, Ricardo Gómez Moreno, detalló la asignación de bolsas para el Premio Estatal de la Juventud, Jóvenes Embajadores, Transformando Emprendedores y Titúlate.</t>
+  </si>
+  <si>
+    <t>El Ejecutivo estatal premió a 18 jóvenes hidalguenses y entregó apoyos sociales por 6.2 millones de pesos a 667 beneficiarios mediante programas de emprendimiento, titulación y liderazgo juvenil.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Ricardo Gómez Moreno, Ricardo Olvera Molina</t>
+  </si>
+  <si>
+    <t>Tres lenguas indígenas de Hidalgo registran disminución en su número de hablantes</t>
+  </si>
+  <si>
+    <t>Las lenguas indígenas tepehua, pame y tének registran una disminución en el número de hablantes en Hidalgo, sumando en conjunto no más de 350 usuarios, informó Prisco Manuel Gutiérrez, comisionado estatal para el Desarrollo Sostenible de los Pueblos Indígenas, atribuyendo el fenómeno a la migración y al desuso generacional.</t>
+  </si>
+  <si>
+    <t>Preservación Lenguas Maternas</t>
+  </si>
+  <si>
+    <t>El comisionado para el Desarrollo Sostenible de los Pueblos Indígenas advirtió sobre la reducción de hablantes de las lenguas tepehua, pame y tének en Hidalgo, llamando a fortalecer su transmisión en el entorno familiar.</t>
+  </si>
+  <si>
     <t>Berenice Gamboa</t>
   </si>
   <si>
-    <t>Claudia Ávila</t>
-  </si>
-  <si>
-    <t>Erick Perales</t>
-  </si>
-  <si>
-    <t>Van a demoler primaria en Tulancingo; edificarán otra</t>
-  </si>
-  <si>
-    <t>Francisco Villeda</t>
-  </si>
-  <si>
-    <t>Semarnath</t>
-  </si>
-  <si>
-    <t>Bienestar</t>
-  </si>
-  <si>
-    <t>Combate Al Huachicol</t>
-  </si>
-  <si>
-    <t>SSPH, PGJEH</t>
-  </si>
-  <si>
-    <t>Combate Al Narcomenudeo</t>
-  </si>
-  <si>
-    <t>Carmen Hernández</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>El Sol de Hidalgo</t>
-  </si>
-  <si>
-    <t>Coordinación interestatal</t>
-  </si>
-  <si>
-    <t>Nota principal</t>
-  </si>
-  <si>
-    <t>Blanca Soriano</t>
-  </si>
-  <si>
-    <t>Gobierno</t>
-  </si>
-  <si>
-    <t>Prevención De Riesgos</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Tello Vargas</t>
-  </si>
-  <si>
-    <t>Tlanchinol</t>
-  </si>
-  <si>
-    <t>Desapariciones</t>
-  </si>
-  <si>
-    <t>Rubén Juárez</t>
-  </si>
-  <si>
-    <t>Lorena Rosas</t>
-  </si>
-  <si>
-    <t>Gabinete de Seguridad</t>
-  </si>
-  <si>
-    <t>Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Actopan</t>
-  </si>
-  <si>
-    <t>Javier Quezada</t>
-  </si>
-  <si>
-    <t>Veida Miranda</t>
-  </si>
-  <si>
-    <t>Tarifario de taxis</t>
-  </si>
-  <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Conservación de especies</t>
-  </si>
-  <si>
-    <t>PGJEH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Convivencia Escolar</t>
-  </si>
-  <si>
-    <t>Ana Luisa Vega</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Impresos locales</t>
-  </si>
-  <si>
-    <t>Rehabilitación del Jardín Colón costará 5.3 mdp</t>
-  </si>
-  <si>
-    <t>Con un plazo de 185 días naturales, el gobierno del estado arrancó la rehabilitación del Jardín Colón en Pachuca con una inversión superior a los 5.3 millones de pesos a través de SIPDUS, contemplando pisos, iluminación y áreas verdes.</t>
-  </si>
-  <si>
-    <t>Rehabilitación de espacios públicos</t>
-  </si>
-  <si>
-    <t>Arrancaron los trabajos de rehabilitación integral del Jardín Colón en Pachuca con una inversión estatal de 5.3 millones de pesos.</t>
-  </si>
-  <si>
-    <t>Fernanda Huerta</t>
-  </si>
-  <si>
-    <t>Supervisará Protección Civil puestos semifijos</t>
-  </si>
-  <si>
-    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos de Hidalgo supervisará 120 puestos de comerciantes y artesanos en la plaza Aniceto Ortega y el atrio de la Parroquia de San Francisco para la Feria Tradicional.</t>
-  </si>
-  <si>
-    <t>Protección Civil estatal inspeccionará 120 puestos semifijos de comerciantes y artesanos instalados por la Feria San Francisco Pachuca.</t>
-  </si>
-  <si>
-    <t>Segobh, Protección Civil</t>
-  </si>
-  <si>
-    <t>Fortalecen alianzas en reunión NODESS</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar inauguró en la UPMH de Tolcayuca el Encuentro Nacional NODESS 2026, reuniendo a productores, cooperativas y emprendedores para impulsar la economía social y solidaria.</t>
-  </si>
-  <si>
-    <t>Tolcayuca</t>
-  </si>
-  <si>
-    <t>Economía social</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca encabezó la inauguración del Encuentro Nacional NODESS 2026 para fortalecer proyectos productivos e impulsar el desarrollo económico regional.</t>
-  </si>
-  <si>
-    <t>Gobierno, Sedeco, UPMH, INAES</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Carlos Henkel Escorza, Catalina Monreal Pérez</t>
-  </si>
-  <si>
-    <t>Descarta Julio Menchaca una nueva alza a tarifa de taxis</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca descartó autorizar un nuevo incremento a la tarifa de taxis en Hidalgo tras peticiones de concesionarios, señalando que la tarifa ajustada recientemente a 45 pesos busca proteger la economía de las familias.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca descartó incrementar nuevamente la tarifa mínima de taxis en Pachuca y la zona metropolitana.</t>
-  </si>
-  <si>
-    <t>Gobernador</t>
-  </si>
-  <si>
-    <t>Gobernador, Semot</t>
-  </si>
-  <si>
-    <t>Continúan los cobros excesivos de taxistas</t>
-  </si>
-  <si>
-    <t>A una semana de la entrada en vigor del nuevo tarifario, usuarios de la zona metropolitana de Pachuca denunciaron que la mayoría de conductores de taxi ignoran las tarifas oficiales e imponen cobros de hasta 150 pesos hacia la Feria.</t>
-  </si>
-  <si>
-    <t>Abusos taxistas</t>
-  </si>
-  <si>
-    <t>Usuarios de transporte en Pachuca acusaron que taxistas continúan aplicando cobros arbitrarios por encima del tarifario autorizado por la Semot.</t>
-  </si>
-  <si>
-    <t>Claudia Ángeles</t>
-  </si>
-  <si>
-    <t>El Maye resguarda más de 50 biznagas</t>
-  </si>
-  <si>
-    <t>El comisariado ejidal de El Maye en Ixmiquilpan informó que en el cerro de la localidad habitan más de 50 biznagas protegidas, destacando un ejemplar gigante que supera los dos metros de altura.</t>
-  </si>
-  <si>
-    <t>Ejidatarios de El Maye en Ixmiquilpan resguardan un núcleo natural con más de 50 biznagas gigantes protegidas contra la extracción ilegal.</t>
-  </si>
-  <si>
-    <t>Omar Santiago</t>
-  </si>
-  <si>
-    <t>Alfonso Rodríguez</t>
-  </si>
-  <si>
-    <t>El Yathé podría dar dos cosechas al año</t>
-  </si>
-  <si>
-    <t>Representantes agrícolas informaron que la presa El Yathé en Alfajayucan, con capacidad para almacenar 44.3 millones de m3 de agua, permitirá beneficiar a 4 mil hectáreas de riego y garantizar hasta dos cosechas anuales.</t>
-  </si>
-  <si>
-    <t>Alfajayucan</t>
-  </si>
-  <si>
-    <t>Presa Yathé</t>
-  </si>
-  <si>
-    <t>La puesta en operación del canal de interconexión en la presa El Yathé diversificará la producción agrícola en la región del Valle del Mezquital.</t>
-  </si>
-  <si>
-    <t>Saderh, Conagua</t>
-  </si>
-  <si>
-    <t>Antonio Nava</t>
-  </si>
-  <si>
-    <t>La caída del puente-vado afecta la economía familiar</t>
-  </si>
-  <si>
-    <t>El colapso del puente-vado del río Calabozo en Huautla dejó incomunicadas a 18 comunidades por quinta ocasión, obligando a los pobladores a pagar fletes de hasta 600 pesos para trasladar alimentos y productos.</t>
-  </si>
-  <si>
-    <t>Huautla</t>
-  </si>
-  <si>
-    <t>Colapso de puente</t>
-  </si>
-  <si>
-    <t>Habitantes de 18 localidades de Huautla enfrentan afectaciones económicas tras el colapso del puente-vado sobre el río Calabozo.</t>
-  </si>
-  <si>
-    <t>Regional</t>
-  </si>
-  <si>
-    <t>Sipdus, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Hidalgo analizará creación de policía metropolitana</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar informó que durante la séptima Reunión de Coordinación Interestatal de Paz y Seguridad se planteó la necesidad de crear una policía metropolitana para atender la seguridad en áreas limítrofes.</t>
-  </si>
-  <si>
-    <t>Durante la Reunión de Coordinación Interestatal se propuso la creación de una policía metropolitana coordinada con la Guardia Nacional y policías estatales.</t>
-  </si>
-  <si>
-    <t>Adela Garmez</t>
-  </si>
-  <si>
-    <t>Gobierno, SSPH, Segobh</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Clara Brugada</t>
-  </si>
-  <si>
-    <t>Descarta atender petición de taxistas</t>
-  </si>
-  <si>
-    <t>Julio Menchaca descartó que la Secretaría de Movilidad y Transporte atienda la petición de taxistas que solicitaron fijar en 50 pesos la tarifa mínima en Pachuca.</t>
-  </si>
-  <si>
-    <t>El gobernador descartó autorizar el aumento a 50 pesos en la tarifa mínima de taxis solicitada por un grupo de conductores en Pachuca.</t>
-  </si>
-  <si>
-    <t>Interiores</t>
-  </si>
-  <si>
-    <t>Semot, Gobernador</t>
-  </si>
-  <si>
-    <t>IHE realiza congreso estatal Juntos por la Convivencia Escolar</t>
-  </si>
-  <si>
-    <t>El Instituto Hidalguense de Educación organizó un espacio de diálogo y formación con especialistas para promover entornos escolares seguros y prevenir la violencia.</t>
-  </si>
-  <si>
-    <t>Comunidades educativas y especialistas abordaron estrategias para construir ambientes seguros, inclusivos y respetuosos en las escuelas hidalguenses.</t>
-  </si>
-  <si>
-    <t>SEPH, CDHEH, PGJEH, Sipinna</t>
-  </si>
-  <si>
-    <t>Margarita Maricarmen Mandujano Cerrilla, Martín Pérez Sierra</t>
-  </si>
-  <si>
-    <t>Unos 50 regidores y funcionarios reintegran dinero por doble pago</t>
-  </si>
-  <si>
-    <t>El contralor estatal Álvaro Bardales informó que cerca de 50 servidores públicos ya devolvieron recursos tras detectarse nombramientos con doble sueldo.</t>
-  </si>
-  <si>
-    <t>Reintegración de recursos</t>
-  </si>
-  <si>
-    <t>Contraloría del Estado reportó avances en la regularización de casi mil funcionarios detectados con percepciones dobles en ayuntamientos y dependencias.</t>
-  </si>
-  <si>
-    <t>Socorro Ávila</t>
-  </si>
-  <si>
-    <t>Contraloría, SEPH, SSH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Álvaro Bardales Ramírez</t>
-  </si>
-  <si>
-    <t>Celebran encuentro nacional para impulsar la economía social</t>
-  </si>
-  <si>
-    <t>En la UPMH se realizó el Encuentro Nacional de Nodess para promover esquemas productivos sustentables e integradores en Hidalgo y el país.</t>
-  </si>
-  <si>
-    <t>Zapotlán</t>
-  </si>
-  <si>
-    <t>Hidalgo destaca a nivel nacional con 20 Nodos de Impulso a la Economía Social instalados en 28 municipios para acompañar a productores locales.</t>
-  </si>
-  <si>
-    <t>Sedeco</t>
-  </si>
-  <si>
-    <t>Sedeco, SEPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Carlos Henkel Escorza, Catalina Monreal Pérez</t>
-  </si>
-  <si>
-    <t>Sebiso sumará a cerca de 11 mil beneficiarios a programas sociales</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno informó que 11 mil personas se incorporarán a padrones de la Sebiso, priorizando municipios vulnerables y apoyo artesanal.</t>
-  </si>
-  <si>
-    <t>Programas Del Bienestar</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar ampliará la cobertura de apoyos sociales en Hidalgo sin requerir ampliación presupuestal extraordinaria.</t>
-  </si>
-  <si>
-    <t>IHE y Casio México evalúan uso de tecnología para fortalecer enseñanza de las matemáticas</t>
-  </si>
-  <si>
-    <t>IHE y Casio México analizaron los alcances del Proyecto Piloto CASIO Educación México en secundarias generales para optimizar tiempos de aprendizaje.</t>
-  </si>
-  <si>
-    <t>Innovación tecnológica</t>
-  </si>
-  <si>
-    <t>Evaluación del programa piloto tecnológico implementado por el IHE e iniciativa privada para la enseñanza didáctica de matemáticas en escuelas públicas.</t>
-  </si>
-  <si>
-    <t>Celebrarán en California quinta edición del Festival de la Barbacoa y el Ximbó</t>
-  </si>
-  <si>
-    <t>Migrantes hidalguenses organizan el Festival del Ximbó y la Barbacoa en Santa Rosa, California, promoviendo la gastronomía estatal con apoyo de Sebiso.</t>
-  </si>
-  <si>
-    <t>Atención A Migrantes</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo apoyará con 100 mil pesos y acompañamiento la realización del festival gastronómico hidalguense en Estados Unidos.</t>
-  </si>
-  <si>
-    <t>Presentan acervos históricos en los Diálogos del Patrimonio</t>
-  </si>
-  <si>
-    <t>Documentos desde 1553 hasta la época moderna forman parte del patrimonio documental resguardado por los poderes del estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>Patrimonio cultural</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura expuso los avances en digitalización y conservación de los acervos históricos de los poderes Ejecutivo, Legislativo y Judicial.</t>
-  </si>
-  <si>
-    <t>Cultura, TSJEH, Congreso</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, Luis Francisco Sánchez Fonseca, José Vergara Vergara</t>
-  </si>
-  <si>
-    <t>IHE fortalece Educación Inicial con Cada momento cuenta</t>
-  </si>
-  <si>
-    <t>El IHE reunió a personal docente y autoridades en el encuentro 'Cada momento cuenta' para consolidar estrategias de atención integral a la primera infancia.</t>
-  </si>
-  <si>
-    <t>Educación inicial</t>
-  </si>
-  <si>
-    <t>Jornada de capacitación para fortalecer vínculos afectivos y la atención centrada en el desarrollo infantil organizada por el IHE.</t>
-  </si>
-  <si>
-    <t>Nancy León Vite</t>
-  </si>
-  <si>
-    <t>Prevén 19.2 mdp para restaurar tres estaciones de ferrocarril</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura destinará 19.2 mdp para la restauración de estaciones ferroviarias en Cuautepec, Santiago Tulantepec y Tula para convertirlas en centros culturales.</t>
-  </si>
-  <si>
-    <t>Cuautepec</t>
-  </si>
-  <si>
-    <t>Estaciones ferroviarias</t>
-  </si>
-  <si>
-    <t>Proyectos aprobados por el INAH permitirán la rehabilitación de tres antiguas estaciones de tren en Hidalgo para su rescate y difusión artística.</t>
-  </si>
-  <si>
-    <t>Cultura, Semarnath, Presidencia</t>
-  </si>
-  <si>
-    <t>La entidad registra 24 casos de miasis humana</t>
-  </si>
-  <si>
-    <t>Reporte de Vigilancia Epidemiológica confirma 24 contagios acumulados de gusano barrenador en Hidalgo, manteniendo protocolos de supervisión activa.</t>
-  </si>
-  <si>
-    <t>Gusano barrenador</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud reportó la presencia de 24 casos de miasis humana por Cochliomyia hominivorax en territorio estatal.</t>
-  </si>
-  <si>
-    <t>Nathali González</t>
-  </si>
-  <si>
-    <t>SSH, Presidencia</t>
-  </si>
-  <si>
-    <t>Tiene Hidalgo alto nivel de calidad en reporte financiero</t>
-  </si>
-  <si>
-    <t>La SHCP ubicó a Hidalgo en el tercer lugar nacional con 98.71 puntos en el Índice de Calidad de la Información sobre el destino y ejercicio de recursos federales transferidos en el segundo trimestre de 2026.</t>
-  </si>
-  <si>
-    <t>Recursos federales</t>
-  </si>
-  <si>
-    <t>La Secretaría de Hacienda y Crédito Público ubicó a Hidalgo en el tercer lugar nacional por su cumplimiento de 98.71 puntos en el Índice de Calidad de la Información de recursos federales.</t>
-  </si>
-  <si>
-    <t>Hacienda</t>
-  </si>
-  <si>
-    <t>Ven en empresas sociales clave contra la migración</t>
-  </si>
-  <si>
-    <t>Para evitar la migración y arraigar a las personas con un modo de vida digno, el INAES y la Secretaría de Economía de Hidalgo apoyan a cooperativas y empresas sociales con equipamiento de hasta 200 mil pesos.</t>
-  </si>
-  <si>
-    <t>El INAES y la Secretaría de Economía destacaron que más de 400 Nodess y apoyos a cooperativas en Tolcayuca ayudan a arraigar la población e inhibir la migración.</t>
-  </si>
-  <si>
-    <t>Miriam Avilés</t>
-  </si>
-  <si>
-    <t>Sedeco, Presidencia</t>
-  </si>
-  <si>
-    <t>Catalina Monreal, Carlos Henkel</t>
-  </si>
-  <si>
-    <t>Destaca Tello apertura comercial y atracción de inversión al estado</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Tello Vargas, titular de la Uplaph, destacó que la incorporación de la región Tula a la ZMVM representa una gran oportunidad comercial y de atracción de inversiones sin generar conflicto ambiental.</t>
-  </si>
-  <si>
-    <t>Tula</t>
-  </si>
-  <si>
-    <t>Atracción De Inversiones</t>
-  </si>
-  <si>
-    <t>El titular de la Uplaph resaltó la oportunidad que representa incorporar a Tula a la Zona Metropolitana del Valle de México para acelerar la atracción de inversiones.</t>
-  </si>
-  <si>
-    <t>Planeación, Pemex, CFE</t>
-  </si>
-  <si>
-    <t>Adecuan lineamientos en educación media superior por pantallas</t>
-  </si>
-  <si>
-    <t>Daniel Fragoso Torres, subsecretario de Educación Media Superior y Superior, informó sobre las adecuaciones normativas en las escuelas de Hidalgo para aplicar los lineamientos federales sobre uso responsable de celulares en aulas.</t>
-  </si>
-  <si>
-    <t>Regulación de dispositivos digitales</t>
-  </si>
-  <si>
-    <t>La SEPH realiza adecuaciones para cumplir con la disposición federal que regula el uso de pantallas y teléfonos inteligentes durante clases en educación básica y media superior.</t>
-  </si>
-  <si>
-    <t>SEPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Daniel Fragoso Torres</t>
-  </si>
-  <si>
-    <t>Estudian crear corporación metropolitana</t>
-  </si>
-  <si>
-    <t>Hidalgo y entidades del centro del país analizan la creación de una Policía Metropolitana y un C5 Metropolitano para reforzar la seguridad en zonas limítrofes.</t>
-  </si>
-  <si>
-    <t>Metropolitana</t>
-  </si>
-  <si>
-    <t>Gobernadores de la zona centro acordaron analizar en un próximo encuentro la propuesta para homologar operaciones de seguridad en áreas confluentes.</t>
-  </si>
-  <si>
-    <t>Gobierno, Guardia Nacional</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Clara Brugada Molina</t>
-  </si>
-  <si>
-    <t>Rechazan modificación a las tarifas de los taxis</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca descartó ajustar la tarifa de 45 pesos para los primeros 4 km del servicio de taxi en Pachuca, señalando que representa un equilibrio económico.</t>
-  </si>
-  <si>
-    <t>El Ejecutivo estatal reiteró que la tarifa publicada en el POEH para los taxis busca proteger el bolsillo de las familias sin perjudicar al gremio.</t>
-  </si>
-  <si>
-    <t>Semot, OEEH</t>
-  </si>
-  <si>
-    <t>Están en revisión 100 casos de plazas dobles</t>
-  </si>
-  <si>
-    <t>La Secretaría de Contraloría mantiene abiertos entre 90 y 100 expedientes de funcionarios que percibían dobles salarios en dependencias educativas, de salud y alcaldías.</t>
-  </si>
-  <si>
-    <t>Doble Plaza</t>
-  </si>
-  <si>
-    <t>El contralor Álvaro Bardales informó que 900 de mil casos identificados de pagos dobles ya concluyeron con licencias, renuncias o devoluciones de dinero.</t>
-  </si>
-  <si>
-    <t>Contraloría, SEPH, SSH</t>
-  </si>
-  <si>
-    <t>Hidalgo, en el top 3 de calidad de la información financiera</t>
-  </si>
-  <si>
-    <t>La SHCP reconoció a Hidalgo con 98.71 puntos entre los tres estados con mejor nivel de reporte en el Índice de Calidad de la Información del SRFT.</t>
-  </si>
-  <si>
-    <t>Hidalgo superó por casi 15 puntos la media nacional de transparencia en la rendición de cuentas de aportaciones y convenios federales.</t>
-  </si>
-  <si>
-    <t>Hacienda, Presidencia</t>
-  </si>
-  <si>
-    <t>Policía estatal detuvo a dos por presunto narcomenudeo</t>
-  </si>
-  <si>
-    <t>La SSPH aprehendió a dos personas en operativos realizados en Tlahuelilpan y San Bartolo Tutotepec con dosis de marihuana y cristal.</t>
-  </si>
-  <si>
-    <t>Tlahuelilpan</t>
-  </si>
-  <si>
-    <t>Agentes estatales decomisaron más de 600 dosis de presuntos estupefacientes y detuvieron a dos implicados que fueron puestos a disposición del MP.</t>
-  </si>
-  <si>
-    <t>Evacúan a estudiantes del CEB de Juan C. Doria por un arma de fuego</t>
-  </si>
-  <si>
-    <t>Alrededor de 500 alumnos fueron desalojados de sus aulas en Pachuca luego de que una estudiante reportara que un compañero traía un arma.</t>
-  </si>
-  <si>
-    <t>Alumno Armado</t>
-  </si>
-  <si>
-    <t>Autoridades escolares y policías aplicaron el protocolo preventivo evacuando 18 aulas del CEB 5/4 tras una alerta por arma de fuego.</t>
-  </si>
-  <si>
-    <t>SEPH, SSPH</t>
-  </si>
-  <si>
-    <t>Otra vez, derrumbe de vado deja incomunicadas a 18 localidades</t>
-  </si>
-  <si>
-    <t>Crecida del río Calabozo en Huautla destruyó el vado provisional entre Tamoyón I y II, dejando sin paso vehicular a 18 comunidades de la zona.</t>
-  </si>
-  <si>
-    <t>Precipitaciones causaron por quinta ocasión la caída del vado en el río Calabozo, suspendiéndose cruces y paso de embarcaciones por seguridad.</t>
-  </si>
-  <si>
-    <t>Francisco Bautista</t>
-  </si>
-  <si>
-    <t>Hay dos denuncias por desaparición de restos</t>
-  </si>
-  <si>
-    <t>La PGJEH integra dos carpetas de investigación tras la sustracción de restos humanos reportada en el panteón municipal San Miguel de Tulancingo.</t>
-  </si>
-  <si>
-    <t>Localización De Restos</t>
-  </si>
-  <si>
-    <t>El ayuntamiento de Tulancingo promovió una investigación formal en conjunto con familiares para esclarecer la profanación en el camposanto.</t>
-  </si>
-  <si>
-    <t>Mirely Santos</t>
-  </si>
-  <si>
-    <t>Alberto Santuario</t>
-  </si>
-  <si>
-    <t>Hidalgo destaca a nivel nacional en calidad de la información financiera</t>
-  </si>
-  <si>
-    <t>La Secretaría de Hacienda y Crédito Público (SHCP) reconoció al estado de Hidalgo por el nivel alcanzado en materia de calidad de la información reportada mediante el Sistema de Recursos Federales Transferidos (SRFT). Hidalgo se ubicó entre las tres entidades con mayor puntuación a nivel nacional en el Índice de Calidad de la Información (ICI), con 98.71 puntos, superando por 14.96 puntos la media nacional.</t>
-  </si>
-  <si>
-    <t>La SHCP reconoció a Hidalgo por ubicarse en el top 3 nacional del Índice de Calidad de la Información financiera con 98.71 puntos.</t>
-  </si>
-  <si>
-    <t>Hacienda, SHCP</t>
-  </si>
-  <si>
-    <t>Proponen crear una Policía Metropolitana entre Hidalgo y estados vecinos</t>
-  </si>
-  <si>
-    <t>Durante la Séptima Reunión Interestatal de Coordinación por la Paz y Seguridad, la jefa de Gobierno de la Ciudad de México propuso crear una Policía Metropolitana entre Hidalgo y estados limítrofes para fortalecer la seguridad en zonas fronterizas. En el encuentro, el gobernador Julio Menchaca destacó la inhabilitación de 19 túneles y el aseguramiento de más de 7 millones de litros de huachicol.</t>
-  </si>
-  <si>
-    <t>En la reunión interestatal de seguridad se propuso crear una Policía Metropolitana entre Hidalgo y estados vecinos; Menchaca resaltó el decomiso de 7 millones de litros de huachicol.</t>
-  </si>
-  <si>
-    <t>Gobierno, Gabinete de Seguridad, Guardia Nacional, SSPH</t>
-  </si>
-  <si>
-    <t>De mil casos de trabajadores con doble ingreso, cerca de 100 continúan bajo revisión</t>
-  </si>
-  <si>
-    <t>El secretario de la Contraloría, Álvaro Bardales Ramírez, informó que cerca de 100 de casi mil casos de servidores públicos que cobraban doble sueldo estatal y municipal siguen bajo investigación. Señaló que más de 900 personas tramitaron licencia a tiempo y alrededor de 50 reembolsaron el dinero cobrado indebidamente.</t>
-  </si>
-  <si>
-    <t>La Contraloría de Hidalgo mantiene bajo revisión 100 expedientes de trabajadores con doble remuneración pública, mientras 50 personas reembolsaron el dinero.</t>
-  </si>
-  <si>
-    <t>Menchaca descarta ajuste la tarifa de taxis ante petición de incremento</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar rechazó la petición de taxistas independientes de incrementar la tarifa de 45 a 50 o 55 pesos, ratificando que el ajuste acordado de 45 pesos es equilibrado y no afectará la economía de la ciudadanía.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca descartó incrementar la tarifa de taxis a 50 pesos como solicitaban conductores independientes, sosteniendo la tarifa autorizada de 45 pesos.</t>
-  </si>
-  <si>
-    <t>Gobernador, Semot, STCH</t>
-  </si>
-  <si>
-    <t>Logra Hidalgo alto nivel en información financiera</t>
-  </si>
-  <si>
-    <t>La Secretaría de Hacienda y Crédito Público (SHCP) reconoció al estado de Hidalgo al obtener 98.71 puntos en el Índice de Calidad de la Información (ICI), ubicándose entre los tres primeros lugares a nivel nacional junto con Nuevo León y Querétaro.</t>
-  </si>
-  <si>
-    <t>La SHCP posicionó a Hidalgo en el tercer lugar nacional en transparencia y calidad de reporte de recursos federales transferidos.</t>
-  </si>
-  <si>
-    <t>SHCP, Gobierno</t>
-  </si>
-  <si>
-    <t>Descarta Julio Menchaca nuevo aumento a tarifa de taxis</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar descartó abrir una nueva mesa de negociación tras fijarse la tarifa mínima en 45 pesos, señalando que la medida busca un equilibrio económico.</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo rechazó la solicitud de choferes independientes de subir a 50 pesos el pasaje mínimo de taxi.</t>
-  </si>
-  <si>
-    <t>Oscar Raúl Pérez</t>
-  </si>
-  <si>
-    <t>Celebrarán festival Internacional de la Barbacoa y el Ximbo</t>
-  </si>
-  <si>
-    <t>La quinta edición del Festival Internacional de la Barbacoa y el Ximbo se realizará el 11 de octubre en Santa Rosa, California, con apoyo de Sebiso.</t>
-  </si>
-  <si>
-    <t>Migrantes hidalguenses en California realizarán la quinta edición del festival gastronómico con un respaldo de 100 mil pesos de Sebiso.</t>
-  </si>
-  <si>
-    <t>Sebiso</t>
-  </si>
-  <si>
-    <t>Nelly Tello</t>
-  </si>
-  <si>
-    <t>Reportan 29 donaciones de órganos en la entidad, 10 fueron multiorgánicas</t>
-  </si>
-  <si>
-    <t>El Ceetra informó que en lo que va de 2026 se han concretado 29 donaciones de órganos en Hidalgo, permitiendo obtener 66 órganos y tejidos con apoyo de traslados aéreos.</t>
-  </si>
-  <si>
-    <t>Donación De Órganos</t>
-  </si>
-  <si>
-    <t>En el marco del Día Mundial del Corazón, la SSH y el Ceetra destacaron la procuración de un corazón y dos riñones en el Hospital 36 del IMSS Pachuca.</t>
-  </si>
-  <si>
-    <t>Ceetra, IMSS, SSH</t>
-  </si>
-  <si>
-    <t>Carlos Ávila Zúñiga, Vanesa Escalante Arroyo</t>
-  </si>
-  <si>
-    <t>Tras deslaves, agentes de policía estatal liberan carretera de Tlanchinol</t>
-  </si>
-  <si>
-    <t>Cuadrillas de la SSPH y personal municipal removieron escombros de deslaves provocados por lluvias en la vía federal México-Tampico para restablecer el paso.</t>
-  </si>
-  <si>
-    <t>Deslaves por lluvias</t>
-  </si>
-  <si>
-    <t>Policías estatales y cuadrillas de Obras Públicas desbloquearon tres tramos afectados por derrumbes en la carretera a Tlanchinol.</t>
-  </si>
-  <si>
-    <t>SSPH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Evitan que más de 700 dosis de drogas llegaran a las calles</t>
-  </si>
-  <si>
-    <t>Elementos de la SSPH detuvieron a una mujer en Tlahuelilpan con 609 dosis de enervantes y a un hombre en San Bartolo Tutotepec con 128 dosis y báscula.</t>
-  </si>
-  <si>
-    <t>Patrullajes de la Policía Estatal en Tlahuelilpan y San Bartolo Tutotepec derivaron en el aseguramiento de dos narcomenudistas y más de 700 dosis de marihuana y cristal.</t>
-  </si>
-  <si>
-    <t>Hidalgo gana 12 medallas al cerrar el primer bloque de Paralimpiada Nacional 2026</t>
-  </si>
-  <si>
-    <t>La delegación hidalguense cosechó 3 oros, 5 platas y 4 bronces en natación adaptada y boccia durante la competencia nacional de la Conade.</t>
-  </si>
-  <si>
-    <t>Paranacionales Conade</t>
-  </si>
-  <si>
-    <t>Paratletas de Hidalgo destacaron en la Paralimpiada Nacional CONADE 2026 con 12 preseas en pruebas de para natación y boccia.</t>
-  </si>
-  <si>
-    <t>Inhide, Conade</t>
-  </si>
-  <si>
-    <t>Melani Yamileth Ávila Trujillo, Luis Antonio Cano Torres, Cristian Yahel Solís Rangel, Ethan Leonardo Miranda Rubio</t>
-  </si>
-  <si>
-    <t>Menchaca apaga taxímetro; banderazo se queda en $45</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar descartó un nuevo aumento a la tarifa de taxis, por lo que el cobro mínimo de 45 pesos se mantendrá para los primeros kilómetros en la zona metropolitana de Pachuca. Ante la propuesta de operadores independientes para elevar el mínimo a 50 pesos, el mandatario señaló que no habrá una segunda modificación y sostuvo que el ajuste de 38 a 45 pesos fue acordado con la Semoth.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca rechazó la solicitud de un grupo independiente de taxistas para subir la tarifa mínima a 50 pesos, ratificando que el cobro se mantendrá en 45 pesos.</t>
-  </si>
-  <si>
-    <t>Entrega Estado buenas cuentas a la Federación</t>
-  </si>
-  <si>
-    <t>Hidalgo se ubicó entre los tres primeros lugares del país en el Índice de Calidad de la Información (ICI), correspondiente al segundo trimestre de 2026, con 98.71 puntos, informó la Secretaría de Hacienda y Crédito Público (SHCP). El indicador evalúa la información reportada por las 32 entidades sobre aportaciones federales, subsidios y convenios.</t>
-  </si>
-  <si>
-    <t>Hidalgo obtuvo una calificación de 98.71 puntos en el Índice de Calidad de la Información de la SHCP, colocándose entre las tres entidades mejor evaluadas del país en transparencia financiera.</t>
-  </si>
-  <si>
-    <t>Ponen tras las rejas a 65 huachicoleros</t>
-  </si>
-  <si>
-    <t>En Hidalgo se han inhabilitado 19 túneles para extraer hidrocarburo durante la actual administración, informó el gobernador Julio Menchaca Salazar. Añadió que 65 personas han sido detenidas por delitos relacionados con el robo de combustible; de ellas, 40 son identificadas como generadoras de violencia y objetivos prioritarios del gobierno federal.</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo reportó la clausura de 19 huachitúneles y la detención de 65 personas ligadas al robo de hidrocarburos, de las cuales 40 eran consideradas objetivos prioritarios.</t>
-  </si>
-  <si>
-    <t>Gabinete de Seguridad, Sedena, GN, FGR</t>
-  </si>
-  <si>
-    <t>Sin rastro de 72 en Valle de Tulancingo</t>
-  </si>
-  <si>
-    <t>Durante 2026, en el Valle de Tulancingo se han activado 72 fichas de búsqueda de personas desaparecidas, de acuerdo con registros de la PGJEH, la Comisión de Búsqueda y Alerta Amber. Tulancingo de Bravo concentra 56 fichas (31 hombres y 25 mujeres), Cuautepec 7, Santiago Tulantepec 4, Acaxochitlán 4 y Acatlán 1.</t>
-  </si>
-  <si>
-    <t>Autoridades estatales registran 72 fichas de búsqueda activadas en el Valle de Tulancingo en lo que va del año, donde predomina la incidencia en Tulancingo de Bravo con 56 personas no localizadas.</t>
-  </si>
-  <si>
-    <t>Karen Aicitel Lira</t>
-  </si>
-  <si>
-    <t>PGJEH, CBPEH</t>
-  </si>
-  <si>
-    <t>Paloma Hernández Vázquez, Iván Ramírez León</t>
-  </si>
-  <si>
-    <t>La escuela primaria Aquiles Serdán, de Tulancingo, presenta daños estructurales, por lo cual será demolida y reconstruida totalmente durante el ciclo escolar 2026-2027, informó el titular de la SEPH, Natividad Castrejón. Se buscan alternativas presenciales o en línea mientras se llevan a cabo las obras.</t>
-  </si>
-  <si>
-    <t>La SEPH demolerá y volverá a edificar la primaria Aquiles Serdán en Tulancingo tras detectar fallas estructurales, gestionando espacios temporales para impartir clases al alumnado.</t>
-  </si>
-  <si>
-    <t>Sigue revisión a 90 de casi mil funcionarios "dobleteros"</t>
-  </si>
-  <si>
-    <t>La Secretaría de Contraloría de Hidalgo redujo a 90 los casos pendientes en la revisión de servidores públicos que recibían doble sueldo al trabajar simultáneamente en dependencias estatales y ayuntamientos.</t>
-  </si>
-  <si>
-    <t>Contraloría estatal informó que de un padrón inicial de mil trabajadores con doble remuneración, unos 50 ya reembolsaron recursos y solo restan 90 en revisión.</t>
-  </si>
-  <si>
-    <t>Luis Godínez</t>
-  </si>
-  <si>
-    <t>Descartan ajustes a la tarifa de los taxis</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar descartó un incremento a la tarifa de taxis de 45 pesos en Pachuca, señalando que la tarifa acordada es equilibrada para no afectar a la ciudadanía.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca confirmó que el banderazo de salida para taxis se mantendrá en 45 pesos pese a solicitudes de transportistas para elevarlo a 50 o 55 pesos.</t>
-  </si>
-  <si>
-    <t>Reforzarán seguridad en la Feria de Pachuca tras derribo de vallas</t>
-  </si>
-  <si>
-    <t>Tras el derribo de vallas e ingreso masivo durante las presentaciones musicales en la Feria de San Francisco, el gobernador Julio Menchaca anunció el reforzamiento de medidas de seguridad.</t>
-  </si>
-  <si>
-    <t>Autoridades estatales reforzarán la seguridad y control de acceso en el recinto ferial de Pachuca para prevenir aglomeraciones de riesgo.</t>
-  </si>
-  <si>
-    <t>Turismo, SSPH, Protección Civil</t>
-  </si>
-  <si>
-    <t>Crecimiento de huachicoleo, por complicidad de autoridades: JMS</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar afirmó que el crecimiento del robo de combustible en administraciones pasadas contó con la complicidad de autoridades locales y federales, destacando la inhabilitación de 19 túneles en su gobierno.</t>
-  </si>
-  <si>
-    <t>El ejecutivo estatal informó sobre la detención de 65 personas y la clausura de 19 túneles huachicoleros durante la actual administración.</t>
-  </si>
-  <si>
-    <t>Gobernador, Gabinete de Seguridad</t>
-  </si>
-  <si>
-    <t>Adultos mayores hidalguenses se reúnen con sus familiares en EU</t>
-  </si>
-  <si>
-    <t>La Dirección General de Atención al Migrante de Hidalgo gestionó cerca de 250 visas para que adultos mayores puedan reencontrarse con sus familias en Estados Unidos.</t>
-  </si>
-  <si>
-    <t>El programa Raíces de Hidalgo concretó 250 trámites de visa en lo que va del año para reunificación familiar de adultos mayores en el extranjero.</t>
-  </si>
-  <si>
-    <t>Manuel Aranda Montero</t>
-  </si>
-  <si>
-    <t>Celebrarán el quinto Festival Internacional de Barbacoa y Ximbó</t>
-  </si>
-  <si>
-    <t>Hidalguenses en el extranjero organizarán la quinta edición del Festival Internacional de Barbacoa y Ximbó en California para promocionar la gastronomía del estado.</t>
-  </si>
-  <si>
-    <t>Festival Gastronómico</t>
-  </si>
-  <si>
-    <t>Migrantes hidalguenses realizarán en Estados Unidos el Quinto Festival Internacional de Barbacoa y Ximbó con la participación de cocineros tradicionales.</t>
-  </si>
-  <si>
-    <t>Turismo, Bienestar</t>
-  </si>
-  <si>
-    <t>Accidentes viales dejan en tan solo dos meses 12 muertos y 14 lesionados</t>
-  </si>
-  <si>
-    <t>Un recuento de Criterio reveló que en los últimos dos meses se han registrado 12 víctimas mortales por accidentes de tránsito en Hidalgo, la mitad motociclistas.</t>
-  </si>
-  <si>
-    <t>Accidente Vial</t>
-  </si>
-  <si>
-    <t>Los percances automovilísticos y de motocicletas en Pachuca, Tepeji y Tula dejaron un saldo trágico de 12 decesos en un periodo de sesenta días.</t>
-  </si>
-  <si>
-    <t>Región Tula concentra 19 proyectos federales</t>
-  </si>
-  <si>
-    <t>El titular de la Unidad de Planeación, Miguel Tello Vargas, destacó que la zona de Tula concentra 19 obras estratégicas como Viviendas para el Bienestar y el Tren México-Querétaro.</t>
-  </si>
-  <si>
-    <t>Proyectos Federales</t>
-  </si>
-  <si>
-    <t>Planeación estatal instó a municipios de la región Tula a preparar infraestructura turística y servicios para aprovechar los desarrollos federales en marcha.</t>
-  </si>
-  <si>
-    <t>Abigail García Torres</t>
-  </si>
-  <si>
-    <t>Planeación, Presidencia</t>
-  </si>
-  <si>
-    <t>Hidalgo responde en la Paralimpiada</t>
-  </si>
-  <si>
-    <t>La delegación hidalguense conquistó 12 medallas en el primer bloque de disciplinas de la Paralimpiada Nacional 2026 y continúa participación en la segunda etapa.</t>
-  </si>
-  <si>
-    <t>Atletas de Hidalgo lograron 12 preseas en pruebas de natación y atletismo adaptado durante los Paranacionales Conade 2026.</t>
-  </si>
-  <si>
-    <t>SEPH, Inhide</t>
+    <t>Prisco Manuel Gutiérrez</t>
   </si>
 </sst>
 </file>
@@ -1398,8 +1254,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ58" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ58" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ47" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ47" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1831,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1981,31 +1837,31 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F2" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -2020,16 +1876,16 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="AA2">
         <v>20</v>
@@ -2044,39 +1900,39 @@
         <v>44</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F3" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -2100,16 +1956,16 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA3">
         <v>12</v>
@@ -2118,52 +1974,54 @@
         <v>56</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD3" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ3" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F4" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G4">
         <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2178,16 +2036,16 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA4">
         <v>20</v>
@@ -2202,45 +2060,43 @@
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="AG4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="AJ4" s="2"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F5" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>49</v>
@@ -2258,16 +2114,16 @@
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Y5" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA5">
         <v>12</v>
@@ -2282,48 +2138,48 @@
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F6" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2338,72 +2194,72 @@
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Y6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F7" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G7">
         <v>8</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2418,72 +2274,70 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA7">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ7" s="2" t="s">
-        <v>145</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AJ7" s="2"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F8" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G8">
         <v>8</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2498,72 +2352,72 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA8">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD8" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F9" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G9">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2578,19 +2432,19 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="AA9">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>56</v>
@@ -2602,48 +2456,48 @@
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F10" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2658,19 +2512,19 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="AA10">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>56</v>
@@ -2682,48 +2536,48 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>163</v>
+        <v>83</v>
       </c>
       <c r="AG10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="F11" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2738,72 +2592,72 @@
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>106</v>
+        <v>161</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F12" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2818,19 +2672,19 @@
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AA12">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>56</v>
@@ -2842,45 +2696,45 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>175</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F13" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>49</v>
@@ -2898,19 +2752,19 @@
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AA13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>56</v>
@@ -2922,48 +2776,48 @@
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F14" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2978,19 +2832,19 @@
         <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AA14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB14" s="2" t="s">
         <v>56</v>
@@ -3002,48 +2856,48 @@
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>187</v>
+        <v>46</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F15" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -3058,19 +2912,19 @@
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>192</v>
+        <v>93</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AA15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>56</v>
@@ -3082,48 +2936,48 @@
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="AG15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F16" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G16">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3138,70 +2992,72 @@
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AA16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ16" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F17" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G17">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3216,70 +3072,72 @@
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="AA17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ17" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F18" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G18">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3294,72 +3152,72 @@
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="AA18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD18" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AJ18" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46297</v>
+      </c>
+      <c r="G19">
+        <v>14</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46295</v>
-      </c>
-      <c r="G19">
-        <v>22</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3374,54 +3232,54 @@
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>213</v>
@@ -3430,16 +3288,16 @@
         <v>214</v>
       </c>
       <c r="F20" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G20">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>215</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3454,19 +3312,19 @@
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="X20" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="X20" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="Y20" s="2" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="AA20">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>56</v>
@@ -3478,48 +3336,48 @@
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>71</v>
+        <v>217</v>
       </c>
       <c r="AG20" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AI20" s="2" t="s">
         <v>218</v>
       </c>
       <c r="AJ20" s="2" t="s">
-        <v>112</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F21" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G21">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3534,52 +3392,54 @@
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="AA21">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD21" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AJ21" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>225</v>
@@ -3588,16 +3448,16 @@
         <v>226</v>
       </c>
       <c r="F22" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3618,13 +3478,13 @@
         <v>228</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="AA22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB22" s="2" t="s">
         <v>56</v>
@@ -3636,43 +3496,43 @@
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="AG22" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AJ22" s="2"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F23" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>48</v>
@@ -3690,16 +3550,16 @@
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA23">
         <v>12</v>
@@ -3714,45 +3574,45 @@
         <v>44</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="AG23" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>187</v>
+        <v>94</v>
       </c>
       <c r="AI23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="AJ23" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="F24" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>238</v>
+        <v>45</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>48</v>
@@ -3770,19 +3630,19 @@
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>239</v>
+        <v>136</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="AA24">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB24" s="2" t="s">
         <v>56</v>
@@ -3794,39 +3654,39 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AG24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH24" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="AI24" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>96</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F25" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -3835,7 +3695,7 @@
         <v>45</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -3850,16 +3710,16 @@
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>244</v>
+        <v>179</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>57</v>
+        <v>229</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA25">
         <v>12</v>
@@ -3868,54 +3728,54 @@
         <v>56</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>233</v>
+        <v>41</v>
       </c>
       <c r="AG25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F26" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -3930,19 +3790,19 @@
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="AA26">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>56</v>
@@ -3954,48 +3814,46 @@
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="AJ26" s="2" t="s">
-        <v>253</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="AJ26" s="2"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F27" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -4010,16 +3868,16 @@
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>57</v>
+        <v>229</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA27">
         <v>12</v>
@@ -4034,54 +3892,52 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="AJ27" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AJ27" s="2"/>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F28" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R28">
         <v>1</v>
       </c>
       <c r="S28">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>58</v>
@@ -4090,16 +3946,16 @@
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>260</v>
+        <v>123</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="Y28" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="AA28">
         <v>20</v>
@@ -4114,39 +3970,37 @@
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="AG28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AJ28" s="2" t="s">
-        <v>182</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="AJ28" s="2"/>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="F29" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -4155,13 +4009,13 @@
         <v>59</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R29">
         <v>1</v>
       </c>
       <c r="S29">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T29" s="2" t="s">
         <v>58</v>
@@ -4170,16 +4024,16 @@
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>55</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA29">
         <v>20</v>
@@ -4194,52 +4048,54 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG29" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="AJ29" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F30" s="1">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G30">
         <v>6</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R30">
         <v>1</v>
       </c>
       <c r="S30">
-        <v>13262</v>
+        <v>12500</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>58</v>
@@ -4248,76 +4104,78 @@
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>87</v>
+        <v>264</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AA30">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AB30" s="2" t="s">
         <v>56</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD30" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AJ30" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="AJ30" s="2" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c 